--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3761,16 +3761,16 @@
         <v>102</v>
       </c>
       <c r="B3" s="1">
-        <v>1493</v>
+        <v>1498</v>
       </c>
       <c r="C3" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -4049,16 +4049,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>45201</v>
+        <v>45206</v>
       </c>
       <c r="CU3" s="1">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="CV3" s="1">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="CW3" s="1">
-        <v>1723</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4787,7 +4787,7 @@
         <v>265</v>
       </c>
       <c r="AM6" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AN6" s="2">
         <v>13</v>
@@ -4931,7 +4931,7 @@
         <v>1527</v>
       </c>
       <c r="CI6" s="2">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="CJ6" s="2">
         <v>60</v>
@@ -4967,7 +4967,7 @@
         <v>2193</v>
       </c>
       <c r="CU6" s="1">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="CV6" s="1">
         <v>76</v>
@@ -5615,16 +5615,16 @@
         <v>2</v>
       </c>
       <c r="J9" s="1">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K9" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M9" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N9" s="1">
         <v>1524</v>
@@ -5879,16 +5879,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2801</v>
+        <v>2805</v>
       </c>
       <c r="CU9" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="CV9" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CW9" s="1">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -15366,7 +15366,7 @@
         <v>44</v>
       </c>
       <c r="G41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="2">
         <v>2</v>
@@ -15462,7 +15462,7 @@
         <v>60</v>
       </c>
       <c r="AM41" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN41" s="2">
         <v>9</v>
@@ -15606,7 +15606,7 @@
         <v>485</v>
       </c>
       <c r="CI41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ41" s="2">
         <v>2</v>
@@ -15642,7 +15642,7 @@
         <v>623</v>
       </c>
       <c r="CU41" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CV41" s="1">
         <v>17</v>
@@ -18410,7 +18410,7 @@
         <v>15</v>
       </c>
       <c r="E51" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -18698,7 +18698,7 @@
         <v>116</v>
       </c>
       <c r="CW51" s="1">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -20865,16 +20865,16 @@
         <v>3</v>
       </c>
       <c r="J59" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" s="1">
         <v>313</v>
@@ -20961,16 +20961,16 @@
         <v>4</v>
       </c>
       <c r="AP59" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AQ59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR59" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS59" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT59" s="1">
         <v>0</v>
@@ -21105,16 +21105,16 @@
         <v>0</v>
       </c>
       <c r="CL59" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="CM59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN59" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO59" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CP59" s="1">
         <v>0</v>
@@ -21129,16 +21129,16 @@
         <v>0</v>
       </c>
       <c r="CT59" s="1">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="CU59" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CV59" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CW59" s="1">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -21451,16 +21451,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6251</v>
+        <v>6287</v>
       </c>
       <c r="C61" s="2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D61" s="2">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="E61" s="2">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21739,16 +21739,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65146</v>
+        <v>65182</v>
       </c>
       <c r="CU61" s="1">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="CV61" s="1">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="CW61" s="1">
-        <v>2318</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22070,7 +22070,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -22181,16 +22181,16 @@
         <v>0</v>
       </c>
       <c r="AP63" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AQ63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR63" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS63" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -22310,19 +22310,19 @@
         <v>0</v>
       </c>
       <c r="CG63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH63" s="1">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="CI63" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ63" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="CK63" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="CL63" s="1">
         <v>22</v>
@@ -22349,16 +22349,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2715</v>
+        <v>2727</v>
       </c>
       <c r="CU63" s="1">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="CV63" s="1">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="CW63" s="1">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22573,7 +22573,7 @@
         <v>21</v>
       </c>
       <c r="BS64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT64" s="2">
         <v>1</v>
@@ -22657,7 +22657,7 @@
         <v>7655</v>
       </c>
       <c r="CU64" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="CV64" s="1">
         <v>146</v>
@@ -28233,16 +28233,16 @@
         <v>0</v>
       </c>
       <c r="Z83" s="1">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AA83" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AB83" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC83" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AD83" s="1">
         <v>352726</v>
@@ -28449,16 +28449,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>422014</v>
+        <v>422010</v>
       </c>
       <c r="CU83" s="1">
-        <v>3532</v>
+        <v>3528</v>
       </c>
       <c r="CV83" s="1">
-        <v>3799</v>
+        <v>3795</v>
       </c>
       <c r="CW83" s="1">
-        <v>5121</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -32560,7 +32560,7 @@
         <v>3</v>
       </c>
       <c r="AS97" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT97" s="1">
         <v>0</v>
@@ -32692,7 +32692,7 @@
         <v>2</v>
       </c>
       <c r="CK97" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CL97" s="1">
         <v>33</v>
@@ -32728,7 +32728,7 @@
         <v>9</v>
       </c>
       <c r="CW97" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -33463,7 +33463,7 @@
         <v>6</v>
       </c>
       <c r="AO100" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AP100" s="1">
         <v>0</v>
@@ -33607,7 +33607,7 @@
         <v>3</v>
       </c>
       <c r="CK100" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CL100" s="1">
         <v>0</v>
@@ -33643,7 +33643,7 @@
         <v>13</v>
       </c>
       <c r="CW100" s="1">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33992,16 +33992,16 @@
         <v>221</v>
       </c>
       <c r="N102" s="1">
-        <v>14110</v>
+        <v>14109</v>
       </c>
       <c r="O102" s="2">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="P102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R102" s="1">
         <v>0</v>
@@ -34037,7 +34037,7 @@
         <v>4</v>
       </c>
       <c r="AC102" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AD102" s="1">
         <v>2252</v>
@@ -34244,16 +34244,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>41753</v>
+        <v>41752</v>
       </c>
       <c r="CU102" s="1">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="CV102" s="1">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="CW102" s="1">
-        <v>1591</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -35260,16 +35260,16 @@
         <v>8</v>
       </c>
       <c r="AD106" s="1">
-        <v>41630</v>
+        <v>41673</v>
       </c>
       <c r="AE106" s="2">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="AF106" s="2">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="AG106" s="2">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="AH106" s="1">
         <v>1</v>
@@ -35464,16 +35464,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>90774</v>
+        <v>90817</v>
       </c>
       <c r="CU106" s="1">
-        <v>456</v>
+        <v>499</v>
       </c>
       <c r="CV106" s="1">
-        <v>946</v>
+        <v>989</v>
       </c>
       <c r="CW106" s="1">
-        <v>2342</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -35789,7 +35789,7 @@
         <v>24</v>
       </c>
       <c r="C108" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
@@ -36077,7 +36077,7 @@
         <v>894</v>
       </c>
       <c r="CU108" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV108" s="1">
         <v>18</v>
@@ -36435,7 +36435,7 @@
         <v>1242</v>
       </c>
       <c r="O110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="2">
         <v>6</v>
@@ -36687,7 +36687,7 @@
         <v>12745</v>
       </c>
       <c r="CU110" s="1">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="CV110" s="1">
         <v>573</v>
@@ -38723,16 +38723,16 @@
         <v>0</v>
       </c>
       <c r="BN117" s="1">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="BO117" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BP117" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BQ117" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BR117" s="1">
         <v>0</v>
@@ -38819,16 +38819,16 @@
         <v>0</v>
       </c>
       <c r="CT117" s="1">
-        <v>12381</v>
+        <v>12382</v>
       </c>
       <c r="CU117" s="1">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="CV117" s="1">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="CW117" s="1">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -41886,16 +41886,16 @@
         <v>227</v>
       </c>
       <c r="B128" s="1">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="C128" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D128" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E128" s="2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
@@ -42174,16 +42174,16 @@
         <v>0</v>
       </c>
       <c r="CT128" s="1">
-        <v>2500</v>
+        <v>2507</v>
       </c>
       <c r="CU128" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CV128" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="CW128" s="1">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="129" spans="1:101">
@@ -44102,7 +44102,7 @@
         <v>3</v>
       </c>
       <c r="AC135" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD135" s="1">
         <v>75794</v>
@@ -44318,7 +44318,7 @@
         <v>35</v>
       </c>
       <c r="CW135" s="1">
-        <v>2619</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44419,7 +44419,7 @@
         <v>628</v>
       </c>
       <c r="AG136" s="2">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="AH136" s="1">
         <v>0</v>
@@ -44623,7 +44623,7 @@
         <v>1158</v>
       </c>
       <c r="CW136" s="1">
-        <v>2559</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -45322,7 +45322,7 @@
         <v>3</v>
       </c>
       <c r="AC139" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD139" s="1">
         <v>0</v>
@@ -45538,7 +45538,7 @@
         <v>55</v>
       </c>
       <c r="CW139" s="1">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="140" spans="1:101">
@@ -46279,7 +46279,7 @@
         <v>63</v>
       </c>
       <c r="AQ142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR142" s="2">
         <v>2</v>
@@ -46423,7 +46423,7 @@
         <v>71</v>
       </c>
       <c r="CM142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN142" s="2">
         <v>3</v>
@@ -46447,7 +46447,7 @@
         <v>559</v>
       </c>
       <c r="CU142" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV142" s="1">
         <v>20</v>
@@ -47200,7 +47200,7 @@
         <v>1</v>
       </c>
       <c r="AS145" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT145" s="1">
         <v>0</v>
@@ -47344,7 +47344,7 @@
         <v>3</v>
       </c>
       <c r="CO145" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP145" s="1">
         <v>0</v>
@@ -47368,7 +47368,7 @@
         <v>41</v>
       </c>
       <c r="CW145" s="1">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -50980,7 +50980,7 @@
         <v>0</v>
       </c>
       <c r="CG157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH157" s="1">
         <v>2720</v>
@@ -51028,7 +51028,7 @@
         <v>429</v>
       </c>
       <c r="CW157" s="1">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51243,7 +51243,7 @@
         <v>16</v>
       </c>
       <c r="BS158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT158" s="2">
         <v>1</v>
@@ -51327,7 +51327,7 @@
         <v>160893</v>
       </c>
       <c r="CU158" s="1">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="CV158" s="1">
         <v>5126</v>
@@ -51341,16 +51341,16 @@
         <v>258</v>
       </c>
       <c r="B159" s="1">
-        <v>7972</v>
+        <v>8024</v>
       </c>
       <c r="C159" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D159" s="2">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="E159" s="2">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="F159" s="1">
         <v>2</v>
@@ -51629,16 +51629,16 @@
         <v>0</v>
       </c>
       <c r="CT159" s="1">
-        <v>24398</v>
+        <v>24450</v>
       </c>
       <c r="CU159" s="1">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="CV159" s="1">
-        <v>816</v>
+        <v>868</v>
       </c>
       <c r="CW159" s="1">
-        <v>1672</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="160" spans="1:101">
@@ -52337,7 +52337,7 @@
         <v>4</v>
       </c>
       <c r="AC162" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD162" s="1">
         <v>5288</v>
@@ -52553,7 +52553,7 @@
         <v>344</v>
       </c>
       <c r="CW162" s="1">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="163" spans="1:101">
@@ -53186,7 +53186,7 @@
         <v>54</v>
       </c>
       <c r="G165" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="2">
         <v>3</v>
@@ -53198,7 +53198,7 @@
         <v>77</v>
       </c>
       <c r="K165" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L165" s="2">
         <v>5</v>
@@ -53462,7 +53462,7 @@
         <v>1008</v>
       </c>
       <c r="CU165" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="CV165" s="1">
         <v>98</v>
@@ -53497,7 +53497,7 @@
         <v>4</v>
       </c>
       <c r="I166" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J166" s="1">
         <v>0</v>
@@ -53773,7 +53773,7 @@
         <v>4</v>
       </c>
       <c r="CW166" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -61523,7 +61523,7 @@
         <v>1</v>
       </c>
       <c r="AO192" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP192" s="1">
         <v>52</v>
@@ -61667,7 +61667,7 @@
         <v>10</v>
       </c>
       <c r="CK192" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CL192" s="1">
         <v>37</v>
@@ -61703,7 +61703,7 @@
         <v>17</v>
       </c>
       <c r="CW192" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62061,7 +62061,7 @@
         <v>21</v>
       </c>
       <c r="Q194" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="R194" s="1">
         <v>0</v>
@@ -62160,16 +62160,16 @@
         <v>0</v>
       </c>
       <c r="AX194" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ194" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA194" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB194" s="1">
         <v>3</v>
@@ -62304,16 +62304,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>31520</v>
+        <v>31521</v>
       </c>
       <c r="CU194" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CV194" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="CW194" s="1">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -63933,7 +63933,7 @@
         <v>54</v>
       </c>
       <c r="AE200" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AF200" s="2">
         <v>7</v>
@@ -64137,7 +64137,7 @@
         <v>15927</v>
       </c>
       <c r="CU200" s="1">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="CV200" s="1">
         <v>209</v>
@@ -64400,7 +64400,7 @@
         <v>0</v>
       </c>
       <c r="CG201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH201" s="1">
         <v>3496</v>
@@ -64448,7 +64448,7 @@
         <v>719</v>
       </c>
       <c r="CW201" s="1">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -65883,7 +65883,7 @@
         <v>24</v>
       </c>
       <c r="BS206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT206" s="2">
         <v>1</v>
@@ -65967,7 +65967,7 @@
         <v>1183</v>
       </c>
       <c r="CU206" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV206" s="1">
         <v>10</v>
@@ -66062,7 +66062,7 @@
         <v>3</v>
       </c>
       <c r="AC207" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD207" s="1">
         <v>2125</v>
@@ -66278,7 +66278,7 @@
         <v>198</v>
       </c>
       <c r="CW207" s="1">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -68137,7 +68137,7 @@
         <v>2</v>
       </c>
       <c r="I214" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J214" s="1">
         <v>0</v>
@@ -68413,7 +68413,7 @@
         <v>2</v>
       </c>
       <c r="CW214" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -69906,7 +69906,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E74" t="s">
         <v>717</v>
@@ -69946,7 +69946,7 @@
         <v>595</v>
       </c>
       <c r="D76">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E76" t="s">
         <v>717</v>
@@ -70006,7 +70006,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="E79" t="s">
         <v>717</v>
@@ -72447,7 +72447,7 @@
         <v>704</v>
       </c>
       <c r="D200">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E200" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3833,16 +3833,16 @@
         <v>0</v>
       </c>
       <c r="Z3" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AA3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB3" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC3" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD3" s="1">
         <v>17993</v>
@@ -4049,16 +4049,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>45206</v>
+        <v>45208</v>
       </c>
       <c r="CU3" s="1">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="CV3" s="1">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="CW3" s="1">
-        <v>1728</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4407,16 +4407,16 @@
         <v>119</v>
       </c>
       <c r="N5" s="1">
-        <v>2917</v>
+        <v>2954</v>
       </c>
       <c r="O5" s="2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P5" s="2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q5" s="2">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>
@@ -4659,16 +4659,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38297</v>
+        <v>38334</v>
       </c>
       <c r="CU5" s="1">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="CV5" s="1">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="CW5" s="1">
-        <v>898</v>
+        <v>935</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5756,7 +5756,7 @@
         <v>2</v>
       </c>
       <c r="BE9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BF9" s="1">
         <v>0</v>
@@ -5888,7 +5888,7 @@
         <v>52</v>
       </c>
       <c r="CW9" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -9018,16 +9018,16 @@
         <v>0</v>
       </c>
       <c r="Z20" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AA20" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB20" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AC20" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD20" s="1">
         <v>0</v>
@@ -9234,16 +9234,16 @@
         <v>0</v>
       </c>
       <c r="CT20" s="1">
-        <v>19881</v>
+        <v>19885</v>
       </c>
       <c r="CU20" s="1">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="CV20" s="1">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="CW20" s="1">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -11527,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="AW28" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX28" s="1">
         <v>4</v>
@@ -11539,7 +11539,7 @@
         <v>0</v>
       </c>
       <c r="BA28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB28" s="1">
         <v>10</v>
@@ -11551,7 +11551,7 @@
         <v>1</v>
       </c>
       <c r="BE28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF28" s="1">
         <v>81</v>
@@ -11683,7 +11683,7 @@
         <v>520</v>
       </c>
       <c r="CW28" s="1">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -14472,16 +14472,16 @@
         <v>42</v>
       </c>
       <c r="N38" s="1">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="O38" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P38" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q38" s="2">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="R38" s="1">
         <v>0</v>
@@ -14724,16 +14724,16 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1866</v>
+        <v>1891</v>
       </c>
       <c r="CU38" s="1">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="CV38" s="1">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="CW38" s="1">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -21487,16 +21487,16 @@
         <v>82</v>
       </c>
       <c r="N61" s="1">
-        <v>42917</v>
+        <v>43152</v>
       </c>
       <c r="O61" s="2">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="P61" s="2">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="Q61" s="2">
-        <v>176</v>
+        <v>411</v>
       </c>
       <c r="R61" s="1">
         <v>0</v>
@@ -21739,16 +21739,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65182</v>
+        <v>65417</v>
       </c>
       <c r="CU61" s="1">
-        <v>184</v>
+        <v>419</v>
       </c>
       <c r="CV61" s="1">
-        <v>312</v>
+        <v>547</v>
       </c>
       <c r="CW61" s="1">
-        <v>2354</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22671,16 +22671,16 @@
         <v>164</v>
       </c>
       <c r="B65" s="1">
-        <v>3637</v>
+        <v>3659</v>
       </c>
       <c r="C65" s="2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D65" s="2">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22959,16 +22959,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>63761</v>
+        <v>63783</v>
       </c>
       <c r="CU65" s="1">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="CV65" s="1">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="CW65" s="1">
-        <v>3067</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -25560,16 +25560,16 @@
         <v>0</v>
       </c>
       <c r="AX74" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB74" s="1">
         <v>19</v>
@@ -25704,16 +25704,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>169478</v>
+        <v>169479</v>
       </c>
       <c r="CU74" s="1">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="CV74" s="1">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="CW74" s="1">
-        <v>5384</v>
+        <v>5385</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -31071,7 +31071,7 @@
         <v>0</v>
       </c>
       <c r="BE92" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF92" s="1">
         <v>0</v>
@@ -31203,7 +31203,7 @@
         <v>17</v>
       </c>
       <c r="CW92" s="1">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -44093,16 +44093,16 @@
         <v>0</v>
       </c>
       <c r="Z135" s="1">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AA135" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB135" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC135" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD135" s="1">
         <v>75794</v>
@@ -44129,28 +44129,28 @@
         <v>0</v>
       </c>
       <c r="AL135" s="1">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="AM135" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN135" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO135" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP135" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AQ135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT135" s="1">
         <v>0</v>
@@ -44273,16 +44273,16 @@
         <v>0</v>
       </c>
       <c r="CH135" s="1">
-        <v>2666</v>
+        <v>2692</v>
       </c>
       <c r="CI135" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CJ135" s="2">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="CK135" s="2">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="CL135" s="1">
         <v>9</v>
@@ -44309,16 +44309,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>128662</v>
+        <v>128695</v>
       </c>
       <c r="CU135" s="1">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="CV135" s="1">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="CW135" s="1">
-        <v>2616</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -49828,16 +49828,16 @@
         <v>0</v>
       </c>
       <c r="F154" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G154" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H154" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I154" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J154" s="1">
         <v>0</v>
@@ -50104,16 +50104,16 @@
         <v>0</v>
       </c>
       <c r="CT154" s="1">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="CU154" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV154" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CW154" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="155" spans="1:101">
@@ -63990,16 +63990,16 @@
         <v>0</v>
       </c>
       <c r="AX200" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB200" s="1">
         <v>6</v>
@@ -64134,16 +64134,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>15927</v>
+        <v>15928</v>
       </c>
       <c r="CU200" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="CV200" s="1">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="CW200" s="1">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -66017,16 +66017,16 @@
         <v>67</v>
       </c>
       <c r="N207" s="1">
-        <v>4985</v>
+        <v>4984</v>
       </c>
       <c r="O207" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q207" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R207" s="1">
         <v>0</v>
@@ -66269,16 +66269,16 @@
         <v>0</v>
       </c>
       <c r="CT207" s="1">
-        <v>13579</v>
+        <v>13578</v>
       </c>
       <c r="CU207" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CV207" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CW207" s="1">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -69906,7 +69906,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="E74" t="s">
         <v>717</v>
@@ -70006,7 +70006,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E79" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3477,7 +3477,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>3</v>
       </c>
       <c r="CW2" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:101">
@@ -3767,7 +3767,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2">
         <v>51</v>
@@ -3791,7 +3791,7 @@
         <v>44</v>
       </c>
       <c r="L3" s="2">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="M3" s="2">
         <v>296</v>
@@ -3839,7 +3839,7 @@
         <v>2</v>
       </c>
       <c r="AB3" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC3" s="2">
         <v>8</v>
@@ -3851,7 +3851,7 @@
         <v>432</v>
       </c>
       <c r="AF3" s="2">
-        <v>857</v>
+        <v>432</v>
       </c>
       <c r="AG3" s="2">
         <v>856</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="AR3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS3" s="2">
         <v>4</v>
@@ -4019,7 +4019,7 @@
         <v>20</v>
       </c>
       <c r="CJ3" s="2">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="CK3" s="2">
         <v>86</v>
@@ -4055,7 +4055,7 @@
         <v>505</v>
       </c>
       <c r="CV3" s="1">
-        <v>1065</v>
+        <v>591</v>
       </c>
       <c r="CW3" s="1">
         <v>1730</v>
@@ -4096,7 +4096,7 @@
         <v>65</v>
       </c>
       <c r="L4" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="M4" s="2">
         <v>408</v>
@@ -4180,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="AN4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO4" s="2">
         <v>8</v>
@@ -4264,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="BP4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ4" s="2">
         <v>1</v>
@@ -4273,7 +4273,7 @@
         <v>19</v>
       </c>
       <c r="BS4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT4" s="2">
         <v>1</v>
@@ -4324,7 +4324,7 @@
         <v>54</v>
       </c>
       <c r="CJ4" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="CK4" s="2">
         <v>161</v>
@@ -4357,10 +4357,10 @@
         <v>42270</v>
       </c>
       <c r="CU4" s="1">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="CV4" s="1">
-        <v>728</v>
+        <v>646</v>
       </c>
       <c r="CW4" s="1">
         <v>1320</v>
@@ -4377,7 +4377,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2">
         <v>13</v>
@@ -4401,7 +4401,7 @@
         <v>21</v>
       </c>
       <c r="L5" s="2">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="M5" s="2">
         <v>119</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AN5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" s="2">
         <v>2</v>
@@ -4578,7 +4578,7 @@
         <v>16</v>
       </c>
       <c r="BS5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT5" s="2">
         <v>1</v>
@@ -4617,22 +4617,22 @@
         <v>0</v>
       </c>
       <c r="CF5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG5" s="2">
         <v>1</v>
       </c>
       <c r="CH5" s="1">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="CI5" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CJ5" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="CK5" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="CL5" s="1">
         <v>0</v>
@@ -4659,16 +4659,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38334</v>
+        <v>38333</v>
       </c>
       <c r="CU5" s="1">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="CV5" s="1">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="CW5" s="1">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="2">
         <v>4</v>
@@ -4970,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="CV6" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="CW6" s="1">
         <v>125</v>
@@ -5609,7 +5609,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -5621,7 +5621,7 @@
         <v>4</v>
       </c>
       <c r="L9" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M9" s="2">
         <v>20</v>
@@ -5717,7 +5717,7 @@
         <v>1</v>
       </c>
       <c r="AR9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS9" s="2">
         <v>3</v>
@@ -5750,7 +5750,7 @@
         <v>22</v>
       </c>
       <c r="BC9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD9" s="2">
         <v>2</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="CN9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO9" s="2">
         <v>2</v>
@@ -5882,10 +5882,10 @@
         <v>2806</v>
       </c>
       <c r="CU9" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CV9" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="CW9" s="1">
         <v>84</v>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="CV13" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CW13" s="1">
         <v>5</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="2">
         <v>2</v>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="CJ15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK15" s="2">
         <v>12</v>
@@ -7715,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="CV15" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CW15" s="1">
         <v>64</v>
@@ -7744,7 +7744,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
@@ -7768,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="2">
         <v>40</v>
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="2">
         <v>2</v>
@@ -7984,7 +7984,7 @@
         <v>1</v>
       </c>
       <c r="CJ16" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CK16" s="2">
         <v>15</v>
@@ -8020,7 +8020,7 @@
         <v>4</v>
       </c>
       <c r="CV16" s="1">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="CW16" s="1">
         <v>107</v>
@@ -8037,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2">
         <v>6</v>
@@ -8157,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="AR17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS17" s="2">
         <v>1</v>
@@ -8289,7 +8289,7 @@
         <v>1</v>
       </c>
       <c r="CJ17" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CK17" s="2">
         <v>25</v>
@@ -8325,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="CV17" s="1">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CW17" s="1">
         <v>48</v>
@@ -8342,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2">
         <v>2</v>
@@ -8630,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="CV18" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CW18" s="1">
         <v>7</v>
@@ -8952,7 +8952,7 @@
         <v>36</v>
       </c>
       <c r="D20" s="2">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E20" s="2">
         <v>151</v>
@@ -8976,7 +8976,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M20" s="2">
         <v>51</v>
@@ -8988,7 +8988,7 @@
         <v>17</v>
       </c>
       <c r="P20" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="2">
         <v>237</v>
@@ -9024,7 +9024,7 @@
         <v>4</v>
       </c>
       <c r="AB20" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC20" s="2">
         <v>8</v>
@@ -9204,7 +9204,7 @@
         <v>17</v>
       </c>
       <c r="CJ20" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="CK20" s="2">
         <v>93</v>
@@ -9240,7 +9240,7 @@
         <v>97</v>
       </c>
       <c r="CV20" s="1">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="CW20" s="1">
         <v>568</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
         <v>2</v>
@@ -9377,7 +9377,7 @@
         <v>1</v>
       </c>
       <c r="AR21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS21" s="2">
         <v>5</v>
@@ -9509,7 +9509,7 @@
         <v>7</v>
       </c>
       <c r="CJ21" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CK21" s="2">
         <v>39</v>
@@ -9545,7 +9545,7 @@
         <v>8</v>
       </c>
       <c r="CV21" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CW21" s="1">
         <v>-21</v>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
         <v>4</v>
@@ -9850,7 +9850,7 @@
         <v>2</v>
       </c>
       <c r="CV22" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CW22" s="1">
         <v>6</v>
@@ -9867,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -9897,16 +9897,16 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O23" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P23" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
@@ -9921,16 +9921,16 @@
         <v>0</v>
       </c>
       <c r="V23" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z23" s="1">
         <v>0</v>
@@ -9987,7 +9987,7 @@
         <v>1</v>
       </c>
       <c r="AR23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS23" s="2">
         <v>5</v>
@@ -10131,7 +10131,7 @@
         <v>1</v>
       </c>
       <c r="CN23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO23" s="2">
         <v>4</v>
@@ -10149,16 +10149,16 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="CU23" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CV23" s="1">
         <v>16</v>
       </c>
       <c r="CW23" s="1">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -10597,7 +10597,7 @@
         <v>0</v>
       </c>
       <c r="AR25" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS25" s="2">
         <v>2</v>
@@ -10729,7 +10729,7 @@
         <v>1</v>
       </c>
       <c r="CJ25" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CK25" s="2">
         <v>22</v>
@@ -10765,7 +10765,7 @@
         <v>1</v>
       </c>
       <c r="CV25" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CW25" s="1">
         <v>26</v>
@@ -10785,7 +10785,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" s="1">
         <v>41</v>
@@ -10797,7 +10797,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J26" s="1">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>3</v>
       </c>
       <c r="CW26" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:101">
@@ -11087,7 +11087,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2">
         <v>6</v>
@@ -11195,7 +11195,7 @@
         <v>2</v>
       </c>
       <c r="AN27" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO27" s="2">
         <v>14</v>
@@ -11243,7 +11243,7 @@
         <v>0</v>
       </c>
       <c r="BD27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE27" s="2">
         <v>1</v>
@@ -11339,7 +11339,7 @@
         <v>10</v>
       </c>
       <c r="CJ27" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CK27" s="2">
         <v>48</v>
@@ -11375,7 +11375,7 @@
         <v>13</v>
       </c>
       <c r="CV27" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="CW27" s="1">
         <v>72</v>
@@ -11404,7 +11404,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
         <v>1</v>
@@ -11416,7 +11416,7 @@
         <v>16</v>
       </c>
       <c r="L28" s="2">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="M28" s="2">
         <v>88</v>
@@ -11446,16 +11446,16 @@
         <v>0</v>
       </c>
       <c r="V28" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" s="1">
         <v>0</v>
@@ -11500,7 +11500,7 @@
         <v>1</v>
       </c>
       <c r="AN28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" s="2">
         <v>2</v>
@@ -11644,7 +11644,7 @@
         <v>7</v>
       </c>
       <c r="CJ28" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CK28" s="2">
         <v>29</v>
@@ -11674,16 +11674,16 @@
         <v>0</v>
       </c>
       <c r="CT28" s="1">
-        <v>23795</v>
+        <v>23796</v>
       </c>
       <c r="CU28" s="1">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="CV28" s="1">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="CW28" s="1">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -11712,7 +11712,7 @@
         <v>3</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         <v>3</v>
       </c>
       <c r="CW29" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:101">
@@ -12017,7 +12017,7 @@
         <v>3</v>
       </c>
       <c r="I30" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J30" s="1">
         <v>0</v>
@@ -12293,7 +12293,7 @@
         <v>3</v>
       </c>
       <c r="CW30" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:101">
@@ -12307,7 +12307,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2">
         <v>8</v>
@@ -12331,7 +12331,7 @@
         <v>8</v>
       </c>
       <c r="L31" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M31" s="2">
         <v>69</v>
@@ -12415,7 +12415,7 @@
         <v>10</v>
       </c>
       <c r="AN31" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AO31" s="2">
         <v>50</v>
@@ -12559,7 +12559,7 @@
         <v>12</v>
       </c>
       <c r="CJ31" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CK31" s="2">
         <v>74</v>
@@ -12595,7 +12595,7 @@
         <v>58</v>
       </c>
       <c r="CV31" s="1">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="CW31" s="1">
         <v>262</v>
@@ -12612,7 +12612,7 @@
         <v>21</v>
       </c>
       <c r="D32" s="2">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E32" s="2">
         <v>126</v>
@@ -12636,10 +12636,10 @@
         <v>33</v>
       </c>
       <c r="L32" s="2">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M32" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="N32" s="1">
         <v>6260</v>
@@ -12684,7 +12684,7 @@
         <v>4</v>
       </c>
       <c r="AB32" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC32" s="2">
         <v>8</v>
@@ -12732,7 +12732,7 @@
         <v>1</v>
       </c>
       <c r="AR32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS32" s="2">
         <v>4</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="AZ32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA32" s="2">
         <v>3</v>
@@ -12864,7 +12864,7 @@
         <v>5</v>
       </c>
       <c r="CJ32" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CK32" s="2">
         <v>14</v>
@@ -12900,10 +12900,10 @@
         <v>64</v>
       </c>
       <c r="CV32" s="1">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="CW32" s="1">
-        <v>497</v>
+        <v>469</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13234,7 +13234,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34" s="2">
         <v>4</v>
@@ -13246,7 +13246,7 @@
         <v>7</v>
       </c>
       <c r="L34" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M34" s="2">
         <v>40</v>
@@ -13324,16 +13324,16 @@
         <v>0</v>
       </c>
       <c r="AL34" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AM34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN34" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO34" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP34" s="1">
         <v>48</v>
@@ -13342,10 +13342,10 @@
         <v>0</v>
       </c>
       <c r="AR34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT34" s="1">
         <v>0</v>
@@ -13468,16 +13468,16 @@
         <v>0</v>
       </c>
       <c r="CH34" s="1">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="CI34" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CJ34" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CK34" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CL34" s="1">
         <v>26</v>
@@ -13489,7 +13489,7 @@
         <v>0</v>
       </c>
       <c r="CO34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP34" s="1">
         <v>0</v>
@@ -13504,16 +13504,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="CU34" s="1">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="CV34" s="1">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="CW34" s="1">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -13542,7 +13542,7 @@
         <v>3</v>
       </c>
       <c r="I35" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J35" s="1">
         <v>0</v>
@@ -13818,7 +13818,7 @@
         <v>3</v>
       </c>
       <c r="CW35" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:101">
@@ -13844,7 +13844,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36" s="2">
         <v>6</v>
@@ -14120,7 +14120,7 @@
         <v>1</v>
       </c>
       <c r="CV36" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW36" s="1">
         <v>6</v>
@@ -14152,7 +14152,7 @@
         <v>3</v>
       </c>
       <c r="I37" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J37" s="1">
         <v>0</v>
@@ -14428,7 +14428,7 @@
         <v>3</v>
       </c>
       <c r="CW37" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:101">
@@ -14436,16 +14436,16 @@
         <v>137</v>
       </c>
       <c r="B38" s="1">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>4</v>
       </c>
       <c r="L38" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M38" s="2">
         <v>42</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="AR38" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS38" s="2">
         <v>5</v>
@@ -14706,7 +14706,7 @@
         <v>0</v>
       </c>
       <c r="CN38" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO38" s="2">
         <v>4</v>
@@ -14724,16 +14724,16 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="CU38" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="CV38" s="1">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="CW38" s="1">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -14747,7 +14747,7 @@
         <v>3</v>
       </c>
       <c r="D39" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2">
         <v>9</v>
@@ -14855,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="AN39" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO39" s="2">
         <v>8</v>
@@ -14999,7 +14999,7 @@
         <v>6</v>
       </c>
       <c r="CJ39" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="CK39" s="2">
         <v>72</v>
@@ -15035,7 +15035,7 @@
         <v>10</v>
       </c>
       <c r="CV39" s="1">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="CW39" s="1">
         <v>90</v>
@@ -15052,7 +15052,7 @@
         <v>85</v>
       </c>
       <c r="D40" s="2">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="E40" s="2">
         <v>-4302</v>
@@ -15076,7 +15076,7 @@
         <v>46</v>
       </c>
       <c r="L40" s="2">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="M40" s="2">
         <v>291</v>
@@ -15133,7 +15133,7 @@
         <v>18393</v>
       </c>
       <c r="AE40" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AF40" s="2">
         <v>348</v>
@@ -15160,7 +15160,7 @@
         <v>4</v>
       </c>
       <c r="AN40" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO40" s="2">
         <v>7</v>
@@ -15304,7 +15304,7 @@
         <v>27</v>
       </c>
       <c r="CJ40" s="2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="CK40" s="2">
         <v>75</v>
@@ -15328,7 +15328,7 @@
         <v>0</v>
       </c>
       <c r="CR40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS40" s="2">
         <v>1</v>
@@ -15337,10 +15337,10 @@
         <v>52295</v>
       </c>
       <c r="CU40" s="1">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="CV40" s="1">
-        <v>1175</v>
+        <v>1062</v>
       </c>
       <c r="CW40" s="1">
         <v>-2570</v>
@@ -15357,7 +15357,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="2">
         <v>3</v>
@@ -15369,7 +15369,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I41" s="2">
         <v>4</v>
@@ -15465,7 +15465,7 @@
         <v>2</v>
       </c>
       <c r="AN41" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO41" s="2">
         <v>17</v>
@@ -15477,7 +15477,7 @@
         <v>0</v>
       </c>
       <c r="AR41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS41" s="2">
         <v>1</v>
@@ -15621,7 +15621,7 @@
         <v>0</v>
       </c>
       <c r="CN41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO41" s="2">
         <v>2</v>
@@ -15645,7 +15645,7 @@
         <v>11</v>
       </c>
       <c r="CV41" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="CW41" s="1">
         <v>58</v>
@@ -15677,7 +15677,7 @@
         <v>3</v>
       </c>
       <c r="I42" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J42" s="1">
         <v>0</v>
@@ -15953,7 +15953,7 @@
         <v>3</v>
       </c>
       <c r="CW42" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:101">
@@ -16087,7 +16087,7 @@
         <v>1</v>
       </c>
       <c r="AR43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS43" s="2">
         <v>3</v>
@@ -16231,7 +16231,7 @@
         <v>1</v>
       </c>
       <c r="CN43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO43" s="2">
         <v>4</v>
@@ -16255,7 +16255,7 @@
         <v>6</v>
       </c>
       <c r="CV43" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CW43" s="1">
         <v>21</v>
@@ -16272,7 +16272,7 @@
         <v>2</v>
       </c>
       <c r="D44" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2">
         <v>18</v>
@@ -16296,7 +16296,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="M44" s="2">
         <v>96</v>
@@ -16356,7 +16356,7 @@
         <v>0</v>
       </c>
       <c r="AF44" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG44" s="2">
         <v>1256</v>
@@ -16392,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="AR44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS44" s="2">
         <v>4</v>
@@ -16404,7 +16404,7 @@
         <v>0</v>
       </c>
       <c r="AV44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW44" s="2">
         <v>1</v>
@@ -16536,7 +16536,7 @@
         <v>0</v>
       </c>
       <c r="CN44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO44" s="2">
         <v>1</v>
@@ -16560,7 +16560,7 @@
         <v>48</v>
       </c>
       <c r="CV44" s="1">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="CW44" s="1">
         <v>1474</v>
@@ -18102,7 +18102,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="2">
         <v>4</v>
@@ -18390,7 +18390,7 @@
         <v>11</v>
       </c>
       <c r="CV50" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CW50" s="1">
         <v>66</v>
@@ -18407,7 +18407,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E51" s="2">
         <v>26</v>
@@ -18515,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="AN51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO51" s="2">
         <v>2</v>
@@ -18659,7 +18659,7 @@
         <v>36</v>
       </c>
       <c r="CJ51" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="CK51" s="2">
         <v>151</v>
@@ -18695,7 +18695,7 @@
         <v>37</v>
       </c>
       <c r="CV51" s="1">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="CW51" s="1">
         <v>179</v>
@@ -18712,7 +18712,7 @@
         <v>2</v>
       </c>
       <c r="D52" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2">
         <v>4</v>
@@ -18724,7 +18724,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I52" s="2">
         <v>4</v>
@@ -18820,7 +18820,7 @@
         <v>10</v>
       </c>
       <c r="AN52" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AO52" s="2">
         <v>22</v>
@@ -19000,7 +19000,7 @@
         <v>19</v>
       </c>
       <c r="CV52" s="1">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="CW52" s="1">
         <v>52</v>
@@ -19017,7 +19017,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="2">
         <v>1</v>
@@ -19125,7 +19125,7 @@
         <v>0</v>
       </c>
       <c r="AN53" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AO53" s="2">
         <v>17</v>
@@ -19269,7 +19269,7 @@
         <v>0</v>
       </c>
       <c r="CJ53" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="CK53" s="2">
         <v>24</v>
@@ -19305,7 +19305,7 @@
         <v>1</v>
       </c>
       <c r="CV53" s="1">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="CW53" s="1">
         <v>47</v>
@@ -19430,7 +19430,7 @@
         <v>0</v>
       </c>
       <c r="AN54" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO54" s="2">
         <v>6</v>
@@ -19586,7 +19586,7 @@
         <v>0</v>
       </c>
       <c r="CN54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO54" s="2">
         <v>3</v>
@@ -19610,7 +19610,7 @@
         <v>5</v>
       </c>
       <c r="CV54" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CW54" s="1">
         <v>30</v>
@@ -19932,7 +19932,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E56" s="2">
         <v>82</v>
@@ -19956,7 +19956,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M56" s="2">
         <v>27</v>
@@ -20184,7 +20184,7 @@
         <v>14</v>
       </c>
       <c r="CJ56" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CK56" s="2">
         <v>42</v>
@@ -20220,7 +20220,7 @@
         <v>77</v>
       </c>
       <c r="CV56" s="1">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="CW56" s="1">
         <v>334</v>
@@ -20249,7 +20249,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57" s="2">
         <v>6</v>
@@ -20525,7 +20525,7 @@
         <v>1</v>
       </c>
       <c r="CV57" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW57" s="1">
         <v>6</v>
@@ -20554,7 +20554,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58" s="2">
         <v>5</v>
@@ -20662,7 +20662,7 @@
         <v>0</v>
       </c>
       <c r="AR58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS58" s="2">
         <v>4</v>
@@ -20806,7 +20806,7 @@
         <v>0</v>
       </c>
       <c r="CN58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO58" s="2">
         <v>3</v>
@@ -20830,7 +20830,7 @@
         <v>0</v>
       </c>
       <c r="CV58" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW58" s="1">
         <v>23</v>
@@ -20847,7 +20847,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="2">
         <v>3</v>
@@ -20967,7 +20967,7 @@
         <v>1</v>
       </c>
       <c r="AR59" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS59" s="2">
         <v>6</v>
@@ -21111,7 +21111,7 @@
         <v>1</v>
       </c>
       <c r="CN59" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CO59" s="2">
         <v>6</v>
@@ -21135,7 +21135,7 @@
         <v>3</v>
       </c>
       <c r="CV59" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CW59" s="1">
         <v>39</v>
@@ -21457,7 +21457,7 @@
         <v>29</v>
       </c>
       <c r="D61" s="2">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E61" s="2">
         <v>126</v>
@@ -21481,7 +21481,7 @@
         <v>12</v>
       </c>
       <c r="L61" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M61" s="2">
         <v>82</v>
@@ -21577,7 +21577,7 @@
         <v>1</v>
       </c>
       <c r="AR61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS61" s="2">
         <v>4</v>
@@ -21709,7 +21709,7 @@
         <v>11</v>
       </c>
       <c r="CJ61" s="2">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="CK61" s="2">
         <v>104</v>
@@ -21745,7 +21745,7 @@
         <v>400</v>
       </c>
       <c r="CV61" s="1">
-        <v>540</v>
+        <v>475</v>
       </c>
       <c r="CW61" s="1">
         <v>2582</v>
@@ -22067,7 +22067,7 @@
         <v>5</v>
       </c>
       <c r="D63" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E63" s="2">
         <v>33</v>
@@ -22088,25 +22088,25 @@
         <v>319</v>
       </c>
       <c r="K63" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L63" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M63" s="2">
         <v>18</v>
       </c>
       <c r="N63" s="1">
-        <v>1049</v>
+        <v>1090</v>
       </c>
       <c r="O63" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P63" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q63" s="2">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="R63" s="1">
         <v>0</v>
@@ -22184,10 +22184,10 @@
         <v>63</v>
       </c>
       <c r="AQ63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR63" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS63" s="2">
         <v>6</v>
@@ -22211,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA63" s="2">
         <v>18</v>
@@ -22268,7 +22268,7 @@
         <v>17</v>
       </c>
       <c r="BS63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT63" s="2">
         <v>1</v>
@@ -22319,7 +22319,7 @@
         <v>11</v>
       </c>
       <c r="CJ63" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CK63" s="2">
         <v>50</v>
@@ -22349,16 +22349,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2736</v>
+        <v>2777</v>
       </c>
       <c r="CU63" s="1">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="CV63" s="1">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="CW63" s="1">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22372,7 +22372,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2">
         <v>19</v>
@@ -22396,7 +22396,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2">
         <v>16</v>
@@ -22453,7 +22453,7 @@
         <v>1931</v>
       </c>
       <c r="AE64" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AF64" s="2">
         <v>110</v>
@@ -22624,7 +22624,7 @@
         <v>2</v>
       </c>
       <c r="CJ64" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="CK64" s="2">
         <v>37</v>
@@ -22657,10 +22657,10 @@
         <v>7815</v>
       </c>
       <c r="CU64" s="1">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="CV64" s="1">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="CW64" s="1">
         <v>469</v>
@@ -22677,7 +22677,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="2">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E65" s="2">
         <v>131</v>
@@ -22701,7 +22701,7 @@
         <v>23</v>
       </c>
       <c r="L65" s="2">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M65" s="2">
         <v>98</v>
@@ -22713,7 +22713,7 @@
         <v>0</v>
       </c>
       <c r="P65" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q65" s="2">
         <v>2701</v>
@@ -22797,7 +22797,7 @@
         <v>1</v>
       </c>
       <c r="AR65" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS65" s="2">
         <v>6</v>
@@ -22821,7 +22821,7 @@
         <v>0</v>
       </c>
       <c r="AZ65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA65" s="2">
         <v>2</v>
@@ -22929,7 +22929,7 @@
         <v>11</v>
       </c>
       <c r="CJ65" s="2">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="CK65" s="2">
         <v>71</v>
@@ -22941,7 +22941,7 @@
         <v>1</v>
       </c>
       <c r="CN65" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO65" s="2">
         <v>6</v>
@@ -22965,7 +22965,7 @@
         <v>63</v>
       </c>
       <c r="CV65" s="1">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="CW65" s="1">
         <v>3065</v>
@@ -23009,7 +23009,7 @@
         <v>50</v>
       </c>
       <c r="M66" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N66" s="1">
         <v>0</v>
@@ -23273,7 +23273,7 @@
         <v>63</v>
       </c>
       <c r="CW66" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:101">
@@ -23592,7 +23592,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68" s="2">
         <v>7</v>
@@ -23610,16 +23610,16 @@
         <v>1</v>
       </c>
       <c r="J68" s="1">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="K68" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L68" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M68" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N68" s="1">
         <v>1051</v>
@@ -23712,7 +23712,7 @@
         <v>2</v>
       </c>
       <c r="AR68" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS68" s="2">
         <v>6</v>
@@ -23874,16 +23874,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2097</v>
+        <v>2101</v>
       </c>
       <c r="CU68" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CV68" s="1">
         <v>29</v>
       </c>
       <c r="CW68" s="1">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="2">
         <v>3</v>
@@ -24185,7 +24185,7 @@
         <v>0</v>
       </c>
       <c r="CV69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW69" s="1">
         <v>3</v>
@@ -24214,7 +24214,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" s="2">
         <v>1</v>
@@ -24229,7 +24229,7 @@
         <v>5</v>
       </c>
       <c r="M70" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N70" s="1">
         <v>1229</v>
@@ -24322,7 +24322,7 @@
         <v>1</v>
       </c>
       <c r="AR70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS70" s="2">
         <v>6</v>
@@ -24466,7 +24466,7 @@
         <v>1</v>
       </c>
       <c r="CN70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO70" s="2">
         <v>4</v>
@@ -24490,10 +24490,10 @@
         <v>5</v>
       </c>
       <c r="CV70" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CW70" s="1">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24507,7 +24507,7 @@
         <v>2</v>
       </c>
       <c r="D71" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="2">
         <v>3</v>
@@ -24519,7 +24519,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I71" s="2">
         <v>5</v>
@@ -24795,7 +24795,7 @@
         <v>3</v>
       </c>
       <c r="CV71" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="CW71" s="1">
         <v>8</v>
@@ -24818,28 +24818,28 @@
         <v>6</v>
       </c>
       <c r="F72" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I72" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J72" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K72" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L72" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M72" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N72" s="1">
         <v>74</v>
@@ -24932,7 +24932,7 @@
         <v>1</v>
       </c>
       <c r="AR72" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS72" s="2">
         <v>6</v>
@@ -25064,7 +25064,7 @@
         <v>2</v>
       </c>
       <c r="CJ72" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK72" s="2">
         <v>11</v>
@@ -25094,16 +25094,16 @@
         <v>0</v>
       </c>
       <c r="CT72" s="1">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CU72" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="CV72" s="1">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="CW72" s="1">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25117,7 +25117,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73" s="2">
         <v>9</v>
@@ -25237,7 +25237,7 @@
         <v>0</v>
       </c>
       <c r="AR73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS73" s="2">
         <v>1</v>
@@ -25381,7 +25381,7 @@
         <v>0</v>
       </c>
       <c r="CN73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO73" s="2">
         <v>1</v>
@@ -25405,7 +25405,7 @@
         <v>19</v>
       </c>
       <c r="CV73" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="CW73" s="1">
         <v>79</v>
@@ -25422,7 +25422,7 @@
         <v>143</v>
       </c>
       <c r="D74" s="2">
-        <v>277</v>
+        <v>217</v>
       </c>
       <c r="E74" s="2">
         <v>476</v>
@@ -25446,10 +25446,10 @@
         <v>41</v>
       </c>
       <c r="L74" s="2">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="M74" s="2">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="N74" s="1">
         <v>78141</v>
@@ -25503,7 +25503,7 @@
         <v>16001</v>
       </c>
       <c r="AE74" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AF74" s="2">
         <v>331</v>
@@ -25527,10 +25527,10 @@
         <v>36001</v>
       </c>
       <c r="AM74" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AN74" s="2">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="AO74" s="2">
         <v>313</v>
@@ -25674,7 +25674,7 @@
         <v>95</v>
       </c>
       <c r="CJ74" s="2">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="CK74" s="2">
         <v>371</v>
@@ -25698,7 +25698,7 @@
         <v>0</v>
       </c>
       <c r="CR74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS74" s="2">
         <v>1</v>
@@ -25707,13 +25707,13 @@
         <v>169497</v>
       </c>
       <c r="CU74" s="1">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="CV74" s="1">
-        <v>2477</v>
+        <v>2292</v>
       </c>
       <c r="CW74" s="1">
-        <v>5408</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25847,7 +25847,7 @@
         <v>0</v>
       </c>
       <c r="AR75" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS75" s="2">
         <v>4</v>
@@ -25979,7 +25979,7 @@
         <v>0</v>
       </c>
       <c r="CJ75" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="CK75" s="2">
         <v>12</v>
@@ -26015,7 +26015,7 @@
         <v>1</v>
       </c>
       <c r="CV75" s="1">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="CW75" s="1">
         <v>21</v>
@@ -26032,7 +26032,7 @@
         <v>51</v>
       </c>
       <c r="D76" s="2">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="E76" s="2">
         <v>223</v>
@@ -26056,7 +26056,7 @@
         <v>56</v>
       </c>
       <c r="L76" s="2">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="M76" s="2">
         <v>348</v>
@@ -26065,10 +26065,10 @@
         <v>115143</v>
       </c>
       <c r="O76" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P76" s="2">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="Q76" s="2">
         <v>1293</v>
@@ -26116,7 +26116,7 @@
         <v>538</v>
       </c>
       <c r="AF76" s="2">
-        <v>442</v>
+        <v>538</v>
       </c>
       <c r="AG76" s="2">
         <v>754</v>
@@ -26317,10 +26317,10 @@
         <v>148085</v>
       </c>
       <c r="CU76" s="1">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="CV76" s="1">
-        <v>870</v>
+        <v>842</v>
       </c>
       <c r="CW76" s="1">
         <v>2727</v>
@@ -26331,16 +26331,16 @@
         <v>176</v>
       </c>
       <c r="B77" s="1">
-        <v>10825</v>
+        <v>10824</v>
       </c>
       <c r="C77" s="2">
-        <v>-4428</v>
+        <v>-4429</v>
       </c>
       <c r="D77" s="2">
-        <v>-4217</v>
+        <v>-4326</v>
       </c>
       <c r="E77" s="2">
-        <v>-3849</v>
+        <v>-3850</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -26358,10 +26358,10 @@
         <v>4649</v>
       </c>
       <c r="K77" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L77" s="2">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="M77" s="2">
         <v>239</v>
@@ -26373,7 +26373,7 @@
         <v>1</v>
       </c>
       <c r="P77" s="2">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="Q77" s="2">
         <v>7965</v>
@@ -26442,13 +26442,13 @@
         <v>1855</v>
       </c>
       <c r="AM77" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AN77" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO77" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26589,7 +26589,7 @@
         <v>88</v>
       </c>
       <c r="CJ77" s="2">
-        <v>294</v>
+        <v>221</v>
       </c>
       <c r="CK77" s="2">
         <v>536</v>
@@ -26619,16 +26619,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>370930</v>
+        <v>370929</v>
       </c>
       <c r="CU77" s="1">
-        <v>-4136</v>
+        <v>-4143</v>
       </c>
       <c r="CV77" s="1">
-        <v>-3587</v>
+        <v>-3818</v>
       </c>
       <c r="CW77" s="1">
-        <v>5261</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26654,7 +26654,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78" s="2">
         <v>6</v>
@@ -26750,7 +26750,7 @@
         <v>12</v>
       </c>
       <c r="AN78" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO78" s="2">
         <v>59</v>
@@ -26894,7 +26894,7 @@
         <v>0</v>
       </c>
       <c r="CJ78" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CK78" s="2">
         <v>62</v>
@@ -26930,7 +26930,7 @@
         <v>13</v>
       </c>
       <c r="CV78" s="1">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="CW78" s="1">
         <v>127</v>
@@ -26947,7 +26947,7 @@
         <v>15</v>
       </c>
       <c r="D79" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2">
         <v>71</v>
@@ -26983,7 +26983,7 @@
         <v>0</v>
       </c>
       <c r="P79" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="2">
         <v>563</v>
@@ -27019,22 +27019,22 @@
         <v>4</v>
       </c>
       <c r="AB79" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC79" s="2">
         <v>8</v>
       </c>
       <c r="AD79" s="1">
-        <v>8583</v>
+        <v>8582</v>
       </c>
       <c r="AE79" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AF79" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG79" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH79" s="1">
         <v>0</v>
@@ -27055,7 +27055,7 @@
         <v>1</v>
       </c>
       <c r="AN79" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AO79" s="2">
         <v>6</v>
@@ -27199,7 +27199,7 @@
         <v>43</v>
       </c>
       <c r="CJ79" s="2">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="CK79" s="2">
         <v>112</v>
@@ -27229,16 +27229,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>89168</v>
+        <v>89167</v>
       </c>
       <c r="CU79" s="1">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="CV79" s="1">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="CW79" s="1">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27360,7 +27360,7 @@
         <v>22</v>
       </c>
       <c r="AN80" s="2">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="AO80" s="2">
         <v>120</v>
@@ -27504,7 +27504,7 @@
         <v>19</v>
       </c>
       <c r="CJ80" s="2">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="CK80" s="2">
         <v>148</v>
@@ -27540,7 +27540,7 @@
         <v>48</v>
       </c>
       <c r="CV80" s="1">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="CW80" s="1">
         <v>277</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="D81" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E81" s="2">
         <v>17</v>
@@ -27581,7 +27581,7 @@
         <v>20</v>
       </c>
       <c r="L81" s="2">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="M81" s="2">
         <v>133</v>
@@ -27671,16 +27671,16 @@
         <v>5</v>
       </c>
       <c r="AP81" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AQ81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR81" s="2">
         <v>1</v>
       </c>
       <c r="AS81" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT81" s="1">
         <v>5</v>
@@ -27803,16 +27803,16 @@
         <v>0</v>
       </c>
       <c r="CH81" s="1">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="CI81" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CJ81" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK81" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CL81" s="1">
         <v>30</v>
@@ -27839,16 +27839,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="CU81" s="1">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CV81" s="1">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="CW81" s="1">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -27862,7 +27862,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E82" s="2">
         <v>3</v>
@@ -27895,7 +27895,7 @@
         <v>37</v>
       </c>
       <c r="O82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" s="2">
         <v>1</v>
@@ -27916,16 +27916,16 @@
         <v>1</v>
       </c>
       <c r="V82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z82" s="1">
         <v>0</v>
@@ -28126,7 +28126,7 @@
         <v>0</v>
       </c>
       <c r="CN82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO82" s="2">
         <v>4</v>
@@ -28144,16 +28144,16 @@
         <v>0</v>
       </c>
       <c r="CT82" s="1">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="CU82" s="1">
         <v>1</v>
       </c>
       <c r="CV82" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CW82" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -28167,7 +28167,7 @@
         <v>60</v>
       </c>
       <c r="D83" s="2">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E83" s="2">
         <v>160</v>
@@ -28191,10 +28191,10 @@
         <v>115</v>
       </c>
       <c r="L83" s="2">
-        <v>289</v>
+        <v>215</v>
       </c>
       <c r="M83" s="2">
-        <v>545</v>
+        <v>453</v>
       </c>
       <c r="N83" s="1">
         <v>39141</v>
@@ -28239,7 +28239,7 @@
         <v>3</v>
       </c>
       <c r="AB83" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC83" s="2">
         <v>6</v>
@@ -28299,7 +28299,7 @@
         <v>0</v>
       </c>
       <c r="AV83" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW83" s="2">
         <v>4</v>
@@ -28311,7 +28311,7 @@
         <v>0</v>
       </c>
       <c r="AZ83" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA83" s="2">
         <v>4</v>
@@ -28419,7 +28419,7 @@
         <v>39</v>
       </c>
       <c r="CJ83" s="2">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="CK83" s="2">
         <v>263</v>
@@ -28455,10 +28455,10 @@
         <v>3570</v>
       </c>
       <c r="CV83" s="1">
-        <v>3836</v>
+        <v>3718</v>
       </c>
       <c r="CW83" s="1">
-        <v>5123</v>
+        <v>5031</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28789,7 +28789,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I85" s="2">
         <v>5</v>
@@ -28891,16 +28891,16 @@
         <v>0</v>
       </c>
       <c r="AP85" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR85" s="2">
         <v>3</v>
       </c>
       <c r="AS85" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT85" s="1">
         <v>0</v>
@@ -29023,16 +29023,16 @@
         <v>0</v>
       </c>
       <c r="CH85" s="1">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="CI85" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CJ85" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="CK85" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CL85" s="1">
         <v>0</v>
@@ -29059,16 +29059,16 @@
         <v>0</v>
       </c>
       <c r="CT85" s="1">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="CU85" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CV85" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="CW85" s="1">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -29118,7 +29118,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="2">
         <v>24</v>
@@ -29190,7 +29190,7 @@
         <v>0</v>
       </c>
       <c r="AN86" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO86" s="2">
         <v>6</v>
@@ -29334,7 +29334,7 @@
         <v>11</v>
       </c>
       <c r="CJ86" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CK86" s="2">
         <v>36</v>
@@ -29370,7 +29370,7 @@
         <v>15</v>
       </c>
       <c r="CV86" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CW86" s="1">
         <v>78</v>
@@ -29495,7 +29495,7 @@
         <v>5</v>
       </c>
       <c r="AN87" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO87" s="2">
         <v>56</v>
@@ -29639,7 +29639,7 @@
         <v>28</v>
       </c>
       <c r="CJ87" s="2">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="CK87" s="2">
         <v>288</v>
@@ -29675,7 +29675,7 @@
         <v>33</v>
       </c>
       <c r="CV87" s="1">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="CW87" s="1">
         <v>345</v>
@@ -29704,7 +29704,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" s="2">
         <v>4</v>
@@ -29716,7 +29716,7 @@
         <v>21</v>
       </c>
       <c r="L88" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M88" s="2">
         <v>81</v>
@@ -29980,7 +29980,7 @@
         <v>262</v>
       </c>
       <c r="CV88" s="1">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="CW88" s="1">
         <v>409</v>
@@ -30009,7 +30009,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I89" s="2">
         <v>4</v>
@@ -30021,7 +30021,7 @@
         <v>8</v>
       </c>
       <c r="L89" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M89" s="2">
         <v>69</v>
@@ -30117,7 +30117,7 @@
         <v>2</v>
       </c>
       <c r="AR89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS89" s="2">
         <v>6</v>
@@ -30249,7 +30249,7 @@
         <v>5</v>
       </c>
       <c r="CJ89" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CK89" s="2">
         <v>22</v>
@@ -30285,7 +30285,7 @@
         <v>17</v>
       </c>
       <c r="CV89" s="1">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="CW89" s="1">
         <v>408</v>
@@ -30631,7 +30631,7 @@
         <v>51</v>
       </c>
       <c r="L91" s="2">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="M91" s="2">
         <v>450</v>
@@ -30691,7 +30691,7 @@
         <v>0</v>
       </c>
       <c r="AF91" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG91" s="2">
         <v>14</v>
@@ -30715,7 +30715,7 @@
         <v>4</v>
       </c>
       <c r="AN91" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AO91" s="2">
         <v>33</v>
@@ -30859,7 +30859,7 @@
         <v>32</v>
       </c>
       <c r="CJ91" s="2">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="CK91" s="2">
         <v>167</v>
@@ -30895,7 +30895,7 @@
         <v>135</v>
       </c>
       <c r="CV91" s="1">
-        <v>456</v>
+        <v>339</v>
       </c>
       <c r="CW91" s="1">
         <v>970</v>
@@ -30912,7 +30912,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E92" s="2">
         <v>17</v>
@@ -30936,7 +30936,7 @@
         <v>4</v>
       </c>
       <c r="L92" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M92" s="2">
         <v>11</v>
@@ -31164,7 +31164,7 @@
         <v>2</v>
       </c>
       <c r="CJ92" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK92" s="2">
         <v>17</v>
@@ -31200,7 +31200,7 @@
         <v>9</v>
       </c>
       <c r="CV92" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CW92" s="1">
         <v>73</v>
@@ -31337,7 +31337,7 @@
         <v>1</v>
       </c>
       <c r="AR93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS93" s="2">
         <v>2</v>
@@ -31469,7 +31469,7 @@
         <v>3</v>
       </c>
       <c r="CJ93" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK93" s="2">
         <v>10</v>
@@ -31505,7 +31505,7 @@
         <v>5</v>
       </c>
       <c r="CV93" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CW93" s="1">
         <v>42</v>
@@ -31534,7 +31534,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I94" s="2">
         <v>4</v>
@@ -31810,7 +31810,7 @@
         <v>1</v>
       </c>
       <c r="CV94" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CW94" s="1">
         <v>6</v>
@@ -32144,7 +32144,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I96" s="2">
         <v>7</v>
@@ -32252,7 +32252,7 @@
         <v>0</v>
       </c>
       <c r="AR96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS96" s="2">
         <v>3</v>
@@ -32420,7 +32420,7 @@
         <v>21</v>
       </c>
       <c r="CV96" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CW96" s="1">
         <v>82</v>
@@ -32449,7 +32449,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I97" s="2">
         <v>6</v>
@@ -32551,16 +32551,16 @@
         <v>0</v>
       </c>
       <c r="AP97" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AQ97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR97" s="2">
         <v>3</v>
       </c>
       <c r="AS97" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT97" s="1">
         <v>0</v>
@@ -32683,16 +32683,16 @@
         <v>0</v>
       </c>
       <c r="CH97" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CI97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ97" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CK97" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL97" s="1">
         <v>33</v>
@@ -32719,16 +32719,16 @@
         <v>0</v>
       </c>
       <c r="CT97" s="1">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="CU97" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV97" s="1">
         <v>9</v>
       </c>
       <c r="CW97" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -32754,7 +32754,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I98" s="2">
         <v>3</v>
@@ -33030,7 +33030,7 @@
         <v>0</v>
       </c>
       <c r="CV98" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW98" s="1">
         <v>3</v>
@@ -33059,7 +33059,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I99" s="2">
         <v>6</v>
@@ -33335,7 +33335,7 @@
         <v>1</v>
       </c>
       <c r="CV99" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW99" s="1">
         <v>6</v>
@@ -33364,7 +33364,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I100" s="2">
         <v>7</v>
@@ -33640,7 +33640,7 @@
         <v>8</v>
       </c>
       <c r="CV100" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW100" s="1">
         <v>39</v>
@@ -33956,16 +33956,16 @@
         <v>201</v>
       </c>
       <c r="B102" s="1">
-        <v>17023</v>
+        <v>17022</v>
       </c>
       <c r="C102" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D102" s="2">
-        <v>552</v>
+        <v>322</v>
       </c>
       <c r="E102" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -33986,7 +33986,7 @@
         <v>47</v>
       </c>
       <c r="L102" s="2">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="M102" s="2">
         <v>221</v>
@@ -34034,7 +34034,7 @@
         <v>4</v>
       </c>
       <c r="AB102" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC102" s="2">
         <v>8</v>
@@ -34046,7 +34046,7 @@
         <v>91</v>
       </c>
       <c r="AF102" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AG102" s="2">
         <v>191</v>
@@ -34070,10 +34070,10 @@
         <v>1</v>
       </c>
       <c r="AN102" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO102" s="2">
         <v>2</v>
-      </c>
-      <c r="AO102" s="2">
-        <v>3</v>
       </c>
       <c r="AP102" s="1">
         <v>33</v>
@@ -34151,7 +34151,7 @@
         <v>522</v>
       </c>
       <c r="BO102" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP102" s="2">
         <v>5</v>
@@ -34214,10 +34214,10 @@
         <v>15</v>
       </c>
       <c r="CJ102" s="2">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="CK102" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="CL102" s="1">
         <v>9</v>
@@ -34244,16 +34244,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>41756</v>
+        <v>41755</v>
       </c>
       <c r="CU102" s="1">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="CV102" s="1">
-        <v>815</v>
+        <v>551</v>
       </c>
       <c r="CW102" s="1">
-        <v>1590</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34375,7 +34375,7 @@
         <v>3</v>
       </c>
       <c r="AN103" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AO103" s="2">
         <v>32</v>
@@ -34519,7 +34519,7 @@
         <v>67</v>
       </c>
       <c r="CJ103" s="2">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="CK103" s="2">
         <v>202</v>
@@ -34555,7 +34555,7 @@
         <v>70</v>
       </c>
       <c r="CV103" s="1">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="CW103" s="1">
         <v>240</v>
@@ -34584,7 +34584,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I104" s="2">
         <v>6</v>
@@ -34860,7 +34860,7 @@
         <v>1</v>
       </c>
       <c r="CV104" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW104" s="1">
         <v>6</v>
@@ -34871,16 +34871,16 @@
         <v>204</v>
       </c>
       <c r="B105" s="1">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C105" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D105" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E105" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F105" s="1">
         <v>4</v>
@@ -34901,7 +34901,7 @@
         <v>6</v>
       </c>
       <c r="L105" s="2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="M105" s="2">
         <v>59</v>
@@ -34997,7 +34997,7 @@
         <v>0</v>
       </c>
       <c r="AR105" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS105" s="2">
         <v>4</v>
@@ -35129,7 +35129,7 @@
         <v>3</v>
       </c>
       <c r="CJ105" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CK105" s="2">
         <v>18</v>
@@ -35159,16 +35159,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7513</v>
+        <v>7521</v>
       </c>
       <c r="CU105" s="1">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="CV105" s="1">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="CW105" s="1">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -35182,7 +35182,7 @@
         <v>79</v>
       </c>
       <c r="D106" s="2">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="E106" s="2">
         <v>450</v>
@@ -35200,16 +35200,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="1">
-        <v>10189</v>
+        <v>10188</v>
       </c>
       <c r="K106" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L106" s="2">
-        <v>522</v>
+        <v>382</v>
       </c>
       <c r="M106" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N106" s="1">
         <v>22427</v>
@@ -35218,7 +35218,7 @@
         <v>1</v>
       </c>
       <c r="P106" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="2">
         <v>263</v>
@@ -35254,7 +35254,7 @@
         <v>0</v>
       </c>
       <c r="AB106" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC106" s="2">
         <v>8</v>
@@ -35266,7 +35266,7 @@
         <v>186</v>
       </c>
       <c r="AF106" s="2">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="AG106" s="2">
         <v>236</v>
@@ -35290,7 +35290,7 @@
         <v>4</v>
       </c>
       <c r="AN106" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO106" s="2">
         <v>23</v>
@@ -35434,7 +35434,7 @@
         <v>80</v>
       </c>
       <c r="CJ106" s="2">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="CK106" s="2">
         <v>324</v>
@@ -35464,16 +35464,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>90817</v>
+        <v>90816</v>
       </c>
       <c r="CU106" s="1">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="CV106" s="1">
-        <v>989</v>
+        <v>724</v>
       </c>
       <c r="CW106" s="1">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -35804,7 +35804,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I108" s="2">
         <v>5</v>
@@ -35828,7 +35828,7 @@
         <v>0</v>
       </c>
       <c r="P108" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q108" s="2">
         <v>6</v>
@@ -36044,7 +36044,7 @@
         <v>6</v>
       </c>
       <c r="CJ108" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CK108" s="2">
         <v>30</v>
@@ -36080,7 +36080,7 @@
         <v>7</v>
       </c>
       <c r="CV108" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="CW108" s="1">
         <v>46</v>
@@ -36402,7 +36402,7 @@
         <v>15</v>
       </c>
       <c r="D110" s="2">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E110" s="2">
         <v>135</v>
@@ -36426,7 +36426,7 @@
         <v>65</v>
       </c>
       <c r="L110" s="2">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="M110" s="2">
         <v>375</v>
@@ -36438,7 +36438,7 @@
         <v>0</v>
       </c>
       <c r="P110" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q110" s="2">
         <v>39</v>
@@ -36474,7 +36474,7 @@
         <v>4</v>
       </c>
       <c r="AB110" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC110" s="2">
         <v>8</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="AN110" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO110" s="2">
         <v>7</v>
@@ -36654,7 +36654,7 @@
         <v>66</v>
       </c>
       <c r="CJ110" s="2">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="CK110" s="2">
         <v>165</v>
@@ -36690,7 +36690,7 @@
         <v>353</v>
       </c>
       <c r="CV110" s="1">
-        <v>573</v>
+        <v>446</v>
       </c>
       <c r="CW110" s="1">
         <v>1013</v>
@@ -36707,7 +36707,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="2">
         <v>2</v>
@@ -36815,7 +36815,7 @@
         <v>4</v>
       </c>
       <c r="AN111" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO111" s="2">
         <v>13</v>
@@ -36971,7 +36971,7 @@
         <v>0</v>
       </c>
       <c r="CN111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO111" s="2">
         <v>1</v>
@@ -36995,7 +36995,7 @@
         <v>22</v>
       </c>
       <c r="CV111" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CW111" s="1">
         <v>87</v>
@@ -37012,7 +37012,7 @@
         <v>18</v>
       </c>
       <c r="D112" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E112" s="2">
         <v>78</v>
@@ -37030,16 +37030,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="1">
-        <v>1067</v>
+        <v>1081</v>
       </c>
       <c r="K112" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L112" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M112" s="2">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="N112" s="1">
         <v>5128</v>
@@ -37132,10 +37132,10 @@
         <v>1</v>
       </c>
       <c r="AR112" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS112" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT112" s="1">
         <v>0</v>
@@ -37276,7 +37276,7 @@
         <v>0</v>
       </c>
       <c r="CN112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO112" s="2">
         <v>1</v>
@@ -37294,16 +37294,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>7689</v>
+        <v>7703</v>
       </c>
       <c r="CU112" s="1">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="CV112" s="1">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="CW112" s="1">
-        <v>433</v>
+        <v>446</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37317,7 +37317,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="2">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E113" s="2">
         <v>107</v>
@@ -37569,7 +37569,7 @@
         <v>34</v>
       </c>
       <c r="CJ113" s="2">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="CK113" s="2">
         <v>97</v>
@@ -37605,7 +37605,7 @@
         <v>8931</v>
       </c>
       <c r="CV113" s="1">
-        <v>9172</v>
+        <v>9145</v>
       </c>
       <c r="CW113" s="1">
         <v>13933</v>
@@ -37634,10 +37634,10 @@
         <v>1</v>
       </c>
       <c r="H114" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I114" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J114" s="1">
         <v>0</v>
@@ -37910,10 +37910,10 @@
         <v>1</v>
       </c>
       <c r="CV114" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW114" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:101">
@@ -38232,7 +38232,7 @@
         <v>23</v>
       </c>
       <c r="D116" s="2">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E116" s="2">
         <v>166</v>
@@ -38256,7 +38256,7 @@
         <v>68</v>
       </c>
       <c r="L116" s="2">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="M116" s="2">
         <v>250</v>
@@ -38286,16 +38286,16 @@
         <v>0</v>
       </c>
       <c r="V116" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z116" s="1">
         <v>97</v>
@@ -38304,7 +38304,7 @@
         <v>3</v>
       </c>
       <c r="AB116" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC116" s="2">
         <v>6</v>
@@ -38316,7 +38316,7 @@
         <v>361</v>
       </c>
       <c r="AF116" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG116" s="2">
         <v>443</v>
@@ -38340,7 +38340,7 @@
         <v>8</v>
       </c>
       <c r="AN116" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO116" s="2">
         <v>26</v>
@@ -38484,7 +38484,7 @@
         <v>12</v>
       </c>
       <c r="CJ116" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="CK116" s="2">
         <v>95</v>
@@ -38514,16 +38514,16 @@
         <v>0</v>
       </c>
       <c r="CT116" s="1">
-        <v>21270</v>
+        <v>21271</v>
       </c>
       <c r="CU116" s="1">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="CV116" s="1">
-        <v>752</v>
+        <v>684</v>
       </c>
       <c r="CW116" s="1">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38537,7 +38537,7 @@
         <v>197</v>
       </c>
       <c r="D117" s="2">
-        <v>426</v>
+        <v>320</v>
       </c>
       <c r="E117" s="2">
         <v>797</v>
@@ -38561,7 +38561,7 @@
         <v>8</v>
       </c>
       <c r="L117" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M117" s="2">
         <v>25</v>
@@ -38645,7 +38645,7 @@
         <v>0</v>
       </c>
       <c r="AN117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO117" s="2">
         <v>3</v>
@@ -38801,7 +38801,7 @@
         <v>0</v>
       </c>
       <c r="CN117" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO117" s="2">
         <v>2</v>
@@ -38825,7 +38825,7 @@
         <v>312</v>
       </c>
       <c r="CV117" s="1">
-        <v>558</v>
+        <v>445</v>
       </c>
       <c r="CW117" s="1">
         <v>1002</v>
@@ -38848,16 +38848,16 @@
         <v>0</v>
       </c>
       <c r="F118" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="2">
         <v>3</v>
       </c>
       <c r="I118" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J118" s="1">
         <v>0</v>
@@ -38962,7 +38962,7 @@
         <v>0</v>
       </c>
       <c r="AR118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS118" s="2">
         <v>1</v>
@@ -39094,7 +39094,7 @@
         <v>7</v>
       </c>
       <c r="CJ118" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CK118" s="2">
         <v>21</v>
@@ -39124,16 +39124,16 @@
         <v>0</v>
       </c>
       <c r="CT118" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="CU118" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV118" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="CW118" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:101">
@@ -39141,16 +39141,16 @@
         <v>218</v>
       </c>
       <c r="B119" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" s="2">
         <v>3</v>
       </c>
       <c r="E119" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1">
         <v>37</v>
@@ -39429,16 +39429,16 @@
         <v>0</v>
       </c>
       <c r="CT119" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="CU119" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV119" s="1">
         <v>4</v>
       </c>
       <c r="CW119" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -39452,7 +39452,7 @@
         <v>0</v>
       </c>
       <c r="D120" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E120" s="2">
         <v>2</v>
@@ -39740,7 +39740,7 @@
         <v>5</v>
       </c>
       <c r="CV120" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW120" s="1">
         <v>25</v>
@@ -39757,7 +39757,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="2">
         <v>2</v>
@@ -39865,7 +39865,7 @@
         <v>5</v>
       </c>
       <c r="AN121" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO121" s="2">
         <v>27</v>
@@ -40009,7 +40009,7 @@
         <v>11</v>
       </c>
       <c r="CJ121" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CK121" s="2">
         <v>32</v>
@@ -40045,7 +40045,7 @@
         <v>17</v>
       </c>
       <c r="CV121" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="CW121" s="1">
         <v>65</v>
@@ -40074,7 +40074,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I122" s="2">
         <v>6</v>
@@ -40350,7 +40350,7 @@
         <v>1</v>
       </c>
       <c r="CV122" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW122" s="1">
         <v>6</v>
@@ -40684,7 +40684,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I124" s="2">
         <v>5</v>
@@ -40702,16 +40702,16 @@
         <v>0</v>
       </c>
       <c r="N124" s="1">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="O124" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P124" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q124" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R124" s="1">
         <v>0</v>
@@ -40792,7 +40792,7 @@
         <v>1</v>
       </c>
       <c r="AR124" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS124" s="2">
         <v>6</v>
@@ -40936,7 +40936,7 @@
         <v>1</v>
       </c>
       <c r="CN124" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CO124" s="2">
         <v>5</v>
@@ -40954,16 +40954,16 @@
         <v>0</v>
       </c>
       <c r="CT124" s="1">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="CU124" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CV124" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CW124" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="125" spans="1:101">
@@ -41599,7 +41599,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I127" s="2">
         <v>5</v>
@@ -41875,7 +41875,7 @@
         <v>1</v>
       </c>
       <c r="CV127" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW127" s="1">
         <v>25</v>
@@ -41889,10 +41889,10 @@
         <v>1050</v>
       </c>
       <c r="C128" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D128" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E128" s="2">
         <v>37</v>
@@ -42000,7 +42000,7 @@
         <v>6</v>
       </c>
       <c r="AN128" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AO128" s="2">
         <v>28</v>
@@ -42144,7 +42144,7 @@
         <v>0</v>
       </c>
       <c r="CJ128" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CK128" s="2">
         <v>20</v>
@@ -42177,10 +42177,10 @@
         <v>2507</v>
       </c>
       <c r="CU128" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CV128" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="CW128" s="1">
         <v>86</v>
@@ -42209,7 +42209,7 @@
         <v>0</v>
       </c>
       <c r="H129" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I129" s="2">
         <v>5</v>
@@ -42485,7 +42485,7 @@
         <v>2</v>
       </c>
       <c r="CV129" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CW129" s="1">
         <v>18</v>
@@ -42610,7 +42610,7 @@
         <v>9</v>
       </c>
       <c r="AN130" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AO130" s="2">
         <v>32</v>
@@ -42754,7 +42754,7 @@
         <v>11</v>
       </c>
       <c r="CJ130" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CK130" s="2">
         <v>23</v>
@@ -42790,7 +42790,7 @@
         <v>178</v>
       </c>
       <c r="CV130" s="1">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="CW130" s="1">
         <v>299</v>
@@ -42807,7 +42807,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" s="2">
         <v>1</v>
@@ -42915,7 +42915,7 @@
         <v>10</v>
       </c>
       <c r="AN131" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO131" s="2">
         <v>20</v>
@@ -43059,7 +43059,7 @@
         <v>7</v>
       </c>
       <c r="CJ131" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CK131" s="2">
         <v>36</v>
@@ -43095,7 +43095,7 @@
         <v>19</v>
       </c>
       <c r="CV131" s="1">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="CW131" s="1">
         <v>189</v>
@@ -43429,7 +43429,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I133" s="2">
         <v>6</v>
@@ -43705,7 +43705,7 @@
         <v>1</v>
       </c>
       <c r="CV133" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW133" s="1">
         <v>6</v>
@@ -44024,10 +44024,10 @@
         <v>298</v>
       </c>
       <c r="C135" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D135" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E135" s="2">
         <v>29</v>
@@ -44099,7 +44099,7 @@
         <v>3</v>
       </c>
       <c r="AB135" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC135" s="2">
         <v>6</v>
@@ -44129,16 +44129,16 @@
         <v>0</v>
       </c>
       <c r="AL135" s="1">
-        <v>1315</v>
+        <v>1322</v>
       </c>
       <c r="AM135" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN135" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AO135" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AP135" s="1">
         <v>35</v>
@@ -44279,7 +44279,7 @@
         <v>26</v>
       </c>
       <c r="CJ135" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CK135" s="2">
         <v>74</v>
@@ -44309,16 +44309,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>128692</v>
+        <v>128699</v>
       </c>
       <c r="CU135" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="CV135" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CW135" s="1">
-        <v>2646</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44332,7 +44332,7 @@
         <v>81</v>
       </c>
       <c r="D136" s="2">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="E136" s="2">
         <v>345</v>
@@ -44356,7 +44356,7 @@
         <v>91</v>
       </c>
       <c r="L136" s="2">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="M136" s="2">
         <v>475</v>
@@ -44404,19 +44404,19 @@
         <v>4</v>
       </c>
       <c r="AB136" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC136" s="2">
         <v>8</v>
       </c>
       <c r="AD136" s="1">
-        <v>11627</v>
+        <v>11628</v>
       </c>
       <c r="AE136" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AF136" s="2">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="AG136" s="2">
         <v>1038</v>
@@ -44440,7 +44440,7 @@
         <v>0</v>
       </c>
       <c r="AN136" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO136" s="2">
         <v>8</v>
@@ -44521,7 +44521,7 @@
         <v>237</v>
       </c>
       <c r="BO136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP136" s="2">
         <v>1</v>
@@ -44584,7 +44584,7 @@
         <v>33</v>
       </c>
       <c r="CJ136" s="2">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="CK136" s="2">
         <v>162</v>
@@ -44614,13 +44614,13 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>60871</v>
+        <v>60872</v>
       </c>
       <c r="CU136" s="1">
         <v>800</v>
       </c>
       <c r="CV136" s="1">
-        <v>1160</v>
+        <v>987</v>
       </c>
       <c r="CW136" s="1">
         <v>2555</v>
@@ -44637,7 +44637,7 @@
         <v>0</v>
       </c>
       <c r="D137" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137" s="2">
         <v>13</v>
@@ -44661,7 +44661,7 @@
         <v>1</v>
       </c>
       <c r="L137" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M137" s="2">
         <v>8</v>
@@ -44889,7 +44889,7 @@
         <v>9</v>
       </c>
       <c r="CJ137" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CK137" s="2">
         <v>30</v>
@@ -44925,7 +44925,7 @@
         <v>952</v>
       </c>
       <c r="CV137" s="1">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="CW137" s="1">
         <v>3411</v>
@@ -44942,7 +44942,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E138" s="2">
         <v>13</v>
@@ -45062,7 +45062,7 @@
         <v>1</v>
       </c>
       <c r="AR138" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS138" s="2">
         <v>6</v>
@@ -45206,7 +45206,7 @@
         <v>1</v>
       </c>
       <c r="CN138" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CO138" s="2">
         <v>4</v>
@@ -45230,7 +45230,7 @@
         <v>3</v>
       </c>
       <c r="CV138" s="1">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="CW138" s="1">
         <v>64</v>
@@ -45271,7 +45271,7 @@
         <v>16</v>
       </c>
       <c r="L139" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="M139" s="2">
         <v>78</v>
@@ -45313,16 +45313,16 @@
         <v>0</v>
       </c>
       <c r="Z139" s="1">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AA139" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB139" s="2">
         <v>3</v>
       </c>
       <c r="AC139" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD139" s="1">
         <v>0</v>
@@ -45355,7 +45355,7 @@
         <v>5</v>
       </c>
       <c r="AN139" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO139" s="2">
         <v>17</v>
@@ -45385,16 +45385,16 @@
         <v>0</v>
       </c>
       <c r="AX139" s="1">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ139" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA139" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB139" s="1">
         <v>90</v>
@@ -45499,7 +45499,7 @@
         <v>5</v>
       </c>
       <c r="CJ139" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CK139" s="2">
         <v>19</v>
@@ -45529,16 +45529,16 @@
         <v>0</v>
       </c>
       <c r="CT139" s="1">
-        <v>4169</v>
+        <v>4173</v>
       </c>
       <c r="CU139" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="CV139" s="1">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="CW139" s="1">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="140" spans="1:101">
@@ -45857,7 +45857,7 @@
         <v>0</v>
       </c>
       <c r="D141" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E141" s="2">
         <v>2</v>
@@ -45881,7 +45881,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M141" s="2">
         <v>4</v>
@@ -45977,7 +45977,7 @@
         <v>1</v>
       </c>
       <c r="AR141" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS141" s="2">
         <v>5</v>
@@ -46109,7 +46109,7 @@
         <v>1</v>
       </c>
       <c r="CJ141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK141" s="2">
         <v>4</v>
@@ -46145,7 +46145,7 @@
         <v>7</v>
       </c>
       <c r="CV141" s="1">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CW141" s="1">
         <v>35</v>
@@ -46174,7 +46174,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2">
         <v>2</v>
@@ -46270,7 +46270,7 @@
         <v>1</v>
       </c>
       <c r="AN142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO142" s="2">
         <v>2</v>
@@ -46426,7 +46426,7 @@
         <v>0</v>
       </c>
       <c r="CN142" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO142" s="2">
         <v>4</v>
@@ -46450,7 +46450,7 @@
         <v>12</v>
       </c>
       <c r="CV142" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CW142" s="1">
         <v>36</v>
@@ -46467,7 +46467,7 @@
         <v>0</v>
       </c>
       <c r="D143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" s="2">
         <v>4</v>
@@ -46587,7 +46587,7 @@
         <v>0</v>
       </c>
       <c r="AR143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS143" s="2">
         <v>3</v>
@@ -46599,7 +46599,7 @@
         <v>2</v>
       </c>
       <c r="AV143" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW143" s="2">
         <v>10</v>
@@ -46731,7 +46731,7 @@
         <v>0</v>
       </c>
       <c r="CN143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO143" s="2">
         <v>4</v>
@@ -46755,7 +46755,7 @@
         <v>10</v>
       </c>
       <c r="CV143" s="1">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="CW143" s="1">
         <v>66</v>
@@ -46784,7 +46784,7 @@
         <v>1</v>
       </c>
       <c r="H144" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I144" s="2">
         <v>5</v>
@@ -46892,7 +46892,7 @@
         <v>1</v>
       </c>
       <c r="AR144" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS144" s="2">
         <v>5</v>
@@ -47036,7 +47036,7 @@
         <v>0</v>
       </c>
       <c r="CN144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO144" s="2">
         <v>3</v>
@@ -47060,7 +47060,7 @@
         <v>3</v>
       </c>
       <c r="CV144" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW144" s="1">
         <v>22</v>
@@ -47185,7 +47185,7 @@
         <v>1</v>
       </c>
       <c r="AN145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO145" s="2">
         <v>2</v>
@@ -47341,7 +47341,7 @@
         <v>1</v>
       </c>
       <c r="CN145" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO145" s="2">
         <v>4</v>
@@ -47365,7 +47365,7 @@
         <v>6</v>
       </c>
       <c r="CV145" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="CW145" s="1">
         <v>107</v>
@@ -47526,7 +47526,7 @@
         <v>0</v>
       </c>
       <c r="AZ146" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA146" s="2">
         <v>5</v>
@@ -47670,7 +47670,7 @@
         <v>16</v>
       </c>
       <c r="CV146" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="CW146" s="1">
         <v>92</v>
@@ -48004,7 +48004,7 @@
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I148" s="2">
         <v>6</v>
@@ -48100,7 +48100,7 @@
         <v>0</v>
       </c>
       <c r="AN148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO148" s="2">
         <v>1</v>
@@ -48247,7 +48247,7 @@
         <v>2</v>
       </c>
       <c r="CK148" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CL148" s="1">
         <v>22</v>
@@ -48256,7 +48256,7 @@
         <v>0</v>
       </c>
       <c r="CN148" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO148" s="2">
         <v>2</v>
@@ -48280,10 +48280,10 @@
         <v>1</v>
       </c>
       <c r="CV148" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CW148" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -48297,7 +48297,7 @@
         <v>0</v>
       </c>
       <c r="D149" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E149" s="2">
         <v>11</v>
@@ -48321,7 +48321,7 @@
         <v>4</v>
       </c>
       <c r="L149" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M149" s="2">
         <v>24</v>
@@ -48405,7 +48405,7 @@
         <v>6</v>
       </c>
       <c r="AN149" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AO149" s="2">
         <v>21</v>
@@ -48417,7 +48417,7 @@
         <v>0</v>
       </c>
       <c r="AR149" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS149" s="2">
         <v>2</v>
@@ -48441,7 +48441,7 @@
         <v>0</v>
       </c>
       <c r="AZ149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA149" s="2">
         <v>1</v>
@@ -48549,7 +48549,7 @@
         <v>7</v>
       </c>
       <c r="CJ149" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CK149" s="2">
         <v>42</v>
@@ -48585,7 +48585,7 @@
         <v>18</v>
       </c>
       <c r="CV149" s="1">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="CW149" s="1">
         <v>165</v>
@@ -48722,7 +48722,7 @@
         <v>2</v>
       </c>
       <c r="AR150" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS150" s="2">
         <v>6</v>
@@ -48854,7 +48854,7 @@
         <v>4</v>
       </c>
       <c r="CJ150" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CK150" s="2">
         <v>8</v>
@@ -48890,7 +48890,7 @@
         <v>6</v>
       </c>
       <c r="CV150" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW150" s="1">
         <v>35</v>
@@ -49027,7 +49027,7 @@
         <v>1</v>
       </c>
       <c r="AR151" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS151" s="2">
         <v>6</v>
@@ -49171,7 +49171,7 @@
         <v>1</v>
       </c>
       <c r="CN151" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO151" s="2">
         <v>4</v>
@@ -49195,7 +49195,7 @@
         <v>2</v>
       </c>
       <c r="CV151" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CW151" s="1">
         <v>14</v>
@@ -49332,7 +49332,7 @@
         <v>1</v>
       </c>
       <c r="AR152" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS152" s="2">
         <v>5</v>
@@ -49413,7 +49413,7 @@
         <v>28</v>
       </c>
       <c r="BS152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT152" s="2">
         <v>1</v>
@@ -49476,7 +49476,7 @@
         <v>0</v>
       </c>
       <c r="CN152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO152" s="2">
         <v>2</v>
@@ -49497,10 +49497,10 @@
         <v>423</v>
       </c>
       <c r="CU152" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV152" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW152" s="1">
         <v>26</v>
@@ -49517,7 +49517,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E153" s="2">
         <v>9</v>
@@ -49541,7 +49541,7 @@
         <v>11</v>
       </c>
       <c r="L153" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="M153" s="2">
         <v>91</v>
@@ -49637,7 +49637,7 @@
         <v>1</v>
       </c>
       <c r="AR153" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS153" s="2">
         <v>6</v>
@@ -49769,7 +49769,7 @@
         <v>4</v>
       </c>
       <c r="CJ153" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK153" s="2">
         <v>25</v>
@@ -49805,7 +49805,7 @@
         <v>135</v>
       </c>
       <c r="CV153" s="1">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="CW153" s="1">
         <v>292</v>
@@ -50444,7 +50444,7 @@
         <v>1</v>
       </c>
       <c r="H156" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I156" s="2">
         <v>3</v>
@@ -50456,7 +50456,7 @@
         <v>6</v>
       </c>
       <c r="L156" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M156" s="2">
         <v>34</v>
@@ -50468,7 +50468,7 @@
         <v>3</v>
       </c>
       <c r="P156" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q156" s="2">
         <v>7</v>
@@ -50552,7 +50552,7 @@
         <v>1</v>
       </c>
       <c r="AR156" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS156" s="2">
         <v>6</v>
@@ -50684,7 +50684,7 @@
         <v>1</v>
       </c>
       <c r="CJ156" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CK156" s="2">
         <v>25</v>
@@ -50720,7 +50720,7 @@
         <v>13</v>
       </c>
       <c r="CV156" s="1">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="CW156" s="1">
         <v>86</v>
@@ -50737,7 +50737,7 @@
         <v>8</v>
       </c>
       <c r="D157" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E157" s="2">
         <v>57</v>
@@ -50755,16 +50755,16 @@
         <v>0</v>
       </c>
       <c r="J157" s="1">
-        <v>1981</v>
+        <v>1997</v>
       </c>
       <c r="K157" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L157" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="M157" s="2">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="N157" s="1">
         <v>59119</v>
@@ -50857,7 +50857,7 @@
         <v>0</v>
       </c>
       <c r="AR157" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS157" s="2">
         <v>5</v>
@@ -50989,7 +50989,7 @@
         <v>20</v>
       </c>
       <c r="CJ157" s="2">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="CK157" s="2">
         <v>74</v>
@@ -51019,16 +51019,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>69329</v>
+        <v>69345</v>
       </c>
       <c r="CU157" s="1">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="CV157" s="1">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="CW157" s="1">
-        <v>1486</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51042,7 +51042,7 @@
         <v>44</v>
       </c>
       <c r="D158" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E158" s="2">
         <v>148</v>
@@ -51066,7 +51066,7 @@
         <v>53</v>
       </c>
       <c r="L158" s="2">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="M158" s="2">
         <v>260</v>
@@ -51114,7 +51114,7 @@
         <v>0</v>
       </c>
       <c r="AB158" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AC158" s="2">
         <v>9</v>
@@ -51126,7 +51126,7 @@
         <v>3513</v>
       </c>
       <c r="AF158" s="2">
-        <v>4789</v>
+        <v>3513</v>
       </c>
       <c r="AG158" s="2">
         <v>4789</v>
@@ -51162,7 +51162,7 @@
         <v>0</v>
       </c>
       <c r="AR158" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS158" s="2">
         <v>5</v>
@@ -51174,7 +51174,7 @@
         <v>0</v>
       </c>
       <c r="AV158" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW158" s="2">
         <v>3</v>
@@ -51294,7 +51294,7 @@
         <v>39</v>
       </c>
       <c r="CJ158" s="2">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="CK158" s="2">
         <v>199</v>
@@ -51330,7 +51330,7 @@
         <v>3652</v>
       </c>
       <c r="CV158" s="1">
-        <v>5126</v>
+        <v>3766</v>
       </c>
       <c r="CW158" s="1">
         <v>5544</v>
@@ -51347,7 +51347,7 @@
         <v>134</v>
       </c>
       <c r="D159" s="2">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="E159" s="2">
         <v>421</v>
@@ -51371,7 +51371,7 @@
         <v>87</v>
       </c>
       <c r="L159" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M159" s="2">
         <v>437</v>
@@ -51383,7 +51383,7 @@
         <v>92</v>
       </c>
       <c r="P159" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Q159" s="2">
         <v>165</v>
@@ -51419,7 +51419,7 @@
         <v>0</v>
       </c>
       <c r="AB159" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC159" s="2">
         <v>7</v>
@@ -51599,7 +51599,7 @@
         <v>136</v>
       </c>
       <c r="CJ159" s="2">
-        <v>274</v>
+        <v>204</v>
       </c>
       <c r="CK159" s="2">
         <v>639</v>
@@ -51635,7 +51635,7 @@
         <v>462</v>
       </c>
       <c r="CV159" s="1">
-        <v>869</v>
+        <v>744</v>
       </c>
       <c r="CW159" s="1">
         <v>1724</v>
@@ -51957,7 +51957,7 @@
         <v>1</v>
       </c>
       <c r="D161" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E161" s="2">
         <v>5</v>
@@ -51969,7 +51969,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I161" s="2">
         <v>5</v>
@@ -52245,7 +52245,7 @@
         <v>2</v>
       </c>
       <c r="CV161" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CW161" s="1">
         <v>10</v>
@@ -52262,7 +52262,7 @@
         <v>20</v>
       </c>
       <c r="D162" s="2">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="E162" s="2">
         <v>114</v>
@@ -52286,7 +52286,7 @@
         <v>27</v>
       </c>
       <c r="L162" s="2">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="M162" s="2">
         <v>159</v>
@@ -52334,7 +52334,7 @@
         <v>4</v>
       </c>
       <c r="AB162" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC162" s="2">
         <v>8</v>
@@ -52370,7 +52370,7 @@
         <v>2</v>
       </c>
       <c r="AN162" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO162" s="2">
         <v>4</v>
@@ -52385,7 +52385,7 @@
         <v>1</v>
       </c>
       <c r="AS162" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT162" s="1">
         <v>6</v>
@@ -52463,7 +52463,7 @@
         <v>7</v>
       </c>
       <c r="BS162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT162" s="2">
         <v>1</v>
@@ -52514,10 +52514,10 @@
         <v>8</v>
       </c>
       <c r="CJ162" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CK162" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="CL162" s="1">
         <v>14</v>
@@ -52547,13 +52547,13 @@
         <v>21364</v>
       </c>
       <c r="CU162" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="CV162" s="1">
-        <v>348</v>
+        <v>259</v>
       </c>
       <c r="CW162" s="1">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="163" spans="1:101">
@@ -52980,7 +52980,7 @@
         <v>0</v>
       </c>
       <c r="AN164" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO164" s="2">
         <v>4</v>
@@ -53118,16 +53118,16 @@
         <v>0</v>
       </c>
       <c r="CH164" s="1">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="CI164" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ164" s="2">
         <v>9</v>
       </c>
       <c r="CK164" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CL164" s="1">
         <v>49</v>
@@ -53154,16 +53154,16 @@
         <v>0</v>
       </c>
       <c r="CT164" s="1">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="CU164" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CV164" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CW164" s="1">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53189,7 +53189,7 @@
         <v>1</v>
       </c>
       <c r="H165" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I165" s="2">
         <v>6</v>
@@ -53201,7 +53201,7 @@
         <v>7</v>
       </c>
       <c r="L165" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M165" s="2">
         <v>19</v>
@@ -53213,7 +53213,7 @@
         <v>23</v>
       </c>
       <c r="P165" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q165" s="2">
         <v>37</v>
@@ -53297,7 +53297,7 @@
         <v>1</v>
       </c>
       <c r="AR165" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS165" s="2">
         <v>5</v>
@@ -53429,7 +53429,7 @@
         <v>5</v>
       </c>
       <c r="CJ165" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CK165" s="2">
         <v>19</v>
@@ -53465,7 +53465,7 @@
         <v>88</v>
       </c>
       <c r="CV165" s="1">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="CW165" s="1">
         <v>158</v>
@@ -53494,7 +53494,7 @@
         <v>3</v>
       </c>
       <c r="H166" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I166" s="2">
         <v>5</v>
@@ -53770,7 +53770,7 @@
         <v>3</v>
       </c>
       <c r="CV166" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW166" s="1">
         <v>7</v>
@@ -53787,7 +53787,7 @@
         <v>4</v>
       </c>
       <c r="D167" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E167" s="2">
         <v>24</v>
@@ -53811,10 +53811,10 @@
         <v>28</v>
       </c>
       <c r="L167" s="2">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="M167" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="N167" s="1">
         <v>2048</v>
@@ -53901,16 +53901,16 @@
         <v>0</v>
       </c>
       <c r="AP167" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AQ167" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR167" s="2">
         <v>3</v>
       </c>
       <c r="AS167" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT167" s="1">
         <v>0</v>
@@ -54039,22 +54039,22 @@
         <v>1</v>
       </c>
       <c r="CJ167" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK167" s="2">
         <v>7</v>
       </c>
       <c r="CL167" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CM167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN167" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO167" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP167" s="1">
         <v>0</v>
@@ -54069,16 +54069,16 @@
         <v>0</v>
       </c>
       <c r="CT167" s="1">
-        <v>4976</v>
+        <v>4978</v>
       </c>
       <c r="CU167" s="1">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="CV167" s="1">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="CW167" s="1">
-        <v>406</v>
+        <v>376</v>
       </c>
     </row>
     <row r="168" spans="1:101">
@@ -54409,7 +54409,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" s="2">
         <v>1</v>
@@ -54421,7 +54421,7 @@
         <v>31</v>
       </c>
       <c r="L169" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="M169" s="2">
         <v>173</v>
@@ -54433,7 +54433,7 @@
         <v>0</v>
       </c>
       <c r="P169" s="2">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="Q169" s="2">
         <v>52</v>
@@ -54502,10 +54502,10 @@
         <v>28</v>
       </c>
       <c r="AM169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN169" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO169" s="2">
         <v>4</v>
@@ -54646,10 +54646,10 @@
         <v>392</v>
       </c>
       <c r="CI169" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CJ169" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CK169" s="2">
         <v>48</v>
@@ -54682,10 +54682,10 @@
         <v>5752</v>
       </c>
       <c r="CU169" s="1">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="CV169" s="1">
-        <v>473</v>
+        <v>417</v>
       </c>
       <c r="CW169" s="1">
         <v>638</v>
@@ -54708,16 +54708,16 @@
         <v>1</v>
       </c>
       <c r="F170" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G170" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" s="2">
         <v>3</v>
       </c>
       <c r="I170" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J170" s="1">
         <v>0</v>
@@ -54810,7 +54810,7 @@
         <v>7</v>
       </c>
       <c r="AN170" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AO170" s="2">
         <v>22</v>
@@ -54954,7 +54954,7 @@
         <v>16</v>
       </c>
       <c r="CJ170" s="2">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="CK170" s="2">
         <v>41</v>
@@ -54984,16 +54984,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="CU170" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CV170" s="1">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="CW170" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -55007,7 +55007,7 @@
         <v>38</v>
       </c>
       <c r="D171" s="2">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="E171" s="2">
         <v>200</v>
@@ -55031,7 +55031,7 @@
         <v>80</v>
       </c>
       <c r="L171" s="2">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="M171" s="2">
         <v>395</v>
@@ -55091,7 +55091,7 @@
         <v>287</v>
       </c>
       <c r="AF171" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG171" s="2">
         <v>364</v>
@@ -55115,7 +55115,7 @@
         <v>1</v>
       </c>
       <c r="AN171" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO171" s="2">
         <v>12</v>
@@ -55259,7 +55259,7 @@
         <v>52</v>
       </c>
       <c r="CJ171" s="2">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="CK171" s="2">
         <v>175</v>
@@ -55295,7 +55295,7 @@
         <v>539</v>
       </c>
       <c r="CV171" s="1">
-        <v>764</v>
+        <v>643</v>
       </c>
       <c r="CW171" s="1">
         <v>1310</v>
@@ -55312,7 +55312,7 @@
         <v>0</v>
       </c>
       <c r="D172" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E172" s="2">
         <v>6</v>
@@ -55564,7 +55564,7 @@
         <v>7</v>
       </c>
       <c r="CJ172" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK172" s="2">
         <v>23</v>
@@ -55600,7 +55600,7 @@
         <v>12</v>
       </c>
       <c r="CV172" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CW172" s="1">
         <v>71</v>
@@ -56227,7 +56227,7 @@
         <v>0</v>
       </c>
       <c r="D175" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" s="2">
         <v>1</v>
@@ -56263,7 +56263,7 @@
         <v>0</v>
       </c>
       <c r="P175" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q175" s="2">
         <v>5</v>
@@ -56347,7 +56347,7 @@
         <v>0</v>
       </c>
       <c r="AR175" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS175" s="2">
         <v>6</v>
@@ -56491,7 +56491,7 @@
         <v>0</v>
       </c>
       <c r="CN175" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO175" s="2">
         <v>6</v>
@@ -56515,7 +56515,7 @@
         <v>1</v>
       </c>
       <c r="CV175" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CW175" s="1">
         <v>23</v>
@@ -56837,7 +56837,7 @@
         <v>4</v>
       </c>
       <c r="D177" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E177" s="2">
         <v>7</v>
@@ -56945,7 +56945,7 @@
         <v>1</v>
       </c>
       <c r="AN177" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AO177" s="2">
         <v>94</v>
@@ -57089,7 +57089,7 @@
         <v>3</v>
       </c>
       <c r="CJ177" s="2">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="CK177" s="2">
         <v>151</v>
@@ -57125,7 +57125,7 @@
         <v>8</v>
       </c>
       <c r="CV177" s="1">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="CW177" s="1">
         <v>256</v>
@@ -57447,7 +57447,7 @@
         <v>34</v>
       </c>
       <c r="D179" s="2">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E179" s="2">
         <v>203</v>
@@ -57471,7 +57471,7 @@
         <v>18</v>
       </c>
       <c r="L179" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M179" s="2">
         <v>83</v>
@@ -57555,7 +57555,7 @@
         <v>4</v>
       </c>
       <c r="AN179" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO179" s="2">
         <v>18</v>
@@ -57618,7 +57618,7 @@
         <v>0</v>
       </c>
       <c r="BI179" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="BJ179" s="1">
         <v>0</v>
@@ -57699,7 +57699,7 @@
         <v>30</v>
       </c>
       <c r="CJ179" s="2">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="CK179" s="2">
         <v>157</v>
@@ -57735,10 +57735,10 @@
         <v>86</v>
       </c>
       <c r="CV179" s="1">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="CW179" s="1">
-        <v>2598</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -57764,7 +57764,7 @@
         <v>1</v>
       </c>
       <c r="H180" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I180" s="2">
         <v>4</v>
@@ -57857,7 +57857,7 @@
         <v>513</v>
       </c>
       <c r="AM180" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN180" s="2">
         <v>20</v>
@@ -58037,10 +58037,10 @@
         <v>799</v>
       </c>
       <c r="CU180" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CV180" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CW180" s="1">
         <v>74</v>
@@ -58054,10 +58054,10 @@
         <v>7959</v>
       </c>
       <c r="C181" s="2">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="D181" s="2">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="E181" s="2">
         <v>298</v>
@@ -58081,7 +58081,7 @@
         <v>44</v>
       </c>
       <c r="L181" s="2">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="M181" s="2">
         <v>204</v>
@@ -58135,16 +58135,16 @@
         <v>0</v>
       </c>
       <c r="AD181" s="1">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AE181" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF181" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG181" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH181" s="1">
         <v>1</v>
@@ -58165,7 +58165,7 @@
         <v>1</v>
       </c>
       <c r="AN181" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO181" s="2">
         <v>8</v>
@@ -58309,7 +58309,7 @@
         <v>40</v>
       </c>
       <c r="CJ181" s="2">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="CK181" s="2">
         <v>100</v>
@@ -58339,16 +58339,16 @@
         <v>0</v>
       </c>
       <c r="CT181" s="1">
-        <v>48733</v>
+        <v>48734</v>
       </c>
       <c r="CU181" s="1">
-        <v>243</v>
+        <v>186</v>
       </c>
       <c r="CV181" s="1">
-        <v>429</v>
+        <v>348</v>
       </c>
       <c r="CW181" s="1">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -58374,7 +58374,7 @@
         <v>1</v>
       </c>
       <c r="H182" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I182" s="2">
         <v>6</v>
@@ -58650,7 +58650,7 @@
         <v>1</v>
       </c>
       <c r="CV182" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW182" s="1">
         <v>6</v>
@@ -58919,7 +58919,7 @@
         <v>12</v>
       </c>
       <c r="CJ183" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CK183" s="2">
         <v>35</v>
@@ -58955,7 +58955,7 @@
         <v>12</v>
       </c>
       <c r="CV183" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CW183" s="1">
         <v>42</v>
@@ -59582,7 +59582,7 @@
         <v>0</v>
       </c>
       <c r="D186" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E186" s="2">
         <v>2</v>
@@ -59594,7 +59594,7 @@
         <v>1</v>
       </c>
       <c r="H186" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I186" s="2">
         <v>5</v>
@@ -59696,16 +59696,16 @@
         <v>0</v>
       </c>
       <c r="AP186" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ186" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR186" s="2">
         <v>3</v>
       </c>
       <c r="AS186" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT186" s="1">
         <v>0</v>
@@ -59840,16 +59840,16 @@
         <v>0</v>
       </c>
       <c r="CL186" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CM186" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN186" s="2">
         <v>3</v>
       </c>
       <c r="CO186" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CP186" s="1">
         <v>0</v>
@@ -59864,16 +59864,16 @@
         <v>0</v>
       </c>
       <c r="CT186" s="1">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="CU186" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV186" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CW186" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" spans="1:101">
@@ -60204,7 +60204,7 @@
         <v>1</v>
       </c>
       <c r="H188" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I188" s="2">
         <v>6</v>
@@ -60480,7 +60480,7 @@
         <v>1</v>
       </c>
       <c r="CV188" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW188" s="1">
         <v>6</v>
@@ -60814,7 +60814,7 @@
         <v>1</v>
       </c>
       <c r="H190" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I190" s="2">
         <v>6</v>
@@ -61090,7 +61090,7 @@
         <v>1</v>
       </c>
       <c r="CV190" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW190" s="1">
         <v>6</v>
@@ -61107,7 +61107,7 @@
         <v>0</v>
       </c>
       <c r="D191" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E191" s="2">
         <v>3</v>
@@ -61119,7 +61119,7 @@
         <v>2</v>
       </c>
       <c r="H191" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I191" s="2">
         <v>5</v>
@@ -61395,7 +61395,7 @@
         <v>23</v>
       </c>
       <c r="CV191" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CW191" s="1">
         <v>42</v>
@@ -61424,7 +61424,7 @@
         <v>1</v>
       </c>
       <c r="H192" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I192" s="2">
         <v>6</v>
@@ -61526,16 +61526,16 @@
         <v>2</v>
       </c>
       <c r="AP192" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AQ192" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR192" s="2">
         <v>2</v>
       </c>
       <c r="AS192" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT192" s="1">
         <v>0</v>
@@ -61658,16 +61658,16 @@
         <v>0</v>
       </c>
       <c r="CH192" s="1">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="CI192" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ192" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CK192" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CL192" s="1">
         <v>37</v>
@@ -61694,16 +61694,16 @@
         <v>0</v>
       </c>
       <c r="CT192" s="1">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="CU192" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CV192" s="1">
         <v>17</v>
       </c>
       <c r="CW192" s="1">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62022,7 +62022,7 @@
         <v>14</v>
       </c>
       <c r="D194" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E194" s="2">
         <v>46</v>
@@ -62046,7 +62046,7 @@
         <v>10</v>
       </c>
       <c r="L194" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="M194" s="2">
         <v>59</v>
@@ -62058,7 +62058,7 @@
         <v>0</v>
       </c>
       <c r="P194" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q194" s="2">
         <v>448</v>
@@ -62094,7 +62094,7 @@
         <v>5</v>
       </c>
       <c r="AB194" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AC194" s="2">
         <v>11</v>
@@ -62142,7 +62142,7 @@
         <v>1</v>
       </c>
       <c r="AR194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS194" s="2">
         <v>6</v>
@@ -62166,7 +62166,7 @@
         <v>1</v>
       </c>
       <c r="AZ194" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA194" s="2">
         <v>3</v>
@@ -62274,7 +62274,7 @@
         <v>0</v>
       </c>
       <c r="CJ194" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CK194" s="2">
         <v>14</v>
@@ -62310,7 +62310,7 @@
         <v>32</v>
       </c>
       <c r="CV194" s="1">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="CW194" s="1">
         <v>594</v>
@@ -62327,7 +62327,7 @@
         <v>0</v>
       </c>
       <c r="D195" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E195" s="2">
         <v>10</v>
@@ -62579,7 +62579,7 @@
         <v>10</v>
       </c>
       <c r="CJ195" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CK195" s="2">
         <v>28</v>
@@ -62615,7 +62615,7 @@
         <v>1914</v>
       </c>
       <c r="CV195" s="1">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="CW195" s="1">
         <v>2900</v>
@@ -62656,22 +62656,22 @@
         <v>4</v>
       </c>
       <c r="L196" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M196" s="2">
         <v>34</v>
       </c>
       <c r="N196" s="1">
-        <v>3282</v>
+        <v>3362</v>
       </c>
       <c r="O196" s="2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P196" s="2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q196" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="R196" s="1">
         <v>0</v>
@@ -62686,16 +62686,16 @@
         <v>0</v>
       </c>
       <c r="V196" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z196" s="1">
         <v>100</v>
@@ -62704,7 +62704,7 @@
         <v>4</v>
       </c>
       <c r="AB196" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC196" s="2">
         <v>8</v>
@@ -62914,16 +62914,16 @@
         <v>0</v>
       </c>
       <c r="CT196" s="1">
-        <v>5291</v>
+        <v>5372</v>
       </c>
       <c r="CU196" s="1">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="CV196" s="1">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="CW196" s="1">
-        <v>162</v>
+        <v>243</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -63852,7 +63852,7 @@
         <v>37</v>
       </c>
       <c r="D200" s="2">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E200" s="2">
         <v>158</v>
@@ -63876,7 +63876,7 @@
         <v>30</v>
       </c>
       <c r="L200" s="2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="M200" s="2">
         <v>121</v>
@@ -63960,7 +63960,7 @@
         <v>5</v>
       </c>
       <c r="AN200" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AO200" s="2">
         <v>21</v>
@@ -64104,7 +64104,7 @@
         <v>34</v>
       </c>
       <c r="CJ200" s="2">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="CK200" s="2">
         <v>99</v>
@@ -64140,7 +64140,7 @@
         <v>108</v>
       </c>
       <c r="CV200" s="1">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="CW200" s="1">
         <v>482</v>
@@ -64157,10 +64157,10 @@
         <v>0</v>
       </c>
       <c r="D201" s="2">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="E201" s="2">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="F201" s="1">
         <v>0</v>
@@ -64181,7 +64181,7 @@
         <v>61</v>
       </c>
       <c r="L201" s="2">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="M201" s="2">
         <v>238</v>
@@ -64238,7 +64238,7 @@
         <v>46598</v>
       </c>
       <c r="AE201" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="AF201" s="2">
         <v>440</v>
@@ -64277,7 +64277,7 @@
         <v>1</v>
       </c>
       <c r="AR201" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS201" s="2">
         <v>2</v>
@@ -64409,7 +64409,7 @@
         <v>45</v>
       </c>
       <c r="CJ201" s="2">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="CK201" s="2">
         <v>144</v>
@@ -64442,13 +64442,13 @@
         <v>85517</v>
       </c>
       <c r="CU201" s="1">
-        <v>547</v>
+        <v>580</v>
       </c>
       <c r="CV201" s="1">
-        <v>747</v>
+        <v>671</v>
       </c>
       <c r="CW201" s="1">
-        <v>1825</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64456,28 +64456,28 @@
         <v>301</v>
       </c>
       <c r="B202" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C202" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D202" s="2">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E202" s="2">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F202" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G202" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H202" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I202" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J202" s="1">
         <v>0</v>
@@ -64744,16 +64744,16 @@
         <v>0</v>
       </c>
       <c r="CT202" s="1">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="CU202" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="CV202" s="1">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="CW202" s="1">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="203" spans="1:101">
@@ -65087,7 +65087,7 @@
         <v>3</v>
       </c>
       <c r="I204" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J204" s="1">
         <v>0</v>
@@ -65363,7 +65363,7 @@
         <v>3</v>
       </c>
       <c r="CW204" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:101">
@@ -65682,7 +65682,7 @@
         <v>5</v>
       </c>
       <c r="D206" s="2">
-        <v>-25</v>
+        <v>-31</v>
       </c>
       <c r="E206" s="2">
         <v>-18</v>
@@ -65718,7 +65718,7 @@
         <v>0</v>
       </c>
       <c r="P206" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q206" s="2">
         <v>12</v>
@@ -65802,7 +65802,7 @@
         <v>0</v>
       </c>
       <c r="AR206" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS206" s="2">
         <v>4</v>
@@ -65934,7 +65934,7 @@
         <v>2</v>
       </c>
       <c r="CJ206" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="CK206" s="2">
         <v>16</v>
@@ -65946,7 +65946,7 @@
         <v>0</v>
       </c>
       <c r="CN206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO206" s="2">
         <v>2</v>
@@ -65970,7 +65970,7 @@
         <v>10</v>
       </c>
       <c r="CV206" s="1">
-        <v>10</v>
+        <v>-21</v>
       </c>
       <c r="CW206" s="1">
         <v>25</v>
@@ -65987,7 +65987,7 @@
         <v>11</v>
       </c>
       <c r="D207" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E207" s="2">
         <v>57</v>
@@ -66011,7 +66011,7 @@
         <v>10</v>
       </c>
       <c r="L207" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="M207" s="2">
         <v>67</v>
@@ -66059,7 +66059,7 @@
         <v>0</v>
       </c>
       <c r="AB207" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC207" s="2">
         <v>3</v>
@@ -66107,7 +66107,7 @@
         <v>1</v>
       </c>
       <c r="AR207" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS207" s="2">
         <v>6</v>
@@ -66188,7 +66188,7 @@
         <v>16</v>
       </c>
       <c r="BS207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT207" s="2">
         <v>1</v>
@@ -66239,7 +66239,7 @@
         <v>10</v>
       </c>
       <c r="CJ207" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="CK207" s="2">
         <v>73</v>
@@ -66272,10 +66272,10 @@
         <v>13577</v>
       </c>
       <c r="CU207" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="CV207" s="1">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="CW207" s="1">
         <v>394</v>
@@ -66292,7 +66292,7 @@
         <v>0</v>
       </c>
       <c r="D208" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E208" s="2">
         <v>9</v>
@@ -66580,7 +66580,7 @@
         <v>1</v>
       </c>
       <c r="CV208" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW208" s="1">
         <v>10</v>
@@ -66705,7 +66705,7 @@
         <v>0</v>
       </c>
       <c r="AN209" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO209" s="2">
         <v>15</v>
@@ -66849,7 +66849,7 @@
         <v>0</v>
       </c>
       <c r="CJ209" s="2">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="CK209" s="2">
         <v>169</v>
@@ -66885,7 +66885,7 @@
         <v>0</v>
       </c>
       <c r="CV209" s="1">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="CW209" s="1">
         <v>197</v>
@@ -66914,7 +66914,7 @@
         <v>1</v>
       </c>
       <c r="H210" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I210" s="2">
         <v>4</v>
@@ -67022,7 +67022,7 @@
         <v>1</v>
       </c>
       <c r="AR210" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS210" s="2">
         <v>6</v>
@@ -67166,7 +67166,7 @@
         <v>0</v>
       </c>
       <c r="CN210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO210" s="2">
         <v>2</v>
@@ -67190,7 +67190,7 @@
         <v>4</v>
       </c>
       <c r="CV210" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CW210" s="1">
         <v>36</v>
@@ -67207,7 +67207,7 @@
         <v>4</v>
       </c>
       <c r="D211" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E211" s="2">
         <v>12</v>
@@ -67231,7 +67231,7 @@
         <v>7</v>
       </c>
       <c r="L211" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="M211" s="2">
         <v>60</v>
@@ -67291,7 +67291,7 @@
         <v>59</v>
       </c>
       <c r="AF211" s="2">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="AG211" s="2">
         <v>68</v>
@@ -67327,7 +67327,7 @@
         <v>1</v>
       </c>
       <c r="AR211" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS211" s="2">
         <v>7</v>
@@ -67459,7 +67459,7 @@
         <v>28</v>
       </c>
       <c r="CJ211" s="2">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="CK211" s="2">
         <v>67</v>
@@ -67495,7 +67495,7 @@
         <v>99</v>
       </c>
       <c r="CV211" s="1">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="CW211" s="1">
         <v>235</v>
@@ -67925,7 +67925,7 @@
         <v>2</v>
       </c>
       <c r="AN213" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO213" s="2">
         <v>9</v>
@@ -68069,7 +68069,7 @@
         <v>4</v>
       </c>
       <c r="CJ213" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CK213" s="2">
         <v>18</v>
@@ -68105,7 +68105,7 @@
         <v>6</v>
       </c>
       <c r="CV213" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CW213" s="1">
         <v>33</v>
@@ -68116,16 +68116,16 @@
         <v>313</v>
       </c>
       <c r="B214" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C214" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D214" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E214" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F214" s="1">
         <v>65</v>
@@ -68134,7 +68134,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I214" s="2">
         <v>4</v>
@@ -68404,16 +68404,16 @@
         <v>0</v>
       </c>
       <c r="CT214" s="1">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CU214" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV214" s="1">
         <v>2</v>
       </c>
       <c r="CW214" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -69946,7 +69946,7 @@
         <v>595</v>
       </c>
       <c r="D76">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E76" t="s">
         <v>717</v>
@@ -70006,7 +70006,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E79" t="s">
         <v>717</v>
@@ -70472,7 +70472,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2971</v>
+        <v>2967</v>
       </c>
       <c r="E102" t="s">
         <v>717</v>
@@ -70552,7 +70552,7 @@
         <v>622</v>
       </c>
       <c r="D106">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E106" t="s">
         <v>717</v>
@@ -71215,7 +71215,7 @@
         <v>652</v>
       </c>
       <c r="D139">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E139" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15049,7 +15049,7 @@
         <v>8624</v>
       </c>
       <c r="C40" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D40" s="2">
         <v>159</v>
@@ -15337,7 +15337,7 @@
         <v>52295</v>
       </c>
       <c r="CU40" s="1">
-        <v>923</v>
+        <v>838</v>
       </c>
       <c r="CV40" s="1">
         <v>1062</v>
@@ -16305,7 +16305,7 @@
         <v>1578</v>
       </c>
       <c r="O44" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="P44" s="2">
         <v>39</v>
@@ -16557,7 +16557,7 @@
         <v>48656</v>
       </c>
       <c r="CU44" s="1">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="CV44" s="1">
         <v>481</v>
@@ -18401,16 +18401,16 @@
         <v>150</v>
       </c>
       <c r="B51" s="1">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="C51" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E51" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -18689,16 +18689,16 @@
         <v>0</v>
       </c>
       <c r="CT51" s="1">
-        <v>1670</v>
+        <v>1679</v>
       </c>
       <c r="CU51" s="1">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="CV51" s="1">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="CW51" s="1">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -22064,7 +22064,7 @@
         <v>499</v>
       </c>
       <c r="C63" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D63" s="2">
         <v>11</v>
@@ -22352,7 +22352,7 @@
         <v>2777</v>
       </c>
       <c r="CU63" s="1">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="CV63" s="1">
         <v>92</v>
@@ -22794,7 +22794,7 @@
         <v>60</v>
       </c>
       <c r="AQ65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR65" s="2">
         <v>2</v>
@@ -22926,7 +22926,7 @@
         <v>1828</v>
       </c>
       <c r="CI65" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CJ65" s="2">
         <v>22</v>
@@ -22938,7 +22938,7 @@
         <v>34</v>
       </c>
       <c r="CM65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN65" s="2">
         <v>2</v>
@@ -22962,7 +22962,7 @@
         <v>63783</v>
       </c>
       <c r="CU65" s="1">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="CV65" s="1">
         <v>157</v>
@@ -23610,16 +23610,16 @@
         <v>1</v>
       </c>
       <c r="J68" s="1">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K68" s="2">
+        <v>4</v>
+      </c>
+      <c r="L68" s="2">
         <v>6</v>
       </c>
-      <c r="L68" s="2">
-        <v>8</v>
-      </c>
       <c r="M68" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N68" s="1">
         <v>1051</v>
@@ -23874,16 +23874,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="CU68" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CV68" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="CW68" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -25503,7 +25503,7 @@
         <v>16001</v>
       </c>
       <c r="AE74" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AF74" s="2">
         <v>331</v>
@@ -25527,7 +25527,7 @@
         <v>36001</v>
       </c>
       <c r="AM74" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AN74" s="2">
         <v>134</v>
@@ -25671,7 +25671,7 @@
         <v>15897</v>
       </c>
       <c r="CI74" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="CJ74" s="2">
         <v>145</v>
@@ -25707,7 +25707,7 @@
         <v>169497</v>
       </c>
       <c r="CU74" s="1">
-        <v>2115</v>
+        <v>2090</v>
       </c>
       <c r="CV74" s="1">
         <v>2292</v>
@@ -26065,7 +26065,7 @@
         <v>115143</v>
       </c>
       <c r="O76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" s="2">
         <v>28</v>
@@ -26317,7 +26317,7 @@
         <v>148085</v>
       </c>
       <c r="CU76" s="1">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="CV76" s="1">
         <v>842</v>
@@ -26439,16 +26439,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="AM77" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN77" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO77" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26619,16 +26619,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>370929</v>
+        <v>370932</v>
       </c>
       <c r="CU77" s="1">
-        <v>-4143</v>
+        <v>-4140</v>
       </c>
       <c r="CV77" s="1">
-        <v>-3818</v>
+        <v>-3815</v>
       </c>
       <c r="CW77" s="1">
-        <v>5259</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26747,7 +26747,7 @@
         <v>66</v>
       </c>
       <c r="AM78" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AN78" s="2">
         <v>21</v>
@@ -26927,7 +26927,7 @@
         <v>162</v>
       </c>
       <c r="CU78" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="CV78" s="1">
         <v>24</v>
@@ -27551,16 +27551,16 @@
         <v>180</v>
       </c>
       <c r="B81" s="1">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C81" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D81" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E81" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F81" s="1">
         <v>5</v>
@@ -27662,7 +27662,7 @@
         <v>41</v>
       </c>
       <c r="AM81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN81" s="2">
         <v>2</v>
@@ -27806,7 +27806,7 @@
         <v>149</v>
       </c>
       <c r="CI81" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CJ81" s="2">
         <v>3</v>
@@ -27839,16 +27839,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="CU81" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CV81" s="1">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="CW81" s="1">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -30114,7 +30114,7 @@
         <v>39</v>
       </c>
       <c r="AQ89" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR89" s="2">
         <v>2</v>
@@ -30246,7 +30246,7 @@
         <v>84</v>
       </c>
       <c r="CI89" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CJ89" s="2">
         <v>8</v>
@@ -30282,7 +30282,7 @@
         <v>2078</v>
       </c>
       <c r="CU89" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CV89" s="1">
         <v>336</v>
@@ -35496,7 +35496,7 @@
         <v>66</v>
       </c>
       <c r="G107" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H107" s="2">
         <v>3</v>
@@ -35772,7 +35772,7 @@
         <v>100</v>
       </c>
       <c r="CU107" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV107" s="1">
         <v>3</v>
@@ -36432,16 +36432,16 @@
         <v>375</v>
       </c>
       <c r="N110" s="1">
-        <v>1242</v>
+        <v>1281</v>
       </c>
       <c r="O110" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="P110" s="2">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="Q110" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="R110" s="1">
         <v>0</v>
@@ -36684,16 +36684,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>12745</v>
+        <v>12784</v>
       </c>
       <c r="CU110" s="1">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="CV110" s="1">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="CW110" s="1">
-        <v>1013</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -37631,7 +37631,7 @@
         <v>60</v>
       </c>
       <c r="G114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" s="2">
         <v>1</v>
@@ -37907,7 +37907,7 @@
         <v>168</v>
       </c>
       <c r="CU114" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV114" s="1">
         <v>2</v>
@@ -46802,16 +46802,16 @@
         <v>0</v>
       </c>
       <c r="N144" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" s="1">
         <v>15</v>
@@ -47054,16 +47054,16 @@
         <v>0</v>
       </c>
       <c r="CT144" s="1">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="CU144" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV144" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW144" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -47098,7 +47098,7 @@
         <v>65</v>
       </c>
       <c r="K145" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L145" s="2">
         <v>2</v>
@@ -47362,7 +47362,7 @@
         <v>1154</v>
       </c>
       <c r="CU145" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CV145" s="1">
         <v>39</v>
@@ -51951,28 +51951,28 @@
         <v>260</v>
       </c>
       <c r="B161" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C161" s="2">
         <v>1</v>
       </c>
       <c r="D161" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E161" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F161" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G161" s="2">
         <v>1</v>
       </c>
       <c r="H161" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I161" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J161" s="1">
         <v>0</v>
@@ -52239,16 +52239,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="CU161" s="1">
         <v>2</v>
       </c>
       <c r="CV161" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CW161" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -53491,7 +53491,7 @@
         <v>54</v>
       </c>
       <c r="G166" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H166" s="2">
         <v>3</v>
@@ -53767,7 +53767,7 @@
         <v>75</v>
       </c>
       <c r="CU166" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CV166" s="1">
         <v>3</v>
@@ -53805,16 +53805,16 @@
         <v>0</v>
       </c>
       <c r="J167" s="1">
-        <v>1618</v>
+        <v>1636</v>
       </c>
       <c r="K167" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L167" s="2">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="M167" s="2">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="N167" s="1">
         <v>2048</v>
@@ -53841,16 +53841,16 @@
         <v>0</v>
       </c>
       <c r="V167" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z167" s="1">
         <v>65</v>
@@ -54069,16 +54069,16 @@
         <v>0</v>
       </c>
       <c r="CT167" s="1">
-        <v>4978</v>
+        <v>4997</v>
       </c>
       <c r="CU167" s="1">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="CV167" s="1">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="CW167" s="1">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="168" spans="1:101">
@@ -55001,16 +55001,16 @@
         <v>270</v>
       </c>
       <c r="B171" s="1">
-        <v>4433</v>
+        <v>4453</v>
       </c>
       <c r="C171" s="2">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D171" s="2">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E171" s="2">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F171" s="1">
         <v>0</v>
@@ -55289,16 +55289,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>18914</v>
+        <v>18934</v>
       </c>
       <c r="CU171" s="1">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="CV171" s="1">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="CW171" s="1">
-        <v>1310</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -58306,7 +58306,7 @@
         <v>1986</v>
       </c>
       <c r="CI181" s="2">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="CJ181" s="2">
         <v>52</v>
@@ -58342,7 +58342,7 @@
         <v>48734</v>
       </c>
       <c r="CU181" s="1">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="CV181" s="1">
         <v>348</v>
@@ -63957,7 +63957,7 @@
         <v>390</v>
       </c>
       <c r="AM200" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN200" s="2">
         <v>11</v>
@@ -64101,7 +64101,7 @@
         <v>988</v>
       </c>
       <c r="CI200" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="CJ200" s="2">
         <v>47</v>
@@ -64137,7 +64137,7 @@
         <v>15945</v>
       </c>
       <c r="CU200" s="1">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="CV200" s="1">
         <v>187</v>
@@ -64190,7 +64190,7 @@
         <v>22550</v>
       </c>
       <c r="O201" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P201" s="2">
         <v>2</v>
@@ -64238,7 +64238,7 @@
         <v>46598</v>
       </c>
       <c r="AE201" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="AF201" s="2">
         <v>440</v>
@@ -64442,7 +64442,7 @@
         <v>85517</v>
       </c>
       <c r="CU201" s="1">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="CV201" s="1">
         <v>671</v>
@@ -71155,7 +71155,7 @@
         <v>648</v>
       </c>
       <c r="D136">
-        <v>10240</v>
+        <v>10244</v>
       </c>
       <c r="E136" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2">
         <v>87</v>
@@ -4360,7 +4360,7 @@
         <v>202</v>
       </c>
       <c r="CV4" s="1">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="CW4" s="1">
         <v>1410</v>
@@ -5615,16 +5615,16 @@
         <v>2</v>
       </c>
       <c r="J9" s="1">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K9" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L9" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M9" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N9" s="1">
         <v>1524</v>
@@ -5879,16 +5879,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2809</v>
+        <v>2812</v>
       </c>
       <c r="CU9" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV9" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="CW9" s="1">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7224,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="AL14" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP14" s="1">
         <v>57</v>
@@ -7404,16 +7404,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="CU14" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CV14" s="1">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CW14" s="1">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -8982,16 +8982,16 @@
         <v>57</v>
       </c>
       <c r="N20" s="1">
-        <v>12398</v>
+        <v>12405</v>
       </c>
       <c r="O20" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P20" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q20" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9234,16 +9234,16 @@
         <v>0</v>
       </c>
       <c r="CT20" s="1">
-        <v>20269</v>
+        <v>20276</v>
       </c>
       <c r="CU20" s="1">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="CV20" s="1">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="CW20" s="1">
-        <v>917</v>
+        <v>924</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9380,7 +9380,7 @@
         <v>2</v>
       </c>
       <c r="AS21" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT21" s="1">
         <v>0</v>
@@ -9512,7 +9512,7 @@
         <v>21</v>
       </c>
       <c r="CK21" s="2">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="CL21" s="1">
         <v>1</v>
@@ -9548,7 +9548,7 @@
         <v>23</v>
       </c>
       <c r="CW21" s="1">
-        <v>-16</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="22" spans="1:101">
@@ -9882,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" s="1">
         <v>3</v>
@@ -10158,7 +10158,7 @@
         <v>17</v>
       </c>
       <c r="CW23" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="BQ34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR34" s="1">
         <v>16</v>
@@ -13513,7 +13513,7 @@
         <v>81</v>
       </c>
       <c r="CW34" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -16275,7 +16275,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1">
         <v>13</v>
@@ -16563,7 +16563,7 @@
         <v>508</v>
       </c>
       <c r="CW44" s="1">
-        <v>1496</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -18213,7 +18213,7 @@
         <v>4</v>
       </c>
       <c r="AO50" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AP50" s="1">
         <v>11</v>
@@ -18357,7 +18357,7 @@
         <v>31</v>
       </c>
       <c r="CK50" s="2">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="CL50" s="1">
         <v>0</v>
@@ -18393,7 +18393,7 @@
         <v>39</v>
       </c>
       <c r="CW50" s="1">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -22094,7 +22094,7 @@
         <v>7</v>
       </c>
       <c r="M63" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N63" s="1">
         <v>1090</v>
@@ -22358,7 +22358,7 @@
         <v>87</v>
       </c>
       <c r="CW63" s="1">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -24220,16 +24220,16 @@
         <v>1</v>
       </c>
       <c r="J70" s="1">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K70" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M70" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N70" s="1">
         <v>1229</v>
@@ -24484,16 +24484,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="CU70" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CV70" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CW70" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25677,7 +25677,7 @@
         <v>209</v>
       </c>
       <c r="CK74" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25713,7 +25713,7 @@
         <v>2542</v>
       </c>
       <c r="CW74" s="1">
-        <v>5384</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26355,16 +26355,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4700</v>
+        <v>4699</v>
       </c>
       <c r="K77" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L77" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M77" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N77" s="1">
         <v>353290</v>
@@ -26373,7 +26373,7 @@
         <v>9551</v>
       </c>
       <c r="P77" s="2">
-        <v>9537</v>
+        <v>9538</v>
       </c>
       <c r="Q77" s="2">
         <v>17515</v>
@@ -26439,16 +26439,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="AM77" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN77" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO77" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26583,16 +26583,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>6933</v>
+        <v>6935</v>
       </c>
       <c r="CI77" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="CJ77" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="CK77" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26619,16 +26619,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>380640</v>
+        <v>380642</v>
       </c>
       <c r="CU77" s="1">
-        <v>9710</v>
+        <v>9712</v>
       </c>
       <c r="CV77" s="1">
-        <v>5847</v>
+        <v>5850</v>
       </c>
       <c r="CW77" s="1">
-        <v>14712</v>
+        <v>14714</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -39757,7 +39757,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="2">
         <v>2</v>
@@ -40045,7 +40045,7 @@
         <v>8</v>
       </c>
       <c r="CV121" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CW121" s="1">
         <v>71</v>
@@ -44640,7 +44640,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F137" s="1">
         <v>16</v>
@@ -44928,7 +44928,7 @@
         <v>997</v>
       </c>
       <c r="CW137" s="1">
-        <v>3445</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -45391,7 +45391,7 @@
         <v>10</v>
       </c>
       <c r="AZ139" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA139" s="2">
         <v>16</v>
@@ -45535,7 +45535,7 @@
         <v>110</v>
       </c>
       <c r="CV139" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CW139" s="1">
         <v>278</v>
@@ -49206,28 +49206,28 @@
         <v>251</v>
       </c>
       <c r="B152" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="1">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G152" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H152" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I152" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J152" s="1">
         <v>67</v>
@@ -49494,16 +49494,16 @@
         <v>0</v>
       </c>
       <c r="CT152" s="1">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="CU152" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="CV152" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CW152" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50426,16 +50426,16 @@
         <v>255</v>
       </c>
       <c r="B156" s="1">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C156" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D156" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E156" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F156" s="1">
         <v>26</v>
@@ -50714,16 +50714,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="CU156" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CV156" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CW156" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -51960,7 +51960,7 @@
         <v>3</v>
       </c>
       <c r="E161" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F161" s="1">
         <v>21</v>
@@ -51972,7 +51972,7 @@
         <v>3</v>
       </c>
       <c r="I161" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J161" s="1">
         <v>0</v>
@@ -52248,7 +52248,7 @@
         <v>6</v>
       </c>
       <c r="CW161" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -58919,7 +58919,7 @@
         <v>0</v>
       </c>
       <c r="CJ183" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CK183" s="2">
         <v>28</v>
@@ -58955,7 +58955,7 @@
         <v>0</v>
       </c>
       <c r="CV183" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CW183" s="1">
         <v>34</v>
@@ -63963,7 +63963,7 @@
         <v>11</v>
       </c>
       <c r="AO200" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP200" s="1">
         <v>24</v>
@@ -64095,7 +64095,7 @@
         <v>0</v>
       </c>
       <c r="CG200" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH200" s="1">
         <v>988</v>
@@ -64107,7 +64107,7 @@
         <v>47</v>
       </c>
       <c r="CK200" s="2">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="CL200" s="1">
         <v>9</v>
@@ -64143,7 +64143,7 @@
         <v>271</v>
       </c>
       <c r="CW200" s="1">
-        <v>500</v>
+        <v>481</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -67016,16 +67016,16 @@
         <v>0</v>
       </c>
       <c r="AP210" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AQ210" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR210" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS210" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT210" s="1">
         <v>0</v>
@@ -67148,28 +67148,28 @@
         <v>0</v>
       </c>
       <c r="CH210" s="1">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="CI210" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CJ210" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CK210" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CL210" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CM210" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN210" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP210" s="1">
         <v>0</v>
@@ -67184,16 +67184,16 @@
         <v>0</v>
       </c>
       <c r="CT210" s="1">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="CU210" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV210" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CW210" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -69183,7 +69183,7 @@
         <v>563</v>
       </c>
       <c r="D38">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -9272,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1">
         <v>0</v>
@@ -9548,7 +9548,7 @@
         <v>23</v>
       </c>
       <c r="CW21" s="1">
-        <v>-30</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="22" spans="1:101">
@@ -9873,16 +9873,16 @@
         <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="1">
         <v>3</v>
@@ -10149,16 +10149,16 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="CU23" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV23" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CW23" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -12642,16 +12642,16 @@
         <v>72</v>
       </c>
       <c r="N32" s="1">
-        <v>6480</v>
+        <v>6479</v>
       </c>
       <c r="O32" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P32" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q32" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="R32" s="1">
         <v>0</v>
@@ -12681,7 +12681,7 @@
         <v>113</v>
       </c>
       <c r="AA32" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="2">
         <v>4</v>
@@ -12894,16 +12894,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>10889</v>
+        <v>10888</v>
       </c>
       <c r="CU32" s="1">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="CV32" s="1">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="CW32" s="1">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -14445,7 +14445,7 @@
         <v>7</v>
       </c>
       <c r="E38" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1">
         <v>21</v>
@@ -14592,16 +14592,16 @@
         <v>0</v>
       </c>
       <c r="BB38" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD38" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE38" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BF38" s="1">
         <v>0</v>
@@ -14724,13 +14724,13 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="CU38" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CV38" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CW38" s="1">
         <v>148</v>
@@ -15360,7 +15360,7 @@
         <v>6</v>
       </c>
       <c r="E41" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F41" s="1">
         <v>45</v>
@@ -15468,7 +15468,7 @@
         <v>15</v>
       </c>
       <c r="AO41" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AP41" s="1">
         <v>11</v>
@@ -15612,7 +15612,7 @@
         <v>18</v>
       </c>
       <c r="CK41" s="2">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="CL41" s="1">
         <v>6</v>
@@ -15648,7 +15648,7 @@
         <v>41</v>
       </c>
       <c r="CW41" s="1">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:101">
@@ -16269,7 +16269,7 @@
         <v>224</v>
       </c>
       <c r="C44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="2">
         <v>8</v>
@@ -16557,7 +16557,7 @@
         <v>48683</v>
       </c>
       <c r="CU44" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CV44" s="1">
         <v>508</v>
@@ -18509,16 +18509,16 @@
         <v>0</v>
       </c>
       <c r="AL51" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AM51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN51" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO51" s="2">
         <v>2</v>
-      </c>
-      <c r="AO51" s="2">
-        <v>3</v>
       </c>
       <c r="AP51" s="1">
         <v>0</v>
@@ -18689,16 +18689,16 @@
         <v>0</v>
       </c>
       <c r="CT51" s="1">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="CU51" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="CV51" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CW51" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -20243,16 +20243,16 @@
         <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
         <v>3</v>
       </c>
       <c r="I57" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -20519,16 +20519,16 @@
         <v>0</v>
       </c>
       <c r="CT57" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CU57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV57" s="1">
         <v>3</v>
       </c>
       <c r="CW57" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:101">
@@ -21451,16 +21451,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6280</v>
+        <v>6300</v>
       </c>
       <c r="C61" s="2">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D61" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E61" s="2">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21739,16 +21739,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65450</v>
+        <v>65470</v>
       </c>
       <c r="CU61" s="1">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="CV61" s="1">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="CW61" s="1">
-        <v>2567</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22211,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA63" s="2">
         <v>18</v>
@@ -22355,7 +22355,7 @@
         <v>63</v>
       </c>
       <c r="CV63" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="CW63" s="1">
         <v>192</v>
@@ -22671,16 +22671,16 @@
         <v>164</v>
       </c>
       <c r="B65" s="1">
-        <v>3659</v>
+        <v>3669</v>
       </c>
       <c r="C65" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D65" s="2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E65" s="2">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22959,16 +22959,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>65407</v>
+        <v>65417</v>
       </c>
       <c r="CU65" s="1">
-        <v>1646</v>
+        <v>1656</v>
       </c>
       <c r="CV65" s="1">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="CW65" s="1">
-        <v>3378</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23284,7 +23284,7 @@
         <v>2422</v>
       </c>
       <c r="C67" s="2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D67" s="2">
         <v>45</v>
@@ -23572,7 +23572,7 @@
         <v>3299</v>
       </c>
       <c r="CU67" s="1">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CV67" s="1">
         <v>45</v>
@@ -24232,16 +24232,16 @@
         <v>9</v>
       </c>
       <c r="N70" s="1">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="O70" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P70" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q70" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="R70" s="1">
         <v>0</v>
@@ -24484,16 +24484,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2198</v>
+        <v>2214</v>
       </c>
       <c r="CU70" s="1">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="CV70" s="1">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="CW70" s="1">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25524,16 +25524,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36136</v>
+        <v>36139</v>
       </c>
       <c r="AM74" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AN74" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AO74" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25671,13 +25671,13 @@
         <v>15974</v>
       </c>
       <c r="CI74" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="CJ74" s="2">
         <v>209</v>
       </c>
       <c r="CK74" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25704,16 +25704,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>169760</v>
+        <v>169763</v>
       </c>
       <c r="CU74" s="1">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="CV74" s="1">
-        <v>2542</v>
+        <v>2545</v>
       </c>
       <c r="CW74" s="1">
-        <v>5383</v>
+        <v>5384</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26062,16 +26062,16 @@
         <v>354</v>
       </c>
       <c r="N76" s="1">
-        <v>116637</v>
+        <v>116632</v>
       </c>
       <c r="O76" s="2">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="P76" s="2">
-        <v>1522</v>
+        <v>1506</v>
       </c>
       <c r="Q76" s="2">
-        <v>2766</v>
+        <v>2760</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26314,16 +26314,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>149681</v>
+        <v>149676</v>
       </c>
       <c r="CU76" s="1">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="CV76" s="1">
-        <v>2427</v>
+        <v>2411</v>
       </c>
       <c r="CW76" s="1">
-        <v>4218</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26370,7 +26370,7 @@
         <v>353290</v>
       </c>
       <c r="O77" s="2">
-        <v>9551</v>
+        <v>9550</v>
       </c>
       <c r="P77" s="2">
         <v>9538</v>
@@ -26448,7 +26448,7 @@
         <v>26</v>
       </c>
       <c r="AO77" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26583,16 +26583,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>6935</v>
+        <v>6940</v>
       </c>
       <c r="CI77" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="CJ77" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="CK77" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26619,16 +26619,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>380642</v>
+        <v>380647</v>
       </c>
       <c r="CU77" s="1">
-        <v>9712</v>
+        <v>9716</v>
       </c>
       <c r="CV77" s="1">
-        <v>5850</v>
+        <v>5855</v>
       </c>
       <c r="CW77" s="1">
-        <v>14714</v>
+        <v>14711</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26950,7 +26950,7 @@
         <v>35</v>
       </c>
       <c r="E79" s="2">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -27028,7 +27028,7 @@
         <v>8582</v>
       </c>
       <c r="AE79" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AF79" s="2">
         <v>181</v>
@@ -27232,13 +27232,13 @@
         <v>89855</v>
       </c>
       <c r="CU79" s="1">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="CV79" s="1">
         <v>1097</v>
       </c>
       <c r="CW79" s="1">
-        <v>2126</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27680,7 +27680,7 @@
         <v>1</v>
       </c>
       <c r="AS81" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT81" s="1">
         <v>5</v>
@@ -27824,7 +27824,7 @@
         <v>1</v>
       </c>
       <c r="CO81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP81" s="1">
         <v>0</v>
@@ -27848,7 +27848,7 @@
         <v>230</v>
       </c>
       <c r="CW81" s="1">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -33053,16 +33053,16 @@
         <v>0</v>
       </c>
       <c r="F99" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I99" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J99" s="1">
         <v>0</v>
@@ -33329,16 +33329,16 @@
         <v>0</v>
       </c>
       <c r="CT99" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CU99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV99" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW99" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:101">
@@ -33995,7 +33995,7 @@
         <v>14437</v>
       </c>
       <c r="O102" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P102" s="2">
         <v>329</v>
@@ -34247,7 +34247,7 @@
         <v>42244</v>
       </c>
       <c r="CU102" s="1">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="CV102" s="1">
         <v>1040</v>
@@ -35132,7 +35132,7 @@
         <v>10</v>
       </c>
       <c r="CK105" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="CL105" s="1">
         <v>26</v>
@@ -35168,7 +35168,7 @@
         <v>217</v>
       </c>
       <c r="CW105" s="1">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -36405,7 +36405,7 @@
         <v>40</v>
       </c>
       <c r="E110" s="2">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -36693,7 +36693,7 @@
         <v>585</v>
       </c>
       <c r="CW110" s="1">
-        <v>1076</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -37422,7 +37422,7 @@
         <v>103</v>
       </c>
       <c r="AM113" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN113" s="2">
         <v>4</v>
@@ -37602,7 +37602,7 @@
         <v>173331</v>
       </c>
       <c r="CU113" s="1">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CV113" s="1">
         <v>9454</v>
@@ -38415,7 +38415,7 @@
         <v>0</v>
       </c>
       <c r="BM116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN116" s="1">
         <v>927</v>
@@ -38523,7 +38523,7 @@
         <v>750</v>
       </c>
       <c r="CW116" s="1">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38854,7 +38854,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I118" s="2">
         <v>5</v>
@@ -39130,7 +39130,7 @@
         <v>11</v>
       </c>
       <c r="CV118" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CW118" s="1">
         <v>39</v>
@@ -39653,7 +39653,7 @@
         <v>18</v>
       </c>
       <c r="BS120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT120" s="2">
         <v>1</v>
@@ -39737,7 +39737,7 @@
         <v>828</v>
       </c>
       <c r="CU120" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV120" s="1">
         <v>16</v>
@@ -39766,7 +39766,7 @@
         <v>46</v>
       </c>
       <c r="G121" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" s="2">
         <v>3</v>
@@ -40042,7 +40042,7 @@
         <v>337</v>
       </c>
       <c r="CU121" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV121" s="1">
         <v>30</v>
@@ -40068,16 +40068,16 @@
         <v>0</v>
       </c>
       <c r="F122" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I122" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J122" s="1">
         <v>0</v>
@@ -40344,16 +40344,16 @@
         <v>0</v>
       </c>
       <c r="CT122" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CU122" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV122" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW122" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:101">
@@ -40983,16 +40983,16 @@
         <v>0</v>
       </c>
       <c r="F125" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G125" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I125" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J125" s="1">
         <v>0</v>
@@ -41259,16 +41259,16 @@
         <v>0</v>
       </c>
       <c r="CT125" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="CU125" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV125" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW125" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:101">
@@ -44030,7 +44030,7 @@
         <v>12</v>
       </c>
       <c r="E135" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -44318,7 +44318,7 @@
         <v>3254</v>
       </c>
       <c r="CW135" s="1">
-        <v>5817</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -45065,7 +45065,7 @@
         <v>4</v>
       </c>
       <c r="AS138" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT138" s="1">
         <v>0</v>
@@ -45197,7 +45197,7 @@
         <v>0</v>
       </c>
       <c r="CK138" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CL138" s="1">
         <v>41</v>
@@ -45233,7 +45233,7 @@
         <v>45</v>
       </c>
       <c r="CW138" s="1">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -46276,16 +46276,16 @@
         <v>2</v>
       </c>
       <c r="AP142" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AQ142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT142" s="1">
         <v>0</v>
@@ -46420,16 +46420,16 @@
         <v>1</v>
       </c>
       <c r="CL142" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="CM142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO142" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP142" s="1">
         <v>0</v>
@@ -46444,16 +46444,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CU142" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CV142" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CW142" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -46581,16 +46581,16 @@
         <v>3</v>
       </c>
       <c r="AP143" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AQ143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR143" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS143" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT143" s="1">
         <v>12</v>
@@ -46599,7 +46599,7 @@
         <v>0</v>
       </c>
       <c r="AV143" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW143" s="2">
         <v>10</v>
@@ -46725,16 +46725,16 @@
         <v>5</v>
       </c>
       <c r="CL143" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="CM143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO143" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP143" s="1">
         <v>0</v>
@@ -46749,16 +46749,16 @@
         <v>0</v>
       </c>
       <c r="CT143" s="1">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="CU143" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CV143" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CW143" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -48175,7 +48175,7 @@
         <v>0</v>
       </c>
       <c r="BM148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN148" s="1">
         <v>0</v>
@@ -48283,7 +48283,7 @@
         <v>17</v>
       </c>
       <c r="CW148" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -48354,7 +48354,7 @@
         <v>9</v>
       </c>
       <c r="W149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X149" s="2">
         <v>1</v>
@@ -48582,7 +48582,7 @@
         <v>5482</v>
       </c>
       <c r="CU149" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CV149" s="1">
         <v>130</v>
@@ -48716,16 +48716,16 @@
         <v>0</v>
       </c>
       <c r="AP150" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ150" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR150" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS150" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT150" s="1">
         <v>0</v>
@@ -48848,16 +48848,16 @@
         <v>0</v>
       </c>
       <c r="CH150" s="1">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CI150" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ150" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CK150" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CL150" s="1">
         <v>37</v>
@@ -48884,16 +48884,16 @@
         <v>0</v>
       </c>
       <c r="CT150" s="1">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="CU150" s="1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CV150" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="CW150" s="1">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="151" spans="1:101">
@@ -49544,7 +49544,7 @@
         <v>51</v>
       </c>
       <c r="M153" s="2">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="N153" s="1">
         <v>153</v>
@@ -49808,7 +49808,7 @@
         <v>192</v>
       </c>
       <c r="CW153" s="1">
-        <v>292</v>
+        <v>274</v>
       </c>
     </row>
     <row r="154" spans="1:101">
@@ -52283,7 +52283,7 @@
         <v>3232</v>
       </c>
       <c r="K162" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L162" s="2">
         <v>83</v>
@@ -52547,7 +52547,7 @@
         <v>21635</v>
       </c>
       <c r="CU162" s="1">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="CV162" s="1">
         <v>530</v>
@@ -53488,16 +53488,16 @@
         <v>2</v>
       </c>
       <c r="F166" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I166" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J166" s="1">
         <v>0</v>
@@ -53764,16 +53764,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="CU166" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV166" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW166" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -57758,16 +57758,16 @@
         <v>2</v>
       </c>
       <c r="F180" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H180" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I180" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J180" s="1">
         <v>0</v>
@@ -58034,16 +58034,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="CU180" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CV180" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CW180" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -58168,7 +58168,7 @@
         <v>4</v>
       </c>
       <c r="AO181" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP181" s="1">
         <v>9</v>
@@ -58348,7 +58348,7 @@
         <v>1509</v>
       </c>
       <c r="CW181" s="1">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -58670,7 +58670,7 @@
         <v>0</v>
       </c>
       <c r="E183" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" s="1">
         <v>47</v>
@@ -58958,7 +58958,7 @@
         <v>15</v>
       </c>
       <c r="CW183" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="184" spans="1:101">
@@ -60808,16 +60808,16 @@
         <v>0</v>
       </c>
       <c r="F190" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G190" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I190" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J190" s="1">
         <v>0</v>
@@ -61084,16 +61084,16 @@
         <v>0</v>
       </c>
       <c r="CT190" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CU190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV190" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW190" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:101">
@@ -62321,16 +62321,16 @@
         <v>294</v>
       </c>
       <c r="B195" s="1">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C195" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D195" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E195" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1">
         <v>18</v>
@@ -62348,7 +62348,7 @@
         <v>160</v>
       </c>
       <c r="K195" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L195" s="2">
         <v>5</v>
@@ -62609,16 +62609,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>67817</v>
+        <v>67820</v>
       </c>
       <c r="CU195" s="1">
         <v>41</v>
       </c>
       <c r="CV195" s="1">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="CW195" s="1">
-        <v>2925</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -62701,7 +62701,7 @@
         <v>100</v>
       </c>
       <c r="AA196" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB196" s="2">
         <v>4</v>
@@ -62917,7 +62917,7 @@
         <v>5390</v>
       </c>
       <c r="CU196" s="1">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="CV196" s="1">
         <v>125</v>
@@ -64232,7 +64232,7 @@
         <v>6</v>
       </c>
       <c r="AC201" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AD201" s="1">
         <v>46598</v>
@@ -64448,7 +64448,7 @@
         <v>1224</v>
       </c>
       <c r="CW201" s="1">
-        <v>2264</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64567,7 +64567,7 @@
         <v>401</v>
       </c>
       <c r="AM202" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AN202" s="2">
         <v>50</v>
@@ -64747,7 +64747,7 @@
         <v>837</v>
       </c>
       <c r="CU202" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CV202" s="1">
         <v>82</v>
@@ -65676,16 +65676,16 @@
         <v>305</v>
       </c>
       <c r="B206" s="1">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C206" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D206" s="2">
-        <v>-31</v>
+        <v>-29</v>
       </c>
       <c r="E206" s="2">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="F206" s="1">
         <v>9</v>
@@ -65964,16 +65964,16 @@
         <v>0</v>
       </c>
       <c r="CT206" s="1">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="CU206" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV206" s="1">
-        <v>-21</v>
+        <v>-19</v>
       </c>
       <c r="CW206" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -68128,16 +68128,16 @@
         <v>1</v>
       </c>
       <c r="F214" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G214" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H214" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I214" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J214" s="1">
         <v>0</v>
@@ -68404,16 +68404,16 @@
         <v>0</v>
       </c>
       <c r="CT214" s="1">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="CU214" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV214" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CW214" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -69906,7 +69906,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E74" t="s">
         <v>717</v>
@@ -70006,7 +70006,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E79" t="s">
         <v>717</v>
@@ -70472,7 +70472,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2969</v>
+        <v>2971</v>
       </c>
       <c r="E102" t="s">
         <v>717</v>
@@ -70752,7 +70752,7 @@
         <v>630</v>
       </c>
       <c r="D116">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E116" t="s">
         <v>717</v>
@@ -71215,7 +71215,7 @@
         <v>652</v>
       </c>
       <c r="D139">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E139" t="s">
         <v>717</v>
@@ -71275,7 +71275,7 @@
         <v>654</v>
       </c>
       <c r="D142">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E142" t="s">
         <v>717</v>
@@ -71295,7 +71295,7 @@
         <v>655</v>
       </c>
       <c r="D143">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E143" t="s">
         <v>717</v>
@@ -71678,7 +71678,7 @@
         <v>670</v>
       </c>
       <c r="D162">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E162" t="s">
         <v>717</v>
@@ -72364,7 +72364,7 @@
         <v>700</v>
       </c>
       <c r="D196">
-        <v>10198</v>
+        <v>10199</v>
       </c>
       <c r="E196" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="843">
   <si>
     <t>ati_all</t>
   </si>
@@ -2048,7 +2048,7 @@
     <t>atip-aiprp@prairiescan.gc.ca</t>
   </si>
   <si>
-    <t>mhembroff@rupertport.com</t>
+    <t>accesstoinformation@rupertport.com</t>
   </si>
   <si>
     <t>atip-aiprp@ps-sp.gc.ca</t>
@@ -2286,9 +2286,6 @@
   </si>
   <si>
     <t>Johanne.gamache@pmprb-cepmb.gc.ca</t>
-  </si>
-  <si>
-    <t>accesstoinformation@rupertport.com</t>
   </si>
   <si>
     <t>generalinquiries-renseignementsgeneraux@nsicop-cpsnr.gc.ca</t>
@@ -3151,292 +3148,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>766</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>767</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>769</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>770</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>776</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>777</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="X1" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>780</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>782</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>783</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>789</v>
-      </c>
-      <c r="AK1" s="3" t="s">
-        <v>790</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="AN1" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="BE1" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="BH1" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BK1" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BL1" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BM1" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="BM1" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="BP1" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BR1" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="BR1" s="3" t="s">
+      <c r="BS1" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="BS1" s="3" t="s">
+      <c r="BT1" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BU1" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="BU1" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="BX1" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="BY1" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="BZ1" s="3" t="s">
+      <c r="CA1" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="CA1" s="3" t="s">
+      <c r="CB1" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CC1" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="CC1" s="3" t="s">
-        <v>830</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="CF1" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CG1" s="3" t="s">
         <v>832</v>
-      </c>
-      <c r="CG1" s="3" t="s">
-        <v>833</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="CJ1" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="CJ1" s="3" t="s">
+      <c r="CK1" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="CK1" s="3" t="s">
+      <c r="CL1" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CM1" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CN1" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CO1" s="3" t="s">
         <v>839</v>
-      </c>
-      <c r="CO1" s="3" t="s">
-        <v>840</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="CR1" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="CR1" s="3" t="s">
+      <c r="CS1" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="CS1" s="3" t="s">
-        <v>843</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -3770,7 +3767,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -3878,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="1">
         <v>73</v>
@@ -4022,7 +4019,7 @@
         <v>43</v>
       </c>
       <c r="CK3" s="2">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="CL3" s="1">
         <v>3</v>
@@ -4058,7 +4055,7 @@
         <v>1200</v>
       </c>
       <c r="CW3" s="1">
-        <v>2243</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4072,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
         <v>87</v>
@@ -4360,7 +4357,7 @@
         <v>198</v>
       </c>
       <c r="CV4" s="1">
-        <v>818</v>
+        <v>744</v>
       </c>
       <c r="CW4" s="1">
         <v>1410</v>
@@ -4676,16 +4673,16 @@
         <v>105</v>
       </c>
       <c r="B6" s="1">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="1">
         <v>40</v>
@@ -4964,16 +4961,16 @@
         <v>0</v>
       </c>
       <c r="CT6" s="1">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="CU6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV6" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CW6" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -6515,7 +6512,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="F12" s="1">
         <v>17</v>
@@ -6803,7 +6800,7 @@
         <v>4</v>
       </c>
       <c r="CW12" s="1">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -7816,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="AF16" s="2">
-        <v>29</v>
+        <v>-106</v>
       </c>
       <c r="AG16" s="2">
         <v>32</v>
@@ -8020,7 +8017,7 @@
         <v>51</v>
       </c>
       <c r="CV16" s="1">
-        <v>86</v>
+        <v>-49</v>
       </c>
       <c r="CW16" s="1">
         <v>155</v>
@@ -11479,7 +11476,7 @@
         <v>435</v>
       </c>
       <c r="AG28" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -11683,7 +11680,7 @@
         <v>518</v>
       </c>
       <c r="CW28" s="1">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12325,16 +12322,16 @@
         <v>2</v>
       </c>
       <c r="J31" s="1">
-        <v>1355</v>
+        <v>1368</v>
       </c>
       <c r="K31" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L31" s="2">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="M31" s="2">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="N31" s="1">
         <v>1955</v>
@@ -12589,16 +12586,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>5717</v>
+        <v>5730</v>
       </c>
       <c r="CU31" s="1">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="CV31" s="1">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="CW31" s="1">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12636,7 +12633,7 @@
         <v>14</v>
       </c>
       <c r="L32" s="2">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M32" s="2">
         <v>86</v>
@@ -12735,7 +12732,7 @@
         <v>2</v>
       </c>
       <c r="AS32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT32" s="1">
         <v>0</v>
@@ -12867,7 +12864,7 @@
         <v>7</v>
       </c>
       <c r="CK32" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CL32" s="1">
         <v>25</v>
@@ -12900,10 +12897,10 @@
         <v>249</v>
       </c>
       <c r="CV32" s="1">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="CW32" s="1">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -15055,7 +15052,7 @@
         <v>222</v>
       </c>
       <c r="E40" s="2">
-        <v>468</v>
+        <v>384</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -15343,7 +15340,7 @@
         <v>1371</v>
       </c>
       <c r="CW40" s="1">
-        <v>2221</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -19442,10 +19439,10 @@
         <v>0</v>
       </c>
       <c r="AR54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS54" s="2">
         <v>2</v>
-      </c>
-      <c r="AS54" s="2">
-        <v>3</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -19574,7 +19571,7 @@
         <v>0</v>
       </c>
       <c r="CJ54" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CK54" s="2">
         <v>17</v>
@@ -19589,7 +19586,7 @@
         <v>0</v>
       </c>
       <c r="CO54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP54" s="1">
         <v>0</v>
@@ -19610,10 +19607,10 @@
         <v>0</v>
       </c>
       <c r="CV54" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CW54" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:101">
@@ -20016,7 +20013,7 @@
         <v>0</v>
       </c>
       <c r="AF56" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AG56" s="2">
         <v>111</v>
@@ -20220,7 +20217,7 @@
         <v>158</v>
       </c>
       <c r="CV56" s="1">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="CW56" s="1">
         <v>430</v>
@@ -20557,7 +20554,7 @@
         <v>3</v>
       </c>
       <c r="I58" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58" s="1">
         <v>0</v>
@@ -20797,7 +20794,7 @@
         <v>6</v>
       </c>
       <c r="CK58" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="CL58" s="1">
         <v>16</v>
@@ -20809,7 +20806,7 @@
         <v>1</v>
       </c>
       <c r="CO58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP58" s="1">
         <v>0</v>
@@ -20833,7 +20830,7 @@
         <v>16</v>
       </c>
       <c r="CW58" s="1">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:101">
@@ -22211,7 +22208,7 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA63" s="2">
         <v>18</v>
@@ -22355,7 +22352,7 @@
         <v>42</v>
       </c>
       <c r="CV63" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="CW63" s="1">
         <v>170</v>
@@ -23912,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J69" s="1">
         <v>0</v>
@@ -24188,7 +24185,7 @@
         <v>0</v>
       </c>
       <c r="CW69" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:101">
@@ -24229,7 +24226,7 @@
         <v>6</v>
       </c>
       <c r="M70" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N70" s="1">
         <v>1245</v>
@@ -24325,7 +24322,7 @@
         <v>3</v>
       </c>
       <c r="AS70" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -24469,7 +24466,7 @@
         <v>1</v>
       </c>
       <c r="CO70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP70" s="1">
         <v>0</v>
@@ -24493,7 +24490,7 @@
         <v>36</v>
       </c>
       <c r="CW70" s="1">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25677,7 +25674,7 @@
         <v>212</v>
       </c>
       <c r="CK74" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25713,7 +25710,7 @@
         <v>2550</v>
       </c>
       <c r="CW74" s="1">
-        <v>5327</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25739,7 +25736,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I75" s="2">
         <v>4</v>
@@ -26015,7 +26012,7 @@
         <v>2</v>
       </c>
       <c r="CV75" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CW75" s="1">
         <v>21</v>
@@ -26448,7 +26445,7 @@
         <v>26</v>
       </c>
       <c r="AO77" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26592,7 +26589,7 @@
         <v>250</v>
       </c>
       <c r="CK77" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26628,7 +26625,7 @@
         <v>5857</v>
       </c>
       <c r="CW77" s="1">
-        <v>14698</v>
+        <v>14665</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27252,7 +27249,7 @@
         <v>0</v>
       </c>
       <c r="D80" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E80" s="2">
         <v>7</v>
@@ -27363,7 +27360,7 @@
         <v>51</v>
       </c>
       <c r="AO80" s="2">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="AP80" s="1">
         <v>0</v>
@@ -27507,7 +27504,7 @@
         <v>51</v>
       </c>
       <c r="CK80" s="2">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="CL80" s="1">
         <v>0</v>
@@ -27540,10 +27537,10 @@
         <v>32</v>
       </c>
       <c r="CV80" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="CW80" s="1">
-        <v>281</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -28484,7 +28481,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I84" s="2">
         <v>4</v>
@@ -28760,7 +28757,7 @@
         <v>0</v>
       </c>
       <c r="CV84" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CW84" s="1">
         <v>4</v>
@@ -30631,7 +30628,7 @@
         <v>70</v>
       </c>
       <c r="L91" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M91" s="2">
         <v>434</v>
@@ -30895,7 +30892,7 @@
         <v>178</v>
       </c>
       <c r="CV91" s="1">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="CW91" s="1">
         <v>978</v>
@@ -35185,7 +35182,7 @@
         <v>198</v>
       </c>
       <c r="E106" s="2">
-        <v>395</v>
+        <v>334</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -35473,7 +35470,7 @@
         <v>1477</v>
       </c>
       <c r="CW106" s="1">
-        <v>2688</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36707,7 +36704,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" s="2">
         <v>2</v>
@@ -36995,7 +36992,7 @@
         <v>10</v>
       </c>
       <c r="CV111" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CW111" s="1">
         <v>64</v>
@@ -37015,7 +37012,7 @@
         <v>35</v>
       </c>
       <c r="E112" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -37303,7 +37300,7 @@
         <v>380</v>
       </c>
       <c r="CW112" s="1">
-        <v>728</v>
+        <v>720</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37317,7 +37314,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="E113" s="2">
         <v>74</v>
@@ -37605,7 +37602,7 @@
         <v>372</v>
       </c>
       <c r="CV113" s="1">
-        <v>9454</v>
+        <v>9402</v>
       </c>
       <c r="CW113" s="1">
         <v>14198</v>
@@ -39153,292 +39150,292 @@
         <v>4</v>
       </c>
       <c r="F119" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I119" s="2">
+        <v>3</v>
+      </c>
+      <c r="J119" s="1">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2">
+        <v>0</v>
+      </c>
+      <c r="N119" s="1">
+        <v>0</v>
+      </c>
+      <c r="O119" s="2">
+        <v>0</v>
+      </c>
+      <c r="P119" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="2">
+        <v>0</v>
+      </c>
+      <c r="R119" s="1">
+        <v>0</v>
+      </c>
+      <c r="S119" s="2">
+        <v>0</v>
+      </c>
+      <c r="T119" s="2">
+        <v>0</v>
+      </c>
+      <c r="U119" s="2">
+        <v>0</v>
+      </c>
+      <c r="V119" s="1">
+        <v>0</v>
+      </c>
+      <c r="W119" s="2">
+        <v>0</v>
+      </c>
+      <c r="X119" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY119" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS119" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT119" s="1">
+        <v>101</v>
+      </c>
+      <c r="CU119" s="1">
         <v>2</v>
       </c>
-      <c r="J119" s="1">
-        <v>0</v>
-      </c>
-      <c r="K119" s="2">
-        <v>0</v>
-      </c>
-      <c r="L119" s="2">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2">
-        <v>0</v>
-      </c>
-      <c r="N119" s="1">
-        <v>0</v>
-      </c>
-      <c r="O119" s="2">
-        <v>0</v>
-      </c>
-      <c r="P119" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="2">
-        <v>0</v>
-      </c>
-      <c r="R119" s="1">
-        <v>0</v>
-      </c>
-      <c r="S119" s="2">
-        <v>0</v>
-      </c>
-      <c r="T119" s="2">
-        <v>0</v>
-      </c>
-      <c r="U119" s="2">
-        <v>0</v>
-      </c>
-      <c r="V119" s="1">
-        <v>0</v>
-      </c>
-      <c r="W119" s="2">
-        <v>0</v>
-      </c>
-      <c r="X119" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y119" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY119" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB119" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF119" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ119" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN119" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR119" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV119" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY119" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ119" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD119" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH119" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL119" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP119" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS119" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT119" s="1">
-        <v>100</v>
-      </c>
-      <c r="CU119" s="1">
-        <v>1</v>
-      </c>
       <c r="CV119" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW119" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -42613,7 +42610,7 @@
         <v>12</v>
       </c>
       <c r="AO130" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP130" s="1">
         <v>32</v>
@@ -42757,7 +42754,7 @@
         <v>11</v>
       </c>
       <c r="CK130" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CL130" s="1">
         <v>37</v>
@@ -42793,7 +42790,7 @@
         <v>187</v>
       </c>
       <c r="CW130" s="1">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -45265,16 +45262,16 @@
         <v>1</v>
       </c>
       <c r="J139" s="1">
-        <v>1166</v>
+        <v>1180</v>
       </c>
       <c r="K139" s="2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L139" s="2">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="M139" s="2">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N139" s="1">
         <v>2150</v>
@@ -45529,16 +45526,16 @@
         <v>0</v>
       </c>
       <c r="CT139" s="1">
-        <v>4272</v>
+        <v>4286</v>
       </c>
       <c r="CU139" s="1">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="CV139" s="1">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="CW139" s="1">
-        <v>278</v>
+        <v>292</v>
       </c>
     </row>
     <row r="140" spans="1:101">
@@ -46602,7 +46599,7 @@
         <v>4</v>
       </c>
       <c r="AW143" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX143" s="1">
         <v>4</v>
@@ -46758,7 +46755,7 @@
         <v>45</v>
       </c>
       <c r="CW143" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -47200,7 +47197,7 @@
         <v>1</v>
       </c>
       <c r="AS145" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT145" s="1">
         <v>0</v>
@@ -47332,7 +47329,7 @@
         <v>0</v>
       </c>
       <c r="CK145" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CL145" s="1">
         <v>67</v>
@@ -47368,7 +47365,7 @@
         <v>53</v>
       </c>
       <c r="CW145" s="1">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -47382,7 +47379,7 @@
         <v>19</v>
       </c>
       <c r="D146" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E146" s="2">
         <v>52</v>
@@ -47406,7 +47403,7 @@
         <v>6</v>
       </c>
       <c r="L146" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M146" s="2">
         <v>24</v>
@@ -47670,7 +47667,7 @@
         <v>59</v>
       </c>
       <c r="CV146" s="1">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="CW146" s="1">
         <v>147</v>
@@ -47998,16 +47995,16 @@
         <v>0</v>
       </c>
       <c r="F148" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G148" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I148" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J148" s="1">
         <v>16</v>
@@ -48274,16 +48271,16 @@
         <v>0</v>
       </c>
       <c r="CT148" s="1">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="CU148" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV148" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW148" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -48788,16 +48785,16 @@
         <v>0</v>
       </c>
       <c r="BN150" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BO150" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BP150" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BQ150" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BR150" s="1">
         <v>3</v>
@@ -48884,16 +48881,16 @@
         <v>0</v>
       </c>
       <c r="CT150" s="1">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="CU150" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CV150" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CW150" s="1">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="151" spans="1:101">
@@ -51602,7 +51599,7 @@
         <v>295</v>
       </c>
       <c r="CK159" s="2">
-        <v>647</v>
+        <v>584</v>
       </c>
       <c r="CL159" s="1">
         <v>0</v>
@@ -51638,7 +51635,7 @@
         <v>846</v>
       </c>
       <c r="CW159" s="1">
-        <v>1586</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="160" spans="1:101">
@@ -53790,7 +53787,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1">
         <v>7</v>
@@ -54078,7 +54075,7 @@
         <v>374</v>
       </c>
       <c r="CW167" s="1">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="168" spans="1:101">
@@ -54714,7 +54711,7 @@
         <v>1</v>
       </c>
       <c r="H170" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I170" s="2">
         <v>4</v>
@@ -54990,7 +54987,7 @@
         <v>16</v>
       </c>
       <c r="CV170" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="CW170" s="1">
         <v>83</v>
@@ -58159,16 +58156,16 @@
         <v>0</v>
       </c>
       <c r="AL181" s="1">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AM181" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN181" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO181" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP181" s="1">
         <v>9</v>
@@ -58312,7 +58309,7 @@
         <v>40</v>
       </c>
       <c r="CK181" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="CL181" s="1">
         <v>3</v>
@@ -58339,16 +58336,16 @@
         <v>0</v>
       </c>
       <c r="CT181" s="1">
-        <v>49895</v>
+        <v>49896</v>
       </c>
       <c r="CU181" s="1">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="CV181" s="1">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="CW181" s="1">
-        <v>2950</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -62052,16 +62049,16 @@
         <v>61</v>
       </c>
       <c r="N194" s="1">
-        <v>28683</v>
+        <v>28685</v>
       </c>
       <c r="O194" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="P194" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="Q194" s="2">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="R194" s="1">
         <v>0</v>
@@ -62304,16 +62301,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32272</v>
+        <v>32274</v>
       </c>
       <c r="CU194" s="1">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="CV194" s="1">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="CW194" s="1">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62330,7 +62327,7 @@
         <v>7</v>
       </c>
       <c r="E195" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F195" s="1">
         <v>18</v>
@@ -62345,16 +62342,16 @@
         <v>2</v>
       </c>
       <c r="J195" s="1">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K195" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L195" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M195" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N195" s="1">
         <v>964</v>
@@ -62609,16 +62606,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>67820</v>
+        <v>67824</v>
       </c>
       <c r="CU195" s="1">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="CV195" s="1">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="CW195" s="1">
-        <v>2928</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -63855,7 +63852,7 @@
         <v>86</v>
       </c>
       <c r="E200" s="2">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F200" s="1">
         <v>0</v>
@@ -63879,7 +63876,7 @@
         <v>65</v>
       </c>
       <c r="M200" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="N200" s="1">
         <v>7967</v>
@@ -64143,7 +64140,7 @@
         <v>253</v>
       </c>
       <c r="CW200" s="1">
-        <v>482</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -65990,7 +65987,7 @@
         <v>29</v>
       </c>
       <c r="E207" s="2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F207" s="1">
         <v>1</v>
@@ -66014,7 +66011,7 @@
         <v>31</v>
       </c>
       <c r="M207" s="2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N207" s="1">
         <v>5042</v>
@@ -66278,7 +66275,7 @@
         <v>295</v>
       </c>
       <c r="CW207" s="1">
-        <v>487</v>
+        <v>465</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -66843,16 +66840,16 @@
         <v>0</v>
       </c>
       <c r="CH209" s="1">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="CI209" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="CJ209" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="CK209" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="CL209" s="1">
         <v>0</v>
@@ -66879,16 +66876,16 @@
         <v>0</v>
       </c>
       <c r="CT209" s="1">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="CU209" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CV209" s="1">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="CW209" s="1">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="210" spans="1:101">
@@ -67919,13 +67916,13 @@
         <v>0</v>
       </c>
       <c r="AL213" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AM213" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN213" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO213" s="2">
         <v>7</v>
@@ -68063,13 +68060,13 @@
         <v>0</v>
       </c>
       <c r="CH213" s="1">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="CI213" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CJ213" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CK213" s="2">
         <v>16</v>
@@ -68099,13 +68096,13 @@
         <v>0</v>
       </c>
       <c r="CT213" s="1">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="CU213" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="CV213" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CW213" s="1">
         <v>29</v>
@@ -69906,7 +69903,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="E74" t="s">
         <v>717</v>
@@ -70532,7 +70529,7 @@
         <v>621</v>
       </c>
       <c r="D105">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E105" t="s">
         <v>717</v>
@@ -70692,7 +70689,7 @@
         <v>535</v>
       </c>
       <c r="D113">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E113" t="s">
         <v>735</v>
@@ -71850,7 +71847,7 @@
         <v>750</v>
       </c>
       <c r="G170" t="s">
-        <v>757</v>
+        <v>677</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -72270,7 +72267,7 @@
         <v>748</v>
       </c>
       <c r="G191" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -72413,7 +72410,7 @@
         <v>750</v>
       </c>
       <c r="G198" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="199" spans="1:7">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -7738,7 +7738,7 @@
         <v>58</v>
       </c>
       <c r="G16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2">
         <v>3</v>
@@ -8014,7 +8014,7 @@
         <v>951</v>
       </c>
       <c r="CU16" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="CV16" s="1">
         <v>-49</v>
@@ -9201,7 +9201,7 @@
         <v>5</v>
       </c>
       <c r="CJ20" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="CK20" s="2">
         <v>92</v>
@@ -9237,7 +9237,7 @@
         <v>413</v>
       </c>
       <c r="CV20" s="1">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="CW20" s="1">
         <v>946</v>
@@ -12325,7 +12325,7 @@
         <v>1368</v>
       </c>
       <c r="K31" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L31" s="2">
         <v>52</v>
@@ -12589,7 +12589,7 @@
         <v>5730</v>
       </c>
       <c r="CU31" s="1">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="CV31" s="1">
         <v>182</v>
@@ -19122,7 +19122,7 @@
         <v>3</v>
       </c>
       <c r="AN53" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AO53" s="2">
         <v>13</v>
@@ -19248,16 +19248,16 @@
         <v>0</v>
       </c>
       <c r="CD53" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CE53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH53" s="1">
         <v>125</v>
@@ -19266,7 +19266,7 @@
         <v>3</v>
       </c>
       <c r="CJ53" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CK53" s="2">
         <v>15</v>
@@ -19296,16 +19296,16 @@
         <v>0</v>
       </c>
       <c r="CT53" s="1">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="CU53" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV53" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="CW53" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:101">
@@ -22058,16 +22058,16 @@
         <v>162</v>
       </c>
       <c r="B63" s="1">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C63" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D63" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E63" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -22178,16 +22178,16 @@
         <v>0</v>
       </c>
       <c r="AP63" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AQ63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR63" s="2">
         <v>3</v>
       </c>
       <c r="AS63" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -22310,16 +22310,16 @@
         <v>0</v>
       </c>
       <c r="CH63" s="1">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="CI63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ63" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CK63" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CL63" s="1">
         <v>22</v>
@@ -22346,16 +22346,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2778</v>
+        <v>2786</v>
       </c>
       <c r="CU63" s="1">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="CV63" s="1">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="CW63" s="1">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22402,7 +22402,7 @@
         <v>4249</v>
       </c>
       <c r="O64" s="2">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="P64" s="2">
         <v>160</v>
@@ -22654,7 +22654,7 @@
         <v>7828</v>
       </c>
       <c r="CU64" s="1">
-        <v>173</v>
+        <v>13</v>
       </c>
       <c r="CV64" s="1">
         <v>304</v>
@@ -24806,7 +24806,7 @@
         <v>7</v>
       </c>
       <c r="C72" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -24818,7 +24818,7 @@
         <v>15</v>
       </c>
       <c r="G72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2">
         <v>2</v>
@@ -25094,7 +25094,7 @@
         <v>461</v>
       </c>
       <c r="CU72" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV72" s="1">
         <v>99</v>
@@ -25476,7 +25476,7 @@
         <v>9</v>
       </c>
       <c r="W74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X74" s="2">
         <v>1</v>
@@ -25503,7 +25503,7 @@
         <v>0</v>
       </c>
       <c r="AF74" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AG74" s="2">
         <v>1247</v>
@@ -25521,16 +25521,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36139</v>
+        <v>36140</v>
       </c>
       <c r="AM74" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AN74" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO74" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25665,16 +25665,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>15979</v>
+        <v>15980</v>
       </c>
       <c r="CI74" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="CJ74" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="CK74" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,16 +25701,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>169768</v>
+        <v>169770</v>
       </c>
       <c r="CU74" s="1">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="CV74" s="1">
-        <v>2550</v>
+        <v>2555</v>
       </c>
       <c r="CW74" s="1">
-        <v>5326</v>
+        <v>5328</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26352,16 +26352,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4699</v>
+        <v>4698</v>
       </c>
       <c r="K77" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L77" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M77" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N77" s="1">
         <v>353290</v>
@@ -26580,16 +26580,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>6940</v>
+        <v>6933</v>
       </c>
       <c r="CI77" s="2">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="CJ77" s="2">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="CK77" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26616,16 +26616,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>380647</v>
+        <v>380639</v>
       </c>
       <c r="CU77" s="1">
-        <v>9717</v>
+        <v>9709</v>
       </c>
       <c r="CV77" s="1">
-        <v>5857</v>
+        <v>5833</v>
       </c>
       <c r="CW77" s="1">
-        <v>14665</v>
+        <v>14657</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27554,7 +27554,7 @@
         <v>6</v>
       </c>
       <c r="D81" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2">
         <v>19</v>
@@ -27692,16 +27692,16 @@
         <v>0</v>
       </c>
       <c r="AX81" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA81" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB81" s="1">
         <v>0</v>
@@ -27836,16 +27836,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6253</v>
+        <v>6254</v>
       </c>
       <c r="CU81" s="1">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="CV81" s="1">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="CW81" s="1">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28161,7 +28161,7 @@
         <v>2632</v>
       </c>
       <c r="C83" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D83" s="2">
         <v>60</v>
@@ -28248,7 +28248,7 @@
         <v>0</v>
       </c>
       <c r="AF83" s="2">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="AG83" s="2">
         <v>3598</v>
@@ -28449,10 +28449,10 @@
         <v>422904</v>
       </c>
       <c r="CU83" s="1">
-        <v>893</v>
+        <v>853</v>
       </c>
       <c r="CV83" s="1">
-        <v>4532</v>
+        <v>4530</v>
       </c>
       <c r="CW83" s="1">
         <v>5823</v>
@@ -28894,7 +28894,7 @@
         <v>1</v>
       </c>
       <c r="AR85" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS85" s="2">
         <v>8</v>
@@ -29026,7 +29026,7 @@
         <v>2</v>
       </c>
       <c r="CJ85" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CK85" s="2">
         <v>30</v>
@@ -29062,7 +29062,7 @@
         <v>4</v>
       </c>
       <c r="CV85" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CW85" s="1">
         <v>44</v>
@@ -30102,22 +30102,22 @@
         <v>0</v>
       </c>
       <c r="AN89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO89" s="2">
         <v>1</v>
       </c>
       <c r="AP89" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AQ89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR89" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS89" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT89" s="1">
         <v>0</v>
@@ -30240,16 +30240,16 @@
         <v>0</v>
       </c>
       <c r="CH89" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="CI89" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ89" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK89" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CL89" s="1">
         <v>9</v>
@@ -30276,16 +30276,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="CU89" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CV89" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CW89" s="1">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -32162,7 +32162,7 @@
         <v>44</v>
       </c>
       <c r="O96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P96" s="2">
         <v>2</v>
@@ -32414,7 +32414,7 @@
         <v>948</v>
       </c>
       <c r="CU96" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV96" s="1">
         <v>24</v>
@@ -33995,7 +33995,7 @@
         <v>328</v>
       </c>
       <c r="P102" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="Q102" s="2">
         <v>594</v>
@@ -34247,7 +34247,7 @@
         <v>487</v>
       </c>
       <c r="CV102" s="1">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="CW102" s="1">
         <v>1900</v>
@@ -34578,7 +34578,7 @@
         <v>37</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="2">
         <v>3</v>
@@ -34854,7 +34854,7 @@
         <v>38</v>
       </c>
       <c r="CU104" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV104" s="1">
         <v>3</v>
@@ -35798,7 +35798,7 @@
         <v>35</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="2">
         <v>1</v>
@@ -36074,7 +36074,7 @@
         <v>918</v>
       </c>
       <c r="CU108" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV108" s="1">
         <v>30</v>
@@ -36127,7 +36127,7 @@
         <v>303</v>
       </c>
       <c r="O109" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P109" s="2">
         <v>6</v>
@@ -36199,7 +36199,7 @@
         <v>93</v>
       </c>
       <c r="AM109" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AN109" s="2">
         <v>10</v>
@@ -36343,7 +36343,7 @@
         <v>333</v>
       </c>
       <c r="CI109" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CJ109" s="2">
         <v>7</v>
@@ -36379,7 +36379,7 @@
         <v>732</v>
       </c>
       <c r="CU109" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CV109" s="1">
         <v>23</v>
@@ -37027,16 +37027,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="1">
-        <v>1081</v>
+        <v>1095</v>
       </c>
       <c r="K112" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="L112" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="M112" s="2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="N112" s="1">
         <v>5420</v>
@@ -37291,16 +37291,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8007</v>
+        <v>8021</v>
       </c>
       <c r="CU112" s="1">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="CV112" s="1">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="CW112" s="1">
-        <v>720</v>
+        <v>734</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37332,16 +37332,16 @@
         <v>0</v>
       </c>
       <c r="J113" s="1">
-        <v>4570</v>
+        <v>4639</v>
       </c>
       <c r="K113" s="2">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="L113" s="2">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="M113" s="2">
-        <v>373</v>
+        <v>442</v>
       </c>
       <c r="N113" s="1">
         <v>7848</v>
@@ -37383,7 +37383,7 @@
         <v>111</v>
       </c>
       <c r="AA113" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB113" s="2">
         <v>4</v>
@@ -37596,16 +37596,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173331</v>
+        <v>173400</v>
       </c>
       <c r="CU113" s="1">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="CV113" s="1">
-        <v>9402</v>
+        <v>9471</v>
       </c>
       <c r="CW113" s="1">
-        <v>14198</v>
+        <v>14267</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38262,7 +38262,7 @@
         <v>4431</v>
       </c>
       <c r="O116" s="2">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="P116" s="2">
         <v>132</v>
@@ -38499,28 +38499,28 @@
         <v>1</v>
       </c>
       <c r="CP116" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21339</v>
+        <v>21340</v>
       </c>
       <c r="CU116" s="1">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="CV116" s="1">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="CW116" s="1">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38558,7 +38558,7 @@
         <v>8</v>
       </c>
       <c r="L117" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M117" s="2">
         <v>33</v>
@@ -38822,7 +38822,7 @@
         <v>186</v>
       </c>
       <c r="CV117" s="1">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="CW117" s="1">
         <v>1050</v>
@@ -38833,28 +38833,28 @@
         <v>217</v>
       </c>
       <c r="B118" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C118" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D118" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E118" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F118" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G118" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J118" s="1">
         <v>0</v>
@@ -39121,16 +39121,16 @@
         <v>0</v>
       </c>
       <c r="CT118" s="1">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="CU118" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CV118" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="CW118" s="1">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="119" spans="1:101">
@@ -42505,16 +42505,16 @@
         <v>5</v>
       </c>
       <c r="F130" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G130" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H130" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I130" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J130" s="1">
         <v>0</v>
@@ -42781,16 +42781,16 @@
         <v>0</v>
       </c>
       <c r="CT130" s="1">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="CU130" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV130" s="1">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="CW130" s="1">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -44129,7 +44129,7 @@
         <v>1322</v>
       </c>
       <c r="AM135" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN135" s="2">
         <v>11</v>
@@ -44309,7 +44309,7 @@
         <v>131904</v>
       </c>
       <c r="CU135" s="1">
-        <v>3209</v>
+        <v>3212</v>
       </c>
       <c r="CV135" s="1">
         <v>3260</v>
@@ -44413,7 +44413,7 @@
         <v>3</v>
       </c>
       <c r="AF136" s="2">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="AG136" s="2">
         <v>1039</v>
@@ -44617,7 +44617,7 @@
         <v>757</v>
       </c>
       <c r="CV136" s="1">
-        <v>1742</v>
+        <v>1728</v>
       </c>
       <c r="CW136" s="1">
         <v>3120</v>
@@ -44883,7 +44883,7 @@
         <v>373</v>
       </c>
       <c r="CI137" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ137" s="2">
         <v>10</v>
@@ -44919,7 +44919,7 @@
         <v>153790</v>
       </c>
       <c r="CU137" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="CV137" s="1">
         <v>1000</v>
@@ -45265,7 +45265,7 @@
         <v>1180</v>
       </c>
       <c r="K139" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L139" s="2">
         <v>37</v>
@@ -45529,7 +45529,7 @@
         <v>4286</v>
       </c>
       <c r="CU139" s="1">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="CV139" s="1">
         <v>155</v>
@@ -45887,7 +45887,7 @@
         <v>98</v>
       </c>
       <c r="O141" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P141" s="2">
         <v>3</v>
@@ -46058,7 +46058,7 @@
         <v>0</v>
       </c>
       <c r="BT141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU141" s="2">
         <v>2</v>
@@ -46139,10 +46139,10 @@
         <v>558</v>
       </c>
       <c r="CU141" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CV141" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW141" s="1">
         <v>32</v>
@@ -46264,7 +46264,7 @@
         <v>26</v>
       </c>
       <c r="AM142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN142" s="2">
         <v>1</v>
@@ -46408,7 +46408,7 @@
         <v>13</v>
       </c>
       <c r="CI142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ142" s="2">
         <v>1</v>
@@ -46444,7 +46444,7 @@
         <v>567</v>
       </c>
       <c r="CU142" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CV142" s="1">
         <v>22</v>
@@ -46521,7 +46521,7 @@
         <v>9</v>
       </c>
       <c r="W143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X143" s="2">
         <v>1</v>
@@ -46599,7 +46599,7 @@
         <v>4</v>
       </c>
       <c r="AW143" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX143" s="1">
         <v>4</v>
@@ -46749,13 +46749,13 @@
         <v>1594</v>
       </c>
       <c r="CU143" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV143" s="1">
         <v>45</v>
       </c>
       <c r="CW143" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -47074,7 +47074,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="2">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E145" s="2">
         <v>32</v>
@@ -47362,7 +47362,7 @@
         <v>14</v>
       </c>
       <c r="CV145" s="1">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="CW145" s="1">
         <v>114</v>
@@ -49760,16 +49760,16 @@
         <v>0</v>
       </c>
       <c r="CH153" s="1">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="CI153" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CJ153" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="CK153" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="CL153" s="1">
         <v>9</v>
@@ -49796,16 +49796,16 @@
         <v>0</v>
       </c>
       <c r="CT153" s="1">
-        <v>2907</v>
+        <v>2921</v>
       </c>
       <c r="CU153" s="1">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="CV153" s="1">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="CW153" s="1">
-        <v>277</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:101">
@@ -50731,7 +50731,7 @@
         <v>2003</v>
       </c>
       <c r="C157" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D157" s="2">
         <v>30</v>
@@ -51019,7 +51019,7 @@
         <v>70434</v>
       </c>
       <c r="CU157" s="1">
-        <v>1113</v>
+        <v>1105</v>
       </c>
       <c r="CV157" s="1">
         <v>1483</v>
@@ -51380,7 +51380,7 @@
         <v>0</v>
       </c>
       <c r="P159" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q159" s="2">
         <v>165</v>
@@ -51632,7 +51632,7 @@
         <v>170</v>
       </c>
       <c r="CV159" s="1">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="CW159" s="1">
         <v>1523</v>
@@ -52289,16 +52289,16 @@
         <v>148</v>
       </c>
       <c r="N162" s="1">
-        <v>9779</v>
+        <v>9778</v>
       </c>
       <c r="O162" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P162" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q162" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="R162" s="1">
         <v>0</v>
@@ -52541,16 +52541,16 @@
         <v>0</v>
       </c>
       <c r="CT162" s="1">
-        <v>21636</v>
+        <v>21635</v>
       </c>
       <c r="CU162" s="1">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="CV162" s="1">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="CW162" s="1">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="163" spans="1:101">
@@ -53853,7 +53853,7 @@
         <v>65</v>
       </c>
       <c r="AA167" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB167" s="2">
         <v>3</v>
@@ -54069,7 +54069,7 @@
         <v>5121</v>
       </c>
       <c r="CU167" s="1">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="CV167" s="1">
         <v>374</v>
@@ -55037,7 +55037,7 @@
         <v>2725</v>
       </c>
       <c r="O171" s="2">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="P171" s="2">
         <v>77</v>
@@ -55289,7 +55289,7 @@
         <v>19017</v>
       </c>
       <c r="CU171" s="1">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="CV171" s="1">
         <v>747</v>
@@ -55333,7 +55333,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M172" s="2">
         <v>10</v>
@@ -55597,7 +55597,7 @@
         <v>24</v>
       </c>
       <c r="CV172" s="1">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="CW172" s="1">
         <v>94</v>
@@ -57585,7 +57585,7 @@
         <v>2</v>
       </c>
       <c r="AY179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ179" s="2">
         <v>1</v>
@@ -57657,7 +57657,7 @@
         <v>7</v>
       </c>
       <c r="BW179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX179" s="2">
         <v>1</v>
@@ -57669,7 +57669,7 @@
         <v>1</v>
       </c>
       <c r="CA179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB179" s="2">
         <v>1</v>
@@ -57729,7 +57729,7 @@
         <v>82653</v>
       </c>
       <c r="CU179" s="1">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="CV179" s="1">
         <v>2393</v>
@@ -57749,7 +57749,7 @@
         <v>0</v>
       </c>
       <c r="D180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" s="2">
         <v>2</v>
@@ -58037,7 +58037,7 @@
         <v>3</v>
       </c>
       <c r="CV180" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CW180" s="1">
         <v>40</v>
@@ -59699,7 +59699,7 @@
         <v>1</v>
       </c>
       <c r="AR186" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS186" s="2">
         <v>8</v>
@@ -59843,7 +59843,7 @@
         <v>1</v>
       </c>
       <c r="CN186" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO186" s="2">
         <v>6</v>
@@ -59867,7 +59867,7 @@
         <v>3</v>
       </c>
       <c r="CV186" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CW186" s="1">
         <v>21</v>
@@ -61353,7 +61353,7 @@
         <v>154</v>
       </c>
       <c r="CI191" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CJ191" s="2">
         <v>17</v>
@@ -61389,7 +61389,7 @@
         <v>657</v>
       </c>
       <c r="CU191" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CV191" s="1">
         <v>25</v>
@@ -62136,7 +62136,7 @@
         <v>62</v>
       </c>
       <c r="AQ194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR194" s="2">
         <v>3</v>
@@ -62280,7 +62280,7 @@
         <v>27</v>
       </c>
       <c r="CM194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN194" s="2">
         <v>1</v>
@@ -62304,7 +62304,7 @@
         <v>32274</v>
       </c>
       <c r="CU194" s="1">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="CV194" s="1">
         <v>796</v>
@@ -62573,7 +62573,7 @@
         <v>497</v>
       </c>
       <c r="CI195" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ195" s="2">
         <v>11</v>
@@ -62609,7 +62609,7 @@
         <v>67824</v>
       </c>
       <c r="CU195" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="CV195" s="1">
         <v>1964</v>
@@ -62653,7 +62653,7 @@
         <v>12</v>
       </c>
       <c r="L196" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M196" s="2">
         <v>32</v>
@@ -62917,7 +62917,7 @@
         <v>99</v>
       </c>
       <c r="CV196" s="1">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="CW196" s="1">
         <v>235</v>
@@ -63951,16 +63951,16 @@
         <v>0</v>
       </c>
       <c r="AL200" s="1">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM200" s="2">
         <v>2</v>
       </c>
       <c r="AN200" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO200" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP200" s="1">
         <v>24</v>
@@ -64095,16 +64095,16 @@
         <v>0</v>
       </c>
       <c r="CH200" s="1">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="CI200" s="2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="CJ200" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CK200" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="CL200" s="1">
         <v>9</v>
@@ -64131,16 +64131,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16030</v>
+        <v>16034</v>
       </c>
       <c r="CU200" s="1">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="CV200" s="1">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="CW200" s="1">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -66233,7 +66233,7 @@
         <v>3169</v>
       </c>
       <c r="CI207" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CJ207" s="2">
         <v>30</v>
@@ -66269,7 +66269,7 @@
         <v>13705</v>
       </c>
       <c r="CU207" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CV207" s="1">
         <v>295</v>
@@ -66295,16 +66295,16 @@
         <v>6</v>
       </c>
       <c r="F208" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G208" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H208" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I208" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J208" s="1">
         <v>0</v>
@@ -66571,16 +66571,16 @@
         <v>0</v>
       </c>
       <c r="CT208" s="1">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU208" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV208" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CW208" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:101">
@@ -67016,7 +67016,7 @@
         <v>50</v>
       </c>
       <c r="AQ210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR210" s="2">
         <v>3</v>
@@ -67148,7 +67148,7 @@
         <v>385</v>
       </c>
       <c r="CI210" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CJ210" s="2">
         <v>9</v>
@@ -67184,7 +67184,7 @@
         <v>850</v>
       </c>
       <c r="CU210" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CV210" s="1">
         <v>20</v>
@@ -72567,7 +72567,7 @@
         <v>708</v>
       </c>
       <c r="D206">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E206" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3782,16 +3782,16 @@
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>4142</v>
+        <v>4179</v>
       </c>
       <c r="K3" s="2">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="L3" s="2">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="M3" s="2">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="N3" s="1">
         <v>19309</v>
@@ -4046,16 +4046,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>45817</v>
+        <v>45854</v>
       </c>
       <c r="CU3" s="1">
-        <v>609</v>
+        <v>646</v>
       </c>
       <c r="CV3" s="1">
-        <v>1194</v>
+        <v>1231</v>
       </c>
       <c r="CW3" s="1">
-        <v>2220</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4324,7 +4324,7 @@
         <v>78</v>
       </c>
       <c r="CK4" s="2">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="CL4" s="1">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>744</v>
       </c>
       <c r="CW4" s="1">
-        <v>1410</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="BE5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BF5" s="1">
         <v>7</v>
@@ -4665,7 +4665,7 @@
         <v>513</v>
       </c>
       <c r="CW5" s="1">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -7143,7 +7143,7 @@
         <v>22</v>
       </c>
       <c r="L14" s="2">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="M14" s="2">
         <v>82</v>
@@ -7407,7 +7407,7 @@
         <v>22</v>
       </c>
       <c r="CV14" s="1">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="CW14" s="1">
         <v>278</v>
@@ -7613,7 +7613,7 @@
         <v>8</v>
       </c>
       <c r="BO15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP15" s="2">
         <v>1</v>
@@ -7709,7 +7709,7 @@
         <v>3236</v>
       </c>
       <c r="CU15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV15" s="1">
         <v>4</v>
@@ -7753,7 +7753,7 @@
         <v>5</v>
       </c>
       <c r="L16" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2">
         <v>7</v>
@@ -8017,7 +8017,7 @@
         <v>49</v>
       </c>
       <c r="CV16" s="1">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="CW16" s="1">
         <v>152</v>
@@ -10723,7 +10723,7 @@
         <v>31</v>
       </c>
       <c r="CI25" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ25" s="2">
         <v>8</v>
@@ -10759,7 +10759,7 @@
         <v>93</v>
       </c>
       <c r="CU25" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV25" s="1">
         <v>8</v>
@@ -11392,7 +11392,7 @@
         <v>5</v>
       </c>
       <c r="E28" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" s="1">
         <v>30</v>
@@ -11410,7 +11410,7 @@
         <v>917</v>
       </c>
       <c r="K28" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2">
         <v>45</v>
@@ -11512,7 +11512,7 @@
         <v>2</v>
       </c>
       <c r="AS28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT28" s="1">
         <v>0</v>
@@ -11644,7 +11644,7 @@
         <v>14</v>
       </c>
       <c r="CK28" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="CL28" s="1">
         <v>20</v>
@@ -11674,13 +11674,13 @@
         <v>23813</v>
       </c>
       <c r="CU28" s="1">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="CV28" s="1">
         <v>519</v>
       </c>
       <c r="CW28" s="1">
-        <v>754</v>
+        <v>746</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12328,7 +12328,7 @@
         <v>13</v>
       </c>
       <c r="L31" s="2">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="M31" s="2">
         <v>70</v>
@@ -12361,7 +12361,7 @@
         <v>10</v>
       </c>
       <c r="W31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" s="2">
         <v>1</v>
@@ -12409,10 +12409,10 @@
         <v>328</v>
       </c>
       <c r="AM31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AO31" s="2">
         <v>39</v>
@@ -12553,10 +12553,10 @@
         <v>541</v>
       </c>
       <c r="CI31" s="2">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="CJ31" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="CK31" s="2">
         <v>52</v>
@@ -12589,10 +12589,10 @@
         <v>5730</v>
       </c>
       <c r="CU31" s="1">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="CV31" s="1">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="CW31" s="1">
         <v>278</v>
@@ -13246,7 +13246,7 @@
         <v>25</v>
       </c>
       <c r="M34" s="2">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N34" s="1">
         <v>1406</v>
@@ -13327,7 +13327,7 @@
         <v>0</v>
       </c>
       <c r="AN34" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO34" s="2">
         <v>8</v>
@@ -13471,7 +13471,7 @@
         <v>0</v>
       </c>
       <c r="CJ34" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CK34" s="2">
         <v>23</v>
@@ -13507,10 +13507,10 @@
         <v>13</v>
       </c>
       <c r="CV34" s="1">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="CW34" s="1">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -14463,7 +14463,7 @@
         <v>5</v>
       </c>
       <c r="L38" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M38" s="2">
         <v>24</v>
@@ -14556,7 +14556,7 @@
         <v>39</v>
       </c>
       <c r="AQ38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR38" s="2">
         <v>3</v>
@@ -14688,7 +14688,7 @@
         <v>301</v>
       </c>
       <c r="CI38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CJ38" s="2">
         <v>3</v>
@@ -14724,10 +14724,10 @@
         <v>1908</v>
       </c>
       <c r="CU38" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CV38" s="1">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="CW38" s="1">
         <v>129</v>
@@ -14744,7 +14744,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2">
         <v>8</v>
@@ -15032,7 +15032,7 @@
         <v>13</v>
       </c>
       <c r="CV39" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CW39" s="1">
         <v>87</v>
@@ -15082,7 +15082,7 @@
         <v>16484</v>
       </c>
       <c r="O40" s="2">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="P40" s="2">
         <v>599</v>
@@ -15133,7 +15133,7 @@
         <v>0</v>
       </c>
       <c r="AF40" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG40" s="2">
         <v>556</v>
@@ -15160,7 +15160,7 @@
         <v>6</v>
       </c>
       <c r="AO40" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP40" s="1">
         <v>27</v>
@@ -15304,7 +15304,7 @@
         <v>49</v>
       </c>
       <c r="CK40" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="CL40" s="1">
         <v>13</v>
@@ -15334,13 +15334,13 @@
         <v>52603</v>
       </c>
       <c r="CU40" s="1">
-        <v>308</v>
+        <v>113</v>
       </c>
       <c r="CV40" s="1">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="CW40" s="1">
-        <v>2137</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -16078,16 +16078,16 @@
         <v>0</v>
       </c>
       <c r="AP43" s="1">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AQ43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS43" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -16222,40 +16222,40 @@
         <v>0</v>
       </c>
       <c r="CL43" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CM43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO43" s="2">
+        <v>5</v>
+      </c>
+      <c r="CP43" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ43" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR43" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS43" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT43" s="1">
+        <v>541</v>
+      </c>
+      <c r="CU43" s="1">
         <v>4</v>
       </c>
-      <c r="CP43" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT43" s="1">
-        <v>539</v>
-      </c>
-      <c r="CU43" s="1">
-        <v>2</v>
-      </c>
       <c r="CV43" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW43" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:101">
@@ -16326,7 +16326,7 @@
         <v>10</v>
       </c>
       <c r="W44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X44" s="2">
         <v>1</v>
@@ -16377,7 +16377,7 @@
         <v>2</v>
       </c>
       <c r="AN44" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO44" s="2">
         <v>3</v>
@@ -16521,7 +16521,7 @@
         <v>5</v>
       </c>
       <c r="CJ44" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CK44" s="2">
         <v>15</v>
@@ -16554,10 +16554,10 @@
         <v>48683</v>
       </c>
       <c r="CU44" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CV44" s="1">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="CW44" s="1">
         <v>1484</v>
@@ -18099,7 +18099,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="2">
         <v>3</v>
@@ -18387,7 +18387,7 @@
         <v>20</v>
       </c>
       <c r="CV50" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="CW50" s="1">
         <v>49</v>
@@ -18820,7 +18820,7 @@
         <v>14</v>
       </c>
       <c r="AO52" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AP52" s="1">
         <v>0</v>
@@ -18964,7 +18964,7 @@
         <v>12</v>
       </c>
       <c r="CK52" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CL52" s="1">
         <v>0</v>
@@ -19000,7 +19000,7 @@
         <v>30</v>
       </c>
       <c r="CW52" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:101">
@@ -21481,7 +21481,7 @@
         <v>32</v>
       </c>
       <c r="M61" s="2">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="N61" s="1">
         <v>43154</v>
@@ -21577,7 +21577,7 @@
         <v>1</v>
       </c>
       <c r="AS61" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT61" s="1">
         <v>0</v>
@@ -21709,7 +21709,7 @@
         <v>56</v>
       </c>
       <c r="CK61" s="2">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="CL61" s="1">
         <v>7</v>
@@ -21745,7 +21745,7 @@
         <v>507</v>
       </c>
       <c r="CW61" s="1">
-        <v>2589</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22701,7 +22701,7 @@
         <v>60</v>
       </c>
       <c r="M65" s="2">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="N65" s="1">
         <v>57325</v>
@@ -22785,7 +22785,7 @@
         <v>0</v>
       </c>
       <c r="AO65" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP65" s="1">
         <v>60</v>
@@ -22797,7 +22797,7 @@
         <v>2</v>
       </c>
       <c r="AS65" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT65" s="1">
         <v>1</v>
@@ -22830,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BE65" s="2">
         <v>15</v>
@@ -22929,7 +22929,7 @@
         <v>38</v>
       </c>
       <c r="CK65" s="2">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="CL65" s="1">
         <v>34</v>
@@ -22941,7 +22941,7 @@
         <v>2</v>
       </c>
       <c r="CO65" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP65" s="1">
         <v>0</v>
@@ -22962,10 +22962,10 @@
         <v>1634</v>
       </c>
       <c r="CV65" s="1">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="CW65" s="1">
-        <v>3364</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -22979,7 +22979,7 @@
         <v>5</v>
       </c>
       <c r="D66" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E66" s="2">
         <v>22</v>
@@ -23003,7 +23003,7 @@
         <v>10</v>
       </c>
       <c r="L66" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M66" s="2">
         <v>83</v>
@@ -23267,7 +23267,7 @@
         <v>15</v>
       </c>
       <c r="CV66" s="1">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="CW66" s="1">
         <v>105</v>
@@ -23595,16 +23595,16 @@
         <v>8</v>
       </c>
       <c r="F68" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="1">
         <v>305</v>
@@ -23613,7 +23613,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M68" s="2">
         <v>8</v>
@@ -23709,10 +23709,10 @@
         <v>1</v>
       </c>
       <c r="AR68" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS68" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT68" s="1">
         <v>0</v>
@@ -23841,10 +23841,10 @@
         <v>3</v>
       </c>
       <c r="CJ68" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CK68" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="CL68" s="1">
         <v>26</v>
@@ -23871,16 +23871,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="CU68" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CV68" s="1">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="CW68" s="1">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -24223,7 +24223,7 @@
         <v>1</v>
       </c>
       <c r="L70" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2">
         <v>8</v>
@@ -24487,7 +24487,7 @@
         <v>20</v>
       </c>
       <c r="CV70" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CW70" s="1">
         <v>63</v>
@@ -24815,28 +24815,28 @@
         <v>6</v>
       </c>
       <c r="F72" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2">
         <v>2</v>
       </c>
       <c r="I72" s="2">
+        <v>5</v>
+      </c>
+      <c r="J72" s="1">
+        <v>76</v>
+      </c>
+      <c r="K72" s="2">
         <v>4</v>
       </c>
-      <c r="J72" s="1">
-        <v>72</v>
-      </c>
-      <c r="K72" s="2">
-        <v>0</v>
-      </c>
       <c r="L72" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M72" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N72" s="1">
         <v>74</v>
@@ -24923,16 +24923,16 @@
         <v>0</v>
       </c>
       <c r="AP72" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR72" s="2">
         <v>3</v>
       </c>
       <c r="AS72" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT72" s="1">
         <v>0</v>
@@ -25055,16 +25055,16 @@
         <v>0</v>
       </c>
       <c r="CH72" s="1">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="CI72" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CJ72" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CK72" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CL72" s="1">
         <v>0</v>
@@ -25091,16 +25091,16 @@
         <v>0</v>
       </c>
       <c r="CT72" s="1">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="CU72" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="CV72" s="1">
         <v>99</v>
       </c>
       <c r="CW72" s="1">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25114,7 +25114,7 @@
         <v>3</v>
       </c>
       <c r="D73" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E73" s="2">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>2</v>
       </c>
       <c r="AN73" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO73" s="2">
         <v>6</v>
@@ -25366,7 +25366,7 @@
         <v>19</v>
       </c>
       <c r="CJ73" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="CK73" s="2">
         <v>60</v>
@@ -25402,7 +25402,7 @@
         <v>25</v>
       </c>
       <c r="CV73" s="1">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="CW73" s="1">
         <v>78</v>
@@ -25503,7 +25503,7 @@
         <v>0</v>
       </c>
       <c r="AF74" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG74" s="2">
         <v>1247</v>
@@ -25530,7 +25530,7 @@
         <v>271</v>
       </c>
       <c r="AO74" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25581,16 +25581,16 @@
         <v>0</v>
       </c>
       <c r="BF74" s="1">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="BG74" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BH74" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI74" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BJ74" s="1">
         <v>1</v>
@@ -25665,16 +25665,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>15987</v>
+        <v>15993</v>
       </c>
       <c r="CI74" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="CJ74" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="CK74" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,16 +25701,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>169777</v>
+        <v>169786</v>
       </c>
       <c r="CU74" s="1">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="CV74" s="1">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="CW74" s="1">
-        <v>5279</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25838,16 +25838,16 @@
         <v>0</v>
       </c>
       <c r="AP75" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS75" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT75" s="1">
         <v>0</v>
@@ -25982,16 +25982,16 @@
         <v>12</v>
       </c>
       <c r="CL75" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP75" s="1">
         <v>0</v>
@@ -26006,16 +26006,16 @@
         <v>0</v>
       </c>
       <c r="CT75" s="1">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="CU75" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CV75" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CW75" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:101">
@@ -26026,13 +26026,13 @@
         <v>5057</v>
       </c>
       <c r="C76" s="2">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D76" s="2">
         <v>119</v>
       </c>
       <c r="E76" s="2">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -26314,13 +26314,13 @@
         <v>149700</v>
       </c>
       <c r="CU76" s="1">
-        <v>1615</v>
+        <v>1600</v>
       </c>
       <c r="CV76" s="1">
         <v>2427</v>
       </c>
       <c r="CW76" s="1">
-        <v>4207</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26334,7 +26334,7 @@
         <v>40</v>
       </c>
       <c r="D77" s="2">
-        <v>-4286</v>
+        <v>-4389</v>
       </c>
       <c r="E77" s="2">
         <v>-3933</v>
@@ -26352,16 +26352,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4698</v>
+        <v>4697</v>
       </c>
       <c r="K77" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L77" s="2">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="M77" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N77" s="1">
         <v>353290</v>
@@ -26406,7 +26406,7 @@
         <v>0</v>
       </c>
       <c r="AB77" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC77" s="2">
         <v>8</v>
@@ -26439,7 +26439,7 @@
         <v>1860</v>
       </c>
       <c r="AM77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN77" s="2">
         <v>22</v>
@@ -26583,10 +26583,10 @@
         <v>6933</v>
       </c>
       <c r="CI77" s="2">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="CJ77" s="2">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="CK77" s="2">
         <v>475</v>
@@ -26616,16 +26616,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>380639</v>
+        <v>380638</v>
       </c>
       <c r="CU77" s="1">
-        <v>9707</v>
+        <v>9698</v>
       </c>
       <c r="CV77" s="1">
-        <v>5829</v>
+        <v>5645</v>
       </c>
       <c r="CW77" s="1">
-        <v>14657</v>
+        <v>14656</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26747,7 +26747,7 @@
         <v>8</v>
       </c>
       <c r="AN78" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AO78" s="2">
         <v>44</v>
@@ -26885,16 +26885,16 @@
         <v>0</v>
       </c>
       <c r="CH78" s="1">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="CI78" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="CJ78" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="CK78" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="CL78" s="1">
         <v>0</v>
@@ -26921,16 +26921,16 @@
         <v>0</v>
       </c>
       <c r="CT78" s="1">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="CU78" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="CV78" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="CW78" s="1">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -26944,7 +26944,7 @@
         <v>14</v>
       </c>
       <c r="D79" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E79" s="2">
         <v>65</v>
@@ -27232,7 +27232,7 @@
         <v>795</v>
       </c>
       <c r="CV79" s="1">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="CW79" s="1">
         <v>2193</v>
@@ -27668,16 +27668,16 @@
         <v>5</v>
       </c>
       <c r="AP81" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AQ81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS81" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT81" s="1">
         <v>5</v>
@@ -27800,16 +27800,16 @@
         <v>0</v>
       </c>
       <c r="CH81" s="1">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="CI81" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ81" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CK81" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CL81" s="1">
         <v>30</v>
@@ -27836,16 +27836,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6254</v>
+        <v>6259</v>
       </c>
       <c r="CU81" s="1">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="CV81" s="1">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="CW81" s="1">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -27865,16 +27865,16 @@
         <v>2</v>
       </c>
       <c r="F82" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
       </c>
       <c r="H82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="1">
         <v>0</v>
@@ -27973,16 +27973,16 @@
         <v>0</v>
       </c>
       <c r="AP82" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ82" s="2">
         <v>1</v>
       </c>
       <c r="AR82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS82" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT82" s="1">
         <v>0</v>
@@ -28105,22 +28105,22 @@
         <v>0</v>
       </c>
       <c r="CH82" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CI82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL82" s="1">
         <v>67</v>
       </c>
       <c r="CM82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN82" s="2">
         <v>2</v>
@@ -28141,16 +28141,16 @@
         <v>0</v>
       </c>
       <c r="CT82" s="1">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="CU82" s="1">
         <v>3</v>
       </c>
       <c r="CV82" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW82" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -28275,7 +28275,7 @@
         <v>15</v>
       </c>
       <c r="AO83" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP83" s="1">
         <v>0</v>
@@ -28419,7 +28419,7 @@
         <v>124</v>
       </c>
       <c r="CK83" s="2">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="CL83" s="1">
         <v>0</v>
@@ -28455,7 +28455,7 @@
         <v>4569</v>
       </c>
       <c r="CW83" s="1">
-        <v>5695</v>
+        <v>5646</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29193,16 +29193,16 @@
         <v>4</v>
       </c>
       <c r="AP86" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AQ86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR86" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS86" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT86" s="1">
         <v>0</v>
@@ -29325,16 +29325,16 @@
         <v>0</v>
       </c>
       <c r="CH86" s="1">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="CI86" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ86" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CK86" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CL86" s="1">
         <v>35</v>
@@ -29361,16 +29361,16 @@
         <v>0</v>
       </c>
       <c r="CT86" s="1">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="CU86" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CV86" s="1">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="CW86" s="1">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29704,7 +29704,7 @@
         <v>2</v>
       </c>
       <c r="I88" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J88" s="1">
         <v>782</v>
@@ -29716,7 +29716,7 @@
         <v>54</v>
       </c>
       <c r="M88" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="N88" s="1">
         <v>1025</v>
@@ -29812,7 +29812,7 @@
         <v>3</v>
       </c>
       <c r="AS88" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT88" s="1">
         <v>0</v>
@@ -29944,7 +29944,7 @@
         <v>24</v>
       </c>
       <c r="CK88" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="CL88" s="1">
         <v>22</v>
@@ -29980,7 +29980,7 @@
         <v>311</v>
       </c>
       <c r="CW88" s="1">
-        <v>417</v>
+        <v>398</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -30117,7 +30117,7 @@
         <v>3</v>
       </c>
       <c r="AS89" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT89" s="1">
         <v>0</v>
@@ -30249,7 +30249,7 @@
         <v>7</v>
       </c>
       <c r="CK89" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CL89" s="1">
         <v>9</v>
@@ -30285,7 +30285,7 @@
         <v>133</v>
       </c>
       <c r="CW89" s="1">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30622,16 +30622,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="1">
-        <v>5234</v>
+        <v>5233</v>
       </c>
       <c r="K91" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L91" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M91" s="2">
-        <v>434</v>
+        <v>342</v>
       </c>
       <c r="N91" s="1">
         <v>4396</v>
@@ -30886,16 +30886,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25442</v>
+        <v>25441</v>
       </c>
       <c r="CU91" s="1">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="CV91" s="1">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="CW91" s="1">
-        <v>978</v>
+        <v>886</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -33989,16 +33989,16 @@
         <v>209</v>
       </c>
       <c r="N102" s="1">
-        <v>14441</v>
+        <v>14442</v>
       </c>
       <c r="O102" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P102" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q102" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="R102" s="1">
         <v>0</v>
@@ -34076,10 +34076,10 @@
         <v>34</v>
       </c>
       <c r="AQ102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS102" s="2">
         <v>3</v>
@@ -34208,10 +34208,10 @@
         <v>1746</v>
       </c>
       <c r="CI102" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CJ102" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="CK102" s="2">
         <v>74</v>
@@ -34241,16 +34241,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>42247</v>
+        <v>42248</v>
       </c>
       <c r="CU102" s="1">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="CV102" s="1">
-        <v>1036</v>
+        <v>1019</v>
       </c>
       <c r="CW102" s="1">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34952,16 +34952,16 @@
         <v>0</v>
       </c>
       <c r="AD105" s="1">
-        <v>4094</v>
+        <v>4319</v>
       </c>
       <c r="AE105" s="2">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="AF105" s="2">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="AG105" s="2">
-        <v>144</v>
+        <v>369</v>
       </c>
       <c r="AH105" s="1">
         <v>0</v>
@@ -34988,16 +34988,16 @@
         <v>2</v>
       </c>
       <c r="AP105" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AQ105" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR105" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS105" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT105" s="1">
         <v>8</v>
@@ -35156,16 +35156,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7547</v>
+        <v>7773</v>
       </c>
       <c r="CU105" s="1">
-        <v>26</v>
+        <v>252</v>
       </c>
       <c r="CV105" s="1">
-        <v>73</v>
+        <v>299</v>
       </c>
       <c r="CW105" s="1">
-        <v>279</v>
+        <v>505</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -36426,7 +36426,7 @@
         <v>206</v>
       </c>
       <c r="M110" s="2">
-        <v>395</v>
+        <v>332</v>
       </c>
       <c r="N110" s="1">
         <v>1283</v>
@@ -36510,7 +36510,7 @@
         <v>2</v>
       </c>
       <c r="AO110" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP110" s="1">
         <v>0</v>
@@ -36654,7 +36654,7 @@
         <v>87</v>
       </c>
       <c r="CK110" s="2">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="CL110" s="1">
         <v>0</v>
@@ -36690,7 +36690,7 @@
         <v>584</v>
       </c>
       <c r="CW110" s="1">
-        <v>1060</v>
+        <v>969</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36806,16 +36806,16 @@
         <v>0</v>
       </c>
       <c r="AL111" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN111" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO111" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP111" s="1">
         <v>44</v>
@@ -36986,16 +36986,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="CU111" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV111" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CW111" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37033,7 +37033,7 @@
         <v>14</v>
       </c>
       <c r="L112" s="2">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M112" s="2">
         <v>80</v>
@@ -37297,7 +37297,7 @@
         <v>325</v>
       </c>
       <c r="CV112" s="1">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="CW112" s="1">
         <v>735</v>
@@ -37338,7 +37338,7 @@
         <v>141</v>
       </c>
       <c r="L113" s="2">
-        <v>291</v>
+        <v>217</v>
       </c>
       <c r="M113" s="2">
         <v>442</v>
@@ -37602,7 +37602,7 @@
         <v>437</v>
       </c>
       <c r="CV113" s="1">
-        <v>9471</v>
+        <v>9397</v>
       </c>
       <c r="CW113" s="1">
         <v>14267</v>
@@ -37619,22 +37619,22 @@
         <v>1</v>
       </c>
       <c r="D114" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" s="2">
         <v>2</v>
       </c>
       <c r="F114" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J114" s="1">
         <v>0</v>
@@ -37901,16 +37901,16 @@
         <v>0</v>
       </c>
       <c r="CT114" s="1">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="CU114" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV114" s="1">
         <v>3</v>
       </c>
       <c r="CW114" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:101">
@@ -38403,16 +38403,16 @@
         <v>0</v>
       </c>
       <c r="BJ116" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BK116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN116" s="1">
         <v>927</v>
@@ -38511,16 +38511,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21340</v>
+        <v>21341</v>
       </c>
       <c r="CU116" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CV116" s="1">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="CW116" s="1">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -39390,16 +39390,16 @@
         <v>0</v>
       </c>
       <c r="CH119" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CI119" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CJ119" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CK119" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CL119" s="1">
         <v>0</v>
@@ -39426,16 +39426,16 @@
         <v>0</v>
       </c>
       <c r="CT119" s="1">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CU119" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CV119" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CW119" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -39464,7 +39464,7 @@
         <v>3</v>
       </c>
       <c r="I120" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J120" s="1">
         <v>0</v>
@@ -39740,7 +39740,7 @@
         <v>11</v>
       </c>
       <c r="CW120" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -40783,16 +40783,16 @@
         <v>0</v>
       </c>
       <c r="AP124" s="1">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AQ124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR124" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS124" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT124" s="1">
         <v>0</v>
@@ -40927,40 +40927,40 @@
         <v>1</v>
       </c>
       <c r="CL124" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="CM124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN124" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO124" s="2">
+        <v>5</v>
+      </c>
+      <c r="CP124" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ124" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR124" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS124" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT124" s="1">
+        <v>923</v>
+      </c>
+      <c r="CU124" s="1">
         <v>4</v>
       </c>
-      <c r="CP124" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ124" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR124" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS124" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT124" s="1">
-        <v>921</v>
-      </c>
-      <c r="CU124" s="1">
-        <v>2</v>
-      </c>
       <c r="CV124" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CW124" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:101">
@@ -41997,7 +41997,7 @@
         <v>3</v>
       </c>
       <c r="AN128" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO128" s="2">
         <v>19</v>
@@ -42141,7 +42141,7 @@
         <v>9</v>
       </c>
       <c r="CJ128" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CK128" s="2">
         <v>16</v>
@@ -42177,7 +42177,7 @@
         <v>12</v>
       </c>
       <c r="CV128" s="1">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="CW128" s="1">
         <v>68</v>
@@ -42203,7 +42203,7 @@
         <v>37</v>
       </c>
       <c r="G129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" s="2">
         <v>2</v>
@@ -42479,7 +42479,7 @@
         <v>288</v>
       </c>
       <c r="CU129" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV129" s="1">
         <v>8</v>
@@ -42502,7 +42502,7 @@
         <v>2</v>
       </c>
       <c r="E130" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F130" s="1">
         <v>42</v>
@@ -42790,7 +42790,7 @@
         <v>188</v>
       </c>
       <c r="CW130" s="1">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -44138,16 +44138,16 @@
         <v>20</v>
       </c>
       <c r="AP135" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AQ135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT135" s="1">
         <v>0</v>
@@ -44270,16 +44270,16 @@
         <v>0</v>
       </c>
       <c r="CH135" s="1">
-        <v>2692</v>
+        <v>2708</v>
       </c>
       <c r="CI135" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CJ135" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="CK135" s="2">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="CL135" s="1">
         <v>9</v>
@@ -44306,16 +44306,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>131904</v>
+        <v>131921</v>
       </c>
       <c r="CU135" s="1">
-        <v>3205</v>
+        <v>3222</v>
       </c>
       <c r="CV135" s="1">
-        <v>3257</v>
+        <v>3274</v>
       </c>
       <c r="CW135" s="1">
-        <v>5817</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44359,16 +44359,16 @@
         <v>401</v>
       </c>
       <c r="N136" s="1">
-        <v>31682</v>
+        <v>31681</v>
       </c>
       <c r="O136" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="P136" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Q136" s="2">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="R136" s="1">
         <v>0</v>
@@ -44440,7 +44440,7 @@
         <v>2</v>
       </c>
       <c r="AO136" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP136" s="1">
         <v>23</v>
@@ -44584,7 +44584,7 @@
         <v>66</v>
       </c>
       <c r="CK136" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="CL136" s="1">
         <v>13</v>
@@ -44611,16 +44611,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>61627</v>
+        <v>61626</v>
       </c>
       <c r="CU136" s="1">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="CV136" s="1">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="CW136" s="1">
-        <v>3040</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -45364,7 +45364,7 @@
         <v>1</v>
       </c>
       <c r="AR139" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS139" s="2">
         <v>2</v>
@@ -45496,7 +45496,7 @@
         <v>2</v>
       </c>
       <c r="CJ139" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CK139" s="2">
         <v>15</v>
@@ -45532,7 +45532,7 @@
         <v>113</v>
       </c>
       <c r="CV139" s="1">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="CW139" s="1">
         <v>270</v>
@@ -46061,7 +46061,7 @@
         <v>0</v>
       </c>
       <c r="BU141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV141" s="1">
         <v>0</v>
@@ -46145,7 +46145,7 @@
         <v>12</v>
       </c>
       <c r="CW141" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46584,7 +46584,7 @@
         <v>2</v>
       </c>
       <c r="AR143" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS143" s="2">
         <v>5</v>
@@ -46716,7 +46716,7 @@
         <v>0</v>
       </c>
       <c r="CJ143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK143" s="2">
         <v>5</v>
@@ -46752,7 +46752,7 @@
         <v>20</v>
       </c>
       <c r="CV143" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="CW143" s="1">
         <v>78</v>
@@ -47074,7 +47074,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" s="2">
         <v>32</v>
@@ -47188,16 +47188,16 @@
         <v>3</v>
       </c>
       <c r="AP145" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AQ145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS145" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT145" s="1">
         <v>0</v>
@@ -47332,16 +47332,16 @@
         <v>0</v>
       </c>
       <c r="CL145" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="CM145" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN145" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO145" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CP145" s="1">
         <v>0</v>
@@ -47356,16 +47356,16 @@
         <v>0</v>
       </c>
       <c r="CT145" s="1">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="CU145" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CV145" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CW145" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -49027,7 +49027,7 @@
         <v>3</v>
       </c>
       <c r="AS151" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT151" s="1">
         <v>0</v>
@@ -49159,7 +49159,7 @@
         <v>3</v>
       </c>
       <c r="CK151" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CL151" s="1">
         <v>50</v>
@@ -49195,7 +49195,7 @@
         <v>8</v>
       </c>
       <c r="CW151" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:101">
@@ -49637,7 +49637,7 @@
         <v>3</v>
       </c>
       <c r="AS153" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT153" s="1">
         <v>0</v>
@@ -49805,7 +49805,7 @@
         <v>209</v>
       </c>
       <c r="CW153" s="1">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="154" spans="1:101">
@@ -50761,7 +50761,7 @@
         <v>82</v>
       </c>
       <c r="M157" s="2">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="N157" s="1">
         <v>60190</v>
@@ -50854,7 +50854,7 @@
         <v>0</v>
       </c>
       <c r="AR157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS157" s="2">
         <v>4</v>
@@ -50986,7 +50986,7 @@
         <v>5</v>
       </c>
       <c r="CJ157" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="CK157" s="2">
         <v>67</v>
@@ -51022,10 +51022,10 @@
         <v>1088</v>
       </c>
       <c r="CV157" s="1">
-        <v>1482</v>
+        <v>1471</v>
       </c>
       <c r="CW157" s="1">
-        <v>2552</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -52364,7 +52364,7 @@
         <v>152</v>
       </c>
       <c r="AM162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN162" s="2">
         <v>3</v>
@@ -52379,7 +52379,7 @@
         <v>0</v>
       </c>
       <c r="AR162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS162" s="2">
         <v>2</v>
@@ -52508,10 +52508,10 @@
         <v>785</v>
       </c>
       <c r="CI162" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CJ162" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CK162" s="2">
         <v>24</v>
@@ -52544,10 +52544,10 @@
         <v>21636</v>
       </c>
       <c r="CU162" s="1">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="CV162" s="1">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="CW162" s="1">
         <v>1061</v>
@@ -52977,7 +52977,7 @@
         <v>0</v>
       </c>
       <c r="AN164" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO164" s="2">
         <v>3</v>
@@ -53121,7 +53121,7 @@
         <v>0</v>
       </c>
       <c r="CJ164" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CK164" s="2">
         <v>15</v>
@@ -53157,7 +53157,7 @@
         <v>3</v>
       </c>
       <c r="CV164" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="CW164" s="1">
         <v>58</v>
@@ -53907,7 +53907,7 @@
         <v>2</v>
       </c>
       <c r="AS167" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT167" s="1">
         <v>0</v>
@@ -53970,16 +53970,16 @@
         <v>0</v>
       </c>
       <c r="BN167" s="1">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="BO167" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BP167" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BQ167" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BR167" s="1">
         <v>13</v>
@@ -54039,7 +54039,7 @@
         <v>1</v>
       </c>
       <c r="CK167" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CL167" s="1">
         <v>32</v>
@@ -54066,16 +54066,16 @@
         <v>0</v>
       </c>
       <c r="CT167" s="1">
-        <v>5121</v>
+        <v>5120</v>
       </c>
       <c r="CU167" s="1">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="CV167" s="1">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="CW167" s="1">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="168" spans="1:101">
@@ -54415,10 +54415,10 @@
         <v>1278</v>
       </c>
       <c r="K169" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L169" s="2">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="M169" s="2">
         <v>147</v>
@@ -54505,13 +54505,13 @@
         <v>1</v>
       </c>
       <c r="AO169" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP169" s="1">
         <v>32</v>
       </c>
       <c r="AQ169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR169" s="2">
         <v>1</v>
@@ -54643,13 +54643,13 @@
         <v>407</v>
       </c>
       <c r="CI169" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CJ169" s="2">
         <v>23</v>
       </c>
       <c r="CK169" s="2">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="CL169" s="1">
         <v>4</v>
@@ -54679,13 +54679,13 @@
         <v>5792</v>
       </c>
       <c r="CU169" s="1">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="CV169" s="1">
-        <v>446</v>
+        <v>398</v>
       </c>
       <c r="CW169" s="1">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -54945,16 +54945,16 @@
         <v>0</v>
       </c>
       <c r="CH170" s="1">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="CI170" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CJ170" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="CK170" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CL170" s="1">
         <v>0</v>
@@ -54981,16 +54981,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="CU170" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CV170" s="1">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="CW170" s="1">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -54998,16 +54998,16 @@
         <v>270</v>
       </c>
       <c r="B171" s="1">
-        <v>4453</v>
+        <v>4475</v>
       </c>
       <c r="C171" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D171" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="E171" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F171" s="1">
         <v>0</v>
@@ -55088,7 +55088,7 @@
         <v>0</v>
       </c>
       <c r="AF171" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AG171" s="2">
         <v>364</v>
@@ -55286,16 +55286,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>19017</v>
+        <v>19039</v>
       </c>
       <c r="CU171" s="1">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="CV171" s="1">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="CW171" s="1">
-        <v>1303</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -55342,7 +55342,7 @@
         <v>2679</v>
       </c>
       <c r="O172" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P172" s="2">
         <v>21</v>
@@ -55501,7 +55501,7 @@
         <v>0</v>
       </c>
       <c r="BP172" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ172" s="2">
         <v>3</v>
@@ -55594,10 +55594,10 @@
         <v>5784</v>
       </c>
       <c r="CU172" s="1">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="CV172" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="CW172" s="1">
         <v>94</v>
@@ -56254,16 +56254,16 @@
         <v>0</v>
       </c>
       <c r="N175" s="1">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="O175" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P175" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q175" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R175" s="1">
         <v>0</v>
@@ -56506,16 +56506,16 @@
         <v>0</v>
       </c>
       <c r="CT175" s="1">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="CU175" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="CV175" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="CW175" s="1">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="176" spans="1:101">
@@ -56945,7 +56945,7 @@
         <v>35</v>
       </c>
       <c r="AO177" s="2">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="AP177" s="1">
         <v>0</v>
@@ -57089,7 +57089,7 @@
         <v>54</v>
       </c>
       <c r="CK177" s="2">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="CL177" s="1">
         <v>0</v>
@@ -57125,7 +57125,7 @@
         <v>94</v>
       </c>
       <c r="CW177" s="1">
-        <v>193</v>
+        <v>159</v>
       </c>
     </row>
     <row r="178" spans="1:101">
@@ -57471,7 +57471,7 @@
         <v>54</v>
       </c>
       <c r="M179" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="N179" s="1">
         <v>71146</v>
@@ -57555,7 +57555,7 @@
         <v>10</v>
       </c>
       <c r="AO179" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP179" s="1">
         <v>30</v>
@@ -57699,7 +57699,7 @@
         <v>95</v>
       </c>
       <c r="CK179" s="2">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="CL179" s="1">
         <v>7</v>
@@ -57735,7 +57735,7 @@
         <v>2393</v>
       </c>
       <c r="CW179" s="1">
-        <v>4717</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -62052,7 +62052,7 @@
         <v>28685</v>
       </c>
       <c r="O194" s="2">
-        <v>736</v>
+        <v>-18</v>
       </c>
       <c r="P194" s="2">
         <v>736</v>
@@ -62076,7 +62076,7 @@
         <v>9</v>
       </c>
       <c r="W194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X194" s="2">
         <v>1</v>
@@ -62139,7 +62139,7 @@
         <v>1</v>
       </c>
       <c r="AR194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS194" s="2">
         <v>6</v>
@@ -62271,7 +62271,7 @@
         <v>1</v>
       </c>
       <c r="CJ194" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CK194" s="2">
         <v>12</v>
@@ -62304,10 +62304,10 @@
         <v>32276</v>
       </c>
       <c r="CU194" s="1">
-        <v>748</v>
+        <v>-7</v>
       </c>
       <c r="CV194" s="1">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="CW194" s="1">
         <v>1320</v>
@@ -62647,16 +62647,16 @@
         <v>0</v>
       </c>
       <c r="J196" s="1">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K196" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L196" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M196" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N196" s="1">
         <v>3363</v>
@@ -62911,16 +62911,16 @@
         <v>0</v>
       </c>
       <c r="CT196" s="1">
-        <v>5390</v>
+        <v>5393</v>
       </c>
       <c r="CU196" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CV196" s="1">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="CW196" s="1">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -64157,7 +64157,7 @@
         <v>63</v>
       </c>
       <c r="E201" s="2">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="F201" s="1">
         <v>0</v>
@@ -64265,7 +64265,7 @@
         <v>6</v>
       </c>
       <c r="AO201" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP201" s="1">
         <v>24</v>
@@ -64409,7 +64409,7 @@
         <v>70</v>
       </c>
       <c r="CK201" s="2">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="CL201" s="1">
         <v>5</v>
@@ -64445,7 +64445,7 @@
         <v>1220</v>
       </c>
       <c r="CW201" s="1">
-        <v>2276</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -66233,7 +66233,7 @@
         <v>3169</v>
       </c>
       <c r="CI207" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CJ207" s="2">
         <v>30</v>
@@ -66269,7 +66269,7 @@
         <v>13705</v>
       </c>
       <c r="CU207" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CV207" s="1">
         <v>295</v>
@@ -67219,7 +67219,7 @@
         <v>1</v>
       </c>
       <c r="I211" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J211" s="1">
         <v>1234</v>
@@ -67228,7 +67228,7 @@
         <v>25</v>
       </c>
       <c r="L211" s="2">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M211" s="2">
         <v>66</v>
@@ -67492,10 +67492,10 @@
         <v>82</v>
       </c>
       <c r="CV211" s="1">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="CW211" s="1">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69060,7 +69060,7 @@
         <v>559</v>
       </c>
       <c r="D32">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E32" t="s">
         <v>717</v>
@@ -71152,7 +71152,7 @@
         <v>648</v>
       </c>
       <c r="D136">
-        <v>10246</v>
+        <v>10247</v>
       </c>
       <c r="E136" t="s">
         <v>717</v>
@@ -71292,7 +71292,7 @@
         <v>655</v>
       </c>
       <c r="D143">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E143" t="s">
         <v>717</v>
@@ -72361,7 +72361,7 @@
         <v>700</v>
       </c>
       <c r="D196">
-        <v>10199</v>
+        <v>10203</v>
       </c>
       <c r="E196" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4171,16 +4171,16 @@
         <v>0</v>
       </c>
       <c r="AL4" s="1">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AM4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO4" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP4" s="1">
         <v>0</v>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="CH4" s="1">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="CI4" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CJ4" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="CK4" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="CL4" s="1">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="CT4" s="1">
-        <v>42537</v>
+        <v>42548</v>
       </c>
       <c r="CU4" s="1">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="CV4" s="1">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="CW4" s="1">
-        <v>1370</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -6506,7 +6506,7 @@
         <v>104</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -6794,7 +6794,7 @@
         <v>229</v>
       </c>
       <c r="CU12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV12" s="1">
         <v>4</v>
@@ -7750,7 +7750,7 @@
         <v>114</v>
       </c>
       <c r="K16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2">
         <v>5</v>
@@ -8014,7 +8014,7 @@
         <v>951</v>
       </c>
       <c r="CU16" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="CV16" s="1">
         <v>53</v>
@@ -8345,292 +8345,292 @@
         <v>2</v>
       </c>
       <c r="F18" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2">
+        <v>5</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>0</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ18" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH18" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL18" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP18" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT18" s="1">
+        <v>170</v>
+      </c>
+      <c r="CU18" s="1">
+        <v>2</v>
+      </c>
+      <c r="CV18" s="1">
         <v>4</v>
       </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
-        <v>0</v>
-      </c>
-      <c r="T18" s="2">
-        <v>0</v>
-      </c>
-      <c r="U18" s="2">
-        <v>0</v>
-      </c>
-      <c r="V18" s="1">
-        <v>0</v>
-      </c>
-      <c r="W18" s="2">
-        <v>0</v>
-      </c>
-      <c r="X18" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ18" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD18" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH18" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL18" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP18" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT18" s="1">
-        <v>169</v>
-      </c>
-      <c r="CU18" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV18" s="1">
-        <v>3</v>
-      </c>
       <c r="CW18" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:101">
@@ -12603,16 +12603,16 @@
         <v>131</v>
       </c>
       <c r="B32" s="1">
-        <v>2566</v>
+        <v>2581</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D32" s="2">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -12753,7 +12753,7 @@
         <v>1</v>
       </c>
       <c r="AZ32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA32" s="2">
         <v>4</v>
@@ -12891,16 +12891,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>10906</v>
+        <v>10921</v>
       </c>
       <c r="CU32" s="1">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="CV32" s="1">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="CW32" s="1">
-        <v>691</v>
+        <v>706</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -14846,16 +14846,16 @@
         <v>0</v>
       </c>
       <c r="AL39" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AM39" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN39" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO39" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AP39" s="1">
         <v>13</v>
@@ -14990,16 +14990,16 @@
         <v>0</v>
       </c>
       <c r="CH39" s="1">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="CI39" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CJ39" s="2">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="CK39" s="2">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="CL39" s="1">
         <v>2</v>
@@ -15026,16 +15026,16 @@
         <v>0</v>
       </c>
       <c r="CT39" s="1">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="CU39" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CV39" s="1">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="CW39" s="1">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -15351,7 +15351,7 @@
         <v>23</v>
       </c>
       <c r="C41" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D41" s="2">
         <v>6</v>
@@ -15459,7 +15459,7 @@
         <v>68</v>
       </c>
       <c r="AM41" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN41" s="2">
         <v>15</v>
@@ -15603,7 +15603,7 @@
         <v>501</v>
       </c>
       <c r="CI41" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CJ41" s="2">
         <v>18</v>
@@ -15639,7 +15639,7 @@
         <v>654</v>
       </c>
       <c r="CU41" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CV41" s="1">
         <v>41</v>
@@ -22447,16 +22447,16 @@
         <v>5</v>
       </c>
       <c r="AD64" s="1">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="AE64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF64" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG64" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22651,16 +22651,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>7851</v>
+        <v>7852</v>
       </c>
       <c r="CU64" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CV64" s="1">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="CW64" s="1">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -25521,16 +25521,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36169</v>
+        <v>36172</v>
       </c>
       <c r="AM74" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="AN74" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AO74" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25665,16 +25665,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16015</v>
+        <v>16017</v>
       </c>
       <c r="CI74" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="CJ74" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="CK74" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,16 +25701,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>169950</v>
+        <v>169955</v>
       </c>
       <c r="CU74" s="1">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="CV74" s="1">
-        <v>2619</v>
+        <v>2624</v>
       </c>
       <c r="CW74" s="1">
-        <v>5361</v>
+        <v>5366</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26331,7 +26331,7 @@
         <v>10824</v>
       </c>
       <c r="C77" s="2">
-        <v>-115</v>
+        <v>-40</v>
       </c>
       <c r="D77" s="2">
         <v>-4429</v>
@@ -26355,7 +26355,7 @@
         <v>4741</v>
       </c>
       <c r="K77" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L77" s="2">
         <v>143</v>
@@ -26490,7 +26490,7 @@
         <v>0</v>
       </c>
       <c r="BD77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE77" s="2">
         <v>1</v>
@@ -26619,10 +26619,10 @@
         <v>380744</v>
       </c>
       <c r="CU77" s="1">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="CV77" s="1">
-        <v>5691</v>
+        <v>5690</v>
       </c>
       <c r="CW77" s="1">
         <v>14615</v>
@@ -27076,7 +27076,7 @@
         <v>1</v>
       </c>
       <c r="AV79" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW79" s="2">
         <v>3</v>
@@ -27232,7 +27232,7 @@
         <v>191</v>
       </c>
       <c r="CV79" s="1">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="CW79" s="1">
         <v>2238</v>
@@ -27587,7 +27587,7 @@
         <v>3535</v>
       </c>
       <c r="O81" s="2">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="P81" s="2">
         <v>147</v>
@@ -27839,7 +27839,7 @@
         <v>6277</v>
       </c>
       <c r="CU81" s="1">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="CV81" s="1">
         <v>219</v>
@@ -30598,16 +30598,16 @@
         <v>190</v>
       </c>
       <c r="B91" s="1">
-        <v>6991</v>
+        <v>7048</v>
       </c>
       <c r="C91" s="2">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="D91" s="2">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="E91" s="2">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -30886,16 +30886,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25519</v>
+        <v>25576</v>
       </c>
       <c r="CU91" s="1">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="CV91" s="1">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="CW91" s="1">
-        <v>921</v>
+        <v>978</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -32246,7 +32246,7 @@
         <v>43</v>
       </c>
       <c r="AQ96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR96" s="2">
         <v>2</v>
@@ -32414,7 +32414,7 @@
         <v>954</v>
       </c>
       <c r="CU96" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV96" s="1">
         <v>30</v>
@@ -32440,16 +32440,16 @@
         <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I97" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J97" s="1">
         <v>0</v>
@@ -32716,16 +32716,16 @@
         <v>0</v>
       </c>
       <c r="CT97" s="1">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="CU97" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV97" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CW97" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -33355,16 +33355,16 @@
         <v>0</v>
       </c>
       <c r="F100" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G100" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I100" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J100" s="1">
         <v>0</v>
@@ -33631,16 +33631,16 @@
         <v>0</v>
       </c>
       <c r="CT100" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CU100" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CV100" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CW100" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -37003,16 +37003,16 @@
         <v>211</v>
       </c>
       <c r="B112" s="1">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C112" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D112" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E112" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -37291,16 +37291,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8028</v>
+        <v>8034</v>
       </c>
       <c r="CU112" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="CV112" s="1">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="CW112" s="1">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37560,16 +37560,16 @@
         <v>0</v>
       </c>
       <c r="CH113" s="1">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="CI113" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CJ113" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="CK113" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37596,16 +37596,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173405</v>
+        <v>173409</v>
       </c>
       <c r="CU113" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="CV113" s="1">
-        <v>9397</v>
+        <v>9401</v>
       </c>
       <c r="CW113" s="1">
-        <v>14222</v>
+        <v>14226</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38454,7 +38454,7 @@
         <v>1</v>
       </c>
       <c r="CA116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB116" s="2">
         <v>1</v>
@@ -38514,7 +38514,7 @@
         <v>21428</v>
       </c>
       <c r="CU116" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="CV116" s="1">
         <v>766</v>
@@ -39458,7 +39458,7 @@
         <v>46</v>
       </c>
       <c r="G120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="2">
         <v>3</v>
@@ -39734,7 +39734,7 @@
         <v>347</v>
       </c>
       <c r="CU120" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CV120" s="1">
         <v>35</v>
@@ -41288,7 +41288,7 @@
         <v>62</v>
       </c>
       <c r="G126" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2">
         <v>3</v>
@@ -41564,7 +41564,7 @@
         <v>822</v>
       </c>
       <c r="CU126" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV126" s="1">
         <v>4</v>
@@ -46168,7 +46168,7 @@
         <v>13</v>
       </c>
       <c r="G142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2">
         <v>2</v>
@@ -46444,7 +46444,7 @@
         <v>1597</v>
       </c>
       <c r="CU142" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV142" s="1">
         <v>45</v>
@@ -47218,7 +47218,7 @@
         <v>3</v>
       </c>
       <c r="AZ145" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA145" s="2">
         <v>9</v>
@@ -47362,7 +47362,7 @@
         <v>13</v>
       </c>
       <c r="CV145" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="CW145" s="1">
         <v>141</v>
@@ -49203,16 +49203,16 @@
         <v>251</v>
       </c>
       <c r="B152" s="1">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D152" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E152" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F152" s="1">
         <v>21</v>
@@ -49491,16 +49491,16 @@
         <v>0</v>
       </c>
       <c r="CT152" s="1">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="CU152" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CV152" s="1">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CW152" s="1">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50980,16 +50980,16 @@
         <v>0</v>
       </c>
       <c r="CH157" s="1">
-        <v>4772</v>
+        <v>4774</v>
       </c>
       <c r="CI157" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CJ157" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="CK157" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="CL157" s="1">
         <v>9</v>
@@ -51016,16 +51016,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>161181</v>
+        <v>161183</v>
       </c>
       <c r="CU157" s="1">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="CV157" s="1">
-        <v>3946</v>
+        <v>3948</v>
       </c>
       <c r="CW157" s="1">
-        <v>5640</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51057,16 +51057,16 @@
         <v>0</v>
       </c>
       <c r="J158" s="1">
-        <v>6864</v>
+        <v>6863</v>
       </c>
       <c r="K158" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L158" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M158" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N158" s="1">
         <v>2969</v>
@@ -51321,16 +51321,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>24785</v>
+        <v>24784</v>
       </c>
       <c r="CU158" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="CV158" s="1">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="CW158" s="1">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -53512,7 +53512,7 @@
         <v>2171</v>
       </c>
       <c r="O166" s="2">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="P166" s="2">
         <v>123</v>
@@ -53764,7 +53764,7 @@
         <v>5154</v>
       </c>
       <c r="CU166" s="1">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="CV166" s="1">
         <v>402</v>
@@ -54720,7 +54720,7 @@
         <v>6268</v>
       </c>
       <c r="K170" s="2">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="L170" s="2">
         <v>206</v>
@@ -54984,7 +54984,7 @@
         <v>19144</v>
       </c>
       <c r="CU170" s="1">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="CV170" s="1">
         <v>770</v>
@@ -58060,292 +58060,292 @@
         <v>0</v>
       </c>
       <c r="F181" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G181" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="2">
+        <v>3</v>
+      </c>
+      <c r="I181" s="2">
+        <v>6</v>
+      </c>
+      <c r="J181" s="1">
+        <v>0</v>
+      </c>
+      <c r="K181" s="2">
+        <v>0</v>
+      </c>
+      <c r="L181" s="2">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2">
+        <v>0</v>
+      </c>
+      <c r="N181" s="1">
+        <v>0</v>
+      </c>
+      <c r="O181" s="2">
+        <v>0</v>
+      </c>
+      <c r="P181" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="2">
+        <v>0</v>
+      </c>
+      <c r="R181" s="1">
+        <v>0</v>
+      </c>
+      <c r="S181" s="2">
+        <v>0</v>
+      </c>
+      <c r="T181" s="2">
+        <v>0</v>
+      </c>
+      <c r="U181" s="2">
+        <v>0</v>
+      </c>
+      <c r="V181" s="1">
+        <v>0</v>
+      </c>
+      <c r="W181" s="2">
+        <v>0</v>
+      </c>
+      <c r="X181" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT181" s="1">
+        <v>77</v>
+      </c>
+      <c r="CU181" s="1">
         <v>2</v>
       </c>
-      <c r="I181" s="2">
-        <v>5</v>
-      </c>
-      <c r="J181" s="1">
-        <v>0</v>
-      </c>
-      <c r="K181" s="2">
-        <v>0</v>
-      </c>
-      <c r="L181" s="2">
-        <v>0</v>
-      </c>
-      <c r="M181" s="2">
-        <v>0</v>
-      </c>
-      <c r="N181" s="1">
-        <v>0</v>
-      </c>
-      <c r="O181" s="2">
-        <v>0</v>
-      </c>
-      <c r="P181" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q181" s="2">
-        <v>0</v>
-      </c>
-      <c r="R181" s="1">
-        <v>0</v>
-      </c>
-      <c r="S181" s="2">
-        <v>0</v>
-      </c>
-      <c r="T181" s="2">
-        <v>0</v>
-      </c>
-      <c r="U181" s="2">
-        <v>0</v>
-      </c>
-      <c r="V181" s="1">
-        <v>0</v>
-      </c>
-      <c r="W181" s="2">
-        <v>0</v>
-      </c>
-      <c r="X181" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y181" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT181" s="1">
-        <v>76</v>
-      </c>
-      <c r="CU181" s="1">
-        <v>1</v>
-      </c>
       <c r="CV181" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW181" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -61338,16 +61338,16 @@
         <v>0</v>
       </c>
       <c r="CD191" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CE191" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF191" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG191" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH191" s="1">
         <v>154</v>
@@ -61386,16 +61386,16 @@
         <v>0</v>
       </c>
       <c r="CT191" s="1">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="CU191" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV191" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CW191" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="192" spans="1:101">
@@ -61415,16 +61415,16 @@
         <v>0</v>
       </c>
       <c r="F192" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G192" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I192" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J192" s="1">
         <v>0</v>
@@ -61691,16 +61691,16 @@
         <v>0</v>
       </c>
       <c r="CT192" s="1">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="CU192" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV192" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CW192" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62052,7 +62052,7 @@
         <v>28678</v>
       </c>
       <c r="O194" s="2">
-        <v>-25</v>
+        <v>-12</v>
       </c>
       <c r="P194" s="2">
         <v>729</v>
@@ -62304,7 +62304,7 @@
         <v>32287</v>
       </c>
       <c r="CU194" s="1">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="CV194" s="1">
         <v>794</v>
@@ -66905,16 +66905,16 @@
         <v>2</v>
       </c>
       <c r="F210" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I210" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J210" s="1">
         <v>2</v>
@@ -67097,16 +67097,16 @@
         <v>0</v>
       </c>
       <c r="BR210" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BS210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU210" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV210" s="1">
         <v>1</v>
@@ -67181,16 +67181,16 @@
         <v>0</v>
       </c>
       <c r="CT210" s="1">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="CU210" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV210" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CW210" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -71132,7 +71132,7 @@
         <v>647</v>
       </c>
       <c r="D135">
-        <v>10253</v>
+        <v>10254</v>
       </c>
       <c r="E135" t="s">
         <v>717</v>
@@ -72467,7 +72467,7 @@
         <v>705</v>
       </c>
       <c r="D201">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E201" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -6506,7 +6506,7 @@
         <v>104</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -6794,7 +6794,7 @@
         <v>229</v>
       </c>
       <c r="CU12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV12" s="1">
         <v>4</v>
@@ -8979,16 +8979,16 @@
         <v>67</v>
       </c>
       <c r="N20" s="1">
-        <v>12426</v>
+        <v>12427</v>
       </c>
       <c r="O20" s="2">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P20" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q20" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9231,16 +9231,16 @@
         <v>0</v>
       </c>
       <c r="CT20" s="1">
-        <v>20354</v>
+        <v>20355</v>
       </c>
       <c r="CU20" s="1">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="CV20" s="1">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="CW20" s="1">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -13835,16 +13835,16 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
@@ -14111,16 +14111,16 @@
         <v>0</v>
       </c>
       <c r="CT36" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CU36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW36" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:101">
@@ -16290,7 +16290,7 @@
         <v>1293</v>
       </c>
       <c r="K44" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
         <v>35</v>
@@ -16554,7 +16554,7 @@
         <v>48683</v>
       </c>
       <c r="CU44" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CV44" s="1">
         <v>482</v>
@@ -18650,16 +18650,16 @@
         <v>0</v>
       </c>
       <c r="CH51" s="1">
-        <v>991</v>
+        <v>1018</v>
       </c>
       <c r="CI51" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="CJ51" s="2">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="CK51" s="2">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="CL51" s="1">
         <v>0</v>
@@ -18686,16 +18686,16 @@
         <v>0</v>
       </c>
       <c r="CT51" s="1">
-        <v>1716</v>
+        <v>1743</v>
       </c>
       <c r="CU51" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="CV51" s="1">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="CW51" s="1">
-        <v>222</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -25665,16 +25665,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16017</v>
+        <v>16022</v>
       </c>
       <c r="CI74" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="CJ74" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="CK74" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,16 +25701,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>169955</v>
+        <v>169960</v>
       </c>
       <c r="CU74" s="1">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="CV74" s="1">
-        <v>2624</v>
+        <v>2629</v>
       </c>
       <c r="CW74" s="1">
-        <v>5366</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26744,7 +26744,7 @@
         <v>79</v>
       </c>
       <c r="AM78" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AN78" s="2">
         <v>25</v>
@@ -26888,7 +26888,7 @@
         <v>140</v>
       </c>
       <c r="CI78" s="2">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="CJ78" s="2">
         <v>69</v>
@@ -26924,7 +26924,7 @@
         <v>245</v>
       </c>
       <c r="CU78" s="1">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="CV78" s="1">
         <v>97</v>
@@ -27351,16 +27351,16 @@
         <v>0</v>
       </c>
       <c r="AL80" s="1">
-        <v>724</v>
+        <v>753</v>
       </c>
       <c r="AM80" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AN80" s="2">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="AO80" s="2">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="AP80" s="1">
         <v>0</v>
@@ -27495,16 +27495,16 @@
         <v>1</v>
       </c>
       <c r="CH80" s="1">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="CI80" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CJ80" s="2">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="CK80" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="CL80" s="1">
         <v>0</v>
@@ -27531,16 +27531,16 @@
         <v>0</v>
       </c>
       <c r="CT80" s="1">
-        <v>1620</v>
+        <v>1656</v>
       </c>
       <c r="CU80" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CV80" s="1">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="CW80" s="1">
-        <v>213</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -29325,16 +29325,16 @@
         <v>0</v>
       </c>
       <c r="CH86" s="1">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="CI86" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CJ86" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CK86" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL86" s="1">
         <v>35</v>
@@ -29361,16 +29361,16 @@
         <v>0</v>
       </c>
       <c r="CT86" s="1">
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="CU86" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV86" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CW86" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29390,16 +29390,16 @@
         <v>1</v>
       </c>
       <c r="F87" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G87" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H87" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" s="1">
         <v>0</v>
@@ -29666,16 +29666,16 @@
         <v>0</v>
       </c>
       <c r="CT87" s="1">
-        <v>2962</v>
+        <v>2965</v>
       </c>
       <c r="CU87" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="CV87" s="1">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="CW87" s="1">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -30850,16 +30850,16 @@
         <v>0</v>
       </c>
       <c r="CH91" s="1">
-        <v>7672</v>
+        <v>7699</v>
       </c>
       <c r="CI91" s="2">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="CJ91" s="2">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="CK91" s="2">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="CL91" s="1">
         <v>5</v>
@@ -30886,16 +30886,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25576</v>
+        <v>25603</v>
       </c>
       <c r="CU91" s="1">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="CV91" s="1">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="CW91" s="1">
-        <v>978</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -33358,7 +33358,7 @@
         <v>46</v>
       </c>
       <c r="G100" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="2">
         <v>3</v>
@@ -33454,7 +33454,7 @@
         <v>57</v>
       </c>
       <c r="AM100" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN100" s="2">
         <v>11</v>
@@ -33598,7 +33598,7 @@
         <v>34</v>
       </c>
       <c r="CI100" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CJ100" s="2">
         <v>8</v>
@@ -33634,7 +33634,7 @@
         <v>149</v>
       </c>
       <c r="CU100" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CV100" s="1">
         <v>22</v>
@@ -34895,7 +34895,7 @@
         <v>964</v>
       </c>
       <c r="K105" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2">
         <v>19</v>
@@ -35159,7 +35159,7 @@
         <v>7779</v>
       </c>
       <c r="CU105" s="1">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="CV105" s="1">
         <v>275</v>
@@ -36432,7 +36432,7 @@
         <v>1283</v>
       </c>
       <c r="O110" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P110" s="2">
         <v>42</v>
@@ -36684,7 +36684,7 @@
         <v>12987</v>
       </c>
       <c r="CU110" s="1">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="CV110" s="1">
         <v>605</v>
@@ -44751,7 +44751,7 @@
         <v>61</v>
       </c>
       <c r="AQ137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR137" s="2">
         <v>3</v>
@@ -44895,7 +44895,7 @@
         <v>41</v>
       </c>
       <c r="CM137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN137" s="2">
         <v>3</v>
@@ -44919,7 +44919,7 @@
         <v>624</v>
       </c>
       <c r="CU137" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CV137" s="1">
         <v>17</v>
@@ -46177,16 +46177,16 @@
         <v>2</v>
       </c>
       <c r="J142" s="1">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="K142" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="L142" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="M142" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="N142" s="1">
         <v>553</v>
@@ -46345,16 +46345,16 @@
         <v>0</v>
       </c>
       <c r="BN142" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BO142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR142" s="1">
         <v>27</v>
@@ -46441,16 +46441,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>1597</v>
+        <v>1612</v>
       </c>
       <c r="CU142" s="1">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="CV142" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="CW142" s="1">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -50130,16 +50130,16 @@
         <v>7</v>
       </c>
       <c r="F155" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I155" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J155" s="1">
         <v>547</v>
@@ -50406,16 +50406,16 @@
         <v>0</v>
       </c>
       <c r="CT155" s="1">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="CU155" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CV155" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CW155" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50839,7 +50839,7 @@
         <v>1047</v>
       </c>
       <c r="AM157" s="2">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="AN157" s="2">
         <v>-37</v>
@@ -51019,7 +51019,7 @@
         <v>161183</v>
       </c>
       <c r="CU157" s="1">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="CV157" s="1">
         <v>3948</v>
@@ -51057,16 +51057,16 @@
         <v>0</v>
       </c>
       <c r="J158" s="1">
-        <v>6863</v>
+        <v>6942</v>
       </c>
       <c r="K158" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L158" s="2">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="M158" s="2">
-        <v>356</v>
+        <v>435</v>
       </c>
       <c r="N158" s="1">
         <v>2969</v>
@@ -51321,16 +51321,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>24784</v>
+        <v>24863</v>
       </c>
       <c r="CU158" s="1">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="CV158" s="1">
-        <v>798</v>
+        <v>877</v>
       </c>
       <c r="CW158" s="1">
-        <v>1489</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -54499,7 +54499,7 @@
         <v>117</v>
       </c>
       <c r="AM169" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AN169" s="2">
         <v>14</v>
@@ -54643,7 +54643,7 @@
         <v>175</v>
       </c>
       <c r="CI169" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="CJ169" s="2">
         <v>28</v>
@@ -54679,7 +54679,7 @@
         <v>350</v>
       </c>
       <c r="CU169" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="CV169" s="1">
         <v>45</v>
@@ -56523,16 +56523,16 @@
         <v>275</v>
       </c>
       <c r="B176" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D176" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E176" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1">
         <v>51</v>
@@ -56811,16 +56811,16 @@
         <v>0</v>
       </c>
       <c r="CT176" s="1">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="CU176" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CV176" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="CW176" s="1">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -58063,7 +58063,7 @@
         <v>69</v>
       </c>
       <c r="G181" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H181" s="2">
         <v>3</v>
@@ -58339,7 +58339,7 @@
         <v>77</v>
       </c>
       <c r="CU181" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV181" s="1">
         <v>3</v>
@@ -62052,7 +62052,7 @@
         <v>28678</v>
       </c>
       <c r="O194" s="2">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="P194" s="2">
         <v>729</v>
@@ -62304,7 +62304,7 @@
         <v>32287</v>
       </c>
       <c r="CU194" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CV194" s="1">
         <v>794</v>
@@ -70549,7 +70549,7 @@
         <v>622</v>
       </c>
       <c r="D106">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E106" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BJ3" s="1">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>1183</v>
       </c>
       <c r="CW3" s="1">
-        <v>2252</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4240,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="2">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="BJ4" s="1">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>742</v>
       </c>
       <c r="CW4" s="1">
-        <v>1381</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
         <v>3</v>
@@ -5612,16 +5612,16 @@
         <v>2</v>
       </c>
       <c r="J9" s="1">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N9" s="1">
         <v>1524</v>
@@ -5876,16 +5876,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2814</v>
+        <v>2815</v>
       </c>
       <c r="CU9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CV9" s="1">
         <v>46</v>
       </c>
       <c r="CW9" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -6503,16 +6503,16 @@
         <v>111</v>
       </c>
       <c r="B12" s="1">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="F12" s="1">
         <v>17</v>
@@ -6791,16 +6791,16 @@
         <v>0</v>
       </c>
       <c r="CT12" s="1">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="CU12" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CV12" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CW12" s="1">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -7155,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="P14" s="2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="2">
         <v>38</v>
@@ -7167,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" s="2">
         <v>1</v>
@@ -7407,7 +7407,7 @@
         <v>15</v>
       </c>
       <c r="CV14" s="1">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="CW14" s="1">
         <v>293</v>
@@ -8985,7 +8985,7 @@
         <v>29</v>
       </c>
       <c r="P20" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q20" s="2">
         <v>598</v>
@@ -9237,7 +9237,7 @@
         <v>86</v>
       </c>
       <c r="CV20" s="1">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="CW20" s="1">
         <v>976</v>
@@ -12298,16 +12298,16 @@
         <v>130</v>
       </c>
       <c r="B31" s="1">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C31" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2">
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" s="1">
         <v>21</v>
@@ -12586,16 +12586,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>5746</v>
+        <v>5748</v>
       </c>
       <c r="CU31" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CV31" s="1">
         <v>160</v>
       </c>
       <c r="CW31" s="1">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12750,7 +12750,7 @@
         <v>24</v>
       </c>
       <c r="AY32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ32" s="2">
         <v>1</v>
@@ -12894,7 +12894,7 @@
         <v>10921</v>
       </c>
       <c r="CU32" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CV32" s="1">
         <v>332</v>
@@ -13237,16 +13237,16 @@
         <v>4</v>
       </c>
       <c r="J34" s="1">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="K34" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L34" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="M34" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="N34" s="1">
         <v>1406</v>
@@ -13258,7 +13258,7 @@
         <v>33</v>
       </c>
       <c r="Q34" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R34" s="1">
         <v>1</v>
@@ -13285,16 +13285,16 @@
         <v>1</v>
       </c>
       <c r="Z34" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AA34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD34" s="1">
         <v>0</v>
@@ -13501,16 +13501,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2515</v>
+        <v>2529</v>
       </c>
       <c r="CU34" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="CV34" s="1">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="CW34" s="1">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -14562,7 +14562,7 @@
         <v>3</v>
       </c>
       <c r="AS38" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -14706,7 +14706,7 @@
         <v>1</v>
       </c>
       <c r="CO38" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP38" s="1">
         <v>0</v>
@@ -14730,7 +14730,7 @@
         <v>75</v>
       </c>
       <c r="CW38" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -14750,16 +14750,16 @@
         <v>8</v>
       </c>
       <c r="F39" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="1">
         <v>0</v>
@@ -15026,16 +15026,16 @@
         <v>0</v>
       </c>
       <c r="CT39" s="1">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="CU39" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CV39" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="CW39" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -15241,7 +15241,7 @@
         <v>0</v>
       </c>
       <c r="BP40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ40" s="2">
         <v>1</v>
@@ -15337,7 +15337,7 @@
         <v>108</v>
       </c>
       <c r="CV40" s="1">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="CW40" s="1">
         <v>2185</v>
@@ -16461,7 +16461,7 @@
         <v>0</v>
       </c>
       <c r="BP44" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BQ44" s="2">
         <v>6</v>
@@ -16557,7 +16557,7 @@
         <v>0</v>
       </c>
       <c r="CV44" s="1">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="CW44" s="1">
         <v>1456</v>
@@ -17489,7 +17489,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="2">
         <v>2</v>
@@ -17501,10 +17501,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" s="1">
         <v>0</v>
@@ -17777,10 +17777,10 @@
         <v>0</v>
       </c>
       <c r="CV48" s="1">
+        <v>0</v>
+      </c>
+      <c r="CW48" s="1">
         <v>3</v>
-      </c>
-      <c r="CW48" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:101">
@@ -17806,7 +17806,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I49" s="2">
         <v>6</v>
@@ -18082,7 +18082,7 @@
         <v>0</v>
       </c>
       <c r="CV49" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CW49" s="1">
         <v>6</v>
@@ -18258,7 +18258,7 @@
         <v>0</v>
       </c>
       <c r="BE50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF50" s="1">
         <v>0</v>
@@ -18390,7 +18390,7 @@
         <v>40</v>
       </c>
       <c r="CW50" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -18407,7 +18407,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -18659,7 +18659,7 @@
         <v>135</v>
       </c>
       <c r="CK51" s="2">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="CL51" s="1">
         <v>0</v>
@@ -18695,7 +18695,7 @@
         <v>154</v>
       </c>
       <c r="CW51" s="1">
-        <v>249</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
@@ -19302,10 +19302,10 @@
         <v>1</v>
       </c>
       <c r="CV53" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW53" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:101">
@@ -20240,292 +20240,292 @@
         <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2">
+        <v>3</v>
+      </c>
+      <c r="I57" s="2">
+        <v>6</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="2">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="2">
+        <v>0</v>
+      </c>
+      <c r="X57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT57" s="1">
+        <v>63</v>
+      </c>
+      <c r="CU57" s="1">
         <v>2</v>
       </c>
-      <c r="I57" s="2">
-        <v>5</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2">
-        <v>0</v>
-      </c>
-      <c r="L57" s="2">
-        <v>0</v>
-      </c>
-      <c r="M57" s="2">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="O57" s="2">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-      <c r="T57" s="2">
-        <v>0</v>
-      </c>
-      <c r="U57" s="2">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
-      <c r="W57" s="2">
-        <v>0</v>
-      </c>
-      <c r="X57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT57" s="1">
-        <v>62</v>
-      </c>
-      <c r="CU57" s="1">
-        <v>1</v>
-      </c>
       <c r="CV57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW57" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:101">
@@ -20883,7 +20883,7 @@
         <v>7</v>
       </c>
       <c r="Q59" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="R59" s="1">
         <v>0</v>
@@ -20967,7 +20967,7 @@
         <v>3</v>
       </c>
       <c r="AS59" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT59" s="1">
         <v>0</v>
@@ -21111,7 +21111,7 @@
         <v>2</v>
       </c>
       <c r="CO59" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP59" s="1">
         <v>0</v>
@@ -21135,7 +21135,7 @@
         <v>24</v>
       </c>
       <c r="CW59" s="1">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -21152,7 +21152,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="2">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="F60" s="1">
         <v>5</v>
@@ -21440,7 +21440,7 @@
         <v>0</v>
       </c>
       <c r="CW60" s="1">
-        <v>10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61" spans="1:101">
@@ -21625,7 +21625,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BJ61" s="1">
         <v>0</v>
@@ -21745,7 +21745,7 @@
         <v>491</v>
       </c>
       <c r="CW61" s="1">
-        <v>2561</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22453,7 +22453,7 @@
         <v>2</v>
       </c>
       <c r="AF64" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG64" s="2">
         <v>153</v>
@@ -22657,7 +22657,7 @@
         <v>25</v>
       </c>
       <c r="CV64" s="1">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="CW64" s="1">
         <v>484</v>
@@ -22866,7 +22866,7 @@
         <v>0</v>
       </c>
       <c r="BP65" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BQ65" s="2">
         <v>10</v>
@@ -22962,7 +22962,7 @@
         <v>41</v>
       </c>
       <c r="CV65" s="1">
-        <v>1774</v>
+        <v>1764</v>
       </c>
       <c r="CW65" s="1">
         <v>3362</v>
@@ -23284,7 +23284,7 @@
         <v>15</v>
       </c>
       <c r="D67" s="2">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E67" s="2">
         <v>88</v>
@@ -23572,7 +23572,7 @@
         <v>15</v>
       </c>
       <c r="CV67" s="1">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="CW67" s="1">
         <v>88</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="1">
         <v>0</v>
@@ -24185,7 +24185,7 @@
         <v>0</v>
       </c>
       <c r="CW69" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:101">
@@ -24199,10 +24199,10 @@
         <v>0</v>
       </c>
       <c r="D70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70" s="1">
         <v>12</v>
@@ -24487,10 +24487,10 @@
         <v>20</v>
       </c>
       <c r="CV70" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CW70" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25120,16 +25120,16 @@
         <v>9</v>
       </c>
       <c r="F73" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" s="1">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="CT73" s="1">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="CU73" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CV73" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CW73" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25521,16 +25521,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36172</v>
+        <v>36178</v>
       </c>
       <c r="AM74" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AN74" s="2">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="AO74" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25614,7 +25614,7 @@
         <v>7</v>
       </c>
       <c r="BQ74" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BR74" s="1">
         <v>0</v>
@@ -25665,16 +25665,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16022</v>
+        <v>16025</v>
       </c>
       <c r="CI74" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="CJ74" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="CK74" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,16 +25701,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>169960</v>
+        <v>169969</v>
       </c>
       <c r="CU74" s="1">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="CV74" s="1">
-        <v>2629</v>
+        <v>2606</v>
       </c>
       <c r="CW74" s="1">
-        <v>5369</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26068,7 +26068,7 @@
         <v>1506</v>
       </c>
       <c r="Q76" s="2">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26200,7 +26200,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ76" s="1">
         <v>0</v>
@@ -26505,7 +26505,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BJ77" s="1">
         <v>0</v>
@@ -26529,7 +26529,7 @@
         <v>11</v>
       </c>
       <c r="BQ77" s="2">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="BR77" s="1">
         <v>0</v>
@@ -26625,7 +26625,7 @@
         <v>5690</v>
       </c>
       <c r="CW77" s="1">
-        <v>14615</v>
+        <v>14570</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27115,7 +27115,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BJ79" s="1">
         <v>0</v>
@@ -27235,7 +27235,7 @@
         <v>1256</v>
       </c>
       <c r="CW79" s="1">
-        <v>2237</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -28248,7 +28248,7 @@
         <v>0</v>
       </c>
       <c r="AF83" s="2">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="AG83" s="2">
         <v>3598</v>
@@ -28296,7 +28296,7 @@
         <v>1</v>
       </c>
       <c r="AV83" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW83" s="2">
         <v>5</v>
@@ -28335,7 +28335,7 @@
         <v>13</v>
       </c>
       <c r="BI83" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BJ83" s="1">
         <v>1</v>
@@ -28452,10 +28452,10 @@
         <v>125</v>
       </c>
       <c r="CV83" s="1">
-        <v>4553</v>
+        <v>4549</v>
       </c>
       <c r="CW83" s="1">
-        <v>5664</v>
+        <v>5658</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29082,7 +29082,7 @@
         <v>4</v>
       </c>
       <c r="E86" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F86" s="1">
         <v>42</v>
@@ -29370,7 +29370,7 @@
         <v>45</v>
       </c>
       <c r="CW86" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29851,16 +29851,16 @@
         <v>0</v>
       </c>
       <c r="BF88" s="1">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BG88" s="2">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BH88" s="2">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BI88" s="2">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BJ88" s="1">
         <v>0</v>
@@ -29971,16 +29971,16 @@
         <v>0</v>
       </c>
       <c r="CT88" s="1">
-        <v>9467</v>
+        <v>9456</v>
       </c>
       <c r="CU88" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="CV88" s="1">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="CW88" s="1">
-        <v>409</v>
+        <v>398</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -30012,16 +30012,16 @@
         <v>2</v>
       </c>
       <c r="J89" s="1">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="K89" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L89" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M89" s="2">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="N89" s="1">
         <v>43</v>
@@ -30030,7 +30030,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="2">
         <v>6</v>
@@ -30276,16 +30276,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2091</v>
+        <v>2100</v>
       </c>
       <c r="CU89" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="CV89" s="1">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="CW89" s="1">
-        <v>378</v>
+        <v>387</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30775,7 +30775,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ91" s="1">
         <v>0</v>
@@ -30895,7 +30895,7 @@
         <v>474</v>
       </c>
       <c r="CW91" s="1">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -31525,16 +31525,16 @@
         <v>1</v>
       </c>
       <c r="F94" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G94" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" s="2">
         <v>2</v>
       </c>
       <c r="I94" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J94" s="1">
         <v>0</v>
@@ -31801,16 +31801,16 @@
         <v>0</v>
       </c>
       <c r="CT94" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="CU94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV94" s="1">
         <v>3</v>
       </c>
       <c r="CW94" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:101">
@@ -32548,16 +32548,16 @@
         <v>0</v>
       </c>
       <c r="AP97" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AQ97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR97" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS97" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT97" s="1">
         <v>0</v>
@@ -32680,16 +32680,16 @@
         <v>0</v>
       </c>
       <c r="CH97" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CI97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ97" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK97" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CL97" s="1">
         <v>33</v>
@@ -32716,16 +32716,16 @@
         <v>0</v>
       </c>
       <c r="CT97" s="1">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="CU97" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CV97" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW97" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -33050,16 +33050,16 @@
         <v>0</v>
       </c>
       <c r="F99" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="2">
         <v>3</v>
       </c>
       <c r="I99" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J99" s="1">
         <v>0</v>
@@ -33326,16 +33326,16 @@
         <v>0</v>
       </c>
       <c r="CT99" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CU99" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV99" s="1">
         <v>3</v>
       </c>
       <c r="CW99" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:101">
@@ -33998,7 +33998,7 @@
         <v>334</v>
       </c>
       <c r="Q102" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="R102" s="1">
         <v>0</v>
@@ -34088,7 +34088,7 @@
         <v>58</v>
       </c>
       <c r="AU102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV102" s="2">
         <v>2</v>
@@ -34100,7 +34100,7 @@
         <v>17</v>
       </c>
       <c r="AY102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ102" s="2">
         <v>2</v>
@@ -34130,7 +34130,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BJ102" s="1">
         <v>0</v>
@@ -34244,13 +34244,13 @@
         <v>42393</v>
       </c>
       <c r="CU102" s="1">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="CV102" s="1">
         <v>980</v>
       </c>
       <c r="CW102" s="1">
-        <v>1892</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34267,7 +34267,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F103" s="1">
         <v>9</v>
@@ -34279,7 +34279,7 @@
         <v>1</v>
       </c>
       <c r="I103" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J103" s="1">
         <v>0</v>
@@ -34555,7 +34555,7 @@
         <v>71</v>
       </c>
       <c r="CW103" s="1">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -34584,7 +34584,7 @@
         <v>3</v>
       </c>
       <c r="I104" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J104" s="1">
         <v>0</v>
@@ -34860,7 +34860,7 @@
         <v>3</v>
       </c>
       <c r="CW104" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:101">
@@ -36402,7 +36402,7 @@
         <v>40</v>
       </c>
       <c r="E110" s="2">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -36417,16 +36417,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="1">
-        <v>4757</v>
+        <v>4756</v>
       </c>
       <c r="K110" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L110" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M110" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N110" s="1">
         <v>1283</v>
@@ -36570,7 +36570,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BJ110" s="1">
         <v>0</v>
@@ -36681,16 +36681,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>12987</v>
+        <v>12986</v>
       </c>
       <c r="CU110" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="CV110" s="1">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="CW110" s="1">
-        <v>1048</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36710,16 +36710,16 @@
         <v>2</v>
       </c>
       <c r="F111" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I111" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J111" s="1">
         <v>0</v>
@@ -36986,16 +36986,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="CU111" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV111" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="CW111" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37485,7 +37485,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="BJ113" s="1">
         <v>0</v>
@@ -37569,7 +37569,7 @@
         <v>89</v>
       </c>
       <c r="CK113" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37605,7 +37605,7 @@
         <v>9401</v>
       </c>
       <c r="CW113" s="1">
-        <v>14226</v>
+        <v>14194</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38591,7 +38591,7 @@
         <v>9</v>
       </c>
       <c r="W117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X117" s="2">
         <v>1</v>
@@ -38636,16 +38636,16 @@
         <v>0</v>
       </c>
       <c r="AL117" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AM117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO117" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP117" s="1">
         <v>61</v>
@@ -38792,16 +38792,16 @@
         <v>13</v>
       </c>
       <c r="CL117" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CM117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO117" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP117" s="1">
         <v>0</v>
@@ -38816,16 +38816,16 @@
         <v>0</v>
       </c>
       <c r="CT117" s="1">
-        <v>12757</v>
+        <v>12759</v>
       </c>
       <c r="CU117" s="1">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="CV117" s="1">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="CW117" s="1">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -38851,7 +38851,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I118" s="2">
         <v>2</v>
@@ -39127,7 +39127,7 @@
         <v>14</v>
       </c>
       <c r="CV118" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW118" s="1">
         <v>19</v>
@@ -39174,16 +39174,16 @@
         <v>0</v>
       </c>
       <c r="N119" s="1">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R119" s="1">
         <v>2</v>
@@ -39426,16 +39426,16 @@
         <v>0</v>
       </c>
       <c r="CT119" s="1">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="CU119" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV119" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CW119" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -39760,16 +39760,16 @@
         <v>0</v>
       </c>
       <c r="F121" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G121" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="2">
         <v>3</v>
       </c>
       <c r="I121" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J121" s="1">
         <v>0</v>
@@ -40036,16 +40036,16 @@
         <v>0</v>
       </c>
       <c r="CT121" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CU121" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV121" s="1">
         <v>3</v>
       </c>
       <c r="CW121" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:101">
@@ -40370,16 +40370,16 @@
         <v>0</v>
       </c>
       <c r="F123" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I123" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J123" s="1">
         <v>142</v>
@@ -40646,16 +40646,16 @@
         <v>0</v>
       </c>
       <c r="CT123" s="1">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="CU123" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV123" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CW123" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -40675,16 +40675,16 @@
         <v>0</v>
       </c>
       <c r="F124" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G124" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H124" s="2">
         <v>3</v>
       </c>
       <c r="I124" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J124" s="1">
         <v>0</v>
@@ -40951,16 +40951,16 @@
         <v>0</v>
       </c>
       <c r="CT124" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="CU124" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV124" s="1">
         <v>3</v>
       </c>
       <c r="CW124" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:101">
@@ -41381,16 +41381,16 @@
         <v>0</v>
       </c>
       <c r="AL126" s="1">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM126" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN126" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AO126" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP126" s="1">
         <v>18</v>
@@ -41561,16 +41561,16 @@
         <v>0</v>
       </c>
       <c r="CT126" s="1">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="CU126" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="CV126" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CW126" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:101">
@@ -41578,16 +41578,16 @@
         <v>226</v>
       </c>
       <c r="B127" s="1">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="C127" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D127" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E127" s="2">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -41866,16 +41866,16 @@
         <v>0</v>
       </c>
       <c r="CT127" s="1">
-        <v>2532</v>
+        <v>2543</v>
       </c>
       <c r="CU127" s="1">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CV127" s="1">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="CW127" s="1">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="128" spans="1:101">
@@ -42009,7 +42009,7 @@
         <v>0</v>
       </c>
       <c r="AR128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS128" s="2">
         <v>3</v>
@@ -42141,7 +42141,7 @@
         <v>0</v>
       </c>
       <c r="CJ128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK128" s="2">
         <v>3</v>
@@ -42177,7 +42177,7 @@
         <v>0</v>
       </c>
       <c r="CV128" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CW128" s="1">
         <v>15</v>
@@ -43713,16 +43713,16 @@
         <v>233</v>
       </c>
       <c r="B134" s="1">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C134" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D134" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E134" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -44001,16 +44001,16 @@
         <v>0</v>
       </c>
       <c r="CT134" s="1">
-        <v>131921</v>
+        <v>131925</v>
       </c>
       <c r="CU134" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="CV134" s="1">
-        <v>3263</v>
+        <v>3267</v>
       </c>
       <c r="CW134" s="1">
-        <v>5834</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44341,7 +44341,7 @@
         <v>0</v>
       </c>
       <c r="H136" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="2">
         <v>2</v>
@@ -44617,7 +44617,7 @@
         <v>8</v>
       </c>
       <c r="CV136" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="CW136" s="1">
         <v>3445</v>
@@ -44754,7 +44754,7 @@
         <v>0</v>
       </c>
       <c r="AR137" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS137" s="2">
         <v>6</v>
@@ -44898,7 +44898,7 @@
         <v>0</v>
       </c>
       <c r="CN137" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO137" s="2">
         <v>5</v>
@@ -44922,7 +44922,7 @@
         <v>9</v>
       </c>
       <c r="CV137" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CW137" s="1">
         <v>70</v>
@@ -47379,7 +47379,7 @@
         <v>0</v>
       </c>
       <c r="D146" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" s="2">
         <v>1</v>
@@ -47391,10 +47391,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2">
+        <v>0</v>
+      </c>
+      <c r="I146" s="2">
         <v>2</v>
-      </c>
-      <c r="I146" s="2">
-        <v>4</v>
       </c>
       <c r="J146" s="1">
         <v>0</v>
@@ -47667,10 +47667,10 @@
         <v>0</v>
       </c>
       <c r="CV146" s="1">
+        <v>0</v>
+      </c>
+      <c r="CW146" s="1">
         <v>3</v>
-      </c>
-      <c r="CW146" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:101">
@@ -49529,7 +49529,7 @@
         <v>3</v>
       </c>
       <c r="I153" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J153" s="1">
         <v>0</v>
@@ -49805,7 +49805,7 @@
         <v>4</v>
       </c>
       <c r="CW153" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="1:101">
@@ -50432,7 +50432,7 @@
         <v>30</v>
       </c>
       <c r="E156" s="2">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -50720,7 +50720,7 @@
         <v>1480</v>
       </c>
       <c r="CW156" s="1">
-        <v>2564</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -50905,7 +50905,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BJ157" s="1">
         <v>0</v>
@@ -50920,16 +50920,16 @@
         <v>0</v>
       </c>
       <c r="BN157" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BO157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR157" s="1">
         <v>16</v>
@@ -51016,16 +51016,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>161183</v>
+        <v>161184</v>
       </c>
       <c r="CU157" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="CV157" s="1">
-        <v>3948</v>
+        <v>3949</v>
       </c>
       <c r="CW157" s="1">
-        <v>5640</v>
+        <v>5632</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51237,16 +51237,16 @@
         <v>0</v>
       </c>
       <c r="BR158" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BS158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT158" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU158" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV158" s="1">
         <v>0</v>
@@ -51321,16 +51321,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>24863</v>
+        <v>24864</v>
       </c>
       <c r="CU158" s="1">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="CV158" s="1">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="CW158" s="1">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51356,10 +51356,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2">
+        <v>0</v>
+      </c>
+      <c r="I159" s="2">
         <v>2</v>
-      </c>
-      <c r="I159" s="2">
-        <v>5</v>
       </c>
       <c r="J159" s="1">
         <v>0</v>
@@ -51632,10 +51632,10 @@
         <v>0</v>
       </c>
       <c r="CV159" s="1">
+        <v>0</v>
+      </c>
+      <c r="CW159" s="1">
         <v>2</v>
-      </c>
-      <c r="CW159" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:101">
@@ -51990,7 +51990,7 @@
         <v>0</v>
       </c>
       <c r="P161" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q161" s="2">
         <v>538</v>
@@ -52098,7 +52098,7 @@
         <v>1</v>
       </c>
       <c r="AZ161" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA161" s="2">
         <v>5</v>
@@ -52242,7 +52242,7 @@
         <v>51</v>
       </c>
       <c r="CV161" s="1">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="CW161" s="1">
         <v>1081</v>
@@ -52887,16 +52887,16 @@
         <v>6</v>
       </c>
       <c r="J164" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K164" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L164" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M164" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N164" s="1">
         <v>241</v>
@@ -53151,16 +53151,16 @@
         <v>0</v>
       </c>
       <c r="CT164" s="1">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="CU164" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CV164" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="CW164" s="1">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53180,292 +53180,292 @@
         <v>2</v>
       </c>
       <c r="F165" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G165" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I165" s="2">
+        <v>6</v>
+      </c>
+      <c r="J165" s="1">
+        <v>0</v>
+      </c>
+      <c r="K165" s="2">
+        <v>0</v>
+      </c>
+      <c r="L165" s="2">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2">
+        <v>0</v>
+      </c>
+      <c r="N165" s="1">
+        <v>0</v>
+      </c>
+      <c r="O165" s="2">
+        <v>0</v>
+      </c>
+      <c r="P165" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="2">
+        <v>0</v>
+      </c>
+      <c r="R165" s="1">
+        <v>0</v>
+      </c>
+      <c r="S165" s="2">
+        <v>0</v>
+      </c>
+      <c r="T165" s="2">
+        <v>0</v>
+      </c>
+      <c r="U165" s="2">
+        <v>0</v>
+      </c>
+      <c r="V165" s="1">
+        <v>0</v>
+      </c>
+      <c r="W165" s="2">
+        <v>0</v>
+      </c>
+      <c r="X165" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP165" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT165" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX165" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY165" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB165" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF165" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ165" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN165" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR165" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV165" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY165" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ165" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD165" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH165" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL165" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP165" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS165" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT165" s="1">
+        <v>77</v>
+      </c>
+      <c r="CU165" s="1">
+        <v>2</v>
+      </c>
+      <c r="CV165" s="1">
         <v>5</v>
       </c>
-      <c r="J165" s="1">
-        <v>0</v>
-      </c>
-      <c r="K165" s="2">
-        <v>0</v>
-      </c>
-      <c r="L165" s="2">
-        <v>0</v>
-      </c>
-      <c r="M165" s="2">
-        <v>0</v>
-      </c>
-      <c r="N165" s="1">
-        <v>0</v>
-      </c>
-      <c r="O165" s="2">
-        <v>0</v>
-      </c>
-      <c r="P165" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q165" s="2">
-        <v>0</v>
-      </c>
-      <c r="R165" s="1">
-        <v>0</v>
-      </c>
-      <c r="S165" s="2">
-        <v>0</v>
-      </c>
-      <c r="T165" s="2">
-        <v>0</v>
-      </c>
-      <c r="U165" s="2">
-        <v>0</v>
-      </c>
-      <c r="V165" s="1">
-        <v>0</v>
-      </c>
-      <c r="W165" s="2">
-        <v>0</v>
-      </c>
-      <c r="X165" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y165" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z165" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD165" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH165" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL165" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP165" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT165" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX165" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY165" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB165" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF165" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ165" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN165" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR165" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV165" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY165" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ165" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD165" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH165" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL165" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP165" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS165" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT165" s="1">
-        <v>76</v>
-      </c>
-      <c r="CU165" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV165" s="1">
-        <v>4</v>
-      </c>
       <c r="CW165" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:101">
@@ -54287,10 +54287,10 @@
         <v>0</v>
       </c>
       <c r="BR168" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BS168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT168" s="2">
         <v>1</v>
@@ -54371,10 +54371,10 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="CU168" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CV168" s="1">
         <v>420</v>
@@ -54397,7 +54397,7 @@
         <v>1</v>
       </c>
       <c r="E169" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F169" s="1">
         <v>44</v>
@@ -54685,7 +54685,7 @@
         <v>45</v>
       </c>
       <c r="CW169" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -54735,7 +54735,7 @@
         <v>0</v>
       </c>
       <c r="P170" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q170" s="2">
         <v>154</v>
@@ -54987,7 +54987,7 @@
         <v>127</v>
       </c>
       <c r="CV170" s="1">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="CW170" s="1">
         <v>1363</v>
@@ -55190,16 +55190,16 @@
         <v>0</v>
       </c>
       <c r="BN171" s="1">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="BO171" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP171" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ171" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BR171" s="1">
         <v>17</v>
@@ -55286,16 +55286,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="CU171" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV171" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CW171" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -57310,7 +57310,7 @@
         <v>0</v>
       </c>
       <c r="BI178" s="2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BJ178" s="1">
         <v>0</v>
@@ -57331,7 +57331,7 @@
         <v>0</v>
       </c>
       <c r="BP178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ178" s="2">
         <v>1</v>
@@ -57346,7 +57346,7 @@
         <v>0</v>
       </c>
       <c r="BU178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV178" s="1">
         <v>7</v>
@@ -57427,10 +57427,10 @@
         <v>68</v>
       </c>
       <c r="CV178" s="1">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="CW178" s="1">
-        <v>4744</v>
+        <v>4715</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -58461,16 +58461,16 @@
         <v>0</v>
       </c>
       <c r="AL182" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO182" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP182" s="1">
         <v>0</v>
@@ -58593,64 +58593,64 @@
         <v>0</v>
       </c>
       <c r="CD182" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CE182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH182" s="1">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="CI182" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CJ182" s="2">
+        <v>28</v>
+      </c>
+      <c r="CK182" s="2">
+        <v>41</v>
+      </c>
+      <c r="CL182" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM182" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN182" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO182" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP182" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ182" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR182" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS182" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT182" s="1">
+        <v>316</v>
+      </c>
+      <c r="CU182" s="1">
         <v>15</v>
       </c>
-      <c r="CK182" s="2">
-        <v>28</v>
-      </c>
-      <c r="CL182" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM182" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN182" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO182" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP182" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ182" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR182" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS182" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT182" s="1">
-        <v>301</v>
-      </c>
-      <c r="CU182" s="1">
-        <v>0</v>
-      </c>
       <c r="CV182" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="CW182" s="1">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="183" spans="1:101">
@@ -60805,16 +60805,16 @@
         <v>0</v>
       </c>
       <c r="F190" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G190" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190" s="2">
         <v>3</v>
       </c>
       <c r="I190" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J190" s="1">
         <v>0</v>
@@ -61081,16 +61081,16 @@
         <v>0</v>
       </c>
       <c r="CT190" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CU190" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV190" s="1">
         <v>3</v>
       </c>
       <c r="CW190" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:101">
@@ -61523,16 +61523,16 @@
         <v>1</v>
       </c>
       <c r="AP192" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AQ192" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR192" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS192" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT192" s="1">
         <v>0</v>
@@ -61655,16 +61655,16 @@
         <v>0</v>
       </c>
       <c r="CH192" s="1">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="CI192" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CJ192" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CK192" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CL192" s="1">
         <v>37</v>
@@ -61691,16 +61691,16 @@
         <v>0</v>
       </c>
       <c r="CT192" s="1">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="CU192" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CV192" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CW192" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62181,16 +62181,16 @@
         <v>0</v>
       </c>
       <c r="BF194" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG194" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH194" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI194" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ194" s="1">
         <v>0</v>
@@ -62301,16 +62301,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32287</v>
+        <v>32289</v>
       </c>
       <c r="CU194" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CV194" s="1">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="CW194" s="1">
-        <v>1315</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62339,19 +62339,19 @@
         <v>1</v>
       </c>
       <c r="I195" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J195" s="1">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K195" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L195" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M195" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N195" s="1">
         <v>964</v>
@@ -62606,13 +62606,13 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>67830</v>
+        <v>67831</v>
       </c>
       <c r="CU195" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CV195" s="1">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="CW195" s="1">
         <v>2927</v>
@@ -62827,13 +62827,13 @@
         <v>0</v>
       </c>
       <c r="BR196" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BS196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU196" s="2">
         <v>2</v>
@@ -62911,13 +62911,13 @@
         <v>0</v>
       </c>
       <c r="CT196" s="1">
-        <v>5396</v>
+        <v>5397</v>
       </c>
       <c r="CU196" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CV196" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="CW196" s="1">
         <v>234</v>
@@ -64020,7 +64020,7 @@
         <v>0</v>
       </c>
       <c r="BI200" s="2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BJ200" s="1">
         <v>0</v>
@@ -64140,7 +64140,7 @@
         <v>260</v>
       </c>
       <c r="CW200" s="1">
-        <v>503</v>
+        <v>476</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64453,16 +64453,16 @@
         <v>301</v>
       </c>
       <c r="B202" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C202" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D202" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E202" s="2">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F202" s="1">
         <v>18</v>
@@ -64474,7 +64474,7 @@
         <v>-1</v>
       </c>
       <c r="I202" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J202" s="1">
         <v>0</v>
@@ -64741,16 +64741,16 @@
         <v>0</v>
       </c>
       <c r="CT202" s="1">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="CU202" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CV202" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CW202" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="203" spans="1:101">
@@ -65673,16 +65673,16 @@
         <v>305</v>
       </c>
       <c r="B206" s="1">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C206" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D206" s="2">
-        <v>-29</v>
+        <v>12</v>
       </c>
       <c r="E206" s="2">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="F206" s="1">
         <v>9</v>
@@ -65781,16 +65781,16 @@
         <v>0</v>
       </c>
       <c r="AL206" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AM206" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN206" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO206" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP206" s="1">
         <v>78</v>
@@ -65799,7 +65799,7 @@
         <v>0</v>
       </c>
       <c r="AR206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS206" s="2">
         <v>2</v>
@@ -65925,16 +65925,16 @@
         <v>0</v>
       </c>
       <c r="CH206" s="1">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="CI206" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ206" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK206" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CL206" s="1">
         <v>34</v>
@@ -65961,16 +65961,16 @@
         <v>0</v>
       </c>
       <c r="CT206" s="1">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="CU206" s="1">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="CV206" s="1">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="CW206" s="1">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -66020,7 +66020,7 @@
         <v>1</v>
       </c>
       <c r="P207" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q207" s="2">
         <v>93</v>
@@ -66155,7 +66155,7 @@
         <v>0</v>
       </c>
       <c r="BI207" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BJ207" s="1">
         <v>0</v>
@@ -66272,10 +66272,10 @@
         <v>36</v>
       </c>
       <c r="CV207" s="1">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="CW207" s="1">
-        <v>488</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -66902,7 +66902,7 @@
         <v>0</v>
       </c>
       <c r="E210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F210" s="1">
         <v>55</v>
@@ -66929,16 +66929,16 @@
         <v>0</v>
       </c>
       <c r="N210" s="1">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="O210" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P210" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q210" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R210" s="1">
         <v>8</v>
@@ -67019,7 +67019,7 @@
         <v>1</v>
       </c>
       <c r="AR210" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS210" s="2">
         <v>5</v>
@@ -67151,7 +67151,7 @@
         <v>1</v>
       </c>
       <c r="CJ210" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CK210" s="2">
         <v>9</v>
@@ -67181,16 +67181,16 @@
         <v>0</v>
       </c>
       <c r="CT210" s="1">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="CU210" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="CV210" s="1">
         <v>16</v>
       </c>
       <c r="CW210" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -67375,7 +67375,7 @@
         <v>0</v>
       </c>
       <c r="BI211" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BJ211" s="1">
         <v>1</v>
@@ -67495,7 +67495,7 @@
         <v>194</v>
       </c>
       <c r="CW211" s="1">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -67808,28 +67808,28 @@
         <v>312</v>
       </c>
       <c r="B213" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C213" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D213" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F213" s="1">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G213" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H213" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I213" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J213" s="1">
         <v>0</v>
@@ -68096,16 +68096,16 @@
         <v>0</v>
       </c>
       <c r="CT213" s="1">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="CU213" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CV213" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CW213" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="214" spans="1:101">
@@ -69643,7 +69643,7 @@
         <v>580</v>
       </c>
       <c r="D61">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E61" t="s">
         <v>717</v>
@@ -69903,7 +69903,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2033</v>
+        <v>2051</v>
       </c>
       <c r="E74" t="s">
         <v>717</v>
@@ -70529,7 +70529,7 @@
         <v>621</v>
       </c>
       <c r="D105">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E105" t="s">
         <v>717</v>
@@ -71555,7 +71555,7 @@
         <v>665</v>
       </c>
       <c r="D156">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E156" t="s">
         <v>717</v>
@@ -72001,7 +72001,7 @@
         <v>685</v>
       </c>
       <c r="D178">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E178" t="s">
         <v>717</v>
@@ -72361,7 +72361,7 @@
         <v>700</v>
       </c>
       <c r="D196">
-        <v>10204</v>
+        <v>10207</v>
       </c>
       <c r="E196" t="s">
         <v>717</v>
@@ -72444,7 +72444,7 @@
         <v>704</v>
       </c>
       <c r="D200">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E200" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -2033,7 +2033,7 @@
     <t>Brodie.larocque@polar-polaire.gc.ca</t>
   </si>
   <si>
-    <t>smackenzie@ppa.gc.ca</t>
+    <t>kchong@ppa.gc.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@ppsc-sppc.gc.ca</t>
@@ -4691,10 +4691,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -4967,10 +4967,10 @@
         <v>3</v>
       </c>
       <c r="CV6" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CW6" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -5600,16 +5600,16 @@
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="1">
         <v>221</v>
@@ -5876,16 +5876,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="CU9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV9" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CW9" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="2">
         <v>38</v>
@@ -7206,7 +7206,7 @@
         <v>85</v>
       </c>
       <c r="AG14" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -7407,10 +7407,10 @@
         <v>15</v>
       </c>
       <c r="CV14" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="CW14" s="1">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7496,10 +7496,10 @@
         <v>0</v>
       </c>
       <c r="AB15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="2">
         <v>3</v>
-      </c>
-      <c r="AC15" s="2">
-        <v>6</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
@@ -7712,10 +7712,10 @@
         <v>0</v>
       </c>
       <c r="CV15" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CW15" s="1">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:101">
@@ -7750,7 +7750,7 @@
         <v>114</v>
       </c>
       <c r="K16" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2">
         <v>5</v>
@@ -7807,16 +7807,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="1">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="AE16" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF16" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG16" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -8011,16 +8011,16 @@
         <v>0</v>
       </c>
       <c r="CT16" s="1">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="CU16" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CV16" s="1">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="CW16" s="1">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -8985,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q20" s="2">
         <v>598</v>
@@ -9237,7 +9237,7 @@
         <v>57</v>
       </c>
       <c r="CV20" s="1">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="CW20" s="1">
         <v>976</v>
@@ -9894,16 +9894,16 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q23" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
@@ -10146,16 +10146,16 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="CU23" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV23" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CW23" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -12445,7 +12445,7 @@
         <v>3</v>
       </c>
       <c r="AY31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ31" s="2">
         <v>1</v>
@@ -12589,7 +12589,7 @@
         <v>5748</v>
       </c>
       <c r="CU31" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CV31" s="1">
         <v>160</v>
@@ -12630,7 +12630,7 @@
         <v>789</v>
       </c>
       <c r="K32" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2">
         <v>47</v>
@@ -12894,7 +12894,7 @@
         <v>10921</v>
       </c>
       <c r="CU32" s="1">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="CV32" s="1">
         <v>332</v>
@@ -14559,7 +14559,7 @@
         <v>1</v>
       </c>
       <c r="AR38" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS38" s="2">
         <v>6</v>
@@ -14703,7 +14703,7 @@
         <v>1</v>
       </c>
       <c r="CN38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO38" s="2">
         <v>4</v>
@@ -14727,7 +14727,7 @@
         <v>11</v>
       </c>
       <c r="CV38" s="1">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="CW38" s="1">
         <v>136</v>
@@ -14747,7 +14747,7 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F39" s="1">
         <v>30</v>
@@ -15035,7 +15035,7 @@
         <v>48</v>
       </c>
       <c r="CW39" s="1">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -20880,7 +20880,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="2">
         <v>7</v>
@@ -20964,7 +20964,7 @@
         <v>1</v>
       </c>
       <c r="AR59" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS59" s="2">
         <v>5</v>
@@ -21048,7 +21048,7 @@
         <v>0</v>
       </c>
       <c r="BT59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU59" s="2">
         <v>2</v>
@@ -21069,7 +21069,7 @@
         <v>1</v>
       </c>
       <c r="CA59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB59" s="2">
         <v>1</v>
@@ -21108,7 +21108,7 @@
         <v>0</v>
       </c>
       <c r="CN59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO59" s="2">
         <v>4</v>
@@ -21129,10 +21129,10 @@
         <v>828</v>
       </c>
       <c r="CU59" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV59" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CW59" s="1">
         <v>33</v>
@@ -21454,7 +21454,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="2">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E61" s="2">
         <v>118</v>
@@ -21742,7 +21742,7 @@
         <v>18</v>
       </c>
       <c r="CV61" s="1">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="CW61" s="1">
         <v>2553</v>
@@ -22067,7 +22067,7 @@
         <v>11</v>
       </c>
       <c r="E63" s="2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -22178,13 +22178,13 @@
         <v>0</v>
       </c>
       <c r="AP63" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AQ63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR63" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS63" s="2">
         <v>6</v>
@@ -22310,16 +22310,16 @@
         <v>0</v>
       </c>
       <c r="CH63" s="1">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="CI63" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="CJ63" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="CK63" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="CL63" s="1">
         <v>22</v>
@@ -22346,16 +22346,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2787</v>
+        <v>2802</v>
       </c>
       <c r="CU63" s="1">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="CV63" s="1">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="CW63" s="1">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22447,16 +22447,16 @@
         <v>5</v>
       </c>
       <c r="AD64" s="1">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="AE64" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF64" s="2">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="AG64" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22651,16 +22651,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>7852</v>
+        <v>7853</v>
       </c>
       <c r="CU64" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CV64" s="1">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="CW64" s="1">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22677,7 +22677,7 @@
         <v>54</v>
       </c>
       <c r="E65" s="2">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22965,7 +22965,7 @@
         <v>1764</v>
       </c>
       <c r="CW65" s="1">
-        <v>3358</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -25590,7 +25590,7 @@
         <v>3</v>
       </c>
       <c r="BI74" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BJ74" s="1">
         <v>1</v>
@@ -25671,7 +25671,7 @@
         <v>54</v>
       </c>
       <c r="CJ74" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="CK74" s="2">
         <v>378</v>
@@ -25707,10 +25707,10 @@
         <v>210</v>
       </c>
       <c r="CV74" s="1">
-        <v>2607</v>
+        <v>2603</v>
       </c>
       <c r="CW74" s="1">
-        <v>5363</v>
+        <v>5357</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26059,16 +26059,16 @@
         <v>351</v>
       </c>
       <c r="N76" s="1">
-        <v>116632</v>
+        <v>116637</v>
       </c>
       <c r="O76" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P76" s="2">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="Q76" s="2">
-        <v>2741</v>
+        <v>2746</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26191,16 +26191,16 @@
         <v>0</v>
       </c>
       <c r="BF76" s="1">
-        <v>744</v>
+        <v>780</v>
       </c>
       <c r="BG76" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH76" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BI76" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BJ76" s="1">
         <v>0</v>
@@ -26311,16 +26311,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>149791</v>
+        <v>149832</v>
       </c>
       <c r="CU76" s="1">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="CV76" s="1">
-        <v>2406</v>
+        <v>2447</v>
       </c>
       <c r="CW76" s="1">
-        <v>4174</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26445,7 +26445,7 @@
         <v>29</v>
       </c>
       <c r="AO77" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26580,16 +26580,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7031</v>
+        <v>7033</v>
       </c>
       <c r="CI77" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CJ77" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CK77" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26616,16 +26616,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>380795</v>
+        <v>380797</v>
       </c>
       <c r="CU77" s="1">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="CV77" s="1">
-        <v>5736</v>
+        <v>5738</v>
       </c>
       <c r="CW77" s="1">
-        <v>14615</v>
+        <v>14605</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -28894,7 +28894,7 @@
         <v>1</v>
       </c>
       <c r="AR85" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS85" s="2">
         <v>9</v>
@@ -29026,7 +29026,7 @@
         <v>9</v>
       </c>
       <c r="CJ85" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CK85" s="2">
         <v>39</v>
@@ -29062,7 +29062,7 @@
         <v>12</v>
       </c>
       <c r="CV85" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="CW85" s="1">
         <v>55</v>
@@ -29190,7 +29190,7 @@
         <v>2</v>
       </c>
       <c r="AO86" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP86" s="1">
         <v>52</v>
@@ -29334,7 +29334,7 @@
         <v>15</v>
       </c>
       <c r="CK86" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CL86" s="1">
         <v>35</v>
@@ -29370,7 +29370,7 @@
         <v>48</v>
       </c>
       <c r="CW86" s="1">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29991,7 +29991,7 @@
         <v>10</v>
       </c>
       <c r="C89" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89" s="2">
         <v>3</v>
@@ -30108,16 +30108,16 @@
         <v>1</v>
       </c>
       <c r="AP89" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AQ89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR89" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS89" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT89" s="1">
         <v>0</v>
@@ -30240,16 +30240,16 @@
         <v>0</v>
       </c>
       <c r="CH89" s="1">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="CI89" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CJ89" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CK89" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CL89" s="1">
         <v>9</v>
@@ -30276,16 +30276,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2138</v>
+        <v>2142</v>
       </c>
       <c r="CU89" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="CV89" s="1">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="CW89" s="1">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30679,7 +30679,7 @@
         <v>3</v>
       </c>
       <c r="AC91" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD91" s="1">
         <v>209</v>
@@ -30895,7 +30895,7 @@
         <v>474</v>
       </c>
       <c r="CW91" s="1">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -32141,10 +32141,10 @@
         <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I96" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J96" s="1">
         <v>2</v>
@@ -32417,10 +32417,10 @@
         <v>16</v>
       </c>
       <c r="CV96" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="CW96" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="1:101">
@@ -33962,7 +33962,7 @@
         <v>386</v>
       </c>
       <c r="E102" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -34157,16 +34157,16 @@
         <v>5</v>
       </c>
       <c r="BR102" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV102" s="1">
         <v>7</v>
@@ -34241,16 +34241,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>42393</v>
+        <v>42394</v>
       </c>
       <c r="CU102" s="1">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CV102" s="1">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="CW102" s="1">
-        <v>1877</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -35266,7 +35266,7 @@
         <v>186</v>
       </c>
       <c r="AG106" s="2">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="AH106" s="1">
         <v>1</v>
@@ -35350,7 +35350,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ106" s="1">
         <v>0</v>
@@ -35371,7 +35371,7 @@
         <v>0</v>
       </c>
       <c r="BP106" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BQ106" s="2">
         <v>11</v>
@@ -35467,10 +35467,10 @@
         <v>318</v>
       </c>
       <c r="CV106" s="1">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="CW106" s="1">
-        <v>2648</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -37449,7 +37449,7 @@
         <v>0</v>
       </c>
       <c r="AW113" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX113" s="1">
         <v>0</v>
@@ -37473,7 +37473,7 @@
         <v>0</v>
       </c>
       <c r="BE113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF113" s="1">
         <v>316</v>
@@ -38223,16 +38223,16 @@
         <v>215</v>
       </c>
       <c r="B116" s="1">
-        <v>4381</v>
+        <v>4400</v>
       </c>
       <c r="C116" s="2">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D116" s="2">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E116" s="2">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -38511,16 +38511,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21428</v>
+        <v>21447</v>
       </c>
       <c r="CU116" s="1">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="CV116" s="1">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="CW116" s="1">
-        <v>1199</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38555,7 +38555,7 @@
         <v>331</v>
       </c>
       <c r="K117" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2">
         <v>18</v>
@@ -38657,7 +38657,7 @@
         <v>2</v>
       </c>
       <c r="AS117" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT117" s="1">
         <v>0</v>
@@ -38789,7 +38789,7 @@
         <v>5</v>
       </c>
       <c r="CK117" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CL117" s="1">
         <v>28</v>
@@ -38819,13 +38819,13 @@
         <v>12761</v>
       </c>
       <c r="CU117" s="1">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="CV117" s="1">
         <v>690</v>
       </c>
       <c r="CW117" s="1">
-        <v>1135</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -39159,7 +39159,7 @@
         <v>2</v>
       </c>
       <c r="I119" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J119" s="1">
         <v>0</v>
@@ -39183,7 +39183,7 @@
         <v>5</v>
       </c>
       <c r="Q119" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R119" s="1">
         <v>2</v>
@@ -39435,7 +39435,7 @@
         <v>17</v>
       </c>
       <c r="CW119" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -40478,16 +40478,16 @@
         <v>0</v>
       </c>
       <c r="AP123" s="1">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AQ123" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR123" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS123" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT123" s="1">
         <v>0</v>
@@ -40622,40 +40622,40 @@
         <v>1</v>
       </c>
       <c r="CL123" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="CM123" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN123" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO123" s="2">
+        <v>6</v>
+      </c>
+      <c r="CP123" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ123" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR123" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS123" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT123" s="1">
+        <v>926</v>
+      </c>
+      <c r="CU123" s="1">
         <v>5</v>
       </c>
-      <c r="CP123" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ123" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR123" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS123" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT123" s="1">
-        <v>924</v>
-      </c>
-      <c r="CU123" s="1">
-        <v>3</v>
-      </c>
       <c r="CV123" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CW123" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -42514,7 +42514,7 @@
         <v>2</v>
       </c>
       <c r="I130" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J130" s="1">
         <v>0</v>
@@ -42790,7 +42790,7 @@
         <v>29</v>
       </c>
       <c r="CW130" s="1">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -44042,16 +44042,16 @@
         <v>0</v>
       </c>
       <c r="J135" s="1">
-        <v>6425</v>
+        <v>6424</v>
       </c>
       <c r="K135" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L135" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M135" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N135" s="1">
         <v>31681</v>
@@ -44105,7 +44105,7 @@
         <v>11631</v>
       </c>
       <c r="AE135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF135" s="2">
         <v>593</v>
@@ -44306,16 +44306,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>61782</v>
+        <v>61781</v>
       </c>
       <c r="CU135" s="1">
         <v>154</v>
       </c>
       <c r="CV135" s="1">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="CW135" s="1">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44631,7 +44631,7 @@
         <v>138</v>
       </c>
       <c r="C137" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D137" s="2">
         <v>7</v>
@@ -44655,7 +44655,7 @@
         <v>39</v>
       </c>
       <c r="K137" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L137" s="2">
         <v>4</v>
@@ -44691,7 +44691,7 @@
         <v>7</v>
       </c>
       <c r="W137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X137" s="2">
         <v>1</v>
@@ -44757,7 +44757,7 @@
         <v>3</v>
       </c>
       <c r="AS137" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT137" s="1">
         <v>0</v>
@@ -44889,7 +44889,7 @@
         <v>1</v>
       </c>
       <c r="CK137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CL137" s="1">
         <v>41</v>
@@ -44919,13 +44919,13 @@
         <v>629</v>
       </c>
       <c r="CU137" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="CV137" s="1">
         <v>19</v>
       </c>
       <c r="CW137" s="1">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -45385,7 +45385,7 @@
         <v>4</v>
       </c>
       <c r="AY139" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ139" s="2">
         <v>1</v>
@@ -45529,7 +45529,7 @@
         <v>5</v>
       </c>
       <c r="CU139" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV139" s="1">
         <v>1</v>
@@ -46159,7 +46159,7 @@
         <v>2</v>
       </c>
       <c r="D142" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E142" s="2">
         <v>5</v>
@@ -46447,7 +46447,7 @@
         <v>32</v>
       </c>
       <c r="CV142" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="CW142" s="1">
         <v>92</v>
@@ -46515,7 +46515,7 @@
         <v>0</v>
       </c>
       <c r="U143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V143" s="1">
         <v>0</v>
@@ -46587,7 +46587,7 @@
         <v>3</v>
       </c>
       <c r="AS143" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT143" s="1">
         <v>0</v>
@@ -46755,7 +46755,7 @@
         <v>10</v>
       </c>
       <c r="CW143" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -47215,7 +47215,7 @@
         <v>37</v>
       </c>
       <c r="AY145" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ145" s="2">
         <v>4</v>
@@ -47359,7 +47359,7 @@
         <v>2435</v>
       </c>
       <c r="CU145" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV145" s="1">
         <v>85</v>
@@ -47735,7 +47735,7 @@
         <v>0</v>
       </c>
       <c r="U147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V147" s="1">
         <v>0</v>
@@ -47891,7 +47891,7 @@
         <v>1</v>
       </c>
       <c r="BU147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV147" s="1">
         <v>0</v>
@@ -47975,7 +47975,7 @@
         <v>16</v>
       </c>
       <c r="CW147" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -50953,7 +50953,7 @@
         <v>0</v>
       </c>
       <c r="BY157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ157" s="1">
         <v>4</v>
@@ -51025,7 +51025,7 @@
         <v>3948</v>
       </c>
       <c r="CW157" s="1">
-        <v>5632</v>
+        <v>5631</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51957,7 +51957,7 @@
         <v>49</v>
       </c>
       <c r="E161" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F161" s="1">
         <v>2</v>
@@ -52140,16 +52140,16 @@
         <v>0</v>
       </c>
       <c r="BN161" s="1">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BO161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR161" s="1">
         <v>7</v>
@@ -52236,16 +52236,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>21686</v>
+        <v>21687</v>
       </c>
       <c r="CU161" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CV161" s="1">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="CW161" s="1">
-        <v>1077</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52878,7 +52878,7 @@
         <v>56</v>
       </c>
       <c r="G164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="2">
         <v>2</v>
@@ -53154,7 +53154,7 @@
         <v>1027</v>
       </c>
       <c r="CU164" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CV164" s="1">
         <v>99</v>
@@ -53177,7 +53177,7 @@
         <v>0</v>
       </c>
       <c r="E165" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F165" s="1">
         <v>56</v>
@@ -53465,7 +53465,7 @@
         <v>5</v>
       </c>
       <c r="CW165" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:101">
@@ -53506,7 +53506,7 @@
         <v>72</v>
       </c>
       <c r="M166" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="N166" s="1">
         <v>2171</v>
@@ -53770,7 +53770,7 @@
         <v>390</v>
       </c>
       <c r="CW166" s="1">
-        <v>514</v>
+        <v>492</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54212,7 +54212,7 @@
         <v>2</v>
       </c>
       <c r="AS168" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT168" s="1">
         <v>0</v>
@@ -54251,16 +54251,16 @@
         <v>0</v>
       </c>
       <c r="BF168" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BG168" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH168" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BI168" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ168" s="1">
         <v>0</v>
@@ -54344,7 +54344,7 @@
         <v>30</v>
       </c>
       <c r="CK168" s="2">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="CL168" s="1">
         <v>4</v>
@@ -54371,16 +54371,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5816</v>
+        <v>5821</v>
       </c>
       <c r="CU168" s="1">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="CV168" s="1">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="CW168" s="1">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -57337,16 +57337,16 @@
         <v>1</v>
       </c>
       <c r="BR178" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BS178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV178" s="1">
         <v>7</v>
@@ -57421,16 +57421,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>82723</v>
+        <v>82724</v>
       </c>
       <c r="CU178" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CV178" s="1">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="CW178" s="1">
-        <v>4752</v>
+        <v>4753</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -58611,7 +58611,7 @@
         <v>13</v>
       </c>
       <c r="CJ182" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CK182" s="2">
         <v>31</v>
@@ -58647,7 +58647,7 @@
         <v>15</v>
       </c>
       <c r="CV182" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="CW182" s="1">
         <v>34</v>
@@ -59394,7 +59394,7 @@
         <v>1</v>
       </c>
       <c r="AR185" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS185" s="2">
         <v>9</v>
@@ -59538,7 +59538,7 @@
         <v>1</v>
       </c>
       <c r="CN185" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO185" s="2">
         <v>7</v>
@@ -59562,7 +59562,7 @@
         <v>3</v>
       </c>
       <c r="CV185" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CW185" s="1">
         <v>23</v>
@@ -62052,7 +62052,7 @@
         <v>28678</v>
       </c>
       <c r="O194" s="2">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="P194" s="2">
         <v>729</v>
@@ -62166,7 +62166,7 @@
         <v>1</v>
       </c>
       <c r="BA194" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB194" s="1">
         <v>3</v>
@@ -62304,13 +62304,13 @@
         <v>32289</v>
       </c>
       <c r="CU194" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV194" s="1">
         <v>796</v>
       </c>
       <c r="CW194" s="1">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -65679,7 +65679,7 @@
         <v>1</v>
       </c>
       <c r="D206" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E206" s="2">
         <v>-22</v>
@@ -65967,7 +65967,7 @@
         <v>27</v>
       </c>
       <c r="CV206" s="1">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="CW206" s="1">
         <v>40</v>
@@ -66236,7 +66236,7 @@
         <v>10</v>
       </c>
       <c r="CJ207" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CK207" s="2">
         <v>71</v>
@@ -66272,7 +66272,7 @@
         <v>36</v>
       </c>
       <c r="CV207" s="1">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="CW207" s="1">
         <v>472</v>
@@ -69540,7 +69540,7 @@
         <v>575</v>
       </c>
       <c r="D56">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E56" t="s">
         <v>717</v>
@@ -69903,7 +69903,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2065</v>
+        <v>2079</v>
       </c>
       <c r="E74" t="s">
         <v>717</v>
@@ -70003,7 +70003,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="E79" t="s">
         <v>717</v>
@@ -70469,7 +70469,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="E102" t="s">
         <v>717</v>
@@ -71841,7 +71841,7 @@
         <v>677</v>
       </c>
       <c r="D170">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E170" t="s">
         <v>717</v>
@@ -72444,7 +72444,7 @@
         <v>704</v>
       </c>
       <c r="D200">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E200" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3758,16 +3758,16 @@
         <v>102</v>
       </c>
       <c r="B3" s="1">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="C3" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -3782,28 +3782,28 @@
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>4179</v>
+        <v>4220</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L3" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M3" s="2">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="N3" s="1">
-        <v>19309</v>
+        <v>19611</v>
       </c>
       <c r="O3" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="P3" s="2">
-        <v>554</v>
+        <v>856</v>
       </c>
       <c r="Q3" s="2">
-        <v>554</v>
+        <v>856</v>
       </c>
       <c r="R3" s="1">
         <v>0</v>
@@ -3842,16 +3842,16 @@
         <v>4</v>
       </c>
       <c r="AD3" s="1">
-        <v>18285</v>
+        <v>18287</v>
       </c>
       <c r="AE3" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AF3" s="2">
-        <v>724</v>
+        <v>294</v>
       </c>
       <c r="AG3" s="2">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -3878,16 +3878,16 @@
         <v>0</v>
       </c>
       <c r="AP3" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS3" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" s="1">
         <v>0</v>
@@ -3959,7 +3959,7 @@
         <v>23</v>
       </c>
       <c r="BQ3" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BR3" s="1">
         <v>3</v>
@@ -4010,16 +4010,16 @@
         <v>0</v>
       </c>
       <c r="CH3" s="1">
-        <v>2010</v>
+        <v>2035</v>
       </c>
       <c r="CI3" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CJ3" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="CK3" s="2">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="CL3" s="1">
         <v>3</v>
@@ -4046,16 +4046,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46250</v>
+        <v>46627</v>
       </c>
       <c r="CU3" s="1">
-        <v>380</v>
+        <v>757</v>
       </c>
       <c r="CV3" s="1">
-        <v>1545</v>
+        <v>1446</v>
       </c>
       <c r="CW3" s="1">
-        <v>2178</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4093,10 +4093,10 @@
         <v>69</v>
       </c>
       <c r="L4" s="2">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="M4" s="2">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="N4" s="1">
         <v>9178</v>
@@ -4108,7 +4108,7 @@
         <v>98</v>
       </c>
       <c r="Q4" s="2">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="R4" s="1">
         <v>1</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="AF4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="2">
         <v>339</v>
-      </c>
-      <c r="AG4" s="2">
-        <v>493</v>
       </c>
       <c r="AH4" s="1">
         <v>0</v>
@@ -4357,10 +4357,10 @@
         <v>136</v>
       </c>
       <c r="CV4" s="1">
-        <v>797</v>
+        <v>393</v>
       </c>
       <c r="CW4" s="1">
-        <v>1363</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4371,37 +4371,37 @@
         <v>233</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
         <v>10</v>
       </c>
       <c r="F5" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="1">
-        <v>1144</v>
+        <v>1163</v>
       </c>
       <c r="K5" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L5" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M5" s="2">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="N5" s="1">
         <v>2965</v>
@@ -4458,7 +4458,7 @@
         <v>-54</v>
       </c>
       <c r="AF5" s="2">
-        <v>317</v>
+        <v>-54</v>
       </c>
       <c r="AG5" s="2">
         <v>317</v>
@@ -4620,16 +4620,16 @@
         <v>1</v>
       </c>
       <c r="CH5" s="1">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="CI5" s="2">
         <v>1</v>
       </c>
       <c r="CJ5" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="CK5" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="CL5" s="1">
         <v>0</v>
@@ -4656,16 +4656,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38343</v>
+        <v>38364</v>
       </c>
       <c r="CU5" s="1">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="CV5" s="1">
-        <v>454</v>
+        <v>68</v>
       </c>
       <c r="CW5" s="1">
-        <v>527</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5630,10 +5630,10 @@
         <v>34</v>
       </c>
       <c r="P9" s="2">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="2">
         <v>58</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>73</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="AP9" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AQ9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" s="2">
         <v>3</v>
       </c>
       <c r="AS9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -5840,10 +5840,10 @@
         <v>0</v>
       </c>
       <c r="CH9" s="1">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="CI9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ9" s="2">
         <v>4</v>
@@ -5876,16 +5876,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2851</v>
+        <v>2854</v>
       </c>
       <c r="CU9" s="1">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="CV9" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="CW9" s="1">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7197,16 +7197,16 @@
         <v>0</v>
       </c>
       <c r="AD14" s="1">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="AE14" s="2">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AF14" s="2">
-        <v>85</v>
+        <v>-9</v>
       </c>
       <c r="AG14" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -7401,16 +7401,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3079</v>
+        <v>3070</v>
       </c>
       <c r="CU14" s="1">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="CV14" s="1">
-        <v>146</v>
+        <v>52</v>
       </c>
       <c r="CW14" s="1">
-        <v>308</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7454,16 +7454,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>2631</v>
+        <v>2734</v>
       </c>
       <c r="O15" s="2">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="P15" s="2">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="2">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="R15" s="1">
         <v>0</v>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="CK15" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CL15" s="1">
         <v>2</v>
@@ -7706,16 +7706,16 @@
         <v>0</v>
       </c>
       <c r="CT15" s="1">
-        <v>3236</v>
+        <v>3339</v>
       </c>
       <c r="CU15" s="1">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="CV15" s="1">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="CW15" s="1">
-        <v>12</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:101">
@@ -8142,10 +8142,10 @@
         <v>5</v>
       </c>
       <c r="AN17" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AO17" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP17" s="1">
         <v>29</v>
@@ -8286,10 +8286,10 @@
         <v>15</v>
       </c>
       <c r="CJ17" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CK17" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CL17" s="1">
         <v>29</v>
@@ -8322,10 +8322,10 @@
         <v>20</v>
       </c>
       <c r="CV17" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="CW17" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:101">
@@ -8949,10 +8949,10 @@
         <v>38</v>
       </c>
       <c r="D20" s="2">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -8973,10 +8973,10 @@
         <v>14</v>
       </c>
       <c r="L20" s="2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="M20" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N20" s="1">
         <v>12650</v>
@@ -8988,7 +8988,7 @@
         <v>586</v>
       </c>
       <c r="Q20" s="2">
-        <v>821</v>
+        <v>605</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9057,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="AN20" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="2">
         <v>2</v>
@@ -9195,16 +9195,16 @@
         <v>0</v>
       </c>
       <c r="CH20" s="1">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="CI20" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CJ20" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CK20" s="2">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="CL20" s="1">
         <v>23</v>
@@ -9231,16 +9231,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20581</v>
+        <v>20595</v>
       </c>
       <c r="CU20" s="1">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="CV20" s="1">
-        <v>776</v>
+        <v>714</v>
       </c>
       <c r="CW20" s="1">
-        <v>1194</v>
+        <v>959</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9359,7 +9359,7 @@
         <v>25</v>
       </c>
       <c r="AM21" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN21" s="2">
         <v>2</v>
@@ -9374,10 +9374,10 @@
         <v>1</v>
       </c>
       <c r="AR21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS21" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT21" s="1">
         <v>0</v>
@@ -9503,13 +9503,13 @@
         <v>218</v>
       </c>
       <c r="CI21" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CJ21" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="CK21" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="CL21" s="1">
         <v>1</v>
@@ -9539,13 +9539,13 @@
         <v>354</v>
       </c>
       <c r="CU21" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="CV21" s="1">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="CW21" s="1">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:101">
@@ -9903,7 +9903,7 @@
         <v>23</v>
       </c>
       <c r="Q23" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
@@ -10155,7 +10155,7 @@
         <v>36</v>
       </c>
       <c r="CW23" s="1">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -10729,7 +10729,7 @@
         <v>10</v>
       </c>
       <c r="CK25" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="CL25" s="1">
         <v>0</v>
@@ -10765,7 +10765,7 @@
         <v>10</v>
       </c>
       <c r="CW25" s="1">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:101">
@@ -11201,7 +11201,7 @@
         <v>12</v>
       </c>
       <c r="AQ27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR27" s="2">
         <v>1</v>
@@ -11333,7 +11333,7 @@
         <v>319</v>
       </c>
       <c r="CI27" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ27" s="2">
         <v>9</v>
@@ -11369,7 +11369,7 @@
         <v>523</v>
       </c>
       <c r="CU27" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CV27" s="1">
         <v>18</v>
@@ -11389,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
@@ -11407,16 +11407,16 @@
         <v>1</v>
       </c>
       <c r="J28" s="1">
-        <v>931</v>
+        <v>944</v>
       </c>
       <c r="K28" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L28" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M28" s="2">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="N28" s="1">
         <v>2024</v>
@@ -11467,16 +11467,16 @@
         <v>0</v>
       </c>
       <c r="AD28" s="1">
-        <v>16461</v>
+        <v>16633</v>
       </c>
       <c r="AE28" s="2">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="AF28" s="2">
-        <v>435</v>
+        <v>172</v>
       </c>
       <c r="AG28" s="2">
-        <v>435</v>
+        <v>607</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -11497,19 +11497,19 @@
         <v>0</v>
       </c>
       <c r="AN28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="2">
         <v>2</v>
       </c>
       <c r="AP28" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AQ28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS28" s="2">
         <v>4</v>
@@ -11635,16 +11635,16 @@
         <v>0</v>
       </c>
       <c r="CH28" s="1">
-        <v>2999</v>
+        <v>3009</v>
       </c>
       <c r="CI28" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CJ28" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CK28" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="CL28" s="1">
         <v>20</v>
@@ -11671,16 +11671,16 @@
         <v>0</v>
       </c>
       <c r="CT28" s="1">
-        <v>23858</v>
+        <v>24054</v>
       </c>
       <c r="CU28" s="1">
-        <v>23</v>
+        <v>219</v>
       </c>
       <c r="CV28" s="1">
-        <v>523</v>
+        <v>259</v>
       </c>
       <c r="CW28" s="1">
-        <v>587</v>
+        <v>779</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12334,16 +12334,16 @@
         <v>68</v>
       </c>
       <c r="N31" s="1">
-        <v>1955</v>
+        <v>1982</v>
       </c>
       <c r="O31" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P31" s="2">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="Q31" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R31" s="1">
         <v>1</v>
@@ -12412,10 +12412,10 @@
         <v>3</v>
       </c>
       <c r="AN31" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AO31" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AP31" s="1">
         <v>18</v>
@@ -12556,10 +12556,10 @@
         <v>13</v>
       </c>
       <c r="CJ31" s="2">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="CK31" s="2">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="CL31" s="1">
         <v>19</v>
@@ -12586,16 +12586,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>5772</v>
+        <v>5799</v>
       </c>
       <c r="CU31" s="1">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="CV31" s="1">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="CW31" s="1">
-        <v>306</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12609,10 +12609,10 @@
         <v>15</v>
       </c>
       <c r="D32" s="2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E32" s="2">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -12639,16 +12639,16 @@
         <v>85</v>
       </c>
       <c r="N32" s="1">
-        <v>6479</v>
+        <v>6579</v>
       </c>
       <c r="O32" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32" s="2">
-        <v>219</v>
+        <v>319</v>
       </c>
       <c r="Q32" s="2">
-        <v>219</v>
+        <v>319</v>
       </c>
       <c r="R32" s="1">
         <v>0</v>
@@ -12720,7 +12720,7 @@
         <v>1</v>
       </c>
       <c r="AO32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP32" s="1">
         <v>45</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="AR32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS32" s="2">
         <v>3</v>
@@ -12861,10 +12861,10 @@
         <v>3</v>
       </c>
       <c r="CJ32" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CK32" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CL32" s="1">
         <v>25</v>
@@ -12891,16 +12891,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>10935</v>
+        <v>11035</v>
       </c>
       <c r="CU32" s="1">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="CV32" s="1">
-        <v>323</v>
+        <v>396</v>
       </c>
       <c r="CW32" s="1">
-        <v>442</v>
+        <v>519</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -12908,28 +12908,28 @@
         <v>132</v>
       </c>
       <c r="B33" s="1">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D33" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F33" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G33" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" s="1">
         <v>0</v>
@@ -13196,16 +13196,16 @@
         <v>0</v>
       </c>
       <c r="CT33" s="1">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="CU33" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CV33" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CW33" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:101">
@@ -13243,7 +13243,7 @@
         <v>12</v>
       </c>
       <c r="L34" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M34" s="2">
         <v>48</v>
@@ -13321,16 +13321,16 @@
         <v>0</v>
       </c>
       <c r="AL34" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO34" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP34" s="1">
         <v>48</v>
@@ -13465,16 +13465,16 @@
         <v>0</v>
       </c>
       <c r="CH34" s="1">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="CI34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK34" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL34" s="1">
         <v>26</v>
@@ -13501,16 +13501,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="CU34" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="CV34" s="1">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="CW34" s="1">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -14595,7 +14595,7 @@
         <v>0</v>
       </c>
       <c r="BD38" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="BE38" s="2">
         <v>22</v>
@@ -14643,7 +14643,7 @@
         <v>0</v>
       </c>
       <c r="BT38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU38" s="2">
         <v>1</v>
@@ -14727,7 +14727,7 @@
         <v>7</v>
       </c>
       <c r="CV38" s="1">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="CW38" s="1">
         <v>109</v>
@@ -15043,16 +15043,16 @@
         <v>139</v>
       </c>
       <c r="B40" s="1">
-        <v>8749</v>
+        <v>8813</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D40" s="2">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="E40" s="2">
-        <v>346</v>
+        <v>410</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -15076,19 +15076,19 @@
         <v>123</v>
       </c>
       <c r="M40" s="2">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="N40" s="1">
-        <v>16484</v>
+        <v>16656</v>
       </c>
       <c r="O40" s="2">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="P40" s="2">
-        <v>599</v>
+        <v>771</v>
       </c>
       <c r="Q40" s="2">
-        <v>599</v>
+        <v>771</v>
       </c>
       <c r="R40" s="1">
         <v>0</v>
@@ -15136,7 +15136,7 @@
         <v>460</v>
       </c>
       <c r="AG40" s="2">
-        <v>957</v>
+        <v>760</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -15235,16 +15235,16 @@
         <v>0</v>
       </c>
       <c r="BN40" s="1">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="BO40" s="2">
+        <v>2</v>
+      </c>
+      <c r="BP40" s="2">
+        <v>2</v>
+      </c>
+      <c r="BQ40" s="2">
         <v>3</v>
-      </c>
-      <c r="BP40" s="2">
-        <v>3</v>
-      </c>
-      <c r="BQ40" s="2">
-        <v>4</v>
       </c>
       <c r="BR40" s="1">
         <v>7</v>
@@ -15331,16 +15331,16 @@
         <v>1</v>
       </c>
       <c r="CT40" s="1">
-        <v>53126</v>
+        <v>53361</v>
       </c>
       <c r="CU40" s="1">
-        <v>460</v>
+        <v>695</v>
       </c>
       <c r="CV40" s="1">
-        <v>1333</v>
+        <v>1568</v>
       </c>
       <c r="CW40" s="1">
-        <v>2258</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -18351,7 +18351,7 @@
         <v>3</v>
       </c>
       <c r="CJ50" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="CK50" s="2">
         <v>35</v>
@@ -18387,7 +18387,7 @@
         <v>11</v>
       </c>
       <c r="CV50" s="1">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="CW50" s="1">
         <v>52</v>
@@ -18817,7 +18817,7 @@
         <v>0</v>
       </c>
       <c r="AN52" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AO52" s="2">
         <v>20</v>
@@ -18961,7 +18961,7 @@
         <v>0</v>
       </c>
       <c r="CJ52" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CK52" s="2">
         <v>22</v>
@@ -18997,7 +18997,7 @@
         <v>0</v>
       </c>
       <c r="CV52" s="1">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="CW52" s="1">
         <v>49</v>
@@ -19439,7 +19439,7 @@
         <v>0</v>
       </c>
       <c r="AR54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS54" s="2">
         <v>2</v>
@@ -19571,7 +19571,7 @@
         <v>14</v>
       </c>
       <c r="CJ54" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CK54" s="2">
         <v>21</v>
@@ -19607,7 +19607,7 @@
         <v>17</v>
       </c>
       <c r="CV54" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CW54" s="1">
         <v>29</v>
@@ -19959,16 +19959,16 @@
         <v>21</v>
       </c>
       <c r="N56" s="1">
-        <v>2275</v>
+        <v>2310</v>
       </c>
       <c r="O56" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="P56" s="2">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="Q56" s="2">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -20007,16 +20007,16 @@
         <v>0</v>
       </c>
       <c r="AD56" s="1">
-        <v>1090</v>
+        <v>1111</v>
       </c>
       <c r="AE56" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF56" s="2">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="AG56" s="2">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
@@ -20037,7 +20037,7 @@
         <v>1</v>
       </c>
       <c r="AN56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO56" s="2">
         <v>2</v>
@@ -20181,10 +20181,10 @@
         <v>18</v>
       </c>
       <c r="CJ56" s="2">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="CK56" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CL56" s="1">
         <v>2</v>
@@ -20211,16 +20211,16 @@
         <v>0</v>
       </c>
       <c r="CT56" s="1">
-        <v>7705</v>
+        <v>7761</v>
       </c>
       <c r="CU56" s="1">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="CV56" s="1">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="CW56" s="1">
-        <v>317</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -20874,16 +20874,16 @@
         <v>4</v>
       </c>
       <c r="N59" s="1">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="O59" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P59" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q59" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R59" s="1">
         <v>0</v>
@@ -20946,16 +20946,16 @@
         <v>0</v>
       </c>
       <c r="AL59" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP59" s="1">
         <v>72</v>
@@ -21027,7 +21027,7 @@
         <v>1</v>
       </c>
       <c r="BM59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN59" s="1">
         <v>28</v>
@@ -21090,16 +21090,16 @@
         <v>0</v>
       </c>
       <c r="CH59" s="1">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="CI59" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CJ59" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="CK59" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="CL59" s="1">
         <v>67</v>
@@ -21126,16 +21126,16 @@
         <v>0</v>
       </c>
       <c r="CT59" s="1">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="CU59" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="CV59" s="1">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="CW59" s="1">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -21472,16 +21472,16 @@
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="K61" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L61" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M61" s="2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="N61" s="1">
         <v>43316</v>
@@ -21538,7 +21538,7 @@
         <v>0</v>
       </c>
       <c r="AF61" s="2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AG61" s="2">
         <v>114</v>
@@ -21556,16 +21556,16 @@
         <v>0</v>
       </c>
       <c r="AL61" s="1">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AM61" s="2">
         <v>1</v>
       </c>
       <c r="AN61" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO61" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP61" s="1">
         <v>36</v>
@@ -21574,7 +21574,7 @@
         <v>0</v>
       </c>
       <c r="AR61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS61" s="2">
         <v>2</v>
@@ -21646,7 +21646,7 @@
         <v>0</v>
       </c>
       <c r="BP61" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ61" s="2">
         <v>2</v>
@@ -21700,16 +21700,16 @@
         <v>0</v>
       </c>
       <c r="CH61" s="1">
-        <v>5292</v>
+        <v>5318</v>
       </c>
       <c r="CI61" s="2">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="CJ61" s="2">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="CK61" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="CL61" s="1">
         <v>7</v>
@@ -21736,16 +21736,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65673</v>
+        <v>65706</v>
       </c>
       <c r="CU61" s="1">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="CV61" s="1">
-        <v>663</v>
+        <v>560</v>
       </c>
       <c r="CW61" s="1">
-        <v>803</v>
+        <v>836</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22082,16 +22082,16 @@
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K63" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L63" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M63" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N63" s="1">
         <v>1118</v>
@@ -22205,7 +22205,7 @@
         <v>20</v>
       </c>
       <c r="AY63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ63" s="2">
         <v>1</v>
@@ -22259,19 +22259,19 @@
         <v>0</v>
       </c>
       <c r="BQ63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR63" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BS63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV63" s="1">
         <v>0</v>
@@ -22346,16 +22346,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2830</v>
+        <v>2836</v>
       </c>
       <c r="CU63" s="1">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="CV63" s="1">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="CW63" s="1">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22381,7 +22381,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" s="2">
         <v>2</v>
@@ -22444,7 +22444,7 @@
         <v>0</v>
       </c>
       <c r="AC64" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD64" s="1">
         <v>1993</v>
@@ -22453,7 +22453,7 @@
         <v>61</v>
       </c>
       <c r="AF64" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AG64" s="2">
         <v>172</v>
@@ -22657,10 +22657,10 @@
         <v>73</v>
       </c>
       <c r="CV64" s="1">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="CW64" s="1">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22692,16 +22692,16 @@
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>1752</v>
+        <v>1773</v>
       </c>
       <c r="K65" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L65" s="2">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="M65" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="N65" s="1">
         <v>57325</v>
@@ -22713,7 +22713,7 @@
         <v>1576</v>
       </c>
       <c r="Q65" s="2">
-        <v>2993</v>
+        <v>1574</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -22740,16 +22740,16 @@
         <v>1</v>
       </c>
       <c r="Z65" s="1">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AA65" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB65" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC65" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD65" s="1">
         <v>329</v>
@@ -22761,7 +22761,7 @@
         <v>11</v>
       </c>
       <c r="AG65" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AH65" s="1">
         <v>4</v>
@@ -22956,16 +22956,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>65483</v>
+        <v>65508</v>
       </c>
       <c r="CU65" s="1">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="CV65" s="1">
-        <v>1723</v>
+        <v>1748</v>
       </c>
       <c r="CW65" s="1">
-        <v>3334</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -22982,7 +22982,7 @@
         <v>9</v>
       </c>
       <c r="E66" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F66" s="1">
         <v>12</v>
@@ -23006,7 +23006,7 @@
         <v>31</v>
       </c>
       <c r="M66" s="2">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="N66" s="1">
         <v>0</v>
@@ -23270,7 +23270,7 @@
         <v>40</v>
       </c>
       <c r="CW66" s="1">
-        <v>130</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:101">
@@ -23287,7 +23287,7 @@
         <v>68</v>
       </c>
       <c r="E67" s="2">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -23575,7 +23575,7 @@
         <v>68</v>
       </c>
       <c r="CW67" s="1">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:101">
@@ -23628,7 +23628,7 @@
         <v>41</v>
       </c>
       <c r="Q68" s="2">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="R68" s="1">
         <v>0</v>
@@ -23880,7 +23880,7 @@
         <v>29</v>
       </c>
       <c r="CW68" s="1">
-        <v>104</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -24217,28 +24217,28 @@
         <v>2</v>
       </c>
       <c r="J70" s="1">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K70" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L70" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M70" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N70" s="1">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="O70" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P70" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q70" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="R70" s="1">
         <v>0</v>
@@ -24481,16 +24481,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2220</v>
+        <v>2239</v>
       </c>
       <c r="CU70" s="1">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="CV70" s="1">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="CW70" s="1">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24504,7 +24504,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E71" s="2">
         <v>3</v>
@@ -24516,7 +24516,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="2">
         <v>5</v>
@@ -24792,7 +24792,7 @@
         <v>0</v>
       </c>
       <c r="CV71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CW71" s="1">
         <v>8</v>
@@ -25216,16 +25216,16 @@
         <v>0</v>
       </c>
       <c r="AL73" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AM73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN73" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO73" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP73" s="1">
         <v>13</v>
@@ -25360,16 +25360,16 @@
         <v>0</v>
       </c>
       <c r="CH73" s="1">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="CI73" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CJ73" s="2">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CK73" s="2">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="CL73" s="1">
         <v>6</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="CT73" s="1">
-        <v>695</v>
+        <v>714</v>
       </c>
       <c r="CU73" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="CV73" s="1">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="CW73" s="1">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25416,13 +25416,13 @@
         <v>12531</v>
       </c>
       <c r="C74" s="2">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D74" s="2">
-        <v>232</v>
+        <v>89</v>
       </c>
       <c r="E74" s="2">
-        <v>437</v>
+        <v>366</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -25503,10 +25503,10 @@
         <v>214</v>
       </c>
       <c r="AF74" s="2">
-        <v>550</v>
+        <v>214</v>
       </c>
       <c r="AG74" s="2">
-        <v>1461</v>
+        <v>545</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25521,16 +25521,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36183</v>
+        <v>36213</v>
       </c>
       <c r="AM74" s="2">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="AN74" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AO74" s="2">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25665,16 +25665,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16057</v>
+        <v>16087</v>
       </c>
       <c r="CI74" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="CJ74" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="CK74" s="2">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,16 +25701,16 @@
         <v>1</v>
       </c>
       <c r="CT74" s="1">
-        <v>171292</v>
+        <v>171352</v>
       </c>
       <c r="CU74" s="1">
-        <v>1454</v>
+        <v>1413</v>
       </c>
       <c r="CV74" s="1">
-        <v>3800</v>
+        <v>3306</v>
       </c>
       <c r="CW74" s="1">
-        <v>5271</v>
+        <v>4332</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26029,10 +26029,10 @@
         <v>33</v>
       </c>
       <c r="D76" s="2">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="E76" s="2">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -26050,10 +26050,10 @@
         <v>5679</v>
       </c>
       <c r="K76" s="2">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="M76" s="2">
         <v>317</v>
@@ -26068,7 +26068,7 @@
         <v>1497</v>
       </c>
       <c r="Q76" s="2">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26095,16 +26095,16 @@
         <v>1</v>
       </c>
       <c r="Z76" s="1">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AA76" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB76" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AC76" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD76" s="1">
         <v>18580</v>
@@ -26113,10 +26113,10 @@
         <v>76</v>
       </c>
       <c r="AF76" s="2">
-        <v>614</v>
+        <v>76</v>
       </c>
       <c r="AG76" s="2">
-        <v>830</v>
+        <v>518</v>
       </c>
       <c r="AH76" s="1">
         <v>0</v>
@@ -26137,7 +26137,7 @@
         <v>0</v>
       </c>
       <c r="AN76" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO76" s="2">
         <v>2</v>
@@ -26152,7 +26152,7 @@
         <v>3</v>
       </c>
       <c r="AS76" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT76" s="1">
         <v>26</v>
@@ -26164,7 +26164,7 @@
         <v>3</v>
       </c>
       <c r="AW76" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX76" s="1">
         <v>10</v>
@@ -26176,7 +26176,7 @@
         <v>2</v>
       </c>
       <c r="BA76" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB76" s="1">
         <v>4</v>
@@ -26281,10 +26281,10 @@
         <v>16</v>
       </c>
       <c r="CJ76" s="2">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="CK76" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="CL76" s="1">
         <v>7</v>
@@ -26311,16 +26311,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>149946</v>
+        <v>149950</v>
       </c>
       <c r="CU76" s="1">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="CV76" s="1">
-        <v>2544</v>
+        <v>1883</v>
       </c>
       <c r="CW76" s="1">
-        <v>3092</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26331,10 +26331,10 @@
         <v>10824</v>
       </c>
       <c r="C77" s="2">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="D77" s="2">
-        <v>-4429</v>
+        <v>-1301</v>
       </c>
       <c r="E77" s="2">
         <v>-4218</v>
@@ -26352,16 +26352,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4739</v>
+        <v>4771</v>
       </c>
       <c r="K77" s="2">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="L77" s="2">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="M77" s="2">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="N77" s="1">
         <v>353289</v>
@@ -26373,7 +26373,7 @@
         <v>9550</v>
       </c>
       <c r="Q77" s="2">
-        <v>17514</v>
+        <v>9538</v>
       </c>
       <c r="R77" s="1">
         <v>0</v>
@@ -26436,16 +26436,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="AM77" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AN77" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AO77" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26580,16 +26580,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7084</v>
+        <v>7097</v>
       </c>
       <c r="CI77" s="2">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="CJ77" s="2">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="CK77" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26598,7 +26598,7 @@
         <v>0</v>
       </c>
       <c r="CN77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO77" s="2">
         <v>2</v>
@@ -26616,16 +26616,16 @@
         <v>0</v>
       </c>
       <c r="CT77" s="1">
-        <v>380851</v>
+        <v>380900</v>
       </c>
       <c r="CU77" s="1">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="CV77" s="1">
-        <v>5613</v>
+        <v>8673</v>
       </c>
       <c r="CW77" s="1">
-        <v>14311</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26741,16 +26741,16 @@
         <v>0</v>
       </c>
       <c r="AL78" s="1">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AM78" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN78" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AO78" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AP78" s="1">
         <v>0</v>
@@ -26888,7 +26888,7 @@
         <v>140</v>
       </c>
       <c r="CI78" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CJ78" s="2">
         <v>69</v>
@@ -26921,16 +26921,16 @@
         <v>0</v>
       </c>
       <c r="CT78" s="1">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="CU78" s="1">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="CV78" s="1">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="CW78" s="1">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -26962,16 +26962,16 @@
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>4455</v>
+        <v>4497</v>
       </c>
       <c r="K79" s="2">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="L79" s="2">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="M79" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N79" s="1">
         <v>68831</v>
@@ -26983,7 +26983,7 @@
         <v>748</v>
       </c>
       <c r="Q79" s="2">
-        <v>1311</v>
+        <v>750</v>
       </c>
       <c r="R79" s="1">
         <v>0</v>
@@ -27028,10 +27028,10 @@
         <v>5</v>
       </c>
       <c r="AF79" s="2">
+        <v>5</v>
+      </c>
+      <c r="AG79" s="2">
         <v>186</v>
-      </c>
-      <c r="AG79" s="2">
-        <v>361</v>
       </c>
       <c r="AH79" s="1">
         <v>0</v>
@@ -27052,7 +27052,7 @@
         <v>0</v>
       </c>
       <c r="AN79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO79" s="2">
         <v>6</v>
@@ -27061,7 +27061,7 @@
         <v>35</v>
       </c>
       <c r="AQ79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR79" s="2">
         <v>2</v>
@@ -27130,16 +27130,16 @@
         <v>0</v>
       </c>
       <c r="BN79" s="1">
-        <v>1247</v>
+        <v>1262</v>
       </c>
       <c r="BO79" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BP79" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="BQ79" s="2">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="BR79" s="1">
         <v>0</v>
@@ -27193,10 +27193,10 @@
         <v>2002</v>
       </c>
       <c r="CI79" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CJ79" s="2">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="CK79" s="2">
         <v>112</v>
@@ -27226,16 +27226,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90068</v>
+        <v>90125</v>
       </c>
       <c r="CU79" s="1">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="CV79" s="1">
-        <v>1263</v>
+        <v>962</v>
       </c>
       <c r="CW79" s="1">
-        <v>2151</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27351,16 +27351,16 @@
         <v>0</v>
       </c>
       <c r="AL80" s="1">
-        <v>753</v>
+        <v>772</v>
       </c>
       <c r="AM80" s="2">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AN80" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AO80" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="AP80" s="1">
         <v>0</v>
@@ -27489,22 +27489,22 @@
         <v>0</v>
       </c>
       <c r="CF80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG80" s="2">
         <v>1</v>
       </c>
       <c r="CH80" s="1">
-        <v>749</v>
+        <v>786</v>
       </c>
       <c r="CI80" s="2">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="CJ80" s="2">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="CK80" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="CL80" s="1">
         <v>0</v>
@@ -27531,16 +27531,16 @@
         <v>0</v>
       </c>
       <c r="CT80" s="1">
-        <v>1657</v>
+        <v>1713</v>
       </c>
       <c r="CU80" s="1">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="CV80" s="1">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="CW80" s="1">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -27548,16 +27548,16 @@
         <v>180</v>
       </c>
       <c r="B81" s="1">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C81" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D81" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E81" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F81" s="1">
         <v>5</v>
@@ -27593,7 +27593,7 @@
         <v>146</v>
       </c>
       <c r="Q81" s="2">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="R81" s="1">
         <v>0</v>
@@ -27701,7 +27701,7 @@
         <v>1</v>
       </c>
       <c r="BA81" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB81" s="1">
         <v>0</v>
@@ -27836,16 +27836,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="CU81" s="1">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="CV81" s="1">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="CW81" s="1">
-        <v>363</v>
+        <v>296</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -27901,16 +27901,16 @@
         <v>1</v>
       </c>
       <c r="R82" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" s="1">
         <v>4</v>
@@ -28141,16 +28141,16 @@
         <v>0</v>
       </c>
       <c r="CT82" s="1">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="CU82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV82" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW82" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -28185,25 +28185,25 @@
         <v>8577</v>
       </c>
       <c r="K83" s="2">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="L83" s="2">
-        <v>319</v>
+        <v>204</v>
       </c>
       <c r="M83" s="2">
         <v>493</v>
       </c>
       <c r="N83" s="1">
-        <v>39862</v>
+        <v>40132</v>
       </c>
       <c r="O83" s="2">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="P83" s="2">
-        <v>721</v>
+        <v>991</v>
       </c>
       <c r="Q83" s="2">
-        <v>721</v>
+        <v>991</v>
       </c>
       <c r="R83" s="1">
         <v>0</v>
@@ -28242,16 +28242,16 @@
         <v>6</v>
       </c>
       <c r="AD83" s="1">
-        <v>352726</v>
+        <v>352902</v>
       </c>
       <c r="AE83" s="2">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AF83" s="2">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AG83" s="2">
-        <v>3307</v>
+        <v>3483</v>
       </c>
       <c r="AH83" s="1">
         <v>0</v>
@@ -28266,16 +28266,16 @@
         <v>0</v>
       </c>
       <c r="AL83" s="1">
-        <v>3387</v>
+        <v>3390</v>
       </c>
       <c r="AM83" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN83" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO83" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP83" s="1">
         <v>0</v>
@@ -28392,7 +28392,7 @@
         <v>0</v>
       </c>
       <c r="CB83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC83" s="2">
         <v>1</v>
@@ -28410,16 +28410,16 @@
         <v>0</v>
       </c>
       <c r="CH83" s="1">
-        <v>13662</v>
+        <v>13733</v>
       </c>
       <c r="CI83" s="2">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="CJ83" s="2">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="CK83" s="2">
-        <v>186</v>
+        <v>257</v>
       </c>
       <c r="CL83" s="1">
         <v>0</v>
@@ -28446,16 +28446,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423158</v>
+        <v>423678</v>
       </c>
       <c r="CU83" s="1">
-        <v>253</v>
+        <v>699</v>
       </c>
       <c r="CV83" s="1">
-        <v>1266</v>
+        <v>1670</v>
       </c>
       <c r="CW83" s="1">
-        <v>4944</v>
+        <v>5464</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28774,7 +28774,7 @@
         <v>0</v>
       </c>
       <c r="D85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" s="2">
         <v>1</v>
@@ -29062,7 +29062,7 @@
         <v>15</v>
       </c>
       <c r="CV85" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CW85" s="1">
         <v>60</v>
@@ -29076,7 +29076,7 @@
         <v>102</v>
       </c>
       <c r="C86" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" s="2">
         <v>5</v>
@@ -29106,7 +29106,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N86" s="1">
         <v>1593</v>
@@ -29364,13 +29364,13 @@
         <v>2826</v>
       </c>
       <c r="CU86" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CV86" s="1">
         <v>61</v>
       </c>
       <c r="CW86" s="1">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29486,16 +29486,16 @@
         <v>0</v>
       </c>
       <c r="AL87" s="1">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AM87" s="2">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="AN87" s="2">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AO87" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP87" s="1">
         <v>24</v>
@@ -29630,16 +29630,16 @@
         <v>0</v>
       </c>
       <c r="CH87" s="1">
-        <v>2357</v>
+        <v>2368</v>
       </c>
       <c r="CI87" s="2">
-        <v>9</v>
+        <v>-8</v>
       </c>
       <c r="CJ87" s="2">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="CK87" s="2">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="CL87" s="1">
         <v>15</v>
@@ -29666,16 +29666,16 @@
         <v>0</v>
       </c>
       <c r="CT87" s="1">
-        <v>2938</v>
+        <v>2948</v>
       </c>
       <c r="CU87" s="1">
-        <v>10</v>
+        <v>-14</v>
       </c>
       <c r="CV87" s="1">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="CW87" s="1">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -29689,10 +29689,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F88" s="1">
         <v>18</v>
@@ -29713,10 +29713,10 @@
         <v>8</v>
       </c>
       <c r="L88" s="2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="M88" s="2">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="N88" s="1">
         <v>1025</v>
@@ -29725,7 +29725,7 @@
         <v>0</v>
       </c>
       <c r="P88" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q88" s="2">
         <v>4</v>
@@ -29773,10 +29773,10 @@
         <v>0</v>
       </c>
       <c r="AF88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="2">
         <v>222</v>
-      </c>
-      <c r="AG88" s="2">
-        <v>265</v>
       </c>
       <c r="AH88" s="1">
         <v>0</v>
@@ -29809,10 +29809,10 @@
         <v>1</v>
       </c>
       <c r="AR88" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS88" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT88" s="1">
         <v>0</v>
@@ -29941,10 +29941,10 @@
         <v>3</v>
       </c>
       <c r="CJ88" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="CK88" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="CL88" s="1">
         <v>22</v>
@@ -29977,10 +29977,10 @@
         <v>6</v>
       </c>
       <c r="CV88" s="1">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="CW88" s="1">
-        <v>397</v>
+        <v>330</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -29994,7 +29994,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
@@ -30018,10 +30018,10 @@
         <v>19</v>
       </c>
       <c r="L89" s="2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="M89" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N89" s="1">
         <v>48</v>
@@ -30282,10 +30282,10 @@
         <v>67</v>
       </c>
       <c r="CV89" s="1">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="CW89" s="1">
-        <v>438</v>
+        <v>428</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30607,7 +30607,7 @@
         <v>124</v>
       </c>
       <c r="E91" s="2">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -30622,28 +30622,28 @@
         <v>0</v>
       </c>
       <c r="J91" s="1">
-        <v>5303</v>
+        <v>5364</v>
       </c>
       <c r="K91" s="2">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L91" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="M91" s="2">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="N91" s="1">
-        <v>4396</v>
+        <v>4418</v>
       </c>
       <c r="O91" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P91" s="2">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="Q91" s="2">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="R91" s="1">
         <v>0</v>
@@ -30715,7 +30715,7 @@
         <v>2</v>
       </c>
       <c r="AO91" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AP91" s="1">
         <v>26</v>
@@ -30859,7 +30859,7 @@
         <v>73</v>
       </c>
       <c r="CK91" s="2">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="CL91" s="1">
         <v>5</v>
@@ -30886,16 +30886,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25611</v>
+        <v>25694</v>
       </c>
       <c r="CU91" s="1">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="CV91" s="1">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="CW91" s="1">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -30909,7 +30909,7 @@
         <v>3</v>
       </c>
       <c r="D92" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E92" s="2">
         <v>15</v>
@@ -30933,7 +30933,7 @@
         <v>2</v>
       </c>
       <c r="L92" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M92" s="2">
         <v>13</v>
@@ -31017,7 +31017,7 @@
         <v>0</v>
       </c>
       <c r="AN92" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO92" s="2">
         <v>4</v>
@@ -31161,10 +31161,10 @@
         <v>4</v>
       </c>
       <c r="CJ92" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CK92" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CL92" s="1">
         <v>25</v>
@@ -31197,10 +31197,10 @@
         <v>9</v>
       </c>
       <c r="CV92" s="1">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="CW92" s="1">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -31334,7 +31334,7 @@
         <v>0</v>
       </c>
       <c r="AR93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS93" s="2">
         <v>3</v>
@@ -31466,7 +31466,7 @@
         <v>0</v>
       </c>
       <c r="CJ93" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CK93" s="2">
         <v>7</v>
@@ -31502,7 +31502,7 @@
         <v>2</v>
       </c>
       <c r="CV93" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CW93" s="1">
         <v>45</v>
@@ -33457,10 +33457,10 @@
         <v>5</v>
       </c>
       <c r="AN100" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AO100" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP100" s="1">
         <v>0</v>
@@ -33601,10 +33601,10 @@
         <v>5</v>
       </c>
       <c r="CJ100" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CK100" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CL100" s="1">
         <v>0</v>
@@ -33637,10 +33637,10 @@
         <v>11</v>
       </c>
       <c r="CV100" s="1">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="CW100" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33983,22 +33983,22 @@
         <v>0</v>
       </c>
       <c r="L102" s="2">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="M102" s="2">
         <v>180</v>
       </c>
       <c r="N102" s="1">
-        <v>14447</v>
+        <v>14647</v>
       </c>
       <c r="O102" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P102" s="2">
-        <v>334</v>
+        <v>534</v>
       </c>
       <c r="Q102" s="2">
-        <v>339</v>
+        <v>539</v>
       </c>
       <c r="R102" s="1">
         <v>0</v>
@@ -34073,16 +34073,16 @@
         <v>2</v>
       </c>
       <c r="AP102" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AQ102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR102" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS102" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT102" s="1">
         <v>59</v>
@@ -34094,7 +34094,7 @@
         <v>2</v>
       </c>
       <c r="AW102" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX102" s="1">
         <v>17</v>
@@ -34106,7 +34106,7 @@
         <v>1</v>
       </c>
       <c r="BA102" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB102" s="1">
         <v>5</v>
@@ -34205,16 +34205,16 @@
         <v>0</v>
       </c>
       <c r="CH102" s="1">
-        <v>1758</v>
+        <v>1779</v>
       </c>
       <c r="CI102" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CJ102" s="2">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="CK102" s="2">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="CL102" s="1">
         <v>9</v>
@@ -34241,16 +34241,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>42612</v>
+        <v>42834</v>
       </c>
       <c r="CU102" s="1">
-        <v>312</v>
+        <v>534</v>
       </c>
       <c r="CV102" s="1">
-        <v>1085</v>
+        <v>1260</v>
       </c>
       <c r="CW102" s="1">
-        <v>1675</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34375,7 +34375,7 @@
         <v>3</v>
       </c>
       <c r="AO103" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP103" s="1">
         <v>0</v>
@@ -34519,7 +34519,7 @@
         <v>67</v>
       </c>
       <c r="CK103" s="2">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="CL103" s="1">
         <v>0</v>
@@ -34555,7 +34555,7 @@
         <v>71</v>
       </c>
       <c r="CW103" s="1">
-        <v>167</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -34892,16 +34892,16 @@
         <v>0</v>
       </c>
       <c r="J105" s="1">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="K105" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L105" s="2">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="M105" s="2">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="N105" s="1">
         <v>1428</v>
@@ -34952,16 +34952,16 @@
         <v>0</v>
       </c>
       <c r="AD105" s="1">
-        <v>4319</v>
+        <v>4465</v>
       </c>
       <c r="AE105" s="2">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AF105" s="2">
-        <v>225</v>
+        <v>371</v>
       </c>
       <c r="AG105" s="2">
-        <v>369</v>
+        <v>515</v>
       </c>
       <c r="AH105" s="1">
         <v>0</v>
@@ -35156,16 +35156,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7790</v>
+        <v>7951</v>
       </c>
       <c r="CU105" s="1">
-        <v>14</v>
+        <v>175</v>
       </c>
       <c r="CV105" s="1">
-        <v>286</v>
+        <v>447</v>
       </c>
       <c r="CW105" s="1">
-        <v>484</v>
+        <v>645</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -35173,16 +35173,16 @@
         <v>205</v>
       </c>
       <c r="B106" s="1">
-        <v>9257</v>
+        <v>9323</v>
       </c>
       <c r="C106" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D106" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="E106" s="2">
-        <v>343</v>
+        <v>409</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -35203,22 +35203,22 @@
         <v>178</v>
       </c>
       <c r="L106" s="2">
-        <v>526</v>
+        <v>381</v>
       </c>
       <c r="M106" s="2">
-        <v>1047</v>
+        <v>904</v>
       </c>
       <c r="N106" s="1">
-        <v>22734</v>
+        <v>22721</v>
       </c>
       <c r="O106" s="2">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="P106" s="2">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="Q106" s="2">
-        <v>570</v>
+        <v>292</v>
       </c>
       <c r="R106" s="1">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>0</v>
       </c>
       <c r="AF106" s="2">
-        <v>186</v>
+        <v>43</v>
       </c>
       <c r="AG106" s="2">
         <v>80</v>
@@ -35281,16 +35281,16 @@
         <v>0</v>
       </c>
       <c r="AL106" s="1">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AM106" s="2">
         <v>2</v>
       </c>
       <c r="AN106" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO106" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP106" s="1">
         <v>8</v>
@@ -35425,16 +35425,16 @@
         <v>0</v>
       </c>
       <c r="CH106" s="1">
-        <v>6321</v>
+        <v>6392</v>
       </c>
       <c r="CI106" s="2">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="CJ106" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="CK106" s="2">
-        <v>280</v>
+        <v>351</v>
       </c>
       <c r="CL106" s="1">
         <v>0</v>
@@ -35461,16 +35461,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>91774</v>
+        <v>91900</v>
       </c>
       <c r="CU106" s="1">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="CV106" s="1">
-        <v>1371</v>
+        <v>1124</v>
       </c>
       <c r="CW106" s="1">
-        <v>2354</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36044,7 +36044,7 @@
         <v>11</v>
       </c>
       <c r="CK108" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="CL108" s="1">
         <v>7</v>
@@ -36080,7 +36080,7 @@
         <v>33</v>
       </c>
       <c r="CW108" s="1">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:101">
@@ -36417,16 +36417,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="1">
-        <v>4755</v>
+        <v>4825</v>
       </c>
       <c r="K110" s="2">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="L110" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="M110" s="2">
-        <v>331</v>
+        <v>401</v>
       </c>
       <c r="N110" s="1">
         <v>1303</v>
@@ -36477,16 +36477,16 @@
         <v>8</v>
       </c>
       <c r="AD110" s="1">
-        <v>2211</v>
+        <v>2261</v>
       </c>
       <c r="AE110" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF110" s="2">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="AG110" s="2">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="AH110" s="1">
         <v>0</v>
@@ -36594,7 +36594,7 @@
         <v>0</v>
       </c>
       <c r="BQ110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR110" s="1">
         <v>0</v>
@@ -36651,7 +36651,7 @@
         <v>23</v>
       </c>
       <c r="CJ110" s="2">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="CK110" s="2">
         <v>132</v>
@@ -36681,16 +36681,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13039</v>
+        <v>13159</v>
       </c>
       <c r="CU110" s="1">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="CV110" s="1">
-        <v>647</v>
+        <v>433</v>
       </c>
       <c r="CW110" s="1">
-        <v>868</v>
+        <v>987</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36806,16 +36806,16 @@
         <v>0</v>
       </c>
       <c r="AL111" s="1">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AM111" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN111" s="2">
         <v>9</v>
       </c>
       <c r="AO111" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AP111" s="1">
         <v>44</v>
@@ -36950,16 +36950,16 @@
         <v>0</v>
       </c>
       <c r="CH111" s="1">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="CI111" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CJ111" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="CK111" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="CL111" s="1">
         <v>27</v>
@@ -36986,16 +36986,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="CU111" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="CV111" s="1">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="CW111" s="1">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37009,7 +37009,7 @@
         <v>15</v>
       </c>
       <c r="D112" s="2">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E112" s="2">
         <v>60</v>
@@ -37033,22 +37033,22 @@
         <v>9</v>
       </c>
       <c r="L112" s="2">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="M112" s="2">
         <v>78</v>
       </c>
       <c r="N112" s="1">
-        <v>5420</v>
+        <v>5612</v>
       </c>
       <c r="O112" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="P112" s="2">
-        <v>292</v>
+        <v>484</v>
       </c>
       <c r="Q112" s="2">
-        <v>292</v>
+        <v>484</v>
       </c>
       <c r="R112" s="1">
         <v>0</v>
@@ -37123,16 +37123,16 @@
         <v>0</v>
       </c>
       <c r="AP112" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AQ112" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR112" s="2">
         <v>3</v>
       </c>
       <c r="AS112" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT112" s="1">
         <v>0</v>
@@ -37255,16 +37255,16 @@
         <v>0</v>
       </c>
       <c r="CH112" s="1">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="CI112" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ112" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CK112" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CL112" s="1">
         <v>26</v>
@@ -37291,16 +37291,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8052</v>
+        <v>8248</v>
       </c>
       <c r="CU112" s="1">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="CV112" s="1">
-        <v>402</v>
+        <v>559</v>
       </c>
       <c r="CW112" s="1">
-        <v>448</v>
+        <v>644</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37338,22 +37338,22 @@
         <v>0</v>
       </c>
       <c r="L113" s="2">
-        <v>217</v>
+        <v>141</v>
       </c>
       <c r="M113" s="2">
         <v>350</v>
       </c>
       <c r="N113" s="1">
-        <v>7848</v>
+        <v>8025</v>
       </c>
       <c r="O113" s="2">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P113" s="2">
-        <v>274</v>
+        <v>451</v>
       </c>
       <c r="Q113" s="2">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="R113" s="1">
         <v>0</v>
@@ -37398,10 +37398,10 @@
         <v>0</v>
       </c>
       <c r="AF113" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG113" s="2">
         <v>8812</v>
-      </c>
-      <c r="AG113" s="2">
-        <v>13156</v>
       </c>
       <c r="AH113" s="1">
         <v>1</v>
@@ -37425,7 +37425,7 @@
         <v>4</v>
       </c>
       <c r="AO113" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AP113" s="1">
         <v>0</v>
@@ -37506,7 +37506,7 @@
         <v>6</v>
       </c>
       <c r="BP113" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BQ113" s="2">
         <v>7</v>
@@ -37566,10 +37566,10 @@
         <v>8</v>
       </c>
       <c r="CJ113" s="2">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="CK113" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37596,16 +37596,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173451</v>
+        <v>173628</v>
       </c>
       <c r="CU113" s="1">
-        <v>51</v>
+        <v>228</v>
       </c>
       <c r="CV113" s="1">
-        <v>9419</v>
+        <v>674</v>
       </c>
       <c r="CW113" s="1">
-        <v>14184</v>
+        <v>9837</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38229,10 +38229,10 @@
         <v>19</v>
       </c>
       <c r="D116" s="2">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E116" s="2">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -38247,28 +38247,28 @@
         <v>0</v>
       </c>
       <c r="J116" s="1">
-        <v>4813</v>
+        <v>4854</v>
       </c>
       <c r="K116" s="2">
         <v>41</v>
       </c>
       <c r="L116" s="2">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="M116" s="2">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="N116" s="1">
-        <v>4431</v>
+        <v>4537</v>
       </c>
       <c r="O116" s="2">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="P116" s="2">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="Q116" s="2">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="R116" s="1">
         <v>0</v>
@@ -38307,16 +38307,16 @@
         <v>6</v>
       </c>
       <c r="AD116" s="1">
-        <v>5082</v>
+        <v>5122</v>
       </c>
       <c r="AE116" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF116" s="2">
-        <v>361</v>
+        <v>40</v>
       </c>
       <c r="AG116" s="2">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="AH116" s="1">
         <v>1</v>
@@ -38331,16 +38331,16 @@
         <v>0</v>
       </c>
       <c r="AL116" s="1">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AM116" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN116" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO116" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP116" s="1">
         <v>27</v>
@@ -38475,16 +38475,16 @@
         <v>0</v>
       </c>
       <c r="CH116" s="1">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="CI116" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="CJ116" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="CK116" s="2">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="CL116" s="1">
         <v>12</v>
@@ -38511,16 +38511,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21451</v>
+        <v>21653</v>
       </c>
       <c r="CU116" s="1">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="CV116" s="1">
-        <v>768</v>
+        <v>518</v>
       </c>
       <c r="CW116" s="1">
-        <v>1015</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38534,10 +38534,10 @@
         <v>380</v>
       </c>
       <c r="D117" s="2">
-        <v>751</v>
+        <v>554</v>
       </c>
       <c r="E117" s="2">
-        <v>1123</v>
+        <v>980</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -38651,7 +38651,7 @@
         <v>61</v>
       </c>
       <c r="AQ117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR117" s="2">
         <v>2</v>
@@ -38726,7 +38726,7 @@
         <v>0</v>
       </c>
       <c r="BP117" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BQ117" s="2">
         <v>20</v>
@@ -38783,7 +38783,7 @@
         <v>161</v>
       </c>
       <c r="CI117" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ117" s="2">
         <v>5</v>
@@ -38819,13 +38819,13 @@
         <v>12983</v>
       </c>
       <c r="CU117" s="1">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="CV117" s="1">
-        <v>802</v>
+        <v>602</v>
       </c>
       <c r="CW117" s="1">
-        <v>1301</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -39342,16 +39342,16 @@
         <v>0</v>
       </c>
       <c r="BR119" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BS119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT119" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU119" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV119" s="1">
         <v>0</v>
@@ -39426,16 +39426,16 @@
         <v>0</v>
       </c>
       <c r="CT119" s="1">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="CU119" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV119" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CW119" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -41288,7 +41288,7 @@
         <v>62</v>
       </c>
       <c r="G126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" s="2">
         <v>2</v>
@@ -41516,7 +41516,7 @@
         <v>5</v>
       </c>
       <c r="CE126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF126" s="2">
         <v>1</v>
@@ -41564,7 +41564,7 @@
         <v>832</v>
       </c>
       <c r="CU126" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV126" s="1">
         <v>13</v>
@@ -42197,7 +42197,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F129" s="1">
         <v>42</v>
@@ -42224,16 +42224,16 @@
         <v>0</v>
       </c>
       <c r="N129" s="1">
-        <v>2266</v>
+        <v>2344</v>
       </c>
       <c r="O129" s="2">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="P129" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="Q129" s="2">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="R129" s="1">
         <v>0</v>
@@ -42254,7 +42254,7 @@
         <v>0</v>
       </c>
       <c r="X129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y129" s="2">
         <v>1</v>
@@ -42302,22 +42302,22 @@
         <v>0</v>
       </c>
       <c r="AN129" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AO129" s="2">
         <v>16</v>
       </c>
       <c r="AP129" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AQ129" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR129" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS129" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT129" s="1">
         <v>0</v>
@@ -42440,16 +42440,16 @@
         <v>0</v>
       </c>
       <c r="CH129" s="1">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="CI129" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="CJ129" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CK129" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="CL129" s="1">
         <v>37</v>
@@ -42476,16 +42476,16 @@
         <v>0</v>
       </c>
       <c r="CT129" s="1">
-        <v>3465</v>
+        <v>3557</v>
       </c>
       <c r="CU129" s="1">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="CV129" s="1">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="CW129" s="1">
-        <v>205</v>
+        <v>296</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -42511,7 +42511,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I130" s="2">
         <v>3</v>
@@ -42604,7 +42604,7 @@
         <v>149</v>
       </c>
       <c r="AM130" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AN130" s="2">
         <v>16</v>
@@ -42748,7 +42748,7 @@
         <v>214</v>
       </c>
       <c r="CI130" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CJ130" s="2">
         <v>23</v>
@@ -42784,10 +42784,10 @@
         <v>1081</v>
       </c>
       <c r="CU130" s="1">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="CV130" s="1">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="CW130" s="1">
         <v>224</v>
@@ -43115,16 +43115,16 @@
         <v>0</v>
       </c>
       <c r="F132" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G132" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" s="2">
         <v>3</v>
       </c>
       <c r="I132" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J132" s="1">
         <v>0</v>
@@ -43391,16 +43391,16 @@
         <v>0</v>
       </c>
       <c r="CT132" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CU132" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV132" s="1">
         <v>3</v>
       </c>
       <c r="CW132" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:101">
@@ -43414,7 +43414,7 @@
         <v>0</v>
       </c>
       <c r="D133" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E133" s="2">
         <v>4</v>
@@ -43423,7 +43423,7 @@
         <v>71</v>
       </c>
       <c r="G133" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H133" s="2">
         <v>3</v>
@@ -43699,10 +43699,10 @@
         <v>95</v>
       </c>
       <c r="CU133" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV133" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CW133" s="1">
         <v>8</v>
@@ -43758,7 +43758,7 @@
         <v>1758</v>
       </c>
       <c r="Q134" s="2">
-        <v>2598</v>
+        <v>1758</v>
       </c>
       <c r="R134" s="1">
         <v>0</v>
@@ -43821,16 +43821,16 @@
         <v>0</v>
       </c>
       <c r="AL134" s="1">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="AM134" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN134" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO134" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AP134" s="1">
         <v>36</v>
@@ -43965,16 +43965,16 @@
         <v>0</v>
       </c>
       <c r="CH134" s="1">
-        <v>2708</v>
+        <v>2724</v>
       </c>
       <c r="CI134" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CJ134" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="CK134" s="2">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="CL134" s="1">
         <v>9</v>
@@ -44001,16 +44001,16 @@
         <v>0</v>
       </c>
       <c r="CT134" s="1">
-        <v>132659</v>
+        <v>132678</v>
       </c>
       <c r="CU134" s="1">
-        <v>738</v>
+        <v>757</v>
       </c>
       <c r="CV134" s="1">
-        <v>3997</v>
+        <v>4016</v>
       </c>
       <c r="CW134" s="1">
-        <v>4872</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44021,10 +44021,10 @@
         <v>7625</v>
       </c>
       <c r="C135" s="2">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D135" s="2">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="E135" s="2">
         <v>349</v>
@@ -44048,7 +44048,7 @@
         <v>53</v>
       </c>
       <c r="L135" s="2">
-        <v>320</v>
+        <v>229</v>
       </c>
       <c r="M135" s="2">
         <v>469</v>
@@ -44063,7 +44063,7 @@
         <v>595</v>
       </c>
       <c r="Q135" s="2">
-        <v>1105</v>
+        <v>593</v>
       </c>
       <c r="R135" s="1">
         <v>0</v>
@@ -44102,16 +44102,16 @@
         <v>12</v>
       </c>
       <c r="AD135" s="1">
-        <v>11631</v>
+        <v>11637</v>
       </c>
       <c r="AE135" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AF135" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="AG135" s="2">
-        <v>1027</v>
+        <v>639</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44126,16 +44126,16 @@
         <v>0</v>
       </c>
       <c r="AL135" s="1">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="AM135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN135" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO135" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP135" s="1">
         <v>23</v>
@@ -44270,16 +44270,16 @@
         <v>0</v>
       </c>
       <c r="CH135" s="1">
-        <v>3086</v>
+        <v>3117</v>
       </c>
       <c r="CI135" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="CJ135" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="CK135" s="2">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="CL135" s="1">
         <v>13</v>
@@ -44306,16 +44306,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>61925</v>
+        <v>61964</v>
       </c>
       <c r="CU135" s="1">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="CV135" s="1">
-        <v>1853</v>
+        <v>1687</v>
       </c>
       <c r="CW135" s="1">
-        <v>3120</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44368,7 +44368,7 @@
         <v>38</v>
       </c>
       <c r="Q136" s="2">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R136" s="1">
         <v>10</v>
@@ -44413,10 +44413,10 @@
         <v>5042</v>
       </c>
       <c r="AF136" s="2">
+        <v>5042</v>
+      </c>
+      <c r="AG136" s="2">
         <v>5983</v>
-      </c>
-      <c r="AG136" s="2">
-        <v>8380</v>
       </c>
       <c r="AH136" s="1">
         <v>0</v>
@@ -44575,16 +44575,16 @@
         <v>0</v>
       </c>
       <c r="CH136" s="1">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="CI136" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="CJ136" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CK136" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="CL136" s="1">
         <v>13</v>
@@ -44611,16 +44611,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>158838</v>
+        <v>158846</v>
       </c>
       <c r="CU136" s="1">
-        <v>5046</v>
+        <v>5054</v>
       </c>
       <c r="CV136" s="1">
-        <v>6046</v>
+        <v>5106</v>
       </c>
       <c r="CW136" s="1">
-        <v>8473</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -44963,7 +44963,7 @@
         <v>14</v>
       </c>
       <c r="L138" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M138" s="2">
         <v>64</v>
@@ -44978,7 +44978,7 @@
         <v>135</v>
       </c>
       <c r="Q138" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="R138" s="1">
         <v>0</v>
@@ -45227,10 +45227,10 @@
         <v>71</v>
       </c>
       <c r="CV138" s="1">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="CW138" s="1">
-        <v>311</v>
+        <v>256</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -45558,10 +45558,10 @@
         <v>47</v>
       </c>
       <c r="G140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I140" s="2">
         <v>4</v>
@@ -45666,10 +45666,10 @@
         <v>33</v>
       </c>
       <c r="AQ140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS140" s="2">
         <v>4</v>
@@ -45798,10 +45798,10 @@
         <v>145</v>
       </c>
       <c r="CI140" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ140" s="2">
         <v>2</v>
-      </c>
-      <c r="CJ140" s="2">
-        <v>3</v>
       </c>
       <c r="CK140" s="2">
         <v>4</v>
@@ -45834,10 +45834,10 @@
         <v>564</v>
       </c>
       <c r="CU140" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CV140" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CW140" s="1">
         <v>26</v>
@@ -45848,16 +45848,16 @@
         <v>240</v>
       </c>
       <c r="B141" s="1">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C141" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D141" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E141" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F141" s="1">
         <v>49</v>
@@ -45890,7 +45890,7 @@
         <v>3</v>
       </c>
       <c r="P141" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q141" s="2">
         <v>8</v>
@@ -46052,16 +46052,16 @@
         <v>0</v>
       </c>
       <c r="BR141" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT141" s="2">
         <v>1</v>
       </c>
       <c r="BU141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV141" s="1">
         <v>0</v>
@@ -46136,16 +46136,16 @@
         <v>0</v>
       </c>
       <c r="CT141" s="1">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="CU141" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CV141" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="CW141" s="1">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46171,7 +46171,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I142" s="2">
         <v>3</v>
@@ -46447,7 +46447,7 @@
         <v>32</v>
       </c>
       <c r="CV142" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="CW142" s="1">
         <v>86</v>
@@ -46473,10 +46473,10 @@
         <v>71</v>
       </c>
       <c r="G143" s="2">
+        <v>1</v>
+      </c>
+      <c r="H143" s="2">
         <v>2</v>
-      </c>
-      <c r="H143" s="2">
-        <v>3</v>
       </c>
       <c r="I143" s="2">
         <v>5</v>
@@ -46581,10 +46581,10 @@
         <v>80</v>
       </c>
       <c r="AQ143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS143" s="2">
         <v>5</v>
@@ -46716,7 +46716,7 @@
         <v>0</v>
       </c>
       <c r="CJ143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK143" s="2">
         <v>3</v>
@@ -46725,7 +46725,7 @@
         <v>72</v>
       </c>
       <c r="CM143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN143" s="2">
         <v>1</v>
@@ -46749,10 +46749,10 @@
         <v>290</v>
       </c>
       <c r="CU143" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CV143" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CW143" s="1">
         <v>18</v>
@@ -47074,7 +47074,7 @@
         <v>2</v>
       </c>
       <c r="D145" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E145" s="2">
         <v>41</v>
@@ -47098,22 +47098,22 @@
         <v>5</v>
       </c>
       <c r="L145" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M145" s="2">
         <v>18</v>
       </c>
       <c r="N145" s="1">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="O145" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P145" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Q145" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="R145" s="1">
         <v>0</v>
@@ -47152,16 +47152,16 @@
         <v>0</v>
       </c>
       <c r="AD145" s="1">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="AE145" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF145" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG145" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH145" s="1">
         <v>19</v>
@@ -47170,7 +47170,7 @@
         <v>0</v>
       </c>
       <c r="AJ145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK145" s="2">
         <v>1</v>
@@ -47221,7 +47221,7 @@
         <v>4</v>
       </c>
       <c r="BA145" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB145" s="1">
         <v>0</v>
@@ -47278,7 +47278,7 @@
         <v>1</v>
       </c>
       <c r="BT145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU145" s="2">
         <v>2</v>
@@ -47326,7 +47326,7 @@
         <v>5</v>
       </c>
       <c r="CJ145" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CK145" s="2">
         <v>9</v>
@@ -47356,16 +47356,16 @@
         <v>0</v>
       </c>
       <c r="CT145" s="1">
-        <v>2439</v>
+        <v>2456</v>
       </c>
       <c r="CU145" s="1">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="CV145" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="CW145" s="1">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -47696,10 +47696,10 @@
         <v>1</v>
       </c>
       <c r="H147" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I147" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J147" s="1">
         <v>18</v>
@@ -47972,10 +47972,10 @@
         <v>7</v>
       </c>
       <c r="CV147" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CW147" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -48013,10 +48013,10 @@
         <v>8</v>
       </c>
       <c r="L148" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M148" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N148" s="1">
         <v>3216</v>
@@ -48028,7 +48028,7 @@
         <v>87</v>
       </c>
       <c r="Q148" s="2">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="R148" s="1">
         <v>0</v>
@@ -48097,10 +48097,10 @@
         <v>2</v>
       </c>
       <c r="AN148" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AO148" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AP148" s="1">
         <v>29</v>
@@ -48241,10 +48241,10 @@
         <v>22</v>
       </c>
       <c r="CJ148" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="CK148" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="CL148" s="1">
         <v>16</v>
@@ -48277,10 +48277,10 @@
         <v>33</v>
       </c>
       <c r="CV148" s="1">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="CW148" s="1">
-        <v>261</v>
+        <v>195</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -48333,7 +48333,7 @@
         <v>21</v>
       </c>
       <c r="Q149" s="2">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="R149" s="1">
         <v>0</v>
@@ -48585,7 +48585,7 @@
         <v>44</v>
       </c>
       <c r="CW149" s="1">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150" spans="1:101">
@@ -48713,7 +48713,7 @@
         <v>0</v>
       </c>
       <c r="AP150" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ150" s="2">
         <v>1</v>
@@ -48722,7 +48722,7 @@
         <v>3</v>
       </c>
       <c r="AS150" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT150" s="1">
         <v>0</v>
@@ -48857,7 +48857,7 @@
         <v>3</v>
       </c>
       <c r="CL150" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CM150" s="2">
         <v>1</v>
@@ -48866,7 +48866,7 @@
         <v>2</v>
       </c>
       <c r="CO150" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP150" s="1">
         <v>0</v>
@@ -48881,7 +48881,7 @@
         <v>0</v>
       </c>
       <c r="CT150" s="1">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="CU150" s="1">
         <v>2</v>
@@ -48890,7 +48890,7 @@
         <v>8</v>
       </c>
       <c r="CW150" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151" spans="1:101">
@@ -49006,7 +49006,7 @@
         <v>0</v>
       </c>
       <c r="AL151" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM151" s="2">
         <v>1</v>
@@ -49015,16 +49015,16 @@
         <v>2</v>
       </c>
       <c r="AO151" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP151" s="1">
         <v>62</v>
       </c>
       <c r="AQ151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR151" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS151" s="2">
         <v>5</v>
@@ -49102,16 +49102,16 @@
         <v>0</v>
       </c>
       <c r="BR151" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU151" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV151" s="1">
         <v>0</v>
@@ -49150,22 +49150,22 @@
         <v>0</v>
       </c>
       <c r="CH151" s="1">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="CI151" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CJ151" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CK151" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CL151" s="1">
         <v>28</v>
       </c>
       <c r="CM151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN151" s="2">
         <v>1</v>
@@ -49186,16 +49186,16 @@
         <v>0</v>
       </c>
       <c r="CT151" s="1">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="CU151" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CV151" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="CW151" s="1">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:101">
@@ -49212,7 +49212,7 @@
         <v>5</v>
       </c>
       <c r="E152" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1">
         <v>21</v>
@@ -49233,10 +49233,10 @@
         <v>17</v>
       </c>
       <c r="L152" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M152" s="2">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="N152" s="1">
         <v>168</v>
@@ -49293,10 +49293,10 @@
         <v>0</v>
       </c>
       <c r="AF152" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG152" s="2">
         <v>116</v>
-      </c>
-      <c r="AG152" s="2">
-        <v>140</v>
       </c>
       <c r="AH152" s="1">
         <v>0</v>
@@ -49323,16 +49323,16 @@
         <v>1</v>
       </c>
       <c r="AP152" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AQ152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR152" s="2">
         <v>2</v>
       </c>
       <c r="AS152" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT152" s="1">
         <v>0</v>
@@ -49455,16 +49455,16 @@
         <v>0</v>
       </c>
       <c r="CH152" s="1">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="CI152" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CJ152" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CK152" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="CL152" s="1">
         <v>9</v>
@@ -49491,16 +49491,16 @@
         <v>0</v>
       </c>
       <c r="CT152" s="1">
-        <v>2971</v>
+        <v>2979</v>
       </c>
       <c r="CU152" s="1">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="CV152" s="1">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="CW152" s="1">
-        <v>315</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50145,7 +50145,7 @@
         <v>553</v>
       </c>
       <c r="K155" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L155" s="2">
         <v>19</v>
@@ -50160,7 +50160,7 @@
         <v>0</v>
       </c>
       <c r="P155" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q155" s="2">
         <v>7</v>
@@ -50241,13 +50241,13 @@
         <v>32</v>
       </c>
       <c r="AQ155" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR155" s="2">
         <v>2</v>
       </c>
-      <c r="AR155" s="2">
-        <v>3</v>
-      </c>
       <c r="AS155" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT155" s="1">
         <v>1</v>
@@ -50373,19 +50373,19 @@
         <v>403</v>
       </c>
       <c r="CI155" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ155" s="2">
         <v>8</v>
       </c>
-      <c r="CJ155" s="2">
-        <v>9</v>
-      </c>
       <c r="CK155" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="CL155" s="1">
         <v>1</v>
       </c>
       <c r="CM155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN155" s="2">
         <v>1</v>
@@ -50409,13 +50409,13 @@
         <v>2626</v>
       </c>
       <c r="CU155" s="1">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="CV155" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="CW155" s="1">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50447,16 +50447,16 @@
         <v>0</v>
       </c>
       <c r="J156" s="1">
-        <v>2016</v>
+        <v>2030</v>
       </c>
       <c r="K156" s="2">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L156" s="2">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="M156" s="2">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="N156" s="1">
         <v>60190</v>
@@ -50513,10 +50513,10 @@
         <v>0</v>
       </c>
       <c r="AF156" s="2">
+        <v>-1</v>
+      </c>
+      <c r="AG156" s="2">
         <v>260</v>
-      </c>
-      <c r="AG156" s="2">
-        <v>384</v>
       </c>
       <c r="AH156" s="1">
         <v>0</v>
@@ -50543,16 +50543,16 @@
         <v>4</v>
       </c>
       <c r="AP156" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AQ156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS156" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT156" s="1">
         <v>2</v>
@@ -50675,16 +50675,16 @@
         <v>0</v>
       </c>
       <c r="CH156" s="1">
-        <v>2742</v>
+        <v>2767</v>
       </c>
       <c r="CI156" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="CJ156" s="2">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="CK156" s="2">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="CL156" s="1">
         <v>13</v>
@@ -50711,16 +50711,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>70471</v>
+        <v>70511</v>
       </c>
       <c r="CU156" s="1">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="CV156" s="1">
-        <v>1411</v>
+        <v>1190</v>
       </c>
       <c r="CW156" s="1">
-        <v>1703</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -50755,13 +50755,13 @@
         <v>3365</v>
       </c>
       <c r="K157" s="2">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L157" s="2">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="M157" s="2">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="N157" s="1">
         <v>11812</v>
@@ -50818,7 +50818,7 @@
         <v>0</v>
       </c>
       <c r="AF157" s="2">
-        <v>3513</v>
+        <v>0</v>
       </c>
       <c r="AG157" s="2">
         <v>4789</v>
@@ -50842,7 +50842,7 @@
         <v>0</v>
       </c>
       <c r="AN157" s="2">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="AO157" s="2">
         <v>-37</v>
@@ -50986,7 +50986,7 @@
         <v>35</v>
       </c>
       <c r="CJ157" s="2">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="CK157" s="2">
         <v>179</v>
@@ -51019,13 +51019,13 @@
         <v>161204</v>
       </c>
       <c r="CU157" s="1">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="CV157" s="1">
-        <v>3919</v>
+        <v>313</v>
       </c>
       <c r="CW157" s="1">
-        <v>5491</v>
+        <v>5437</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51033,16 +51033,16 @@
         <v>257</v>
       </c>
       <c r="B158" s="1">
-        <v>8101</v>
+        <v>8161</v>
       </c>
       <c r="C158" s="2">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D158" s="2">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="E158" s="2">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="F158" s="1">
         <v>2</v>
@@ -51060,13 +51060,13 @@
         <v>6942</v>
       </c>
       <c r="K158" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L158" s="2">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="M158" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="N158" s="1">
         <v>2969</v>
@@ -51075,10 +51075,10 @@
         <v>0</v>
       </c>
       <c r="P158" s="2">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="Q158" s="2">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="R158" s="1">
         <v>0</v>
@@ -51147,10 +51147,10 @@
         <v>4</v>
       </c>
       <c r="AN158" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AO158" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="AP158" s="1">
         <v>3</v>
@@ -51291,10 +51291,10 @@
         <v>82</v>
       </c>
       <c r="CJ158" s="2">
-        <v>309</v>
+        <v>173</v>
       </c>
       <c r="CK158" s="2">
-        <v>559</v>
+        <v>447</v>
       </c>
       <c r="CL158" s="1">
         <v>0</v>
@@ -51321,16 +51321,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>24872</v>
+        <v>24932</v>
       </c>
       <c r="CU158" s="1">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="CV158" s="1">
-        <v>801</v>
+        <v>534</v>
       </c>
       <c r="CW158" s="1">
-        <v>1529</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51978,22 +51978,22 @@
         <v>27</v>
       </c>
       <c r="L161" s="2">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="M161" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="N161" s="1">
-        <v>9779</v>
+        <v>10033</v>
       </c>
       <c r="O161" s="2">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="P161" s="2">
-        <v>224</v>
+        <v>478</v>
       </c>
       <c r="Q161" s="2">
-        <v>223</v>
+        <v>477</v>
       </c>
       <c r="R161" s="1">
         <v>0</v>
@@ -52038,7 +52038,7 @@
         <v>313</v>
       </c>
       <c r="AF161" s="2">
-        <v>457</v>
+        <v>313</v>
       </c>
       <c r="AG161" s="2">
         <v>457</v>
@@ -52056,16 +52056,16 @@
         <v>0</v>
       </c>
       <c r="AL161" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM161" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN161" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO161" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP161" s="1">
         <v>35</v>
@@ -52200,16 +52200,16 @@
         <v>0</v>
       </c>
       <c r="CH161" s="1">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="CI161" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ161" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="CK161" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="CL161" s="1">
         <v>14</v>
@@ -52236,16 +52236,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>22022</v>
+        <v>22289</v>
       </c>
       <c r="CU161" s="1">
-        <v>377</v>
+        <v>644</v>
       </c>
       <c r="CV161" s="1">
-        <v>853</v>
+        <v>948</v>
       </c>
       <c r="CW161" s="1">
-        <v>1027</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52567,7 +52567,7 @@
         <v>5</v>
       </c>
       <c r="E163" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F163" s="1">
         <v>30</v>
@@ -52579,7 +52579,7 @@
         <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" s="1">
         <v>110</v>
@@ -52594,16 +52594,16 @@
         <v>0</v>
       </c>
       <c r="N163" s="1">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="O163" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P163" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q163" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R163" s="1">
         <v>1</v>
@@ -52666,16 +52666,16 @@
         <v>0</v>
       </c>
       <c r="AL163" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AM163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO163" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP163" s="1">
         <v>128</v>
@@ -52810,16 +52810,16 @@
         <v>0</v>
       </c>
       <c r="CH163" s="1">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="CI163" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CJ163" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CK163" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CL163" s="1">
         <v>49</v>
@@ -52846,16 +52846,16 @@
         <v>0</v>
       </c>
       <c r="CT163" s="1">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="CU163" s="1">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="CV163" s="1">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="CW163" s="1">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -52890,7 +52890,7 @@
         <v>91</v>
       </c>
       <c r="K164" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L164" s="2">
         <v>14</v>
@@ -52905,7 +52905,7 @@
         <v>0</v>
       </c>
       <c r="P164" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q164" s="2">
         <v>22</v>
@@ -52947,16 +52947,16 @@
         <v>0</v>
       </c>
       <c r="AD164" s="1">
-        <v>436</v>
+        <v>505</v>
       </c>
       <c r="AE164" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AF164" s="2">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="AG164" s="2">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="AH164" s="1">
         <v>1</v>
@@ -52971,25 +52971,25 @@
         <v>0</v>
       </c>
       <c r="AL164" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP164" s="1">
         <v>16</v>
       </c>
       <c r="AQ164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR164" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS164" s="2">
         <v>5</v>
@@ -53115,16 +53115,16 @@
         <v>0</v>
       </c>
       <c r="CH164" s="1">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="CI164" s="2">
         <v>3</v>
       </c>
       <c r="CJ164" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CK164" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CL164" s="1">
         <v>3</v>
@@ -53151,16 +53151,16 @@
         <v>0</v>
       </c>
       <c r="CT164" s="1">
-        <v>1031</v>
+        <v>1104</v>
       </c>
       <c r="CU164" s="1">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="CV164" s="1">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="CW164" s="1">
-        <v>121</v>
+        <v>194</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53473,16 +53473,16 @@
         <v>265</v>
       </c>
       <c r="B166" s="1">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C166" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D166" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E166" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F166" s="1">
         <v>7</v>
@@ -53509,16 +53509,16 @@
         <v>130</v>
       </c>
       <c r="N166" s="1">
-        <v>2171</v>
+        <v>2195</v>
       </c>
       <c r="O166" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P166" s="2">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="Q166" s="2">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="R166" s="1">
         <v>0</v>
@@ -53593,16 +53593,16 @@
         <v>0</v>
       </c>
       <c r="AP166" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AQ166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR166" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS166" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT166" s="1">
         <v>0</v>
@@ -53725,16 +53725,16 @@
         <v>0</v>
       </c>
       <c r="CH166" s="1">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="CI166" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ166" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CK166" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CL166" s="1">
         <v>32</v>
@@ -53761,16 +53761,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>5176</v>
+        <v>5207</v>
       </c>
       <c r="CU166" s="1">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="CV166" s="1">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="CW166" s="1">
-        <v>472</v>
+        <v>503</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54173,7 +54173,7 @@
         <v>0</v>
       </c>
       <c r="AF168" s="2">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="AG168" s="2">
         <v>287</v>
@@ -54203,16 +54203,16 @@
         <v>3</v>
       </c>
       <c r="AP168" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AQ168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR168" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS168" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT168" s="1">
         <v>0</v>
@@ -54335,16 +54335,16 @@
         <v>0</v>
       </c>
       <c r="CH168" s="1">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="CI168" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CJ168" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="CK168" s="2">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="CL168" s="1">
         <v>4</v>
@@ -54371,16 +54371,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5861</v>
+        <v>5871</v>
       </c>
       <c r="CU168" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="CV168" s="1">
-        <v>402</v>
+        <v>125</v>
       </c>
       <c r="CW168" s="1">
-        <v>582</v>
+        <v>592</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54693,16 +54693,16 @@
         <v>269</v>
       </c>
       <c r="B170" s="1">
-        <v>4475</v>
+        <v>4506</v>
       </c>
       <c r="C170" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D170" s="2">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="E170" s="2">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
@@ -54726,7 +54726,7 @@
         <v>206</v>
       </c>
       <c r="M170" s="2">
-        <v>476</v>
+        <v>339</v>
       </c>
       <c r="N170" s="1">
         <v>2725</v>
@@ -54738,7 +54738,7 @@
         <v>76</v>
       </c>
       <c r="Q170" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="R170" s="1">
         <v>0</v>
@@ -54777,16 +54777,16 @@
         <v>7</v>
       </c>
       <c r="AD170" s="1">
-        <v>3476</v>
+        <v>3566</v>
       </c>
       <c r="AE170" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF170" s="2">
-        <v>287</v>
+        <v>90</v>
       </c>
       <c r="AG170" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AH170" s="1">
         <v>10</v>
@@ -54810,7 +54810,7 @@
         <v>3</v>
       </c>
       <c r="AO170" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP170" s="1">
         <v>36</v>
@@ -54894,7 +54894,7 @@
         <v>0</v>
       </c>
       <c r="BQ170" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR170" s="1">
         <v>14</v>
@@ -54954,7 +54954,7 @@
         <v>111</v>
       </c>
       <c r="CK170" s="2">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="CL170" s="1">
         <v>17</v>
@@ -54981,16 +54981,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19155</v>
+        <v>19276</v>
       </c>
       <c r="CU170" s="1">
-        <v>47</v>
+        <v>168</v>
       </c>
       <c r="CV170" s="1">
-        <v>742</v>
+        <v>576</v>
       </c>
       <c r="CW170" s="1">
-        <v>1329</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -55115,7 +55115,7 @@
         <v>5</v>
       </c>
       <c r="AO171" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP171" s="1">
         <v>6</v>
@@ -55250,16 +55250,16 @@
         <v>0</v>
       </c>
       <c r="CH171" s="1">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="CI171" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CJ171" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CK171" s="2">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="CL171" s="1">
         <v>6</v>
@@ -55286,16 +55286,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>5810</v>
+        <v>5805</v>
       </c>
       <c r="CU171" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="CV171" s="1">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="CW171" s="1">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -55931,10 +55931,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I174" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J174" s="1">
         <v>0</v>
@@ -56042,7 +56042,7 @@
         <v>1</v>
       </c>
       <c r="AS174" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT174" s="1">
         <v>0</v>
@@ -56186,7 +56186,7 @@
         <v>0</v>
       </c>
       <c r="CO174" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP174" s="1">
         <v>0</v>
@@ -56207,10 +56207,10 @@
         <v>0</v>
       </c>
       <c r="CV174" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CW174" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:101">
@@ -56631,160 +56631,160 @@
         <v>0</v>
       </c>
       <c r="AL176" s="1">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="AM176" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AN176" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AO176" s="2">
+        <v>68</v>
+      </c>
+      <c r="AP176" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ176" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR176" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS176" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT176" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU176" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV176" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW176" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX176" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY176" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB176" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF176" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ176" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN176" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR176" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV176" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY176" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ176" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA176" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB176" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC176" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD176" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE176" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF176" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG176" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH176" s="1">
+        <v>726</v>
+      </c>
+      <c r="CI176" s="2">
+        <v>29</v>
+      </c>
+      <c r="CJ176" s="2">
         <v>56</v>
       </c>
-      <c r="AP176" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ176" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR176" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS176" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT176" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU176" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV176" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW176" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX176" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY176" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB176" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF176" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ176" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN176" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR176" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV176" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY176" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ176" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA176" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB176" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC176" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD176" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE176" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF176" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG176" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH176" s="1">
-        <v>697</v>
-      </c>
-      <c r="CI176" s="2">
-        <v>19</v>
-      </c>
-      <c r="CJ176" s="2">
-        <v>30</v>
-      </c>
       <c r="CK176" s="2">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="CL176" s="1">
         <v>0</v>
@@ -56811,16 +56811,16 @@
         <v>0</v>
       </c>
       <c r="CT176" s="1">
-        <v>1244</v>
+        <v>1285</v>
       </c>
       <c r="CU176" s="1">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="CV176" s="1">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="CW176" s="1">
-        <v>153</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57133,16 +57133,16 @@
         <v>277</v>
       </c>
       <c r="B178" s="1">
-        <v>7767</v>
+        <v>7801</v>
       </c>
       <c r="C178" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D178" s="2">
         <v>85</v>
       </c>
       <c r="E178" s="2">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="F178" s="1">
         <v>0</v>
@@ -57157,16 +57157,16 @@
         <v>0</v>
       </c>
       <c r="J178" s="1">
-        <v>1769</v>
+        <v>1780</v>
       </c>
       <c r="K178" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="L178" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M178" s="2">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="N178" s="1">
         <v>71146</v>
@@ -57178,7 +57178,7 @@
         <v>2151</v>
       </c>
       <c r="Q178" s="2">
-        <v>4283</v>
+        <v>2148</v>
       </c>
       <c r="R178" s="1">
         <v>0</v>
@@ -57229,28 +57229,28 @@
         <v>0</v>
       </c>
       <c r="AH178" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK178" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL178" s="1">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AM178" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN178" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO178" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP178" s="1">
         <v>30</v>
@@ -57385,16 +57385,16 @@
         <v>0</v>
       </c>
       <c r="CH178" s="1">
-        <v>1109</v>
+        <v>1127</v>
       </c>
       <c r="CI178" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CJ178" s="2">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="CK178" s="2">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="CL178" s="1">
         <v>7</v>
@@ -57421,16 +57421,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>82756</v>
+        <v>82823</v>
       </c>
       <c r="CU178" s="1">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="CV178" s="1">
-        <v>2398</v>
+        <v>2413</v>
       </c>
       <c r="CW178" s="1">
-        <v>4695</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57546,16 +57546,16 @@
         <v>0</v>
       </c>
       <c r="AL179" s="1">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="AM179" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AN179" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AO179" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="AP179" s="1">
         <v>5</v>
@@ -57690,16 +57690,16 @@
         <v>0</v>
       </c>
       <c r="CH179" s="1">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="CI179" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CJ179" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CK179" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CL179" s="1">
         <v>11</v>
@@ -57726,16 +57726,16 @@
         <v>0</v>
       </c>
       <c r="CT179" s="1">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="CU179" s="1">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="CV179" s="1">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="CW179" s="1">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -57746,7 +57746,7 @@
         <v>7995</v>
       </c>
       <c r="C180" s="2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D180" s="2">
         <v>62</v>
@@ -57773,22 +57773,22 @@
         <v>27</v>
       </c>
       <c r="L180" s="2">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="M180" s="2">
         <v>218</v>
       </c>
       <c r="N180" s="1">
-        <v>35991</v>
+        <v>36939</v>
       </c>
       <c r="O180" s="2">
-        <v>0</v>
+        <v>948</v>
       </c>
       <c r="P180" s="2">
-        <v>1121</v>
+        <v>2069</v>
       </c>
       <c r="Q180" s="2">
-        <v>1119</v>
+        <v>2067</v>
       </c>
       <c r="R180" s="1">
         <v>0</v>
@@ -57935,28 +57935,28 @@
         <v>0</v>
       </c>
       <c r="BN180" s="1">
-        <v>952</v>
+        <v>996</v>
       </c>
       <c r="BO180" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BP180" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BQ180" s="2">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="BR180" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BS180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU180" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV180" s="1">
         <v>0</v>
@@ -58031,16 +58031,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>50044</v>
+        <v>51037</v>
       </c>
       <c r="CU180" s="1">
-        <v>88</v>
+        <v>1045</v>
       </c>
       <c r="CV180" s="1">
-        <v>1401</v>
+        <v>2350</v>
       </c>
       <c r="CW180" s="1">
-        <v>1740</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -58614,7 +58614,7 @@
         <v>25</v>
       </c>
       <c r="CK182" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="CL182" s="1">
         <v>0</v>
@@ -58650,7 +58650,7 @@
         <v>27</v>
       </c>
       <c r="CW182" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183" spans="1:101">
@@ -58856,7 +58856,7 @@
         <v>0</v>
       </c>
       <c r="BP183" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BQ183" s="2">
         <v>7</v>
@@ -58952,7 +58952,7 @@
         <v>0</v>
       </c>
       <c r="CV183" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CW183" s="1">
         <v>7</v>
@@ -59286,7 +59286,7 @@
         <v>1</v>
       </c>
       <c r="H185" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I185" s="2">
         <v>5</v>
@@ -59562,7 +59562,7 @@
         <v>2</v>
       </c>
       <c r="CV185" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CW185" s="1">
         <v>18</v>
@@ -59893,10 +59893,10 @@
         <v>71</v>
       </c>
       <c r="G187" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I187" s="2">
         <v>5</v>
@@ -60169,10 +60169,10 @@
         <v>79</v>
       </c>
       <c r="CU187" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV187" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW187" s="1">
         <v>5</v>
@@ -62040,25 +62040,25 @@
         <v>927</v>
       </c>
       <c r="K194" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L194" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="M194" s="2">
         <v>50</v>
       </c>
       <c r="N194" s="1">
-        <v>28678</v>
+        <v>29160</v>
       </c>
       <c r="O194" s="2">
-        <v>-7</v>
+        <v>482</v>
       </c>
       <c r="P194" s="2">
-        <v>729</v>
+        <v>1211</v>
       </c>
       <c r="Q194" s="2">
-        <v>750</v>
+        <v>1232</v>
       </c>
       <c r="R194" s="1">
         <v>0</v>
@@ -62217,16 +62217,16 @@
         <v>0</v>
       </c>
       <c r="BR194" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU194" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV194" s="1">
         <v>8</v>
@@ -62301,16 +62301,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32304</v>
+        <v>32787</v>
       </c>
       <c r="CU194" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="CV194" s="1">
-        <v>794</v>
+        <v>1267</v>
       </c>
       <c r="CW194" s="1">
-        <v>891</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62363,7 +62363,7 @@
         <v>35</v>
       </c>
       <c r="Q195" s="2">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="R195" s="1">
         <v>9</v>
@@ -62408,10 +62408,10 @@
         <v>3325</v>
       </c>
       <c r="AF195" s="2">
+        <v>3325</v>
+      </c>
+      <c r="AG195" s="2">
         <v>5225</v>
-      </c>
-      <c r="AG195" s="2">
-        <v>6148</v>
       </c>
       <c r="AH195" s="1">
         <v>0</v>
@@ -62570,16 +62570,16 @@
         <v>0</v>
       </c>
       <c r="CH195" s="1">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="CI195" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CJ195" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CK195" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="CL195" s="1">
         <v>9</v>
@@ -62606,16 +62606,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>71156</v>
+        <v>71163</v>
       </c>
       <c r="CU195" s="1">
-        <v>3332</v>
+        <v>3339</v>
       </c>
       <c r="CV195" s="1">
-        <v>5289</v>
+        <v>3388</v>
       </c>
       <c r="CW195" s="1">
-        <v>6249</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -62737,7 +62737,7 @@
         <v>0</v>
       </c>
       <c r="AN196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO196" s="2">
         <v>2</v>
@@ -62752,7 +62752,7 @@
         <v>2</v>
       </c>
       <c r="AS196" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT196" s="1">
         <v>0</v>
@@ -62881,10 +62881,10 @@
         <v>2</v>
       </c>
       <c r="CJ196" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CK196" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="CL196" s="1">
         <v>3</v>
@@ -62917,10 +62917,10 @@
         <v>59</v>
       </c>
       <c r="CV196" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="CW196" s="1">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -63849,7 +63849,7 @@
         <v>43</v>
       </c>
       <c r="D200" s="2">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="E200" s="2">
         <v>144</v>
@@ -63870,25 +63870,25 @@
         <v>2013</v>
       </c>
       <c r="K200" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L200" s="2">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="M200" s="2">
         <v>88</v>
       </c>
       <c r="N200" s="1">
-        <v>7967</v>
+        <v>7999</v>
       </c>
       <c r="O200" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P200" s="2">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="Q200" s="2">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="R200" s="1">
         <v>0</v>
@@ -64131,16 +64131,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16156</v>
+        <v>16188</v>
       </c>
       <c r="CU200" s="1">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="CV200" s="1">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="CW200" s="1">
-        <v>439</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64178,10 +64178,10 @@
         <v>41</v>
       </c>
       <c r="L201" s="2">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="M201" s="2">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="N201" s="1">
         <v>23044</v>
@@ -64232,16 +64232,16 @@
         <v>6</v>
       </c>
       <c r="AD201" s="1">
-        <v>46598</v>
+        <v>48204</v>
       </c>
       <c r="AE201" s="2">
-        <v>0</v>
+        <v>1606</v>
       </c>
       <c r="AF201" s="2">
-        <v>477</v>
+        <v>1648</v>
       </c>
       <c r="AG201" s="2">
-        <v>846</v>
+        <v>2046</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64256,16 +64256,16 @@
         <v>0</v>
       </c>
       <c r="AL201" s="1">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM201" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN201" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO201" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP201" s="1">
         <v>25</v>
@@ -64274,7 +64274,7 @@
         <v>0</v>
       </c>
       <c r="AR201" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS201" s="2">
         <v>4</v>
@@ -64400,16 +64400,16 @@
         <v>0</v>
       </c>
       <c r="CH201" s="1">
-        <v>3552</v>
+        <v>3569</v>
       </c>
       <c r="CI201" s="2">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="CJ201" s="2">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="CK201" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="CL201" s="1">
         <v>5</v>
@@ -64436,16 +64436,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>86142</v>
+        <v>87766</v>
       </c>
       <c r="CU201" s="1">
-        <v>59</v>
+        <v>1683</v>
       </c>
       <c r="CV201" s="1">
-        <v>1195</v>
+        <v>2322</v>
       </c>
       <c r="CW201" s="1">
-        <v>1803</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64567,10 +64567,10 @@
         <v>25</v>
       </c>
       <c r="AN202" s="2">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="AO202" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AP202" s="1">
         <v>0</v>
@@ -64711,10 +64711,10 @@
         <v>15</v>
       </c>
       <c r="CJ202" s="2">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="CK202" s="2">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="CL202" s="1">
         <v>0</v>
@@ -64747,10 +64747,10 @@
         <v>41</v>
       </c>
       <c r="CV202" s="1">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="CW202" s="1">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="203" spans="1:101">
@@ -65790,7 +65790,7 @@
         <v>5</v>
       </c>
       <c r="AO206" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP206" s="1">
         <v>78</v>
@@ -65970,7 +65970,7 @@
         <v>40</v>
       </c>
       <c r="CW206" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -65984,10 +65984,10 @@
         <v>8</v>
       </c>
       <c r="D207" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E207" s="2">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F207" s="1">
         <v>1</v>
@@ -66008,22 +66008,22 @@
         <v>15</v>
       </c>
       <c r="L207" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M207" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N207" s="1">
-        <v>5043</v>
+        <v>5091</v>
       </c>
       <c r="O207" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="P207" s="2">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="Q207" s="2">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="R207" s="1">
         <v>0</v>
@@ -66062,16 +66062,16 @@
         <v>6</v>
       </c>
       <c r="AD207" s="1">
-        <v>2163</v>
+        <v>2320</v>
       </c>
       <c r="AE207" s="2">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="AF207" s="2">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="AG207" s="2">
-        <v>139</v>
+        <v>296</v>
       </c>
       <c r="AH207" s="1">
         <v>0</v>
@@ -66098,7 +66098,7 @@
         <v>0</v>
       </c>
       <c r="AP207" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AQ207" s="2">
         <v>1</v>
@@ -66107,7 +66107,7 @@
         <v>3</v>
       </c>
       <c r="AS207" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT207" s="1">
         <v>0</v>
@@ -66182,16 +66182,16 @@
         <v>0</v>
       </c>
       <c r="BR207" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS207" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT207" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU207" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV207" s="1">
         <v>0</v>
@@ -66230,22 +66230,22 @@
         <v>0</v>
       </c>
       <c r="CH207" s="1">
-        <v>3179</v>
+        <v>3185</v>
       </c>
       <c r="CI207" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CJ207" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="CK207" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="CL207" s="1">
         <v>13</v>
       </c>
       <c r="CM207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN207" s="2">
         <v>1</v>
@@ -66266,16 +66266,16 @@
         <v>0</v>
       </c>
       <c r="CT207" s="1">
-        <v>13779</v>
+        <v>13992</v>
       </c>
       <c r="CU207" s="1">
-        <v>73</v>
+        <v>274</v>
       </c>
       <c r="CV207" s="1">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="CW207" s="1">
-        <v>414</v>
+        <v>611</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -66696,196 +66696,196 @@
         <v>0</v>
       </c>
       <c r="AL209" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM209" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN209" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO209" s="2">
+        <v>15</v>
+      </c>
+      <c r="AP209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH209" s="1">
+        <v>221</v>
+      </c>
+      <c r="CI209" s="2">
+        <v>15</v>
+      </c>
+      <c r="CJ209" s="2">
+        <v>33</v>
+      </c>
+      <c r="CK209" s="2">
+        <v>88</v>
+      </c>
+      <c r="CL209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT209" s="1">
+        <v>686</v>
+      </c>
+      <c r="CU209" s="1">
         <v>16</v>
       </c>
-      <c r="AP209" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT209" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX209" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH209" s="1">
-        <v>206</v>
-      </c>
-      <c r="CI209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ209" s="2">
-        <v>18</v>
-      </c>
-      <c r="CK209" s="2">
-        <v>187</v>
-      </c>
-      <c r="CL209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT209" s="1">
-        <v>670</v>
-      </c>
-      <c r="CU209" s="1">
-        <v>0</v>
-      </c>
       <c r="CV209" s="1">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="CW209" s="1">
-        <v>203</v>
+        <v>103</v>
       </c>
     </row>
     <row r="210" spans="1:101">
@@ -67198,16 +67198,16 @@
         <v>310</v>
       </c>
       <c r="B211" s="1">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C211" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D211" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E211" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F211" s="1">
         <v>15</v>
@@ -67222,16 +67222,16 @@
         <v>1</v>
       </c>
       <c r="J211" s="1">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="K211" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L211" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M211" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="N211" s="1">
         <v>801</v>
@@ -67282,16 +67282,16 @@
         <v>0</v>
       </c>
       <c r="AD211" s="1">
-        <v>2578</v>
+        <v>2960</v>
       </c>
       <c r="AE211" s="2">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="AF211" s="2">
-        <v>59</v>
+        <v>382</v>
       </c>
       <c r="AG211" s="2">
-        <v>41</v>
+        <v>423</v>
       </c>
       <c r="AH211" s="1">
         <v>3</v>
@@ -67486,16 +67486,16 @@
         <v>0</v>
       </c>
       <c r="CT211" s="1">
-        <v>5808</v>
+        <v>6204</v>
       </c>
       <c r="CU211" s="1">
-        <v>22</v>
+        <v>417</v>
       </c>
       <c r="CV211" s="1">
-        <v>174</v>
+        <v>507</v>
       </c>
       <c r="CW211" s="1">
-        <v>242</v>
+        <v>638</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -67925,7 +67925,7 @@
         <v>5</v>
       </c>
       <c r="AO213" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP213" s="1">
         <v>3</v>
@@ -68105,7 +68105,7 @@
         <v>20</v>
       </c>
       <c r="CW213" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="214" spans="1:101">
@@ -69943,7 +69943,7 @@
         <v>595</v>
       </c>
       <c r="D76">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E76" t="s">
         <v>717</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>4</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="CV2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW2" s="1">
         <v>5</v>
@@ -3755,7 +3755,7 @@
         <v>1513</v>
       </c>
       <c r="C3" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2">
         <v>15</v>
@@ -3776,16 +3776,16 @@
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>4220</v>
+        <v>4242</v>
       </c>
       <c r="K3" s="2">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="L3" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="M3" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="N3" s="1">
         <v>19611</v>
@@ -3794,7 +3794,7 @@
         <v>302</v>
       </c>
       <c r="P3" s="2">
-        <v>856</v>
+        <v>302</v>
       </c>
       <c r="Q3" s="2">
         <v>856</v>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="X3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="2">
         <v>1</v>
@@ -3839,7 +3839,7 @@
         <v>18287</v>
       </c>
       <c r="AE3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="2">
         <v>294</v>
@@ -3872,16 +3872,16 @@
         <v>0</v>
       </c>
       <c r="AP3" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AQ3" s="2">
         <v>1</v>
       </c>
       <c r="AR3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS3" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" s="1">
         <v>0</v>
@@ -4004,16 +4004,16 @@
         <v>0</v>
       </c>
       <c r="CH3" s="1">
-        <v>2035</v>
+        <v>2060</v>
       </c>
       <c r="CI3" s="2">
         <v>25</v>
       </c>
       <c r="CJ3" s="2">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="CK3" s="2">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="CL3" s="1">
         <v>3</v>
@@ -4040,16 +4040,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46632</v>
+        <v>46680</v>
       </c>
       <c r="CU3" s="1">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="CV3" s="1">
-        <v>1407</v>
+        <v>863</v>
       </c>
       <c r="CW3" s="1">
-        <v>2015</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4087,7 +4087,7 @@
         <v>64</v>
       </c>
       <c r="L4" s="2">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="M4" s="2">
         <v>355</v>
@@ -4351,7 +4351,7 @@
         <v>225</v>
       </c>
       <c r="CV4" s="1">
-        <v>461</v>
+        <v>372</v>
       </c>
       <c r="CW4" s="1">
         <v>1205</v>
@@ -4362,40 +4362,40 @@
         <v>104</v>
       </c>
       <c r="B5" s="1">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1">
         <v>19</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="1">
-        <v>1163</v>
+        <v>1185</v>
       </c>
       <c r="K5" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L5" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M5" s="2">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="N5" s="1">
         <v>2965</v>
@@ -4650,16 +4650,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38655</v>
+        <v>38681</v>
       </c>
       <c r="CU5" s="1">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="CV5" s="1">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="CW5" s="1">
-        <v>807</v>
+        <v>833</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AP9" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AQ9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR9" s="2">
         <v>3</v>
       </c>
       <c r="AS9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -5834,16 +5834,16 @@
         <v>0</v>
       </c>
       <c r="CH9" s="1">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="CI9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CJ9" s="2">
         <v>4</v>
       </c>
       <c r="CK9" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CL9" s="1">
         <v>8</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2857</v>
+        <v>2859</v>
       </c>
       <c r="CU9" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CV9" s="1">
         <v>51</v>
       </c>
       <c r="CW9" s="1">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7137,7 +7137,7 @@
         <v>9</v>
       </c>
       <c r="L14" s="2">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="M14" s="2">
         <v>103</v>
@@ -7194,7 +7194,7 @@
         <v>2022</v>
       </c>
       <c r="AE14" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AF14" s="2">
         <v>4</v>
@@ -7398,10 +7398,10 @@
         <v>3096</v>
       </c>
       <c r="CU14" s="1">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="CV14" s="1">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="CW14" s="1">
         <v>277</v>
@@ -7843,7 +7843,7 @@
         <v>2</v>
       </c>
       <c r="AR16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS16" s="2">
         <v>5</v>
@@ -7975,7 +7975,7 @@
         <v>1</v>
       </c>
       <c r="CJ16" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CK16" s="2">
         <v>5</v>
@@ -8011,7 +8011,7 @@
         <v>4</v>
       </c>
       <c r="CV16" s="1">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="CW16" s="1">
         <v>98</v>
@@ -8136,7 +8136,7 @@
         <v>1</v>
       </c>
       <c r="AN17" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO17" s="2">
         <v>19</v>
@@ -8292,7 +8292,7 @@
         <v>0</v>
       </c>
       <c r="CN17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO17" s="2">
         <v>1</v>
@@ -8316,7 +8316,7 @@
         <v>10</v>
       </c>
       <c r="CV17" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CW17" s="1">
         <v>51</v>
@@ -8943,7 +8943,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="2">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2">
         <v>161</v>
@@ -8961,16 +8961,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="K20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="M20" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N20" s="1">
         <v>12650</v>
@@ -8979,7 +8979,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="2">
-        <v>586</v>
+        <v>270</v>
       </c>
       <c r="Q20" s="2">
         <v>606</v>
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="2">
         <v>1</v>
@@ -9192,10 +9192,10 @@
         <v>1057</v>
       </c>
       <c r="CI20" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CJ20" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="CK20" s="2">
         <v>100</v>
@@ -9225,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20637</v>
+        <v>20636</v>
       </c>
       <c r="CU20" s="1">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="CV20" s="1">
-        <v>752</v>
+        <v>385</v>
       </c>
       <c r="CW20" s="1">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9978,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="AR23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS23" s="2">
         <v>5</v>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="CJ23" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK23" s="2">
         <v>5</v>
@@ -10146,7 +10146,7 @@
         <v>3</v>
       </c>
       <c r="CV23" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="CW23" s="1">
         <v>45</v>
@@ -10773,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2">
         <v>10</v>
@@ -11061,7 +11061,7 @@
         <v>0</v>
       </c>
       <c r="CV26" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CW26" s="1">
         <v>11</v>
@@ -11186,7 +11186,7 @@
         <v>9</v>
       </c>
       <c r="AN27" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO27" s="2">
         <v>13</v>
@@ -11330,7 +11330,7 @@
         <v>9</v>
       </c>
       <c r="CJ27" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="CK27" s="2">
         <v>37</v>
@@ -11366,7 +11366,7 @@
         <v>19</v>
       </c>
       <c r="CV27" s="1">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="CW27" s="1">
         <v>62</v>
@@ -11389,28 +11389,28 @@
         <v>8</v>
       </c>
       <c r="F28" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="1">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="K28" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="L28" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M28" s="2">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="N28" s="1">
         <v>2024</v>
@@ -11497,16 +11497,16 @@
         <v>1</v>
       </c>
       <c r="AP28" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AQ28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR28" s="2">
         <v>3</v>
       </c>
       <c r="AS28" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT28" s="1">
         <v>0</v>
@@ -11629,16 +11629,16 @@
         <v>0</v>
       </c>
       <c r="CH28" s="1">
-        <v>3009</v>
+        <v>3012</v>
       </c>
       <c r="CI28" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CJ28" s="2">
         <v>20</v>
       </c>
       <c r="CK28" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="CL28" s="1">
         <v>20</v>
@@ -11665,16 +11665,16 @@
         <v>0</v>
       </c>
       <c r="CT28" s="1">
-        <v>24058</v>
+        <v>24074</v>
       </c>
       <c r="CU28" s="1">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="CV28" s="1">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="CW28" s="1">
-        <v>765</v>
+        <v>781</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -11700,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
         <v>5</v>
@@ -11976,7 +11976,7 @@
         <v>0</v>
       </c>
       <c r="CV29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW29" s="1">
         <v>5</v>
@@ -12005,7 +12005,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
         <v>5</v>
@@ -12281,7 +12281,7 @@
         <v>0</v>
       </c>
       <c r="CV30" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW30" s="1">
         <v>5</v>
@@ -12331,7 +12331,7 @@
         <v>1982</v>
       </c>
       <c r="O31" s="2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P31" s="2">
         <v>27</v>
@@ -12550,7 +12550,7 @@
         <v>128</v>
       </c>
       <c r="CJ31" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="CK31" s="2">
         <v>181</v>
@@ -12583,10 +12583,10 @@
         <v>5975</v>
       </c>
       <c r="CU31" s="1">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="CV31" s="1">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="CW31" s="1">
         <v>428</v>
@@ -12636,10 +12636,10 @@
         <v>6579</v>
       </c>
       <c r="O32" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="2">
-        <v>319</v>
+        <v>99</v>
       </c>
       <c r="Q32" s="2">
         <v>319</v>
@@ -12663,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="2">
         <v>1</v>
@@ -12723,7 +12723,7 @@
         <v>0</v>
       </c>
       <c r="AR32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS32" s="2">
         <v>2</v>
@@ -12741,16 +12741,16 @@
         <v>0</v>
       </c>
       <c r="AX32" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA32" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB32" s="1">
         <v>3</v>
@@ -12855,7 +12855,7 @@
         <v>4</v>
       </c>
       <c r="CJ32" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK32" s="2">
         <v>14</v>
@@ -12885,16 +12885,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>11088</v>
+        <v>11089</v>
       </c>
       <c r="CU32" s="1">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="CV32" s="1">
-        <v>423</v>
+        <v>201</v>
       </c>
       <c r="CW32" s="1">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13231,16 +13231,16 @@
         <v>6</v>
       </c>
       <c r="J34" s="1">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="K34" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L34" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M34" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="N34" s="1">
         <v>1429</v>
@@ -13495,16 +13495,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2568</v>
+        <v>2576</v>
       </c>
       <c r="CU34" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="CV34" s="1">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="CW34" s="1">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -13518,7 +13518,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -13530,7 +13530,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="2">
         <v>4</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="CV35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW35" s="1">
         <v>5</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I37" s="2">
         <v>5</v>
@@ -14416,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="CV37" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW37" s="1">
         <v>5</v>
@@ -15040,10 +15040,10 @@
         <v>8771</v>
       </c>
       <c r="C40" s="2">
-        <v>22</v>
+        <v>-42</v>
       </c>
       <c r="D40" s="2">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2">
         <v>306</v>
@@ -15067,7 +15067,7 @@
         <v>34</v>
       </c>
       <c r="L40" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="M40" s="2">
         <v>217</v>
@@ -15151,7 +15151,7 @@
         <v>0</v>
       </c>
       <c r="AN40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO40" s="2">
         <v>6</v>
@@ -15295,7 +15295,7 @@
         <v>17</v>
       </c>
       <c r="CJ40" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="CK40" s="2">
         <v>69</v>
@@ -15328,10 +15328,10 @@
         <v>53375</v>
       </c>
       <c r="CU40" s="1">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="CV40" s="1">
-        <v>884</v>
+        <v>773</v>
       </c>
       <c r="CW40" s="1">
         <v>2142</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="2">
         <v>1</v>
@@ -15665,7 +15665,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
         <v>4</v>
@@ -15941,7 +15941,7 @@
         <v>0</v>
       </c>
       <c r="CV42" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW42" s="1">
         <v>5</v>
@@ -16072,16 +16072,16 @@
         <v>0</v>
       </c>
       <c r="AP43" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AQ43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR43" s="2">
         <v>3</v>
       </c>
       <c r="AS43" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -16216,16 +16216,16 @@
         <v>0</v>
       </c>
       <c r="CL43" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CM43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN43" s="2">
         <v>3</v>
       </c>
       <c r="CO43" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CP43" s="1">
         <v>0</v>
@@ -16240,16 +16240,16 @@
         <v>0</v>
       </c>
       <c r="CT43" s="1">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CU43" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CV43" s="1">
         <v>26</v>
       </c>
       <c r="CW43" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:101">
@@ -16257,16 +16257,16 @@
         <v>143</v>
       </c>
       <c r="B44" s="1">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C44" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1">
         <v>13</v>
@@ -16371,7 +16371,7 @@
         <v>1</v>
       </c>
       <c r="AN44" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO44" s="2">
         <v>6</v>
@@ -16545,16 +16545,16 @@
         <v>0</v>
       </c>
       <c r="CT44" s="1">
-        <v>50620</v>
+        <v>50625</v>
       </c>
       <c r="CU44" s="1">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="CV44" s="1">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="CW44" s="1">
-        <v>2445</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -16580,7 +16580,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I45" s="2">
         <v>5</v>
@@ -16856,7 +16856,7 @@
         <v>0</v>
       </c>
       <c r="CV45" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW45" s="1">
         <v>5</v>
@@ -18506,7 +18506,7 @@
         <v>0</v>
       </c>
       <c r="AN51" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO51" s="2">
         <v>1</v>
@@ -18650,7 +18650,7 @@
         <v>38</v>
       </c>
       <c r="CJ51" s="2">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="CK51" s="2">
         <v>173</v>
@@ -18686,7 +18686,7 @@
         <v>44</v>
       </c>
       <c r="CV51" s="1">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="CW51" s="1">
         <v>202</v>
@@ -18811,7 +18811,7 @@
         <v>1</v>
       </c>
       <c r="AN52" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO52" s="2">
         <v>17</v>
@@ -18955,7 +18955,7 @@
         <v>1</v>
       </c>
       <c r="CJ52" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CK52" s="2">
         <v>23</v>
@@ -18991,7 +18991,7 @@
         <v>2</v>
       </c>
       <c r="CV52" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CW52" s="1">
         <v>44</v>
@@ -19110,16 +19110,16 @@
         <v>0</v>
       </c>
       <c r="AL53" s="1">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="AM53" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN53" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AO53" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AP53" s="1">
         <v>1</v>
@@ -19254,52 +19254,52 @@
         <v>1</v>
       </c>
       <c r="CH53" s="1">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="CI53" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CJ53" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CK53" s="2">
+        <v>26</v>
+      </c>
+      <c r="CL53" s="1">
+        <v>1</v>
+      </c>
+      <c r="CM53" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN53" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO53" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP53" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ53" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR53" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS53" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT53" s="1">
+        <v>353</v>
+      </c>
+      <c r="CU53" s="1">
         <v>17</v>
       </c>
-      <c r="CL53" s="1">
-        <v>1</v>
-      </c>
-      <c r="CM53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP53" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT53" s="1">
-        <v>338</v>
-      </c>
-      <c r="CU53" s="1">
-        <v>2</v>
-      </c>
       <c r="CV53" s="1">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="CW53" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:101">
@@ -19917,16 +19917,16 @@
         <v>155</v>
       </c>
       <c r="B56" s="1">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="C56" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D56" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E56" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -19941,22 +19941,22 @@
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="K56" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L56" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M56" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N56" s="1">
         <v>2310</v>
       </c>
       <c r="O56" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="P56" s="2">
         <v>35</v>
@@ -20004,7 +20004,7 @@
         <v>1111</v>
       </c>
       <c r="AE56" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AF56" s="2">
         <v>21</v>
@@ -20175,7 +20175,7 @@
         <v>0</v>
       </c>
       <c r="CJ56" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CK56" s="2">
         <v>39</v>
@@ -20205,16 +20205,16 @@
         <v>0</v>
       </c>
       <c r="CT56" s="1">
-        <v>7770</v>
+        <v>7784</v>
       </c>
       <c r="CU56" s="1">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="CV56" s="1">
         <v>106</v>
       </c>
       <c r="CW56" s="1">
-        <v>350</v>
+        <v>364</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -20844,16 +20844,16 @@
         <v>7</v>
       </c>
       <c r="F59" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J59" s="1">
         <v>29</v>
@@ -21120,16 +21120,16 @@
         <v>0</v>
       </c>
       <c r="CT59" s="1">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="CU59" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CV59" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CW59" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -21472,7 +21472,7 @@
         <v>6</v>
       </c>
       <c r="L61" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M61" s="2">
         <v>48</v>
@@ -21508,7 +21508,7 @@
         <v>0</v>
       </c>
       <c r="X61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="2">
         <v>1</v>
@@ -21553,25 +21553,25 @@
         <v>1069</v>
       </c>
       <c r="AM61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN61" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO61" s="2">
         <v>5</v>
       </c>
       <c r="AP61" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AQ61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT61" s="1">
         <v>0</v>
@@ -21694,16 +21694,16 @@
         <v>0</v>
       </c>
       <c r="CH61" s="1">
-        <v>5318</v>
+        <v>5332</v>
       </c>
       <c r="CI61" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="CJ61" s="2">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="CK61" s="2">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="CL61" s="1">
         <v>7</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65902</v>
+        <v>65917</v>
       </c>
       <c r="CU61" s="1">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="CV61" s="1">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="CW61" s="1">
-        <v>967</v>
+        <v>982</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22118,7 +22118,7 @@
         <v>0</v>
       </c>
       <c r="X63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y63" s="2">
         <v>1</v>
@@ -22346,7 +22346,7 @@
         <v>33</v>
       </c>
       <c r="CV63" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="CW63" s="1">
         <v>178</v>
@@ -22375,7 +22375,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="2">
         <v>2</v>
@@ -22387,7 +22387,7 @@
         <v>4</v>
       </c>
       <c r="L64" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M64" s="2">
         <v>15</v>
@@ -22615,7 +22615,7 @@
         <v>6</v>
       </c>
       <c r="CJ64" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="CK64" s="2">
         <v>30</v>
@@ -22651,7 +22651,7 @@
         <v>19</v>
       </c>
       <c r="CV64" s="1">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="CW64" s="1">
         <v>407</v>
@@ -22692,22 +22692,22 @@
         <v>21</v>
       </c>
       <c r="L65" s="2">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="M65" s="2">
         <v>100</v>
       </c>
       <c r="N65" s="1">
-        <v>58959</v>
+        <v>58956</v>
       </c>
       <c r="O65" s="2">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="P65" s="2">
-        <v>3210</v>
+        <v>1631</v>
       </c>
       <c r="Q65" s="2">
-        <v>3209</v>
+        <v>3206</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>111</v>
       </c>
       <c r="AA65" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB65" s="2">
         <v>4</v>
@@ -22770,16 +22770,16 @@
         <v>0</v>
       </c>
       <c r="AL65" s="1">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AM65" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN65" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO65" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP65" s="1">
         <v>60</v>
@@ -22914,16 +22914,16 @@
         <v>0</v>
       </c>
       <c r="CH65" s="1">
-        <v>1871</v>
+        <v>1878</v>
       </c>
       <c r="CI65" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CJ65" s="2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="CK65" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="CL65" s="1">
         <v>34</v>
@@ -22950,16 +22950,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67151</v>
+        <v>67159</v>
       </c>
       <c r="CU65" s="1">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="CV65" s="1">
-        <v>3341</v>
+        <v>1752</v>
       </c>
       <c r="CW65" s="1">
-        <v>3525</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -22973,7 +22973,7 @@
         <v>5</v>
       </c>
       <c r="D66" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E66" s="2">
         <v>27</v>
@@ -22997,7 +22997,7 @@
         <v>26</v>
       </c>
       <c r="L66" s="2">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="M66" s="2">
         <v>107</v>
@@ -23261,7 +23261,7 @@
         <v>31</v>
       </c>
       <c r="CV66" s="1">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="CW66" s="1">
         <v>134</v>
@@ -23583,7 +23583,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="2">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="E68" s="2">
         <v>-25</v>
@@ -23619,7 +23619,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="2">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="Q68" s="2">
         <v>41</v>
@@ -23643,7 +23643,7 @@
         <v>0</v>
       </c>
       <c r="X68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="2">
         <v>1</v>
@@ -23703,7 +23703,7 @@
         <v>0</v>
       </c>
       <c r="AR68" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS68" s="2">
         <v>6</v>
@@ -23835,7 +23835,7 @@
         <v>0</v>
       </c>
       <c r="CJ68" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CK68" s="2">
         <v>20</v>
@@ -23871,7 +23871,7 @@
         <v>1</v>
       </c>
       <c r="CV68" s="1">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="CW68" s="1">
         <v>54</v>
@@ -24214,7 +24214,7 @@
         <v>281</v>
       </c>
       <c r="K70" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L70" s="2">
         <v>21</v>
@@ -24226,7 +24226,7 @@
         <v>1259</v>
       </c>
       <c r="O70" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P70" s="2">
         <v>30</v>
@@ -24313,7 +24313,7 @@
         <v>0</v>
       </c>
       <c r="AR70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS70" s="2">
         <v>5</v>
@@ -24445,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="CJ70" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CK70" s="2">
         <v>6</v>
@@ -24478,10 +24478,10 @@
         <v>2255</v>
       </c>
       <c r="CU70" s="1">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="CV70" s="1">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="CW70" s="1">
         <v>78</v>
@@ -24923,7 +24923,7 @@
         <v>1</v>
       </c>
       <c r="AR72" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS72" s="2">
         <v>6</v>
@@ -25055,7 +25055,7 @@
         <v>4</v>
       </c>
       <c r="CJ72" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CK72" s="2">
         <v>17</v>
@@ -25091,7 +25091,7 @@
         <v>7</v>
       </c>
       <c r="CV72" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="CW72" s="1">
         <v>157</v>
@@ -25108,7 +25108,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E73" s="2">
         <v>6</v>
@@ -25216,7 +25216,7 @@
         <v>1</v>
       </c>
       <c r="AN73" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO73" s="2">
         <v>6</v>
@@ -25360,7 +25360,7 @@
         <v>18</v>
       </c>
       <c r="CJ73" s="2">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CK73" s="2">
         <v>61</v>
@@ -25396,7 +25396,7 @@
         <v>19</v>
       </c>
       <c r="CV73" s="1">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="CW73" s="1">
         <v>75</v>
@@ -25431,16 +25431,16 @@
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>10075</v>
+        <v>10112</v>
       </c>
       <c r="K74" s="2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L74" s="2">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="M74" s="2">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="N74" s="1">
         <v>79173</v>
@@ -25521,7 +25521,7 @@
         <v>40</v>
       </c>
       <c r="AN74" s="2">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="AO74" s="2">
         <v>356</v>
@@ -25563,16 +25563,16 @@
         <v>1</v>
       </c>
       <c r="BB74" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BC74" s="2">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BD74" s="2">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BE74" s="2">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BF74" s="1">
         <v>314</v>
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16138</v>
+        <v>16141</v>
       </c>
       <c r="CI74" s="2">
         <v>81</v>
       </c>
       <c r="CJ74" s="2">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="CK74" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171468</v>
+        <v>171504</v>
       </c>
       <c r="CU74" s="1">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="CV74" s="1">
-        <v>1919</v>
+        <v>1870</v>
       </c>
       <c r="CW74" s="1">
-        <v>4263</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26083,7 +26083,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="2">
         <v>1</v>
@@ -26143,7 +26143,7 @@
         <v>0</v>
       </c>
       <c r="AR76" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS76" s="2">
         <v>5</v>
@@ -26155,7 +26155,7 @@
         <v>0</v>
       </c>
       <c r="AV76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW76" s="2">
         <v>4</v>
@@ -26167,7 +26167,7 @@
         <v>0</v>
       </c>
       <c r="AZ76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA76" s="2">
         <v>3</v>
@@ -26275,7 +26275,7 @@
         <v>0</v>
       </c>
       <c r="CJ76" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CK76" s="2">
         <v>78</v>
@@ -26311,7 +26311,7 @@
         <v>963</v>
       </c>
       <c r="CV76" s="1">
-        <v>1247</v>
+        <v>1229</v>
       </c>
       <c r="CW76" s="1">
         <v>3666</v>
@@ -26328,7 +26328,7 @@
         <v>13</v>
       </c>
       <c r="D77" s="2">
-        <v>13</v>
+        <v>-102</v>
       </c>
       <c r="E77" s="2">
         <v>-4313</v>
@@ -26346,16 +26346,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4835</v>
+        <v>4880</v>
       </c>
       <c r="K77" s="2">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="L77" s="2">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="M77" s="2">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26364,7 +26364,7 @@
         <v>9556</v>
       </c>
       <c r="P77" s="2">
-        <v>19105</v>
+        <v>9555</v>
       </c>
       <c r="Q77" s="2">
         <v>19092</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390711</v>
+        <v>390756</v>
       </c>
       <c r="CU77" s="1">
-        <v>9860</v>
+        <v>9905</v>
       </c>
       <c r="CV77" s="1">
-        <v>19661</v>
+        <v>10042</v>
       </c>
       <c r="CW77" s="1">
-        <v>15964</v>
+        <v>16009</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26639,16 +26639,16 @@
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I78" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -26738,7 +26738,7 @@
         <v>87</v>
       </c>
       <c r="AM78" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AN78" s="2">
         <v>21</v>
@@ -26879,16 +26879,16 @@
         <v>0</v>
       </c>
       <c r="CH78" s="1">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="CI78" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ78" s="2">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="CK78" s="2">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="CL78" s="1">
         <v>0</v>
@@ -26915,16 +26915,16 @@
         <v>0</v>
       </c>
       <c r="CT78" s="1">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="CU78" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CV78" s="1">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="CW78" s="1">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -26938,7 +26938,7 @@
         <v>13</v>
       </c>
       <c r="D79" s="2">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E79" s="2">
         <v>78</v>
@@ -26959,7 +26959,7 @@
         <v>4497</v>
       </c>
       <c r="K79" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2">
         <v>94</v>
@@ -26974,7 +26974,7 @@
         <v>391</v>
       </c>
       <c r="P79" s="2">
-        <v>1139</v>
+        <v>497</v>
       </c>
       <c r="Q79" s="2">
         <v>1139</v>
@@ -26998,7 +26998,7 @@
         <v>0</v>
       </c>
       <c r="X79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="2">
         <v>1</v>
@@ -27058,22 +27058,22 @@
         <v>0</v>
       </c>
       <c r="AR79" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS79" s="2">
         <v>2</v>
       </c>
       <c r="AT79" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW79" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX79" s="1">
         <v>0</v>
@@ -27190,7 +27190,7 @@
         <v>12</v>
       </c>
       <c r="CJ79" s="2">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="CK79" s="2">
         <v>115</v>
@@ -27220,16 +27220,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90545</v>
+        <v>90546</v>
       </c>
       <c r="CU79" s="1">
-        <v>477</v>
+        <v>436</v>
       </c>
       <c r="CV79" s="1">
-        <v>1378</v>
+        <v>691</v>
       </c>
       <c r="CW79" s="1">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27345,16 +27345,16 @@
         <v>0</v>
       </c>
       <c r="AL80" s="1">
-        <v>772</v>
+        <v>794</v>
       </c>
       <c r="AM80" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AN80" s="2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO80" s="2">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="AP80" s="1">
         <v>0</v>
@@ -27489,16 +27489,16 @@
         <v>1</v>
       </c>
       <c r="CH80" s="1">
-        <v>786</v>
+        <v>809</v>
       </c>
       <c r="CI80" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="CJ80" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="CK80" s="2">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="CL80" s="1">
         <v>0</v>
@@ -27525,16 +27525,16 @@
         <v>0</v>
       </c>
       <c r="CT80" s="1">
-        <v>1713</v>
+        <v>1758</v>
       </c>
       <c r="CU80" s="1">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="CV80" s="1">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="CW80" s="1">
-        <v>204</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -27566,16 +27566,16 @@
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>1551</v>
+        <v>1578</v>
       </c>
       <c r="K81" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L81" s="2">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="M81" s="2">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="N81" s="1">
         <v>3606</v>
@@ -27650,16 +27650,16 @@
         <v>0</v>
       </c>
       <c r="AL81" s="1">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AM81" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN81" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO81" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP81" s="1">
         <v>58</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="CH81" s="1">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="CI81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ81" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CK81" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CL81" s="1">
         <v>30</v>
@@ -27830,16 +27830,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6373</v>
+        <v>6405</v>
       </c>
       <c r="CU81" s="1">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="CV81" s="1">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="CW81" s="1">
-        <v>353</v>
+        <v>385</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -27898,7 +27898,7 @@
         <v>10</v>
       </c>
       <c r="S82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" s="2">
         <v>1</v>
@@ -28138,7 +28138,7 @@
         <v>319</v>
       </c>
       <c r="CU82" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV82" s="1">
         <v>10</v>
@@ -28176,16 +28176,16 @@
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>8577</v>
+        <v>8638</v>
       </c>
       <c r="K83" s="2">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L83" s="2">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="M83" s="2">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="N83" s="1">
         <v>40131</v>
@@ -28239,7 +28239,7 @@
         <v>352902</v>
       </c>
       <c r="AE83" s="2">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="AF83" s="2">
         <v>176</v>
@@ -28440,16 +28440,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423681</v>
+        <v>423742</v>
       </c>
       <c r="CU83" s="1">
-        <v>523</v>
+        <v>408</v>
       </c>
       <c r="CV83" s="1">
-        <v>856</v>
+        <v>917</v>
       </c>
       <c r="CW83" s="1">
-        <v>5348</v>
+        <v>5409</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28774,16 +28774,16 @@
         <v>1</v>
       </c>
       <c r="F85" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G85" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="2">
         <v>3</v>
       </c>
       <c r="I85" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J85" s="1">
         <v>0</v>
@@ -29050,16 +29050,16 @@
         <v>0</v>
       </c>
       <c r="CT85" s="1">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="CU85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV85" s="1">
         <v>30</v>
       </c>
       <c r="CW85" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -29486,7 +29486,7 @@
         <v>-1</v>
       </c>
       <c r="AN87" s="2">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AO87" s="2">
         <v>6</v>
@@ -29630,7 +29630,7 @@
         <v>11</v>
       </c>
       <c r="CJ87" s="2">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="CK87" s="2">
         <v>83</v>
@@ -29666,7 +29666,7 @@
         <v>11</v>
       </c>
       <c r="CV87" s="1">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="CW87" s="1">
         <v>93</v>
@@ -29695,7 +29695,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" s="2">
         <v>3</v>
@@ -29707,7 +29707,7 @@
         <v>8</v>
       </c>
       <c r="L88" s="2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="M88" s="2">
         <v>70</v>
@@ -29971,7 +29971,7 @@
         <v>102</v>
       </c>
       <c r="CV88" s="1">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="CW88" s="1">
         <v>424</v>
@@ -30598,7 +30598,7 @@
         <v>37</v>
       </c>
       <c r="D91" s="2">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="E91" s="2">
         <v>254</v>
@@ -30622,7 +30622,7 @@
         <v>62</v>
       </c>
       <c r="L91" s="2">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="M91" s="2">
         <v>325</v>
@@ -30634,7 +30634,7 @@
         <v>22</v>
       </c>
       <c r="P91" s="2">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="Q91" s="2">
         <v>66</v>
@@ -30706,7 +30706,7 @@
         <v>3</v>
       </c>
       <c r="AN91" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO91" s="2">
         <v>9</v>
@@ -30850,7 +30850,7 @@
         <v>43</v>
       </c>
       <c r="CJ91" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="CK91" s="2">
         <v>185</v>
@@ -30886,7 +30886,7 @@
         <v>167</v>
       </c>
       <c r="CV91" s="1">
-        <v>514</v>
+        <v>366</v>
       </c>
       <c r="CW91" s="1">
         <v>853</v>
@@ -30897,16 +30897,16 @@
         <v>191</v>
       </c>
       <c r="B92" s="1">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C92" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92" s="2">
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F92" s="1">
         <v>13</v>
@@ -30927,7 +30927,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M92" s="2">
         <v>12</v>
@@ -30939,7 +30939,7 @@
         <v>15</v>
       </c>
       <c r="P92" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="Q92" s="2">
         <v>40</v>
@@ -30963,7 +30963,7 @@
         <v>0</v>
       </c>
       <c r="X92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="2">
         <v>1</v>
@@ -31011,7 +31011,7 @@
         <v>4</v>
       </c>
       <c r="AN92" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO92" s="2">
         <v>8</v>
@@ -31155,7 +31155,7 @@
         <v>1</v>
       </c>
       <c r="CJ92" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CK92" s="2">
         <v>12</v>
@@ -31185,16 +31185,16 @@
         <v>0</v>
       </c>
       <c r="CT92" s="1">
-        <v>3786</v>
+        <v>3788</v>
       </c>
       <c r="CU92" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CV92" s="1">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="CW92" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -31244,7 +31244,7 @@
         <v>15</v>
       </c>
       <c r="P93" s="2">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="Q93" s="2">
         <v>44</v>
@@ -31328,7 +31328,7 @@
         <v>0</v>
       </c>
       <c r="AR93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS93" s="2">
         <v>2</v>
@@ -31472,7 +31472,7 @@
         <v>1</v>
       </c>
       <c r="CN93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO93" s="2">
         <v>2</v>
@@ -31496,7 +31496,7 @@
         <v>24</v>
       </c>
       <c r="CV93" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="CW93" s="1">
         <v>67</v>
@@ -33953,7 +33953,7 @@
         <v>125</v>
       </c>
       <c r="D102" s="2">
-        <v>484</v>
+        <v>372</v>
       </c>
       <c r="E102" s="2">
         <v>806</v>
@@ -33977,7 +33977,7 @@
         <v>0</v>
       </c>
       <c r="L102" s="2">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="M102" s="2">
         <v>153</v>
@@ -33989,7 +33989,7 @@
         <v>200</v>
       </c>
       <c r="P102" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q102" s="2">
         <v>539</v>
@@ -34070,7 +34070,7 @@
         <v>36</v>
       </c>
       <c r="AQ102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR102" s="2">
         <v>2</v>
@@ -34202,7 +34202,7 @@
         <v>1800</v>
       </c>
       <c r="CI102" s="2">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="CJ102" s="2">
         <v>54</v>
@@ -34238,10 +34238,10 @@
         <v>42989</v>
       </c>
       <c r="CU102" s="1">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="CV102" s="1">
-        <v>1217</v>
+        <v>1074</v>
       </c>
       <c r="CW102" s="1">
         <v>1785</v>
@@ -35167,16 +35167,16 @@
         <v>205</v>
       </c>
       <c r="B106" s="1">
-        <v>9323</v>
+        <v>9396</v>
       </c>
       <c r="C106" s="2">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="D106" s="2">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="E106" s="2">
-        <v>342</v>
+        <v>415</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -35197,7 +35197,7 @@
         <v>91</v>
       </c>
       <c r="L106" s="2">
-        <v>474</v>
+        <v>269</v>
       </c>
       <c r="M106" s="2">
         <v>856</v>
@@ -35275,16 +35275,16 @@
         <v>0</v>
       </c>
       <c r="AL106" s="1">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="AM106" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AN106" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO106" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AP106" s="1">
         <v>8</v>
@@ -35419,16 +35419,16 @@
         <v>0</v>
       </c>
       <c r="CH106" s="1">
-        <v>6392</v>
+        <v>6442</v>
       </c>
       <c r="CI106" s="2">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="CJ106" s="2">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="CK106" s="2">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="CL106" s="1">
         <v>0</v>
@@ -35455,16 +35455,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92296</v>
+        <v>92424</v>
       </c>
       <c r="CU106" s="1">
-        <v>522</v>
+        <v>650</v>
       </c>
       <c r="CV106" s="1">
-        <v>1116</v>
+        <v>972</v>
       </c>
       <c r="CW106" s="1">
-        <v>2204</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -35819,7 +35819,7 @@
         <v>8</v>
       </c>
       <c r="P108" s="2">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="Q108" s="2">
         <v>25</v>
@@ -36071,7 +36071,7 @@
         <v>9</v>
       </c>
       <c r="CV108" s="1">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="CW108" s="1">
         <v>49</v>
@@ -36417,7 +36417,7 @@
         <v>70</v>
       </c>
       <c r="L110" s="2">
-        <v>211</v>
+        <v>121</v>
       </c>
       <c r="M110" s="2">
         <v>328</v>
@@ -36447,16 +36447,16 @@
         <v>0</v>
       </c>
       <c r="V110" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z110" s="1">
         <v>132</v>
@@ -36501,7 +36501,7 @@
         <v>0</v>
       </c>
       <c r="AN110" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO110" s="2">
         <v>3</v>
@@ -36645,7 +36645,7 @@
         <v>23</v>
       </c>
       <c r="CJ110" s="2">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="CK110" s="2">
         <v>133</v>
@@ -36675,16 +36675,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13208</v>
+        <v>13209</v>
       </c>
       <c r="CU110" s="1">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="CV110" s="1">
-        <v>424</v>
+        <v>317</v>
       </c>
       <c r="CW110" s="1">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36803,7 +36803,7 @@
         <v>119</v>
       </c>
       <c r="AM111" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN111" s="2">
         <v>9</v>
@@ -36812,16 +36812,16 @@
         <v>14</v>
       </c>
       <c r="AP111" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AQ111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS111" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT111" s="1">
         <v>0</v>
@@ -36944,16 +36944,16 @@
         <v>0</v>
       </c>
       <c r="CH111" s="1">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="CI111" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CJ111" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="CK111" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="CL111" s="1">
         <v>27</v>
@@ -36980,16 +36980,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="CU111" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="CV111" s="1">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="CW111" s="1">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37003,7 +37003,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E112" s="2">
         <v>50</v>
@@ -37039,7 +37039,7 @@
         <v>192</v>
       </c>
       <c r="P112" s="2">
-        <v>484</v>
+        <v>192</v>
       </c>
       <c r="Q112" s="2">
         <v>484</v>
@@ -37123,7 +37123,7 @@
         <v>2</v>
       </c>
       <c r="AR112" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS112" s="2">
         <v>6</v>
@@ -37255,7 +37255,7 @@
         <v>9</v>
       </c>
       <c r="CJ112" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CK112" s="2">
         <v>20</v>
@@ -37291,7 +37291,7 @@
         <v>218</v>
       </c>
       <c r="CV112" s="1">
-        <v>566</v>
+        <v>263</v>
       </c>
       <c r="CW112" s="1">
         <v>643</v>
@@ -37560,7 +37560,7 @@
         <v>19</v>
       </c>
       <c r="CJ113" s="2">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="CK113" s="2">
         <v>112</v>
@@ -37596,7 +37596,7 @@
         <v>322</v>
       </c>
       <c r="CV113" s="1">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="CW113" s="1">
         <v>9955</v>
@@ -38217,16 +38217,16 @@
         <v>215</v>
       </c>
       <c r="B116" s="1">
-        <v>4400</v>
+        <v>4421</v>
       </c>
       <c r="C116" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D116" s="2">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E116" s="2">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -38241,22 +38241,22 @@
         <v>0</v>
       </c>
       <c r="J116" s="1">
-        <v>4854</v>
+        <v>4904</v>
       </c>
       <c r="K116" s="2">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="L116" s="2">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="M116" s="2">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="N116" s="1">
         <v>4537</v>
       </c>
       <c r="O116" s="2">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="P116" s="2">
         <v>106</v>
@@ -38337,16 +38337,16 @@
         <v>17</v>
       </c>
       <c r="AP116" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR116" s="2">
         <v>1</v>
       </c>
       <c r="AS116" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT116" s="1">
         <v>61</v>
@@ -38355,7 +38355,7 @@
         <v>1</v>
       </c>
       <c r="AV116" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW116" s="2">
         <v>8</v>
@@ -38472,10 +38472,10 @@
         <v>1189</v>
       </c>
       <c r="CI116" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CJ116" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="CK116" s="2">
         <v>56</v>
@@ -38487,7 +38487,7 @@
         <v>0</v>
       </c>
       <c r="CN116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO116" s="2">
         <v>1</v>
@@ -38505,16 +38505,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21658</v>
+        <v>21730</v>
       </c>
       <c r="CU116" s="1">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="CV116" s="1">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="CW116" s="1">
-        <v>1071</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38528,7 +38528,7 @@
         <v>165</v>
       </c>
       <c r="D117" s="2">
-        <v>719</v>
+        <v>545</v>
       </c>
       <c r="E117" s="2">
         <v>1039</v>
@@ -38648,7 +38648,7 @@
         <v>0</v>
       </c>
       <c r="AR117" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS117" s="2">
         <v>4</v>
@@ -38780,7 +38780,7 @@
         <v>4</v>
       </c>
       <c r="CJ117" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CK117" s="2">
         <v>13</v>
@@ -38816,7 +38816,7 @@
         <v>171</v>
       </c>
       <c r="CV117" s="1">
-        <v>765</v>
+        <v>588</v>
       </c>
       <c r="CW117" s="1">
         <v>1216</v>
@@ -39339,7 +39339,7 @@
         <v>19</v>
       </c>
       <c r="BS119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT119" s="2">
         <v>1</v>
@@ -39423,7 +39423,7 @@
         <v>842</v>
       </c>
       <c r="CU119" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV119" s="1">
         <v>18</v>
@@ -40418,7 +40418,7 @@
         <v>0</v>
       </c>
       <c r="X123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y123" s="2">
         <v>1</v>
@@ -40646,7 +40646,7 @@
         <v>3</v>
       </c>
       <c r="CV123" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW123" s="1">
         <v>30</v>
@@ -41279,16 +41279,16 @@
         <v>0</v>
       </c>
       <c r="F126" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G126" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H126" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I126" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J126" s="1">
         <v>0</v>
@@ -41555,16 +41555,16 @@
         <v>0</v>
       </c>
       <c r="CT126" s="1">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="CU126" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV126" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CW126" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:101">
@@ -42302,16 +42302,16 @@
         <v>12</v>
       </c>
       <c r="AP129" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AQ129" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR129" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS129" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT129" s="1">
         <v>0</v>
@@ -42434,16 +42434,16 @@
         <v>0</v>
       </c>
       <c r="CH129" s="1">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="CI129" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CJ129" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="CK129" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CL129" s="1">
         <v>37</v>
@@ -42470,16 +42470,16 @@
         <v>0</v>
       </c>
       <c r="CT129" s="1">
-        <v>3558</v>
+        <v>3562</v>
       </c>
       <c r="CU129" s="1">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="CV129" s="1">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="CW129" s="1">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -42595,16 +42595,16 @@
         <v>0</v>
       </c>
       <c r="AL130" s="1">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AM130" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN130" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AO130" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AP130" s="1">
         <v>0</v>
@@ -42739,16 +42739,16 @@
         <v>0</v>
       </c>
       <c r="CH130" s="1">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="CI130" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ130" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="CK130" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="CL130" s="1">
         <v>0</v>
@@ -42775,16 +42775,16 @@
         <v>0</v>
       </c>
       <c r="CT130" s="1">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="CU130" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="CV130" s="1">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="CW130" s="1">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -43109,292 +43109,292 @@
         <v>0</v>
       </c>
       <c r="F132" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G132" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H132" s="2">
+        <v>3</v>
+      </c>
+      <c r="I132" s="2">
+        <v>6</v>
+      </c>
+      <c r="J132" s="1">
+        <v>0</v>
+      </c>
+      <c r="K132" s="2">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2">
+        <v>0</v>
+      </c>
+      <c r="N132" s="1">
+        <v>0</v>
+      </c>
+      <c r="O132" s="2">
+        <v>0</v>
+      </c>
+      <c r="P132" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="2">
+        <v>0</v>
+      </c>
+      <c r="R132" s="1">
+        <v>0</v>
+      </c>
+      <c r="S132" s="2">
+        <v>0</v>
+      </c>
+      <c r="T132" s="2">
+        <v>0</v>
+      </c>
+      <c r="U132" s="2">
+        <v>0</v>
+      </c>
+      <c r="V132" s="1">
+        <v>0</v>
+      </c>
+      <c r="W132" s="2">
+        <v>0</v>
+      </c>
+      <c r="X132" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB132" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF132" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ132" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN132" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR132" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV132" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY132" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ132" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD132" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH132" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL132" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP132" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS132" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT132" s="1">
+        <v>44</v>
+      </c>
+      <c r="CU132" s="1">
         <v>2</v>
       </c>
-      <c r="I132" s="2">
-        <v>5</v>
-      </c>
-      <c r="J132" s="1">
-        <v>0</v>
-      </c>
-      <c r="K132" s="2">
-        <v>0</v>
-      </c>
-      <c r="L132" s="2">
-        <v>0</v>
-      </c>
-      <c r="M132" s="2">
-        <v>0</v>
-      </c>
-      <c r="N132" s="1">
-        <v>0</v>
-      </c>
-      <c r="O132" s="2">
-        <v>0</v>
-      </c>
-      <c r="P132" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="2">
-        <v>0</v>
-      </c>
-      <c r="R132" s="1">
-        <v>0</v>
-      </c>
-      <c r="S132" s="2">
-        <v>0</v>
-      </c>
-      <c r="T132" s="2">
-        <v>0</v>
-      </c>
-      <c r="U132" s="2">
-        <v>0</v>
-      </c>
-      <c r="V132" s="1">
-        <v>0</v>
-      </c>
-      <c r="W132" s="2">
-        <v>0</v>
-      </c>
-      <c r="X132" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y132" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY132" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY132" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS132" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT132" s="1">
-        <v>43</v>
-      </c>
-      <c r="CU132" s="1">
-        <v>1</v>
-      </c>
       <c r="CV132" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW132" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:101">
@@ -43749,7 +43749,7 @@
         <v>1</v>
       </c>
       <c r="P134" s="2">
-        <v>1759</v>
+        <v>718</v>
       </c>
       <c r="Q134" s="2">
         <v>1759</v>
@@ -43773,7 +43773,7 @@
         <v>0</v>
       </c>
       <c r="X134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y134" s="2">
         <v>1</v>
@@ -43797,7 +43797,7 @@
         <v>1746</v>
       </c>
       <c r="AF134" s="2">
-        <v>3915</v>
+        <v>1763</v>
       </c>
       <c r="AG134" s="2">
         <v>3915</v>
@@ -43818,7 +43818,7 @@
         <v>1328</v>
       </c>
       <c r="AM134" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AN134" s="2">
         <v>6</v>
@@ -43962,7 +43962,7 @@
         <v>2741</v>
       </c>
       <c r="CI134" s="2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="CJ134" s="2">
         <v>49</v>
@@ -43998,10 +43998,10 @@
         <v>134448</v>
       </c>
       <c r="CU134" s="1">
-        <v>1789</v>
+        <v>1770</v>
       </c>
       <c r="CV134" s="1">
-        <v>5744</v>
+        <v>2550</v>
       </c>
       <c r="CW134" s="1">
         <v>5804</v>
@@ -44036,16 +44036,16 @@
         <v>0</v>
       </c>
       <c r="J135" s="1">
-        <v>6478</v>
+        <v>6539</v>
       </c>
       <c r="K135" s="2">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L135" s="2">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="M135" s="2">
-        <v>417</v>
+        <v>478</v>
       </c>
       <c r="N135" s="1">
         <v>32057</v>
@@ -44054,7 +44054,7 @@
         <v>378</v>
       </c>
       <c r="P135" s="2">
-        <v>973</v>
+        <v>375</v>
       </c>
       <c r="Q135" s="2">
         <v>971</v>
@@ -44096,16 +44096,16 @@
         <v>8</v>
       </c>
       <c r="AD135" s="1">
-        <v>11787</v>
+        <v>11788</v>
       </c>
       <c r="AE135" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AF135" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG135" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44126,7 +44126,7 @@
         <v>2</v>
       </c>
       <c r="AN135" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO135" s="2">
         <v>5</v>
@@ -44144,16 +44144,16 @@
         <v>0</v>
       </c>
       <c r="AT135" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU135" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV135" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW135" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX135" s="1">
         <v>3</v>
@@ -44264,16 +44264,16 @@
         <v>0</v>
       </c>
       <c r="CH135" s="1">
-        <v>3117</v>
+        <v>3161</v>
       </c>
       <c r="CI135" s="2">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="CJ135" s="2">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="CK135" s="2">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="CL135" s="1">
         <v>13</v>
@@ -44300,16 +44300,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62492</v>
+        <v>62600</v>
       </c>
       <c r="CU135" s="1">
-        <v>567</v>
+        <v>669</v>
       </c>
       <c r="CV135" s="1">
-        <v>1580</v>
+        <v>973</v>
       </c>
       <c r="CW135" s="1">
-        <v>2607</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44347,7 +44347,7 @@
         <v>1</v>
       </c>
       <c r="L136" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M136" s="2">
         <v>7</v>
@@ -44359,7 +44359,7 @@
         <v>19</v>
       </c>
       <c r="P136" s="2">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="Q136" s="2">
         <v>57</v>
@@ -44383,7 +44383,7 @@
         <v>0</v>
       </c>
       <c r="X136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y136" s="2">
         <v>1</v>
@@ -44611,7 +44611,7 @@
         <v>31</v>
       </c>
       <c r="CV136" s="1">
-        <v>5125</v>
+        <v>5082</v>
       </c>
       <c r="CW136" s="1">
         <v>6080</v>
@@ -44969,7 +44969,7 @@
         <v>0</v>
       </c>
       <c r="P138" s="2">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="Q138" s="2">
         <v>135</v>
@@ -44993,7 +44993,7 @@
         <v>0</v>
       </c>
       <c r="X138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y138" s="2">
         <v>1</v>
@@ -45221,7 +45221,7 @@
         <v>28</v>
       </c>
       <c r="CV138" s="1">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="CW138" s="1">
         <v>264</v>
@@ -45555,7 +45555,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I140" s="2">
         <v>4</v>
@@ -45807,7 +45807,7 @@
         <v>1</v>
       </c>
       <c r="CN140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO140" s="2">
         <v>3</v>
@@ -45831,7 +45831,7 @@
         <v>3</v>
       </c>
       <c r="CV140" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW140" s="1">
         <v>22</v>
@@ -45842,16 +45842,16 @@
         <v>240</v>
       </c>
       <c r="B141" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C141" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D141" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E141" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1">
         <v>49</v>
@@ -46130,16 +46130,16 @@
         <v>0</v>
       </c>
       <c r="CT141" s="1">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="CU141" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV141" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CW141" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46458,7 +46458,7 @@
         <v>0</v>
       </c>
       <c r="D143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" s="2">
         <v>1</v>
@@ -46578,7 +46578,7 @@
         <v>1</v>
       </c>
       <c r="AR143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS143" s="2">
         <v>5</v>
@@ -46710,7 +46710,7 @@
         <v>0</v>
       </c>
       <c r="CJ143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK143" s="2">
         <v>3</v>
@@ -46746,7 +46746,7 @@
         <v>4</v>
       </c>
       <c r="CV143" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CW143" s="1">
         <v>19</v>
@@ -46799,7 +46799,7 @@
         <v>6</v>
       </c>
       <c r="P144" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q144" s="2">
         <v>14</v>
@@ -46823,7 +46823,7 @@
         <v>0</v>
       </c>
       <c r="X144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y144" s="2">
         <v>1</v>
@@ -46835,7 +46835,7 @@
         <v>0</v>
       </c>
       <c r="AB144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC144" s="2">
         <v>1</v>
@@ -46871,7 +46871,7 @@
         <v>2</v>
       </c>
       <c r="AN144" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO144" s="2">
         <v>4</v>
@@ -47027,7 +47027,7 @@
         <v>1</v>
       </c>
       <c r="CN144" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO144" s="2">
         <v>5</v>
@@ -47051,7 +47051,7 @@
         <v>11</v>
       </c>
       <c r="CV144" s="1">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="CW144" s="1">
         <v>67</v>
@@ -47062,16 +47062,16 @@
         <v>244</v>
       </c>
       <c r="B145" s="1">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C145" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D145" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E145" s="2">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F145" s="1">
         <v>1</v>
@@ -47092,7 +47092,7 @@
         <v>5</v>
       </c>
       <c r="L145" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M145" s="2">
         <v>23</v>
@@ -47101,10 +47101,10 @@
         <v>815</v>
       </c>
       <c r="O145" s="2">
+        <v>0</v>
+      </c>
+      <c r="P145" s="2">
         <v>8</v>
-      </c>
-      <c r="P145" s="2">
-        <v>34</v>
       </c>
       <c r="Q145" s="2">
         <v>34</v>
@@ -47128,7 +47128,7 @@
         <v>0</v>
       </c>
       <c r="X145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y145" s="2">
         <v>1</v>
@@ -47182,16 +47182,16 @@
         <v>1</v>
       </c>
       <c r="AP145" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ145" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR145" s="2">
         <v>3</v>
       </c>
       <c r="AS145" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT145" s="1">
         <v>0</v>
@@ -47314,16 +47314,16 @@
         <v>0</v>
       </c>
       <c r="CH145" s="1">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="CI145" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ145" s="2">
         <v>7</v>
       </c>
       <c r="CK145" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CL145" s="1">
         <v>40</v>
@@ -47350,16 +47350,16 @@
         <v>0</v>
       </c>
       <c r="CT145" s="1">
-        <v>2464</v>
+        <v>2475</v>
       </c>
       <c r="CU145" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CV145" s="1">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="CW145" s="1">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -47690,7 +47690,7 @@
         <v>1</v>
       </c>
       <c r="H147" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I147" s="2">
         <v>6</v>
@@ -47780,16 +47780,16 @@
         <v>0</v>
       </c>
       <c r="AL147" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP147" s="1">
         <v>43</v>
@@ -47960,16 +47960,16 @@
         <v>0</v>
       </c>
       <c r="CT147" s="1">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="CU147" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV147" s="1">
         <v>14</v>
       </c>
       <c r="CW147" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -48007,7 +48007,7 @@
         <v>2</v>
       </c>
       <c r="L148" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M148" s="2">
         <v>21</v>
@@ -48019,7 +48019,7 @@
         <v>37</v>
       </c>
       <c r="P148" s="2">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="Q148" s="2">
         <v>124</v>
@@ -48091,7 +48091,7 @@
         <v>1</v>
       </c>
       <c r="AN148" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO148" s="2">
         <v>11</v>
@@ -48235,7 +48235,7 @@
         <v>8</v>
       </c>
       <c r="CJ148" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="CK148" s="2">
         <v>48</v>
@@ -48271,7 +48271,7 @@
         <v>61</v>
       </c>
       <c r="CV148" s="1">
-        <v>196</v>
+        <v>94</v>
       </c>
       <c r="CW148" s="1">
         <v>228</v>
@@ -48324,7 +48324,7 @@
         <v>14</v>
       </c>
       <c r="P149" s="2">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="Q149" s="2">
         <v>35</v>
@@ -48576,7 +48576,7 @@
         <v>20</v>
       </c>
       <c r="CV149" s="1">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="CW149" s="1">
         <v>64</v>
@@ -48707,7 +48707,7 @@
         <v>0</v>
       </c>
       <c r="AP150" s="1">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AQ150" s="2">
         <v>1</v>
@@ -48716,7 +48716,7 @@
         <v>3</v>
       </c>
       <c r="AS150" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT150" s="1">
         <v>0</v>
@@ -48839,22 +48839,22 @@
         <v>0</v>
       </c>
       <c r="CH150" s="1">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="CI150" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ150" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CK150" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CL150" s="1">
         <v>52</v>
       </c>
       <c r="CM150" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN150" s="2">
         <v>2</v>
@@ -48875,16 +48875,16 @@
         <v>0</v>
       </c>
       <c r="CT150" s="1">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="CU150" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV150" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CW150" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:101">
@@ -49003,7 +49003,7 @@
         <v>24</v>
       </c>
       <c r="AM151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN151" s="2">
         <v>2</v>
@@ -49012,16 +49012,16 @@
         <v>3</v>
       </c>
       <c r="AP151" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AQ151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR151" s="2">
         <v>2</v>
       </c>
       <c r="AS151" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT151" s="1">
         <v>0</v>
@@ -49099,7 +49099,7 @@
         <v>29</v>
       </c>
       <c r="BS151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT151" s="2">
         <v>1</v>
@@ -49144,16 +49144,16 @@
         <v>0</v>
       </c>
       <c r="CH151" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="CI151" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CJ151" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CK151" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CL151" s="1">
         <v>28</v>
@@ -49180,16 +49180,16 @@
         <v>0</v>
       </c>
       <c r="CT151" s="1">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CU151" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="CV151" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CW151" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:101">
@@ -49317,16 +49317,16 @@
         <v>1</v>
       </c>
       <c r="AP152" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AQ152" s="2">
         <v>1</v>
       </c>
       <c r="AR152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS152" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT152" s="1">
         <v>0</v>
@@ -49449,16 +49449,16 @@
         <v>0</v>
       </c>
       <c r="CH152" s="1">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CI152" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CJ152" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="CK152" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="CL152" s="1">
         <v>9</v>
@@ -49485,16 +49485,16 @@
         <v>0</v>
       </c>
       <c r="CT152" s="1">
-        <v>3005</v>
+        <v>3008</v>
       </c>
       <c r="CU152" s="1">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="CV152" s="1">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="CW152" s="1">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50136,16 +50136,16 @@
         <v>4</v>
       </c>
       <c r="J155" s="1">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="K155" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L155" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M155" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N155" s="1">
         <v>1204</v>
@@ -50178,7 +50178,7 @@
         <v>0</v>
       </c>
       <c r="X155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y155" s="2">
         <v>1</v>
@@ -50400,16 +50400,16 @@
         <v>0</v>
       </c>
       <c r="CT155" s="1">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="CU155" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="CV155" s="1">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="CW155" s="1">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50444,7 +50444,7 @@
         <v>2053</v>
       </c>
       <c r="K156" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="L156" s="2">
         <v>56</v>
@@ -50459,7 +50459,7 @@
         <v>837</v>
       </c>
       <c r="P156" s="2">
-        <v>1908</v>
+        <v>837</v>
       </c>
       <c r="Q156" s="2">
         <v>1908</v>
@@ -50483,7 +50483,7 @@
         <v>0</v>
       </c>
       <c r="X156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y156" s="2">
         <v>1</v>
@@ -50540,7 +50540,7 @@
         <v>54</v>
       </c>
       <c r="AQ156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR156" s="2">
         <v>1</v>
@@ -50672,7 +50672,7 @@
         <v>2778</v>
       </c>
       <c r="CI156" s="2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="CJ156" s="2">
         <v>53</v>
@@ -50708,10 +50708,10 @@
         <v>71477</v>
       </c>
       <c r="CU156" s="1">
-        <v>1006</v>
+        <v>966</v>
       </c>
       <c r="CV156" s="1">
-        <v>2126</v>
+        <v>1054</v>
       </c>
       <c r="CW156" s="1">
         <v>2536</v>
@@ -50722,16 +50722,16 @@
         <v>256</v>
       </c>
       <c r="B157" s="1">
-        <v>4941</v>
+        <v>4973</v>
       </c>
       <c r="C157" s="2">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D157" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="E157" s="2">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -50746,16 +50746,16 @@
         <v>0</v>
       </c>
       <c r="J157" s="1">
-        <v>3417</v>
+        <v>3472</v>
       </c>
       <c r="K157" s="2">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="L157" s="2">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="M157" s="2">
-        <v>249</v>
+        <v>304</v>
       </c>
       <c r="N157" s="1">
         <v>11983</v>
@@ -50848,7 +50848,7 @@
         <v>1</v>
       </c>
       <c r="AR157" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS157" s="2">
         <v>4</v>
@@ -50980,7 +50980,7 @@
         <v>34</v>
       </c>
       <c r="CJ157" s="2">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="CK157" s="2">
         <v>184</v>
@@ -51010,16 +51010,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>166194</v>
+        <v>166281</v>
       </c>
       <c r="CU157" s="1">
-        <v>4990</v>
+        <v>5077</v>
       </c>
       <c r="CV157" s="1">
-        <v>5301</v>
+        <v>5285</v>
       </c>
       <c r="CW157" s="1">
-        <v>9067</v>
+        <v>9154</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51030,7 +51030,7 @@
         <v>8161</v>
       </c>
       <c r="C158" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D158" s="2">
         <v>137</v>
@@ -51141,7 +51141,7 @@
         <v>4</v>
       </c>
       <c r="AN158" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AO158" s="2">
         <v>40</v>
@@ -51285,7 +51285,7 @@
         <v>110</v>
       </c>
       <c r="CJ158" s="2">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="CK158" s="2">
         <v>487</v>
@@ -51318,10 +51318,10 @@
         <v>25172</v>
       </c>
       <c r="CU158" s="1">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="CV158" s="1">
-        <v>721</v>
+        <v>625</v>
       </c>
       <c r="CW158" s="1">
         <v>1465</v>
@@ -51948,7 +51948,7 @@
         <v>15</v>
       </c>
       <c r="D161" s="2">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E161" s="2">
         <v>101</v>
@@ -51972,7 +51972,7 @@
         <v>25</v>
       </c>
       <c r="L161" s="2">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="M161" s="2">
         <v>135</v>
@@ -52053,7 +52053,7 @@
         <v>160</v>
       </c>
       <c r="AM161" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN161" s="2">
         <v>8</v>
@@ -52197,7 +52197,7 @@
         <v>810</v>
       </c>
       <c r="CI161" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="CJ161" s="2">
         <v>25</v>
@@ -52233,10 +52233,10 @@
         <v>22345</v>
       </c>
       <c r="CU161" s="1">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="CV161" s="1">
-        <v>972</v>
+        <v>934</v>
       </c>
       <c r="CW161" s="1">
         <v>1240</v>
@@ -52591,7 +52591,7 @@
         <v>254</v>
       </c>
       <c r="O163" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P163" s="2">
         <v>10</v>
@@ -52843,7 +52843,7 @@
         <v>1128</v>
       </c>
       <c r="CU163" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="CV163" s="1">
         <v>22</v>
@@ -52983,7 +52983,7 @@
         <v>1</v>
       </c>
       <c r="AR164" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS164" s="2">
         <v>5</v>
@@ -53127,7 +53127,7 @@
         <v>1</v>
       </c>
       <c r="CN164" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO164" s="2">
         <v>2</v>
@@ -53151,7 +53151,7 @@
         <v>87</v>
       </c>
       <c r="CV164" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="CW164" s="1">
         <v>200</v>
@@ -53470,7 +53470,7 @@
         <v>416</v>
       </c>
       <c r="C166" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D166" s="2">
         <v>10</v>
@@ -53587,16 +53587,16 @@
         <v>0</v>
       </c>
       <c r="AP166" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AQ166" s="2">
         <v>1</v>
       </c>
       <c r="AR166" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS166" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT166" s="1">
         <v>0</v>
@@ -53719,16 +53719,16 @@
         <v>0</v>
       </c>
       <c r="CH166" s="1">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CI166" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ166" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CK166" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CL166" s="1">
         <v>32</v>
@@ -53755,16 +53755,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>5247</v>
+        <v>5252</v>
       </c>
       <c r="CU166" s="1">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="CV166" s="1">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="CW166" s="1">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54200,7 +54200,7 @@
         <v>34</v>
       </c>
       <c r="AQ168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR168" s="2">
         <v>2</v>
@@ -54329,16 +54329,16 @@
         <v>0</v>
       </c>
       <c r="CH168" s="1">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="CI168" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CJ168" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="CK168" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="CL168" s="1">
         <v>4</v>
@@ -54365,16 +54365,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5939</v>
+        <v>5947</v>
       </c>
       <c r="CU168" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="CV168" s="1">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="CW168" s="1">
-        <v>604</v>
+        <v>612</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54717,7 +54717,7 @@
         <v>56</v>
       </c>
       <c r="L170" s="2">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="M170" s="2">
         <v>336</v>
@@ -54801,7 +54801,7 @@
         <v>2</v>
       </c>
       <c r="AN170" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO170" s="2">
         <v>8</v>
@@ -54945,7 +54945,7 @@
         <v>11</v>
       </c>
       <c r="CJ170" s="2">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="CK170" s="2">
         <v>138</v>
@@ -54981,7 +54981,7 @@
         <v>301</v>
       </c>
       <c r="CV170" s="1">
-        <v>523</v>
+        <v>438</v>
       </c>
       <c r="CW170" s="1">
         <v>1185</v>
@@ -54998,7 +54998,7 @@
         <v>3</v>
       </c>
       <c r="D171" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E171" s="2">
         <v>9</v>
@@ -55247,7 +55247,7 @@
         <v>820</v>
       </c>
       <c r="CI171" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CJ171" s="2">
         <v>1</v>
@@ -55283,10 +55283,10 @@
         <v>5829</v>
       </c>
       <c r="CU171" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="CV171" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="CW171" s="1">
         <v>93</v>
@@ -55925,7 +55925,7 @@
         <v>1</v>
       </c>
       <c r="H174" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I174" s="2">
         <v>4</v>
@@ -56033,7 +56033,7 @@
         <v>1</v>
       </c>
       <c r="AR174" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS174" s="2">
         <v>4</v>
@@ -56201,7 +56201,7 @@
         <v>6</v>
       </c>
       <c r="CV174" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW174" s="1">
         <v>22</v>
@@ -56631,7 +56631,7 @@
         <v>12</v>
       </c>
       <c r="AN176" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AO176" s="2">
         <v>62</v>
@@ -56775,7 +56775,7 @@
         <v>29</v>
       </c>
       <c r="CJ176" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="CK176" s="2">
         <v>105</v>
@@ -56811,7 +56811,7 @@
         <v>42</v>
       </c>
       <c r="CV176" s="1">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="CW176" s="1">
         <v>175</v>
@@ -57127,16 +57127,16 @@
         <v>277</v>
       </c>
       <c r="B178" s="1">
-        <v>7801</v>
+        <v>7825</v>
       </c>
       <c r="C178" s="2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D178" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E178" s="2">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F178" s="1">
         <v>0</v>
@@ -57151,16 +57151,16 @@
         <v>0</v>
       </c>
       <c r="J178" s="1">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="K178" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L178" s="2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="M178" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="N178" s="1">
         <v>73475</v>
@@ -57169,7 +57169,7 @@
         <v>2329</v>
       </c>
       <c r="P178" s="2">
-        <v>4481</v>
+        <v>2329</v>
       </c>
       <c r="Q178" s="2">
         <v>4477</v>
@@ -57193,7 +57193,7 @@
         <v>0</v>
       </c>
       <c r="X178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y178" s="2">
         <v>1</v>
@@ -57415,16 +57415,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>85152</v>
+        <v>85186</v>
       </c>
       <c r="CU178" s="1">
-        <v>2396</v>
+        <v>2385</v>
       </c>
       <c r="CV178" s="1">
-        <v>4697</v>
+        <v>2533</v>
       </c>
       <c r="CW178" s="1">
-        <v>4892</v>
+        <v>4926</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57767,7 +57767,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="2">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="M180" s="2">
         <v>189</v>
@@ -57776,10 +57776,10 @@
         <v>36939</v>
       </c>
       <c r="O180" s="2">
+        <v>0</v>
+      </c>
+      <c r="P180" s="2">
         <v>948</v>
-      </c>
-      <c r="P180" s="2">
-        <v>2069</v>
       </c>
       <c r="Q180" s="2">
         <v>2067</v>
@@ -57803,7 +57803,7 @@
         <v>0</v>
       </c>
       <c r="X180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y180" s="2">
         <v>1</v>
@@ -57932,7 +57932,7 @@
         <v>996</v>
       </c>
       <c r="BO180" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BP180" s="2">
         <v>44</v>
@@ -57944,7 +57944,7 @@
         <v>34</v>
       </c>
       <c r="BS180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT180" s="2">
         <v>1</v>
@@ -58028,10 +58028,10 @@
         <v>51108</v>
       </c>
       <c r="CU180" s="1">
-        <v>1064</v>
+        <v>71</v>
       </c>
       <c r="CV180" s="1">
-        <v>2374</v>
+        <v>1213</v>
       </c>
       <c r="CW180" s="1">
         <v>2722</v>
@@ -59274,16 +59274,16 @@
         <v>0</v>
       </c>
       <c r="F185" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G185" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H185" s="2">
         <v>3</v>
       </c>
       <c r="I185" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J185" s="1">
         <v>0</v>
@@ -59550,16 +59550,16 @@
         <v>0</v>
       </c>
       <c r="CT185" s="1">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="CU185" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV185" s="1">
         <v>9</v>
       </c>
       <c r="CW185" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -62037,7 +62037,7 @@
         <v>14</v>
       </c>
       <c r="L194" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="M194" s="2">
         <v>53</v>
@@ -62301,7 +62301,7 @@
         <v>523</v>
       </c>
       <c r="CV194" s="1">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="CW194" s="1">
         <v>1359</v>
@@ -62354,7 +62354,7 @@
         <v>15</v>
       </c>
       <c r="P195" s="2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="Q195" s="2">
         <v>50</v>
@@ -62378,7 +62378,7 @@
         <v>0</v>
       </c>
       <c r="X195" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y195" s="2">
         <v>1</v>
@@ -62606,7 +62606,7 @@
         <v>30</v>
       </c>
       <c r="CV195" s="1">
-        <v>3405</v>
+        <v>3369</v>
       </c>
       <c r="CW195" s="1">
         <v>5328</v>
@@ -62647,7 +62647,7 @@
         <v>6</v>
       </c>
       <c r="L196" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M196" s="2">
         <v>30</v>
@@ -62743,7 +62743,7 @@
         <v>0</v>
       </c>
       <c r="AR196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS196" s="2">
         <v>3</v>
@@ -62875,7 +62875,7 @@
         <v>10</v>
       </c>
       <c r="CJ196" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CK196" s="2">
         <v>27</v>
@@ -62911,7 +62911,7 @@
         <v>20</v>
       </c>
       <c r="CV196" s="1">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="CW196" s="1">
         <v>210</v>
@@ -63843,7 +63843,7 @@
         <v>56</v>
       </c>
       <c r="D200" s="2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="E200" s="2">
         <v>185</v>
@@ -63867,7 +63867,7 @@
         <v>13</v>
       </c>
       <c r="L200" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M200" s="2">
         <v>91</v>
@@ -63879,7 +63879,7 @@
         <v>32</v>
       </c>
       <c r="P200" s="2">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="Q200" s="2">
         <v>85</v>
@@ -63903,7 +63903,7 @@
         <v>0</v>
       </c>
       <c r="X200" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y200" s="2">
         <v>1</v>
@@ -64131,7 +64131,7 @@
         <v>123</v>
       </c>
       <c r="CV200" s="1">
-        <v>334</v>
+        <v>250</v>
       </c>
       <c r="CW200" s="1">
         <v>521</v>
@@ -64148,7 +64148,7 @@
         <v>-1</v>
       </c>
       <c r="D201" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E201" s="2">
         <v>62</v>
@@ -64172,7 +64172,7 @@
         <v>37</v>
       </c>
       <c r="L201" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="M201" s="2">
         <v>218</v>
@@ -64184,7 +64184,7 @@
         <v>209</v>
       </c>
       <c r="P201" s="2">
-        <v>703</v>
+        <v>211</v>
       </c>
       <c r="Q201" s="2">
         <v>705</v>
@@ -64208,7 +64208,7 @@
         <v>0</v>
       </c>
       <c r="X201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y201" s="2">
         <v>1</v>
@@ -64250,16 +64250,16 @@
         <v>0</v>
       </c>
       <c r="AL201" s="1">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM201" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN201" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO201" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP201" s="1">
         <v>25</v>
@@ -64394,16 +64394,16 @@
         <v>0</v>
       </c>
       <c r="CH201" s="1">
-        <v>3569</v>
+        <v>3590</v>
       </c>
       <c r="CI201" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CJ201" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="CK201" s="2">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="CL201" s="1">
         <v>5</v>
@@ -64430,16 +64430,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88014</v>
+        <v>88036</v>
       </c>
       <c r="CU201" s="1">
-        <v>1872</v>
+        <v>1877</v>
       </c>
       <c r="CV201" s="1">
-        <v>2487</v>
+        <v>1966</v>
       </c>
       <c r="CW201" s="1">
-        <v>3168</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64561,7 +64561,7 @@
         <v>0</v>
       </c>
       <c r="AN202" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO202" s="2">
         <v>78</v>
@@ -64705,7 +64705,7 @@
         <v>0</v>
       </c>
       <c r="CJ202" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CK202" s="2">
         <v>54</v>
@@ -64741,7 +64741,7 @@
         <v>0</v>
       </c>
       <c r="CV202" s="1">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="CW202" s="1">
         <v>126</v>
@@ -65075,7 +65075,7 @@
         <v>0</v>
       </c>
       <c r="H204" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I204" s="2">
         <v>5</v>
@@ -65351,7 +65351,7 @@
         <v>0</v>
       </c>
       <c r="CV204" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW204" s="1">
         <v>5</v>
@@ -65978,7 +65978,7 @@
         <v>5</v>
       </c>
       <c r="D207" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E207" s="2">
         <v>42</v>
@@ -66002,7 +66002,7 @@
         <v>15</v>
       </c>
       <c r="L207" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M207" s="2">
         <v>61</v>
@@ -66011,10 +66011,10 @@
         <v>5091</v>
       </c>
       <c r="O207" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="P207" s="2">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="Q207" s="2">
         <v>107</v>
@@ -66038,7 +66038,7 @@
         <v>0</v>
       </c>
       <c r="X207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y207" s="2">
         <v>1</v>
@@ -66050,7 +66050,7 @@
         <v>3</v>
       </c>
       <c r="AB207" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC207" s="2">
         <v>6</v>
@@ -66059,7 +66059,7 @@
         <v>2320</v>
       </c>
       <c r="AE207" s="2">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="AF207" s="2">
         <v>157</v>
@@ -66092,7 +66092,7 @@
         <v>0</v>
       </c>
       <c r="AP207" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AQ207" s="2">
         <v>1</v>
@@ -66101,7 +66101,7 @@
         <v>3</v>
       </c>
       <c r="AS207" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT207" s="1">
         <v>0</v>
@@ -66179,7 +66179,7 @@
         <v>17</v>
       </c>
       <c r="BS207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT207" s="2">
         <v>1</v>
@@ -66224,16 +66224,16 @@
         <v>0</v>
       </c>
       <c r="CH207" s="1">
-        <v>3185</v>
+        <v>3204</v>
       </c>
       <c r="CI207" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="CJ207" s="2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="CK207" s="2">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="CL207" s="1">
         <v>13</v>
@@ -66260,16 +66260,16 @@
         <v>0</v>
       </c>
       <c r="CT207" s="1">
-        <v>14015</v>
+        <v>14035</v>
       </c>
       <c r="CU207" s="1">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="CV207" s="1">
-        <v>399</v>
+        <v>330</v>
       </c>
       <c r="CW207" s="1">
-        <v>605</v>
+        <v>625</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -67210,7 +67210,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I211" s="2">
         <v>1</v>
@@ -67219,7 +67219,7 @@
         <v>1262</v>
       </c>
       <c r="K211" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L211" s="2">
         <v>45</v>
@@ -67450,7 +67450,7 @@
         <v>29</v>
       </c>
       <c r="CJ211" s="2">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="CK211" s="2">
         <v>116</v>
@@ -67483,10 +67483,10 @@
         <v>6267</v>
       </c>
       <c r="CU211" s="1">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="CV211" s="1">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="CW211" s="1">
         <v>702</v>
@@ -67910,16 +67910,16 @@
         <v>0</v>
       </c>
       <c r="AL213" s="1">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AM213" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN213" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO213" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AP213" s="1">
         <v>3</v>
@@ -68090,16 +68090,16 @@
         <v>0</v>
       </c>
       <c r="CT213" s="1">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="CU213" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CV213" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="CW213" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="214" spans="1:101">
@@ -68737,7 +68737,7 @@
         <v>718</v>
       </c>
       <c r="F16" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -69054,7 +69054,7 @@
         <v>559</v>
       </c>
       <c r="D32">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E32" t="s">
         <v>715</v>
@@ -69717,7 +69717,7 @@
         <v>584</v>
       </c>
       <c r="D65">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E65" t="s">
         <v>715</v>
@@ -69857,7 +69857,7 @@
         <v>591</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>726</v>
@@ -69897,7 +69897,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="E74" t="s">
         <v>715</v>
@@ -69997,7 +69997,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="E79" t="s">
         <v>715</v>
@@ -70763,7 +70763,7 @@
         <v>631</v>
       </c>
       <c r="D117">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E117" t="s">
         <v>715</v>
@@ -71126,7 +71126,7 @@
         <v>646</v>
       </c>
       <c r="D135">
-        <v>10261</v>
+        <v>10260</v>
       </c>
       <c r="E135" t="s">
         <v>715</v>
@@ -72561,7 +72561,7 @@
         <v>706</v>
       </c>
       <c r="D206">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E206" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3791,7 +3791,7 @@
         <v>19611</v>
       </c>
       <c r="O3" s="2">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="P3" s="2">
         <v>302</v>
@@ -4043,7 +4043,7 @@
         <v>46680</v>
       </c>
       <c r="CU3" s="1">
-        <v>355</v>
+        <v>53</v>
       </c>
       <c r="CV3" s="1">
         <v>863</v>
@@ -4617,7 +4617,7 @@
         <v>3184</v>
       </c>
       <c r="CI5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ5" s="2">
         <v>2</v>
@@ -4653,7 +4653,7 @@
         <v>38681</v>
       </c>
       <c r="CU5" s="1">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="CV5" s="1">
         <v>319</v>
@@ -5705,7 +5705,7 @@
         <v>43</v>
       </c>
       <c r="AQ9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR9" s="2">
         <v>3</v>
@@ -5837,7 +5837,7 @@
         <v>491</v>
       </c>
       <c r="CI9" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CJ9" s="2">
         <v>4</v>
@@ -5873,7 +5873,7 @@
         <v>2859</v>
       </c>
       <c r="CU9" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CV9" s="1">
         <v>51</v>
@@ -7451,7 +7451,7 @@
         <v>2786</v>
       </c>
       <c r="O15" s="2">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="P15" s="2">
         <v>155</v>
@@ -7703,7 +7703,7 @@
         <v>3403</v>
       </c>
       <c r="CU15" s="1">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="CV15" s="1">
         <v>167</v>
@@ -9045,16 +9045,16 @@
         <v>0</v>
       </c>
       <c r="AL20" s="1">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP20" s="1">
         <v>79</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="CH20" s="1">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="CI20" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ20" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="CK20" s="2">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="CL20" s="1">
         <v>23</v>
@@ -9225,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20636</v>
+        <v>20648</v>
       </c>
       <c r="CU20" s="1">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="CV20" s="1">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="CW20" s="1">
-        <v>960</v>
+        <v>972</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -11180,16 +11180,16 @@
         <v>0</v>
       </c>
       <c r="AL27" s="1">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AM27" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AN27" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO27" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AP27" s="1">
         <v>12</v>
@@ -11324,16 +11324,16 @@
         <v>0</v>
       </c>
       <c r="CH27" s="1">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="CI27" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CJ27" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="CK27" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="CL27" s="1">
         <v>1</v>
@@ -11360,16 +11360,16 @@
         <v>0</v>
       </c>
       <c r="CT27" s="1">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="CU27" s="1">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="CV27" s="1">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="CW27" s="1">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:101">
@@ -11404,7 +11404,7 @@
         <v>955</v>
       </c>
       <c r="K28" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L28" s="2">
         <v>38</v>
@@ -11464,7 +11464,7 @@
         <v>16634</v>
       </c>
       <c r="AE28" s="2">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="AF28" s="2">
         <v>173</v>
@@ -11500,7 +11500,7 @@
         <v>69</v>
       </c>
       <c r="AQ28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR28" s="2">
         <v>3</v>
@@ -11632,7 +11632,7 @@
         <v>3012</v>
       </c>
       <c r="CI28" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="CJ28" s="2">
         <v>20</v>
@@ -11668,7 +11668,7 @@
         <v>24074</v>
       </c>
       <c r="CU28" s="1">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="CV28" s="1">
         <v>262</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="AL32" s="1">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN32" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO32" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP32" s="1">
         <v>45</v>
@@ -12849,16 +12849,16 @@
         <v>0</v>
       </c>
       <c r="CH32" s="1">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="CI32" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CJ32" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CK32" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CL32" s="1">
         <v>25</v>
@@ -12885,16 +12885,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>11089</v>
+        <v>11092</v>
       </c>
       <c r="CU32" s="1">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="CV32" s="1">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CW32" s="1">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -12905,7 +12905,7 @@
         <v>78</v>
       </c>
       <c r="C33" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D33" s="2">
         <v>10</v>
@@ -12917,7 +12917,7 @@
         <v>37</v>
       </c>
       <c r="G33" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33" s="2">
         <v>4</v>
@@ -13193,7 +13193,7 @@
         <v>115</v>
       </c>
       <c r="CU33" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CV33" s="1">
         <v>14</v>
@@ -13318,7 +13318,7 @@
         <v>76</v>
       </c>
       <c r="AM34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" s="2">
         <v>2</v>
@@ -13462,7 +13462,7 @@
         <v>222</v>
       </c>
       <c r="CI34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CJ34" s="2">
         <v>4</v>
@@ -13498,7 +13498,7 @@
         <v>2576</v>
       </c>
       <c r="CU34" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CV34" s="1">
         <v>75</v>
@@ -15076,7 +15076,7 @@
         <v>16656</v>
       </c>
       <c r="O40" s="2">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="P40" s="2">
         <v>172</v>
@@ -15232,7 +15232,7 @@
         <v>1604</v>
       </c>
       <c r="BO40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BP40" s="2">
         <v>2</v>
@@ -15328,7 +15328,7 @@
         <v>53375</v>
       </c>
       <c r="CU40" s="1">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="CV40" s="1">
         <v>773</v>
@@ -18392,16 +18392,16 @@
         <v>150</v>
       </c>
       <c r="B51" s="1">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C51" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E51" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -18680,16 +18680,16 @@
         <v>0</v>
       </c>
       <c r="CT51" s="1">
-        <v>1787</v>
+        <v>1794</v>
       </c>
       <c r="CU51" s="1">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="CV51" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="CW51" s="1">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -20871,7 +20871,7 @@
         <v>321</v>
       </c>
       <c r="O59" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P59" s="2">
         <v>8</v>
@@ -20943,7 +20943,7 @@
         <v>64</v>
       </c>
       <c r="AM59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN59" s="2">
         <v>1</v>
@@ -21087,7 +21087,7 @@
         <v>79</v>
       </c>
       <c r="CI59" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CJ59" s="2">
         <v>9</v>
@@ -21123,7 +21123,7 @@
         <v>856</v>
       </c>
       <c r="CU59" s="1">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="CV59" s="1">
         <v>39</v>
@@ -21466,16 +21466,16 @@
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>1979</v>
+        <v>1993</v>
       </c>
       <c r="K61" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L61" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="M61" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="N61" s="1">
         <v>43316</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65917</v>
+        <v>65931</v>
       </c>
       <c r="CU61" s="1">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="CV61" s="1">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="CW61" s="1">
-        <v>982</v>
+        <v>996</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22079,7 +22079,7 @@
         <v>327</v>
       </c>
       <c r="K63" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2">
         <v>8</v>
@@ -22259,7 +22259,7 @@
         <v>18</v>
       </c>
       <c r="BS63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT63" s="2">
         <v>1</v>
@@ -22343,7 +22343,7 @@
         <v>2863</v>
       </c>
       <c r="CU63" s="1">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="CV63" s="1">
         <v>85</v>
@@ -22686,16 +22686,16 @@
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="K65" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L65" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M65" s="2">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="N65" s="1">
         <v>58956</v>
@@ -22950,16 +22950,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67159</v>
+        <v>67168</v>
       </c>
       <c r="CU65" s="1">
-        <v>1672</v>
+        <v>1660</v>
       </c>
       <c r="CV65" s="1">
-        <v>1752</v>
+        <v>1761</v>
       </c>
       <c r="CW65" s="1">
-        <v>3533</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23577,16 +23577,16 @@
         <v>167</v>
       </c>
       <c r="B68" s="1">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" s="2">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="E68" s="2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="F68" s="1">
         <v>20</v>
@@ -23601,16 +23601,16 @@
         <v>1</v>
       </c>
       <c r="J68" s="1">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N68" s="1">
         <v>1092</v>
@@ -23865,16 +23865,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="CU68" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV68" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CW68" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -24307,16 +24307,16 @@
         <v>0</v>
       </c>
       <c r="AP70" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AQ70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS70" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -24439,16 +24439,16 @@
         <v>0</v>
       </c>
       <c r="CH70" s="1">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CI70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CK70" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CL70" s="1">
         <v>44</v>
@@ -24475,16 +24475,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="CU70" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CV70" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="CW70" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24953,16 +24953,16 @@
         <v>0</v>
       </c>
       <c r="BB72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF72" s="1">
         <v>0</v>
@@ -25085,16 +25085,16 @@
         <v>0</v>
       </c>
       <c r="CT72" s="1">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="CU72" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV72" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CW72" s="1">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25102,16 +25102,16 @@
         <v>172</v>
       </c>
       <c r="B73" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C73" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D73" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1">
         <v>45</v>
@@ -25210,16 +25210,16 @@
         <v>0</v>
       </c>
       <c r="AL73" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AM73" s="2">
         <v>1</v>
       </c>
       <c r="AN73" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO73" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP73" s="1">
         <v>13</v>
@@ -25354,16 +25354,16 @@
         <v>0</v>
       </c>
       <c r="CH73" s="1">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="CI73" s="2">
         <v>18</v>
       </c>
       <c r="CJ73" s="2">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="CK73" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="CL73" s="1">
         <v>6</v>
@@ -25390,16 +25390,16 @@
         <v>0</v>
       </c>
       <c r="CT73" s="1">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="CU73" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CV73" s="1">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="CW73" s="1">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25515,16 +25515,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36223</v>
+        <v>36229</v>
       </c>
       <c r="AM74" s="2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="AN74" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AO74" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16141</v>
+        <v>16143</v>
       </c>
       <c r="CI74" s="2">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="CJ74" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="CK74" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171504</v>
+        <v>171512</v>
       </c>
       <c r="CU74" s="1">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="CV74" s="1">
-        <v>1870</v>
+        <v>1878</v>
       </c>
       <c r="CW74" s="1">
-        <v>4299</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26053,16 +26053,16 @@
         <v>324</v>
       </c>
       <c r="N76" s="1">
-        <v>117531</v>
+        <v>117541</v>
       </c>
       <c r="O76" s="2">
-        <v>892</v>
+        <v>902</v>
       </c>
       <c r="P76" s="2">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="Q76" s="2">
-        <v>2416</v>
+        <v>2426</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26092,7 +26092,7 @@
         <v>103</v>
       </c>
       <c r="AA76" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB76" s="2">
         <v>4</v>
@@ -26305,16 +26305,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>150909</v>
+        <v>150919</v>
       </c>
       <c r="CU76" s="1">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="CV76" s="1">
-        <v>1229</v>
+        <v>1239</v>
       </c>
       <c r="CW76" s="1">
-        <v>3666</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26349,7 +26349,7 @@
         <v>4880</v>
       </c>
       <c r="K77" s="2">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="L77" s="2">
         <v>179</v>
@@ -26433,7 +26433,7 @@
         <v>1906</v>
       </c>
       <c r="AM77" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AN77" s="2">
         <v>47</v>
@@ -26556,7 +26556,7 @@
         <v>0</v>
       </c>
       <c r="CB77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CC77" s="2">
         <v>2</v>
@@ -26577,7 +26577,7 @@
         <v>7202</v>
       </c>
       <c r="CI77" s="2">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="CJ77" s="2">
         <v>269</v>
@@ -26613,10 +26613,10 @@
         <v>390756</v>
       </c>
       <c r="CU77" s="1">
-        <v>9905</v>
+        <v>9856</v>
       </c>
       <c r="CV77" s="1">
-        <v>10042</v>
+        <v>10041</v>
       </c>
       <c r="CW77" s="1">
         <v>16009</v>
@@ -26956,16 +26956,16 @@
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>4497</v>
+        <v>4545</v>
       </c>
       <c r="K79" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L79" s="2">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="M79" s="2">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="N79" s="1">
         <v>69222</v>
@@ -27127,7 +27127,7 @@
         <v>1262</v>
       </c>
       <c r="BO79" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BP79" s="2">
         <v>15</v>
@@ -27220,16 +27220,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90546</v>
+        <v>90594</v>
       </c>
       <c r="CU79" s="1">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="CV79" s="1">
-        <v>691</v>
+        <v>739</v>
       </c>
       <c r="CW79" s="1">
-        <v>1823</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27545,7 +27545,7 @@
         <v>843</v>
       </c>
       <c r="C81" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D81" s="2">
         <v>10</v>
@@ -27833,7 +27833,7 @@
         <v>6405</v>
       </c>
       <c r="CU81" s="1">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="CV81" s="1">
         <v>303</v>
@@ -28191,7 +28191,7 @@
         <v>40131</v>
       </c>
       <c r="O83" s="2">
-        <v>269</v>
+        <v>-1</v>
       </c>
       <c r="P83" s="2">
         <v>269</v>
@@ -28260,16 +28260,16 @@
         <v>0</v>
       </c>
       <c r="AL83" s="1">
-        <v>3390</v>
+        <v>3398</v>
       </c>
       <c r="AM83" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN83" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AO83" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AP83" s="1">
         <v>0</v>
@@ -28404,16 +28404,16 @@
         <v>0</v>
       </c>
       <c r="CH83" s="1">
-        <v>13733</v>
+        <v>13773</v>
       </c>
       <c r="CI83" s="2">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="CJ83" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="CK83" s="2">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="CL83" s="1">
         <v>0</v>
@@ -28440,16 +28440,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423742</v>
+        <v>423790</v>
       </c>
       <c r="CU83" s="1">
-        <v>408</v>
+        <v>112</v>
       </c>
       <c r="CV83" s="1">
-        <v>917</v>
+        <v>965</v>
       </c>
       <c r="CW83" s="1">
-        <v>5409</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29480,16 +29480,16 @@
         <v>0</v>
       </c>
       <c r="AL87" s="1">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM87" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN87" s="2">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AO87" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP87" s="1">
         <v>24</v>
@@ -29624,16 +29624,16 @@
         <v>1</v>
       </c>
       <c r="CH87" s="1">
-        <v>2368</v>
+        <v>2392</v>
       </c>
       <c r="CI87" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="CJ87" s="2">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="CK87" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="CL87" s="1">
         <v>15</v>
@@ -29660,16 +29660,16 @@
         <v>0</v>
       </c>
       <c r="CT87" s="1">
-        <v>2949</v>
+        <v>2974</v>
       </c>
       <c r="CU87" s="1">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="CV87" s="1">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="CW87" s="1">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -29677,16 +29677,16 @@
         <v>187</v>
       </c>
       <c r="B88" s="1">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C88" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D88" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E88" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F88" s="1">
         <v>18</v>
@@ -29701,16 +29701,16 @@
         <v>3</v>
       </c>
       <c r="J88" s="1">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="K88" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L88" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="M88" s="2">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="N88" s="1">
         <v>1035</v>
@@ -29797,16 +29797,16 @@
         <v>0</v>
       </c>
       <c r="AP88" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AQ88" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR88" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS88" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT88" s="1">
         <v>0</v>
@@ -29929,16 +29929,16 @@
         <v>0</v>
       </c>
       <c r="CH88" s="1">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="CI88" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CJ88" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="CK88" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="CL88" s="1">
         <v>22</v>
@@ -29965,16 +29965,16 @@
         <v>0</v>
       </c>
       <c r="CT88" s="1">
-        <v>9562</v>
+        <v>9583</v>
       </c>
       <c r="CU88" s="1">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="CV88" s="1">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="CW88" s="1">
-        <v>424</v>
+        <v>445</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -30619,7 +30619,7 @@
         <v>5365</v>
       </c>
       <c r="K91" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2">
         <v>131</v>
@@ -30631,7 +30631,7 @@
         <v>4418</v>
       </c>
       <c r="O91" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P91" s="2">
         <v>22</v>
@@ -30700,16 +30700,16 @@
         <v>0</v>
       </c>
       <c r="AL91" s="1">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AM91" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN91" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO91" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP91" s="1">
         <v>26</v>
@@ -30844,16 +30844,16 @@
         <v>0</v>
       </c>
       <c r="CH91" s="1">
-        <v>7742</v>
+        <v>7746</v>
       </c>
       <c r="CI91" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="CJ91" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="CK91" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="CL91" s="1">
         <v>5</v>
@@ -30880,16 +30880,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25778</v>
+        <v>25783</v>
       </c>
       <c r="CU91" s="1">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="CV91" s="1">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="CW91" s="1">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -33445,16 +33445,16 @@
         <v>0</v>
       </c>
       <c r="AL100" s="1">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AM100" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN100" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO100" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AP100" s="1">
         <v>0</v>
@@ -33589,52 +33589,52 @@
         <v>0</v>
       </c>
       <c r="CH100" s="1">
+        <v>38</v>
+      </c>
+      <c r="CI100" s="2">
+        <v>4</v>
+      </c>
+      <c r="CJ100" s="2">
+        <v>10</v>
+      </c>
+      <c r="CK100" s="2">
+        <v>13</v>
+      </c>
+      <c r="CL100" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM100" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN100" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO100" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP100" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ100" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR100" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS100" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT100" s="1">
+        <v>159</v>
+      </c>
+      <c r="CU100" s="1">
+        <v>10</v>
+      </c>
+      <c r="CV100" s="1">
+        <v>24</v>
+      </c>
+      <c r="CW100" s="1">
         <v>36</v>
-      </c>
-      <c r="CI100" s="2">
-        <v>2</v>
-      </c>
-      <c r="CJ100" s="2">
-        <v>8</v>
-      </c>
-      <c r="CK100" s="2">
-        <v>11</v>
-      </c>
-      <c r="CL100" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM100" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN100" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO100" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP100" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ100" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR100" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS100" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT100" s="1">
-        <v>154</v>
-      </c>
-      <c r="CU100" s="1">
-        <v>5</v>
-      </c>
-      <c r="CV100" s="1">
-        <v>19</v>
-      </c>
-      <c r="CW100" s="1">
-        <v>31</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33971,22 +33971,22 @@
         <v>0</v>
       </c>
       <c r="J102" s="1">
-        <v>5061</v>
+        <v>5096</v>
       </c>
       <c r="K102" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L102" s="2">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="M102" s="2">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="N102" s="1">
         <v>14647</v>
       </c>
       <c r="O102" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P102" s="2">
         <v>537</v>
@@ -34235,16 +34235,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>42989</v>
+        <v>43024</v>
       </c>
       <c r="CU102" s="1">
-        <v>355</v>
+        <v>190</v>
       </c>
       <c r="CV102" s="1">
-        <v>1074</v>
+        <v>1109</v>
       </c>
       <c r="CW102" s="1">
-        <v>1785</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34889,7 +34889,7 @@
         <v>984</v>
       </c>
       <c r="K105" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2">
         <v>33</v>
@@ -34949,7 +34949,7 @@
         <v>4468</v>
       </c>
       <c r="AE105" s="2">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="AF105" s="2">
         <v>374</v>
@@ -35153,7 +35153,7 @@
         <v>7959</v>
       </c>
       <c r="CU105" s="1">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="CV105" s="1">
         <v>425</v>
@@ -35170,7 +35170,7 @@
         <v>9396</v>
       </c>
       <c r="C106" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="D106" s="2">
         <v>217</v>
@@ -35191,22 +35191,22 @@
         <v>0</v>
       </c>
       <c r="J106" s="1">
-        <v>10662</v>
+        <v>10792</v>
       </c>
       <c r="K106" s="2">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="L106" s="2">
-        <v>269</v>
+        <v>399</v>
       </c>
       <c r="M106" s="2">
-        <v>856</v>
+        <v>986</v>
       </c>
       <c r="N106" s="1">
         <v>22916</v>
       </c>
       <c r="O106" s="2">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="P106" s="2">
         <v>182</v>
@@ -35278,7 +35278,7 @@
         <v>559</v>
       </c>
       <c r="AM106" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN106" s="2">
         <v>9</v>
@@ -35422,7 +35422,7 @@
         <v>6442</v>
       </c>
       <c r="CI106" s="2">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="CJ106" s="2">
         <v>181</v>
@@ -35455,16 +35455,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92424</v>
+        <v>92554</v>
       </c>
       <c r="CU106" s="1">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="CV106" s="1">
-        <v>972</v>
+        <v>1102</v>
       </c>
       <c r="CW106" s="1">
-        <v>2332</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36411,16 +36411,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="1">
-        <v>4825</v>
+        <v>4914</v>
       </c>
       <c r="K110" s="2">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L110" s="2">
-        <v>121</v>
+        <v>210</v>
       </c>
       <c r="M110" s="2">
-        <v>328</v>
+        <v>417</v>
       </c>
       <c r="N110" s="1">
         <v>1303</v>
@@ -36474,7 +36474,7 @@
         <v>2261</v>
       </c>
       <c r="AE110" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF110" s="2">
         <v>50</v>
@@ -36495,16 +36495,16 @@
         <v>0</v>
       </c>
       <c r="AL110" s="1">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="AM110" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN110" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AO110" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AP110" s="1">
         <v>0</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="CH110" s="1">
-        <v>1856</v>
+        <v>1881</v>
       </c>
       <c r="CI110" s="2">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="CJ110" s="2">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="CK110" s="2">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="CL110" s="1">
         <v>0</v>
@@ -36675,16 +36675,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13209</v>
+        <v>13330</v>
       </c>
       <c r="CU110" s="1">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CV110" s="1">
-        <v>317</v>
+        <v>438</v>
       </c>
       <c r="CW110" s="1">
-        <v>910</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -37036,7 +37036,7 @@
         <v>5612</v>
       </c>
       <c r="O112" s="2">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="P112" s="2">
         <v>192</v>
@@ -37120,7 +37120,7 @@
         <v>73</v>
       </c>
       <c r="AQ112" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR112" s="2">
         <v>3</v>
@@ -37252,7 +37252,7 @@
         <v>262</v>
       </c>
       <c r="CI112" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CJ112" s="2">
         <v>15</v>
@@ -37288,7 +37288,7 @@
         <v>8270</v>
       </c>
       <c r="CU112" s="1">
-        <v>218</v>
+        <v>22</v>
       </c>
       <c r="CV112" s="1">
         <v>263</v>
@@ -37341,7 +37341,7 @@
         <v>8023</v>
       </c>
       <c r="O113" s="2">
-        <v>175</v>
+        <v>-2</v>
       </c>
       <c r="P113" s="2">
         <v>175</v>
@@ -37593,7 +37593,7 @@
         <v>173773</v>
       </c>
       <c r="CU113" s="1">
-        <v>322</v>
+        <v>145</v>
       </c>
       <c r="CV113" s="1">
         <v>450</v>
@@ -37619,292 +37619,292 @@
         <v>2</v>
       </c>
       <c r="F114" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I114" s="2">
+        <v>4</v>
+      </c>
+      <c r="J114" s="1">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2">
+        <v>0</v>
+      </c>
+      <c r="N114" s="1">
+        <v>0</v>
+      </c>
+      <c r="O114" s="2">
+        <v>0</v>
+      </c>
+      <c r="P114" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="2">
+        <v>0</v>
+      </c>
+      <c r="R114" s="1">
+        <v>0</v>
+      </c>
+      <c r="S114" s="2">
+        <v>0</v>
+      </c>
+      <c r="T114" s="2">
+        <v>0</v>
+      </c>
+      <c r="U114" s="2">
+        <v>0</v>
+      </c>
+      <c r="V114" s="1">
+        <v>0</v>
+      </c>
+      <c r="W114" s="2">
+        <v>0</v>
+      </c>
+      <c r="X114" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT114" s="1">
+        <v>172</v>
+      </c>
+      <c r="CU114" s="1">
+        <v>1</v>
+      </c>
+      <c r="CV114" s="1">
         <v>3</v>
       </c>
-      <c r="J114" s="1">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2">
-        <v>0</v>
-      </c>
-      <c r="N114" s="1">
-        <v>0</v>
-      </c>
-      <c r="O114" s="2">
-        <v>0</v>
-      </c>
-      <c r="P114" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="2">
-        <v>0</v>
-      </c>
-      <c r="R114" s="1">
-        <v>0</v>
-      </c>
-      <c r="S114" s="2">
-        <v>0</v>
-      </c>
-      <c r="T114" s="2">
-        <v>0</v>
-      </c>
-      <c r="U114" s="2">
-        <v>0</v>
-      </c>
-      <c r="V114" s="1">
-        <v>0</v>
-      </c>
-      <c r="W114" s="2">
-        <v>0</v>
-      </c>
-      <c r="X114" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y114" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT114" s="1">
-        <v>171</v>
-      </c>
-      <c r="CU114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CV114" s="1">
-        <v>2</v>
-      </c>
       <c r="CW114" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:101">
@@ -38244,7 +38244,7 @@
         <v>4904</v>
       </c>
       <c r="K116" s="2">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="L116" s="2">
         <v>132</v>
@@ -38304,7 +38304,7 @@
         <v>5122</v>
       </c>
       <c r="AE116" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF116" s="2">
         <v>40</v>
@@ -38328,7 +38328,7 @@
         <v>366</v>
       </c>
       <c r="AM116" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN116" s="2">
         <v>5</v>
@@ -38469,16 +38469,16 @@
         <v>0</v>
       </c>
       <c r="CH116" s="1">
-        <v>1189</v>
+        <v>1200</v>
       </c>
       <c r="CI116" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CJ116" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="CK116" s="2">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="CL116" s="1">
         <v>12</v>
@@ -38505,16 +38505,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21730</v>
+        <v>21741</v>
       </c>
       <c r="CU116" s="1">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="CV116" s="1">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="CW116" s="1">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38666,16 +38666,16 @@
         <v>0</v>
       </c>
       <c r="AX117" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY117" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ117" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA117" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB117" s="1">
         <v>9</v>
@@ -38810,16 +38810,16 @@
         <v>0</v>
       </c>
       <c r="CT117" s="1">
-        <v>13154</v>
+        <v>13155</v>
       </c>
       <c r="CU117" s="1">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CV117" s="1">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="CW117" s="1">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -42221,7 +42221,7 @@
         <v>2344</v>
       </c>
       <c r="O129" s="2">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="P129" s="2">
         <v>78</v>
@@ -42305,7 +42305,7 @@
         <v>35</v>
       </c>
       <c r="AQ129" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR129" s="2">
         <v>3</v>
@@ -42437,7 +42437,7 @@
         <v>498</v>
       </c>
       <c r="CI129" s="2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="CJ129" s="2">
         <v>22</v>
@@ -42473,7 +42473,7 @@
         <v>3562</v>
       </c>
       <c r="CU129" s="1">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="CV129" s="1">
         <v>106</v>
@@ -43112,7 +43112,7 @@
         <v>39</v>
       </c>
       <c r="G132" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H132" s="2">
         <v>3</v>
@@ -43388,7 +43388,7 @@
         <v>44</v>
       </c>
       <c r="CU132" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV132" s="1">
         <v>3</v>
@@ -43414,16 +43414,16 @@
         <v>4</v>
       </c>
       <c r="F133" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G133" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I133" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J133" s="1">
         <v>0</v>
@@ -43690,16 +43690,16 @@
         <v>0</v>
       </c>
       <c r="CT133" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="CU133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV133" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW133" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:101">
@@ -44012,16 +44012,16 @@
         <v>234</v>
       </c>
       <c r="B135" s="1">
-        <v>7625</v>
+        <v>7667</v>
       </c>
       <c r="C135" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D135" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="E135" s="2">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -44123,7 +44123,7 @@
         <v>837</v>
       </c>
       <c r="AM135" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN135" s="2">
         <v>3</v>
@@ -44267,7 +44267,7 @@
         <v>3161</v>
       </c>
       <c r="CI135" s="2">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="CJ135" s="2">
         <v>93</v>
@@ -44300,16 +44300,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62600</v>
+        <v>62642</v>
       </c>
       <c r="CU135" s="1">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="CV135" s="1">
-        <v>973</v>
+        <v>1015</v>
       </c>
       <c r="CW135" s="1">
-        <v>2715</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44572,7 +44572,7 @@
         <v>386</v>
       </c>
       <c r="CI136" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="CJ136" s="2">
         <v>13</v>
@@ -44608,7 +44608,7 @@
         <v>158869</v>
       </c>
       <c r="CU136" s="1">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="CV136" s="1">
         <v>5082</v>
@@ -45537,16 +45537,16 @@
         <v>239</v>
       </c>
       <c r="B140" s="1">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C140" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D140" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F140" s="1">
         <v>47</v>
@@ -45801,16 +45801,16 @@
         <v>3</v>
       </c>
       <c r="CL140" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CM140" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN140" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO140" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CP140" s="1">
         <v>0</v>
@@ -45825,16 +45825,16 @@
         <v>0</v>
       </c>
       <c r="CT140" s="1">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="CU140" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CV140" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CW140" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -45845,7 +45845,7 @@
         <v>82</v>
       </c>
       <c r="C141" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D141" s="2">
         <v>7</v>
@@ -46049,7 +46049,7 @@
         <v>25</v>
       </c>
       <c r="BS141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT141" s="2">
         <v>1</v>
@@ -46082,16 +46082,16 @@
         <v>0</v>
       </c>
       <c r="CD141" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CE141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH141" s="1">
         <v>14</v>
@@ -46106,40 +46106,40 @@
         <v>2</v>
       </c>
       <c r="CL141" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="CM141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO141" s="2">
+        <v>4</v>
+      </c>
+      <c r="CP141" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ141" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR141" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS141" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT141" s="1">
+        <v>583</v>
+      </c>
+      <c r="CU141" s="1">
         <v>3</v>
       </c>
-      <c r="CP141" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ141" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR141" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS141" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT141" s="1">
-        <v>581</v>
-      </c>
-      <c r="CU141" s="1">
-        <v>5</v>
-      </c>
       <c r="CV141" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CW141" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46464,16 +46464,16 @@
         <v>1</v>
       </c>
       <c r="F143" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I143" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J143" s="1">
         <v>0</v>
@@ -46560,16 +46560,16 @@
         <v>0</v>
       </c>
       <c r="AL143" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP143" s="1">
         <v>81</v>
@@ -46704,16 +46704,16 @@
         <v>0</v>
       </c>
       <c r="CH143" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CI143" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ143" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CK143" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CL143" s="1">
         <v>73</v>
@@ -46740,16 +46740,16 @@
         <v>0</v>
       </c>
       <c r="CT143" s="1">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="CU143" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CV143" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CW143" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -47149,7 +47149,7 @@
         <v>101</v>
       </c>
       <c r="AE145" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AF145" s="2">
         <v>9</v>
@@ -47353,7 +47353,7 @@
         <v>2475</v>
       </c>
       <c r="CU145" s="1">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="CV145" s="1">
         <v>53</v>
@@ -48001,16 +48001,16 @@
         <v>1</v>
       </c>
       <c r="J148" s="1">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="K148" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L148" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M148" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N148" s="1">
         <v>3253</v>
@@ -48085,16 +48085,16 @@
         <v>0</v>
       </c>
       <c r="AL148" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AM148" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN148" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO148" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP148" s="1">
         <v>29</v>
@@ -48229,16 +48229,16 @@
         <v>0</v>
       </c>
       <c r="CH148" s="1">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="CI148" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CJ148" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="CK148" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CL148" s="1">
         <v>16</v>
@@ -48265,16 +48265,16 @@
         <v>0</v>
       </c>
       <c r="CT148" s="1">
-        <v>5576</v>
+        <v>5590</v>
       </c>
       <c r="CU148" s="1">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="CV148" s="1">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="CW148" s="1">
-        <v>228</v>
+        <v>242</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -50501,16 +50501,16 @@
         <v>0</v>
       </c>
       <c r="AD156" s="1">
-        <v>3093</v>
+        <v>3095</v>
       </c>
       <c r="AE156" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AF156" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AG156" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AH156" s="1">
         <v>0</v>
@@ -50705,16 +50705,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>71477</v>
+        <v>71479</v>
       </c>
       <c r="CU156" s="1">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="CV156" s="1">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="CW156" s="1">
-        <v>2536</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -51027,16 +51027,16 @@
         <v>257</v>
       </c>
       <c r="B158" s="1">
-        <v>8161</v>
+        <v>8243</v>
       </c>
       <c r="C158" s="2">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D158" s="2">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="E158" s="2">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="F158" s="1">
         <v>2</v>
@@ -51051,16 +51051,16 @@
         <v>0</v>
       </c>
       <c r="J158" s="1">
-        <v>7013</v>
+        <v>7081</v>
       </c>
       <c r="K158" s="2">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="L158" s="2">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="M158" s="2">
-        <v>451</v>
+        <v>519</v>
       </c>
       <c r="N158" s="1">
         <v>3024</v>
@@ -51315,16 +51315,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25172</v>
+        <v>25322</v>
       </c>
       <c r="CU158" s="1">
-        <v>240</v>
+        <v>390</v>
       </c>
       <c r="CV158" s="1">
-        <v>625</v>
+        <v>775</v>
       </c>
       <c r="CW158" s="1">
-        <v>1465</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51981,7 +51981,7 @@
         <v>10033</v>
       </c>
       <c r="O161" s="2">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="P161" s="2">
         <v>478</v>
@@ -52233,7 +52233,7 @@
         <v>22345</v>
       </c>
       <c r="CU161" s="1">
-        <v>310</v>
+        <v>56</v>
       </c>
       <c r="CV161" s="1">
         <v>934</v>
@@ -52663,7 +52663,7 @@
         <v>88</v>
       </c>
       <c r="AM163" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN163" s="2">
         <v>1</v>
@@ -52807,7 +52807,7 @@
         <v>161</v>
       </c>
       <c r="CI163" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ163" s="2">
         <v>7</v>
@@ -52843,7 +52843,7 @@
         <v>1128</v>
       </c>
       <c r="CU163" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV163" s="1">
         <v>22</v>
@@ -52944,7 +52944,7 @@
         <v>505</v>
       </c>
       <c r="AE164" s="2">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="AF164" s="2">
         <v>69</v>
@@ -52968,7 +52968,7 @@
         <v>26</v>
       </c>
       <c r="AM164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN164" s="2">
         <v>1</v>
@@ -53112,7 +53112,7 @@
         <v>153</v>
       </c>
       <c r="CI164" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ164" s="2">
         <v>6</v>
@@ -53148,7 +53148,7 @@
         <v>1118</v>
       </c>
       <c r="CU164" s="1">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="CV164" s="1">
         <v>100</v>
@@ -53506,7 +53506,7 @@
         <v>2217</v>
       </c>
       <c r="O166" s="2">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="P166" s="2">
         <v>25</v>
@@ -53758,7 +53758,7 @@
         <v>5252</v>
       </c>
       <c r="CU166" s="1">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="CV166" s="1">
         <v>110</v>
@@ -54690,7 +54690,7 @@
         <v>4531</v>
       </c>
       <c r="C170" s="2">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D170" s="2">
         <v>78</v>
@@ -54774,7 +54774,7 @@
         <v>3602</v>
       </c>
       <c r="AE170" s="2">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="AF170" s="2">
         <v>126</v>
@@ -54795,16 +54795,16 @@
         <v>0</v>
       </c>
       <c r="AL170" s="1">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM170" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN170" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO170" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP170" s="1">
         <v>36</v>
@@ -54939,16 +54939,16 @@
         <v>0</v>
       </c>
       <c r="CH170" s="1">
-        <v>1435</v>
+        <v>1451</v>
       </c>
       <c r="CI170" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="CJ170" s="2">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="CK170" s="2">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="CL170" s="1">
         <v>17</v>
@@ -54975,16 +54975,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19456</v>
+        <v>19473</v>
       </c>
       <c r="CU170" s="1">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="CV170" s="1">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="CW170" s="1">
-        <v>1185</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -56625,16 +56625,16 @@
         <v>0</v>
       </c>
       <c r="AL176" s="1">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AM176" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AN176" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AO176" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="AP176" s="1">
         <v>0</v>
@@ -56769,16 +56769,16 @@
         <v>0</v>
       </c>
       <c r="CH176" s="1">
-        <v>726</v>
+        <v>748</v>
       </c>
       <c r="CI176" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="CJ176" s="2">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="CK176" s="2">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="CL176" s="1">
         <v>0</v>
@@ -56805,16 +56805,16 @@
         <v>0</v>
       </c>
       <c r="CT176" s="1">
-        <v>1286</v>
+        <v>1313</v>
       </c>
       <c r="CU176" s="1">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="CV176" s="1">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="CW176" s="1">
-        <v>175</v>
+        <v>202</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57226,7 +57226,7 @@
         <v>25</v>
       </c>
       <c r="AI178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ178" s="2">
         <v>1</v>
@@ -57235,16 +57235,16 @@
         <v>2</v>
       </c>
       <c r="AL178" s="1">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="AM178" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AN178" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AO178" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AP178" s="1">
         <v>30</v>
@@ -57379,16 +57379,16 @@
         <v>0</v>
       </c>
       <c r="CH178" s="1">
-        <v>1127</v>
+        <v>1152</v>
       </c>
       <c r="CI178" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="CJ178" s="2">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="CK178" s="2">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="CL178" s="1">
         <v>7</v>
@@ -57415,16 +57415,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>85186</v>
+        <v>85227</v>
       </c>
       <c r="CU178" s="1">
-        <v>2385</v>
+        <v>2404</v>
       </c>
       <c r="CV178" s="1">
-        <v>2533</v>
+        <v>2574</v>
       </c>
       <c r="CW178" s="1">
-        <v>4926</v>
+        <v>4967</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57543,7 +57543,7 @@
         <v>534</v>
       </c>
       <c r="AM179" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AN179" s="2">
         <v>21</v>
@@ -57687,7 +57687,7 @@
         <v>226</v>
       </c>
       <c r="CI179" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CJ179" s="2">
         <v>20</v>
@@ -57723,7 +57723,7 @@
         <v>843</v>
       </c>
       <c r="CU179" s="1">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="CV179" s="1">
         <v>44</v>
@@ -62046,7 +62046,7 @@
         <v>29177</v>
       </c>
       <c r="O194" s="2">
-        <v>499</v>
+        <v>17</v>
       </c>
       <c r="P194" s="2">
         <v>474</v>
@@ -62214,7 +62214,7 @@
         <v>17</v>
       </c>
       <c r="BS194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT194" s="2">
         <v>1</v>
@@ -62298,7 +62298,7 @@
         <v>32827</v>
       </c>
       <c r="CU194" s="1">
-        <v>523</v>
+        <v>40</v>
       </c>
       <c r="CV194" s="1">
         <v>535</v>
@@ -62567,7 +62567,7 @@
         <v>515</v>
       </c>
       <c r="CI195" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="CJ195" s="2">
         <v>18</v>
@@ -62603,7 +62603,7 @@
         <v>71186</v>
       </c>
       <c r="CU195" s="1">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="CV195" s="1">
         <v>3369</v>
@@ -62641,16 +62641,16 @@
         <v>0</v>
       </c>
       <c r="J196" s="1">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="K196" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L196" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M196" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N196" s="1">
         <v>3415</v>
@@ -62725,16 +62725,16 @@
         <v>0</v>
       </c>
       <c r="AL196" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AM196" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN196" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO196" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP196" s="1">
         <v>15</v>
@@ -62869,16 +62869,16 @@
         <v>0</v>
       </c>
       <c r="CH196" s="1">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="CI196" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CJ196" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CK196" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="CL196" s="1">
         <v>3</v>
@@ -62905,16 +62905,16 @@
         <v>0</v>
       </c>
       <c r="CT196" s="1">
-        <v>5472</v>
+        <v>5481</v>
       </c>
       <c r="CU196" s="1">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="CV196" s="1">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="CW196" s="1">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -63861,22 +63861,22 @@
         <v>0</v>
       </c>
       <c r="J200" s="1">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="K200" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L200" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M200" s="2">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="N200" s="1">
         <v>7999</v>
       </c>
       <c r="O200" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P200" s="2">
         <v>33</v>
@@ -64125,16 +64125,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16279</v>
+        <v>16289</v>
       </c>
       <c r="CU200" s="1">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="CV200" s="1">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="CW200" s="1">
-        <v>521</v>
+        <v>531</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64166,16 +64166,16 @@
         <v>0</v>
       </c>
       <c r="J201" s="1">
-        <v>3500</v>
+        <v>3540</v>
       </c>
       <c r="K201" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="L201" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="M201" s="2">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="N201" s="1">
         <v>23253</v>
@@ -64229,7 +64229,7 @@
         <v>48204</v>
       </c>
       <c r="AE201" s="2">
-        <v>1606</v>
+        <v>0</v>
       </c>
       <c r="AF201" s="2">
         <v>1606</v>
@@ -64253,7 +64253,7 @@
         <v>333</v>
       </c>
       <c r="AM201" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN201" s="2">
         <v>2</v>
@@ -64430,16 +64430,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88036</v>
+        <v>88076</v>
       </c>
       <c r="CU201" s="1">
-        <v>1877</v>
+        <v>310</v>
       </c>
       <c r="CV201" s="1">
-        <v>1966</v>
+        <v>2006</v>
       </c>
       <c r="CW201" s="1">
-        <v>3190</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -65972,16 +65972,16 @@
         <v>306</v>
       </c>
       <c r="B207" s="1">
-        <v>1363</v>
+        <v>1378</v>
       </c>
       <c r="C207" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D207" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E207" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F207" s="1">
         <v>1</v>
@@ -65996,16 +65996,16 @@
         <v>0</v>
       </c>
       <c r="J207" s="1">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="K207" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L207" s="2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M207" s="2">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N207" s="1">
         <v>5091</v>
@@ -66260,16 +66260,16 @@
         <v>0</v>
       </c>
       <c r="CT207" s="1">
-        <v>14035</v>
+        <v>14059</v>
       </c>
       <c r="CU207" s="1">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="CV207" s="1">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="CW207" s="1">
-        <v>625</v>
+        <v>649</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -66693,7 +66693,7 @@
         <v>26</v>
       </c>
       <c r="AM209" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN209" s="2">
         <v>1</v>
@@ -66837,7 +66837,7 @@
         <v>221</v>
       </c>
       <c r="CI209" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CJ209" s="2">
         <v>22</v>
@@ -66873,7 +66873,7 @@
         <v>705</v>
       </c>
       <c r="CU209" s="1">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="CV209" s="1">
         <v>42</v>
@@ -67192,16 +67192,16 @@
         <v>310</v>
       </c>
       <c r="B211" s="1">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C211" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D211" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E211" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F211" s="1">
         <v>15</v>
@@ -67279,7 +67279,7 @@
         <v>2960</v>
       </c>
       <c r="AE211" s="2">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AF211" s="2">
         <v>382</v>
@@ -67480,16 +67480,16 @@
         <v>0</v>
       </c>
       <c r="CT211" s="1">
-        <v>6267</v>
+        <v>6273</v>
       </c>
       <c r="CU211" s="1">
-        <v>447</v>
+        <v>69</v>
       </c>
       <c r="CV211" s="1">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="CW211" s="1">
-        <v>702</v>
+        <v>708</v>
       </c>
     </row>
     <row r="212" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4081,16 +4081,16 @@
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>6940</v>
+        <v>7007</v>
       </c>
       <c r="K4" s="2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L4" s="2">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="M4" s="2">
-        <v>355</v>
+        <v>422</v>
       </c>
       <c r="N4" s="1">
         <v>9299</v>
@@ -4165,16 +4165,16 @@
         <v>0</v>
       </c>
       <c r="AL4" s="1">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AM4" s="2">
         <v>2</v>
       </c>
       <c r="AN4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO4" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP4" s="1">
         <v>0</v>
@@ -4309,16 +4309,16 @@
         <v>0</v>
       </c>
       <c r="CH4" s="1">
-        <v>2143</v>
+        <v>2156</v>
       </c>
       <c r="CI4" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="CJ4" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="CK4" s="2">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="CL4" s="1">
         <v>0</v>
@@ -4345,16 +4345,16 @@
         <v>0</v>
       </c>
       <c r="CT4" s="1">
-        <v>42829</v>
+        <v>42911</v>
       </c>
       <c r="CU4" s="1">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="CV4" s="1">
-        <v>372</v>
+        <v>443</v>
       </c>
       <c r="CW4" s="1">
-        <v>1205</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -4964,7 +4964,7 @@
         <v>50</v>
       </c>
       <c r="CW6" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -6503,10 +6503,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1">
         <v>17</v>
@@ -6614,7 +6614,7 @@
         <v>72</v>
       </c>
       <c r="AO12" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="AP12" s="1">
         <v>0</v>
@@ -6758,7 +6758,7 @@
         <v>93</v>
       </c>
       <c r="CK12" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="CL12" s="1">
         <v>0</v>
@@ -6791,10 +6791,10 @@
         <v>174</v>
       </c>
       <c r="CV12" s="1">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="CW12" s="1">
-        <v>254</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -7451,7 +7451,7 @@
         <v>2786</v>
       </c>
       <c r="O15" s="2">
-        <v>52</v>
+        <v>-2</v>
       </c>
       <c r="P15" s="2">
         <v>155</v>
@@ -7664,16 +7664,16 @@
         <v>0</v>
       </c>
       <c r="CH15" s="1">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="CI15" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CJ15" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CK15" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CL15" s="1">
         <v>2</v>
@@ -7700,16 +7700,16 @@
         <v>0</v>
       </c>
       <c r="CT15" s="1">
-        <v>3403</v>
+        <v>3415</v>
       </c>
       <c r="CU15" s="1">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="CV15" s="1">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="CW15" s="1">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:101">
@@ -7747,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2">
         <v>7</v>
@@ -7840,7 +7840,7 @@
         <v>67</v>
       </c>
       <c r="AQ16" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR16" s="2">
         <v>2</v>
@@ -7972,7 +7972,7 @@
         <v>177</v>
       </c>
       <c r="CI16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ16" s="2">
         <v>1</v>
@@ -7984,7 +7984,7 @@
         <v>30</v>
       </c>
       <c r="CM16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN16" s="2">
         <v>1</v>
@@ -8008,10 +8008,10 @@
         <v>963</v>
       </c>
       <c r="CU16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV16" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CW16" s="1">
         <v>98</v>
@@ -8031,7 +8031,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1">
         <v>13</v>
@@ -8319,7 +8319,7 @@
         <v>32</v>
       </c>
       <c r="CW17" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:101">
@@ -8348,7 +8348,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -8624,7 +8624,7 @@
         <v>3</v>
       </c>
       <c r="CW18" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:101">
@@ -8937,16 +8937,16 @@
         <v>119</v>
       </c>
       <c r="B20" s="1">
-        <v>5047</v>
+        <v>5082</v>
       </c>
       <c r="C20" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -8964,7 +8964,7 @@
         <v>902</v>
       </c>
       <c r="K20" s="2">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="2">
         <v>18</v>
@@ -8979,7 +8979,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="2">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="Q20" s="2">
         <v>606</v>
@@ -9066,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="AS20" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AT20" s="1">
         <v>0</v>
@@ -9138,7 +9138,7 @@
         <v>2</v>
       </c>
       <c r="BQ20" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BR20" s="1">
         <v>13</v>
@@ -9198,7 +9198,7 @@
         <v>30</v>
       </c>
       <c r="CK20" s="2">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="CL20" s="1">
         <v>23</v>
@@ -9225,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20648</v>
+        <v>20683</v>
       </c>
       <c r="CU20" s="1">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="CV20" s="1">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="CW20" s="1">
-        <v>972</v>
+        <v>918</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9362,13 +9362,13 @@
         <v>2</v>
       </c>
       <c r="AP21" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS21" s="2">
         <v>4</v>
@@ -9494,16 +9494,16 @@
         <v>0</v>
       </c>
       <c r="CH21" s="1">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="CI21" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CJ21" s="2">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="CK21" s="2">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="CL21" s="1">
         <v>1</v>
@@ -9530,16 +9530,16 @@
         <v>0</v>
       </c>
       <c r="CT21" s="1">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="CU21" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CV21" s="1">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="CW21" s="1">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:101">
@@ -9873,7 +9873,7 @@
         <v>3</v>
       </c>
       <c r="I23" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" s="1">
         <v>3</v>
@@ -10149,7 +10149,7 @@
         <v>27</v>
       </c>
       <c r="CW23" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -11380,7 +11380,7 @@
         <v>303</v>
       </c>
       <c r="C28" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2">
         <v>4</v>
@@ -11668,7 +11668,7 @@
         <v>24074</v>
       </c>
       <c r="CU28" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CV28" s="1">
         <v>262</v>
@@ -12400,16 +12400,16 @@
         <v>0</v>
       </c>
       <c r="AL31" s="1">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AM31" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN31" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AO31" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AP31" s="1">
         <v>18</v>
@@ -12544,16 +12544,16 @@
         <v>0</v>
       </c>
       <c r="CH31" s="1">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="CI31" s="2">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="CJ31" s="2">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="CK31" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="CL31" s="1">
         <v>19</v>
@@ -12580,16 +12580,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>5975</v>
+        <v>5992</v>
       </c>
       <c r="CU31" s="1">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="CV31" s="1">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="CW31" s="1">
-        <v>428</v>
+        <v>445</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12750,7 +12750,7 @@
         <v>2</v>
       </c>
       <c r="BA32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB32" s="1">
         <v>3</v>
@@ -12894,7 +12894,7 @@
         <v>204</v>
       </c>
       <c r="CW32" s="1">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13234,7 +13234,7 @@
         <v>499</v>
       </c>
       <c r="K34" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L34" s="2">
         <v>34</v>
@@ -13498,7 +13498,7 @@
         <v>2576</v>
       </c>
       <c r="CU34" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CV34" s="1">
         <v>75</v>
@@ -13829,16 +13829,16 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2">
         <v>3</v>
       </c>
       <c r="I36" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
@@ -14105,16 +14105,16 @@
         <v>0</v>
       </c>
       <c r="CT36" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CU36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV36" s="1">
         <v>3</v>
       </c>
       <c r="CW36" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:101">
@@ -14436,7 +14436,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1">
         <v>21</v>
@@ -14547,16 +14547,16 @@
         <v>0</v>
       </c>
       <c r="AP38" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AQ38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR38" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS38" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -14622,7 +14622,7 @@
         <v>24</v>
       </c>
       <c r="BO38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP38" s="2">
         <v>1</v>
@@ -14691,16 +14691,16 @@
         <v>3</v>
       </c>
       <c r="CL38" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CM38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO38" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP38" s="1">
         <v>0</v>
@@ -14715,13 +14715,13 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="CU38" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CV38" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="CW38" s="1">
         <v>123</v>
@@ -14738,7 +14738,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
@@ -14858,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="AR39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS39" s="2">
         <v>2</v>
@@ -14990,7 +14990,7 @@
         <v>0</v>
       </c>
       <c r="CJ39" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="CK39" s="2">
         <v>52</v>
@@ -15026,7 +15026,7 @@
         <v>0</v>
       </c>
       <c r="CV39" s="1">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="CW39" s="1">
         <v>70</v>
@@ -15061,16 +15061,16 @@
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>4155</v>
+        <v>4194</v>
       </c>
       <c r="K40" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L40" s="2">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="M40" s="2">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="N40" s="1">
         <v>16656</v>
@@ -15103,7 +15103,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="2">
         <v>1</v>
@@ -15289,16 +15289,16 @@
         <v>0</v>
       </c>
       <c r="CH40" s="1">
-        <v>2335</v>
+        <v>2351</v>
       </c>
       <c r="CI40" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CJ40" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="CK40" s="2">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="CL40" s="1">
         <v>13</v>
@@ -15325,16 +15325,16 @@
         <v>0</v>
       </c>
       <c r="CT40" s="1">
-        <v>53375</v>
+        <v>53430</v>
       </c>
       <c r="CU40" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV40" s="1">
-        <v>773</v>
+        <v>827</v>
       </c>
       <c r="CW40" s="1">
-        <v>2142</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E41" s="2">
         <v>6</v>
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="AN41" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AO41" s="2">
         <v>16</v>
@@ -15600,7 +15600,7 @@
         <v>0</v>
       </c>
       <c r="CJ41" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="CK41" s="2">
         <v>20</v>
@@ -15636,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="CV41" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="CW41" s="1">
         <v>45</v>
@@ -16287,7 +16287,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="2">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="M44" s="2">
         <v>106</v>
@@ -16368,7 +16368,7 @@
         <v>381</v>
       </c>
       <c r="AM44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN44" s="2">
         <v>3</v>
@@ -16548,10 +16548,10 @@
         <v>50625</v>
       </c>
       <c r="CU44" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="CV44" s="1">
-        <v>1961</v>
+        <v>1942</v>
       </c>
       <c r="CW44" s="1">
         <v>2450</v>
@@ -18805,16 +18805,16 @@
         <v>0</v>
       </c>
       <c r="AL52" s="1">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AM52" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN52" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO52" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP52" s="1">
         <v>0</v>
@@ -18985,16 +18985,16 @@
         <v>0</v>
       </c>
       <c r="CT52" s="1">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="CU52" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV52" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CW52" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:101">
@@ -19116,7 +19116,7 @@
         <v>6</v>
       </c>
       <c r="AN53" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO53" s="2">
         <v>27</v>
@@ -19260,7 +19260,7 @@
         <v>9</v>
       </c>
       <c r="CJ53" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="CK53" s="2">
         <v>26</v>
@@ -19296,7 +19296,7 @@
         <v>17</v>
       </c>
       <c r="CV53" s="1">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="CW53" s="1">
         <v>60</v>
@@ -20169,16 +20169,16 @@
         <v>0</v>
       </c>
       <c r="CH56" s="1">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="CI56" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CJ56" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="CK56" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="CL56" s="1">
         <v>2</v>
@@ -20205,16 +20205,16 @@
         <v>0</v>
       </c>
       <c r="CT56" s="1">
-        <v>7784</v>
+        <v>7796</v>
       </c>
       <c r="CU56" s="1">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="CV56" s="1">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="CW56" s="1">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -20838,7 +20838,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E59" s="2">
         <v>7</v>
@@ -20850,7 +20850,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="2">
         <v>3</v>
@@ -21126,7 +21126,7 @@
         <v>7</v>
       </c>
       <c r="CV59" s="1">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="CW59" s="1">
         <v>53</v>
@@ -21637,7 +21637,7 @@
         <v>341</v>
       </c>
       <c r="BO61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP61" s="2">
         <v>1</v>
@@ -21733,7 +21733,7 @@
         <v>65931</v>
       </c>
       <c r="CU61" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CV61" s="1">
         <v>481</v>
@@ -22085,7 +22085,7 @@
         <v>8</v>
       </c>
       <c r="M63" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N63" s="1">
         <v>1118</v>
@@ -22349,7 +22349,7 @@
         <v>85</v>
       </c>
       <c r="CW63" s="1">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22360,7 +22360,7 @@
         <v>425</v>
       </c>
       <c r="C64" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64" s="2">
         <v>8</v>
@@ -22384,7 +22384,7 @@
         <v>275</v>
       </c>
       <c r="K64" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2">
         <v>8</v>
@@ -22432,7 +22432,7 @@
         <v>97</v>
       </c>
       <c r="AA64" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB64" s="2">
         <v>3</v>
@@ -22444,7 +22444,7 @@
         <v>1995</v>
       </c>
       <c r="AE64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF64" s="2">
         <v>64</v>
@@ -22564,7 +22564,7 @@
         <v>23</v>
       </c>
       <c r="BS64" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT64" s="2">
         <v>2</v>
@@ -22612,7 +22612,7 @@
         <v>668</v>
       </c>
       <c r="CI64" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CJ64" s="2">
         <v>18</v>
@@ -22648,7 +22648,7 @@
         <v>7931</v>
       </c>
       <c r="CU64" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="CV64" s="1">
         <v>104</v>
@@ -22662,16 +22662,16 @@
         <v>164</v>
       </c>
       <c r="B65" s="1">
-        <v>3687</v>
+        <v>3702</v>
       </c>
       <c r="C65" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D65" s="2">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E65" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22686,16 +22686,16 @@
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="K65" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L65" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M65" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N65" s="1">
         <v>58956</v>
@@ -22749,7 +22749,7 @@
         <v>338</v>
       </c>
       <c r="AE65" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AF65" s="2">
         <v>9</v>
@@ -22950,16 +22950,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67168</v>
+        <v>67185</v>
       </c>
       <c r="CU65" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="CV65" s="1">
-        <v>1761</v>
+        <v>1778</v>
       </c>
       <c r="CW65" s="1">
-        <v>3542</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -22991,16 +22991,16 @@
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="K66" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L66" s="2">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="M66" s="2">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="N66" s="1">
         <v>0</v>
@@ -23255,16 +23255,16 @@
         <v>0</v>
       </c>
       <c r="CT66" s="1">
-        <v>1644</v>
+        <v>1658</v>
       </c>
       <c r="CU66" s="1">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="CV66" s="1">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="CW66" s="1">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:101">
@@ -23272,16 +23272,16 @@
         <v>166</v>
       </c>
       <c r="B67" s="1">
-        <v>2461</v>
+        <v>2481</v>
       </c>
       <c r="C67" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D67" s="2">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E67" s="2">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -23560,16 +23560,16 @@
         <v>0</v>
       </c>
       <c r="CT67" s="1">
-        <v>3338</v>
+        <v>3358</v>
       </c>
       <c r="CU67" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CV67" s="1">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="CW67" s="1">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:101">
@@ -23601,16 +23601,16 @@
         <v>1</v>
       </c>
       <c r="J68" s="1">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N68" s="1">
         <v>1092</v>
@@ -23865,16 +23865,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="CU68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV68" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW68" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -23894,16 +23894,16 @@
         <v>3</v>
       </c>
       <c r="F69" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I69" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69" s="1">
         <v>0</v>
@@ -24170,16 +24170,16 @@
         <v>0</v>
       </c>
       <c r="CT69" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="CU69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV69" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CW69" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:101">
@@ -25407,16 +25407,16 @@
         <v>173</v>
       </c>
       <c r="B74" s="1">
-        <v>12569</v>
+        <v>12605</v>
       </c>
       <c r="C74" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D74" s="2">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E74" s="2">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -25500,7 +25500,7 @@
         <v>214</v>
       </c>
       <c r="AG74" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25515,16 +25515,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36263</v>
+        <v>36267</v>
       </c>
       <c r="AM74" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AN74" s="2">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="AO74" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25542,7 +25542,7 @@
         <v>47</v>
       </c>
       <c r="AU74" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV74" s="2">
         <v>4</v>
@@ -25602,7 +25602,7 @@
         <v>509</v>
       </c>
       <c r="BO74" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BP74" s="2">
         <v>10</v>
@@ -25665,10 +25665,10 @@
         <v>73</v>
       </c>
       <c r="CJ74" s="2">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="CK74" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171570</v>
+        <v>171610</v>
       </c>
       <c r="CU74" s="1">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="CV74" s="1">
-        <v>1936</v>
+        <v>1920</v>
       </c>
       <c r="CW74" s="1">
-        <v>4361</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26044,7 +26044,7 @@
         <v>5809</v>
       </c>
       <c r="K76" s="2">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="L76" s="2">
         <v>202</v>
@@ -26125,16 +26125,16 @@
         <v>0</v>
       </c>
       <c r="AL76" s="1">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO76" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP76" s="1">
         <v>49</v>
@@ -26260,7 +26260,7 @@
         <v>16</v>
       </c>
       <c r="CE76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF76" s="2">
         <v>1</v>
@@ -26269,16 +26269,16 @@
         <v>1</v>
       </c>
       <c r="CH76" s="1">
-        <v>2226</v>
+        <v>2251</v>
       </c>
       <c r="CI76" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CJ76" s="2">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="CK76" s="2">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="CL76" s="1">
         <v>7</v>
@@ -26305,16 +26305,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>150987</v>
+        <v>151013</v>
       </c>
       <c r="CU76" s="1">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="CV76" s="1">
-        <v>1307</v>
+        <v>1333</v>
       </c>
       <c r="CW76" s="1">
-        <v>3733</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26322,16 +26322,16 @@
         <v>176</v>
       </c>
       <c r="B77" s="1">
-        <v>10837</v>
+        <v>10858</v>
       </c>
       <c r="C77" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D77" s="2">
-        <v>-102</v>
+        <v>-6</v>
       </c>
       <c r="E77" s="2">
-        <v>-4313</v>
+        <v>-4292</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -26352,7 +26352,7 @@
         <v>109</v>
       </c>
       <c r="L77" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M77" s="2">
         <v>343</v>
@@ -26388,7 +26388,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y77" s="2">
         <v>1</v>
@@ -26433,7 +26433,7 @@
         <v>1906</v>
       </c>
       <c r="AM77" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AN77" s="2">
         <v>47</v>
@@ -26574,16 +26574,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7202</v>
+        <v>7275</v>
       </c>
       <c r="CI77" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="CJ77" s="2">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="CK77" s="2">
-        <v>541</v>
+        <v>585</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390756</v>
+        <v>390850</v>
       </c>
       <c r="CU77" s="1">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="CV77" s="1">
-        <v>10041</v>
+        <v>10210</v>
       </c>
       <c r="CW77" s="1">
-        <v>15992</v>
+        <v>16057</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26648,7 +26648,7 @@
         <v>3</v>
       </c>
       <c r="I78" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -26741,7 +26741,7 @@
         <v>0</v>
       </c>
       <c r="AN78" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AO78" s="2">
         <v>42</v>
@@ -26885,7 +26885,7 @@
         <v>4</v>
       </c>
       <c r="CJ78" s="2">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="CK78" s="2">
         <v>73</v>
@@ -26921,10 +26921,10 @@
         <v>5</v>
       </c>
       <c r="CV78" s="1">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="CW78" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -26971,7 +26971,7 @@
         <v>69222</v>
       </c>
       <c r="O79" s="2">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="P79" s="2">
         <v>497</v>
@@ -27184,16 +27184,16 @@
         <v>0</v>
       </c>
       <c r="CH79" s="1">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="CI79" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CJ79" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CK79" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CL79" s="1">
         <v>2</v>
@@ -27220,16 +27220,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90616</v>
+        <v>90617</v>
       </c>
       <c r="CU79" s="1">
-        <v>478</v>
+        <v>88</v>
       </c>
       <c r="CV79" s="1">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="CW79" s="1">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27584,7 +27584,7 @@
         <v>72</v>
       </c>
       <c r="P81" s="2">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="Q81" s="2">
         <v>218</v>
@@ -27836,7 +27836,7 @@
         <v>107</v>
       </c>
       <c r="CV81" s="1">
-        <v>303</v>
+        <v>155</v>
       </c>
       <c r="CW81" s="1">
         <v>385</v>
@@ -28260,16 +28260,16 @@
         <v>0</v>
       </c>
       <c r="AL83" s="1">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="AM83" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN83" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO83" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP83" s="1">
         <v>0</v>
@@ -28440,16 +28440,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423790</v>
+        <v>423791</v>
       </c>
       <c r="CU83" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="CV83" s="1">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="CW83" s="1">
-        <v>5457</v>
+        <v>5458</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29076,7 +29076,7 @@
         <v>5</v>
       </c>
       <c r="E86" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F86" s="1">
         <v>42</v>
@@ -29364,7 +29364,7 @@
         <v>34</v>
       </c>
       <c r="CW86" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29764,7 +29764,7 @@
         <v>5093</v>
       </c>
       <c r="AE88" s="2">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="AF88" s="2">
         <v>74</v>
@@ -29803,7 +29803,7 @@
         <v>1</v>
       </c>
       <c r="AR88" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS88" s="2">
         <v>6</v>
@@ -29935,7 +29935,7 @@
         <v>5</v>
       </c>
       <c r="CJ88" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CK88" s="2">
         <v>39</v>
@@ -29968,10 +29968,10 @@
         <v>9583</v>
       </c>
       <c r="CU88" s="1">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="CV88" s="1">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="CW88" s="1">
         <v>440</v>
@@ -30592,16 +30592,16 @@
         <v>190</v>
       </c>
       <c r="B91" s="1">
-        <v>7085</v>
+        <v>7101</v>
       </c>
       <c r="C91" s="2">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D91" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E91" s="2">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -30703,10 +30703,10 @@
         <v>762</v>
       </c>
       <c r="AM91" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN91" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO91" s="2">
         <v>10</v>
@@ -30844,16 +30844,16 @@
         <v>0</v>
       </c>
       <c r="CH91" s="1">
-        <v>7746</v>
+        <v>7747</v>
       </c>
       <c r="CI91" s="2">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="CJ91" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="CK91" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CL91" s="1">
         <v>5</v>
@@ -30880,16 +30880,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25837</v>
+        <v>25854</v>
       </c>
       <c r="CU91" s="1">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="CV91" s="1">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="CW91" s="1">
-        <v>850</v>
+        <v>867</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -31008,7 +31008,7 @@
         <v>794</v>
       </c>
       <c r="AM92" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN92" s="2">
         <v>4</v>
@@ -31149,16 +31149,16 @@
         <v>0</v>
       </c>
       <c r="CH92" s="1">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="CI92" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CJ92" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CK92" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="CL92" s="1">
         <v>25</v>
@@ -31185,16 +31185,16 @@
         <v>0</v>
       </c>
       <c r="CT92" s="1">
-        <v>3788</v>
+        <v>3794</v>
       </c>
       <c r="CU92" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV92" s="1">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="CW92" s="1">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -31241,7 +31241,7 @@
         <v>869</v>
       </c>
       <c r="O93" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P93" s="2">
         <v>16</v>
@@ -31268,7 +31268,7 @@
         <v>0</v>
       </c>
       <c r="X93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y93" s="2">
         <v>1</v>
@@ -31493,10 +31493,10 @@
         <v>1178</v>
       </c>
       <c r="CU93" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CV93" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CW93" s="1">
         <v>67</v>
@@ -32243,7 +32243,7 @@
         <v>0</v>
       </c>
       <c r="AR96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS96" s="2">
         <v>3</v>
@@ -32411,7 +32411,7 @@
         <v>1</v>
       </c>
       <c r="CV96" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW96" s="1">
         <v>46</v>
@@ -32434,16 +32434,16 @@
         <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" s="2">
         <v>3</v>
       </c>
       <c r="I97" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J97" s="1">
         <v>0</v>
@@ -32551,7 +32551,7 @@
         <v>3</v>
       </c>
       <c r="AS97" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT97" s="1">
         <v>0</v>
@@ -32683,7 +32683,7 @@
         <v>3</v>
       </c>
       <c r="CK97" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CL97" s="1">
         <v>33</v>
@@ -32710,16 +32710,16 @@
         <v>0</v>
       </c>
       <c r="CT97" s="1">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="CU97" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV97" s="1">
         <v>9</v>
       </c>
       <c r="CW97" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -33044,13 +33044,13 @@
         <v>0</v>
       </c>
       <c r="F99" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I99" s="2">
         <v>6</v>
@@ -33320,13 +33320,13 @@
         <v>0</v>
       </c>
       <c r="CT99" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CU99" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV99" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW99" s="1">
         <v>6</v>
@@ -33349,16 +33349,16 @@
         <v>0</v>
       </c>
       <c r="F100" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G100" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="2">
         <v>3</v>
       </c>
       <c r="I100" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J100" s="1">
         <v>0</v>
@@ -33451,7 +33451,7 @@
         <v>3</v>
       </c>
       <c r="AN100" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO100" s="2">
         <v>17</v>
@@ -33595,7 +33595,7 @@
         <v>2</v>
       </c>
       <c r="CJ100" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CK100" s="2">
         <v>13</v>
@@ -33625,16 +33625,16 @@
         <v>0</v>
       </c>
       <c r="CT100" s="1">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CU100" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CV100" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CW100" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33989,7 +33989,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="2">
-        <v>537</v>
+        <v>210</v>
       </c>
       <c r="Q102" s="2">
         <v>539</v>
@@ -34241,7 +34241,7 @@
         <v>190</v>
       </c>
       <c r="CV102" s="1">
-        <v>1109</v>
+        <v>782</v>
       </c>
       <c r="CW102" s="1">
         <v>1820</v>
@@ -34572,13 +34572,13 @@
         <v>39</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="2">
         <v>3</v>
       </c>
       <c r="I104" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J104" s="1">
         <v>0</v>
@@ -34848,13 +34848,13 @@
         <v>40</v>
       </c>
       <c r="CU104" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV104" s="1">
         <v>3</v>
       </c>
       <c r="CW104" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:101">
@@ -34886,16 +34886,16 @@
         <v>0</v>
       </c>
       <c r="J105" s="1">
-        <v>984</v>
+        <v>997</v>
       </c>
       <c r="K105" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L105" s="2">
         <v>33</v>
       </c>
       <c r="M105" s="2">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="N105" s="1">
         <v>1428</v>
@@ -34946,16 +34946,16 @@
         <v>0</v>
       </c>
       <c r="AD105" s="1">
-        <v>4468</v>
+        <v>4469</v>
       </c>
       <c r="AE105" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF105" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG105" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AH105" s="1">
         <v>0</v>
@@ -35117,7 +35117,7 @@
         <v>276</v>
       </c>
       <c r="CI105" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CJ105" s="2">
         <v>8</v>
@@ -35150,16 +35150,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7959</v>
+        <v>7973</v>
       </c>
       <c r="CU105" s="1">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CV105" s="1">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="CW105" s="1">
-        <v>629</v>
+        <v>643</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -35206,7 +35206,7 @@
         <v>22916</v>
       </c>
       <c r="O106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="2">
         <v>182</v>
@@ -35458,7 +35458,7 @@
         <v>92554</v>
       </c>
       <c r="CU106" s="1">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CV106" s="1">
         <v>1102</v>
@@ -36429,10 +36429,10 @@
         <v>0</v>
       </c>
       <c r="P110" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q110" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R110" s="1">
         <v>0</v>
@@ -36681,10 +36681,10 @@
         <v>148</v>
       </c>
       <c r="CV110" s="1">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="CW110" s="1">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36997,16 +36997,16 @@
         <v>211</v>
       </c>
       <c r="B112" s="1">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="C112" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D112" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E112" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -37285,16 +37285,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8270</v>
+        <v>8280</v>
       </c>
       <c r="CU112" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="CV112" s="1">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="CW112" s="1">
-        <v>643</v>
+        <v>653</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37329,7 +37329,7 @@
         <v>4762</v>
       </c>
       <c r="K113" s="2">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="L113" s="2">
         <v>192</v>
@@ -37554,16 +37554,16 @@
         <v>0</v>
       </c>
       <c r="CH113" s="1">
-        <v>1446</v>
+        <v>1474</v>
       </c>
       <c r="CI113" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="CJ113" s="2">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="CK113" s="2">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37590,16 +37590,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173773</v>
+        <v>173801</v>
       </c>
       <c r="CU113" s="1">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="CV113" s="1">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="CW113" s="1">
-        <v>9896</v>
+        <v>9924</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38451,7 +38451,7 @@
         <v>0</v>
       </c>
       <c r="CB116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC116" s="2">
         <v>1</v>
@@ -38469,16 +38469,16 @@
         <v>0</v>
       </c>
       <c r="CH116" s="1">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="CI116" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CJ116" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CK116" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="CL116" s="1">
         <v>12</v>
@@ -38505,16 +38505,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21741</v>
+        <v>21740</v>
       </c>
       <c r="CU116" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="CV116" s="1">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="CW116" s="1">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38669,7 +38669,7 @@
         <v>2</v>
       </c>
       <c r="AY117" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ117" s="2">
         <v>2</v>
@@ -38813,7 +38813,7 @@
         <v>13155</v>
       </c>
       <c r="CU117" s="1">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="CV117" s="1">
         <v>589</v>
@@ -38836,7 +38836,7 @@
         <v>1</v>
       </c>
       <c r="E118" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F118" s="1">
         <v>39</v>
@@ -38935,28 +38935,28 @@
         <v>0</v>
       </c>
       <c r="AL118" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP118" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ118" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR118" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS118" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT118" s="1">
         <v>0</v>
@@ -39079,16 +39079,16 @@
         <v>0</v>
       </c>
       <c r="CH118" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CI118" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ118" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CK118" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CL118" s="1">
         <v>0</v>
@@ -39115,16 +39115,16 @@
         <v>0</v>
       </c>
       <c r="CT118" s="1">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="CU118" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="CV118" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="CW118" s="1">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119" spans="1:101">
@@ -39455,7 +39455,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I120" s="2">
         <v>5</v>
@@ -39731,7 +39731,7 @@
         <v>16</v>
       </c>
       <c r="CV120" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CW120" s="1">
         <v>72</v>
@@ -39754,13 +39754,13 @@
         <v>1</v>
       </c>
       <c r="F121" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I121" s="2">
         <v>5</v>
@@ -40030,13 +40030,13 @@
         <v>0</v>
       </c>
       <c r="CT121" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CU121" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV121" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW121" s="1">
         <v>6</v>
@@ -40364,16 +40364,16 @@
         <v>0</v>
       </c>
       <c r="F123" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G123" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H123" s="2">
         <v>3</v>
       </c>
       <c r="I123" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J123" s="1">
         <v>142</v>
@@ -40640,16 +40640,16 @@
         <v>0</v>
       </c>
       <c r="CT123" s="1">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="CU123" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV123" s="1">
         <v>13</v>
       </c>
       <c r="CW123" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -41282,10 +41282,10 @@
         <v>64</v>
       </c>
       <c r="G126" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I126" s="2">
         <v>6</v>
@@ -41558,10 +41558,10 @@
         <v>834</v>
       </c>
       <c r="CU126" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV126" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CW126" s="1">
         <v>17</v>
@@ -42003,7 +42003,7 @@
         <v>0</v>
       </c>
       <c r="AR128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS128" s="2">
         <v>3</v>
@@ -42147,7 +42147,7 @@
         <v>0</v>
       </c>
       <c r="CN128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO128" s="2">
         <v>1</v>
@@ -42171,7 +42171,7 @@
         <v>4</v>
       </c>
       <c r="CV128" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CW128" s="1">
         <v>15</v>
@@ -42200,7 +42200,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I129" s="2">
         <v>4</v>
@@ -42476,7 +42476,7 @@
         <v>5</v>
       </c>
       <c r="CV129" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="CW129" s="1">
         <v>292</v>
@@ -42508,7 +42508,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J130" s="1">
         <v>0</v>
@@ -42784,7 +42784,7 @@
         <v>130</v>
       </c>
       <c r="CW130" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -44099,7 +44099,7 @@
         <v>11788</v>
       </c>
       <c r="AE135" s="2">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="AF135" s="2">
         <v>159</v>
@@ -44303,7 +44303,7 @@
         <v>62642</v>
       </c>
       <c r="CU135" s="1">
-        <v>300</v>
+        <v>154</v>
       </c>
       <c r="CV135" s="1">
         <v>1015</v>
@@ -44317,16 +44317,16 @@
         <v>235</v>
       </c>
       <c r="B136" s="1">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C136" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D136" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E136" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F136" s="1">
         <v>17</v>
@@ -44353,16 +44353,16 @@
         <v>7</v>
       </c>
       <c r="N136" s="1">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="O136" s="2">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="P136" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q136" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="R136" s="1">
         <v>10</v>
@@ -44605,16 +44605,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>158869</v>
+        <v>158865</v>
       </c>
       <c r="CU136" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV136" s="1">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="CW136" s="1">
-        <v>6080</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -44748,7 +44748,7 @@
         <v>1</v>
       </c>
       <c r="AR137" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS137" s="2">
         <v>6</v>
@@ -44892,7 +44892,7 @@
         <v>1</v>
       </c>
       <c r="CN137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO137" s="2">
         <v>5</v>
@@ -44916,7 +44916,7 @@
         <v>7</v>
       </c>
       <c r="CV137" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CW137" s="1">
         <v>66</v>
@@ -44951,16 +44951,16 @@
         <v>1</v>
       </c>
       <c r="J138" s="1">
-        <v>1194</v>
+        <v>1208</v>
       </c>
       <c r="K138" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L138" s="2">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="M138" s="2">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="N138" s="1">
         <v>2200</v>
@@ -45215,16 +45215,16 @@
         <v>0</v>
       </c>
       <c r="CT138" s="1">
-        <v>4390</v>
+        <v>4404</v>
       </c>
       <c r="CU138" s="1">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="CV138" s="1">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="CW138" s="1">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -46159,16 +46159,16 @@
         <v>4</v>
       </c>
       <c r="F142" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2">
         <v>2</v>
       </c>
       <c r="I142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J142" s="1">
         <v>429</v>
@@ -46435,16 +46435,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="CU142" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV142" s="1">
         <v>60</v>
       </c>
       <c r="CW142" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -47209,7 +47209,7 @@
         <v>38</v>
       </c>
       <c r="AY145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ145" s="2">
         <v>4</v>
@@ -47353,7 +47353,7 @@
         <v>2475</v>
       </c>
       <c r="CU145" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV145" s="1">
         <v>53</v>
@@ -48058,7 +48058,7 @@
         <v>10</v>
       </c>
       <c r="AC148" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AD148" s="1">
         <v>0</v>
@@ -48274,7 +48274,7 @@
         <v>108</v>
       </c>
       <c r="CW148" s="1">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -49197,16 +49197,16 @@
         <v>251</v>
       </c>
       <c r="B152" s="1">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D152" s="2">
         <v>2</v>
       </c>
       <c r="E152" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1">
         <v>22</v>
@@ -49485,16 +49485,16 @@
         <v>0</v>
       </c>
       <c r="CT152" s="1">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="CU152" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CV152" s="1">
         <v>105</v>
       </c>
       <c r="CW152" s="1">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50151,7 +50151,7 @@
         <v>1204</v>
       </c>
       <c r="O155" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P155" s="2">
         <v>18</v>
@@ -50235,7 +50235,7 @@
         <v>33</v>
       </c>
       <c r="AQ155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR155" s="2">
         <v>3</v>
@@ -50367,7 +50367,7 @@
         <v>407</v>
       </c>
       <c r="CI155" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ155" s="2">
         <v>12</v>
@@ -50403,7 +50403,7 @@
         <v>2654</v>
       </c>
       <c r="CU155" s="1">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="CV155" s="1">
         <v>52</v>
@@ -50420,13 +50420,13 @@
         <v>2026</v>
       </c>
       <c r="C156" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D156" s="2">
         <v>34</v>
       </c>
       <c r="E156" s="2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -50708,13 +50708,13 @@
         <v>71479</v>
       </c>
       <c r="CU156" s="1">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="CV156" s="1">
         <v>1056</v>
       </c>
       <c r="CW156" s="1">
-        <v>2538</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -50761,10 +50761,10 @@
         <v>11983</v>
       </c>
       <c r="O157" s="2">
+        <v>0</v>
+      </c>
+      <c r="P157" s="2">
         <v>171</v>
-      </c>
-      <c r="P157" s="2">
-        <v>274</v>
       </c>
       <c r="Q157" s="2">
         <v>274</v>
@@ -50788,7 +50788,7 @@
         <v>0</v>
       </c>
       <c r="X157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y157" s="2">
         <v>1</v>
@@ -50830,16 +50830,16 @@
         <v>0</v>
       </c>
       <c r="AL157" s="1">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AM157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN157" s="2">
-        <v>-40</v>
+        <v>1</v>
       </c>
       <c r="AO157" s="2">
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="AP157" s="1">
         <v>49</v>
@@ -50974,16 +50974,16 @@
         <v>0</v>
       </c>
       <c r="CH157" s="1">
-        <v>4808</v>
+        <v>4861</v>
       </c>
       <c r="CI157" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="CJ157" s="2">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="CK157" s="2">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="CL157" s="1">
         <v>9</v>
@@ -51010,16 +51010,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>166281</v>
+        <v>166335</v>
       </c>
       <c r="CU157" s="1">
-        <v>311</v>
+        <v>194</v>
       </c>
       <c r="CV157" s="1">
-        <v>5285</v>
+        <v>5275</v>
       </c>
       <c r="CW157" s="1">
-        <v>9154</v>
+        <v>9208</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51057,7 +51057,7 @@
         <v>69</v>
       </c>
       <c r="L158" s="2">
-        <v>292</v>
+        <v>218</v>
       </c>
       <c r="M158" s="2">
         <v>457</v>
@@ -51072,7 +51072,7 @@
         <v>55</v>
       </c>
       <c r="Q158" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R158" s="1">
         <v>0</v>
@@ -51135,16 +51135,16 @@
         <v>0</v>
       </c>
       <c r="AL158" s="1">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="AM158" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AN158" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AO158" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AP158" s="1">
         <v>3</v>
@@ -51279,16 +51279,16 @@
         <v>0</v>
       </c>
       <c r="CH158" s="1">
-        <v>5802</v>
+        <v>5929</v>
       </c>
       <c r="CI158" s="2">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="CJ158" s="2">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="CK158" s="2">
-        <v>487</v>
+        <v>614</v>
       </c>
       <c r="CL158" s="1">
         <v>0</v>
@@ -51315,16 +51315,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25322</v>
+        <v>25461</v>
       </c>
       <c r="CU158" s="1">
-        <v>206</v>
+        <v>345</v>
       </c>
       <c r="CV158" s="1">
-        <v>775</v>
+        <v>840</v>
       </c>
       <c r="CW158" s="1">
-        <v>1550</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51966,16 +51966,16 @@
         <v>0</v>
       </c>
       <c r="J161" s="1">
-        <v>3284</v>
+        <v>3318</v>
       </c>
       <c r="K161" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L161" s="2">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="M161" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="N161" s="1">
         <v>10033</v>
@@ -51984,7 +51984,7 @@
         <v>0</v>
       </c>
       <c r="P161" s="2">
-        <v>478</v>
+        <v>254</v>
       </c>
       <c r="Q161" s="2">
         <v>477</v>
@@ -52230,16 +52230,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>22345</v>
+        <v>22379</v>
       </c>
       <c r="CU161" s="1">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="CV161" s="1">
-        <v>934</v>
+        <v>744</v>
       </c>
       <c r="CW161" s="1">
-        <v>1240</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52561,7 +52561,7 @@
         <v>3</v>
       </c>
       <c r="E163" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F163" s="1">
         <v>30</v>
@@ -52594,7 +52594,7 @@
         <v>0</v>
       </c>
       <c r="P163" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q163" s="2">
         <v>10</v>
@@ -52618,7 +52618,7 @@
         <v>0</v>
       </c>
       <c r="X163" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y163" s="2">
         <v>1</v>
@@ -52804,16 +52804,16 @@
         <v>0</v>
       </c>
       <c r="CH163" s="1">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="CI163" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ163" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CK163" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CL163" s="1">
         <v>49</v>
@@ -52840,16 +52840,16 @@
         <v>0</v>
       </c>
       <c r="CT163" s="1">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="CU163" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV163" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CW163" s="1">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -52896,7 +52896,7 @@
         <v>249</v>
       </c>
       <c r="O164" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P164" s="2">
         <v>8</v>
@@ -53148,7 +53148,7 @@
         <v>1118</v>
       </c>
       <c r="CU164" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CV164" s="1">
         <v>100</v>
@@ -53509,7 +53509,7 @@
         <v>22</v>
       </c>
       <c r="P166" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="Q166" s="2">
         <v>169</v>
@@ -53761,7 +53761,7 @@
         <v>45</v>
       </c>
       <c r="CV166" s="1">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="CW166" s="1">
         <v>529</v>
@@ -54083,7 +54083,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" s="2">
         <v>10</v>
@@ -54371,7 +54371,7 @@
         <v>27</v>
       </c>
       <c r="CV168" s="1">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="CW168" s="1">
         <v>611</v>
@@ -54496,7 +54496,7 @@
         <v>0</v>
       </c>
       <c r="AN169" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AO169" s="2">
         <v>14</v>
@@ -54640,7 +54640,7 @@
         <v>0</v>
       </c>
       <c r="CJ169" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="CK169" s="2">
         <v>28</v>
@@ -54676,7 +54676,7 @@
         <v>1</v>
       </c>
       <c r="CV169" s="1">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="CW169" s="1">
         <v>48</v>
@@ -54711,16 +54711,16 @@
         <v>0</v>
       </c>
       <c r="J170" s="1">
-        <v>6324</v>
+        <v>6368</v>
       </c>
       <c r="K170" s="2">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="L170" s="2">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="M170" s="2">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="N170" s="1">
         <v>2774</v>
@@ -54855,16 +54855,16 @@
         <v>0</v>
       </c>
       <c r="BF170" s="1">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="BG170" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH170" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BI170" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BJ170" s="1">
         <v>0</v>
@@ -54882,7 +54882,7 @@
         <v>24</v>
       </c>
       <c r="BO170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP170" s="2">
         <v>1</v>
@@ -54975,16 +54975,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19473</v>
+        <v>19519</v>
       </c>
       <c r="CU170" s="1">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="CV170" s="1">
-        <v>455</v>
+        <v>501</v>
       </c>
       <c r="CW170" s="1">
-        <v>1202</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -55001,7 +55001,7 @@
         <v>3</v>
       </c>
       <c r="E171" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F171" s="1">
         <v>16</v>
@@ -55025,7 +55025,7 @@
         <v>17</v>
       </c>
       <c r="M171" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N171" s="1">
         <v>2698</v>
@@ -55103,7 +55103,7 @@
         <v>1188</v>
       </c>
       <c r="AM171" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN171" s="2">
         <v>2</v>
@@ -55247,7 +55247,7 @@
         <v>820</v>
       </c>
       <c r="CI171" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CJ171" s="2">
         <v>1</v>
@@ -55283,13 +55283,13 @@
         <v>5829</v>
       </c>
       <c r="CU171" s="1">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="CV171" s="1">
         <v>45</v>
       </c>
       <c r="CW171" s="1">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -55907,22 +55907,22 @@
         <v>273</v>
       </c>
       <c r="B174" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C174" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E174" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F174" s="1">
         <v>35</v>
       </c>
       <c r="G174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174" s="2">
         <v>1</v>
@@ -56027,16 +56027,16 @@
         <v>0</v>
       </c>
       <c r="AP174" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ174" s="2">
         <v>1</v>
       </c>
       <c r="AR174" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS174" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT174" s="1">
         <v>0</v>
@@ -56171,16 +56171,16 @@
         <v>0</v>
       </c>
       <c r="CL174" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CM174" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN174" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO174" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CP174" s="1">
         <v>0</v>
@@ -56195,16 +56195,16 @@
         <v>0</v>
       </c>
       <c r="CT174" s="1">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="CU174" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CV174" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CW174" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:101">
@@ -56529,16 +56529,16 @@
         <v>6</v>
       </c>
       <c r="F176" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I176" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J176" s="1">
         <v>0</v>
@@ -56778,7 +56778,7 @@
         <v>70</v>
       </c>
       <c r="CK176" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="CL176" s="1">
         <v>0</v>
@@ -56805,16 +56805,16 @@
         <v>0</v>
       </c>
       <c r="CT176" s="1">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="CU176" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CV176" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="CW176" s="1">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57441,19 +57441,19 @@
         <v>0</v>
       </c>
       <c r="E179" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" s="1">
         <v>26</v>
       </c>
       <c r="G179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179" s="2">
         <v>3</v>
       </c>
       <c r="I179" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J179" s="1">
         <v>0</v>
@@ -57549,7 +57549,7 @@
         <v>21</v>
       </c>
       <c r="AO179" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AP179" s="1">
         <v>5</v>
@@ -57693,7 +57693,7 @@
         <v>20</v>
       </c>
       <c r="CK179" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="CL179" s="1">
         <v>11</v>
@@ -57723,13 +57723,13 @@
         <v>843</v>
       </c>
       <c r="CU179" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV179" s="1">
         <v>44</v>
       </c>
       <c r="CW179" s="1">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -58060,10 +58060,10 @@
         <v>1</v>
       </c>
       <c r="H181" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I181" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J181" s="1">
         <v>0</v>
@@ -58336,10 +58336,10 @@
         <v>1</v>
       </c>
       <c r="CV181" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW181" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -58847,7 +58847,7 @@
         <v>51</v>
       </c>
       <c r="BO183" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP183" s="2">
         <v>1</v>
@@ -58943,7 +58943,7 @@
         <v>65</v>
       </c>
       <c r="CU183" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV183" s="1">
         <v>1</v>
@@ -59884,16 +59884,16 @@
         <v>0</v>
       </c>
       <c r="F187" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G187" s="2">
         <v>1</v>
       </c>
       <c r="H187" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I187" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J187" s="1">
         <v>0</v>
@@ -60160,16 +60160,16 @@
         <v>0</v>
       </c>
       <c r="CT187" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CU187" s="1">
         <v>1</v>
       </c>
       <c r="CV187" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW187" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:101">
@@ -60799,13 +60799,13 @@
         <v>0</v>
       </c>
       <c r="F190" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G190" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I190" s="2">
         <v>6</v>
@@ -61075,13 +61075,13 @@
         <v>0</v>
       </c>
       <c r="CT190" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CU190" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV190" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW190" s="1">
         <v>6</v>
@@ -61101,7 +61101,7 @@
         <v>2</v>
       </c>
       <c r="E191" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F191" s="1">
         <v>34</v>
@@ -61125,7 +61125,7 @@
         <v>0</v>
       </c>
       <c r="M191" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N191" s="1">
         <v>11</v>
@@ -61209,7 +61209,7 @@
         <v>6</v>
       </c>
       <c r="AO191" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AP191" s="1">
         <v>37</v>
@@ -61389,7 +61389,7 @@
         <v>13</v>
       </c>
       <c r="CW191" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:101">
@@ -61409,16 +61409,16 @@
         <v>0</v>
       </c>
       <c r="F192" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G192" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192" s="2">
         <v>3</v>
       </c>
       <c r="I192" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J192" s="1">
         <v>0</v>
@@ -61526,7 +61526,7 @@
         <v>3</v>
       </c>
       <c r="AS192" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT192" s="1">
         <v>0</v>
@@ -61658,7 +61658,7 @@
         <v>4</v>
       </c>
       <c r="CK192" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CL192" s="1">
         <v>37</v>
@@ -61685,16 +61685,16 @@
         <v>0</v>
       </c>
       <c r="CT192" s="1">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="CU192" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV192" s="1">
         <v>10</v>
       </c>
       <c r="CW192" s="1">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62031,16 +62031,16 @@
         <v>0</v>
       </c>
       <c r="J194" s="1">
-        <v>941</v>
+        <v>960</v>
       </c>
       <c r="K194" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L194" s="2">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="M194" s="2">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="N194" s="1">
         <v>29177</v>
@@ -62049,7 +62049,7 @@
         <v>17</v>
       </c>
       <c r="P194" s="2">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="Q194" s="2">
         <v>1228</v>
@@ -62295,16 +62295,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32827</v>
+        <v>32846</v>
       </c>
       <c r="CU194" s="1">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="CV194" s="1">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="CW194" s="1">
-        <v>1350</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62312,13 +62312,13 @@
         <v>294</v>
       </c>
       <c r="B195" s="1">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C195" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D195" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E195" s="2">
         <v>10</v>
@@ -62348,16 +62348,16 @@
         <v>11</v>
       </c>
       <c r="N195" s="1">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="O195" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="P195" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q195" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R195" s="1">
         <v>9</v>
@@ -62600,16 +62600,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>71186</v>
+        <v>71185</v>
       </c>
       <c r="CU195" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV195" s="1">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="CW195" s="1">
-        <v>5328</v>
+        <v>5325</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -63972,7 +63972,7 @@
         <v>46</v>
       </c>
       <c r="AU200" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV200" s="2">
         <v>5</v>
@@ -64128,7 +64128,7 @@
         <v>16289</v>
       </c>
       <c r="CU200" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CV200" s="1">
         <v>260</v>
@@ -64459,16 +64459,16 @@
         <v>0</v>
       </c>
       <c r="F202" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G202" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H202" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I202" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J202" s="1">
         <v>0</v>
@@ -64555,16 +64555,16 @@
         <v>0</v>
       </c>
       <c r="AL202" s="1">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="AM202" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AN202" s="2">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="AO202" s="2">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="AP202" s="1">
         <v>0</v>
@@ -64699,16 +64699,16 @@
         <v>0</v>
       </c>
       <c r="CH202" s="1">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="CI202" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CJ202" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="CK202" s="2">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="CL202" s="1">
         <v>0</v>
@@ -64735,16 +64735,16 @@
         <v>0</v>
       </c>
       <c r="CT202" s="1">
-        <v>878</v>
+        <v>904</v>
       </c>
       <c r="CU202" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CV202" s="1">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="CW202" s="1">
-        <v>123</v>
+        <v>149</v>
       </c>
     </row>
     <row r="203" spans="1:101">
@@ -66690,16 +66690,16 @@
         <v>0</v>
       </c>
       <c r="AL209" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AM209" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN209" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO209" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AP209" s="1">
         <v>0</v>
@@ -66834,16 +66834,16 @@
         <v>0</v>
       </c>
       <c r="CH209" s="1">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="CI209" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CJ209" s="2">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="CK209" s="2">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="CL209" s="1">
         <v>0</v>
@@ -66870,16 +66870,16 @@
         <v>0</v>
       </c>
       <c r="CT209" s="1">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="CU209" s="1">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="CV209" s="1">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="CW209" s="1">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="210" spans="1:101">
@@ -66905,7 +66905,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I210" s="2">
         <v>4</v>
@@ -67181,7 +67181,7 @@
         <v>5</v>
       </c>
       <c r="CV210" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW210" s="1">
         <v>38</v>
@@ -67285,7 +67285,7 @@
         <v>382</v>
       </c>
       <c r="AG211" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AH211" s="1">
         <v>3</v>
@@ -67489,7 +67489,7 @@
         <v>504</v>
       </c>
       <c r="CW211" s="1">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -67802,16 +67802,16 @@
         <v>312</v>
       </c>
       <c r="B213" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C213" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D213" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E213" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F213" s="1">
         <v>42</v>
@@ -68090,16 +68090,16 @@
         <v>0</v>
       </c>
       <c r="CT213" s="1">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CU213" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CV213" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CW213" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214" spans="1:101">
@@ -68119,16 +68119,16 @@
         <v>1</v>
       </c>
       <c r="F214" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G214" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H214" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I214" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J214" s="1">
         <v>0</v>
@@ -68395,16 +68395,16 @@
         <v>0</v>
       </c>
       <c r="CT214" s="1">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CU214" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV214" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CW214" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -69534,7 +69534,7 @@
         <v>575</v>
       </c>
       <c r="D56">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E56" t="s">
         <v>715</v>
@@ -69897,7 +69897,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E74" t="s">
         <v>715</v>
@@ -70523,7 +70523,7 @@
         <v>621</v>
       </c>
       <c r="D105">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E105" t="s">
         <v>715</v>
@@ -70743,7 +70743,7 @@
         <v>630</v>
       </c>
       <c r="D116">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E116" t="s">
         <v>715</v>
@@ -72355,7 +72355,7 @@
         <v>698</v>
       </c>
       <c r="D196">
-        <v>10215</v>
+        <v>10253</v>
       </c>
       <c r="E196" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -6509,16 +6509,16 @@
         <v>17</v>
       </c>
       <c r="F12" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -6737,16 +6737,16 @@
         <v>0</v>
       </c>
       <c r="CD12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CE12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH12" s="1">
         <v>145</v>
@@ -6785,16 +6785,16 @@
         <v>0</v>
       </c>
       <c r="CT12" s="1">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CU12" s="1">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CV12" s="1">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CW12" s="1">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -7167,16 +7167,16 @@
         <v>1</v>
       </c>
       <c r="V14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" s="1">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="CU14" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CV14" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="CW14" s="1">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
         <v>2</v>
@@ -8316,7 +8316,7 @@
         <v>10</v>
       </c>
       <c r="CV17" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CW17" s="1">
         <v>50</v>
@@ -14433,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>14</v>
       </c>
       <c r="CV38" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="CW38" s="1">
         <v>123</v>
@@ -14732,16 +14732,16 @@
         <v>138</v>
       </c>
       <c r="B39" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F39" s="1">
         <v>31</v>
@@ -14840,16 +14840,16 @@
         <v>0</v>
       </c>
       <c r="AL39" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AM39" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN39" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AO39" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AP39" s="1">
         <v>14</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="CH39" s="1">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="CI39" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="CJ39" s="2">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="CK39" s="2">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="CL39" s="1">
         <v>2</v>
@@ -15020,16 +15020,16 @@
         <v>0</v>
       </c>
       <c r="CT39" s="1">
-        <v>568</v>
+        <v>606</v>
       </c>
       <c r="CU39" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CV39" s="1">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="CW39" s="1">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -16365,16 +16365,16 @@
         <v>0</v>
       </c>
       <c r="AL44" s="1">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM44" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN44" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO44" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP44" s="1">
         <v>61</v>
@@ -16509,16 +16509,16 @@
         <v>0</v>
       </c>
       <c r="CH44" s="1">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="CI44" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CJ44" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="CK44" s="2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="CL44" s="1">
         <v>33</v>
@@ -16545,16 +16545,16 @@
         <v>0</v>
       </c>
       <c r="CT44" s="1">
-        <v>50625</v>
+        <v>50635</v>
       </c>
       <c r="CU44" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="CV44" s="1">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="CW44" s="1">
-        <v>2450</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -18099,16 +18099,16 @@
         <v>8</v>
       </c>
       <c r="F50" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J50" s="1">
         <v>0</v>
@@ -18207,16 +18207,16 @@
         <v>11</v>
       </c>
       <c r="AP50" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT50" s="1">
         <v>0</v>
@@ -18339,16 +18339,16 @@
         <v>0</v>
       </c>
       <c r="CH50" s="1">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="CI50" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ50" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="CK50" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="CL50" s="1">
         <v>0</v>
@@ -18375,16 +18375,16 @@
         <v>0</v>
       </c>
       <c r="CT50" s="1">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="CU50" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CV50" s="1">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="CW50" s="1">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -19020,7 +19020,7 @@
         <v>2</v>
       </c>
       <c r="H53" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" s="2">
         <v>6</v>
@@ -19296,7 +19296,7 @@
         <v>17</v>
       </c>
       <c r="CV53" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CW53" s="1">
         <v>60</v>
@@ -19415,16 +19415,16 @@
         <v>0</v>
       </c>
       <c r="AL54" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN54" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO54" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP54" s="1">
         <v>14</v>
@@ -19559,16 +19559,16 @@
         <v>0</v>
       </c>
       <c r="CH54" s="1">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="CI54" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ54" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CK54" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CL54" s="1">
         <v>8</v>
@@ -19595,16 +19595,16 @@
         <v>0</v>
       </c>
       <c r="CT54" s="1">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="CU54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV54" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CW54" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:101">
@@ -20994,7 +20994,7 @@
         <v>0</v>
       </c>
       <c r="BD59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE59" s="2">
         <v>1</v>
@@ -21126,7 +21126,7 @@
         <v>7</v>
       </c>
       <c r="CV59" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CW59" s="1">
         <v>53</v>
@@ -22205,7 +22205,7 @@
         <v>1</v>
       </c>
       <c r="BA63" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB63" s="1">
         <v>4</v>
@@ -22349,7 +22349,7 @@
         <v>85</v>
       </c>
       <c r="CW63" s="1">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22357,16 +22357,16 @@
         <v>163</v>
       </c>
       <c r="B64" s="1">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C64" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D64" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E64" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F64" s="1">
         <v>18</v>
@@ -22381,16 +22381,16 @@
         <v>2</v>
       </c>
       <c r="J64" s="1">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M64" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N64" s="1">
         <v>4249</v>
@@ -22465,16 +22465,16 @@
         <v>0</v>
       </c>
       <c r="AL64" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP64" s="1">
         <v>51</v>
@@ -22609,16 +22609,16 @@
         <v>0</v>
       </c>
       <c r="CH64" s="1">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="CI64" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ64" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CK64" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CL64" s="1">
         <v>10</v>
@@ -22645,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>7931</v>
+        <v>7940</v>
       </c>
       <c r="CU64" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CV64" s="1">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="CW64" s="1">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -25120,7 +25120,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2">
         <v>2</v>
@@ -25396,7 +25396,7 @@
         <v>21</v>
       </c>
       <c r="CV73" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="CW73" s="1">
         <v>96</v>
@@ -25437,7 +25437,7 @@
         <v>37</v>
       </c>
       <c r="L74" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M74" s="2">
         <v>192</v>
@@ -25515,16 +25515,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36267</v>
+        <v>36271</v>
       </c>
       <c r="AM74" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AN74" s="2">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="AO74" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16167</v>
+        <v>16168</v>
       </c>
       <c r="CI74" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="CJ74" s="2">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="CK74" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171610</v>
+        <v>171615</v>
       </c>
       <c r="CU74" s="1">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="CV74" s="1">
-        <v>1920</v>
+        <v>1855</v>
       </c>
       <c r="CW74" s="1">
-        <v>4397</v>
+        <v>4402</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25712,28 +25712,28 @@
         <v>174</v>
       </c>
       <c r="B75" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G75" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I75" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J75" s="1">
         <v>0</v>
@@ -26000,16 +26000,16 @@
         <v>0</v>
       </c>
       <c r="CT75" s="1">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="CU75" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CV75" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CW75" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:101">
@@ -26059,7 +26059,7 @@
         <v>10</v>
       </c>
       <c r="P76" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="Q76" s="2">
         <v>2426</v>
@@ -26311,7 +26311,7 @@
         <v>108</v>
       </c>
       <c r="CV76" s="1">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="CW76" s="1">
         <v>3759</v>
@@ -26574,16 +26574,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7275</v>
+        <v>7295</v>
       </c>
       <c r="CI77" s="2">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="CJ77" s="2">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="CK77" s="2">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390850</v>
+        <v>390870</v>
       </c>
       <c r="CU77" s="1">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="CV77" s="1">
-        <v>10210</v>
+        <v>10230</v>
       </c>
       <c r="CW77" s="1">
-        <v>16057</v>
+        <v>16077</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27237,28 +27237,28 @@
         <v>179</v>
       </c>
       <c r="B80" s="1">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C80" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D80" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E80" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" s="1">
         <v>0</v>
@@ -27525,16 +27525,16 @@
         <v>0</v>
       </c>
       <c r="CT80" s="1">
-        <v>1758</v>
+        <v>1764</v>
       </c>
       <c r="CU80" s="1">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="CV80" s="1">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="CW80" s="1">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -28182,7 +28182,7 @@
         <v>61</v>
       </c>
       <c r="L83" s="2">
-        <v>265</v>
+        <v>186</v>
       </c>
       <c r="M83" s="2">
         <v>480</v>
@@ -28446,7 +28446,7 @@
         <v>113</v>
       </c>
       <c r="CV83" s="1">
-        <v>966</v>
+        <v>887</v>
       </c>
       <c r="CW83" s="1">
         <v>5458</v>
@@ -28469,16 +28469,16 @@
         <v>0</v>
       </c>
       <c r="F84" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H84" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I84" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J84" s="1">
         <v>0</v>
@@ -28745,16 +28745,16 @@
         <v>0</v>
       </c>
       <c r="CT84" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="CU84" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV84" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CW84" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:101">
@@ -30012,7 +30012,7 @@
         <v>8</v>
       </c>
       <c r="L89" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="M89" s="2">
         <v>57</v>
@@ -30276,7 +30276,7 @@
         <v>11</v>
       </c>
       <c r="CV89" s="1">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="CW89" s="1">
         <v>218</v>
@@ -36393,7 +36393,7 @@
         <v>21</v>
       </c>
       <c r="D110" s="2">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E110" s="2">
         <v>106</v>
@@ -36681,7 +36681,7 @@
         <v>148</v>
       </c>
       <c r="CV110" s="1">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="CW110" s="1">
         <v>1029</v>
@@ -38349,16 +38349,16 @@
         <v>2</v>
       </c>
       <c r="AT116" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AU116" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV116" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW116" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX116" s="1">
         <v>3</v>
@@ -38505,16 +38505,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21740</v>
+        <v>21741</v>
       </c>
       <c r="CU116" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="CV116" s="1">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="CW116" s="1">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38839,16 +38839,16 @@
         <v>2</v>
       </c>
       <c r="F118" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G118" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J118" s="1">
         <v>0</v>
@@ -39115,16 +39115,16 @@
         <v>0</v>
       </c>
       <c r="CT118" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CU118" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV118" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CW118" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="1:101">
@@ -39258,7 +39258,7 @@
         <v>2</v>
       </c>
       <c r="AR119" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS119" s="2">
         <v>7</v>
@@ -39402,7 +39402,7 @@
         <v>2</v>
       </c>
       <c r="CN119" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CO119" s="2">
         <v>7</v>
@@ -39426,7 +39426,7 @@
         <v>5</v>
       </c>
       <c r="CV119" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CW119" s="1">
         <v>30</v>
@@ -42194,16 +42194,16 @@
         <v>2</v>
       </c>
       <c r="F129" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G129" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I129" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J129" s="1">
         <v>0</v>
@@ -42470,16 +42470,16 @@
         <v>0</v>
       </c>
       <c r="CT129" s="1">
-        <v>3562</v>
+        <v>3563</v>
       </c>
       <c r="CU129" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CV129" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="CW129" s="1">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -45080,7 +45080,7 @@
         <v>14</v>
       </c>
       <c r="BA138" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB138" s="1">
         <v>90</v>
@@ -45224,7 +45224,7 @@
         <v>133</v>
       </c>
       <c r="CW138" s="1">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -46775,7 +46775,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I144" s="2">
         <v>3</v>
@@ -47051,7 +47051,7 @@
         <v>2</v>
       </c>
       <c r="CV144" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW144" s="1">
         <v>67</v>
@@ -47212,7 +47212,7 @@
         <v>0</v>
       </c>
       <c r="AZ145" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA145" s="2">
         <v>7</v>
@@ -47356,7 +47356,7 @@
         <v>16</v>
       </c>
       <c r="CV145" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CW145" s="1">
         <v>135</v>
@@ -48480,7 +48480,7 @@
         <v>1</v>
       </c>
       <c r="BP149" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BQ149" s="2">
         <v>10</v>
@@ -48576,7 +48576,7 @@
         <v>6</v>
       </c>
       <c r="CV149" s="1">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="CW149" s="1">
         <v>64</v>
@@ -50232,16 +50232,16 @@
         <v>0</v>
       </c>
       <c r="AP155" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AQ155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR155" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS155" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT155" s="1">
         <v>1</v>
@@ -50364,16 +50364,16 @@
         <v>0</v>
       </c>
       <c r="CH155" s="1">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="CI155" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ155" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CK155" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CL155" s="1">
         <v>1</v>
@@ -50400,16 +50400,16 @@
         <v>0</v>
       </c>
       <c r="CT155" s="1">
-        <v>2654</v>
+        <v>2659</v>
       </c>
       <c r="CU155" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CV155" s="1">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="CW155" s="1">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50561,16 +50561,16 @@
         <v>0</v>
       </c>
       <c r="AX156" s="1">
+        <v>8</v>
+      </c>
+      <c r="AY156" s="2">
         <v>4</v>
       </c>
-      <c r="AY156" s="2">
-        <v>0</v>
-      </c>
       <c r="AZ156" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA156" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB156" s="1">
         <v>1</v>
@@ -50633,16 +50633,16 @@
         <v>0</v>
       </c>
       <c r="BV156" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ156" s="1">
         <v>0</v>
@@ -50705,16 +50705,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>71479</v>
+        <v>71484</v>
       </c>
       <c r="CU156" s="1">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CV156" s="1">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="CW156" s="1">
-        <v>2528</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -50830,16 +50830,16 @@
         <v>0</v>
       </c>
       <c r="AL157" s="1">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="AM157" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN157" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO157" s="2">
-        <v>-36</v>
+        <v>-34</v>
       </c>
       <c r="AP157" s="1">
         <v>49</v>
@@ -51010,16 +51010,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>166335</v>
+        <v>166337</v>
       </c>
       <c r="CU157" s="1">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="CV157" s="1">
-        <v>5275</v>
+        <v>5277</v>
       </c>
       <c r="CW157" s="1">
-        <v>9208</v>
+        <v>9210</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -53174,16 +53174,16 @@
         <v>0</v>
       </c>
       <c r="F165" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G165" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I165" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J165" s="1">
         <v>0</v>
@@ -53450,16 +53450,16 @@
         <v>0</v>
       </c>
       <c r="CT165" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CU165" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV165" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW165" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:101">
@@ -54089,16 +54089,16 @@
         <v>10</v>
       </c>
       <c r="F168" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" s="1">
         <v>1326</v>
@@ -54365,16 +54365,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="CU168" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CV168" s="1">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CW168" s="1">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54711,16 +54711,16 @@
         <v>0</v>
       </c>
       <c r="J170" s="1">
-        <v>6368</v>
+        <v>6367</v>
       </c>
       <c r="K170" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L170" s="2">
         <v>168</v>
       </c>
       <c r="M170" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N170" s="1">
         <v>2774</v>
@@ -54975,16 +54975,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19519</v>
+        <v>19518</v>
       </c>
       <c r="CU170" s="1">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CV170" s="1">
         <v>501</v>
       </c>
       <c r="CW170" s="1">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -60189,16 +60189,16 @@
         <v>15</v>
       </c>
       <c r="F188" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G188" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H188" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I188" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J188" s="1">
         <v>0</v>
@@ -60465,16 +60465,16 @@
         <v>0</v>
       </c>
       <c r="CT188" s="1">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="CU188" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV188" s="1">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="CW188" s="1">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="189" spans="1:101">
@@ -69717,7 +69717,7 @@
         <v>584</v>
       </c>
       <c r="D65">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E65" t="s">
         <v>715</v>
@@ -69957,7 +69957,7 @@
         <v>596</v>
       </c>
       <c r="D77">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E77" t="s">
         <v>715</v>
@@ -72355,7 +72355,7 @@
         <v>698</v>
       </c>
       <c r="D196">
-        <v>10253</v>
+        <v>10255</v>
       </c>
       <c r="E196" t="s">
         <v>715</v>
@@ -72661,7 +72661,7 @@
         <v>711</v>
       </c>
       <c r="D211">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E211" t="s">
         <v>743</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4174,7 +4174,7 @@
         <v>5</v>
       </c>
       <c r="AO4" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP4" s="1">
         <v>0</v>
@@ -4318,7 +4318,7 @@
         <v>58</v>
       </c>
       <c r="CK4" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="CL4" s="1">
         <v>0</v>
@@ -4354,7 +4354,7 @@
         <v>443</v>
       </c>
       <c r="CW4" s="1">
-        <v>1287</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -5588,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
         <v>3</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="M9" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N9" s="1">
         <v>1558</v>
@@ -5876,10 +5876,10 @@
         <v>5</v>
       </c>
       <c r="CV9" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="CW9" s="1">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -6608,7 +6608,7 @@
         <v>125</v>
       </c>
       <c r="AM12" s="2">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="AN12" s="2">
         <v>72</v>
@@ -6752,7 +6752,7 @@
         <v>145</v>
       </c>
       <c r="CI12" s="2">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="CJ12" s="2">
         <v>93</v>
@@ -6788,7 +6788,7 @@
         <v>410</v>
       </c>
       <c r="CU12" s="1">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="CV12" s="1">
         <v>181</v>
@@ -8339,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -8348,7 +8348,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -8615,7 +8615,7 @@
         <v>0</v>
       </c>
       <c r="CT18" s="1">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CU18" s="1">
         <v>1</v>
@@ -8624,7 +8624,7 @@
         <v>3</v>
       </c>
       <c r="CW18" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:101">
@@ -8973,16 +8973,16 @@
         <v>58</v>
       </c>
       <c r="N20" s="1">
-        <v>12650</v>
+        <v>12653</v>
       </c>
       <c r="O20" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P20" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q20" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9225,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20683</v>
+        <v>20686</v>
       </c>
       <c r="CU20" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="CV20" s="1">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CW20" s="1">
-        <v>918</v>
+        <v>921</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9864,16 +9864,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="1">
         <v>3</v>
@@ -10140,16 +10140,16 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="CU23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV23" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CW23" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -12292,16 +12292,16 @@
         <v>130</v>
       </c>
       <c r="B31" s="1">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C31" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F31" s="1">
         <v>21</v>
@@ -12580,16 +12580,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>5992</v>
+        <v>5995</v>
       </c>
       <c r="CU31" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="CV31" s="1">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="CW31" s="1">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -13237,7 +13237,7 @@
         <v>8</v>
       </c>
       <c r="L34" s="2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M34" s="2">
         <v>49</v>
@@ -13501,7 +13501,7 @@
         <v>12</v>
       </c>
       <c r="CV34" s="1">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="CW34" s="1">
         <v>146</v>
@@ -14427,16 +14427,16 @@
         <v>137</v>
       </c>
       <c r="B38" s="1">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C38" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1">
         <v>21</v>
@@ -14715,16 +14715,16 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="CU38" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CV38" s="1">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CW38" s="1">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -21541,7 +21541,7 @@
         <v>23</v>
       </c>
       <c r="AI61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ61" s="2">
         <v>1</v>
@@ -21733,7 +21733,7 @@
         <v>65931</v>
       </c>
       <c r="CU61" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CV61" s="1">
         <v>481</v>
@@ -22806,16 +22806,16 @@
         <v>0</v>
       </c>
       <c r="AX65" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ65" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA65" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB65" s="1">
         <v>24</v>
@@ -22950,16 +22950,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67185</v>
+        <v>67186</v>
       </c>
       <c r="CU65" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CV65" s="1">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="CW65" s="1">
-        <v>3559</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -24196,7 +24196,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="1">
         <v>14</v>
@@ -24484,7 +24484,7 @@
         <v>60</v>
       </c>
       <c r="CW70" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24809,16 +24809,16 @@
         <v>4</v>
       </c>
       <c r="F72" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J72" s="1">
         <v>78</v>
@@ -25085,16 +25085,16 @@
         <v>0</v>
       </c>
       <c r="CT72" s="1">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="CU72" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CV72" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CW72" s="1">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25662,13 +25662,13 @@
         <v>16168</v>
       </c>
       <c r="CI74" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="CJ74" s="2">
         <v>194</v>
       </c>
       <c r="CK74" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25698,13 +25698,13 @@
         <v>171615</v>
       </c>
       <c r="CU74" s="1">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CV74" s="1">
         <v>1855</v>
       </c>
       <c r="CW74" s="1">
-        <v>4402</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26325,7 +26325,7 @@
         <v>10858</v>
       </c>
       <c r="C77" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D77" s="2">
         <v>-6</v>
@@ -26409,7 +26409,7 @@
         <v>1182</v>
       </c>
       <c r="AE77" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF77" s="2">
         <v>42</v>
@@ -26430,16 +26430,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="AM77" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AN77" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AO77" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390870</v>
+        <v>390873</v>
       </c>
       <c r="CU77" s="1">
-        <v>306</v>
+        <v>254</v>
       </c>
       <c r="CV77" s="1">
-        <v>10230</v>
+        <v>10233</v>
       </c>
       <c r="CW77" s="1">
-        <v>16077</v>
+        <v>16080</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -29175,16 +29175,16 @@
         <v>0</v>
       </c>
       <c r="AL86" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AM86" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN86" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO86" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP86" s="1">
         <v>52</v>
@@ -29214,7 +29214,7 @@
         <v>8</v>
       </c>
       <c r="AY86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ86" s="2">
         <v>1</v>
@@ -29355,16 +29355,16 @@
         <v>0</v>
       </c>
       <c r="CT86" s="1">
-        <v>2830</v>
+        <v>2832</v>
       </c>
       <c r="CU86" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV86" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CW86" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -31313,7 +31313,7 @@
         <v>81</v>
       </c>
       <c r="AM93" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN93" s="2">
         <v>5</v>
@@ -31457,7 +31457,7 @@
         <v>99</v>
       </c>
       <c r="CI93" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ93" s="2">
         <v>6</v>
@@ -31493,7 +31493,7 @@
         <v>1178</v>
       </c>
       <c r="CU93" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CV93" s="1">
         <v>29</v>
@@ -32437,7 +32437,7 @@
         <v>78</v>
       </c>
       <c r="G97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="2">
         <v>3</v>
@@ -32713,7 +32713,7 @@
         <v>222</v>
       </c>
       <c r="CU97" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV97" s="1">
         <v>9</v>
@@ -33352,7 +33352,7 @@
         <v>48</v>
       </c>
       <c r="G100" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="2">
         <v>3</v>
@@ -33628,7 +33628,7 @@
         <v>160</v>
       </c>
       <c r="CU100" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV100" s="1">
         <v>22</v>
@@ -36029,16 +36029,16 @@
         <v>0</v>
       </c>
       <c r="CH108" s="1">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="CI108" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CJ108" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CK108" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CL108" s="1">
         <v>7</v>
@@ -36065,16 +36065,16 @@
         <v>0</v>
       </c>
       <c r="CT108" s="1">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="CU108" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CV108" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="CW108" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:101">
@@ -36396,7 +36396,7 @@
         <v>42</v>
       </c>
       <c r="E110" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -36684,7 +36684,7 @@
         <v>420</v>
       </c>
       <c r="CW110" s="1">
-        <v>1029</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -38355,7 +38355,7 @@
         <v>2</v>
       </c>
       <c r="AV116" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW116" s="2">
         <v>9</v>
@@ -38511,7 +38511,7 @@
         <v>88</v>
       </c>
       <c r="CV116" s="1">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="CW116" s="1">
         <v>1154</v>
@@ -40373,7 +40373,7 @@
         <v>3</v>
       </c>
       <c r="I123" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J123" s="1">
         <v>142</v>
@@ -40649,7 +40649,7 @@
         <v>13</v>
       </c>
       <c r="CW123" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -40678,7 +40678,7 @@
         <v>3</v>
       </c>
       <c r="I124" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J124" s="1">
         <v>0</v>
@@ -40954,7 +40954,7 @@
         <v>3</v>
       </c>
       <c r="CW124" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:101">
@@ -41572,16 +41572,16 @@
         <v>226</v>
       </c>
       <c r="B127" s="1">
-        <v>1061</v>
+        <v>1078</v>
       </c>
       <c r="C127" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D127" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E127" s="2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -41860,16 +41860,16 @@
         <v>0</v>
       </c>
       <c r="CT127" s="1">
-        <v>2566</v>
+        <v>2583</v>
       </c>
       <c r="CU127" s="1">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="CV127" s="1">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="CW127" s="1">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:101">
@@ -43794,7 +43794,7 @@
         <v>79709</v>
       </c>
       <c r="AE134" s="2">
-        <v>1746</v>
+        <v>0</v>
       </c>
       <c r="AF134" s="2">
         <v>1763</v>
@@ -43998,7 +43998,7 @@
         <v>134448</v>
       </c>
       <c r="CU134" s="1">
-        <v>1770</v>
+        <v>24</v>
       </c>
       <c r="CV134" s="1">
         <v>2550</v>
@@ -44099,10 +44099,10 @@
         <v>11788</v>
       </c>
       <c r="AE135" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AF135" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG135" s="2">
         <v>764</v>
@@ -44303,10 +44303,10 @@
         <v>62642</v>
       </c>
       <c r="CU135" s="1">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="CV135" s="1">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="CW135" s="1">
         <v>2757</v>
@@ -45080,7 +45080,7 @@
         <v>14</v>
       </c>
       <c r="BA138" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BB138" s="1">
         <v>90</v>
@@ -45224,7 +45224,7 @@
         <v>133</v>
       </c>
       <c r="CW138" s="1">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -45540,7 +45540,7 @@
         <v>119</v>
       </c>
       <c r="C140" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" s="2">
         <v>3</v>
@@ -45660,7 +45660,7 @@
         <v>34</v>
       </c>
       <c r="AQ140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR140" s="2">
         <v>2</v>
@@ -45804,7 +45804,7 @@
         <v>11</v>
       </c>
       <c r="CM140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN140" s="2">
         <v>2</v>
@@ -45828,7 +45828,7 @@
         <v>570</v>
       </c>
       <c r="CU140" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CV140" s="1">
         <v>12</v>
@@ -48477,7 +48477,7 @@
         <v>11</v>
       </c>
       <c r="BO149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP149" s="2">
         <v>3</v>
@@ -48573,7 +48573,7 @@
         <v>904</v>
       </c>
       <c r="CU149" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV149" s="1">
         <v>29</v>
@@ -50124,16 +50124,16 @@
         <v>2</v>
       </c>
       <c r="F155" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G155" s="2">
         <v>1</v>
       </c>
       <c r="H155" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I155" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J155" s="1">
         <v>557</v>
@@ -50400,16 +50400,16 @@
         <v>0</v>
       </c>
       <c r="CT155" s="1">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="CU155" s="1">
         <v>10</v>
       </c>
       <c r="CV155" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="CW155" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -51060,13 +51060,13 @@
         <v>218</v>
       </c>
       <c r="M158" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N158" s="1">
         <v>3024</v>
       </c>
       <c r="O158" s="2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="P158" s="2">
         <v>55</v>
@@ -51318,13 +51318,13 @@
         <v>25461</v>
       </c>
       <c r="CU158" s="1">
-        <v>345</v>
+        <v>290</v>
       </c>
       <c r="CV158" s="1">
         <v>840</v>
       </c>
       <c r="CW158" s="1">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -53479,16 +53479,16 @@
         <v>19</v>
       </c>
       <c r="F166" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J166" s="1">
         <v>1698</v>
@@ -53506,7 +53506,7 @@
         <v>2217</v>
       </c>
       <c r="O166" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P166" s="2">
         <v>46</v>
@@ -53755,16 +53755,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>5252</v>
+        <v>5253</v>
       </c>
       <c r="CU166" s="1">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CV166" s="1">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="CW166" s="1">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54714,7 +54714,7 @@
         <v>6367</v>
       </c>
       <c r="K170" s="2">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="L170" s="2">
         <v>168</v>
@@ -54978,7 +54978,7 @@
         <v>19518</v>
       </c>
       <c r="CU170" s="1">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="CV170" s="1">
         <v>501</v>
@@ -55019,7 +55019,7 @@
         <v>284</v>
       </c>
       <c r="K171" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L171" s="2">
         <v>17</v>
@@ -55283,7 +55283,7 @@
         <v>5829</v>
       </c>
       <c r="CU171" s="1">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="CV171" s="1">
         <v>45</v>
@@ -57444,16 +57444,16 @@
         <v>1</v>
       </c>
       <c r="F179" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G179" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I179" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J179" s="1">
         <v>0</v>
@@ -57720,16 +57720,16 @@
         <v>0</v>
       </c>
       <c r="CT179" s="1">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="CU179" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV179" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CW179" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -61412,7 +61412,7 @@
         <v>76</v>
       </c>
       <c r="G192" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H192" s="2">
         <v>3</v>
@@ -61688,7 +61688,7 @@
         <v>611</v>
       </c>
       <c r="CU192" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV192" s="1">
         <v>10</v>
@@ -67007,13 +67007,13 @@
         <v>1</v>
       </c>
       <c r="AP210" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AQ210" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR210" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS210" s="2">
         <v>5</v>
@@ -67139,16 +67139,16 @@
         <v>0</v>
       </c>
       <c r="CH210" s="1">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="CI210" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CJ210" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CK210" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CL210" s="1">
         <v>23</v>
@@ -67160,7 +67160,7 @@
         <v>-1</v>
       </c>
       <c r="CO210" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP210" s="1">
         <v>0</v>
@@ -67175,16 +67175,16 @@
         <v>0</v>
       </c>
       <c r="CT210" s="1">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="CU210" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CV210" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CW210" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -67285,7 +67285,7 @@
         <v>382</v>
       </c>
       <c r="AG211" s="2">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="AH211" s="1">
         <v>3</v>
@@ -67489,7 +67489,7 @@
         <v>504</v>
       </c>
       <c r="CW211" s="1">
-        <v>708</v>
+        <v>692</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -67805,7 +67805,7 @@
         <v>31</v>
       </c>
       <c r="C213" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D213" s="2">
         <v>5</v>
@@ -68093,7 +68093,7 @@
         <v>269</v>
       </c>
       <c r="CU213" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CV213" s="1">
         <v>24</v>
@@ -68122,7 +68122,7 @@
         <v>70</v>
       </c>
       <c r="G214" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H214" s="2">
         <v>5</v>
@@ -68398,7 +68398,7 @@
         <v>165</v>
       </c>
       <c r="CU214" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV214" s="1">
         <v>5</v>
@@ -69897,7 +69897,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2196</v>
+        <v>2205</v>
       </c>
       <c r="E74" t="s">
         <v>715</v>
@@ -71326,7 +71326,7 @@
         <v>656</v>
       </c>
       <c r="D145">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E145" t="s">
         <v>715</v>
@@ -72438,7 +72438,7 @@
         <v>702</v>
       </c>
       <c r="D200">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E200" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="828">
   <si>
     <t>ati_all</t>
   </si>
@@ -995,15 +995,9 @@
     <t>Atlantic Pilotage Authority Canada | Administration de pilotage de l'Atlantique Canada</t>
   </si>
   <si>
-    <t>Asia-Pacific Foundation of Canada | Fondation Asie Pacifique du Canada</t>
-  </si>
-  <si>
     <t>Administrative Tribunals Support Service of Canada | Service canadien d'appui aux tribunaux administratifs</t>
   </si>
   <si>
-    <t>Bank of Canada | Banque du Canada</t>
-  </si>
-  <si>
     <t>British Columbia Treaty Commission | Commission des Traités de la Colombie-Britannique</t>
   </si>
   <si>
@@ -1013,39 +1007,24 @@
     <t>Belledune Port Authority | Administration portuaire de Belledune</t>
   </si>
   <si>
-    <t>Canadian Northern Economic Development Agency | Agence canadienne de développement économique du Nord</t>
-  </si>
-  <si>
     <t>Courts Administration Service | Service administratif des tribunaux judiciaires</t>
   </si>
   <si>
     <t>Accessibility Standards Canada | Normes d’accessibilité Canada</t>
   </si>
   <si>
-    <t>Canadian Air Transport Security Authority | Administration canadienne de la sûreté du transport aérien</t>
-  </si>
-  <si>
     <t>Copyright Board Canada | Commission du droit d'auteur du Canada</t>
   </si>
   <si>
     <t>Canadian Broadcasting Company | Radio-Canada</t>
   </si>
   <si>
-    <t>Canada Border Services Agency | Agence des services frontaliers du Canada</t>
-  </si>
-  <si>
     <t>Canada Council for the Arts | Conseil des arts du Canada</t>
   </si>
   <si>
     <t>Canadian Commercial Corporation | Corporation commerciale canadienne</t>
   </si>
   <si>
-    <t>Canadian Centre for Occupational Health and Safety | Centre canadien d'hygiène et de sécurité au travail</t>
-  </si>
-  <si>
-    <t>Canadian Cultural Property Export Review Board | Commission canadienne d'examen des exportations de biens culturels</t>
-  </si>
-  <si>
     <t>Canadian Dairy Commission | Commission canadienne du lait</t>
   </si>
   <si>
@@ -1634,15 +1613,9 @@
     <t>bbradley@atlanticpilotage.com</t>
   </si>
   <si>
-    <t>atip.coordinator@asiapacific.ca</t>
-  </si>
-  <si>
     <t>ATIP-AIPRP@tribunal.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@bankofcanada.ca</t>
-  </si>
-  <si>
     <t>sgustin@bctreaty.ca</t>
   </si>
   <si>
@@ -1652,31 +1625,19 @@
     <t>moffitt@portofbelledune.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@cannor.gc.ca</t>
-  </si>
-  <si>
     <t>NC-COMM-ATIP-AIPRP-GD@hrsdc-rhdcc.gc.ca</t>
   </si>
   <si>
-    <t>atip@catsa.gc.ca</t>
-  </si>
-  <si>
     <t>nancy.laframboise@cb-cda.gc.ca</t>
   </si>
   <si>
     <t>Peter.Hull@cbc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@cbsa-asfc.gc.ca</t>
-  </si>
-  <si>
     <t>atip-aiprp@canadacouncil.ca</t>
   </si>
   <si>
     <t>atip.aiprp@ccc.ca</t>
-  </si>
-  <si>
-    <t>atip_aiprp@ccohs.ca</t>
   </si>
   <si>
     <t>priscilla.revolus@cdc-ccl.gc.ca</t>
@@ -3142,292 +3103,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="AO1" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="AP1" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="AR1" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="AU1" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="AV1" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="AW1" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="AX1" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="AY1" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="AZ1" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>793</v>
-      </c>
-      <c r="AS1" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="AT1" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="AU1" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="AV1" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="AW1" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="AX1" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="AY1" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="AZ1" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="BA1" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="BB1" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="BC1" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="BD1" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="BE1" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -6500,7 +6461,7 @@
         <v>118</v>
       </c>
       <c r="C12" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>14</v>
@@ -6788,7 +6749,7 @@
         <v>410</v>
       </c>
       <c r="CU12" s="1">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="CV12" s="1">
         <v>181</v>
@@ -7374,7 +7335,7 @@
         <v>29</v>
       </c>
       <c r="CM14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN14" s="2">
         <v>1</v>
@@ -7398,7 +7359,7 @@
         <v>3097</v>
       </c>
       <c r="CU14" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV14" s="1">
         <v>57</v>
@@ -11464,7 +11425,7 @@
         <v>16634</v>
       </c>
       <c r="AE28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="2">
         <v>173</v>
@@ -11668,7 +11629,7 @@
         <v>24074</v>
       </c>
       <c r="CU28" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV28" s="1">
         <v>262</v>
@@ -12747,7 +12708,7 @@
         <v>1</v>
       </c>
       <c r="AZ32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA32" s="2">
         <v>3</v>
@@ -12891,7 +12852,7 @@
         <v>27</v>
       </c>
       <c r="CV32" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="CW32" s="1">
         <v>545</v>
@@ -14550,7 +14511,7 @@
         <v>42</v>
       </c>
       <c r="AQ38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR38" s="2">
         <v>4</v>
@@ -14694,7 +14655,7 @@
         <v>30</v>
       </c>
       <c r="CM38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN38" s="2">
         <v>3</v>
@@ -14718,7 +14679,7 @@
         <v>1951</v>
       </c>
       <c r="CU38" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CV38" s="1">
         <v>48</v>
@@ -19017,7 +18978,7 @@
         <v>74</v>
       </c>
       <c r="G53" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2">
         <v>2</v>
@@ -19293,7 +19254,7 @@
         <v>353</v>
       </c>
       <c r="CU53" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CV53" s="1">
         <v>41</v>
@@ -22079,7 +22040,7 @@
         <v>327</v>
       </c>
       <c r="K63" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2">
         <v>8</v>
@@ -22343,7 +22304,7 @@
         <v>2863</v>
       </c>
       <c r="CU63" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CV63" s="1">
         <v>85</v>
@@ -24214,7 +24175,7 @@
         <v>281</v>
       </c>
       <c r="K70" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L70" s="2">
         <v>21</v>
@@ -24478,7 +24439,7 @@
         <v>2257</v>
       </c>
       <c r="CU70" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CV70" s="1">
         <v>60</v>
@@ -26349,7 +26310,7 @@
         <v>4880</v>
       </c>
       <c r="K77" s="2">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="L77" s="2">
         <v>180</v>
@@ -26577,7 +26538,7 @@
         <v>7295</v>
       </c>
       <c r="CI77" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="CJ77" s="2">
         <v>362</v>
@@ -26613,7 +26574,7 @@
         <v>390873</v>
       </c>
       <c r="CU77" s="1">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="CV77" s="1">
         <v>10233</v>
@@ -27581,7 +27542,7 @@
         <v>3606</v>
       </c>
       <c r="O81" s="2">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P81" s="2">
         <v>71</v>
@@ -27833,7 +27794,7 @@
         <v>6405</v>
       </c>
       <c r="CU81" s="1">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="CV81" s="1">
         <v>155</v>
@@ -34085,7 +34046,7 @@
         <v>1</v>
       </c>
       <c r="AV102" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW102" s="2">
         <v>5</v>
@@ -34097,7 +34058,7 @@
         <v>0</v>
       </c>
       <c r="AZ102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA102" s="2">
         <v>2</v>
@@ -34241,7 +34202,7 @@
         <v>190</v>
       </c>
       <c r="CV102" s="1">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="CW102" s="1">
         <v>1820</v>
@@ -38588,7 +38549,7 @@
         <v>0</v>
       </c>
       <c r="X117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y117" s="2">
         <v>1</v>
@@ -38816,7 +38777,7 @@
         <v>171</v>
       </c>
       <c r="CV117" s="1">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="CW117" s="1">
         <v>1217</v>
@@ -39745,7 +39706,7 @@
         <v>2</v>
       </c>
       <c r="C121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" s="2">
         <v>1</v>
@@ -40033,7 +39994,7 @@
         <v>80</v>
       </c>
       <c r="CU121" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV121" s="1">
         <v>4</v>
@@ -40672,7 +40633,7 @@
         <v>67</v>
       </c>
       <c r="G124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="2">
         <v>3</v>
@@ -40948,7 +40909,7 @@
         <v>67</v>
       </c>
       <c r="CU124" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV124" s="1">
         <v>3</v>
@@ -42197,7 +42158,7 @@
         <v>44</v>
       </c>
       <c r="G129" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H129" s="2">
         <v>3</v>
@@ -42473,7 +42434,7 @@
         <v>3563</v>
       </c>
       <c r="CU129" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV129" s="1">
         <v>106</v>
@@ -44344,7 +44305,7 @@
         <v>164</v>
       </c>
       <c r="K136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="2">
         <v>2</v>
@@ -44608,7 +44569,7 @@
         <v>158865</v>
       </c>
       <c r="CU136" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CV136" s="1">
         <v>5078</v>
@@ -46174,7 +46135,7 @@
         <v>429</v>
       </c>
       <c r="K142" s="2">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="2">
         <v>32</v>
@@ -46438,7 +46399,7 @@
         <v>1637</v>
       </c>
       <c r="CU142" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CV142" s="1">
         <v>60</v>
@@ -49212,7 +49173,7 @@
         <v>22</v>
       </c>
       <c r="G152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152" s="2">
         <v>1</v>
@@ -49488,7 +49449,7 @@
         <v>3009</v>
       </c>
       <c r="CU152" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CV152" s="1">
         <v>105</v>
@@ -51054,7 +51015,7 @@
         <v>7081</v>
       </c>
       <c r="K158" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L158" s="2">
         <v>218</v>
@@ -51318,7 +51279,7 @@
         <v>25461</v>
       </c>
       <c r="CU158" s="1">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CV158" s="1">
         <v>840</v>
@@ -58057,7 +58018,7 @@
         <v>70</v>
       </c>
       <c r="G181" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H181" s="2">
         <v>2</v>
@@ -58333,7 +58294,7 @@
         <v>78</v>
       </c>
       <c r="CU181" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV181" s="1">
         <v>2</v>
@@ -68414,7 +68375,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="30" customHeight="1">
@@ -68448,16 +68409,16 @@
         <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="F2" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -68468,16 +68429,16 @@
         <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="D3">
         <v>398</v>
       </c>
       <c r="E3" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F3" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -68488,16 +68449,16 @@
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="D4">
         <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F4" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -68508,16 +68469,16 @@
         <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="D5">
         <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F5" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -68528,19 +68489,19 @@
         <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F6" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="G6" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -68551,1290 +68512,1290 @@
         <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="D7">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F7" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
         <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F8" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
         <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D9">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F9" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F10" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="F11" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
         <v>330</v>
       </c>
-      <c r="C12" t="s">
-        <v>543</v>
-      </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F12" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F13" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F14" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
+      <c r="C15" t="s">
+        <v>538</v>
+      </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F15" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="F16" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F17" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
       <c r="C18" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F18" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
         <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>549</v>
+        <v>526</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F19" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F20" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
         <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F21" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="F22" t="s">
-        <v>747</v>
+        <v>735</v>
+      </c>
+      <c r="G22" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
         <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F23" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
         <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F24" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
         <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="E25" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F25" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="F26" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B27" t="s">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="D27">
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F27" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s">
         <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="D28">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="F28" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="F29" t="s">
-        <v>748</v>
-      </c>
-      <c r="G29" t="s">
-        <v>533</v>
+        <v>735</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
         <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="F30" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
         <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D31">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F31" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
         <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="D32">
-        <v>267</v>
+        <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="F32" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
         <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E33" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="F33" t="s">
-        <v>748</v>
+        <v>732</v>
+      </c>
+      <c r="G33" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B34" t="s">
         <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F34" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
         <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="F35" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
         <v>354</v>
       </c>
-      <c r="C36" t="s">
-        <v>562</v>
-      </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="F36" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B37" t="s">
         <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E37" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F37" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B38" t="s">
         <v>356</v>
       </c>
       <c r="C38" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="F38" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
       </c>
       <c r="C39" t="s">
-        <v>564</v>
+        <v>532</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>724</v>
+        <v>702</v>
       </c>
       <c r="F39" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B40" t="s">
         <v>358</v>
       </c>
       <c r="C40" t="s">
-        <v>565</v>
+        <v>532</v>
       </c>
       <c r="D40">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F40" t="s">
-        <v>745</v>
-      </c>
-      <c r="G40" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s">
         <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="F41" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
         <v>360</v>
       </c>
       <c r="C42" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="F42" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
         <v>361</v>
       </c>
+      <c r="C43" t="s">
+        <v>556</v>
+      </c>
       <c r="D43">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F43" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B44" t="s">
         <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D44">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E44" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F44" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s">
         <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="F45" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
         <v>364</v>
       </c>
       <c r="C46" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F46" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B47" t="s">
         <v>365</v>
       </c>
       <c r="C47" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F47" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B48" t="s">
         <v>366</v>
       </c>
       <c r="C48" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F48" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B49" t="s">
         <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F49" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B50" t="s">
         <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F50" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B51" t="s">
         <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D51">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="F51" t="s">
-        <v>747</v>
+        <v>735</v>
+      </c>
+      <c r="G51" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B52" t="s">
         <v>370</v>
       </c>
       <c r="C52" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F52" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B53" t="s">
         <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F53" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B54" t="s">
         <v>372</v>
       </c>
       <c r="C54" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="E54" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F54" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B55" t="s">
         <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="F55" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B56" t="s">
         <v>374</v>
       </c>
       <c r="C56" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D56">
-        <v>193</v>
+        <v>94</v>
       </c>
       <c r="E56" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F56" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B57" t="s">
         <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E57" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F57" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
         <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="E58" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="F58" t="s">
-        <v>748</v>
-      </c>
-      <c r="G58" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
         <v>377</v>
       </c>
       <c r="C59" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D59">
-        <v>32</v>
+        <v>332</v>
       </c>
       <c r="E59" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F59" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B60" t="s">
         <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F60" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B61" t="s">
         <v>379</v>
       </c>
       <c r="C61" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D61">
-        <v>332</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F61" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B62" t="s">
         <v>380</v>
       </c>
       <c r="C62" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>724</v>
+        <v>702</v>
       </c>
       <c r="F62" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B63" t="s">
         <v>381</v>
       </c>
       <c r="C63" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="D63">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F63" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B64" t="s">
         <v>382</v>
       </c>
       <c r="C64" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D64">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F64" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B65" t="s">
         <v>383</v>
       </c>
       <c r="C65" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D65">
-        <v>272</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F65" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B66" t="s">
         <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D66">
-        <v>332</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F66" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B67" t="s">
         <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D67">
-        <v>19</v>
+        <v>2205</v>
       </c>
       <c r="E67" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F67" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B68" t="s">
         <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D68">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E68" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F68" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B69" t="s">
         <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D69">
-        <v>19</v>
+        <v>915</v>
       </c>
       <c r="E69" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F69" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B70" t="s">
         <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D70">
-        <v>8</v>
+        <v>175</v>
       </c>
       <c r="E70" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F70" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B71" t="s">
         <v>389</v>
       </c>
       <c r="C71" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -69843,2891 +69804,2751 @@
         <v>715</v>
       </c>
       <c r="F71" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B72" t="s">
         <v>390</v>
       </c>
       <c r="C72" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>1197</v>
       </c>
       <c r="E72" t="s">
-        <v>726</v>
+        <v>702</v>
       </c>
       <c r="F72" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B73" t="s">
         <v>391</v>
       </c>
       <c r="C73" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F73" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B74" t="s">
         <v>392</v>
       </c>
       <c r="C74" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="D74">
-        <v>2205</v>
+        <v>53</v>
       </c>
       <c r="E74" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F74" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B75" t="s">
         <v>393</v>
       </c>
       <c r="C75" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>727</v>
+        <v>702</v>
       </c>
       <c r="F75" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B76" t="s">
         <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>595</v>
+        <v>536</v>
       </c>
       <c r="D76">
-        <v>915</v>
+        <v>265</v>
       </c>
       <c r="E76" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F76" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B77" t="s">
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="D77">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F77" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B78" t="s">
         <v>396</v>
       </c>
       <c r="C78" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>728</v>
+        <v>702</v>
       </c>
       <c r="F78" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B79" t="s">
         <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="D79">
-        <v>1197</v>
+        <v>36</v>
       </c>
       <c r="E79" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F79" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B80" t="s">
         <v>398</v>
       </c>
       <c r="C80" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D80">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F80" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B81" t="s">
         <v>399</v>
       </c>
       <c r="C81" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="D81">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F81" t="s">
-        <v>748</v>
+        <v>733</v>
+      </c>
+      <c r="G81" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B82" t="s">
         <v>400</v>
       </c>
       <c r="C82" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E82" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F82" t="s">
-        <v>748</v>
+        <v>733</v>
+      </c>
+      <c r="G82" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B83" t="s">
         <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>546</v>
+        <v>594</v>
       </c>
       <c r="D83">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F83" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B84" t="s">
         <v>402</v>
       </c>
       <c r="C84" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E84" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F84" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B85" t="s">
         <v>403</v>
       </c>
       <c r="C85" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D85">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E85" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F85" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B86" t="s">
         <v>404</v>
       </c>
-      <c r="C86" t="s">
-        <v>603</v>
-      </c>
       <c r="D86">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F86" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B87" t="s">
         <v>405</v>
       </c>
       <c r="C87" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F87" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B88" t="s">
         <v>406</v>
       </c>
       <c r="C88" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="D88">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F88" t="s">
-        <v>746</v>
-      </c>
-      <c r="G88" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B89" t="s">
         <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="D89">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="F89" t="s">
-        <v>746</v>
-      </c>
-      <c r="G89" t="s">
-        <v>606</v>
+        <v>733</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B90" t="s">
         <v>408</v>
       </c>
       <c r="C90" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F90" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
         <v>409</v>
       </c>
       <c r="C91" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="D91">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F91" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B92" t="s">
         <v>410</v>
       </c>
       <c r="C92" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="D92">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F92" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B93" t="s">
         <v>411</v>
       </c>
+      <c r="C93" t="s">
+        <v>603</v>
+      </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F93" t="s">
-        <v>748</v>
+        <v>735</v>
+      </c>
+      <c r="G93" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B94" t="s">
         <v>412</v>
       </c>
       <c r="C94" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="F94" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B95" t="s">
         <v>413</v>
       </c>
       <c r="C95" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>2978</v>
       </c>
       <c r="E95" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F95" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B96" t="s">
         <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F96" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B97" t="s">
         <v>415</v>
       </c>
       <c r="C97" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="F97" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B98" t="s">
         <v>416</v>
       </c>
       <c r="C98" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="E98" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F98" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B99" t="s">
         <v>417</v>
       </c>
       <c r="C99" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="E99" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="F99" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B100" t="s">
         <v>418</v>
       </c>
       <c r="C100" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F100" t="s">
-        <v>748</v>
-      </c>
-      <c r="G100" t="s">
-        <v>616</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B101" t="s">
         <v>419</v>
       </c>
       <c r="C101" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E101" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F101" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B102" t="s">
         <v>420</v>
       </c>
       <c r="C102" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D102">
-        <v>2978</v>
+        <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="F102" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B103" t="s">
         <v>421</v>
       </c>
       <c r="C103" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>730</v>
+        <v>702</v>
       </c>
       <c r="F103" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B104" t="s">
         <v>422</v>
       </c>
       <c r="C104" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="F104" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B105" t="s">
         <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D105">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F105" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B106" t="s">
         <v>424</v>
       </c>
       <c r="C106" t="s">
-        <v>622</v>
+        <v>528</v>
       </c>
       <c r="D106">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="E106" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="F106" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
         <v>425</v>
       </c>
       <c r="C107" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F107" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B108" t="s">
         <v>426</v>
       </c>
       <c r="C108" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="D108">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="F108" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B109" t="s">
         <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="E109" t="s">
+        <v>702</v>
+      </c>
+      <c r="F109" t="s">
         <v>732</v>
       </c>
-      <c r="F109" t="s">
-        <v>748</v>
-      </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B110" t="s">
         <v>428</v>
       </c>
       <c r="C110" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="D110">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E110" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F110" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B111" t="s">
         <v>429</v>
       </c>
       <c r="C111" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F111" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B112" t="s">
         <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="D112">
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F112" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B113" t="s">
         <v>431</v>
       </c>
       <c r="C113" t="s">
-        <v>535</v>
+        <v>621</v>
       </c>
       <c r="D113">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E113" t="s">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="F113" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B114" t="s">
         <v>432</v>
       </c>
       <c r="C114" t="s">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F114" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B115" t="s">
         <v>433</v>
       </c>
       <c r="C115" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>734</v>
+        <v>702</v>
       </c>
       <c r="F115" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B116" t="s">
         <v>434</v>
       </c>
       <c r="C116" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="D116">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F116" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B117" t="s">
         <v>435</v>
       </c>
       <c r="C117" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="D117">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F117" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B118" t="s">
         <v>436</v>
       </c>
       <c r="C118" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F118" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B119" t="s">
         <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F119" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B120" t="s">
         <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D120">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F120" t="s">
-        <v>747</v>
+        <v>734</v>
+      </c>
+      <c r="G120" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B121" t="s">
         <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="F121" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B122" t="s">
         <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F122" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B123" t="s">
         <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F123" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B124" t="s">
         <v>442</v>
       </c>
       <c r="C124" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="F124" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B125" t="s">
         <v>443</v>
       </c>
       <c r="C125" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F125" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B126" t="s">
         <v>444</v>
       </c>
       <c r="C126" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F126" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B127" t="s">
         <v>445</v>
       </c>
       <c r="C127" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D127">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E127" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F127" t="s">
-        <v>747</v>
-      </c>
-      <c r="G127" t="s">
-        <v>640</v>
+        <v>731</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B128" t="s">
         <v>446</v>
       </c>
       <c r="C128" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>10260</v>
       </c>
       <c r="E128" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F128" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B129" t="s">
         <v>447</v>
       </c>
       <c r="C129" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="D129">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F129" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B130" t="s">
         <v>448</v>
       </c>
       <c r="C130" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="F130" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B131" t="s">
         <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="E131" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="F131" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B132" t="s">
         <v>450</v>
       </c>
       <c r="C132" t="s">
-        <v>645</v>
+        <v>586</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="F132" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B133" t="s">
         <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F133" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B134" t="s">
         <v>452</v>
       </c>
       <c r="C134" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="D134">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E134" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F134" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B135" t="s">
         <v>453</v>
       </c>
       <c r="C135" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D135">
-        <v>10260</v>
+        <v>22</v>
       </c>
       <c r="E135" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F135" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B136" t="s">
         <v>454</v>
       </c>
       <c r="C136" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F136" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B137" t="s">
         <v>455</v>
       </c>
       <c r="C137" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E137" t="s">
+        <v>702</v>
+      </c>
+      <c r="F137" t="s">
         <v>735</v>
       </c>
-      <c r="F137" t="s">
-        <v>746</v>
-      </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B138" t="s">
         <v>456</v>
       </c>
       <c r="C138" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="D138">
-        <v>374</v>
+        <v>49</v>
       </c>
       <c r="E138" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F138" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B139" t="s">
         <v>457</v>
       </c>
       <c r="C139" t="s">
-        <v>599</v>
+        <v>555</v>
       </c>
       <c r="D139">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>736</v>
+        <v>707</v>
       </c>
       <c r="F139" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B140" t="s">
         <v>458</v>
       </c>
       <c r="C140" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F140" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B141" t="s">
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="D141">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F141" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B142" t="s">
         <v>460</v>
       </c>
-      <c r="C142" t="s">
-        <v>653</v>
-      </c>
       <c r="D142">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F142" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B143" t="s">
         <v>461</v>
       </c>
       <c r="C143" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="D143">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="F143" t="s">
-        <v>746</v>
+        <v>735</v>
+      </c>
+      <c r="G143" t="s">
+        <v>739</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B144" t="s">
         <v>462</v>
       </c>
       <c r="C144" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="F144" t="s">
-        <v>748</v>
+        <v>735</v>
+      </c>
+      <c r="G144" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B145" t="s">
         <v>463</v>
       </c>
       <c r="C145" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="D145">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="E145" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="F145" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B146" t="s">
         <v>464</v>
       </c>
       <c r="C146" t="s">
-        <v>568</v>
+        <v>649</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F146" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B147" t="s">
         <v>465</v>
       </c>
       <c r="C147" t="s">
-        <v>657</v>
+        <v>535</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F147" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B148" t="s">
         <v>466</v>
       </c>
       <c r="C148" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="D148">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E148" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F148" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B149" t="s">
         <v>467</v>
       </c>
+      <c r="C149" t="s">
+        <v>651</v>
+      </c>
       <c r="D149">
-        <v>1</v>
+        <v>597</v>
       </c>
       <c r="E149" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F149" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B150" t="s">
         <v>468</v>
       </c>
       <c r="C150" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="E150" t="s">
-        <v>737</v>
+        <v>702</v>
       </c>
       <c r="F150" t="s">
-        <v>748</v>
-      </c>
-      <c r="G150" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B151" t="s">
         <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E151" t="s">
-        <v>738</v>
+        <v>702</v>
       </c>
       <c r="F151" t="s">
-        <v>748</v>
-      </c>
-      <c r="G151" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B152" t="s">
         <v>470</v>
       </c>
       <c r="C152" t="s">
-        <v>661</v>
+        <v>555</v>
       </c>
       <c r="D152">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>739</v>
+        <v>707</v>
       </c>
       <c r="F152" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B153" t="s">
         <v>471</v>
       </c>
       <c r="C153" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F153" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
         <v>472</v>
       </c>
       <c r="C154" t="s">
-        <v>544</v>
+        <v>655</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="E154" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F154" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B155" t="s">
         <v>473</v>
       </c>
       <c r="C155" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="D155">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E155" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="F155" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B156" t="s">
         <v>474</v>
       </c>
       <c r="C156" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="D156">
-        <v>597</v>
+        <v>16</v>
       </c>
       <c r="E156" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F156" t="s">
-        <v>744</v>
+        <v>733</v>
+      </c>
+      <c r="G156" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B157" t="s">
         <v>475</v>
       </c>
       <c r="C157" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D157">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="E157" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F157" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B158" t="s">
         <v>476</v>
       </c>
       <c r="C158" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="D158">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E158" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F158" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B159" t="s">
         <v>477</v>
       </c>
       <c r="C159" t="s">
-        <v>568</v>
+        <v>659</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E159" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F159" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B160" t="s">
         <v>478</v>
       </c>
       <c r="C160" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="D160">
         <v>0</v>
       </c>
       <c r="E160" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F160" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B161" t="s">
         <v>479</v>
       </c>
       <c r="C161" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="D161">
-        <v>761</v>
+        <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="F161" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B162" t="s">
         <v>480</v>
       </c>
       <c r="C162" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="F162" t="s">
-        <v>748</v>
+        <v>735</v>
+      </c>
+      <c r="G162" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B163" t="s">
         <v>481</v>
       </c>
       <c r="C163" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D163">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E163" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F163" t="s">
-        <v>746</v>
-      </c>
-      <c r="G163" t="s">
-        <v>754</v>
+        <v>732</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B164" t="s">
         <v>482</v>
       </c>
       <c r="C164" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="E164" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F164" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B165" t="s">
         <v>483</v>
       </c>
       <c r="C165" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F165" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B166" t="s">
         <v>484</v>
       </c>
       <c r="C166" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D166">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F166" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B167" t="s">
         <v>485</v>
       </c>
       <c r="C167" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D167">
         <v>0</v>
       </c>
       <c r="E167" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F167" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B168" t="s">
         <v>486</v>
       </c>
       <c r="C168" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D168">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E168" t="s">
-        <v>739</v>
+        <v>702</v>
       </c>
       <c r="F168" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B169" t="s">
         <v>487</v>
       </c>
       <c r="C169" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D169">
         <v>0</v>
       </c>
       <c r="E169" t="s">
-        <v>741</v>
+        <v>702</v>
       </c>
       <c r="F169" t="s">
-        <v>748</v>
-      </c>
-      <c r="G169" t="s">
-        <v>675</v>
+        <v>735</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B170" t="s">
         <v>488</v>
       </c>
       <c r="C170" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D170">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E170" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F170" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B171" t="s">
         <v>489</v>
       </c>
       <c r="C171" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D171">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="E171" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F171" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B172" t="s">
         <v>490</v>
       </c>
       <c r="C172" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D172">
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F172" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B173" t="s">
         <v>491</v>
       </c>
       <c r="C173" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="E173" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F173" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B174" t="s">
         <v>492</v>
       </c>
       <c r="C174" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D174">
         <v>0</v>
       </c>
       <c r="E174" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F174" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B175" t="s">
         <v>493</v>
       </c>
       <c r="C175" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E175" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F175" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B176" t="s">
         <v>494</v>
       </c>
-      <c r="C176" t="s">
-        <v>682</v>
-      </c>
       <c r="D176">
         <v>0</v>
       </c>
       <c r="E176" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F176" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B177" t="s">
         <v>495</v>
       </c>
       <c r="C177" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="D177">
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F177" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B178" t="s">
         <v>496</v>
       </c>
       <c r="C178" t="s">
-        <v>684</v>
+        <v>589</v>
       </c>
       <c r="D178">
-        <v>242</v>
+        <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F178" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B179" t="s">
         <v>497</v>
       </c>
       <c r="C179" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="D179">
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F179" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B180" t="s">
         <v>498</v>
       </c>
       <c r="C180" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="D180">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F180" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B181" t="s">
         <v>499</v>
       </c>
       <c r="C181" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F181" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B182" t="s">
         <v>500</v>
       </c>
       <c r="C182" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="D182">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F182" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B183" t="s">
         <v>501</v>
       </c>
+      <c r="C183" t="s">
+        <v>602</v>
+      </c>
       <c r="D183">
         <v>0</v>
       </c>
       <c r="E183" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F183" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B184" t="s">
         <v>502</v>
       </c>
       <c r="C184" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E184" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F184" t="s">
-        <v>748</v>
+        <v>733</v>
+      </c>
+      <c r="G184" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B185" t="s">
         <v>503</v>
       </c>
       <c r="C185" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D185">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E185" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F185" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B186" t="s">
         <v>504</v>
       </c>
       <c r="C186" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D186">
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F186" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B187" t="s">
         <v>505</v>
       </c>
       <c r="C187" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E187" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F187" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B188" t="s">
         <v>506</v>
       </c>
       <c r="C188" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E188" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F188" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B189" t="s">
         <v>507</v>
       </c>
       <c r="C189" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>10255</v>
       </c>
       <c r="E189" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="F189" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B190" t="s">
         <v>508</v>
       </c>
       <c r="C190" t="s">
-        <v>615</v>
+        <v>686</v>
       </c>
       <c r="D190">
         <v>0</v>
       </c>
       <c r="E190" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="F190" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B191" t="s">
         <v>509</v>
       </c>
       <c r="C191" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="D191">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E191" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F191" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="G191" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B192" t="s">
         <v>510</v>
       </c>
       <c r="C192" t="s">
-        <v>613</v>
+        <v>688</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F192" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B193" t="s">
         <v>511</v>
       </c>
       <c r="C193" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="E193" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F193" t="s">
-        <v>748</v>
+        <v>735</v>
+      </c>
+      <c r="G193" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B194" t="s">
         <v>512</v>
       </c>
       <c r="C194" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D194">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E194" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F194" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B195" t="s">
         <v>513</v>
       </c>
       <c r="C195" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D195">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E195" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F195" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B196" t="s">
         <v>514</v>
       </c>
       <c r="C196" t="s">
-        <v>698</v>
+        <v>526</v>
       </c>
       <c r="D196">
-        <v>10255</v>
+        <v>0</v>
       </c>
       <c r="E196" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="F196" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B197" t="s">
         <v>515</v>
       </c>
       <c r="C197" t="s">
-        <v>699</v>
+        <v>526</v>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="F197" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B198" t="s">
         <v>516</v>
       </c>
       <c r="C198" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F198" t="s">
-        <v>748</v>
-      </c>
-      <c r="G198" t="s">
-        <v>756</v>
+        <v>735</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B199" t="s">
         <v>517</v>
       </c>
       <c r="C199" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="E199" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F199" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B200" t="s">
         <v>518</v>
       </c>
       <c r="C200" t="s">
+        <v>694</v>
+      </c>
+      <c r="D200">
+        <v>126</v>
+      </c>
+      <c r="E200" t="s">
         <v>702</v>
       </c>
-      <c r="D200">
-        <v>314</v>
-      </c>
-      <c r="E200" t="s">
-        <v>715</v>
-      </c>
       <c r="F200" t="s">
-        <v>748</v>
-      </c>
-      <c r="G200" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B201" t="s">
         <v>519</v>
       </c>
       <c r="C201" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="D201">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F201" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B202" t="s">
         <v>520</v>
       </c>
       <c r="C202" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="D202">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F202" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B203" t="s">
         <v>521</v>
       </c>
       <c r="C203" t="s">
-        <v>533</v>
+        <v>697</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E203" t="s">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="F203" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B204" t="s">
         <v>522</v>
       </c>
       <c r="C204" t="s">
-        <v>533</v>
+        <v>698</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E204" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="F204" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B205" t="s">
         <v>523</v>
       </c>
       <c r="C205" t="s">
-        <v>705</v>
+        <v>661</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E205" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F205" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B206" t="s">
         <v>524</v>
       </c>
       <c r="C206" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="D206">
-        <v>438</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F206" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B207" t="s">
         <v>525</v>
       </c>
       <c r="C207" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="D207">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="F207" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7">
-      <c r="A208" t="s">
-        <v>307</v>
-      </c>
-      <c r="B208" t="s">
-        <v>526</v>
-      </c>
-      <c r="C208" t="s">
-        <v>708</v>
-      </c>
-      <c r="D208">
-        <v>1</v>
-      </c>
-      <c r="E208" t="s">
-        <v>715</v>
-      </c>
-      <c r="F208" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209" t="s">
-        <v>308</v>
-      </c>
-      <c r="B209" t="s">
-        <v>527</v>
-      </c>
-      <c r="C209" t="s">
-        <v>709</v>
-      </c>
-      <c r="D209">
-        <v>0</v>
-      </c>
-      <c r="E209" t="s">
-        <v>715</v>
-      </c>
-      <c r="F209" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210" t="s">
-        <v>309</v>
-      </c>
-      <c r="B210" t="s">
-        <v>528</v>
-      </c>
-      <c r="C210" t="s">
-        <v>710</v>
-      </c>
-      <c r="D210">
-        <v>23</v>
-      </c>
-      <c r="E210" t="s">
-        <v>715</v>
-      </c>
-      <c r="F210" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211" t="s">
-        <v>310</v>
-      </c>
-      <c r="B211" t="s">
-        <v>529</v>
-      </c>
-      <c r="C211" t="s">
-        <v>711</v>
-      </c>
-      <c r="D211">
-        <v>26</v>
-      </c>
-      <c r="E211" t="s">
-        <v>743</v>
-      </c>
-      <c r="F211" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212" t="s">
-        <v>311</v>
-      </c>
-      <c r="B212" t="s">
-        <v>530</v>
-      </c>
-      <c r="C212" t="s">
-        <v>674</v>
-      </c>
-      <c r="D212">
-        <v>18</v>
-      </c>
-      <c r="E212" t="s">
-        <v>715</v>
-      </c>
-      <c r="F212" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" t="s">
-        <v>312</v>
-      </c>
-      <c r="B213" t="s">
-        <v>531</v>
-      </c>
-      <c r="C213" t="s">
-        <v>712</v>
-      </c>
-      <c r="D213">
-        <v>2</v>
-      </c>
-      <c r="E213" t="s">
-        <v>715</v>
-      </c>
-      <c r="F213" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214" t="s">
-        <v>313</v>
-      </c>
-      <c r="B214" t="s">
-        <v>532</v>
-      </c>
-      <c r="C214" t="s">
-        <v>713</v>
-      </c>
-      <c r="D214">
-        <v>0</v>
-      </c>
-      <c r="E214" t="s">
-        <v>715</v>
-      </c>
-      <c r="F214" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="704">
   <si>
     <t>ati_all</t>
   </si>
@@ -986,16 +986,19 @@
     <t>Crown-Indigenous Relations and Northern Affairs Canada | Relations Couronne-Autochtones et Affaires du Nord Canada</t>
   </si>
   <si>
-    <t>Atlantic Canada Opportunities Agency | Agence de promotion économique du Canada atlantique</t>
-  </si>
-  <si>
     <t>Atomic Energy of Canada Limited | Énergie atomique du Canada, Limitée</t>
   </si>
   <si>
     <t>Atlantic Pilotage Authority Canada | Administration de pilotage de l'Atlantique Canada</t>
   </si>
   <si>
+    <t>Asia-Pacific Foundation of Canada | Fondation Asie Pacifique du Canada</t>
+  </si>
+  <si>
     <t>Administrative Tribunals Support Service of Canada | Service canadien d'appui aux tribunaux administratifs</t>
+  </si>
+  <si>
+    <t>Bank of Canada | Banque du Canada</t>
   </si>
   <si>
     <t>British Columbia Treaty Commission | Commission des Traités de la Colombie-Britannique</t>
@@ -1004,7 +1007,7 @@
     <t>Business Development Bank of Canada | Banque de développement du Canada</t>
   </si>
   <si>
-    <t>Belledune Port Authority | Administration portuaire de Belledune</t>
+    <t>Canadian Northern Economic Development Agency | Agence canadienne de développement économique du Nord</t>
   </si>
   <si>
     <t>Courts Administration Service | Service administratif des tribunaux judiciaires</t>
@@ -1013,31 +1016,31 @@
     <t>Accessibility Standards Canada | Normes d’accessibilité Canada</t>
   </si>
   <si>
-    <t>Copyright Board Canada | Commission du droit d'auteur du Canada</t>
+    <t>Canadian Air Transport Security Authority | Administration canadienne de la sûreté du transport aérien</t>
   </si>
   <si>
     <t>Canadian Broadcasting Company | Radio-Canada</t>
   </si>
   <si>
+    <t>Canada Border Services Agency | Agence des services frontaliers du Canada</t>
+  </si>
+  <si>
     <t>Canada Council for the Arts | Conseil des arts du Canada</t>
   </si>
   <si>
-    <t>Canadian Commercial Corporation | Corporation commerciale canadienne</t>
+    <t>Canadian Centre for Occupational Health and Safety | Centre canadien d'hygiène et de sécurité au travail</t>
+  </si>
+  <si>
+    <t>Canadian Cultural Property Export Review Board | Commission canadienne d'examen des exportations de biens culturels</t>
   </si>
   <si>
     <t>Canadian Dairy Commission | Commission canadienne du lait</t>
-  </si>
-  <si>
-    <t>Canada Development Investment Corporation | Corporation de développement des investissements du Canada</t>
   </si>
   <si>
     <t>Canada Deposit Insurance Corporation | Société d'assurance-dépôts du Canada</t>
   </si>
   <si>
     <t>Canada Economic Development for Quebec Regions | Développement économique Canada pour les régions du Québec</t>
-  </si>
-  <si>
-    <t>Canada Enterprise Emergency Funding Corporation | La Corporation de financement d’urgence d’entreprises du Canada</t>
   </si>
   <si>
     <t>Canada Eldor Inc. | Canada Eldor Inc.</t>
@@ -1067,9 +1070,6 @@
     <t>Canadian Human Rights Commission | Commission canadienne des droits de la personne</t>
   </si>
   <si>
-    <t>Canada Infrastructure Bank | La Banque de l’infrastructure du Canada</t>
-  </si>
-  <si>
     <t>Immigration, Refugees and Citizenship Canada | Immigration, Réfugiés et Citoyenneté Canada</t>
   </si>
   <si>
@@ -1077,9 +1077,6 @@
   </si>
   <si>
     <t>Canada Innovation Corporation | La Corporation d’innovation du Canada</t>
-  </si>
-  <si>
-    <t>Canadian Intergovernmental Conference Secretariat | Secrétariat des conférences intergouvernementales canadiennes</t>
   </si>
   <si>
     <t>Canadian Institutes of Health Research | Instituts de recherche en santé du Canada</t>
@@ -1091,43 +1088,16 @@
     <t>Canada Industrial Relations Board | Conseil canadien des relations industrielles</t>
   </si>
   <si>
-    <t>Canadian International Trade Tribunal | Tribunal canadien du commerce extérieur</t>
-  </si>
-  <si>
     <t>Canada Lands Company CLC Limited | Société immobilière du Canada CLC limitée</t>
   </si>
   <si>
-    <t>Canada Lands Company Limited | Société immobilière du Canada Limitée</t>
-  </si>
-  <si>
     <t>Canadian Museum of History | Musée canadien de l'histoire</t>
-  </si>
-  <si>
-    <t>Canada Mortgage and Housing Corporation | Société canadienne d'hypothèques et de logement</t>
   </si>
   <si>
     <t>Canadian Museum for Human Rights | Musée canadien pour les droits de la personne</t>
   </si>
   <si>
     <t>Canadian Museum of Immigration at Pier 21 | Musée canadien de l'immigration du Quai 21</t>
-  </si>
-  <si>
-    <t>Canadian Museum of Nature | Musée canadien de la nature</t>
-  </si>
-  <si>
-    <t>Canada-Newfoundland and Labrador Offshore Petroleum Board | Office Canada–Terre-Neuve-et Labrador des hydrocarbures extracôtiers</t>
-  </si>
-  <si>
-    <t>Canadian Nuclear Safety Commission | Commission canadienne de sûreté nucléaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada-Nova Scotia Offshore Energy Regulator  | Régie Canada-Nouvelle-Écosse de l’énergie extracôtière </t>
-  </si>
-  <si>
-    <t>College of Patent Agents and Trademark Agents | Collège des agents de brevets et des agents de marques de commerce</t>
-  </si>
-  <si>
-    <t>Civilian Review and Complaints Commission for the RCMP | Commission civile d'examen et de traitement des plaintes relatives à la Gendarmerie royale du Canada</t>
   </si>
   <si>
     <t>Canada Post | Postes Canada</t>
@@ -1137,12 +1107,6 @@
   </si>
   <si>
     <t>Canadian Race Relations Foundation | La Fondation Canadienne des relations raciales</t>
-  </si>
-  <si>
-    <t>Canadian Radio-television and Telecommunications Commission | Conseil de la radiodiffusion et des télécommunications canadiennes</t>
-  </si>
-  <si>
-    <t>Canadian Space Agency | Agence spatiale canadienne</t>
   </si>
   <si>
     <t>Correctional Service of Canada | Service correctionnel du Canada</t>
@@ -1160,70 +1124,34 @@
     <t>Canada Science and Technology Museum | Musée des sciences et de la technologie du Canada</t>
   </si>
   <si>
-    <t>Canadian Transportation Agency | Office des transports du Canada</t>
-  </si>
-  <si>
     <t>Destination Canada | Destination Canada</t>
   </si>
   <si>
     <t>Canada Water Agency | Agence de l’eau du Canada</t>
   </si>
   <si>
-    <t>Defence Construction Canada | Construction de Défense Canada</t>
-  </si>
-  <si>
     <t>Global Affairs Canada | Affaires mondiales Canada</t>
-  </si>
-  <si>
-    <t>Development Finance Institution - FinDev Canada | Institution de financement du développement - FinDev Canada</t>
   </si>
   <si>
     <t>Fisheries and Oceans Canada | Pêches et Océans Canada</t>
   </si>
   <si>
-    <t>National Defence | Défense nationale</t>
-  </si>
-  <si>
     <t>Downsview Metro Devco Inc. | Gestion Downsview Métro Devco</t>
-  </si>
-  <si>
-    <t>Environment and Climate Change Canada | Environnement et Changement climatique Canada</t>
   </si>
   <si>
     <t>Export Development Canada | Exportation et développement Canada</t>
   </si>
   <si>
-    <t>Elections Canada | Élections Canada</t>
-  </si>
-  <si>
-    <t>RCMP External Review Committee | Comité externe d'examen de la GRC</t>
-  </si>
-  <si>
     <t>Employment and Social Development Canada | Emploi et Développement social Canada</t>
   </si>
   <si>
-    <t>Exinvest Inc. | Exinvest Inc.</t>
-  </si>
-  <si>
     <t>Federal Bridge Corporation | Société des ponts fédéraux</t>
-  </si>
-  <si>
-    <t>Financial Consumer Agency of Canada | Agence de la consommation en matière financière du Canada</t>
   </si>
   <si>
     <t>Farm Credit Canada | Financement agricole Canada</t>
   </si>
   <si>
     <t>Federal Economic Development Agency for Southern Ontario | Agence fédérale de développement économique pour le Sud de l'Ontario</t>
-  </si>
-  <si>
-    <t>Federal Economic Development Agency for Northern Ontario | Agence fédérale de développement économique pour le Nord de l’Ontario</t>
-  </si>
-  <si>
-    <t>Freshwater Fish Marketing Corporation | Office de commercialisation du poisson d'eau douce</t>
-  </si>
-  <si>
-    <t>Department of Finance Canada | Ministère des Finances Canada</t>
   </si>
   <si>
     <t>Financial Transactions and Reports Analysis Centre of Canada | Centre d'analyse des opérations et déclarations financières du Canada</t>
@@ -1241,12 +1169,6 @@
     <t>Farm Products Council of Canada | Conseil des produits agricoles du Canada</t>
   </si>
   <si>
-    <t>Office of the Administrator of the Fund for Railway Accidents Involving Designated Goods; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation pour les accidents ferroviaires impliquant des marchandises désignées; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
-  </si>
-  <si>
-    <t>Great Lakes Pilotage Authority Canada | Administration de pilotage des Grands Lacs Canada</t>
-  </si>
-  <si>
     <t>Gwich’in Land and Water Board | Office Gwich’in des terres et des eaux</t>
   </si>
   <si>
@@ -1256,13 +1178,7 @@
     <t>Hamilton-Oshawa  Port Authority | Administration portuaire de Hamilton-Oshawa</t>
   </si>
   <si>
-    <t>Health Canada | Santé Canada</t>
-  </si>
-  <si>
     <t>VIA HFR - VIA TGF Inc. | VIA HFR - VIA TGF Inc.</t>
-  </si>
-  <si>
-    <t>Historic Sites and Monuments Board of Canada | Commission des lieux et monuments historiques du Canada</t>
   </si>
   <si>
     <t>Impact Assessment Agency of Canada | Agence d'évaluation d'impact du Canada</t>
@@ -1283,9 +1199,6 @@
     <t>Department of Housing, Infrastructure and Communities | Ministère du Logement, de l’Infrastructure et des Collectivités</t>
   </si>
   <si>
-    <t>Canada Foundation for Innovation | Fondation canadienne pour l’innovation</t>
-  </si>
-  <si>
     <t>Immigration and Refugee Board of Canada | Commission de l'immigration et du statut de réfugié du Canada</t>
   </si>
   <si>
@@ -1295,13 +1208,7 @@
     <t>Jacques Cartier and Champlain Bridges Incorporated | Ponts Jacques Cartier et Champlain Incorporée</t>
   </si>
   <si>
-    <t>The Joint Federal/Provincial Commission into the April 2020 Nova Scotia Mass Casualty | Commission fédérale-provinciale sur les événements d’avril 2020 en Nouvelle Écosse</t>
-  </si>
-  <si>
     <t>Department of Justice Canada | Ministère de la Justice Canada</t>
-  </si>
-  <si>
-    <t>Library and Archives Canada | Bibliothèque et Archives Canada</t>
   </si>
   <si>
     <t>Marine Atlantic Inc. | Marine Atlantique S.C.C.</t>
@@ -1316,16 +1223,10 @@
     <t>Mackenzie Valley Land and Water Board | Office des terres et des eaux de la vallée du Mackenzie Valley</t>
   </si>
   <si>
-    <t>Montreal Port Authority | Administration portuaire de Montréal</t>
-  </si>
-  <si>
     <t>Military Police Complaints Commission of Canada | Commission d'examen des plaintes concernant la police militaire du Canada</t>
   </si>
   <si>
     <t>Mackenzie Valley Environmental Impact Review Board | Office d’examen des répercussions environnementales de la vallée du Mackenzie</t>
-  </si>
-  <si>
-    <t>National Arts Centre | Centre national des Arts</t>
   </si>
   <si>
     <t>The National Battlefields Commission | Commission des champs de bataille nationaux</t>
@@ -1349,28 +1250,13 @@
     <t>Nanaimo Port Authority | Administration portuaire de Nanaïmo</t>
   </si>
   <si>
-    <t>Northern Pipeline Agency Canada | Administration du pipe-line du Nord Canada</t>
-  </si>
-  <si>
     <t>National Research Council Canada | Conseil national de recherches Canada</t>
-  </si>
-  <si>
-    <t>Natural Resources Canada | Ressources naturelles Canada</t>
   </si>
   <si>
     <t>Natural Sciences and Engineering Research Council of Canada | Conseil de recherches en sciences naturelles et en génie du Canada</t>
   </si>
   <si>
-    <t>National Security and Intelligence Review Agency | Office de surveillance des activités en matière de sécurité nationale et de renseignement</t>
-  </si>
-  <si>
     <t>Office of the Auditor General of Canada | Bureau du vérificateur général du Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commissioner of Canada Elections  | Commissaire aux élections fédérales </t>
-  </si>
-  <si>
-    <t>The Correctional Investigator Canada | L'Enquêteur correctionnel Canada</t>
   </si>
   <si>
     <t>Office of the Commissioner of Lobbying of Canada | Commissariat au lobbying du Canada</t>
@@ -1382,25 +1268,10 @@
     <t>Office of the Intelligence Commissioner | Bureau du commissaire au renseignement</t>
   </si>
   <si>
-    <t>Office of the Information Commissioner of Canada | Commissariat à l'information du Canada</t>
-  </si>
-  <si>
-    <t>Office of the Privacy Commissioner of Canada | Commissariat à la protection de la vie privée du Canada</t>
-  </si>
-  <si>
     <t>Old Port of Montreal Corporation Inc. | Société du Vieux-Port de Montréal Inc.</t>
   </si>
   <si>
-    <t>Law Commission of Canada | Commission du droit du Canada</t>
-  </si>
-  <si>
-    <t>Office of the Superintendent of Financial Institutions Canada | Bureau du surintendant des institutions financières Canada</t>
-  </si>
-  <si>
     <t>Office of the Secretary to the Governor General | Bureau du secrétaire du gouverneur général</t>
-  </si>
-  <si>
-    <t>Office of the Taxpayers' Ombudsperson | Bureau de l'ombudsman des contribuables</t>
   </si>
   <si>
     <t>Office of the Veterans Ombudsman | Bureau de l'ombudsman des vétérans</t>
@@ -1409,31 +1280,16 @@
     <t>Pacific Economic Development Canada | Développement économique Canada pour le Pacifique</t>
   </si>
   <si>
-    <t>Port Alberni Port Authority | Administration portuaire de Port Alberni</t>
-  </si>
-  <si>
     <t>Port of Belledune | Port de Belledune</t>
   </si>
   <si>
     <t>Parole Board of Canada | Commission des libérations conditionnelles du Canada</t>
   </si>
   <si>
-    <t>Parks Canada | Parcs Canada</t>
-  </si>
-  <si>
     <t>Canadian Heritage | Patrimoine canadien</t>
   </si>
   <si>
-    <t>Privy Council Office | Bureau du Conseil privé</t>
-  </si>
-  <si>
     <t>Parc Downsview Park Inc. | Parc Downsview Park Inc</t>
-  </si>
-  <si>
-    <t>Pierre Elliott Trudeau Foundation | Fondation Pierre Elliott Trudeau</t>
-  </si>
-  <si>
-    <t>Public Health Agency of Canada | Agence de la santé publique du Canada</t>
   </si>
   <si>
     <t>President of the King’s Privy Council for Canada | Président du Conseil privé du Roi pour le Canada</t>
@@ -1445,22 +1301,13 @@
     <t>Polar Knowledge Canada | Savoir polaire Canada</t>
   </si>
   <si>
-    <t>Pacific Pilotage Authority Canada | Administration de pilotage du Pacifique Canada</t>
-  </si>
-  <si>
     <t>Public Prosecution Service of Canada | Service des poursuites pénales du Canada</t>
   </si>
   <si>
     <t>Passport Canada | Passeport Canada</t>
   </si>
   <si>
-    <t>Prairies Economic Development Canada | Développement économique Canada pour les Prairies</t>
-  </si>
-  <si>
     <t>Prince Rupert Port Authority | L’Administration portuaire de Prince Rupert</t>
-  </si>
-  <si>
-    <t>Public Safety Canada | Sécurité publique Canada</t>
   </si>
   <si>
     <t>Public Service Commission of Canada | Commission de la fonction publique du Canada</t>
@@ -1475,9 +1322,6 @@
     <t>Office of the Public Sector Integrity Commissioner of Canada | Commissariat à l'intégrité du secteur public du Canada</t>
   </si>
   <si>
-    <t>Public Service Labour Relations Board | Commission des relations de travail dans la fonction publique</t>
-  </si>
-  <si>
     <t>Public Sector Pension Investment Board | Office d’investissement des régimes de pensions du secteur public</t>
   </si>
   <si>
@@ -1488,9 +1332,6 @@
   </si>
   <si>
     <t>Quebec Port Authority | Administration portuaire de Québec</t>
-  </si>
-  <si>
-    <t>Royal Canadian Mounted Police | Gendarmerie royale du Canada</t>
   </si>
   <si>
     <t>Revera Inc. | Revera Inc.</t>
@@ -1514,18 +1355,6 @@
     <t>St. John's Port Authority | Administration portuaire de St. John's</t>
   </si>
   <si>
-    <t xml:space="preserve">Laurentian Pilotage Authority  | Administration de pilotage des Laurentides </t>
-  </si>
-  <si>
-    <t>Sahtu Land Use Planning Board | Conseil de l’aménagement du territoire du Sahtu</t>
-  </si>
-  <si>
-    <t>Sahtu Land and Water Board | Office des terres et des eaux du Sahtu</t>
-  </si>
-  <si>
-    <t>Secretariat of the National Security and Intelligence Committee of Parliamentarians | Secrétariat du Comité des parlementaires sur la sécurité nationale et le renseignement</t>
-  </si>
-  <si>
     <t>Office of the Administrator of the Ship-source Oil Pollution Fund; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation des dommages dus à la pollution par les hydrocarbures causée par les navires; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
   </si>
   <si>
@@ -1547,16 +1376,7 @@
     <t>Status of Women Canada | Condition féminine Canada</t>
   </si>
   <si>
-    <t>Thunder Bay Port Authority | Administration portuaire de Thunder Bay</t>
-  </si>
-  <si>
     <t>Treasury Board of Canada Secretariat | Secrétariat du Conseil du Trésor du Canada</t>
-  </si>
-  <si>
-    <t>Transport Canada | Transports Canada</t>
-  </si>
-  <si>
-    <t>Telefilm Canada | Téléfilm Canada</t>
   </si>
   <si>
     <t>Trans Mountain Corporation | Trans Mountain Corporation</t>
@@ -1569,9 +1389,6 @@
   </si>
   <si>
     <t>Transportation Safety Board of Canada | Bureau de la sécurité des transports du Canada</t>
-  </si>
-  <si>
-    <t>Veterans Affairs Canada | Anciens Combattants Canada</t>
   </si>
   <si>
     <t>Vancouver Fraser Port Authority | Administration portuaire Vancouver Fraser</t>
@@ -1589,12 +1406,6 @@
     <t>Western Economic Diversification Canada | Diversification de l'économie de l'Ouest Canada</t>
   </si>
   <si>
-    <t>Windsor-Detroit Bridge Authority | Autorité du pont Windsor-Détroit</t>
-  </si>
-  <si>
-    <t>Yukon Environmental and Socio-economic Assessment Board | Office d’évaluation environnementale et socio-économique du Yukon</t>
-  </si>
-  <si>
     <t>atip-aiprp@cdev.gc.ca</t>
   </si>
   <si>
@@ -1604,16 +1415,19 @@
     <t>aadnc.atiprequest-aiprpdemande.aandc@canada.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@acoa-apeca.gc.ca</t>
-  </si>
-  <si>
     <t>igaudreault@aecl.ca</t>
   </si>
   <si>
     <t>bbradley@atlanticpilotage.com</t>
   </si>
   <si>
+    <t>atip.coordinator@asiapacific.ca</t>
+  </si>
+  <si>
     <t>ATIP-AIPRP@tribunal.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@bankofcanada.ca</t>
   </si>
   <si>
     <t>sgustin@bctreaty.ca</t>
@@ -1622,22 +1436,25 @@
     <t>atip-aiprp@bdc.ca</t>
   </si>
   <si>
-    <t>moffitt@portofbelledune.ca</t>
+    <t>atip-aiprp@cannor.gc.ca</t>
   </si>
   <si>
     <t>NC-COMM-ATIP-AIPRP-GD@hrsdc-rhdcc.gc.ca</t>
   </si>
   <si>
-    <t>nancy.laframboise@cb-cda.gc.ca</t>
+    <t>atip@catsa.gc.ca</t>
   </si>
   <si>
     <t>Peter.Hull@cbc.ca</t>
   </si>
   <si>
+    <t>ATIP-AIPRP@cbsa-asfc.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@canadacouncil.ca</t>
   </si>
   <si>
-    <t>atip.aiprp@ccc.ca</t>
+    <t>atip_aiprp@ccohs.ca</t>
   </si>
   <si>
     <t>priscilla.revolus@cdc-ccl.gc.ca</t>
@@ -1670,9 +1487,6 @@
     <t>atip.aiprp@chrc-ccdp.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@cib-bic.ca</t>
-  </si>
-  <si>
     <t>ATIP-AIPRP@cic.gc.ca</t>
   </si>
   <si>
@@ -1688,31 +1502,10 @@
     <t>AIPRP-ATIP@museedelhistoire.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@cmhc.ca</t>
-  </si>
-  <si>
     <t>atip@humanrights.ca</t>
   </si>
   <si>
     <t>ablack@pier21.ca</t>
-  </si>
-  <si>
-    <t>kdoucette@nature.ca</t>
-  </si>
-  <si>
-    <t>TBennett@cnlopb.nl.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@cnsc-ccsn.gc.ca</t>
-  </si>
-  <si>
-    <t>atip@cnsoer.ca</t>
-  </si>
-  <si>
-    <t>adiaz@cpata-cabamc.ca</t>
-  </si>
-  <si>
-    <t>ATIP.AIPRP@crcc-ccetp.gc.ca</t>
   </si>
   <si>
     <t>ATIP_AIPRP@canadapost.postescanada.ca</t>
@@ -1722,12 +1515,6 @@
   </si>
   <si>
     <t>atavassoli@crrf-fcrr.ca</t>
-  </si>
-  <si>
-    <t>AIPRP-ATIP@crtc.gc.ca</t>
-  </si>
-  <si>
-    <t>AIPRP-ATIP@asc-csa.gc.ca</t>
   </si>
   <si>
     <t>CSC.ATIP-AIPRP.SCC@csc-scc.gc.ca</t>
@@ -1745,64 +1532,31 @@
     <t>atip-aiprp@ingeniumcanada.org</t>
   </si>
   <si>
-    <t>OTC.AIPRP-ATIP.CTA@otc-cta.gc.ca</t>
-  </si>
-  <si>
     <t>atip-aiprp@destinationcanada.com</t>
   </si>
   <si>
     <t>atip-aiprp@cwa-aec.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@DCC-CDC.gc.ca</t>
+    <t>dcp@international.gc.ca</t>
   </si>
   <si>
-    <t>dcp@international.gc.ca</t>
+    <t>atip-laiprp@dfo-mpo.gc.ca</t>
+  </si>
+  <si>
+    <t>atip@northcrestdev.ca</t>
   </si>
   <si>
     <t>atipteam@edc.ca</t>
   </si>
   <si>
-    <t>atip-laiprp@dfo-mpo.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@forces.gc.ca</t>
-  </si>
-  <si>
-    <t>atip@northcrestdev.ca</t>
-  </si>
-  <si>
-    <t>ecatip-ecaiprp@ec.gc.ca</t>
-  </si>
-  <si>
-    <t>aiprp-atip@elections.ca</t>
-  </si>
-  <si>
-    <t>corporateandhrservices-servicesgenerauxetrh@erc-cee.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIPteam@edc.ca</t>
-  </si>
-  <si>
     <t>info@federalbridge.ca</t>
-  </si>
-  <si>
-    <t>Nathalie.forester@fcac-acfc.gc.ca</t>
   </si>
   <si>
     <t>ATIP_AIPRP@fcc-fac.ca</t>
   </si>
   <si>
     <t>atip-aiprp@feddevontario.gc.ca</t>
-  </si>
-  <si>
-    <t>fednor-atipinbox@ised-isde.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIPcontrol@freshwaterfish.com</t>
-  </si>
-  <si>
-    <t>fin.atip-aiprp.fin@canada.ca</t>
   </si>
   <si>
     <t>atip-aiprp@fintrac-canafe.gc.ca</t>
@@ -1817,12 +1571,6 @@
     <t>FPCATIP-AIPRPCPAC.CPAC@canada.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@sr-nr.gc.ca</t>
-  </si>
-  <si>
-    <t>mpoirier@glpa-apgl.com</t>
-  </si>
-  <si>
     <t>snorrish@wlwb.ca</t>
   </si>
   <si>
@@ -1832,13 +1580,7 @@
     <t>atip@hopaports.ca</t>
   </si>
   <si>
-    <t>access.informal-demandes.informelles@hc-sc.gc.ca</t>
-  </si>
-  <si>
     <t>atip-aiprp@hfr-tgf.ca</t>
-  </si>
-  <si>
-    <t>pc.clmhc-hsmbc.pc@canada.ca</t>
   </si>
   <si>
     <t>atip-aiprp@iaac-aeic.gc.ca</t>
@@ -1859,9 +1601,6 @@
     <t>atip-aiprp@infc.gc.ca</t>
   </si>
   <si>
-    <t>isabelle.henrie@innovation.ca</t>
-  </si>
-  <si>
     <t>atip@irb-cisr.gc.ca</t>
   </si>
   <si>
@@ -1869,9 +1608,6 @@
   </si>
   <si>
     <t>ATIP-AIPRP-JusticeCanada@justice.gc.ca</t>
-  </si>
-  <si>
-    <t>daiprp-atipd@bac-lac.gc.ca</t>
   </si>
   <si>
     <t>atip-aiprp@ma.ca</t>
@@ -1883,16 +1619,10 @@
     <t>atip@mint.ca</t>
   </si>
   <si>
-    <t>rouaneta@port-montreal.com</t>
-  </si>
-  <si>
     <t>atip-aiprp@mpcc-cppm.gc.ca</t>
   </si>
   <si>
     <t>atipcoordinator@reviewboard.ca</t>
-  </si>
-  <si>
-    <t>carl.martin@nac-cna.ca</t>
   </si>
   <si>
     <t>anne.chouinard@ccbn-nbc.gc.ca</t>
@@ -1916,22 +1646,13 @@
     <t>bwashburn@npa.ca</t>
   </si>
   <si>
-    <t>AIPRP.ATIP@NRCan-RNCan.gc.ca</t>
-  </si>
-  <si>
     <t>ATIP-AIPRP@nrc-cnrc.gc.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@NSERC-CRSNG.GC.CA</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@nsira-ossnr.gc.ca</t>
-  </si>
-  <si>
     <t>atip-aiprp@oag-bvg.gc.ca</t>
-  </si>
-  <si>
-    <t>jean-frederic.boulais@oci-bec.gc.ca</t>
   </si>
   <si>
     <t>atip-aiprp@ocl-cal.gc.ca</t>
@@ -1943,34 +1664,16 @@
     <t>Info@ico-bcr.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-Services-AIPRP@oic-ci.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@priv.gc.ca</t>
-  </si>
-  <si>
-    <t>BMS-SGA@lcc-cdc.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@osfi-bsif.gc.ca</t>
-  </si>
-  <si>
-    <t>josee.gaudet@oto-boc.gc.ca</t>
-  </si>
-  <si>
     <t>ovoatip-bovaiprp@ombudsman-veterans.gc.ca</t>
   </si>
   <si>
     <t>pacifican.atip-aiprp@pacifican.gc.ca</t>
   </si>
   <si>
-    <t>molson@papa-appa.ca</t>
+    <t>moffitt@portofbelledune.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@PBC-CLCC.GC.CA</t>
-  </si>
-  <si>
-    <t>aiprp-atip@pc.gc.ca</t>
   </si>
   <si>
     <t>aiprp-atip@pch.gc.ca</t>
@@ -1979,19 +1682,10 @@
     <t>ATIP-AIPRP@pco-bcp.gc.ca</t>
   </si>
   <si>
-    <t>communications@FondationTrudeau.ca</t>
-  </si>
-  <si>
-    <t>access.informal-demandes.informelles@phac-aspc.gc.ca</t>
-  </si>
-  <si>
     <t>pmprb.atip-aiprb.cepmb@pmprb-cepmb.gc.ca</t>
   </si>
   <si>
     <t>Brodie.larocque@polar-polaire.gc.ca</t>
-  </si>
-  <si>
-    <t>kchong@ppa.gc.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@ppsc-sppc.gc.ca</t>
@@ -2000,13 +1694,7 @@
     <t>ATIP-AIPRP@pptc.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@prairiescan.gc.ca</t>
-  </si>
-  <si>
     <t>accesstoinformation@rupertport.com</t>
-  </si>
-  <si>
-    <t>atip-aiprp@ps-sp.gc.ca</t>
   </si>
   <si>
     <t>CFP.AIPRP-ATIP.PSC@cfp-psc.gc.ca</t>
@@ -2021,9 +1709,6 @@
     <t>info@psic-ispc.gc.ca</t>
   </si>
   <si>
-    <t>Julie.Raymond@pslrb-crtfp.gc.ca</t>
-  </si>
-  <si>
     <t>ATIP@investpsp.ca</t>
   </si>
   <si>
@@ -2034,9 +1719,6 @@
   </si>
   <si>
     <t>demande-acces@portquebec.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@rcmp-grc.gc.ca</t>
   </si>
   <si>
     <t>info@investpsp.ca</t>
@@ -2054,13 +1736,7 @@
     <t>shanrahan@sjpa-apsj.com</t>
   </si>
   <si>
-    <t>Josee.Bonneville@apl.gc.ca</t>
-  </si>
-  <si>
-    <t>exec_director@sahtulanduseplan.org</t>
-  </si>
-  <si>
-    <t>Secretariat@nsicop-cpsnr.gc.ca</t>
+    <t>atip-aiprp@sr-nr.gc.ca</t>
   </si>
   <si>
     <t>apoudrier@portsaguenay.ca</t>
@@ -2081,25 +1757,13 @@
     <t>anick.perreault@swc-cfc.gc.ca</t>
   </si>
   <si>
-    <t>tbport@tbaytel.net</t>
-  </si>
-  <si>
     <t>atip.aiprp@tbs-sct.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP/AIPRP@tc.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@telefilm.ca</t>
   </si>
   <si>
     <t>DEl-Jawhary@portstoronto.com</t>
   </si>
   <si>
     <t>AIPRP-ATIP@bst-tsb.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@veterans.gc.ca</t>
   </si>
   <si>
     <t>AccesstoInformation@portmetrovancouver.com</t>
@@ -2114,10 +1778,7 @@
     <t>FEGC.AIPRP-ATIP.WAGE@fegc-wage.gc.ca</t>
   </si>
   <si>
-    <t>Cordell.Lewis@wdbridge.com</t>
-  </si>
-  <si>
-    <t>atip@yesab.ca</t>
+    <t>atip-aiprp@prairiescan.gc.ca</t>
   </si>
   <si>
     <t>2025-09-09</t>
@@ -2129,13 +1790,7 @@
     <t>2018-08-21</t>
   </si>
   <si>
-    <t>2023-09-16</t>
-  </si>
-  <si>
     <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2021-01-09</t>
   </si>
   <si>
     <t>2018-07-27</t>
@@ -2150,22 +1805,16 @@
     <t>2023-11-09</t>
   </si>
   <si>
-    <t>2018-04-24</t>
+    <t>2023-03-28</t>
   </si>
   <si>
-    <t>2023-03-28</t>
+    <t>2018-04-24</t>
   </si>
   <si>
     <t>2024-11-21</t>
   </si>
   <si>
-    <t>2023-06-13</t>
-  </si>
-  <si>
     <t>2025-06-25</t>
-  </si>
-  <si>
-    <t>2021-12-23</t>
   </si>
   <si>
     <t>2023-12-01</t>
@@ -2178,18 +1827,6 @@
   </si>
   <si>
     <t>2018-02-01</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2020-01-18</t>
-  </si>
-  <si>
-    <t>2022-10-11</t>
-  </si>
-  <si>
-    <t>2016-12-13</t>
   </si>
   <si>
     <t>2017-05-20</t>
@@ -2216,34 +1853,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>1.1</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
     <t>IRCC.Open-Ouvert.IRCC@cic.gc.ca</t>
   </si>
   <si>
-    <t>admin@cpata-cabamc.ca</t>
-  </si>
-  <si>
     <t>im-it-gi-ti@feddevontario.gc.ca</t>
-  </si>
-  <si>
-    <t>info@oto-boc.gc.ca</t>
   </si>
   <si>
     <t>open-ouvert@tbs-sct.gc.ca</t>
   </si>
   <si>
     <t>Johanne.gamache@pmprb-cepmb.gc.ca</t>
-  </si>
-  <si>
-    <t>generalinquiries-renseignementsgeneraux@nsicop-cpsnr.gc.ca</t>
   </si>
   <si>
     <t>tina.sparrow@swc-cfc.gc.ca</t>
@@ -3103,292 +2731,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>744</v>
+        <v>620</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>745</v>
+        <v>621</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>746</v>
+        <v>622</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>747</v>
+        <v>623</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>748</v>
+        <v>624</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>749</v>
+        <v>625</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>750</v>
+        <v>626</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>751</v>
+        <v>627</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>752</v>
+        <v>628</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>753</v>
+        <v>629</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>754</v>
+        <v>630</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>755</v>
+        <v>631</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>756</v>
+        <v>632</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>757</v>
+        <v>633</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>758</v>
+        <v>634</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>759</v>
+        <v>635</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>760</v>
+        <v>636</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>761</v>
+        <v>637</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>762</v>
+        <v>638</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>763</v>
+        <v>639</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>764</v>
+        <v>640</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>765</v>
+        <v>641</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>766</v>
+        <v>642</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>767</v>
+        <v>643</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>768</v>
+        <v>644</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>769</v>
+        <v>645</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>770</v>
+        <v>646</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>771</v>
+        <v>647</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>772</v>
+        <v>648</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>773</v>
+        <v>649</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>774</v>
+        <v>650</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>775</v>
+        <v>651</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>776</v>
+        <v>652</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>777</v>
+        <v>653</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>778</v>
+        <v>654</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>779</v>
+        <v>655</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>780</v>
+        <v>656</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>781</v>
+        <v>657</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>782</v>
+        <v>658</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>783</v>
+        <v>659</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>784</v>
+        <v>660</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>785</v>
+        <v>661</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>786</v>
+        <v>662</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>787</v>
+        <v>663</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>788</v>
+        <v>664</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>789</v>
+        <v>665</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>790</v>
+        <v>666</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>791</v>
+        <v>667</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>792</v>
+        <v>668</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>793</v>
+        <v>669</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>794</v>
+        <v>670</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>795</v>
+        <v>671</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>796</v>
+        <v>672</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>797</v>
+        <v>673</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>798</v>
+        <v>674</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>799</v>
+        <v>675</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>800</v>
+        <v>676</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>801</v>
+        <v>677</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>802</v>
+        <v>678</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>803</v>
+        <v>679</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>804</v>
+        <v>680</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>805</v>
+        <v>681</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>806</v>
+        <v>682</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>807</v>
+        <v>683</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>808</v>
+        <v>684</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>809</v>
+        <v>685</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>810</v>
+        <v>686</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>811</v>
+        <v>687</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>812</v>
+        <v>688</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>813</v>
+        <v>689</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>814</v>
+        <v>690</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>815</v>
+        <v>691</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>816</v>
+        <v>692</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>817</v>
+        <v>693</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>818</v>
+        <v>694</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>819</v>
+        <v>695</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>820</v>
+        <v>696</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>821</v>
+        <v>697</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>822</v>
+        <v>698</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>823</v>
+        <v>699</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>824</v>
+        <v>700</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>825</v>
+        <v>701</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>826</v>
+        <v>702</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>827</v>
+        <v>703</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -4027,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -4315,7 +3943,7 @@
         <v>443</v>
       </c>
       <c r="CW4" s="1">
-        <v>1274</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4739,7 +4367,7 @@
         <v>272</v>
       </c>
       <c r="AM6" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN6" s="2">
         <v>7</v>
@@ -4883,7 +4511,7 @@
         <v>1566</v>
       </c>
       <c r="CI6" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="CJ6" s="2">
         <v>39</v>
@@ -4919,7 +4547,7 @@
         <v>2244</v>
       </c>
       <c r="CU6" s="1">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="CV6" s="1">
         <v>50</v>
@@ -5570,7 +5198,7 @@
         <v>223</v>
       </c>
       <c r="K9" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2">
         <v>6</v>
@@ -5834,7 +5462,7 @@
         <v>2859</v>
       </c>
       <c r="CU9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CV9" s="1">
         <v>50</v>
@@ -7191,7 +6819,7 @@
         <v>59</v>
       </c>
       <c r="AQ14" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR14" s="2">
         <v>2</v>
@@ -7359,7 +6987,7 @@
         <v>3097</v>
       </c>
       <c r="CU14" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CV14" s="1">
         <v>57</v>
@@ -8943,7 +8571,7 @@
         <v>255</v>
       </c>
       <c r="Q20" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9195,7 +8823,7 @@
         <v>417</v>
       </c>
       <c r="CW20" s="1">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9828,7 +9456,7 @@
         <v>64</v>
       </c>
       <c r="G23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2">
         <v>4</v>
@@ -10104,7 +9732,7 @@
         <v>731</v>
       </c>
       <c r="CU23" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV23" s="1">
         <v>28</v>
@@ -15073,7 +14701,7 @@
         <v>115</v>
       </c>
       <c r="AA40" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="2">
         <v>4</v>
@@ -15289,7 +14917,7 @@
         <v>53430</v>
       </c>
       <c r="CU40" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV40" s="1">
         <v>827</v>
@@ -25443,7 +25071,7 @@
         <v>126</v>
       </c>
       <c r="AA74" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB74" s="2">
         <v>3</v>
@@ -25659,7 +25287,7 @@
         <v>171615</v>
       </c>
       <c r="CU74" s="1">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="CV74" s="1">
         <v>1855</v>
@@ -25981,7 +25609,7 @@
         <v>5094</v>
       </c>
       <c r="C76" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D76" s="2">
         <v>61</v>
@@ -26269,7 +25897,7 @@
         <v>151013</v>
       </c>
       <c r="CU76" s="1">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="CV76" s="1">
         <v>1332</v>
@@ -26328,7 +25956,7 @@
         <v>9555</v>
       </c>
       <c r="Q77" s="2">
-        <v>19092</v>
+        <v>19093</v>
       </c>
       <c r="R77" s="1">
         <v>0</v>
@@ -26538,7 +26166,7 @@
         <v>7295</v>
       </c>
       <c r="CI77" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="CJ77" s="2">
         <v>362</v>
@@ -26574,13 +26202,13 @@
         <v>390873</v>
       </c>
       <c r="CU77" s="1">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="CV77" s="1">
         <v>10233</v>
       </c>
       <c r="CW77" s="1">
-        <v>16080</v>
+        <v>16081</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -33008,7 +32636,7 @@
         <v>80</v>
       </c>
       <c r="G99" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" s="2">
         <v>4</v>
@@ -33284,7 +32912,7 @@
         <v>80</v>
       </c>
       <c r="CU99" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV99" s="1">
         <v>4</v>
@@ -34228,7 +33856,7 @@
         <v>12</v>
       </c>
       <c r="G103" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2">
         <v>3</v>
@@ -34504,7 +34132,7 @@
         <v>1007</v>
       </c>
       <c r="CU103" s="1">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="CV103" s="1">
         <v>110</v>
@@ -39407,7 +39035,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" s="1">
         <v>48</v>
@@ -39695,7 +39323,7 @@
         <v>41</v>
       </c>
       <c r="CW120" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -43743,7 +43371,7 @@
         <v>101</v>
       </c>
       <c r="AA134" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB134" s="2">
         <v>3</v>
@@ -43959,7 +43587,7 @@
         <v>134448</v>
       </c>
       <c r="CU134" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CV134" s="1">
         <v>2550</v>
@@ -44060,7 +43688,7 @@
         <v>11788</v>
       </c>
       <c r="AE135" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF135" s="2">
         <v>158</v>
@@ -44264,7 +43892,7 @@
         <v>62642</v>
       </c>
       <c r="CU135" s="1">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="CV135" s="1">
         <v>1014</v>
@@ -45041,7 +44669,7 @@
         <v>14</v>
       </c>
       <c r="BA138" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB138" s="1">
         <v>90</v>
@@ -45185,7 +44813,7 @@
         <v>133</v>
       </c>
       <c r="CW138" s="1">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -48013,7 +47641,7 @@
         <v>119</v>
       </c>
       <c r="AA148" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB148" s="2">
         <v>10</v>
@@ -48229,7 +47857,7 @@
         <v>5590</v>
       </c>
       <c r="CU148" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CV148" s="1">
         <v>108</v>
@@ -53138,7 +52766,7 @@
         <v>58</v>
       </c>
       <c r="G165" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H165" s="2">
         <v>4</v>
@@ -53414,7 +53042,7 @@
         <v>79</v>
       </c>
       <c r="CU165" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV165" s="1">
         <v>4</v>
@@ -57504,7 +57132,7 @@
         <v>534</v>
       </c>
       <c r="AM179" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN179" s="2">
         <v>21</v>
@@ -57648,7 +57276,7 @@
         <v>226</v>
       </c>
       <c r="CI179" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ179" s="2">
         <v>20</v>
@@ -57684,7 +57312,7 @@
         <v>844</v>
       </c>
       <c r="CU179" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="CV179" s="1">
         <v>45</v>
@@ -58569,7 +58197,7 @@
         <v>27</v>
       </c>
       <c r="CK182" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CL182" s="1">
         <v>0</v>
@@ -58605,7 +58233,7 @@
         <v>29</v>
       </c>
       <c r="CW182" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:101">
@@ -60763,7 +60391,7 @@
         <v>79</v>
       </c>
       <c r="G190" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H190" s="2">
         <v>4</v>
@@ -61039,7 +60667,7 @@
         <v>80</v>
       </c>
       <c r="CU190" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV190" s="1">
         <v>4</v>
@@ -61164,7 +60792,7 @@
         <v>269</v>
       </c>
       <c r="AM191" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN191" s="2">
         <v>6</v>
@@ -61308,7 +60936,7 @@
         <v>156</v>
       </c>
       <c r="CI191" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ191" s="2">
         <v>2</v>
@@ -61344,7 +60972,7 @@
         <v>670</v>
       </c>
       <c r="CU191" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="CV191" s="1">
         <v>13</v>
@@ -66008,7 +65636,7 @@
         <v>86</v>
       </c>
       <c r="AA207" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB207" s="2">
         <v>3</v>
@@ -66224,7 +65852,7 @@
         <v>14059</v>
       </c>
       <c r="CU207" s="1">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="CV207" s="1">
         <v>354</v>
@@ -68375,7 +68003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="30" customHeight="1">
@@ -68409,16 +68037,16 @@
         <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>526</v>
+        <v>463</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>701</v>
+        <v>588</v>
       </c>
       <c r="F2" t="s">
-        <v>731</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -68429,16 +68057,16 @@
         <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>527</v>
+        <v>464</v>
       </c>
       <c r="D3">
         <v>398</v>
       </c>
       <c r="E3" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F3" t="s">
-        <v>732</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -68449,79 +68077,79 @@
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>528</v>
+        <v>465</v>
       </c>
       <c r="D4">
         <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F4" t="s">
-        <v>732</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
         <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>529</v>
+        <v>466</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F5" t="s">
-        <v>733</v>
+        <v>612</v>
+      </c>
+      <c r="G5" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
         <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>530</v>
+        <v>467</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F6" t="s">
-        <v>734</v>
-      </c>
-      <c r="G6" t="s">
-        <v>530</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
         <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>531</v>
+        <v>468</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F7" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -68532,496 +68160,493 @@
         <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>532</v>
+        <v>469</v>
       </c>
       <c r="D8">
         <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F8" t="s">
-        <v>733</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
         <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>533</v>
+        <v>470</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="F9" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>534</v>
+        <v>471</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>702</v>
+        <v>590</v>
       </c>
       <c r="F10" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>535</v>
+        <v>472</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>704</v>
+        <v>589</v>
       </c>
       <c r="F11" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
         <v>330</v>
       </c>
+      <c r="C12" t="s">
+        <v>473</v>
+      </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F12" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
-      <c r="C13" t="s">
-        <v>536</v>
-      </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>705</v>
+        <v>589</v>
       </c>
       <c r="F13" t="s">
-        <v>731</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>537</v>
+        <v>474</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>702</v>
+        <v>591</v>
       </c>
       <c r="F14" t="s">
-        <v>735</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
       <c r="C15" t="s">
-        <v>538</v>
+        <v>475</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F15" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>539</v>
+        <v>476</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F16" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>540</v>
+        <v>477</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F17" t="s">
-        <v>734</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
       <c r="C18" t="s">
-        <v>541</v>
+        <v>478</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F18" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B19" t="s">
         <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>526</v>
+        <v>479</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F19" t="s">
-        <v>734</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>542</v>
+        <v>469</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F20" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
         <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>543</v>
+        <v>480</v>
       </c>
       <c r="D21">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F21" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>526</v>
+        <v>481</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>706</v>
+        <v>589</v>
       </c>
       <c r="F22" t="s">
-        <v>735</v>
-      </c>
-      <c r="G22" t="s">
-        <v>526</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B23" t="s">
         <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>544</v>
+        <v>482</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>707</v>
+        <v>589</v>
       </c>
       <c r="F23" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B24" t="s">
         <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>545</v>
+        <v>483</v>
       </c>
       <c r="D24">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>702</v>
+        <v>592</v>
       </c>
       <c r="F24" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s">
         <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>546</v>
+        <v>484</v>
       </c>
       <c r="D25">
-        <v>267</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F25" t="s">
-        <v>731</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>547</v>
+        <v>485</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>708</v>
+        <v>589</v>
       </c>
       <c r="F26" t="s">
-        <v>735</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" t="s">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>548</v>
+        <v>486</v>
       </c>
       <c r="D27">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>702</v>
+        <v>593</v>
       </c>
       <c r="F27" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B28" t="s">
         <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>526</v>
+        <v>487</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>709</v>
+        <v>589</v>
       </c>
       <c r="F28" t="s">
-        <v>734</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>549</v>
+        <v>463</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>710</v>
+        <v>594</v>
       </c>
       <c r="F29" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
         <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>544</v>
+        <v>488</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>707</v>
+        <v>595</v>
       </c>
       <c r="F30" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
         <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>550</v>
+        <v>483</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>702</v>
+        <v>592</v>
       </c>
       <c r="F31" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s">
         <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>551</v>
+        <v>489</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>711</v>
+        <v>589</v>
       </c>
       <c r="F32" t="s">
-        <v>734</v>
+        <v>614</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -69032,19 +68657,19 @@
         <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>552</v>
+        <v>490</v>
       </c>
       <c r="D33">
         <v>62</v>
       </c>
       <c r="E33" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F33" t="s">
-        <v>732</v>
+        <v>611</v>
       </c>
       <c r="G33" t="s">
-        <v>736</v>
+        <v>615</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -69055,16 +68680,16 @@
         <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>553</v>
+        <v>491</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>712</v>
+        <v>596</v>
       </c>
       <c r="F34" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -69075,3480 +68700,2211 @@
         <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>526</v>
+        <v>463</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>709</v>
+        <v>594</v>
       </c>
       <c r="F35" t="s">
-        <v>734</v>
+        <v>612</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s">
         <v>354</v>
       </c>
+      <c r="C36" t="s">
+        <v>492</v>
+      </c>
       <c r="D36">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E36" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F36" t="s">
-        <v>735</v>
+        <v>610</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" t="s">
         <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>554</v>
+        <v>463</v>
       </c>
       <c r="D37">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>702</v>
+        <v>588</v>
       </c>
       <c r="F37" t="s">
-        <v>731</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" t="s">
         <v>356</v>
       </c>
       <c r="C38" t="s">
-        <v>526</v>
+        <v>469</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>701</v>
+        <v>589</v>
       </c>
       <c r="F38" t="s">
-        <v>731</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
       </c>
       <c r="C39" t="s">
-        <v>532</v>
+        <v>493</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>702</v>
+        <v>592</v>
       </c>
       <c r="F39" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
         <v>358</v>
       </c>
       <c r="C40" t="s">
-        <v>532</v>
+        <v>494</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F40" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B41" t="s">
         <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>555</v>
+        <v>495</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>707</v>
+        <v>589</v>
       </c>
       <c r="F41" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
         <v>360</v>
       </c>
       <c r="C42" t="s">
-        <v>555</v>
+        <v>496</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F42" t="s">
-        <v>734</v>
+        <v>612</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B43" t="s">
         <v>361</v>
       </c>
       <c r="C43" t="s">
-        <v>556</v>
+        <v>497</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F43" t="s">
-        <v>734</v>
+        <v>612</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
         <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>557</v>
+        <v>498</v>
       </c>
       <c r="D44">
-        <v>37</v>
+        <v>332</v>
       </c>
       <c r="E44" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F44" t="s">
-        <v>734</v>
+        <v>610</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
         <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>558</v>
+        <v>499</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>702</v>
+        <v>597</v>
       </c>
       <c r="F45" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
         <v>364</v>
       </c>
       <c r="C46" t="s">
-        <v>559</v>
+        <v>500</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>272</v>
       </c>
       <c r="E46" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F46" t="s">
-        <v>734</v>
+        <v>614</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
         <v>365</v>
       </c>
       <c r="C47" t="s">
-        <v>560</v>
+        <v>501</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="E47" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F47" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>366</v>
       </c>
       <c r="C48" t="s">
-        <v>561</v>
+        <v>502</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F48" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
         <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="D49">
-        <v>193</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F49" t="s">
-        <v>731</v>
+        <v>610</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
         <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>563</v>
+        <v>504</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F50" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
         <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>564</v>
+        <v>505</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>704</v>
+        <v>589</v>
       </c>
       <c r="F51" t="s">
-        <v>735</v>
-      </c>
-      <c r="G51" t="s">
-        <v>737</v>
+        <v>613</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s">
         <v>370</v>
       </c>
       <c r="C52" t="s">
-        <v>565</v>
+        <v>506</v>
       </c>
       <c r="D52">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
-        <v>702</v>
+        <v>598</v>
       </c>
       <c r="F52" t="s">
-        <v>733</v>
+        <v>611</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B53" t="s">
         <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>566</v>
+        <v>507</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2205</v>
       </c>
       <c r="E53" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F53" t="s">
-        <v>734</v>
+        <v>611</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
         <v>372</v>
       </c>
       <c r="C54" t="s">
-        <v>567</v>
+        <v>508</v>
       </c>
       <c r="D54">
-        <v>332</v>
+        <v>915</v>
       </c>
       <c r="E54" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F54" t="s">
-        <v>731</v>
+        <v>611</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
         <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>568</v>
+        <v>509</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>711</v>
+        <v>599</v>
       </c>
       <c r="F55" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="B56" t="s">
         <v>374</v>
       </c>
       <c r="C56" t="s">
-        <v>569</v>
+        <v>510</v>
       </c>
       <c r="D56">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F56" t="s">
-        <v>733</v>
+        <v>612</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B57" t="s">
         <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>570</v>
+        <v>474</v>
       </c>
       <c r="D57">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="E57" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F57" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B58" t="s">
         <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>571</v>
+        <v>511</v>
       </c>
       <c r="D58">
-        <v>272</v>
+        <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F58" t="s">
-        <v>733</v>
+        <v>612</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="B59" t="s">
         <v>377</v>
       </c>
       <c r="C59" t="s">
-        <v>572</v>
+        <v>512</v>
       </c>
       <c r="D59">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F59" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B60" t="s">
         <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>573</v>
+        <v>513</v>
       </c>
       <c r="D60">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F60" t="s">
-        <v>733</v>
+        <v>614</v>
+      </c>
+      <c r="G60" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="B61" t="s">
         <v>379</v>
       </c>
       <c r="C61" t="s">
-        <v>574</v>
+        <v>514</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E61" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F61" t="s">
-        <v>731</v>
+        <v>613</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="B62" t="s">
         <v>380</v>
       </c>
-      <c r="C62" t="s">
-        <v>575</v>
-      </c>
       <c r="D62">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F62" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="B63" t="s">
         <v>381</v>
       </c>
       <c r="C63" t="s">
-        <v>576</v>
+        <v>515</v>
       </c>
       <c r="D63">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>702</v>
+        <v>592</v>
       </c>
       <c r="F63" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="B64" t="s">
         <v>382</v>
       </c>
       <c r="C64" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F64" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="B65" t="s">
         <v>383</v>
       </c>
       <c r="C65" t="s">
-        <v>578</v>
+        <v>517</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>713</v>
+        <v>589</v>
       </c>
       <c r="F65" t="s">
-        <v>732</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="B66" t="s">
         <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>702</v>
+        <v>590</v>
       </c>
       <c r="F66" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="B67" t="s">
         <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>580</v>
+        <v>519</v>
       </c>
       <c r="D67">
-        <v>2205</v>
+        <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>702</v>
+        <v>592</v>
       </c>
       <c r="F67" t="s">
-        <v>732</v>
+        <v>613</v>
+      </c>
+      <c r="G67" t="s">
+        <v>519</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="B68" t="s">
         <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>581</v>
+        <v>520</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>714</v>
+        <v>592</v>
       </c>
       <c r="F68" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="B69" t="s">
         <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>582</v>
+        <v>521</v>
       </c>
       <c r="D69">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>702</v>
+        <v>600</v>
       </c>
       <c r="F69" t="s">
-        <v>732</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B70" t="s">
         <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>583</v>
+        <v>522</v>
       </c>
       <c r="D70">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="E70" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F70" t="s">
-        <v>732</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="B71" t="s">
         <v>389</v>
       </c>
       <c r="C71" t="s">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="E71" t="s">
-        <v>715</v>
+        <v>589</v>
       </c>
       <c r="F71" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="B72" t="s">
         <v>390</v>
       </c>
       <c r="C72" t="s">
-        <v>585</v>
+        <v>524</v>
       </c>
       <c r="D72">
-        <v>1197</v>
+        <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F72" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="B73" t="s">
         <v>391</v>
       </c>
       <c r="C73" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="D73">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>702</v>
+        <v>601</v>
       </c>
       <c r="F73" t="s">
-        <v>734</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="B74" t="s">
         <v>392</v>
       </c>
       <c r="C74" t="s">
-        <v>586</v>
+        <v>526</v>
       </c>
       <c r="D74">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>702</v>
+        <v>602</v>
       </c>
       <c r="F74" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="B75" t="s">
         <v>393</v>
       </c>
       <c r="C75" t="s">
-        <v>587</v>
+        <v>527</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F75" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="B76" t="s">
         <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D76">
-        <v>265</v>
+        <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F76" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="B77" t="s">
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>588</v>
+        <v>465</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>707</v>
+        <v>603</v>
       </c>
       <c r="F77" t="s">
-        <v>735</v>
+        <v>611</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="B78" t="s">
         <v>396</v>
       </c>
       <c r="C78" t="s">
+        <v>529</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
         <v>589</v>
       </c>
-      <c r="D78">
-        <v>11</v>
-      </c>
-      <c r="E78" t="s">
-        <v>702</v>
-      </c>
       <c r="F78" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="B79" t="s">
         <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="D79">
-        <v>36</v>
+        <v>527</v>
       </c>
       <c r="E79" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F79" t="s">
-        <v>733</v>
+        <v>611</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="B80" t="s">
         <v>398</v>
       </c>
       <c r="C80" t="s">
-        <v>591</v>
+        <v>531</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F80" t="s">
-        <v>734</v>
+        <v>612</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="B81" t="s">
         <v>399</v>
       </c>
       <c r="C81" t="s">
-        <v>592</v>
+        <v>532</v>
       </c>
       <c r="D81">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E81" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F81" t="s">
-        <v>733</v>
-      </c>
-      <c r="G81" t="s">
-        <v>738</v>
+        <v>614</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="B82" t="s">
         <v>400</v>
       </c>
       <c r="C82" t="s">
-        <v>593</v>
+        <v>533</v>
       </c>
       <c r="D82">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E82" t="s">
-        <v>716</v>
+        <v>589</v>
       </c>
       <c r="F82" t="s">
-        <v>733</v>
-      </c>
-      <c r="G82" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="B83" t="s">
         <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>594</v>
+        <v>518</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>702</v>
+        <v>590</v>
       </c>
       <c r="F83" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="B84" t="s">
         <v>402</v>
       </c>
       <c r="C84" t="s">
-        <v>595</v>
+        <v>534</v>
       </c>
       <c r="D84">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F84" t="s">
-        <v>732</v>
+        <v>614</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="B85" t="s">
         <v>403</v>
       </c>
       <c r="C85" t="s">
-        <v>596</v>
+        <v>535</v>
       </c>
       <c r="D85">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>702</v>
+        <v>590</v>
       </c>
       <c r="F85" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="B86" t="s">
         <v>404</v>
       </c>
+      <c r="C86" t="s">
+        <v>536</v>
+      </c>
       <c r="D86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F86" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="B87" t="s">
         <v>405</v>
       </c>
       <c r="C87" t="s">
-        <v>597</v>
+        <v>537</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>707</v>
+        <v>589</v>
       </c>
       <c r="F87" t="s">
-        <v>735</v>
+        <v>612</v>
+      </c>
+      <c r="G87" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="B88" t="s">
         <v>406</v>
       </c>
       <c r="C88" t="s">
-        <v>598</v>
+        <v>538</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F88" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="B89" t="s">
         <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>599</v>
+        <v>539</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F89" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="B90" t="s">
         <v>408</v>
       </c>
       <c r="C90" t="s">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="F90" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B91" t="s">
         <v>409</v>
       </c>
       <c r="C91" t="s">
-        <v>601</v>
+        <v>541</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>702</v>
+        <v>590</v>
       </c>
       <c r="F91" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B92" t="s">
         <v>410</v>
       </c>
       <c r="C92" t="s">
-        <v>602</v>
+        <v>542</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="F92" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="B93" t="s">
         <v>411</v>
       </c>
       <c r="C93" t="s">
-        <v>603</v>
+        <v>543</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>707</v>
+        <v>589</v>
       </c>
       <c r="F93" t="s">
-        <v>735</v>
-      </c>
-      <c r="G93" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="B94" t="s">
         <v>412</v>
       </c>
       <c r="C94" t="s">
-        <v>604</v>
+        <v>544</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
-        <v>707</v>
+        <v>589</v>
       </c>
       <c r="F94" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="B95" t="s">
         <v>413</v>
       </c>
       <c r="C95" t="s">
-        <v>605</v>
+        <v>545</v>
       </c>
       <c r="D95">
-        <v>2978</v>
+        <v>374</v>
       </c>
       <c r="E95" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F95" t="s">
-        <v>732</v>
+        <v>613</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="B96" t="s">
         <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>606</v>
+        <v>546</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>717</v>
+        <v>589</v>
       </c>
       <c r="F96" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="B97" t="s">
         <v>415</v>
       </c>
       <c r="C97" t="s">
-        <v>607</v>
+        <v>547</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E97" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="F97" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="B98" t="s">
         <v>416</v>
       </c>
       <c r="C98" t="s">
-        <v>608</v>
+        <v>548</v>
       </c>
       <c r="D98">
-        <v>131</v>
+        <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F98" t="s">
-        <v>733</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="B99" t="s">
         <v>417</v>
       </c>
       <c r="C99" t="s">
-        <v>609</v>
+        <v>493</v>
       </c>
       <c r="D99">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>702</v>
+        <v>592</v>
       </c>
       <c r="F99" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="B100" t="s">
         <v>418</v>
       </c>
-      <c r="C100" t="s">
-        <v>610</v>
-      </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F100" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="B101" t="s">
         <v>419</v>
       </c>
       <c r="C101" t="s">
-        <v>611</v>
+        <v>549</v>
       </c>
       <c r="D101">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>718</v>
+        <v>604</v>
       </c>
       <c r="F101" t="s">
-        <v>731</v>
+        <v>613</v>
+      </c>
+      <c r="G101" t="s">
+        <v>617</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="B102" t="s">
         <v>420</v>
       </c>
       <c r="C102" t="s">
-        <v>612</v>
+        <v>550</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E102" t="s">
-        <v>719</v>
+        <v>605</v>
       </c>
       <c r="F102" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="B103" t="s">
         <v>421</v>
       </c>
       <c r="C103" t="s">
+        <v>551</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
+        <v>589</v>
+      </c>
+      <c r="F103" t="s">
         <v>613</v>
       </c>
-      <c r="D103">
-        <v>21</v>
-      </c>
-      <c r="E103" t="s">
-        <v>702</v>
-      </c>
-      <c r="F103" t="s">
-        <v>733</v>
-      </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="B104" t="s">
         <v>422</v>
       </c>
       <c r="C104" t="s">
+        <v>552</v>
+      </c>
+      <c r="D104">
+        <v>19</v>
+      </c>
+      <c r="E104" t="s">
+        <v>589</v>
+      </c>
+      <c r="F104" t="s">
         <v>614</v>
       </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
-        <v>702</v>
-      </c>
-      <c r="F104" t="s">
-        <v>735</v>
-      </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="B105" t="s">
         <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>615</v>
+        <v>553</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="E105" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F105" t="s">
-        <v>733</v>
+        <v>611</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="B106" t="s">
         <v>424</v>
       </c>
       <c r="C106" t="s">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="D106">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>720</v>
+        <v>592</v>
       </c>
       <c r="F106" t="s">
-        <v>732</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>213</v>
+        <v>261</v>
       </c>
       <c r="B107" t="s">
         <v>425</v>
       </c>
       <c r="C107" t="s">
-        <v>616</v>
+        <v>554</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>702</v>
+        <v>606</v>
       </c>
       <c r="F107" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="B108" t="s">
         <v>426</v>
       </c>
       <c r="C108" t="s">
-        <v>612</v>
+        <v>555</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E108" t="s">
-        <v>721</v>
+        <v>589</v>
       </c>
       <c r="F108" t="s">
-        <v>735</v>
+        <v>614</v>
+      </c>
+      <c r="G108" t="s">
+        <v>618</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>215</v>
+        <v>263</v>
       </c>
       <c r="B109" t="s">
         <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>617</v>
+        <v>556</v>
       </c>
       <c r="D109">
-        <v>527</v>
+        <v>3</v>
       </c>
       <c r="E109" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F109" t="s">
-        <v>732</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="B110" t="s">
         <v>428</v>
       </c>
       <c r="C110" t="s">
-        <v>618</v>
+        <v>557</v>
       </c>
       <c r="D110">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="E110" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F110" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c r="B111" t="s">
         <v>429</v>
       </c>
       <c r="C111" t="s">
-        <v>619</v>
+        <v>558</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F111" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="B112" t="s">
         <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>620</v>
+        <v>559</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>702</v>
+        <v>607</v>
       </c>
       <c r="F112" t="s">
-        <v>733</v>
+        <v>613</v>
+      </c>
+      <c r="G112" t="s">
+        <v>559</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="B113" t="s">
         <v>431</v>
       </c>
       <c r="C113" t="s">
-        <v>621</v>
+        <v>560</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="E113" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F113" t="s">
-        <v>734</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="B114" t="s">
         <v>432</v>
       </c>
       <c r="C114" t="s">
-        <v>602</v>
+        <v>561</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="F114" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
       <c r="B115" t="s">
         <v>433</v>
       </c>
       <c r="C115" t="s">
-        <v>622</v>
+        <v>562</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F115" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="B116" t="s">
         <v>434</v>
       </c>
       <c r="C116" t="s">
-        <v>623</v>
+        <v>563</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F116" t="s">
-        <v>733</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="B117" t="s">
         <v>435</v>
       </c>
       <c r="C117" t="s">
-        <v>624</v>
+        <v>564</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="F117" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="B118" t="s">
         <v>436</v>
       </c>
       <c r="C118" t="s">
-        <v>625</v>
+        <v>565</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F118" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="B119" t="s">
         <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>626</v>
+        <v>566</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="E119" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F119" t="s">
-        <v>735</v>
+        <v>611</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="B120" t="s">
         <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>627</v>
+        <v>567</v>
       </c>
       <c r="D120">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F120" t="s">
-        <v>734</v>
-      </c>
-      <c r="G120" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="B121" t="s">
         <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>628</v>
+        <v>568</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F121" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>228</v>
+        <v>281</v>
       </c>
       <c r="B122" t="s">
         <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>629</v>
+        <v>569</v>
       </c>
       <c r="D122">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E122" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F122" t="s">
-        <v>735</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>229</v>
+        <v>282</v>
       </c>
       <c r="B123" t="s">
         <v>441</v>
       </c>
-      <c r="C123" t="s">
-        <v>630</v>
-      </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F123" t="s">
-        <v>734</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>230</v>
+        <v>283</v>
       </c>
       <c r="B124" t="s">
         <v>442</v>
       </c>
       <c r="C124" t="s">
-        <v>631</v>
+        <v>570</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="F124" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>231</v>
+        <v>284</v>
       </c>
       <c r="B125" t="s">
         <v>443</v>
       </c>
       <c r="C125" t="s">
-        <v>632</v>
+        <v>511</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F125" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>232</v>
+        <v>285</v>
       </c>
       <c r="B126" t="s">
         <v>444</v>
       </c>
       <c r="C126" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F126" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="B127" t="s">
         <v>445</v>
       </c>
       <c r="C127" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="D127">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F127" t="s">
-        <v>731</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="B128" t="s">
         <v>446</v>
       </c>
       <c r="C128" t="s">
-        <v>633</v>
+        <v>573</v>
       </c>
       <c r="D128">
-        <v>10260</v>
+        <v>3</v>
       </c>
       <c r="E128" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F128" t="s">
-        <v>732</v>
+        <v>613</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="B129" t="s">
         <v>447</v>
       </c>
       <c r="C129" t="s">
-        <v>635</v>
+        <v>574</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F129" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="B130" t="s">
         <v>448</v>
       </c>
       <c r="C130" t="s">
-        <v>636</v>
+        <v>575</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="E130" t="s">
-        <v>722</v>
+        <v>589</v>
       </c>
       <c r="F130" t="s">
-        <v>733</v>
+        <v>614</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="B131" t="s">
         <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>637</v>
+        <v>576</v>
       </c>
       <c r="D131">
-        <v>374</v>
+        <v>10</v>
       </c>
       <c r="E131" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F131" t="s">
-        <v>735</v>
+        <v>610</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="B132" t="s">
         <v>450</v>
       </c>
       <c r="C132" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>10255</v>
       </c>
       <c r="E132" t="s">
-        <v>723</v>
+        <v>589</v>
       </c>
       <c r="F132" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
       <c r="B133" t="s">
         <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>638</v>
+        <v>578</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>702</v>
+        <v>592</v>
       </c>
       <c r="F133" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="B134" t="s">
         <v>452</v>
       </c>
       <c r="C134" t="s">
-        <v>639</v>
+        <v>579</v>
       </c>
       <c r="D134">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F134" t="s">
-        <v>733</v>
+        <v>613</v>
+      </c>
+      <c r="G134" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="B135" t="s">
         <v>453</v>
       </c>
       <c r="C135" t="s">
-        <v>640</v>
+        <v>580</v>
       </c>
       <c r="D135">
-        <v>22</v>
+        <v>314</v>
       </c>
       <c r="E135" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F135" t="s">
-        <v>733</v>
+        <v>613</v>
+      </c>
+      <c r="G135" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="B136" t="s">
         <v>454</v>
       </c>
       <c r="C136" t="s">
-        <v>641</v>
+        <v>463</v>
       </c>
       <c r="D136">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>702</v>
+        <v>608</v>
       </c>
       <c r="F136" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="B137" t="s">
         <v>455</v>
       </c>
       <c r="C137" t="s">
-        <v>642</v>
+        <v>463</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>702</v>
+        <v>608</v>
       </c>
       <c r="F137" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>244</v>
+        <v>304</v>
       </c>
       <c r="B138" t="s">
         <v>456</v>
       </c>
       <c r="C138" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="D138">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F138" t="s">
-        <v>733</v>
+        <v>613</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="B139" t="s">
         <v>457</v>
       </c>
       <c r="C139" t="s">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="E139" t="s">
-        <v>707</v>
+        <v>589</v>
       </c>
       <c r="F139" t="s">
-        <v>735</v>
+        <v>613</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>246</v>
+        <v>307</v>
       </c>
       <c r="B140" t="s">
         <v>458</v>
       </c>
       <c r="C140" t="s">
-        <v>644</v>
+        <v>583</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F140" t="s">
-        <v>731</v>
+        <v>613</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="B141" t="s">
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>645</v>
+        <v>584</v>
       </c>
       <c r="D141">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F141" t="s">
-        <v>733</v>
+        <v>612</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="B142" t="s">
         <v>460</v>
       </c>
+      <c r="C142" t="s">
+        <v>585</v>
+      </c>
       <c r="D142">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E142" t="s">
-        <v>702</v>
+        <v>589</v>
       </c>
       <c r="F142" t="s">
-        <v>735</v>
+        <v>614</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="B143" t="s">
         <v>461</v>
       </c>
       <c r="C143" t="s">
-        <v>646</v>
+        <v>586</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E143" t="s">
-        <v>724</v>
+        <v>609</v>
       </c>
       <c r="F143" t="s">
-        <v>735</v>
-      </c>
-      <c r="G143" t="s">
-        <v>739</v>
+        <v>611</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="B144" t="s">
         <v>462</v>
       </c>
       <c r="C144" t="s">
-        <v>647</v>
+        <v>587</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E144" t="s">
-        <v>725</v>
+        <v>589</v>
       </c>
       <c r="F144" t="s">
-        <v>735</v>
-      </c>
-      <c r="G144" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" t="s">
-        <v>251</v>
-      </c>
-      <c r="B145" t="s">
-        <v>463</v>
-      </c>
-      <c r="C145" t="s">
-        <v>648</v>
-      </c>
-      <c r="D145">
-        <v>5</v>
-      </c>
-      <c r="E145" t="s">
-        <v>726</v>
-      </c>
-      <c r="F145" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146" t="s">
-        <v>252</v>
-      </c>
-      <c r="B146" t="s">
-        <v>464</v>
-      </c>
-      <c r="C146" t="s">
-        <v>649</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>702</v>
-      </c>
-      <c r="F146" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" t="s">
-        <v>253</v>
-      </c>
-      <c r="B147" t="s">
-        <v>465</v>
-      </c>
-      <c r="C147" t="s">
-        <v>535</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>702</v>
-      </c>
-      <c r="F147" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148" t="s">
-        <v>254</v>
-      </c>
-      <c r="B148" t="s">
-        <v>466</v>
-      </c>
-      <c r="C148" t="s">
-        <v>650</v>
-      </c>
-      <c r="D148">
-        <v>19</v>
-      </c>
-      <c r="E148" t="s">
-        <v>702</v>
-      </c>
-      <c r="F148" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" t="s">
-        <v>255</v>
-      </c>
-      <c r="B149" t="s">
-        <v>467</v>
-      </c>
-      <c r="C149" t="s">
-        <v>651</v>
-      </c>
-      <c r="D149">
-        <v>597</v>
-      </c>
-      <c r="E149" t="s">
-        <v>702</v>
-      </c>
-      <c r="F149" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" t="s">
-        <v>256</v>
-      </c>
-      <c r="B150" t="s">
-        <v>468</v>
-      </c>
-      <c r="C150" t="s">
-        <v>652</v>
-      </c>
-      <c r="D150">
-        <v>135</v>
-      </c>
-      <c r="E150" t="s">
-        <v>702</v>
-      </c>
-      <c r="F150" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151" t="s">
-        <v>257</v>
-      </c>
-      <c r="B151" t="s">
-        <v>469</v>
-      </c>
-      <c r="C151" t="s">
-        <v>653</v>
-      </c>
-      <c r="D151">
-        <v>5</v>
-      </c>
-      <c r="E151" t="s">
-        <v>702</v>
-      </c>
-      <c r="F151" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" t="s">
-        <v>258</v>
-      </c>
-      <c r="B152" t="s">
-        <v>470</v>
-      </c>
-      <c r="C152" t="s">
-        <v>555</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="E152" t="s">
-        <v>707</v>
-      </c>
-      <c r="F152" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" t="s">
-        <v>259</v>
-      </c>
-      <c r="B153" t="s">
-        <v>471</v>
-      </c>
-      <c r="C153" t="s">
-        <v>654</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-      <c r="E153" t="s">
-        <v>702</v>
-      </c>
-      <c r="F153" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" t="s">
-        <v>260</v>
-      </c>
-      <c r="B154" t="s">
-        <v>472</v>
-      </c>
-      <c r="C154" t="s">
-        <v>655</v>
-      </c>
-      <c r="D154">
-        <v>761</v>
-      </c>
-      <c r="E154" t="s">
-        <v>702</v>
-      </c>
-      <c r="F154" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155" t="s">
-        <v>261</v>
-      </c>
-      <c r="B155" t="s">
-        <v>473</v>
-      </c>
-      <c r="C155" t="s">
-        <v>653</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
-      </c>
-      <c r="E155" t="s">
-        <v>727</v>
-      </c>
-      <c r="F155" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" t="s">
-        <v>262</v>
-      </c>
-      <c r="B156" t="s">
-        <v>474</v>
-      </c>
-      <c r="C156" t="s">
-        <v>656</v>
-      </c>
-      <c r="D156">
-        <v>16</v>
-      </c>
-      <c r="E156" t="s">
-        <v>702</v>
-      </c>
-      <c r="F156" t="s">
-        <v>733</v>
-      </c>
-      <c r="G156" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" t="s">
-        <v>263</v>
-      </c>
-      <c r="B157" t="s">
-        <v>475</v>
-      </c>
-      <c r="C157" t="s">
-        <v>657</v>
-      </c>
-      <c r="D157">
-        <v>3</v>
-      </c>
-      <c r="E157" t="s">
-        <v>702</v>
-      </c>
-      <c r="F157" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" t="s">
-        <v>264</v>
-      </c>
-      <c r="B158" t="s">
-        <v>476</v>
-      </c>
-      <c r="C158" t="s">
-        <v>658</v>
-      </c>
-      <c r="D158">
-        <v>2</v>
-      </c>
-      <c r="E158" t="s">
-        <v>702</v>
-      </c>
-      <c r="F158" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" t="s">
-        <v>265</v>
-      </c>
-      <c r="B159" t="s">
-        <v>477</v>
-      </c>
-      <c r="C159" t="s">
-        <v>659</v>
-      </c>
-      <c r="D159">
-        <v>8</v>
-      </c>
-      <c r="E159" t="s">
-        <v>702</v>
-      </c>
-      <c r="F159" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160" t="s">
-        <v>266</v>
-      </c>
-      <c r="B160" t="s">
-        <v>478</v>
-      </c>
-      <c r="C160" t="s">
-        <v>660</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="E160" t="s">
-        <v>702</v>
-      </c>
-      <c r="F160" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
-        <v>267</v>
-      </c>
-      <c r="B161" t="s">
-        <v>479</v>
-      </c>
-      <c r="C161" t="s">
-        <v>661</v>
-      </c>
-      <c r="D161">
-        <v>11</v>
-      </c>
-      <c r="E161" t="s">
-        <v>726</v>
-      </c>
-      <c r="F161" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
-        <v>268</v>
-      </c>
-      <c r="B162" t="s">
-        <v>480</v>
-      </c>
-      <c r="C162" t="s">
-        <v>662</v>
-      </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="E162" t="s">
-        <v>728</v>
-      </c>
-      <c r="F162" t="s">
-        <v>735</v>
-      </c>
-      <c r="G162" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" t="s">
-        <v>269</v>
-      </c>
-      <c r="B163" t="s">
-        <v>481</v>
-      </c>
-      <c r="C163" t="s">
-        <v>663</v>
-      </c>
-      <c r="D163">
-        <v>13</v>
-      </c>
-      <c r="E163" t="s">
-        <v>702</v>
-      </c>
-      <c r="F163" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164" t="s">
-        <v>270</v>
-      </c>
-      <c r="B164" t="s">
-        <v>482</v>
-      </c>
-      <c r="C164" t="s">
-        <v>664</v>
-      </c>
-      <c r="D164">
-        <v>134</v>
-      </c>
-      <c r="E164" t="s">
-        <v>702</v>
-      </c>
-      <c r="F164" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" t="s">
-        <v>271</v>
-      </c>
-      <c r="B165" t="s">
-        <v>483</v>
-      </c>
-      <c r="C165" t="s">
-        <v>665</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-      <c r="E165" t="s">
-        <v>702</v>
-      </c>
-      <c r="F165" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" t="s">
-        <v>272</v>
-      </c>
-      <c r="B166" t="s">
-        <v>484</v>
-      </c>
-      <c r="C166" t="s">
-        <v>666</v>
-      </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-      <c r="E166" t="s">
-        <v>702</v>
-      </c>
-      <c r="F166" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" t="s">
-        <v>273</v>
-      </c>
-      <c r="B167" t="s">
-        <v>485</v>
-      </c>
-      <c r="C167" t="s">
-        <v>667</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="E167" t="s">
-        <v>702</v>
-      </c>
-      <c r="F167" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" t="s">
-        <v>274</v>
-      </c>
-      <c r="B168" t="s">
-        <v>486</v>
-      </c>
-      <c r="C168" t="s">
-        <v>668</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="E168" t="s">
-        <v>702</v>
-      </c>
-      <c r="F168" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
-        <v>275</v>
-      </c>
-      <c r="B169" t="s">
-        <v>487</v>
-      </c>
-      <c r="C169" t="s">
-        <v>669</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="E169" t="s">
-        <v>702</v>
-      </c>
-      <c r="F169" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" t="s">
-        <v>276</v>
-      </c>
-      <c r="B170" t="s">
-        <v>488</v>
-      </c>
-      <c r="C170" t="s">
-        <v>670</v>
-      </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-      <c r="E170" t="s">
-        <v>702</v>
-      </c>
-      <c r="F170" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" t="s">
-        <v>277</v>
-      </c>
-      <c r="B171" t="s">
-        <v>489</v>
-      </c>
-      <c r="C171" t="s">
-        <v>671</v>
-      </c>
-      <c r="D171">
-        <v>242</v>
-      </c>
-      <c r="E171" t="s">
-        <v>702</v>
-      </c>
-      <c r="F171" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" t="s">
-        <v>278</v>
-      </c>
-      <c r="B172" t="s">
-        <v>490</v>
-      </c>
-      <c r="C172" t="s">
-        <v>672</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-      <c r="E172" t="s">
-        <v>702</v>
-      </c>
-      <c r="F172" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173" t="s">
-        <v>279</v>
-      </c>
-      <c r="B173" t="s">
-        <v>491</v>
-      </c>
-      <c r="C173" t="s">
-        <v>673</v>
-      </c>
-      <c r="D173">
-        <v>97</v>
-      </c>
-      <c r="E173" t="s">
-        <v>702</v>
-      </c>
-      <c r="F173" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="A174" t="s">
-        <v>280</v>
-      </c>
-      <c r="B174" t="s">
-        <v>492</v>
-      </c>
-      <c r="C174" t="s">
-        <v>674</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="E174" t="s">
-        <v>702</v>
-      </c>
-      <c r="F174" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175" t="s">
-        <v>281</v>
-      </c>
-      <c r="B175" t="s">
-        <v>493</v>
-      </c>
-      <c r="C175" t="s">
-        <v>675</v>
-      </c>
-      <c r="D175">
-        <v>12</v>
-      </c>
-      <c r="E175" t="s">
-        <v>702</v>
-      </c>
-      <c r="F175" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176" t="s">
-        <v>282</v>
-      </c>
-      <c r="B176" t="s">
-        <v>494</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="E176" t="s">
-        <v>702</v>
-      </c>
-      <c r="F176" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
-      <c r="A177" t="s">
-        <v>283</v>
-      </c>
-      <c r="B177" t="s">
-        <v>495</v>
-      </c>
-      <c r="C177" t="s">
-        <v>676</v>
-      </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="E177" t="s">
-        <v>702</v>
-      </c>
-      <c r="F177" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
-      <c r="A178" t="s">
-        <v>284</v>
-      </c>
-      <c r="B178" t="s">
-        <v>496</v>
-      </c>
-      <c r="C178" t="s">
-        <v>589</v>
-      </c>
-      <c r="D178">
-        <v>9</v>
-      </c>
-      <c r="E178" t="s">
-        <v>702</v>
-      </c>
-      <c r="F178" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179" t="s">
-        <v>285</v>
-      </c>
-      <c r="B179" t="s">
-        <v>497</v>
-      </c>
-      <c r="C179" t="s">
-        <v>677</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="E179" t="s">
-        <v>702</v>
-      </c>
-      <c r="F179" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
-      <c r="A180" t="s">
-        <v>286</v>
-      </c>
-      <c r="B180" t="s">
-        <v>498</v>
-      </c>
-      <c r="C180" t="s">
-        <v>678</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="E180" t="s">
-        <v>702</v>
-      </c>
-      <c r="F180" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
-      <c r="A181" t="s">
-        <v>287</v>
-      </c>
-      <c r="B181" t="s">
-        <v>499</v>
-      </c>
-      <c r="C181" t="s">
-        <v>679</v>
-      </c>
-      <c r="D181">
-        <v>1</v>
-      </c>
-      <c r="E181" t="s">
-        <v>702</v>
-      </c>
-      <c r="F181" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
-      <c r="A182" t="s">
-        <v>288</v>
-      </c>
-      <c r="B182" t="s">
-        <v>500</v>
-      </c>
-      <c r="C182" t="s">
-        <v>680</v>
-      </c>
-      <c r="D182">
-        <v>0</v>
-      </c>
-      <c r="E182" t="s">
-        <v>703</v>
-      </c>
-      <c r="F182" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
-      <c r="A183" t="s">
-        <v>289</v>
-      </c>
-      <c r="B183" t="s">
-        <v>501</v>
-      </c>
-      <c r="C183" t="s">
-        <v>602</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="E183" t="s">
-        <v>703</v>
-      </c>
-      <c r="F183" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
-      <c r="A184" t="s">
-        <v>290</v>
-      </c>
-      <c r="B184" t="s">
-        <v>502</v>
-      </c>
-      <c r="C184" t="s">
-        <v>681</v>
-      </c>
-      <c r="D184">
-        <v>7</v>
-      </c>
-      <c r="E184" t="s">
-        <v>707</v>
-      </c>
-      <c r="F184" t="s">
-        <v>733</v>
-      </c>
-      <c r="G184" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
-      <c r="A185" t="s">
-        <v>291</v>
-      </c>
-      <c r="B185" t="s">
-        <v>503</v>
-      </c>
-      <c r="C185" t="s">
-        <v>600</v>
-      </c>
-      <c r="D185">
-        <v>3</v>
-      </c>
-      <c r="E185" t="s">
-        <v>702</v>
-      </c>
-      <c r="F185" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
-      <c r="A186" t="s">
-        <v>292</v>
-      </c>
-      <c r="B186" t="s">
-        <v>504</v>
-      </c>
-      <c r="C186" t="s">
-        <v>682</v>
-      </c>
-      <c r="D186">
-        <v>0</v>
-      </c>
-      <c r="E186" t="s">
-        <v>702</v>
-      </c>
-      <c r="F186" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7">
-      <c r="A187" t="s">
-        <v>293</v>
-      </c>
-      <c r="B187" t="s">
-        <v>505</v>
-      </c>
-      <c r="C187" t="s">
-        <v>683</v>
-      </c>
-      <c r="D187">
-        <v>116</v>
-      </c>
-      <c r="E187" t="s">
-        <v>702</v>
-      </c>
-      <c r="F187" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7">
-      <c r="A188" t="s">
-        <v>294</v>
-      </c>
-      <c r="B188" t="s">
-        <v>506</v>
-      </c>
-      <c r="C188" t="s">
-        <v>684</v>
-      </c>
-      <c r="D188">
-        <v>10</v>
-      </c>
-      <c r="E188" t="s">
-        <v>702</v>
-      </c>
-      <c r="F188" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
-      <c r="A189" t="s">
-        <v>295</v>
-      </c>
-      <c r="B189" t="s">
-        <v>507</v>
-      </c>
-      <c r="C189" t="s">
-        <v>685</v>
-      </c>
-      <c r="D189">
-        <v>10255</v>
-      </c>
-      <c r="E189" t="s">
-        <v>702</v>
-      </c>
-      <c r="F189" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7">
-      <c r="A190" t="s">
-        <v>296</v>
-      </c>
-      <c r="B190" t="s">
-        <v>508</v>
-      </c>
-      <c r="C190" t="s">
-        <v>686</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="E190" t="s">
-        <v>707</v>
-      </c>
-      <c r="F190" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7">
-      <c r="A191" t="s">
-        <v>297</v>
-      </c>
-      <c r="B191" t="s">
-        <v>509</v>
-      </c>
-      <c r="C191" t="s">
-        <v>687</v>
-      </c>
-      <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="E191" t="s">
-        <v>702</v>
-      </c>
-      <c r="F191" t="s">
-        <v>735</v>
-      </c>
-      <c r="G191" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7">
-      <c r="A192" t="s">
-        <v>298</v>
-      </c>
-      <c r="B192" t="s">
-        <v>510</v>
-      </c>
-      <c r="C192" t="s">
-        <v>688</v>
-      </c>
-      <c r="D192">
-        <v>0</v>
-      </c>
-      <c r="E192" t="s">
-        <v>707</v>
-      </c>
-      <c r="F192" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7">
-      <c r="A193" t="s">
-        <v>299</v>
-      </c>
-      <c r="B193" t="s">
-        <v>511</v>
-      </c>
-      <c r="C193" t="s">
-        <v>689</v>
-      </c>
-      <c r="D193">
-        <v>314</v>
-      </c>
-      <c r="E193" t="s">
-        <v>702</v>
-      </c>
-      <c r="F193" t="s">
-        <v>735</v>
-      </c>
-      <c r="G193" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
-      <c r="A194" t="s">
-        <v>300</v>
-      </c>
-      <c r="B194" t="s">
-        <v>512</v>
-      </c>
-      <c r="C194" t="s">
-        <v>690</v>
-      </c>
-      <c r="D194">
-        <v>49</v>
-      </c>
-      <c r="E194" t="s">
-        <v>702</v>
-      </c>
-      <c r="F194" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
-      <c r="A195" t="s">
-        <v>301</v>
-      </c>
-      <c r="B195" t="s">
-        <v>513</v>
-      </c>
-      <c r="C195" t="s">
-        <v>691</v>
-      </c>
-      <c r="D195">
-        <v>7</v>
-      </c>
-      <c r="E195" t="s">
-        <v>702</v>
-      </c>
-      <c r="F195" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
-      <c r="A196" t="s">
-        <v>302</v>
-      </c>
-      <c r="B196" t="s">
-        <v>514</v>
-      </c>
-      <c r="C196" t="s">
-        <v>526</v>
-      </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-      <c r="E196" t="s">
-        <v>729</v>
-      </c>
-      <c r="F196" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
-      <c r="A197" t="s">
-        <v>303</v>
-      </c>
-      <c r="B197" t="s">
-        <v>515</v>
-      </c>
-      <c r="C197" t="s">
-        <v>526</v>
-      </c>
-      <c r="D197">
-        <v>0</v>
-      </c>
-      <c r="E197" t="s">
-        <v>729</v>
-      </c>
-      <c r="F197" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
-      <c r="A198" t="s">
-        <v>304</v>
-      </c>
-      <c r="B198" t="s">
-        <v>516</v>
-      </c>
-      <c r="C198" t="s">
-        <v>692</v>
-      </c>
-      <c r="D198">
-        <v>0</v>
-      </c>
-      <c r="E198" t="s">
-        <v>702</v>
-      </c>
-      <c r="F198" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
-      <c r="A199" t="s">
-        <v>305</v>
-      </c>
-      <c r="B199" t="s">
-        <v>517</v>
-      </c>
-      <c r="C199" t="s">
-        <v>693</v>
-      </c>
-      <c r="D199">
-        <v>438</v>
-      </c>
-      <c r="E199" t="s">
-        <v>702</v>
-      </c>
-      <c r="F199" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
-      <c r="A200" t="s">
-        <v>306</v>
-      </c>
-      <c r="B200" t="s">
-        <v>518</v>
-      </c>
-      <c r="C200" t="s">
-        <v>694</v>
-      </c>
-      <c r="D200">
-        <v>126</v>
-      </c>
-      <c r="E200" t="s">
-        <v>702</v>
-      </c>
-      <c r="F200" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
-      <c r="A201" t="s">
-        <v>307</v>
-      </c>
-      <c r="B201" t="s">
-        <v>519</v>
-      </c>
-      <c r="C201" t="s">
-        <v>695</v>
-      </c>
-      <c r="D201">
-        <v>1</v>
-      </c>
-      <c r="E201" t="s">
-        <v>702</v>
-      </c>
-      <c r="F201" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
-      <c r="A202" t="s">
-        <v>308</v>
-      </c>
-      <c r="B202" t="s">
-        <v>520</v>
-      </c>
-      <c r="C202" t="s">
-        <v>696</v>
-      </c>
-      <c r="D202">
-        <v>0</v>
-      </c>
-      <c r="E202" t="s">
-        <v>702</v>
-      </c>
-      <c r="F202" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7">
-      <c r="A203" t="s">
-        <v>309</v>
-      </c>
-      <c r="B203" t="s">
-        <v>521</v>
-      </c>
-      <c r="C203" t="s">
-        <v>697</v>
-      </c>
-      <c r="D203">
-        <v>23</v>
-      </c>
-      <c r="E203" t="s">
-        <v>702</v>
-      </c>
-      <c r="F203" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7">
-      <c r="A204" t="s">
-        <v>310</v>
-      </c>
-      <c r="B204" t="s">
-        <v>522</v>
-      </c>
-      <c r="C204" t="s">
-        <v>698</v>
-      </c>
-      <c r="D204">
-        <v>26</v>
-      </c>
-      <c r="E204" t="s">
-        <v>730</v>
-      </c>
-      <c r="F204" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7">
-      <c r="A205" t="s">
-        <v>311</v>
-      </c>
-      <c r="B205" t="s">
-        <v>523</v>
-      </c>
-      <c r="C205" t="s">
-        <v>661</v>
-      </c>
-      <c r="D205">
-        <v>18</v>
-      </c>
-      <c r="E205" t="s">
-        <v>702</v>
-      </c>
-      <c r="F205" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7">
-      <c r="A206" t="s">
-        <v>312</v>
-      </c>
-      <c r="B206" t="s">
-        <v>524</v>
-      </c>
-      <c r="C206" t="s">
-        <v>699</v>
-      </c>
-      <c r="D206">
-        <v>2</v>
-      </c>
-      <c r="E206" t="s">
-        <v>702</v>
-      </c>
-      <c r="F206" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7">
-      <c r="A207" t="s">
-        <v>313</v>
-      </c>
-      <c r="B207" t="s">
-        <v>525</v>
-      </c>
-      <c r="C207" t="s">
-        <v>700</v>
-      </c>
-      <c r="D207">
-        <v>0</v>
-      </c>
-      <c r="E207" t="s">
-        <v>702</v>
-      </c>
-      <c r="F207" t="s">
-        <v>735</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="841">
   <si>
     <t>ati_all</t>
   </si>
@@ -986,6 +986,9 @@
     <t>Crown-Indigenous Relations and Northern Affairs Canada | Relations Couronne-Autochtones et Affaires du Nord Canada</t>
   </si>
   <si>
+    <t>Atlantic Canada Opportunities Agency | Agence de promotion économique du Canada atlantique</t>
+  </si>
+  <si>
     <t>Atomic Energy of Canada Limited | Énergie atomique du Canada, Limitée</t>
   </si>
   <si>
@@ -1007,6 +1010,9 @@
     <t>Business Development Bank of Canada | Banque de développement du Canada</t>
   </si>
   <si>
+    <t>Belledune Port Authority | Administration portuaire de Belledune</t>
+  </si>
+  <si>
     <t>Canadian Northern Economic Development Agency | Agence canadienne de développement économique du Nord</t>
   </si>
   <si>
@@ -1019,6 +1025,9 @@
     <t>Canadian Air Transport Security Authority | Administration canadienne de la sûreté du transport aérien</t>
   </si>
   <si>
+    <t>Copyright Board Canada | Commission du droit d'auteur du Canada</t>
+  </si>
+  <si>
     <t>Canadian Broadcasting Company | Radio-Canada</t>
   </si>
   <si>
@@ -1028,6 +1037,9 @@
     <t>Canada Council for the Arts | Conseil des arts du Canada</t>
   </si>
   <si>
+    <t>Canadian Commercial Corporation | Corporation commerciale canadienne</t>
+  </si>
+  <si>
     <t>Canadian Centre for Occupational Health and Safety | Centre canadien d'hygiène et de sécurité au travail</t>
   </si>
   <si>
@@ -1037,12 +1049,18 @@
     <t>Canadian Dairy Commission | Commission canadienne du lait</t>
   </si>
   <si>
+    <t>Canada Development Investment Corporation | Corporation de développement des investissements du Canada</t>
+  </si>
+  <si>
     <t>Canada Deposit Insurance Corporation | Société d'assurance-dépôts du Canada</t>
   </si>
   <si>
     <t>Canada Economic Development for Quebec Regions | Développement économique Canada pour les régions du Québec</t>
   </si>
   <si>
+    <t>Canada Enterprise Emergency Funding Corporation | La Corporation de financement d’urgence d’entreprises du Canada</t>
+  </si>
+  <si>
     <t>Canada Eldor Inc. | Canada Eldor Inc.</t>
   </si>
   <si>
@@ -1070,6 +1088,9 @@
     <t>Canadian Human Rights Commission | Commission canadienne des droits de la personne</t>
   </si>
   <si>
+    <t>Canada Infrastructure Bank | La Banque de l’infrastructure du Canada</t>
+  </si>
+  <si>
     <t>Immigration, Refugees and Citizenship Canada | Immigration, Réfugiés et Citoyenneté Canada</t>
   </si>
   <si>
@@ -1079,6 +1100,9 @@
     <t>Canada Innovation Corporation | La Corporation d’innovation du Canada</t>
   </si>
   <si>
+    <t>Canadian Intergovernmental Conference Secretariat | Secrétariat des conférences intergouvernementales canadiennes</t>
+  </si>
+  <si>
     <t>Canadian Institutes of Health Research | Instituts de recherche en santé du Canada</t>
   </si>
   <si>
@@ -1088,18 +1112,45 @@
     <t>Canada Industrial Relations Board | Conseil canadien des relations industrielles</t>
   </si>
   <si>
+    <t>Canadian International Trade Tribunal | Tribunal canadien du commerce extérieur</t>
+  </si>
+  <si>
     <t>Canada Lands Company CLC Limited | Société immobilière du Canada CLC limitée</t>
   </si>
   <si>
+    <t>Canada Lands Company Limited | Société immobilière du Canada Limitée</t>
+  </si>
+  <si>
     <t>Canadian Museum of History | Musée canadien de l'histoire</t>
   </si>
   <si>
+    <t>Canada Mortgage and Housing Corporation | Société canadienne d'hypothèques et de logement</t>
+  </si>
+  <si>
     <t>Canadian Museum for Human Rights | Musée canadien pour les droits de la personne</t>
   </si>
   <si>
     <t>Canadian Museum of Immigration at Pier 21 | Musée canadien de l'immigration du Quai 21</t>
   </si>
   <si>
+    <t>Canadian Museum of Nature | Musée canadien de la nature</t>
+  </si>
+  <si>
+    <t>Canada-Newfoundland and Labrador Offshore Petroleum Board | Office Canada–Terre-Neuve-et Labrador des hydrocarbures extracôtiers</t>
+  </si>
+  <si>
+    <t>Canadian Nuclear Safety Commission | Commission canadienne de sûreté nucléaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada-Nova Scotia Offshore Energy Regulator  | Régie Canada-Nouvelle-Écosse de l’énergie extracôtière </t>
+  </si>
+  <si>
+    <t>College of Patent Agents and Trademark Agents | Collège des agents de brevets et des agents de marques de commerce</t>
+  </si>
+  <si>
+    <t>Civilian Review and Complaints Commission for the RCMP | Commission civile d'examen et de traitement des plaintes relatives à la Gendarmerie royale du Canada</t>
+  </si>
+  <si>
     <t>Canada Post | Postes Canada</t>
   </si>
   <si>
@@ -1109,6 +1160,12 @@
     <t>Canadian Race Relations Foundation | La Fondation Canadienne des relations raciales</t>
   </si>
   <si>
+    <t>Canadian Radio-television and Telecommunications Commission | Conseil de la radiodiffusion et des télécommunications canadiennes</t>
+  </si>
+  <si>
+    <t>Canadian Space Agency | Agence spatiale canadienne</t>
+  </si>
+  <si>
     <t>Correctional Service of Canada | Service correctionnel du Canada</t>
   </si>
   <si>
@@ -1124,36 +1181,72 @@
     <t>Canada Science and Technology Museum | Musée des sciences et de la technologie du Canada</t>
   </si>
   <si>
+    <t>Canadian Transportation Agency | Office des transports du Canada</t>
+  </si>
+  <si>
     <t>Destination Canada | Destination Canada</t>
   </si>
   <si>
     <t>Canada Water Agency | Agence de l’eau du Canada</t>
   </si>
   <si>
+    <t>Defence Construction Canada | Construction de Défense Canada</t>
+  </si>
+  <si>
     <t>Global Affairs Canada | Affaires mondiales Canada</t>
   </si>
   <si>
+    <t>Development Finance Institution - FinDev Canada | Institution de financement du développement - FinDev Canada</t>
+  </si>
+  <si>
     <t>Fisheries and Oceans Canada | Pêches et Océans Canada</t>
   </si>
   <si>
+    <t>National Defence | Défense nationale</t>
+  </si>
+  <si>
     <t>Downsview Metro Devco Inc. | Gestion Downsview Métro Devco</t>
   </si>
   <si>
+    <t>Environment and Climate Change Canada | Environnement et Changement climatique Canada</t>
+  </si>
+  <si>
     <t>Export Development Canada | Exportation et développement Canada</t>
   </si>
   <si>
+    <t>Elections Canada | Élections Canada</t>
+  </si>
+  <si>
+    <t>RCMP External Review Committee | Comité externe d'examen de la GRC</t>
+  </si>
+  <si>
     <t>Employment and Social Development Canada | Emploi et Développement social Canada</t>
   </si>
   <si>
+    <t>Exinvest Inc. | Exinvest Inc.</t>
+  </si>
+  <si>
     <t>Federal Bridge Corporation | Société des ponts fédéraux</t>
   </si>
   <si>
+    <t>Financial Consumer Agency of Canada | Agence de la consommation en matière financière du Canada</t>
+  </si>
+  <si>
     <t>Farm Credit Canada | Financement agricole Canada</t>
   </si>
   <si>
     <t>Federal Economic Development Agency for Southern Ontario | Agence fédérale de développement économique pour le Sud de l'Ontario</t>
   </si>
   <si>
+    <t>Federal Economic Development Agency for Northern Ontario | Agence fédérale de développement économique pour le Nord de l’Ontario</t>
+  </si>
+  <si>
+    <t>Freshwater Fish Marketing Corporation | Office de commercialisation du poisson d'eau douce</t>
+  </si>
+  <si>
+    <t>Department of Finance Canada | Ministère des Finances Canada</t>
+  </si>
+  <si>
     <t>Financial Transactions and Reports Analysis Centre of Canada | Centre d'analyse des opérations et déclarations financières du Canada</t>
   </si>
   <si>
@@ -1169,6 +1262,12 @@
     <t>Farm Products Council of Canada | Conseil des produits agricoles du Canada</t>
   </si>
   <si>
+    <t>Office of the Administrator of the Fund for Railway Accidents Involving Designated Goods; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation pour les accidents ferroviaires impliquant des marchandises désignées; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
+  </si>
+  <si>
+    <t>Great Lakes Pilotage Authority Canada | Administration de pilotage des Grands Lacs Canada</t>
+  </si>
+  <si>
     <t>Gwich’in Land and Water Board | Office Gwich’in des terres et des eaux</t>
   </si>
   <si>
@@ -1178,9 +1277,15 @@
     <t>Hamilton-Oshawa  Port Authority | Administration portuaire de Hamilton-Oshawa</t>
   </si>
   <si>
+    <t>Health Canada | Santé Canada</t>
+  </si>
+  <si>
     <t>VIA HFR - VIA TGF Inc. | VIA HFR - VIA TGF Inc.</t>
   </si>
   <si>
+    <t>Historic Sites and Monuments Board of Canada | Commission des lieux et monuments historiques du Canada</t>
+  </si>
+  <si>
     <t>Impact Assessment Agency of Canada | Agence d'évaluation d'impact du Canada</t>
   </si>
   <si>
@@ -1199,6 +1304,9 @@
     <t>Department of Housing, Infrastructure and Communities | Ministère du Logement, de l’Infrastructure et des Collectivités</t>
   </si>
   <si>
+    <t>Canada Foundation for Innovation | Fondation canadienne pour l’innovation</t>
+  </si>
+  <si>
     <t>Immigration and Refugee Board of Canada | Commission de l'immigration et du statut de réfugié du Canada</t>
   </si>
   <si>
@@ -1208,9 +1316,15 @@
     <t>Jacques Cartier and Champlain Bridges Incorporated | Ponts Jacques Cartier et Champlain Incorporée</t>
   </si>
   <si>
+    <t>The Joint Federal/Provincial Commission into the April 2020 Nova Scotia Mass Casualty | Commission fédérale-provinciale sur les événements d’avril 2020 en Nouvelle Écosse</t>
+  </si>
+  <si>
     <t>Department of Justice Canada | Ministère de la Justice Canada</t>
   </si>
   <si>
+    <t>Library and Archives Canada | Bibliothèque et Archives Canada</t>
+  </si>
+  <si>
     <t>Marine Atlantic Inc. | Marine Atlantique S.C.C.</t>
   </si>
   <si>
@@ -1223,12 +1337,18 @@
     <t>Mackenzie Valley Land and Water Board | Office des terres et des eaux de la vallée du Mackenzie Valley</t>
   </si>
   <si>
+    <t>Montreal Port Authority | Administration portuaire de Montréal</t>
+  </si>
+  <si>
     <t>Military Police Complaints Commission of Canada | Commission d'examen des plaintes concernant la police militaire du Canada</t>
   </si>
   <si>
     <t>Mackenzie Valley Environmental Impact Review Board | Office d’examen des répercussions environnementales de la vallée du Mackenzie</t>
   </si>
   <si>
+    <t>National Arts Centre | Centre national des Arts</t>
+  </si>
+  <si>
     <t>The National Battlefields Commission | Commission des champs de bataille nationaux</t>
   </si>
   <si>
@@ -1250,15 +1370,30 @@
     <t>Nanaimo Port Authority | Administration portuaire de Nanaïmo</t>
   </si>
   <si>
+    <t>Northern Pipeline Agency Canada | Administration du pipe-line du Nord Canada</t>
+  </si>
+  <si>
     <t>National Research Council Canada | Conseil national de recherches Canada</t>
   </si>
   <si>
+    <t>Natural Resources Canada | Ressources naturelles Canada</t>
+  </si>
+  <si>
     <t>Natural Sciences and Engineering Research Council of Canada | Conseil de recherches en sciences naturelles et en génie du Canada</t>
   </si>
   <si>
+    <t>National Security and Intelligence Review Agency | Office de surveillance des activités en matière de sécurité nationale et de renseignement</t>
+  </si>
+  <si>
     <t>Office of the Auditor General of Canada | Bureau du vérificateur général du Canada</t>
   </si>
   <si>
+    <t xml:space="preserve">Commissioner of Canada Elections  | Commissaire aux élections fédérales </t>
+  </si>
+  <si>
+    <t>The Correctional Investigator Canada | L'Enquêteur correctionnel Canada</t>
+  </si>
+  <si>
     <t>Office of the Commissioner of Lobbying of Canada | Commissariat au lobbying du Canada</t>
   </si>
   <si>
@@ -1268,30 +1403,60 @@
     <t>Office of the Intelligence Commissioner | Bureau du commissaire au renseignement</t>
   </si>
   <si>
+    <t>Office of the Information Commissioner of Canada | Commissariat à l'information du Canada</t>
+  </si>
+  <si>
+    <t>Office of the Privacy Commissioner of Canada | Commissariat à la protection de la vie privée du Canada</t>
+  </si>
+  <si>
     <t>Old Port of Montreal Corporation Inc. | Société du Vieux-Port de Montréal Inc.</t>
   </si>
   <si>
+    <t>Law Commission of Canada | Commission du droit du Canada</t>
+  </si>
+  <si>
+    <t>Office of the Superintendent of Financial Institutions Canada | Bureau du surintendant des institutions financières Canada</t>
+  </si>
+  <si>
     <t>Office of the Secretary to the Governor General | Bureau du secrétaire du gouverneur général</t>
   </si>
   <si>
+    <t>Office of the Taxpayers' Ombudsperson | Bureau de l'ombudsman des contribuables</t>
+  </si>
+  <si>
     <t>Office of the Veterans Ombudsman | Bureau de l'ombudsman des vétérans</t>
   </si>
   <si>
     <t>Pacific Economic Development Canada | Développement économique Canada pour le Pacifique</t>
   </si>
   <si>
+    <t>Port Alberni Port Authority | Administration portuaire de Port Alberni</t>
+  </si>
+  <si>
     <t>Port of Belledune | Port de Belledune</t>
   </si>
   <si>
     <t>Parole Board of Canada | Commission des libérations conditionnelles du Canada</t>
   </si>
   <si>
+    <t>Parks Canada | Parcs Canada</t>
+  </si>
+  <si>
     <t>Canadian Heritage | Patrimoine canadien</t>
   </si>
   <si>
+    <t>Privy Council Office | Bureau du Conseil privé</t>
+  </si>
+  <si>
     <t>Parc Downsview Park Inc. | Parc Downsview Park Inc</t>
   </si>
   <si>
+    <t>Pierre Elliott Trudeau Foundation | Fondation Pierre Elliott Trudeau</t>
+  </si>
+  <si>
+    <t>Public Health Agency of Canada | Agence de la santé publique du Canada</t>
+  </si>
+  <si>
     <t>President of the King’s Privy Council for Canada | Président du Conseil privé du Roi pour le Canada</t>
   </si>
   <si>
@@ -1301,15 +1466,24 @@
     <t>Polar Knowledge Canada | Savoir polaire Canada</t>
   </si>
   <si>
+    <t>Pacific Pilotage Authority Canada | Administration de pilotage du Pacifique Canada</t>
+  </si>
+  <si>
     <t>Public Prosecution Service of Canada | Service des poursuites pénales du Canada</t>
   </si>
   <si>
     <t>Passport Canada | Passeport Canada</t>
   </si>
   <si>
+    <t>Prairies Economic Development Canada | Développement économique Canada pour les Prairies</t>
+  </si>
+  <si>
     <t>Prince Rupert Port Authority | L’Administration portuaire de Prince Rupert</t>
   </si>
   <si>
+    <t>Public Safety Canada | Sécurité publique Canada</t>
+  </si>
+  <si>
     <t>Public Service Commission of Canada | Commission de la fonction publique du Canada</t>
   </si>
   <si>
@@ -1322,6 +1496,9 @@
     <t>Office of the Public Sector Integrity Commissioner of Canada | Commissariat à l'intégrité du secteur public du Canada</t>
   </si>
   <si>
+    <t>Public Service Labour Relations Board | Commission des relations de travail dans la fonction publique</t>
+  </si>
+  <si>
     <t>Public Sector Pension Investment Board | Office d’investissement des régimes de pensions du secteur public</t>
   </si>
   <si>
@@ -1334,6 +1511,9 @@
     <t>Quebec Port Authority | Administration portuaire de Québec</t>
   </si>
   <si>
+    <t>Royal Canadian Mounted Police | Gendarmerie royale du Canada</t>
+  </si>
+  <si>
     <t>Revera Inc. | Revera Inc.</t>
   </si>
   <si>
@@ -1355,6 +1535,18 @@
     <t>St. John's Port Authority | Administration portuaire de St. John's</t>
   </si>
   <si>
+    <t xml:space="preserve">Laurentian Pilotage Authority  | Administration de pilotage des Laurentides </t>
+  </si>
+  <si>
+    <t>Sahtu Land Use Planning Board | Conseil de l’aménagement du territoire du Sahtu</t>
+  </si>
+  <si>
+    <t>Sahtu Land and Water Board | Office des terres et des eaux du Sahtu</t>
+  </si>
+  <si>
+    <t>Secretariat of the National Security and Intelligence Committee of Parliamentarians | Secrétariat du Comité des parlementaires sur la sécurité nationale et le renseignement</t>
+  </si>
+  <si>
     <t>Office of the Administrator of the Ship-source Oil Pollution Fund; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation des dommages dus à la pollution par les hydrocarbures causée par les navires; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
   </si>
   <si>
@@ -1376,9 +1568,18 @@
     <t>Status of Women Canada | Condition féminine Canada</t>
   </si>
   <si>
+    <t>Thunder Bay Port Authority | Administration portuaire de Thunder Bay</t>
+  </si>
+  <si>
     <t>Treasury Board of Canada Secretariat | Secrétariat du Conseil du Trésor du Canada</t>
   </si>
   <si>
+    <t>Transport Canada | Transports Canada</t>
+  </si>
+  <si>
+    <t>Telefilm Canada | Téléfilm Canada</t>
+  </si>
+  <si>
     <t>Trans Mountain Corporation | Trans Mountain Corporation</t>
   </si>
   <si>
@@ -1391,6 +1592,9 @@
     <t>Transportation Safety Board of Canada | Bureau de la sécurité des transports du Canada</t>
   </si>
   <si>
+    <t>Veterans Affairs Canada | Anciens Combattants Canada</t>
+  </si>
+  <si>
     <t>Vancouver Fraser Port Authority | Administration portuaire Vancouver Fraser</t>
   </si>
   <si>
@@ -1406,6 +1610,12 @@
     <t>Western Economic Diversification Canada | Diversification de l'économie de l'Ouest Canada</t>
   </si>
   <si>
+    <t>Windsor-Detroit Bridge Authority | Autorité du pont Windsor-Détroit</t>
+  </si>
+  <si>
+    <t>Yukon Environmental and Socio-economic Assessment Board | Office d’évaluation environnementale et socio-économique du Yukon</t>
+  </si>
+  <si>
     <t>atip-aiprp@cdev.gc.ca</t>
   </si>
   <si>
@@ -1415,6 +1625,9 @@
     <t>aadnc.atiprequest-aiprpdemande.aandc@canada.ca</t>
   </si>
   <si>
+    <t>atip-aiprp@acoa-apeca.gc.ca</t>
+  </si>
+  <si>
     <t>igaudreault@aecl.ca</t>
   </si>
   <si>
@@ -1436,6 +1649,9 @@
     <t>atip-aiprp@bdc.ca</t>
   </si>
   <si>
+    <t>moffitt@portofbelledune.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@cannor.gc.ca</t>
   </si>
   <si>
@@ -1445,6 +1661,9 @@
     <t>atip@catsa.gc.ca</t>
   </si>
   <si>
+    <t>nancy.laframboise@cb-cda.gc.ca</t>
+  </si>
+  <si>
     <t>Peter.Hull@cbc.ca</t>
   </si>
   <si>
@@ -1454,6 +1673,9 @@
     <t>atip-aiprp@canadacouncil.ca</t>
   </si>
   <si>
+    <t>atip.aiprp@ccc.ca</t>
+  </si>
+  <si>
     <t>atip_aiprp@ccohs.ca</t>
   </si>
   <si>
@@ -1487,6 +1709,9 @@
     <t>atip.aiprp@chrc-ccdp.gc.ca</t>
   </si>
   <si>
+    <t>atip-aiprp@cib-bic.ca</t>
+  </si>
+  <si>
     <t>ATIP-AIPRP@cic.gc.ca</t>
   </si>
   <si>
@@ -1502,12 +1727,33 @@
     <t>AIPRP-ATIP@museedelhistoire.ca</t>
   </si>
   <si>
+    <t>ATIP-AIPRP@cmhc.ca</t>
+  </si>
+  <si>
     <t>atip@humanrights.ca</t>
   </si>
   <si>
     <t>ablack@pier21.ca</t>
   </si>
   <si>
+    <t>kdoucette@nature.ca</t>
+  </si>
+  <si>
+    <t>TBennett@cnlopb.nl.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@cnsc-ccsn.gc.ca</t>
+  </si>
+  <si>
+    <t>atip@cnsoer.ca</t>
+  </si>
+  <si>
+    <t>adiaz@cpata-cabamc.ca</t>
+  </si>
+  <si>
+    <t>ATIP.AIPRP@crcc-ccetp.gc.ca</t>
+  </si>
+  <si>
     <t>ATIP_AIPRP@canadapost.postescanada.ca</t>
   </si>
   <si>
@@ -1517,6 +1763,12 @@
     <t>atavassoli@crrf-fcrr.ca</t>
   </si>
   <si>
+    <t>AIPRP-ATIP@crtc.gc.ca</t>
+  </si>
+  <si>
+    <t>AIPRP-ATIP@asc-csa.gc.ca</t>
+  </si>
+  <si>
     <t>CSC.ATIP-AIPRP.SCC@csc-scc.gc.ca</t>
   </si>
   <si>
@@ -1532,33 +1784,66 @@
     <t>atip-aiprp@ingeniumcanada.org</t>
   </si>
   <si>
+    <t>OTC.AIPRP-ATIP.CTA@otc-cta.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@destinationcanada.com</t>
   </si>
   <si>
     <t>atip-aiprp@cwa-aec.gc.ca</t>
   </si>
   <si>
+    <t>ATIP-AIPRP@DCC-CDC.gc.ca</t>
+  </si>
+  <si>
     <t>dcp@international.gc.ca</t>
   </si>
   <si>
+    <t>atipteam@edc.ca</t>
+  </si>
+  <si>
     <t>atip-laiprp@dfo-mpo.gc.ca</t>
   </si>
   <si>
+    <t>ATIP-AIPRP@forces.gc.ca</t>
+  </si>
+  <si>
     <t>atip@northcrestdev.ca</t>
   </si>
   <si>
-    <t>atipteam@edc.ca</t>
+    <t>ecatip-ecaiprp@ec.gc.ca</t>
+  </si>
+  <si>
+    <t>aiprp-atip@elections.ca</t>
+  </si>
+  <si>
+    <t>corporateandhrservices-servicesgenerauxetrh@erc-cee.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIPteam@edc.ca</t>
   </si>
   <si>
     <t>info@federalbridge.ca</t>
   </si>
   <si>
+    <t>Nathalie.forester@fcac-acfc.gc.ca</t>
+  </si>
+  <si>
     <t>ATIP_AIPRP@fcc-fac.ca</t>
   </si>
   <si>
     <t>atip-aiprp@feddevontario.gc.ca</t>
   </si>
   <si>
+    <t>fednor-atipinbox@ised-isde.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIPcontrol@freshwaterfish.com</t>
+  </si>
+  <si>
+    <t>fin.atip-aiprp.fin@canada.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@fintrac-canafe.gc.ca</t>
   </si>
   <si>
@@ -1571,6 +1856,12 @@
     <t>FPCATIP-AIPRPCPAC.CPAC@canada.ca</t>
   </si>
   <si>
+    <t>atip-aiprp@sr-nr.gc.ca</t>
+  </si>
+  <si>
+    <t>mpoirier@glpa-apgl.com</t>
+  </si>
+  <si>
     <t>snorrish@wlwb.ca</t>
   </si>
   <si>
@@ -1580,9 +1871,15 @@
     <t>atip@hopaports.ca</t>
   </si>
   <si>
+    <t>access.informal-demandes.informelles@hc-sc.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@hfr-tgf.ca</t>
   </si>
   <si>
+    <t>pc.clmhc-hsmbc.pc@canada.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@iaac-aeic.gc.ca</t>
   </si>
   <si>
@@ -1601,6 +1898,9 @@
     <t>atip-aiprp@infc.gc.ca</t>
   </si>
   <si>
+    <t>isabelle.henrie@innovation.ca</t>
+  </si>
+  <si>
     <t>atip@irb-cisr.gc.ca</t>
   </si>
   <si>
@@ -1610,6 +1910,9 @@
     <t>ATIP-AIPRP-JusticeCanada@justice.gc.ca</t>
   </si>
   <si>
+    <t>daiprp-atipd@bac-lac.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@ma.ca</t>
   </si>
   <si>
@@ -1619,12 +1922,18 @@
     <t>atip@mint.ca</t>
   </si>
   <si>
+    <t>rouaneta@port-montreal.com</t>
+  </si>
+  <si>
     <t>atip-aiprp@mpcc-cppm.gc.ca</t>
   </si>
   <si>
     <t>atipcoordinator@reviewboard.ca</t>
   </si>
   <si>
+    <t>carl.martin@nac-cna.ca</t>
+  </si>
+  <si>
     <t>anne.chouinard@ccbn-nbc.gc.ca</t>
   </si>
   <si>
@@ -1646,15 +1955,24 @@
     <t>bwashburn@npa.ca</t>
   </si>
   <si>
+    <t>AIPRP.ATIP@NRCan-RNCan.gc.ca</t>
+  </si>
+  <si>
     <t>ATIP-AIPRP@nrc-cnrc.gc.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@NSERC-CRSNG.GC.CA</t>
   </si>
   <si>
+    <t>ATIP-AIPRP@nsira-ossnr.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@oag-bvg.gc.ca</t>
   </si>
   <si>
+    <t>jean-frederic.boulais@oci-bec.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@ocl-cal.gc.ca</t>
   </si>
   <si>
@@ -1664,39 +1982,72 @@
     <t>Info@ico-bcr.gc.ca</t>
   </si>
   <si>
+    <t>ATIP-Services-AIPRP@oic-ci.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@priv.gc.ca</t>
+  </si>
+  <si>
+    <t>BMS-SGA@lcc-cdc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@osfi-bsif.gc.ca</t>
+  </si>
+  <si>
+    <t>josee.gaudet@oto-boc.gc.ca</t>
+  </si>
+  <si>
     <t>ovoatip-bovaiprp@ombudsman-veterans.gc.ca</t>
   </si>
   <si>
     <t>pacifican.atip-aiprp@pacifican.gc.ca</t>
   </si>
   <si>
-    <t>moffitt@portofbelledune.ca</t>
+    <t>molson@papa-appa.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@PBC-CLCC.GC.CA</t>
   </si>
   <si>
+    <t>aiprp-atip@pc.gc.ca</t>
+  </si>
+  <si>
     <t>aiprp-atip@pch.gc.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@pco-bcp.gc.ca</t>
   </si>
   <si>
+    <t>communications@FondationTrudeau.ca</t>
+  </si>
+  <si>
+    <t>access.informal-demandes.informelles@phac-aspc.gc.ca</t>
+  </si>
+  <si>
     <t>pmprb.atip-aiprb.cepmb@pmprb-cepmb.gc.ca</t>
   </si>
   <si>
     <t>Brodie.larocque@polar-polaire.gc.ca</t>
   </si>
   <si>
+    <t>kchong@ppa.gc.ca</t>
+  </si>
+  <si>
     <t>ATIP-AIPRP@ppsc-sppc.gc.ca</t>
   </si>
   <si>
     <t>ATIP-AIPRP@pptc.gc.ca</t>
   </si>
   <si>
+    <t>atip-aiprp@prairiescan.gc.ca</t>
+  </si>
+  <si>
     <t>accesstoinformation@rupertport.com</t>
   </si>
   <si>
+    <t>atip-aiprp@ps-sp.gc.ca</t>
+  </si>
+  <si>
     <t>CFP.AIPRP-ATIP.PSC@cfp-psc.gc.ca</t>
   </si>
   <si>
@@ -1709,6 +2060,9 @@
     <t>info@psic-ispc.gc.ca</t>
   </si>
   <si>
+    <t>Julie.Raymond@pslrb-crtfp.gc.ca</t>
+  </si>
+  <si>
     <t>ATIP@investpsp.ca</t>
   </si>
   <si>
@@ -1721,6 +2075,9 @@
     <t>demande-acces@portquebec.ca</t>
   </si>
   <si>
+    <t>ATIP-AIPRP@rcmp-grc.gc.ca</t>
+  </si>
+  <si>
     <t>info@investpsp.ca</t>
   </si>
   <si>
@@ -1736,7 +2093,13 @@
     <t>shanrahan@sjpa-apsj.com</t>
   </si>
   <si>
-    <t>atip-aiprp@sr-nr.gc.ca</t>
+    <t>Josee.Bonneville@apl.gc.ca</t>
+  </si>
+  <si>
+    <t>exec_director@sahtulanduseplan.org</t>
+  </si>
+  <si>
+    <t>Secretariat@nsicop-cpsnr.gc.ca</t>
   </si>
   <si>
     <t>apoudrier@portsaguenay.ca</t>
@@ -1757,15 +2120,27 @@
     <t>anick.perreault@swc-cfc.gc.ca</t>
   </si>
   <si>
+    <t>tbport@tbaytel.net</t>
+  </si>
+  <si>
     <t>atip.aiprp@tbs-sct.gc.ca</t>
   </si>
   <si>
+    <t>ATIP/AIPRP@tc.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@telefilm.ca</t>
+  </si>
+  <si>
     <t>DEl-Jawhary@portstoronto.com</t>
   </si>
   <si>
     <t>AIPRP-ATIP@bst-tsb.gc.ca</t>
   </si>
   <si>
+    <t>atip-aiprp@veterans.gc.ca</t>
+  </si>
+  <si>
     <t>AccesstoInformation@portmetrovancouver.com</t>
   </si>
   <si>
@@ -1778,7 +2153,10 @@
     <t>FEGC.AIPRP-ATIP.WAGE@fegc-wage.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@prairiescan.gc.ca</t>
+    <t>Cordell.Lewis@wdbridge.com</t>
+  </si>
+  <si>
+    <t>atip@yesab.ca</t>
   </si>
   <si>
     <t>2025-09-09</t>
@@ -1790,9 +2168,15 @@
     <t>2018-08-21</t>
   </si>
   <si>
+    <t>2023-09-16</t>
+  </si>
+  <si>
     <t>2019-12-12</t>
   </si>
   <si>
+    <t>2021-01-09</t>
+  </si>
+  <si>
     <t>2018-07-27</t>
   </si>
   <si>
@@ -1805,18 +2189,24 @@
     <t>2023-11-09</t>
   </si>
   <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
     <t>2023-03-28</t>
   </si>
   <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
     <t>2024-11-21</t>
   </si>
   <si>
+    <t>2023-06-13</t>
+  </si>
+  <si>
     <t>2025-06-25</t>
   </si>
   <si>
+    <t>2021-12-23</t>
+  </si>
+  <si>
     <t>2023-12-01</t>
   </si>
   <si>
@@ -1829,6 +2219,18 @@
     <t>2018-02-01</t>
   </si>
   <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2020-01-18</t>
+  </si>
+  <si>
+    <t>2022-10-11</t>
+  </si>
+  <si>
+    <t>2016-12-13</t>
+  </si>
+  <si>
     <t>2017-05-20</t>
   </si>
   <si>
@@ -1853,25 +2255,34 @@
     <t>1</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>1.1</t>
-  </si>
-  <si>
     <t>IRCC.Open-Ouvert.IRCC@cic.gc.ca</t>
   </si>
   <si>
+    <t>admin@cpata-cabamc.ca</t>
+  </si>
+  <si>
     <t>im-it-gi-ti@feddevontario.gc.ca</t>
   </si>
   <si>
+    <t>info@oto-boc.gc.ca</t>
+  </si>
+  <si>
     <t>open-ouvert@tbs-sct.gc.ca</t>
   </si>
   <si>
     <t>Johanne.gamache@pmprb-cepmb.gc.ca</t>
+  </si>
+  <si>
+    <t>generalinquiries-renseignementsgeneraux@nsicop-cpsnr.gc.ca</t>
   </si>
   <si>
     <t>tina.sparrow@swc-cfc.gc.ca</t>
@@ -2731,292 +3142,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>620</v>
+        <v>757</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>621</v>
+        <v>758</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>622</v>
+        <v>759</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>623</v>
+        <v>760</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>624</v>
+        <v>761</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>625</v>
+        <v>762</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>626</v>
+        <v>763</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>627</v>
+        <v>764</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>628</v>
+        <v>765</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>629</v>
+        <v>766</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>630</v>
+        <v>767</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>631</v>
+        <v>768</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>632</v>
+        <v>769</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>633</v>
+        <v>770</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>634</v>
+        <v>771</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>635</v>
+        <v>772</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>636</v>
+        <v>773</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>637</v>
+        <v>774</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>638</v>
+        <v>775</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>639</v>
+        <v>776</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>640</v>
+        <v>777</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>641</v>
+        <v>778</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>642</v>
+        <v>779</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>643</v>
+        <v>780</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>644</v>
+        <v>781</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>645</v>
+        <v>782</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>646</v>
+        <v>783</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>647</v>
+        <v>784</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>648</v>
+        <v>785</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>649</v>
+        <v>786</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>650</v>
+        <v>787</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>651</v>
+        <v>788</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>652</v>
+        <v>789</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>653</v>
+        <v>790</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>654</v>
+        <v>791</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>655</v>
+        <v>792</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>656</v>
+        <v>793</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>657</v>
+        <v>794</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>658</v>
+        <v>795</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>659</v>
+        <v>796</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>660</v>
+        <v>797</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>661</v>
+        <v>798</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>662</v>
+        <v>799</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>663</v>
+        <v>800</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>664</v>
+        <v>801</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>665</v>
+        <v>802</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>666</v>
+        <v>803</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>667</v>
+        <v>804</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>668</v>
+        <v>805</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>669</v>
+        <v>806</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>670</v>
+        <v>807</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>671</v>
+        <v>808</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>672</v>
+        <v>809</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>673</v>
+        <v>810</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>674</v>
+        <v>811</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>675</v>
+        <v>812</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>676</v>
+        <v>813</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>677</v>
+        <v>814</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>678</v>
+        <v>815</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>679</v>
+        <v>816</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>680</v>
+        <v>817</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>681</v>
+        <v>818</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>682</v>
+        <v>819</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>683</v>
+        <v>820</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>684</v>
+        <v>821</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>685</v>
+        <v>822</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>686</v>
+        <v>823</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>687</v>
+        <v>824</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>688</v>
+        <v>825</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>689</v>
+        <v>826</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>690</v>
+        <v>827</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>691</v>
+        <v>828</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>692</v>
+        <v>829</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>693</v>
+        <v>830</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>694</v>
+        <v>831</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>695</v>
+        <v>832</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>696</v>
+        <v>833</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>697</v>
+        <v>834</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>698</v>
+        <v>835</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>699</v>
+        <v>836</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>700</v>
+        <v>837</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>701</v>
+        <v>838</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>702</v>
+        <v>839</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>703</v>
+        <v>840</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -5201,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2">
         <v>12</v>
@@ -5465,7 +5876,7 @@
         <v>3</v>
       </c>
       <c r="CV9" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="CW9" s="1">
         <v>94</v>
@@ -6810,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO14" s="2">
         <v>2</v>
@@ -6990,7 +7401,7 @@
         <v>15</v>
       </c>
       <c r="CV14" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="CW14" s="1">
         <v>278</v>
@@ -8550,16 +8961,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="K20" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M20" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N20" s="1">
         <v>12653</v>
@@ -8568,7 +8979,7 @@
         <v>3</v>
       </c>
       <c r="P20" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="Q20" s="2">
         <v>607</v>
@@ -8814,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20686</v>
+        <v>20685</v>
       </c>
       <c r="CU20" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CV20" s="1">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="CW20" s="1">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9459,7 +9870,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
@@ -9735,7 +10146,7 @@
         <v>3</v>
       </c>
       <c r="CV23" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CW23" s="1">
         <v>45</v>
@@ -12228,7 +12639,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="2">
         <v>319</v>
@@ -12480,7 +12891,7 @@
         <v>27</v>
       </c>
       <c r="CV32" s="1">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="CW32" s="1">
         <v>545</v>
@@ -13421,7 +13832,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
         <v>3</v>
@@ -13697,7 +14108,7 @@
         <v>38</v>
       </c>
       <c r="CU36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV36" s="1">
         <v>3</v>
@@ -14178,7 +14589,7 @@
         <v>0</v>
       </c>
       <c r="BD38" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE38" s="2">
         <v>22</v>
@@ -14310,7 +14721,7 @@
         <v>15</v>
       </c>
       <c r="CV38" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="CW38" s="1">
         <v>126</v>
@@ -15873,7 +16284,7 @@
         <v>1347</v>
       </c>
       <c r="K44" s="2">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="L44" s="2">
         <v>54</v>
@@ -16137,7 +16548,7 @@
         <v>50635</v>
       </c>
       <c r="CU44" s="1">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="CV44" s="1">
         <v>1952</v>
@@ -18095,7 +18506,7 @@
         <v>0</v>
       </c>
       <c r="AN51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO51" s="2">
         <v>1</v>
@@ -18236,7 +18647,7 @@
         <v>1056</v>
       </c>
       <c r="CI51" s="2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CJ51" s="2">
         <v>65</v>
@@ -18272,10 +18683,10 @@
         <v>1794</v>
       </c>
       <c r="CU51" s="1">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="CV51" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CW51" s="1">
         <v>209</v>
@@ -19829,10 +20240,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -20105,10 +20516,10 @@
         <v>0</v>
       </c>
       <c r="CV57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW57" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:101">
@@ -20128,16 +20539,16 @@
         <v>0</v>
       </c>
       <c r="F58" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58" s="1">
         <v>0</v>
@@ -20236,16 +20647,16 @@
         <v>9</v>
       </c>
       <c r="AP58" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS58" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT58" s="1">
         <v>0</v>
@@ -20380,16 +20791,16 @@
         <v>12</v>
       </c>
       <c r="CL58" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CM58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP58" s="1">
         <v>0</v>
@@ -20404,16 +20815,16 @@
         <v>0</v>
       </c>
       <c r="CT58" s="1">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="CU58" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV58" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CW58" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:101">
@@ -21037,7 +21448,7 @@
         <v>194</v>
       </c>
       <c r="D61" s="2">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E61" s="2">
         <v>305</v>
@@ -21325,7 +21736,7 @@
         <v>223</v>
       </c>
       <c r="CV61" s="1">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="CW61" s="1">
         <v>996</v>
@@ -21794,7 +22205,7 @@
         <v>1</v>
       </c>
       <c r="BA63" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB63" s="1">
         <v>4</v>
@@ -21938,7 +22349,7 @@
         <v>85</v>
       </c>
       <c r="CW63" s="1">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22030,16 +22441,16 @@
         <v>5</v>
       </c>
       <c r="AD64" s="1">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="AE64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF64" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AG64" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22234,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>7940</v>
+        <v>7941</v>
       </c>
       <c r="CU64" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV64" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="CW64" s="1">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22257,7 +22668,7 @@
         <v>15</v>
       </c>
       <c r="D65" s="2">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E65" s="2">
         <v>106</v>
@@ -22545,7 +22956,7 @@
         <v>35</v>
       </c>
       <c r="CV65" s="1">
-        <v>1779</v>
+        <v>1769</v>
       </c>
       <c r="CW65" s="1">
         <v>3560</v>
@@ -23788,16 +24199,16 @@
         <v>1</v>
       </c>
       <c r="F70" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
       </c>
       <c r="H70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J70" s="1">
         <v>281</v>
@@ -23806,7 +24217,7 @@
         <v>13</v>
       </c>
       <c r="L70" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M70" s="2">
         <v>26</v>
@@ -23818,7 +24229,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Q70" s="2">
         <v>30</v>
@@ -24064,16 +24475,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="CU70" s="1">
         <v>16</v>
       </c>
       <c r="CV70" s="1">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="CW70" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25110,7 +25521,7 @@
         <v>52</v>
       </c>
       <c r="AN74" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AO74" s="2">
         <v>403</v>
@@ -25251,7 +25662,7 @@
         <v>16168</v>
       </c>
       <c r="CI74" s="2">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="CJ74" s="2">
         <v>194</v>
@@ -25287,10 +25698,10 @@
         <v>171615</v>
       </c>
       <c r="CU74" s="1">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="CV74" s="1">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="CW74" s="1">
         <v>4397</v>
@@ -25648,10 +26059,10 @@
         <v>10</v>
       </c>
       <c r="P76" s="2">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="Q76" s="2">
-        <v>2426</v>
+        <v>2415</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -25900,10 +26311,10 @@
         <v>125</v>
       </c>
       <c r="CV76" s="1">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="CW76" s="1">
-        <v>3759</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -25941,7 +26352,7 @@
         <v>45</v>
       </c>
       <c r="L77" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M77" s="2">
         <v>343</v>
@@ -26025,7 +26436,7 @@
         <v>13</v>
       </c>
       <c r="AN77" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AO77" s="2">
         <v>75</v>
@@ -26169,7 +26580,7 @@
         <v>110</v>
       </c>
       <c r="CJ77" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="CK77" s="2">
         <v>605</v>
@@ -26205,7 +26616,7 @@
         <v>196</v>
       </c>
       <c r="CV77" s="1">
-        <v>10233</v>
+        <v>10226</v>
       </c>
       <c r="CW77" s="1">
         <v>16081</v>
@@ -27780,7 +28191,7 @@
         <v>40131</v>
       </c>
       <c r="O83" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P83" s="2">
         <v>269</v>
@@ -28032,7 +28443,7 @@
         <v>423791</v>
       </c>
       <c r="CU83" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="CV83" s="1">
         <v>887</v>
@@ -31099,7 +31510,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94" s="2">
         <v>2</v>
@@ -31387,7 +31798,7 @@
         <v>61</v>
       </c>
       <c r="CU94" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV94" s="1">
         <v>4</v>
@@ -32639,7 +33050,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I99" s="2">
         <v>6</v>
@@ -32915,7 +33326,7 @@
         <v>1</v>
       </c>
       <c r="CV99" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW99" s="1">
         <v>6</v>
@@ -35707,16 +36118,16 @@
         <v>0</v>
       </c>
       <c r="N109" s="1">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="O109" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P109" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q109" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R109" s="1">
         <v>0</v>
@@ -35779,16 +36190,16 @@
         <v>0</v>
       </c>
       <c r="AL109" s="1">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AM109" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN109" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO109" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AP109" s="1">
         <v>0</v>
@@ -35923,16 +36334,16 @@
         <v>0</v>
       </c>
       <c r="CH109" s="1">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="CI109" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CJ109" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CK109" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="CL109" s="1">
         <v>3</v>
@@ -35959,16 +36370,16 @@
         <v>0</v>
       </c>
       <c r="CT109" s="1">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="CU109" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CV109" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CW109" s="1">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:101">
@@ -37143,16 +37554,16 @@
         <v>0</v>
       </c>
       <c r="CH113" s="1">
-        <v>1474</v>
+        <v>1486</v>
       </c>
       <c r="CI113" s="2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="CJ113" s="2">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="CK113" s="2">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37179,16 +37590,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173801</v>
+        <v>173813</v>
       </c>
       <c r="CU113" s="1">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="CV113" s="1">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="CW113" s="1">
-        <v>9924</v>
+        <v>9936</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -39349,7 +39760,7 @@
         <v>1</v>
       </c>
       <c r="H121" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I121" s="2">
         <v>5</v>
@@ -39625,7 +40036,7 @@
         <v>1</v>
       </c>
       <c r="CV121" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW121" s="1">
         <v>6</v>
@@ -40264,7 +40675,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I124" s="2">
         <v>5</v>
@@ -40540,7 +40951,7 @@
         <v>0</v>
       </c>
       <c r="CV124" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW124" s="1">
         <v>5</v>
@@ -45557,7 +45968,7 @@
         <v>0</v>
       </c>
       <c r="AR141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS141" s="2">
         <v>4</v>
@@ -45701,7 +46112,7 @@
         <v>1</v>
       </c>
       <c r="CN141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO141" s="2">
         <v>4</v>
@@ -45725,7 +46136,7 @@
         <v>3</v>
       </c>
       <c r="CV141" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CW141" s="1">
         <v>41</v>
@@ -45862,7 +46273,7 @@
         <v>0</v>
       </c>
       <c r="AR142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS142" s="2">
         <v>4</v>
@@ -45877,7 +46288,7 @@
         <v>2</v>
       </c>
       <c r="AW142" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX142" s="1">
         <v>4</v>
@@ -46006,7 +46417,7 @@
         <v>0</v>
       </c>
       <c r="CN142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO142" s="2">
         <v>3</v>
@@ -46030,10 +46441,10 @@
         <v>5</v>
       </c>
       <c r="CV142" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="CW142" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -46795,16 +47206,16 @@
         <v>0</v>
       </c>
       <c r="AX145" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AY145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ145" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA145" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB145" s="1">
         <v>0</v>
@@ -46939,16 +47350,16 @@
         <v>0</v>
       </c>
       <c r="CT145" s="1">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="CU145" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CV145" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CW145" s="1">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -47997,7 +48408,7 @@
         <v>2</v>
       </c>
       <c r="AR149" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS149" s="2">
         <v>6</v>
@@ -48129,7 +48540,7 @@
         <v>3</v>
       </c>
       <c r="CJ149" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CK149" s="2">
         <v>12</v>
@@ -48165,7 +48576,7 @@
         <v>5</v>
       </c>
       <c r="CV149" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CW149" s="1">
         <v>64</v>
@@ -48487,7 +48898,7 @@
         <v>0</v>
       </c>
       <c r="D151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="2">
         <v>1</v>
@@ -48499,7 +48910,7 @@
         <v>0</v>
       </c>
       <c r="H151" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I151" s="2">
         <v>7</v>
@@ -48775,7 +49186,7 @@
         <v>2</v>
       </c>
       <c r="CV151" s="1">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="CW151" s="1">
         <v>42</v>
@@ -49707,7 +50118,7 @@
         <v>0</v>
       </c>
       <c r="D155" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E155" s="2">
         <v>2</v>
@@ -49995,7 +50406,7 @@
         <v>10</v>
       </c>
       <c r="CV155" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="CW155" s="1">
         <v>92</v>
@@ -50338,7 +50749,7 @@
         <v>3472</v>
       </c>
       <c r="K157" s="2">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="L157" s="2">
         <v>165</v>
@@ -50602,7 +51013,7 @@
         <v>166337</v>
       </c>
       <c r="CU157" s="1">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="CV157" s="1">
         <v>5277</v>
@@ -52769,7 +53180,7 @@
         <v>1</v>
       </c>
       <c r="H165" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I165" s="2">
         <v>7</v>
@@ -53045,7 +53456,7 @@
         <v>1</v>
       </c>
       <c r="CV165" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW165" s="1">
         <v>7</v>
@@ -56109,7 +56520,7 @@
         <v>115</v>
       </c>
       <c r="C176" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D176" s="2">
         <v>2</v>
@@ -56397,7 +56808,7 @@
         <v>1314</v>
       </c>
       <c r="CU176" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CV176" s="1">
         <v>105</v>
@@ -57039,7 +57450,7 @@
         <v>1</v>
       </c>
       <c r="H179" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I179" s="2">
         <v>5</v>
@@ -57315,7 +57726,7 @@
         <v>1</v>
       </c>
       <c r="CV179" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="CW179" s="1">
         <v>68</v>
@@ -57643,16 +58054,16 @@
         <v>0</v>
       </c>
       <c r="F181" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G181" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I181" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J181" s="1">
         <v>0</v>
@@ -57919,16 +58330,16 @@
         <v>0</v>
       </c>
       <c r="CT181" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CU181" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV181" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW181" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -60394,7 +60805,7 @@
         <v>1</v>
       </c>
       <c r="H190" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I190" s="2">
         <v>6</v>
@@ -60670,7 +61081,7 @@
         <v>1</v>
       </c>
       <c r="CV190" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW190" s="1">
         <v>6</v>
@@ -61907,7 +62318,7 @@
         <v>2</v>
       </c>
       <c r="D195" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E195" s="2">
         <v>10</v>
@@ -62195,7 +62606,7 @@
         <v>6</v>
       </c>
       <c r="CV195" s="1">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="CW195" s="1">
         <v>5325</v>
@@ -63570,16 +63981,16 @@
         <v>5</v>
       </c>
       <c r="AX200" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ200" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA200" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB200" s="1">
         <v>6</v>
@@ -63714,16 +64125,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16289</v>
+        <v>16290</v>
       </c>
       <c r="CU200" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="CV200" s="1">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW200" s="1">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -65262,7 +65673,7 @@
         <v>4</v>
       </c>
       <c r="D206" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E206" s="2">
         <v>-24</v>
@@ -65550,7 +65961,7 @@
         <v>14</v>
       </c>
       <c r="CV206" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CW206" s="1">
         <v>23</v>
@@ -66602,7 +67013,7 @@
         <v>2</v>
       </c>
       <c r="AR210" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS210" s="2">
         <v>5</v>
@@ -66734,7 +67145,7 @@
         <v>6</v>
       </c>
       <c r="CJ210" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CK210" s="2">
         <v>15</v>
@@ -66746,7 +67157,7 @@
         <v>0</v>
       </c>
       <c r="CN210" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO210" s="2">
         <v>-1</v>
@@ -66770,7 +67181,7 @@
         <v>8</v>
       </c>
       <c r="CV210" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CW210" s="1">
         <v>39</v>
@@ -67714,7 +68125,7 @@
         <v>1</v>
       </c>
       <c r="H214" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I214" s="2">
         <v>5</v>
@@ -67990,7 +68401,7 @@
         <v>1</v>
       </c>
       <c r="CV214" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CW214" s="1">
         <v>6</v>
@@ -68003,7 +68414,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="30" customHeight="1">
@@ -68037,16 +68448,16 @@
         <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>588</v>
+        <v>714</v>
       </c>
       <c r="F2" t="s">
-        <v>610</v>
+        <v>744</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -68057,16 +68468,16 @@
         <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>464</v>
+        <v>534</v>
       </c>
       <c r="D3">
         <v>398</v>
       </c>
       <c r="E3" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F3" t="s">
-        <v>611</v>
+        <v>745</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -68077,2834 +68488,4246 @@
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>465</v>
+        <v>535</v>
       </c>
       <c r="D4">
         <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F4" t="s">
-        <v>611</v>
+        <v>745</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
         <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>466</v>
+        <v>536</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F5" t="s">
-        <v>612</v>
-      </c>
-      <c r="G5" t="s">
-        <v>466</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
         <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>467</v>
+        <v>537</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F6" t="s">
-        <v>612</v>
+        <v>747</v>
+      </c>
+      <c r="G6" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
         <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>468</v>
+        <v>538</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F7" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>469</v>
+        <v>539</v>
       </c>
       <c r="D8">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F8" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
         <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>470</v>
+        <v>540</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F9" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>590</v>
+        <v>715</v>
       </c>
       <c r="F10" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>472</v>
+        <v>542</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>589</v>
+        <v>716</v>
       </c>
       <c r="F11" t="s">
-        <v>612</v>
+        <v>748</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
         <v>330</v>
       </c>
       <c r="C12" t="s">
-        <v>473</v>
+        <v>543</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F12" t="s">
-        <v>614</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
+      <c r="C13" t="s">
+        <v>544</v>
+      </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>589</v>
+        <v>717</v>
       </c>
       <c r="F13" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>474</v>
+        <v>545</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>591</v>
+        <v>715</v>
       </c>
       <c r="F14" t="s">
-        <v>610</v>
+        <v>746</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
-      <c r="C15" t="s">
-        <v>475</v>
-      </c>
       <c r="D15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F15" t="s">
-        <v>612</v>
+        <v>748</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>546</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>589</v>
+        <v>718</v>
       </c>
       <c r="F16" t="s">
-        <v>613</v>
+        <v>744</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>477</v>
+        <v>547</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F17" t="s">
-        <v>610</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
       <c r="C18" t="s">
-        <v>478</v>
+        <v>548</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F18" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
         <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>479</v>
+        <v>549</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F19" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>469</v>
+        <v>550</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F20" t="s">
-        <v>613</v>
+        <v>744</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B21" t="s">
         <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>480</v>
+        <v>551</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F21" t="s">
-        <v>612</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>481</v>
+        <v>552</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F22" t="s">
-        <v>612</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
         <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>482</v>
+        <v>553</v>
       </c>
       <c r="D23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F23" t="s">
-        <v>613</v>
+        <v>744</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
         <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>483</v>
+        <v>540</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="F24" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
         <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>484</v>
+        <v>554</v>
       </c>
       <c r="D25">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F25" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>485</v>
+        <v>533</v>
       </c>
       <c r="D26">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F26" t="s">
-        <v>610</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>486</v>
+        <v>555</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>593</v>
+        <v>715</v>
       </c>
       <c r="F27" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
         <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F28" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>594</v>
+        <v>719</v>
       </c>
       <c r="F29" t="s">
-        <v>612</v>
+        <v>748</v>
+      </c>
+      <c r="G29" t="s">
+        <v>533</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
         <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>488</v>
+        <v>557</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>595</v>
+        <v>720</v>
       </c>
       <c r="F30" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
         <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>483</v>
+        <v>558</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="F31" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
         <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>489</v>
+        <v>559</v>
       </c>
       <c r="D32">
-        <v>30</v>
+        <v>267</v>
       </c>
       <c r="E32" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F32" t="s">
-        <v>614</v>
+        <v>744</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B33" t="s">
         <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>490</v>
+        <v>560</v>
       </c>
       <c r="D33">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>589</v>
+        <v>721</v>
       </c>
       <c r="F33" t="s">
-        <v>611</v>
-      </c>
-      <c r="G33" t="s">
-        <v>615</v>
+        <v>748</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B34" t="s">
         <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>491</v>
+        <v>561</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>596</v>
+        <v>715</v>
       </c>
       <c r="F34" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s">
         <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>594</v>
+        <v>722</v>
       </c>
       <c r="F35" t="s">
-        <v>612</v>
+        <v>747</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
         <v>354</v>
       </c>
       <c r="C36" t="s">
-        <v>492</v>
+        <v>562</v>
       </c>
       <c r="D36">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>589</v>
+        <v>723</v>
       </c>
       <c r="F36" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s">
         <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>588</v>
+        <v>720</v>
       </c>
       <c r="F37" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s">
         <v>356</v>
       </c>
       <c r="C38" t="s">
-        <v>469</v>
+        <v>563</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F38" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
       </c>
       <c r="C39" t="s">
-        <v>493</v>
+        <v>564</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>592</v>
+        <v>724</v>
       </c>
       <c r="F39" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
         <v>358</v>
       </c>
       <c r="C40" t="s">
-        <v>494</v>
+        <v>565</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F40" t="s">
-        <v>612</v>
+        <v>745</v>
+      </c>
+      <c r="G40" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
         <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>495</v>
+        <v>566</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>589</v>
+        <v>725</v>
       </c>
       <c r="F41" t="s">
-        <v>612</v>
+        <v>748</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
         <v>360</v>
       </c>
       <c r="C42" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>589</v>
+        <v>722</v>
       </c>
       <c r="F42" t="s">
-        <v>612</v>
+        <v>747</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B43" t="s">
         <v>361</v>
       </c>
-      <c r="C43" t="s">
-        <v>497</v>
-      </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F43" t="s">
-        <v>612</v>
+        <v>748</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B44" t="s">
         <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>498</v>
+        <v>567</v>
       </c>
       <c r="D44">
-        <v>332</v>
+        <v>33</v>
       </c>
       <c r="E44" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F44" t="s">
-        <v>610</v>
+        <v>744</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s">
         <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>597</v>
+        <v>714</v>
       </c>
       <c r="F45" t="s">
-        <v>613</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
         <v>364</v>
       </c>
       <c r="C46" t="s">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="D46">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F46" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="B47" t="s">
         <v>365</v>
       </c>
       <c r="C47" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="D47">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F47" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B48" t="s">
         <v>366</v>
       </c>
       <c r="C48" t="s">
-        <v>502</v>
+        <v>568</v>
       </c>
       <c r="D48">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>589</v>
+        <v>720</v>
       </c>
       <c r="F48" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="B49" t="s">
         <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>503</v>
+        <v>568</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F49" t="s">
-        <v>610</v>
+        <v>747</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
         <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D50">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F50" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
         <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E51" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F51" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
         <v>370</v>
       </c>
       <c r="C52" t="s">
-        <v>506</v>
+        <v>571</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>598</v>
+        <v>715</v>
       </c>
       <c r="F52" t="s">
-        <v>611</v>
+        <v>747</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
         <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>507</v>
+        <v>572</v>
       </c>
       <c r="D53">
-        <v>2205</v>
+        <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F53" t="s">
-        <v>611</v>
+        <v>747</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="B54" t="s">
         <v>372</v>
       </c>
       <c r="C54" t="s">
-        <v>508</v>
+        <v>573</v>
       </c>
       <c r="D54">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F54" t="s">
-        <v>611</v>
+        <v>747</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s">
         <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>509</v>
+        <v>574</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>599</v>
+        <v>715</v>
       </c>
       <c r="F55" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B56" t="s">
         <v>374</v>
       </c>
       <c r="C56" t="s">
-        <v>510</v>
+        <v>575</v>
       </c>
       <c r="D56">
-        <v>13</v>
+        <v>193</v>
       </c>
       <c r="E56" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F56" t="s">
-        <v>612</v>
+        <v>744</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="B57" t="s">
         <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>474</v>
+        <v>576</v>
       </c>
       <c r="D57">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F57" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="B58" t="s">
         <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>511</v>
+        <v>577</v>
       </c>
       <c r="D58">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>589</v>
+        <v>717</v>
       </c>
       <c r="F58" t="s">
-        <v>612</v>
+        <v>748</v>
+      </c>
+      <c r="G58" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
         <v>377</v>
       </c>
       <c r="C59" t="s">
-        <v>512</v>
+        <v>578</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E59" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F59" t="s">
-        <v>612</v>
+        <v>746</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="B60" t="s">
         <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>513</v>
+        <v>579</v>
       </c>
       <c r="D60">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F60" t="s">
-        <v>614</v>
-      </c>
-      <c r="G60" t="s">
-        <v>616</v>
+        <v>747</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="B61" t="s">
         <v>379</v>
       </c>
       <c r="C61" t="s">
-        <v>514</v>
+        <v>580</v>
       </c>
       <c r="D61">
-        <v>28</v>
+        <v>332</v>
       </c>
       <c r="E61" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F61" t="s">
-        <v>613</v>
+        <v>744</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="B62" t="s">
         <v>380</v>
       </c>
+      <c r="C62" t="s">
+        <v>581</v>
+      </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>589</v>
+        <v>724</v>
       </c>
       <c r="F62" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="B63" t="s">
         <v>381</v>
       </c>
       <c r="C63" t="s">
-        <v>515</v>
+        <v>582</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="E63" t="s">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="F63" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="B64" t="s">
         <v>382</v>
       </c>
       <c r="C64" t="s">
-        <v>516</v>
+        <v>583</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F64" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="B65" t="s">
         <v>383</v>
       </c>
       <c r="C65" t="s">
-        <v>517</v>
+        <v>584</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="E65" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F65" t="s">
-        <v>614</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B66" t="s">
         <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>518</v>
+        <v>585</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="E66" t="s">
-        <v>590</v>
+        <v>715</v>
       </c>
       <c r="F66" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="B67" t="s">
         <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>519</v>
+        <v>586</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="F67" t="s">
-        <v>613</v>
-      </c>
-      <c r="G67" t="s">
-        <v>519</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="B68" t="s">
         <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>520</v>
+        <v>587</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="F68" t="s">
-        <v>613</v>
+        <v>744</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B69" t="s">
         <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>521</v>
+        <v>588</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>600</v>
+        <v>715</v>
       </c>
       <c r="F69" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="B70" t="s">
         <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>522</v>
+        <v>589</v>
       </c>
       <c r="D70">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F70" t="s">
-        <v>614</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="B71" t="s">
         <v>389</v>
       </c>
       <c r="C71" t="s">
-        <v>523</v>
+        <v>590</v>
       </c>
       <c r="D71">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F71" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="B72" t="s">
         <v>390</v>
       </c>
       <c r="C72" t="s">
-        <v>524</v>
+        <v>591</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
-        <v>589</v>
+        <v>726</v>
       </c>
       <c r="F72" t="s">
-        <v>613</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B73" t="s">
         <v>391</v>
       </c>
       <c r="C73" t="s">
-        <v>525</v>
+        <v>592</v>
       </c>
       <c r="D73">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
-        <v>601</v>
+        <v>715</v>
       </c>
       <c r="F73" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="B74" t="s">
         <v>392</v>
       </c>
       <c r="C74" t="s">
-        <v>526</v>
+        <v>593</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>2205</v>
       </c>
       <c r="E74" t="s">
-        <v>602</v>
+        <v>715</v>
       </c>
       <c r="F74" t="s">
-        <v>613</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="B75" t="s">
         <v>393</v>
       </c>
       <c r="C75" t="s">
-        <v>527</v>
+        <v>594</v>
       </c>
       <c r="D75">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E75" t="s">
-        <v>589</v>
+        <v>727</v>
       </c>
       <c r="F75" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B76" t="s">
         <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>528</v>
+        <v>595</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>915</v>
       </c>
       <c r="E76" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F76" t="s">
-        <v>614</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="B77" t="s">
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>465</v>
+        <v>596</v>
       </c>
       <c r="D77">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="E77" t="s">
-        <v>603</v>
+        <v>715</v>
       </c>
       <c r="F77" t="s">
-        <v>611</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
       <c r="B78" t="s">
         <v>396</v>
       </c>
       <c r="C78" t="s">
-        <v>529</v>
+        <v>597</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>589</v>
+        <v>728</v>
       </c>
       <c r="F78" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="B79" t="s">
         <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>530</v>
+        <v>598</v>
       </c>
       <c r="D79">
-        <v>527</v>
+        <v>1197</v>
       </c>
       <c r="E79" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F79" t="s">
-        <v>611</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
         <v>398</v>
       </c>
       <c r="C80" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F80" t="s">
-        <v>612</v>
+        <v>747</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="B81" t="s">
         <v>399</v>
       </c>
       <c r="C81" t="s">
-        <v>532</v>
+        <v>599</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="E81" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F81" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="B82" t="s">
         <v>400</v>
       </c>
       <c r="C82" t="s">
-        <v>533</v>
+        <v>600</v>
       </c>
       <c r="D82">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F82" t="s">
-        <v>612</v>
+        <v>748</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="B83" t="s">
         <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="E83" t="s">
-        <v>590</v>
+        <v>715</v>
       </c>
       <c r="F83" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="B84" t="s">
         <v>402</v>
       </c>
       <c r="C84" t="s">
-        <v>534</v>
+        <v>601</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>589</v>
+        <v>720</v>
       </c>
       <c r="F84" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="B85" t="s">
         <v>403</v>
       </c>
       <c r="C85" t="s">
-        <v>535</v>
+        <v>602</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>590</v>
+        <v>715</v>
       </c>
       <c r="F85" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="B86" t="s">
         <v>404</v>
       </c>
       <c r="C86" t="s">
-        <v>536</v>
+        <v>603</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F86" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="B87" t="s">
         <v>405</v>
       </c>
       <c r="C87" t="s">
-        <v>537</v>
+        <v>604</v>
       </c>
       <c r="D87">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F87" t="s">
-        <v>612</v>
-      </c>
-      <c r="G87" t="s">
-        <v>537</v>
+        <v>747</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="B88" t="s">
         <v>406</v>
       </c>
       <c r="C88" t="s">
-        <v>538</v>
+        <v>605</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F88" t="s">
-        <v>613</v>
+        <v>746</v>
+      </c>
+      <c r="G88" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="B89" t="s">
         <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>539</v>
+        <v>606</v>
       </c>
       <c r="D89">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>589</v>
+        <v>729</v>
       </c>
       <c r="F89" t="s">
-        <v>613</v>
+        <v>746</v>
+      </c>
+      <c r="G89" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="B90" t="s">
         <v>408</v>
       </c>
       <c r="C90" t="s">
-        <v>540</v>
+        <v>607</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F90" t="s">
-        <v>612</v>
+        <v>747</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
         <v>409</v>
       </c>
       <c r="C91" t="s">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E91" t="s">
-        <v>590</v>
+        <v>715</v>
       </c>
       <c r="F91" t="s">
-        <v>613</v>
+        <v>745</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="B92" t="s">
         <v>410</v>
       </c>
       <c r="C92" t="s">
-        <v>542</v>
+        <v>609</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E92" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F92" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="B93" t="s">
         <v>411</v>
       </c>
-      <c r="C93" t="s">
-        <v>543</v>
-      </c>
       <c r="D93">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F93" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="B94" t="s">
         <v>412</v>
       </c>
       <c r="C94" t="s">
-        <v>544</v>
+        <v>610</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>589</v>
+        <v>720</v>
       </c>
       <c r="F94" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="B95" t="s">
         <v>413</v>
       </c>
       <c r="C95" t="s">
-        <v>545</v>
+        <v>611</v>
       </c>
       <c r="D95">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F95" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="B96" t="s">
         <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>546</v>
+        <v>612</v>
       </c>
       <c r="D96">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F96" t="s">
-        <v>614</v>
+        <v>746</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="B97" t="s">
         <v>415</v>
       </c>
       <c r="C97" t="s">
-        <v>547</v>
+        <v>613</v>
       </c>
       <c r="D97">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>589</v>
+        <v>716</v>
       </c>
       <c r="F97" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="B98" t="s">
         <v>416</v>
       </c>
       <c r="C98" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="D98">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F98" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="B99" t="s">
         <v>417</v>
       </c>
       <c r="C99" t="s">
-        <v>493</v>
+        <v>615</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>592</v>
+        <v>716</v>
       </c>
       <c r="F99" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
         <v>418</v>
       </c>
+      <c r="C100" t="s">
+        <v>616</v>
+      </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>589</v>
+        <v>720</v>
       </c>
       <c r="F100" t="s">
-        <v>613</v>
+        <v>748</v>
+      </c>
+      <c r="G100" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="B101" t="s">
         <v>419</v>
       </c>
       <c r="C101" t="s">
-        <v>549</v>
+        <v>617</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>604</v>
+        <v>720</v>
       </c>
       <c r="F101" t="s">
-        <v>613</v>
-      </c>
-      <c r="G101" t="s">
-        <v>617</v>
+        <v>748</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="B102" t="s">
         <v>420</v>
       </c>
       <c r="C102" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>2978</v>
       </c>
       <c r="E102" t="s">
-        <v>605</v>
+        <v>715</v>
       </c>
       <c r="F102" t="s">
-        <v>614</v>
+        <v>745</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="B103" t="s">
         <v>421</v>
       </c>
       <c r="C103" t="s">
-        <v>551</v>
+        <v>619</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="F103" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="B104" t="s">
         <v>422</v>
       </c>
       <c r="C104" t="s">
-        <v>552</v>
+        <v>620</v>
       </c>
       <c r="D104">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>589</v>
+        <v>716</v>
       </c>
       <c r="F104" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="B105" t="s">
         <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>553</v>
+        <v>621</v>
       </c>
       <c r="D105">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E105" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F105" t="s">
-        <v>611</v>
+        <v>746</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="B106" t="s">
         <v>424</v>
       </c>
       <c r="C106" t="s">
-        <v>493</v>
+        <v>622</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="E106" t="s">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="F106" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="B107" t="s">
         <v>425</v>
       </c>
       <c r="C107" t="s">
-        <v>554</v>
+        <v>623</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>606</v>
+        <v>715</v>
       </c>
       <c r="F107" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="B108" t="s">
         <v>426</v>
       </c>
       <c r="C108" t="s">
-        <v>555</v>
+        <v>624</v>
       </c>
       <c r="D108">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
-        <v>589</v>
+        <v>731</v>
       </c>
       <c r="F108" t="s">
-        <v>614</v>
-      </c>
-      <c r="G108" t="s">
-        <v>618</v>
+        <v>744</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="B109" t="s">
         <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>556</v>
+        <v>625</v>
       </c>
       <c r="D109">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>589</v>
+        <v>732</v>
       </c>
       <c r="F109" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="B110" t="s">
         <v>428</v>
       </c>
       <c r="C110" t="s">
-        <v>557</v>
+        <v>626</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E110" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F110" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="B111" t="s">
         <v>429</v>
       </c>
       <c r="C111" t="s">
-        <v>558</v>
+        <v>627</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F111" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="B112" t="s">
         <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>559</v>
+        <v>628</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>607</v>
+        <v>715</v>
       </c>
       <c r="F112" t="s">
-        <v>613</v>
-      </c>
-      <c r="G112" t="s">
-        <v>559</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>270</v>
+        <v>212</v>
       </c>
       <c r="B113" t="s">
         <v>431</v>
       </c>
       <c r="C113" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="D113">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>589</v>
+        <v>733</v>
       </c>
       <c r="F113" t="s">
-        <v>614</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="B114" t="s">
         <v>432</v>
       </c>
       <c r="C114" t="s">
-        <v>561</v>
+        <v>629</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F114" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
       <c r="B115" t="s">
         <v>433</v>
       </c>
       <c r="C115" t="s">
-        <v>562</v>
+        <v>625</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>589</v>
+        <v>734</v>
       </c>
       <c r="F115" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="B116" t="s">
         <v>434</v>
       </c>
       <c r="C116" t="s">
-        <v>563</v>
+        <v>630</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="E116" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F116" t="s">
-        <v>614</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="B117" t="s">
         <v>435</v>
       </c>
       <c r="C117" t="s">
-        <v>564</v>
+        <v>631</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E117" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F117" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="B118" t="s">
         <v>436</v>
       </c>
       <c r="C118" t="s">
-        <v>565</v>
+        <v>632</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F118" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="B119" t="s">
         <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>566</v>
+        <v>633</v>
       </c>
       <c r="D119">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F119" t="s">
-        <v>611</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>278</v>
+        <v>219</v>
       </c>
       <c r="B120" t="s">
         <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>567</v>
+        <v>634</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E120" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F120" t="s">
-        <v>613</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="B121" t="s">
         <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>589</v>
+        <v>716</v>
       </c>
       <c r="F121" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="B122" t="s">
         <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>569</v>
+        <v>635</v>
       </c>
       <c r="D122">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F122" t="s">
-        <v>612</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="B123" t="s">
         <v>441</v>
       </c>
+      <c r="C123" t="s">
+        <v>636</v>
+      </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F123" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>283</v>
+        <v>223</v>
       </c>
       <c r="B124" t="s">
         <v>442</v>
       </c>
       <c r="C124" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>589</v>
+        <v>716</v>
       </c>
       <c r="F124" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="B125" t="s">
         <v>443</v>
       </c>
       <c r="C125" t="s">
-        <v>511</v>
+        <v>638</v>
       </c>
       <c r="D125">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F125" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="B126" t="s">
         <v>444</v>
       </c>
       <c r="C126" t="s">
-        <v>571</v>
+        <v>639</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F126" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>286</v>
+        <v>226</v>
       </c>
       <c r="B127" t="s">
         <v>445</v>
       </c>
       <c r="C127" t="s">
-        <v>572</v>
+        <v>640</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F127" t="s">
-        <v>613</v>
+        <v>747</v>
+      </c>
+      <c r="G127" t="s">
+        <v>640</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="B128" t="s">
         <v>446</v>
       </c>
       <c r="C128" t="s">
-        <v>573</v>
+        <v>641</v>
       </c>
       <c r="D128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F128" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="B129" t="s">
         <v>447</v>
       </c>
       <c r="C129" t="s">
-        <v>574</v>
+        <v>642</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F129" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>293</v>
+        <v>229</v>
       </c>
       <c r="B130" t="s">
         <v>448</v>
       </c>
       <c r="C130" t="s">
-        <v>575</v>
+        <v>643</v>
       </c>
       <c r="D130">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F130" t="s">
-        <v>614</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>294</v>
+        <v>230</v>
       </c>
       <c r="B131" t="s">
         <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>576</v>
+        <v>644</v>
       </c>
       <c r="D131">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>589</v>
+        <v>716</v>
       </c>
       <c r="F131" t="s">
-        <v>610</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="B132" t="s">
         <v>450</v>
       </c>
       <c r="C132" t="s">
-        <v>577</v>
+        <v>645</v>
       </c>
       <c r="D132">
-        <v>10255</v>
+        <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F132" t="s">
-        <v>614</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>296</v>
+        <v>232</v>
       </c>
       <c r="B133" t="s">
         <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>578</v>
+        <v>646</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="F133" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>297</v>
+        <v>233</v>
       </c>
       <c r="B134" t="s">
         <v>452</v>
       </c>
       <c r="C134" t="s">
-        <v>579</v>
+        <v>647</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E134" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F134" t="s">
-        <v>613</v>
-      </c>
-      <c r="G134" t="s">
-        <v>619</v>
+        <v>744</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="B135" t="s">
         <v>453</v>
       </c>
       <c r="C135" t="s">
-        <v>580</v>
+        <v>646</v>
       </c>
       <c r="D135">
-        <v>314</v>
+        <v>10260</v>
       </c>
       <c r="E135" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F135" t="s">
-        <v>613</v>
-      </c>
-      <c r="G135" t="s">
-        <v>617</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="B136" t="s">
         <v>454</v>
       </c>
       <c r="C136" t="s">
-        <v>463</v>
+        <v>648</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E136" t="s">
-        <v>608</v>
+        <v>715</v>
       </c>
       <c r="F136" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>303</v>
+        <v>236</v>
       </c>
       <c r="B137" t="s">
         <v>455</v>
       </c>
       <c r="C137" t="s">
-        <v>463</v>
+        <v>649</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>608</v>
+        <v>735</v>
       </c>
       <c r="F137" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
         <v>456</v>
       </c>
       <c r="C138" t="s">
-        <v>581</v>
+        <v>650</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="E138" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F138" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>305</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
         <v>457</v>
       </c>
       <c r="C139" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="D139">
-        <v>438</v>
+        <v>5</v>
       </c>
       <c r="E139" t="s">
-        <v>589</v>
+        <v>736</v>
       </c>
       <c r="F139" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>307</v>
+        <v>239</v>
       </c>
       <c r="B140" t="s">
         <v>458</v>
       </c>
       <c r="C140" t="s">
-        <v>583</v>
+        <v>651</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F140" t="s">
-        <v>613</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>308</v>
+        <v>240</v>
       </c>
       <c r="B141" t="s">
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>584</v>
+        <v>652</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E141" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F141" t="s">
-        <v>612</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="B142" t="s">
         <v>460</v>
       </c>
       <c r="C142" t="s">
-        <v>585</v>
+        <v>653</v>
       </c>
       <c r="D142">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E142" t="s">
-        <v>589</v>
+        <v>715</v>
       </c>
       <c r="F142" t="s">
-        <v>614</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>310</v>
+        <v>242</v>
       </c>
       <c r="B143" t="s">
         <v>461</v>
       </c>
       <c r="C143" t="s">
-        <v>586</v>
+        <v>654</v>
       </c>
       <c r="D143">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
-        <v>609</v>
+        <v>715</v>
       </c>
       <c r="F143" t="s">
-        <v>611</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>311</v>
+        <v>243</v>
       </c>
       <c r="B144" t="s">
         <v>462</v>
       </c>
       <c r="C144" t="s">
-        <v>587</v>
+        <v>655</v>
       </c>
       <c r="D144">
+        <v>4</v>
+      </c>
+      <c r="E144" t="s">
+        <v>715</v>
+      </c>
+      <c r="F144" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>244</v>
+      </c>
+      <c r="B145" t="s">
+        <v>463</v>
+      </c>
+      <c r="C145" t="s">
+        <v>656</v>
+      </c>
+      <c r="D145">
+        <v>49</v>
+      </c>
+      <c r="E145" t="s">
+        <v>715</v>
+      </c>
+      <c r="F145" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>245</v>
+      </c>
+      <c r="B146" t="s">
+        <v>464</v>
+      </c>
+      <c r="C146" t="s">
+        <v>568</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146" t="s">
+        <v>720</v>
+      </c>
+      <c r="F146" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>246</v>
+      </c>
+      <c r="B147" t="s">
+        <v>465</v>
+      </c>
+      <c r="C147" t="s">
+        <v>657</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>715</v>
+      </c>
+      <c r="F147" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>247</v>
+      </c>
+      <c r="B148" t="s">
+        <v>466</v>
+      </c>
+      <c r="C148" t="s">
+        <v>658</v>
+      </c>
+      <c r="D148">
+        <v>36</v>
+      </c>
+      <c r="E148" t="s">
+        <v>715</v>
+      </c>
+      <c r="F148" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>248</v>
+      </c>
+      <c r="B149" t="s">
+        <v>467</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149" t="s">
+        <v>715</v>
+      </c>
+      <c r="F149" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>249</v>
+      </c>
+      <c r="B150" t="s">
+        <v>468</v>
+      </c>
+      <c r="C150" t="s">
+        <v>659</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150" t="s">
+        <v>737</v>
+      </c>
+      <c r="F150" t="s">
+        <v>748</v>
+      </c>
+      <c r="G150" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>250</v>
+      </c>
+      <c r="B151" t="s">
+        <v>469</v>
+      </c>
+      <c r="C151" t="s">
+        <v>660</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151" t="s">
+        <v>738</v>
+      </c>
+      <c r="F151" t="s">
+        <v>748</v>
+      </c>
+      <c r="G151" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>251</v>
+      </c>
+      <c r="B152" t="s">
+        <v>470</v>
+      </c>
+      <c r="C152" t="s">
+        <v>661</v>
+      </c>
+      <c r="D152">
+        <v>5</v>
+      </c>
+      <c r="E152" t="s">
+        <v>739</v>
+      </c>
+      <c r="F152" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>252</v>
+      </c>
+      <c r="B153" t="s">
+        <v>471</v>
+      </c>
+      <c r="C153" t="s">
+        <v>662</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153" t="s">
+        <v>715</v>
+      </c>
+      <c r="F153" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>253</v>
+      </c>
+      <c r="B154" t="s">
+        <v>472</v>
+      </c>
+      <c r="C154" t="s">
+        <v>544</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154" t="s">
+        <v>715</v>
+      </c>
+      <c r="F154" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>254</v>
+      </c>
+      <c r="B155" t="s">
+        <v>473</v>
+      </c>
+      <c r="C155" t="s">
+        <v>663</v>
+      </c>
+      <c r="D155">
+        <v>19</v>
+      </c>
+      <c r="E155" t="s">
+        <v>715</v>
+      </c>
+      <c r="F155" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>255</v>
+      </c>
+      <c r="B156" t="s">
+        <v>474</v>
+      </c>
+      <c r="C156" t="s">
+        <v>664</v>
+      </c>
+      <c r="D156">
+        <v>597</v>
+      </c>
+      <c r="E156" t="s">
+        <v>715</v>
+      </c>
+      <c r="F156" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>256</v>
+      </c>
+      <c r="B157" t="s">
+        <v>475</v>
+      </c>
+      <c r="C157" t="s">
+        <v>665</v>
+      </c>
+      <c r="D157">
+        <v>135</v>
+      </c>
+      <c r="E157" t="s">
+        <v>715</v>
+      </c>
+      <c r="F157" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>257</v>
+      </c>
+      <c r="B158" t="s">
+        <v>476</v>
+      </c>
+      <c r="C158" t="s">
+        <v>666</v>
+      </c>
+      <c r="D158">
+        <v>5</v>
+      </c>
+      <c r="E158" t="s">
+        <v>715</v>
+      </c>
+      <c r="F158" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>258</v>
+      </c>
+      <c r="B159" t="s">
+        <v>477</v>
+      </c>
+      <c r="C159" t="s">
+        <v>568</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159" t="s">
+        <v>720</v>
+      </c>
+      <c r="F159" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>259</v>
+      </c>
+      <c r="B160" t="s">
+        <v>478</v>
+      </c>
+      <c r="C160" t="s">
+        <v>667</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160" t="s">
+        <v>715</v>
+      </c>
+      <c r="F160" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>260</v>
+      </c>
+      <c r="B161" t="s">
+        <v>479</v>
+      </c>
+      <c r="C161" t="s">
+        <v>668</v>
+      </c>
+      <c r="D161">
+        <v>761</v>
+      </c>
+      <c r="E161" t="s">
+        <v>715</v>
+      </c>
+      <c r="F161" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>261</v>
+      </c>
+      <c r="B162" t="s">
+        <v>480</v>
+      </c>
+      <c r="C162" t="s">
+        <v>666</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162" t="s">
+        <v>740</v>
+      </c>
+      <c r="F162" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>262</v>
+      </c>
+      <c r="B163" t="s">
+        <v>481</v>
+      </c>
+      <c r="C163" t="s">
+        <v>669</v>
+      </c>
+      <c r="D163">
+        <v>16</v>
+      </c>
+      <c r="E163" t="s">
+        <v>715</v>
+      </c>
+      <c r="F163" t="s">
+        <v>746</v>
+      </c>
+      <c r="G163" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>263</v>
+      </c>
+      <c r="B164" t="s">
+        <v>482</v>
+      </c>
+      <c r="C164" t="s">
+        <v>670</v>
+      </c>
+      <c r="D164">
+        <v>3</v>
+      </c>
+      <c r="E164" t="s">
+        <v>715</v>
+      </c>
+      <c r="F164" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>264</v>
+      </c>
+      <c r="B165" t="s">
+        <v>483</v>
+      </c>
+      <c r="C165" t="s">
+        <v>671</v>
+      </c>
+      <c r="D165">
+        <v>2</v>
+      </c>
+      <c r="E165" t="s">
+        <v>715</v>
+      </c>
+      <c r="F165" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>265</v>
+      </c>
+      <c r="B166" t="s">
+        <v>484</v>
+      </c>
+      <c r="C166" t="s">
+        <v>672</v>
+      </c>
+      <c r="D166">
+        <v>8</v>
+      </c>
+      <c r="E166" t="s">
+        <v>715</v>
+      </c>
+      <c r="F166" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>266</v>
+      </c>
+      <c r="B167" t="s">
+        <v>485</v>
+      </c>
+      <c r="C167" t="s">
+        <v>673</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167" t="s">
+        <v>715</v>
+      </c>
+      <c r="F167" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>267</v>
+      </c>
+      <c r="B168" t="s">
+        <v>486</v>
+      </c>
+      <c r="C168" t="s">
+        <v>674</v>
+      </c>
+      <c r="D168">
+        <v>11</v>
+      </c>
+      <c r="E168" t="s">
+        <v>739</v>
+      </c>
+      <c r="F168" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>268</v>
+      </c>
+      <c r="B169" t="s">
+        <v>487</v>
+      </c>
+      <c r="C169" t="s">
+        <v>675</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169" t="s">
+        <v>741</v>
+      </c>
+      <c r="F169" t="s">
+        <v>748</v>
+      </c>
+      <c r="G169" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>269</v>
+      </c>
+      <c r="B170" t="s">
+        <v>488</v>
+      </c>
+      <c r="C170" t="s">
+        <v>676</v>
+      </c>
+      <c r="D170">
+        <v>13</v>
+      </c>
+      <c r="E170" t="s">
+        <v>715</v>
+      </c>
+      <c r="F170" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>270</v>
+      </c>
+      <c r="B171" t="s">
+        <v>489</v>
+      </c>
+      <c r="C171" t="s">
+        <v>677</v>
+      </c>
+      <c r="D171">
+        <v>134</v>
+      </c>
+      <c r="E171" t="s">
+        <v>715</v>
+      </c>
+      <c r="F171" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>271</v>
+      </c>
+      <c r="B172" t="s">
+        <v>490</v>
+      </c>
+      <c r="C172" t="s">
+        <v>678</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172" t="s">
+        <v>715</v>
+      </c>
+      <c r="F172" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>272</v>
+      </c>
+      <c r="B173" t="s">
+        <v>491</v>
+      </c>
+      <c r="C173" t="s">
+        <v>679</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173" t="s">
+        <v>715</v>
+      </c>
+      <c r="F173" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>273</v>
+      </c>
+      <c r="B174" t="s">
+        <v>492</v>
+      </c>
+      <c r="C174" t="s">
+        <v>680</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174" t="s">
+        <v>715</v>
+      </c>
+      <c r="F174" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>274</v>
+      </c>
+      <c r="B175" t="s">
+        <v>493</v>
+      </c>
+      <c r="C175" t="s">
+        <v>681</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175" t="s">
+        <v>715</v>
+      </c>
+      <c r="F175" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>275</v>
+      </c>
+      <c r="B176" t="s">
+        <v>494</v>
+      </c>
+      <c r="C176" t="s">
+        <v>682</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176" t="s">
+        <v>715</v>
+      </c>
+      <c r="F176" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>276</v>
+      </c>
+      <c r="B177" t="s">
+        <v>495</v>
+      </c>
+      <c r="C177" t="s">
+        <v>683</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177" t="s">
+        <v>715</v>
+      </c>
+      <c r="F177" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>277</v>
+      </c>
+      <c r="B178" t="s">
+        <v>496</v>
+      </c>
+      <c r="C178" t="s">
+        <v>684</v>
+      </c>
+      <c r="D178">
+        <v>242</v>
+      </c>
+      <c r="E178" t="s">
+        <v>715</v>
+      </c>
+      <c r="F178" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>278</v>
+      </c>
+      <c r="B179" t="s">
+        <v>497</v>
+      </c>
+      <c r="C179" t="s">
+        <v>685</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179" t="s">
+        <v>715</v>
+      </c>
+      <c r="F179" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>279</v>
+      </c>
+      <c r="B180" t="s">
+        <v>498</v>
+      </c>
+      <c r="C180" t="s">
+        <v>686</v>
+      </c>
+      <c r="D180">
+        <v>97</v>
+      </c>
+      <c r="E180" t="s">
+        <v>715</v>
+      </c>
+      <c r="F180" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>280</v>
+      </c>
+      <c r="B181" t="s">
+        <v>499</v>
+      </c>
+      <c r="C181" t="s">
+        <v>687</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181" t="s">
+        <v>715</v>
+      </c>
+      <c r="F181" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>281</v>
+      </c>
+      <c r="B182" t="s">
+        <v>500</v>
+      </c>
+      <c r="C182" t="s">
+        <v>688</v>
+      </c>
+      <c r="D182">
+        <v>12</v>
+      </c>
+      <c r="E182" t="s">
+        <v>715</v>
+      </c>
+      <c r="F182" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>282</v>
+      </c>
+      <c r="B183" t="s">
+        <v>501</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183" t="s">
+        <v>715</v>
+      </c>
+      <c r="F183" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>283</v>
+      </c>
+      <c r="B184" t="s">
+        <v>502</v>
+      </c>
+      <c r="C184" t="s">
+        <v>689</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184" t="s">
+        <v>715</v>
+      </c>
+      <c r="F184" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>284</v>
+      </c>
+      <c r="B185" t="s">
+        <v>503</v>
+      </c>
+      <c r="C185" t="s">
+        <v>602</v>
+      </c>
+      <c r="D185">
+        <v>9</v>
+      </c>
+      <c r="E185" t="s">
+        <v>715</v>
+      </c>
+      <c r="F185" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>285</v>
+      </c>
+      <c r="B186" t="s">
+        <v>504</v>
+      </c>
+      <c r="C186" t="s">
+        <v>690</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186" t="s">
+        <v>715</v>
+      </c>
+      <c r="F186" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>286</v>
+      </c>
+      <c r="B187" t="s">
+        <v>505</v>
+      </c>
+      <c r="C187" t="s">
+        <v>691</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187" t="s">
+        <v>715</v>
+      </c>
+      <c r="F187" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>287</v>
+      </c>
+      <c r="B188" t="s">
+        <v>506</v>
+      </c>
+      <c r="C188" t="s">
+        <v>692</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="E188" t="s">
+        <v>715</v>
+      </c>
+      <c r="F188" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>288</v>
+      </c>
+      <c r="B189" t="s">
+        <v>507</v>
+      </c>
+      <c r="C189" t="s">
+        <v>693</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189" t="s">
+        <v>716</v>
+      </c>
+      <c r="F189" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>289</v>
+      </c>
+      <c r="B190" t="s">
+        <v>508</v>
+      </c>
+      <c r="C190" t="s">
+        <v>615</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190" t="s">
+        <v>716</v>
+      </c>
+      <c r="F190" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>290</v>
+      </c>
+      <c r="B191" t="s">
+        <v>509</v>
+      </c>
+      <c r="C191" t="s">
+        <v>694</v>
+      </c>
+      <c r="D191">
+        <v>7</v>
+      </c>
+      <c r="E191" t="s">
+        <v>720</v>
+      </c>
+      <c r="F191" t="s">
+        <v>746</v>
+      </c>
+      <c r="G191" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>291</v>
+      </c>
+      <c r="B192" t="s">
+        <v>510</v>
+      </c>
+      <c r="C192" t="s">
+        <v>613</v>
+      </c>
+      <c r="D192">
+        <v>3</v>
+      </c>
+      <c r="E192" t="s">
+        <v>715</v>
+      </c>
+      <c r="F192" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>292</v>
+      </c>
+      <c r="B193" t="s">
+        <v>511</v>
+      </c>
+      <c r="C193" t="s">
+        <v>695</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193" t="s">
+        <v>715</v>
+      </c>
+      <c r="F193" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>293</v>
+      </c>
+      <c r="B194" t="s">
+        <v>512</v>
+      </c>
+      <c r="C194" t="s">
+        <v>696</v>
+      </c>
+      <c r="D194">
+        <v>116</v>
+      </c>
+      <c r="E194" t="s">
+        <v>715</v>
+      </c>
+      <c r="F194" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>294</v>
+      </c>
+      <c r="B195" t="s">
+        <v>513</v>
+      </c>
+      <c r="C195" t="s">
+        <v>697</v>
+      </c>
+      <c r="D195">
+        <v>10</v>
+      </c>
+      <c r="E195" t="s">
+        <v>715</v>
+      </c>
+      <c r="F195" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>295</v>
+      </c>
+      <c r="B196" t="s">
+        <v>514</v>
+      </c>
+      <c r="C196" t="s">
+        <v>698</v>
+      </c>
+      <c r="D196">
+        <v>10255</v>
+      </c>
+      <c r="E196" t="s">
+        <v>715</v>
+      </c>
+      <c r="F196" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>296</v>
+      </c>
+      <c r="B197" t="s">
+        <v>515</v>
+      </c>
+      <c r="C197" t="s">
+        <v>699</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197" t="s">
+        <v>720</v>
+      </c>
+      <c r="F197" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>297</v>
+      </c>
+      <c r="B198" t="s">
+        <v>516</v>
+      </c>
+      <c r="C198" t="s">
+        <v>700</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198" t="s">
+        <v>715</v>
+      </c>
+      <c r="F198" t="s">
+        <v>748</v>
+      </c>
+      <c r="G198" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>298</v>
+      </c>
+      <c r="B199" t="s">
+        <v>517</v>
+      </c>
+      <c r="C199" t="s">
+        <v>701</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199" t="s">
+        <v>720</v>
+      </c>
+      <c r="F199" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>299</v>
+      </c>
+      <c r="B200" t="s">
+        <v>518</v>
+      </c>
+      <c r="C200" t="s">
+        <v>702</v>
+      </c>
+      <c r="D200">
+        <v>314</v>
+      </c>
+      <c r="E200" t="s">
+        <v>715</v>
+      </c>
+      <c r="F200" t="s">
+        <v>748</v>
+      </c>
+      <c r="G200" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>300</v>
+      </c>
+      <c r="B201" t="s">
+        <v>519</v>
+      </c>
+      <c r="C201" t="s">
+        <v>703</v>
+      </c>
+      <c r="D201">
+        <v>49</v>
+      </c>
+      <c r="E201" t="s">
+        <v>715</v>
+      </c>
+      <c r="F201" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>301</v>
+      </c>
+      <c r="B202" t="s">
+        <v>520</v>
+      </c>
+      <c r="C202" t="s">
+        <v>704</v>
+      </c>
+      <c r="D202">
+        <v>7</v>
+      </c>
+      <c r="E202" t="s">
+        <v>715</v>
+      </c>
+      <c r="F202" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
+        <v>302</v>
+      </c>
+      <c r="B203" t="s">
+        <v>521</v>
+      </c>
+      <c r="C203" t="s">
+        <v>533</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203" t="s">
+        <v>742</v>
+      </c>
+      <c r="F203" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
+        <v>303</v>
+      </c>
+      <c r="B204" t="s">
+        <v>522</v>
+      </c>
+      <c r="C204" t="s">
+        <v>533</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204" t="s">
+        <v>742</v>
+      </c>
+      <c r="F204" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" t="s">
+        <v>304</v>
+      </c>
+      <c r="B205" t="s">
+        <v>523</v>
+      </c>
+      <c r="C205" t="s">
+        <v>705</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205" t="s">
+        <v>715</v>
+      </c>
+      <c r="F205" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>305</v>
+      </c>
+      <c r="B206" t="s">
+        <v>524</v>
+      </c>
+      <c r="C206" t="s">
+        <v>706</v>
+      </c>
+      <c r="D206">
+        <v>438</v>
+      </c>
+      <c r="E206" t="s">
+        <v>715</v>
+      </c>
+      <c r="F206" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" t="s">
+        <v>306</v>
+      </c>
+      <c r="B207" t="s">
+        <v>525</v>
+      </c>
+      <c r="C207" t="s">
+        <v>707</v>
+      </c>
+      <c r="D207">
+        <v>126</v>
+      </c>
+      <c r="E207" t="s">
+        <v>715</v>
+      </c>
+      <c r="F207" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>307</v>
+      </c>
+      <c r="B208" t="s">
+        <v>526</v>
+      </c>
+      <c r="C208" t="s">
+        <v>708</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208" t="s">
+        <v>715</v>
+      </c>
+      <c r="F208" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>308</v>
+      </c>
+      <c r="B209" t="s">
+        <v>527</v>
+      </c>
+      <c r="C209" t="s">
+        <v>709</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209" t="s">
+        <v>715</v>
+      </c>
+      <c r="F209" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>309</v>
+      </c>
+      <c r="B210" t="s">
+        <v>528</v>
+      </c>
+      <c r="C210" t="s">
+        <v>710</v>
+      </c>
+      <c r="D210">
+        <v>23</v>
+      </c>
+      <c r="E210" t="s">
+        <v>715</v>
+      </c>
+      <c r="F210" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>310</v>
+      </c>
+      <c r="B211" t="s">
+        <v>529</v>
+      </c>
+      <c r="C211" t="s">
+        <v>711</v>
+      </c>
+      <c r="D211">
+        <v>26</v>
+      </c>
+      <c r="E211" t="s">
+        <v>743</v>
+      </c>
+      <c r="F211" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>311</v>
+      </c>
+      <c r="B212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C212" t="s">
+        <v>674</v>
+      </c>
+      <c r="D212">
         <v>18</v>
       </c>
-      <c r="E144" t="s">
-        <v>589</v>
-      </c>
-      <c r="F144" t="s">
-        <v>611</v>
+      <c r="E212" t="s">
+        <v>715</v>
+      </c>
+      <c r="F212" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>312</v>
+      </c>
+      <c r="B213" t="s">
+        <v>531</v>
+      </c>
+      <c r="C213" t="s">
+        <v>712</v>
+      </c>
+      <c r="D213">
+        <v>2</v>
+      </c>
+      <c r="E213" t="s">
+        <v>715</v>
+      </c>
+      <c r="F213" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>313</v>
+      </c>
+      <c r="B214" t="s">
+        <v>532</v>
+      </c>
+      <c r="C214" t="s">
+        <v>713</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214" t="s">
+        <v>715</v>
+      </c>
+      <c r="F214" t="s">
+        <v>748</v>
       </c>
     </row>
   </sheetData>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -13288,7 +13288,7 @@
         <v>2</v>
       </c>
       <c r="AC34" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD34" s="1">
         <v>0</v>
@@ -13504,7 +13504,7 @@
         <v>65</v>
       </c>
       <c r="CW34" s="1">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -14460,7 +14460,7 @@
         <v>21</v>
       </c>
       <c r="M38" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N38" s="1">
         <v>840</v>
@@ -14724,7 +14724,7 @@
         <v>47</v>
       </c>
       <c r="CW38" s="1">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -18401,7 +18401,7 @@
         <v>17</v>
       </c>
       <c r="E51" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -18689,7 +18689,7 @@
         <v>82</v>
       </c>
       <c r="CW51" s="1">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -21451,7 +21451,7 @@
         <v>214</v>
       </c>
       <c r="E61" s="2">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21739,7 +21739,7 @@
         <v>461</v>
       </c>
       <c r="CW61" s="1">
-        <v>996</v>
+        <v>966</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22205,7 +22205,7 @@
         <v>1</v>
       </c>
       <c r="BA63" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BB63" s="1">
         <v>4</v>
@@ -22349,7 +22349,7 @@
         <v>85</v>
       </c>
       <c r="CW63" s="1">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -25668,7 +25668,7 @@
         <v>194</v>
       </c>
       <c r="CK74" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25704,7 +25704,7 @@
         <v>1852</v>
       </c>
       <c r="CW74" s="1">
-        <v>4397</v>
+        <v>4396</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26965,7 +26965,7 @@
         <v>142</v>
       </c>
       <c r="M79" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N79" s="1">
         <v>69222</v>
@@ -27229,7 +27229,7 @@
         <v>762</v>
       </c>
       <c r="CW79" s="1">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -32246,7 +32246,7 @@
         <v>1</v>
       </c>
       <c r="AS96" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT96" s="1">
         <v>0</v>
@@ -32378,7 +32378,7 @@
         <v>9</v>
       </c>
       <c r="CK96" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CL96" s="1">
         <v>16</v>
@@ -32414,7 +32414,7 @@
         <v>17</v>
       </c>
       <c r="CW96" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97" spans="1:101">
@@ -64187,7 +64187,7 @@
         <v>211</v>
       </c>
       <c r="Q201" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="R201" s="1">
         <v>0</v>
@@ -64439,7 +64439,7 @@
         <v>2006</v>
       </c>
       <c r="CW201" s="1">
-        <v>3230</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -67321,7 +67321,7 @@
         <v>3</v>
       </c>
       <c r="AS211" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT211" s="1">
         <v>9</v>
@@ -67489,7 +67489,7 @@
         <v>504</v>
       </c>
       <c r="CW211" s="1">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69637,7 +69637,7 @@
         <v>580</v>
       </c>
       <c r="D61">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E61" t="s">
         <v>715</v>
@@ -69737,7 +69737,7 @@
         <v>585</v>
       </c>
       <c r="D66">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E66" t="s">
         <v>715</v>
@@ -69897,7 +69897,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="E74" t="s">
         <v>715</v>
@@ -69937,7 +69937,7 @@
         <v>595</v>
       </c>
       <c r="D76">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="E76" t="s">
         <v>715</v>
@@ -70037,7 +70037,7 @@
         <v>599</v>
       </c>
       <c r="D81">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E81" t="s">
         <v>715</v>
@@ -70743,7 +70743,7 @@
         <v>630</v>
       </c>
       <c r="D116">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E116" t="s">
         <v>715</v>
@@ -72355,7 +72355,7 @@
         <v>698</v>
       </c>
       <c r="D196">
-        <v>10255</v>
+        <v>10256</v>
       </c>
       <c r="E196" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -7146,10 +7146,10 @@
         <v>128</v>
       </c>
       <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
         <v>2</v>
-      </c>
-      <c r="P14" s="2">
-        <v>3</v>
       </c>
       <c r="Q14" s="2">
         <v>40</v>
@@ -7158,7 +7158,7 @@
         <v>2</v>
       </c>
       <c r="S14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T14" s="2">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>2022</v>
       </c>
       <c r="AE14" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="2">
         <v>4</v>
@@ -7398,10 +7398,10 @@
         <v>3097</v>
       </c>
       <c r="CU14" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="CV14" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CW14" s="1">
         <v>278</v>
@@ -7487,7 +7487,7 @@
         <v>95</v>
       </c>
       <c r="AA15" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="2">
         <v>3</v>
@@ -7703,7 +7703,7 @@
         <v>3415</v>
       </c>
       <c r="CU15" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CV15" s="1">
         <v>179</v>
@@ -8979,7 +8979,7 @@
         <v>3</v>
       </c>
       <c r="P20" s="2">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="Q20" s="2">
         <v>607</v>
@@ -9231,7 +9231,7 @@
         <v>52</v>
       </c>
       <c r="CV20" s="1">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="CW20" s="1">
         <v>918</v>
@@ -11087,7 +11087,7 @@
         <v>65</v>
       </c>
       <c r="G27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2">
         <v>2</v>
@@ -11363,7 +11363,7 @@
         <v>551</v>
       </c>
       <c r="CU27" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CV27" s="1">
         <v>38</v>
@@ -12295,7 +12295,7 @@
         <v>709</v>
       </c>
       <c r="C31" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
         <v>10</v>
@@ -12313,7 +12313,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="1">
         <v>1384</v>
@@ -12583,13 +12583,13 @@
         <v>5995</v>
       </c>
       <c r="CU31" s="1">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="CV31" s="1">
         <v>279</v>
       </c>
       <c r="CW31" s="1">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12624,7 +12624,7 @@
         <v>822</v>
       </c>
       <c r="K32" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2">
         <v>47</v>
@@ -12888,7 +12888,7 @@
         <v>11092</v>
       </c>
       <c r="CU32" s="1">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="CV32" s="1">
         <v>204</v>
@@ -14553,10 +14553,10 @@
         <v>1</v>
       </c>
       <c r="AR38" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS38" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -14685,7 +14685,7 @@
         <v>0</v>
       </c>
       <c r="CJ38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK38" s="2">
         <v>3</v>
@@ -14700,7 +14700,7 @@
         <v>3</v>
       </c>
       <c r="CO38" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP38" s="1">
         <v>0</v>
@@ -14721,10 +14721,10 @@
         <v>15</v>
       </c>
       <c r="CV38" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="CW38" s="1">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -15040,7 +15040,7 @@
         <v>8771</v>
       </c>
       <c r="C40" s="2">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="D40" s="2">
         <v>85</v>
@@ -15124,7 +15124,7 @@
         <v>18806</v>
       </c>
       <c r="AE40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF40" s="2">
         <v>413</v>
@@ -15328,7 +15328,7 @@
         <v>53430</v>
       </c>
       <c r="CU40" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV40" s="1">
         <v>827</v>
@@ -21442,16 +21442,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6514</v>
+        <v>6531</v>
       </c>
       <c r="C61" s="2">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D61" s="2">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="E61" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21484,7 +21484,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q61" s="2">
         <v>399</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65931</v>
+        <v>65948</v>
       </c>
       <c r="CU61" s="1">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="CV61" s="1">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="CW61" s="1">
-        <v>966</v>
+        <v>983</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22076,16 +22076,16 @@
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K63" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M63" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N63" s="1">
         <v>1118</v>
@@ -22172,16 +22172,16 @@
         <v>0</v>
       </c>
       <c r="AP63" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AQ63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR63" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS63" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -22304,16 +22304,16 @@
         <v>0</v>
       </c>
       <c r="CH63" s="1">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="CI63" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="CJ63" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="CK63" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="CL63" s="1">
         <v>22</v>
@@ -22340,16 +22340,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2863</v>
+        <v>2871</v>
       </c>
       <c r="CU63" s="1">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="CV63" s="1">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="CW63" s="1">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22393,16 +22393,16 @@
         <v>16</v>
       </c>
       <c r="N64" s="1">
-        <v>4249</v>
+        <v>4319</v>
       </c>
       <c r="O64" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P64" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q64" s="2">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="R64" s="1">
         <v>0</v>
@@ -22444,7 +22444,7 @@
         <v>1996</v>
       </c>
       <c r="AE64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF64" s="2">
         <v>65</v>
@@ -22645,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>7941</v>
+        <v>8011</v>
       </c>
       <c r="CU64" s="1">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="CV64" s="1">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="CW64" s="1">
-        <v>417</v>
+        <v>487</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -23278,7 +23278,7 @@
         <v>20</v>
       </c>
       <c r="D67" s="2">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E67" s="2">
         <v>104</v>
@@ -23566,7 +23566,7 @@
         <v>20</v>
       </c>
       <c r="CV67" s="1">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="CW67" s="1">
         <v>104</v>
@@ -26367,7 +26367,7 @@
         <v>9555</v>
       </c>
       <c r="Q77" s="2">
-        <v>19093</v>
+        <v>19095</v>
       </c>
       <c r="R77" s="1">
         <v>0</v>
@@ -26430,16 +26430,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="AM77" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN77" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AO77" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390873</v>
+        <v>390874</v>
       </c>
       <c r="CU77" s="1">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="CV77" s="1">
-        <v>10226</v>
+        <v>10227</v>
       </c>
       <c r="CW77" s="1">
-        <v>16081</v>
+        <v>16084</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27070,7 +27070,7 @@
         <v>1</v>
       </c>
       <c r="AV79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW79" s="2">
         <v>5</v>
@@ -27226,7 +27226,7 @@
         <v>88</v>
       </c>
       <c r="CV79" s="1">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="CW79" s="1">
         <v>1860</v>
@@ -27548,7 +27548,7 @@
         <v>3</v>
       </c>
       <c r="D81" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" s="2">
         <v>21</v>
@@ -27686,16 +27686,16 @@
         <v>0</v>
       </c>
       <c r="AX81" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA81" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB81" s="1">
         <v>0</v>
@@ -27830,16 +27830,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6405</v>
+        <v>6406</v>
       </c>
       <c r="CU81" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CV81" s="1">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="CW81" s="1">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -29328,7 +29328,7 @@
         <v>5</v>
       </c>
       <c r="CK86" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CL86" s="1">
         <v>35</v>
@@ -29364,7 +29364,7 @@
         <v>36</v>
       </c>
       <c r="CW86" s="1">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -31319,7 +31319,7 @@
         <v>5</v>
       </c>
       <c r="AO93" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP93" s="1">
         <v>37</v>
@@ -31463,7 +31463,7 @@
         <v>6</v>
       </c>
       <c r="CK93" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CL93" s="1">
         <v>36</v>
@@ -31499,7 +31499,7 @@
         <v>29</v>
       </c>
       <c r="CW93" s="1">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:101">
@@ -31525,7 +31525,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94" s="2">
         <v>3</v>
@@ -31801,7 +31801,7 @@
         <v>0</v>
       </c>
       <c r="CV94" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW94" s="1">
         <v>6</v>
@@ -32138,7 +32138,7 @@
         <v>3</v>
       </c>
       <c r="I96" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J96" s="1">
         <v>2</v>
@@ -32414,7 +32414,7 @@
         <v>17</v>
       </c>
       <c r="CW96" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97" spans="1:101">
@@ -32739,16 +32739,16 @@
         <v>0</v>
       </c>
       <c r="F98" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G98" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H98" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I98" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J98" s="1">
         <v>0</v>
@@ -33015,16 +33015,16 @@
         <v>0</v>
       </c>
       <c r="CT98" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CU98" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CV98" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW98" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:101">
@@ -33654,16 +33654,16 @@
         <v>0</v>
       </c>
       <c r="F101" s="1">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G101" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H101" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I101" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J101" s="1">
         <v>0</v>
@@ -33930,16 +33930,16 @@
         <v>0</v>
       </c>
       <c r="CT101" s="1">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="CU101" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CV101" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CW101" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:101">
@@ -34016,7 +34016,7 @@
         <v>0</v>
       </c>
       <c r="Y102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="1">
         <v>127</v>
@@ -34244,7 +34244,7 @@
         <v>780</v>
       </c>
       <c r="CW102" s="1">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34261,7 +34261,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F103" s="1">
         <v>12</v>
@@ -34273,7 +34273,7 @@
         <v>3</v>
       </c>
       <c r="I103" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J103" s="1">
         <v>0</v>
@@ -34549,7 +34549,7 @@
         <v>110</v>
       </c>
       <c r="CW103" s="1">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -35167,16 +35167,16 @@
         <v>205</v>
       </c>
       <c r="B106" s="1">
-        <v>9396</v>
+        <v>9449</v>
       </c>
       <c r="C106" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D106" s="2">
-        <v>217</v>
+        <v>270</v>
       </c>
       <c r="E106" s="2">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -35455,16 +35455,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92554</v>
+        <v>92607</v>
       </c>
       <c r="CU106" s="1">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="CV106" s="1">
-        <v>1102</v>
+        <v>1155</v>
       </c>
       <c r="CW106" s="1">
-        <v>2579</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -37024,7 +37024,7 @@
         <v>1119</v>
       </c>
       <c r="K112" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2">
         <v>38</v>
@@ -37288,7 +37288,7 @@
         <v>8280</v>
       </c>
       <c r="CU112" s="1">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="CV112" s="1">
         <v>273</v>
@@ -38292,7 +38292,7 @@
         <v>101</v>
       </c>
       <c r="AA116" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB116" s="2">
         <v>4</v>
@@ -38355,7 +38355,7 @@
         <v>2</v>
       </c>
       <c r="AV116" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW116" s="2">
         <v>9</v>
@@ -38508,10 +38508,10 @@
         <v>21741</v>
       </c>
       <c r="CU116" s="1">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="CV116" s="1">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="CW116" s="1">
         <v>1154</v>
@@ -40367,7 +40367,7 @@
         <v>49</v>
       </c>
       <c r="G123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H123" s="2">
         <v>3</v>
@@ -40472,13 +40472,13 @@
         <v>0</v>
       </c>
       <c r="AP123" s="1">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AQ123" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR123" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS123" s="2">
         <v>6</v>
@@ -40616,13 +40616,13 @@
         <v>0</v>
       </c>
       <c r="CL123" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="CM123" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN123" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CO123" s="2">
         <v>6</v>
@@ -40640,13 +40640,13 @@
         <v>0</v>
       </c>
       <c r="CT123" s="1">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="CU123" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV123" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW123" s="1">
         <v>30</v>
@@ -41898,7 +41898,7 @@
         <v>2</v>
       </c>
       <c r="I128" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J128" s="1">
         <v>0</v>
@@ -41988,7 +41988,7 @@
         <v>49</v>
       </c>
       <c r="AM128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN128" s="2">
         <v>1</v>
@@ -42168,13 +42168,13 @@
         <v>294</v>
       </c>
       <c r="CU128" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV128" s="1">
         <v>6</v>
       </c>
       <c r="CW128" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:101">
@@ -44323,7 +44323,7 @@
         <v>2</v>
       </c>
       <c r="D136" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E136" s="2">
         <v>7</v>
@@ -44611,7 +44611,7 @@
         <v>-1</v>
       </c>
       <c r="CV136" s="1">
-        <v>5078</v>
+        <v>5075</v>
       </c>
       <c r="CW136" s="1">
         <v>6075</v>
@@ -45851,7 +45851,7 @@
         <v>7</v>
       </c>
       <c r="E141" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F141" s="1">
         <v>49</v>
@@ -46139,7 +46139,7 @@
         <v>17</v>
       </c>
       <c r="CW141" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46285,7 +46285,7 @@
         <v>0</v>
       </c>
       <c r="AV142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW142" s="2">
         <v>5</v>
@@ -46441,7 +46441,7 @@
         <v>5</v>
       </c>
       <c r="CV142" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CW142" s="1">
         <v>88</v>
@@ -47215,7 +47215,7 @@
         <v>4</v>
       </c>
       <c r="BA145" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB145" s="1">
         <v>0</v>
@@ -47359,7 +47359,7 @@
         <v>53</v>
       </c>
       <c r="CW145" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -47801,7 +47801,7 @@
         <v>2</v>
       </c>
       <c r="AS147" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT147" s="1">
         <v>0</v>
@@ -47945,7 +47945,7 @@
         <v>2</v>
       </c>
       <c r="CO147" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP147" s="1">
         <v>0</v>
@@ -47969,7 +47969,7 @@
         <v>14</v>
       </c>
       <c r="CW147" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -48405,7 +48405,7 @@
         <v>81</v>
       </c>
       <c r="AQ149" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR149" s="2">
         <v>3</v>
@@ -48537,7 +48537,7 @@
         <v>163</v>
       </c>
       <c r="CI149" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CJ149" s="2">
         <v>6</v>
@@ -48573,7 +48573,7 @@
         <v>904</v>
       </c>
       <c r="CU149" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CV149" s="1">
         <v>26</v>
@@ -51066,7 +51066,7 @@
         <v>3024</v>
       </c>
       <c r="O158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P158" s="2">
         <v>55</v>
@@ -51318,7 +51318,7 @@
         <v>25461</v>
       </c>
       <c r="CU158" s="1">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="CV158" s="1">
         <v>840</v>
@@ -52011,7 +52011,7 @@
         <v>0</v>
       </c>
       <c r="Y161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z161" s="1">
         <v>120</v>
@@ -52092,7 +52092,7 @@
         <v>0</v>
       </c>
       <c r="AZ161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA161" s="2">
         <v>4</v>
@@ -52236,10 +52236,10 @@
         <v>65</v>
       </c>
       <c r="CV161" s="1">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="CW161" s="1">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -53596,7 +53596,7 @@
         <v>3</v>
       </c>
       <c r="AS166" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT166" s="1">
         <v>0</v>
@@ -53740,7 +53740,7 @@
         <v>0</v>
       </c>
       <c r="CO166" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP166" s="1">
         <v>0</v>
@@ -53764,7 +53764,7 @@
         <v>132</v>
       </c>
       <c r="CW166" s="1">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54490,28 +54490,28 @@
         <v>0</v>
       </c>
       <c r="AL169" s="1">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM169" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN169" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO169" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AP169" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT169" s="1">
         <v>0</v>
@@ -54634,16 +54634,16 @@
         <v>0</v>
       </c>
       <c r="CH169" s="1">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="CI169" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CJ169" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="CK169" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="CL169" s="1">
         <v>0</v>
@@ -54670,16 +54670,16 @@
         <v>0</v>
       </c>
       <c r="CT169" s="1">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="CU169" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="CV169" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CW169" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -54720,7 +54720,7 @@
         <v>168</v>
       </c>
       <c r="M170" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N170" s="1">
         <v>2774</v>
@@ -54984,7 +54984,7 @@
         <v>501</v>
       </c>
       <c r="CW170" s="1">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -57737,16 +57737,16 @@
         <v>279</v>
       </c>
       <c r="B180" s="1">
-        <v>8041</v>
+        <v>8072</v>
       </c>
       <c r="C180" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D180" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E180" s="2">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="F180" s="1">
         <v>1</v>
@@ -58025,16 +58025,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51108</v>
+        <v>51139</v>
       </c>
       <c r="CU180" s="1">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="CV180" s="1">
-        <v>1213</v>
+        <v>1244</v>
       </c>
       <c r="CW180" s="1">
-        <v>2722</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -58602,7 +58602,7 @@
         <v>215</v>
       </c>
       <c r="CI182" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="CJ182" s="2">
         <v>27</v>
@@ -58638,7 +58638,7 @@
         <v>330</v>
       </c>
       <c r="CU182" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="CV182" s="1">
         <v>29</v>
@@ -62220,7 +62220,7 @@
         <v>1</v>
       </c>
       <c r="BU194" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV194" s="1">
         <v>8</v>
@@ -62304,7 +62304,7 @@
         <v>568</v>
       </c>
       <c r="CW194" s="1">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -63954,7 +63954,7 @@
         <v>10</v>
       </c>
       <c r="AO200" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AP200" s="1">
         <v>24</v>
@@ -64098,7 +64098,7 @@
         <v>38</v>
       </c>
       <c r="CK200" s="2">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="CL200" s="1">
         <v>9</v>
@@ -64134,7 +64134,7 @@
         <v>261</v>
       </c>
       <c r="CW200" s="1">
-        <v>532</v>
+        <v>513</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -69737,7 +69737,7 @@
         <v>585</v>
       </c>
       <c r="D66">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E66" t="s">
         <v>715</v>
@@ -69897,7 +69897,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2200</v>
+        <v>2216</v>
       </c>
       <c r="E74" t="s">
         <v>715</v>
@@ -70463,7 +70463,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="E102" t="s">
         <v>715</v>
@@ -71126,7 +71126,7 @@
         <v>646</v>
       </c>
       <c r="D135">
-        <v>10260</v>
+        <v>10261</v>
       </c>
       <c r="E135" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4132,7 +4132,7 @@
         <v>117</v>
       </c>
       <c r="AA4" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2">
         <v>3</v>
@@ -4348,7 +4348,7 @@
         <v>42911</v>
       </c>
       <c r="CU4" s="1">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="CV4" s="1">
         <v>443</v>
@@ -4679,16 +4679,16 @@
         <v>4</v>
       </c>
       <c r="F6" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -4955,16 +4955,16 @@
         <v>0</v>
       </c>
       <c r="CT6" s="1">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="CU6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV6" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CW6" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -6608,7 +6608,7 @@
         <v>125</v>
       </c>
       <c r="AM12" s="2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="2">
         <v>72</v>
@@ -6752,7 +6752,7 @@
         <v>145</v>
       </c>
       <c r="CI12" s="2">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="CJ12" s="2">
         <v>93</v>
@@ -6788,7 +6788,7 @@
         <v>410</v>
       </c>
       <c r="CU12" s="1">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="CV12" s="1">
         <v>181</v>
@@ -7747,7 +7747,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2">
         <v>8</v>
@@ -8011,7 +8011,7 @@
         <v>1</v>
       </c>
       <c r="CV16" s="1">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="CW16" s="1">
         <v>99</v>
@@ -11084,16 +11084,16 @@
         <v>6</v>
       </c>
       <c r="F27" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="1">
         <v>0</v>
@@ -11360,16 +11360,16 @@
         <v>0</v>
       </c>
       <c r="CT27" s="1">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="CU27" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV27" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CW27" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:101">
@@ -12442,7 +12442,7 @@
         <v>1</v>
       </c>
       <c r="AZ31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA31" s="2">
         <v>2</v>
@@ -12586,7 +12586,7 @@
         <v>29</v>
       </c>
       <c r="CV31" s="1">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="CW31" s="1">
         <v>447</v>
@@ -12627,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="2">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="M32" s="2">
         <v>95</v>
@@ -12891,7 +12891,7 @@
         <v>21</v>
       </c>
       <c r="CV32" s="1">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="CW32" s="1">
         <v>558</v>
@@ -13411,16 +13411,16 @@
         <v>4</v>
       </c>
       <c r="BR34" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV34" s="1">
         <v>0</v>
@@ -13495,16 +13495,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="CU34" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV34" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="CW34" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -16389,16 +16389,16 @@
         <v>1</v>
       </c>
       <c r="AT44" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AU44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" s="1">
         <v>1</v>
@@ -16545,16 +16545,16 @@
         <v>0</v>
       </c>
       <c r="CT44" s="1">
-        <v>50635</v>
+        <v>50636</v>
       </c>
       <c r="CU44" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CV44" s="1">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="CW44" s="1">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -21066,7 +21066,7 @@
         <v>0</v>
       </c>
       <c r="CB59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC59" s="2">
         <v>1</v>
@@ -21126,7 +21126,7 @@
         <v>7</v>
       </c>
       <c r="CV59" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CW59" s="1">
         <v>53</v>
@@ -21442,16 +21442,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6531</v>
+        <v>6512</v>
       </c>
       <c r="C61" s="2">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="D61" s="2">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="E61" s="2">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65948</v>
+        <v>65929</v>
       </c>
       <c r="CU61" s="1">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="CV61" s="1">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="CW61" s="1">
-        <v>983</v>
+        <v>964</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22441,16 +22441,16 @@
         <v>5</v>
       </c>
       <c r="AD64" s="1">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="AE64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF64" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG64" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22645,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8011</v>
+        <v>8012</v>
       </c>
       <c r="CU64" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CV64" s="1">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="CW64" s="1">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -25662,7 +25662,7 @@
         <v>16168</v>
       </c>
       <c r="CI74" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CJ74" s="2">
         <v>194</v>
@@ -25698,7 +25698,7 @@
         <v>171615</v>
       </c>
       <c r="CU74" s="1">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="CV74" s="1">
         <v>1852</v>
@@ -29017,7 +29017,7 @@
         <v>263</v>
       </c>
       <c r="CI85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ85" s="2">
         <v>24</v>
@@ -29053,7 +29053,7 @@
         <v>397</v>
       </c>
       <c r="CU85" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV85" s="1">
         <v>30</v>
@@ -29988,7 +29988,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
@@ -30276,7 +30276,7 @@
         <v>11</v>
       </c>
       <c r="CV89" s="1">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="CW89" s="1">
         <v>218</v>
@@ -35206,7 +35206,7 @@
         <v>22916</v>
       </c>
       <c r="O106" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P106" s="2">
         <v>182</v>
@@ -35458,7 +35458,7 @@
         <v>92607</v>
       </c>
       <c r="CU106" s="1">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="CV106" s="1">
         <v>1155</v>
@@ -36387,16 +36387,16 @@
         <v>209</v>
       </c>
       <c r="B110" s="1">
-        <v>2491</v>
+        <v>2498</v>
       </c>
       <c r="C110" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D110" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E110" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -36675,16 +36675,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13329</v>
+        <v>13336</v>
       </c>
       <c r="CU110" s="1">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="CV110" s="1">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="CW110" s="1">
-        <v>1004</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -37189,16 +37189,16 @@
         <v>0</v>
       </c>
       <c r="BN112" s="1">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BO112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR112" s="1">
         <v>6</v>
@@ -37285,16 +37285,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8280</v>
+        <v>8282</v>
       </c>
       <c r="CU112" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CV112" s="1">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="CW112" s="1">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37377,7 +37377,7 @@
         <v>114</v>
       </c>
       <c r="AA113" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB113" s="2">
         <v>3</v>
@@ -37593,7 +37593,7 @@
         <v>173813</v>
       </c>
       <c r="CU113" s="1">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="CV113" s="1">
         <v>482</v>
@@ -38552,7 +38552,7 @@
         <v>1</v>
       </c>
       <c r="L117" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M117" s="2">
         <v>22</v>
@@ -38816,7 +38816,7 @@
         <v>171</v>
       </c>
       <c r="CV117" s="1">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="CW117" s="1">
         <v>1217</v>
@@ -39545,16 +39545,16 @@
         <v>0</v>
       </c>
       <c r="AL120" s="1">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="AM120" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AN120" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AO120" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AP120" s="1">
         <v>0</v>
@@ -39689,16 +39689,16 @@
         <v>0</v>
       </c>
       <c r="CH120" s="1">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="CI120" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CJ120" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CK120" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CL120" s="1">
         <v>0</v>
@@ -39725,16 +39725,16 @@
         <v>0</v>
       </c>
       <c r="CT120" s="1">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="CU120" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="CV120" s="1">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="CW120" s="1">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -41880,7 +41880,7 @@
         <v>42</v>
       </c>
       <c r="C128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" s="2">
         <v>1</v>
@@ -41892,7 +41892,7 @@
         <v>40</v>
       </c>
       <c r="G128" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H128" s="2">
         <v>3</v>
@@ -42168,7 +42168,7 @@
         <v>295</v>
       </c>
       <c r="CU128" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CV128" s="1">
         <v>7</v>
@@ -43707,16 +43707,16 @@
         <v>233</v>
       </c>
       <c r="B134" s="1">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C134" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D134" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E134" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -43995,16 +43995,16 @@
         <v>0</v>
       </c>
       <c r="CT134" s="1">
-        <v>134448</v>
+        <v>134456</v>
       </c>
       <c r="CU134" s="1">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="CV134" s="1">
-        <v>2550</v>
+        <v>2558</v>
       </c>
       <c r="CW134" s="1">
-        <v>5804</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44102,7 +44102,7 @@
         <v>1</v>
       </c>
       <c r="AF135" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG135" s="2">
         <v>764</v>
@@ -44306,7 +44306,7 @@
         <v>150</v>
       </c>
       <c r="CV135" s="1">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="CW135" s="1">
         <v>2757</v>
@@ -44389,16 +44389,16 @@
         <v>1</v>
       </c>
       <c r="Z136" s="1">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AA136" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB136" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC136" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD136" s="1">
         <v>156594</v>
@@ -44605,16 +44605,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>158865</v>
+        <v>158871</v>
       </c>
       <c r="CU136" s="1">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CV136" s="1">
-        <v>5075</v>
+        <v>5081</v>
       </c>
       <c r="CW136" s="1">
-        <v>6075</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -44628,7 +44628,7 @@
         <v>5</v>
       </c>
       <c r="D137" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E137" s="2">
         <v>12</v>
@@ -44652,7 +44652,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M137" s="2">
         <v>39</v>
@@ -44688,7 +44688,7 @@
         <v>0</v>
       </c>
       <c r="X137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y137" s="2">
         <v>1</v>
@@ -44742,16 +44742,16 @@
         <v>0</v>
       </c>
       <c r="AP137" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AQ137" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR137" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS137" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT137" s="1">
         <v>0</v>
@@ -44886,16 +44886,16 @@
         <v>1</v>
       </c>
       <c r="CL137" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CM137" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN137" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO137" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP137" s="1">
         <v>0</v>
@@ -44910,16 +44910,16 @@
         <v>0</v>
       </c>
       <c r="CT137" s="1">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="CU137" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV137" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CW137" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -44930,7 +44930,7 @@
         <v>98</v>
       </c>
       <c r="C138" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D138" s="2">
         <v>12</v>
@@ -44942,7 +44942,7 @@
         <v>11</v>
       </c>
       <c r="G138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" s="2">
         <v>1</v>
@@ -45218,7 +45218,7 @@
         <v>4404</v>
       </c>
       <c r="CU138" s="1">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="CV138" s="1">
         <v>132</v>
@@ -45382,7 +45382,7 @@
         <v>0</v>
       </c>
       <c r="AZ139" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA139" s="2">
         <v>1</v>
@@ -45526,7 +45526,7 @@
         <v>0</v>
       </c>
       <c r="CV139" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW139" s="1">
         <v>1</v>
@@ -47212,7 +47212,7 @@
         <v>1</v>
       </c>
       <c r="AZ145" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA145" s="2">
         <v>7</v>
@@ -47356,7 +47356,7 @@
         <v>17</v>
       </c>
       <c r="CV145" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="CW145" s="1">
         <v>135</v>
@@ -50857,7 +50857,7 @@
         <v>41</v>
       </c>
       <c r="AU157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV157" s="2">
         <v>1</v>
@@ -51013,7 +51013,7 @@
         <v>166337</v>
       </c>
       <c r="CU157" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="CV157" s="1">
         <v>5277</v>
@@ -52875,7 +52875,7 @@
         <v>2</v>
       </c>
       <c r="H164" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I164" s="2">
         <v>6</v>
@@ -53151,7 +53151,7 @@
         <v>13</v>
       </c>
       <c r="CV164" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="CW164" s="1">
         <v>204</v>
@@ -53470,7 +53470,7 @@
         <v>416</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" s="2">
         <v>10</v>
@@ -53542,7 +53542,7 @@
         <v>68</v>
       </c>
       <c r="AA166" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB166" s="2">
         <v>3</v>
@@ -53758,7 +53758,7 @@
         <v>5253</v>
       </c>
       <c r="CU166" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="CV166" s="1">
         <v>132</v>
@@ -60285,16 +60285,16 @@
         <v>0</v>
       </c>
       <c r="AL188" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM188" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN188" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO188" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP188" s="1">
         <v>4</v>
@@ -60429,16 +60429,16 @@
         <v>0</v>
       </c>
       <c r="CH188" s="1">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="CI188" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CJ188" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="CK188" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="CL188" s="1">
         <v>0</v>
@@ -60465,16 +60465,16 @@
         <v>0</v>
       </c>
       <c r="CT188" s="1">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="CU188" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="CV188" s="1">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="CW188" s="1">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="189" spans="1:101">
@@ -62049,7 +62049,7 @@
         <v>17</v>
       </c>
       <c r="P194" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="Q194" s="2">
         <v>1228</v>
@@ -62127,16 +62127,16 @@
         <v>2</v>
       </c>
       <c r="AP194" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AQ194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR194" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS194" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT194" s="1">
         <v>2</v>
@@ -62259,16 +62259,16 @@
         <v>0</v>
       </c>
       <c r="CH194" s="1">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="CI194" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ194" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CK194" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CL194" s="1">
         <v>27</v>
@@ -62295,16 +62295,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32846</v>
+        <v>32848</v>
       </c>
       <c r="CU194" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="CV194" s="1">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="CW194" s="1">
-        <v>1368</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62384,16 +62384,16 @@
         <v>1</v>
       </c>
       <c r="Z195" s="1">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AA195" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB195" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC195" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD195" s="1">
         <v>69164</v>
@@ -62600,16 +62600,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>71185</v>
+        <v>71191</v>
       </c>
       <c r="CU195" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CV195" s="1">
-        <v>3365</v>
+        <v>3371</v>
       </c>
       <c r="CW195" s="1">
-        <v>5325</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -70463,7 +70463,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2979</v>
+        <v>2981</v>
       </c>
       <c r="E102" t="s">
         <v>715</v>
@@ -70743,7 +70743,7 @@
         <v>630</v>
       </c>
       <c r="D116">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E116" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -5585,7 +5585,7 @@
         <v>118</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -5606,16 +5606,16 @@
         <v>2</v>
       </c>
       <c r="J9" s="1">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K9" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M9" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N9" s="1">
         <v>1558</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2859</v>
+        <v>2862</v>
       </c>
       <c r="CU9" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CV9" s="1">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="CW9" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -12621,16 +12621,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="K32" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L32" s="2">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="M32" s="2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="N32" s="1">
         <v>6579</v>
@@ -12885,16 +12885,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>11105</v>
+        <v>11125</v>
       </c>
       <c r="CU32" s="1">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="CV32" s="1">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="CW32" s="1">
-        <v>558</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13222,7 +13222,7 @@
         <v>63</v>
       </c>
       <c r="G34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>3</v>
@@ -13498,7 +13498,7 @@
         <v>2577</v>
       </c>
       <c r="CU34" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV34" s="1">
         <v>66</v>
@@ -25407,16 +25407,16 @@
         <v>173</v>
       </c>
       <c r="B74" s="1">
-        <v>12605</v>
+        <v>12604</v>
       </c>
       <c r="C74" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D74" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E74" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171615</v>
+        <v>171614</v>
       </c>
       <c r="CU74" s="1">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CV74" s="1">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="CW74" s="1">
-        <v>4395</v>
+        <v>4394</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26346,16 +26346,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4880</v>
+        <v>4879</v>
       </c>
       <c r="K77" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L77" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M77" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390876</v>
+        <v>390875</v>
       </c>
       <c r="CU77" s="1">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CV77" s="1">
-        <v>10229</v>
+        <v>10228</v>
       </c>
       <c r="CW77" s="1">
-        <v>16086</v>
+        <v>16085</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27007,7 +27007,7 @@
         <v>136</v>
       </c>
       <c r="AA79" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB79" s="2">
         <v>3</v>
@@ -27223,7 +27223,7 @@
         <v>90617</v>
       </c>
       <c r="CU79" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="CV79" s="1">
         <v>761</v>
@@ -29310,7 +29310,7 @@
         <v>12</v>
       </c>
       <c r="CE86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF86" s="2">
         <v>1</v>
@@ -29358,7 +29358,7 @@
         <v>2832</v>
       </c>
       <c r="CU86" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV86" s="1">
         <v>36</v>
@@ -32545,7 +32545,7 @@
         <v>61</v>
       </c>
       <c r="AQ97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR97" s="2">
         <v>3</v>
@@ -32677,7 +32677,7 @@
         <v>40</v>
       </c>
       <c r="CI97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ97" s="2">
         <v>3</v>
@@ -32713,7 +32713,7 @@
         <v>222</v>
       </c>
       <c r="CU97" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CV97" s="1">
         <v>9</v>
@@ -34572,7 +34572,7 @@
         <v>39</v>
       </c>
       <c r="G104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
         <v>2</v>
@@ -34848,7 +34848,7 @@
         <v>40</v>
       </c>
       <c r="CU104" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV104" s="1">
         <v>2</v>
@@ -40475,7 +40475,7 @@
         <v>171</v>
       </c>
       <c r="AQ123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR123" s="2">
         <v>4</v>
@@ -40619,7 +40619,7 @@
         <v>96</v>
       </c>
       <c r="CM123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN123" s="2">
         <v>4</v>
@@ -40643,7 +40643,7 @@
         <v>936</v>
       </c>
       <c r="CU123" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CV123" s="1">
         <v>15</v>
@@ -43746,7 +43746,7 @@
         <v>50045</v>
       </c>
       <c r="O134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P134" s="2">
         <v>718</v>
@@ -43998,7 +43998,7 @@
         <v>134456</v>
       </c>
       <c r="CU134" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CV134" s="1">
         <v>2558</v>
@@ -44745,7 +44745,7 @@
         <v>64</v>
       </c>
       <c r="AQ137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR137" s="2">
         <v>3</v>
@@ -44889,7 +44889,7 @@
         <v>43</v>
       </c>
       <c r="CM137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN137" s="2">
         <v>2</v>
@@ -44913,7 +44913,7 @@
         <v>638</v>
       </c>
       <c r="CU137" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CV137" s="1">
         <v>14</v>
@@ -45074,7 +45074,7 @@
         <v>159</v>
       </c>
       <c r="AY138" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ138" s="2">
         <v>13</v>
@@ -45218,7 +45218,7 @@
         <v>4404</v>
       </c>
       <c r="CU138" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="CV138" s="1">
         <v>132</v>
@@ -46171,16 +46171,16 @@
         <v>4</v>
       </c>
       <c r="J142" s="1">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="K142" s="2">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="L142" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="M142" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="N142" s="1">
         <v>565</v>
@@ -46435,16 +46435,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>1637</v>
+        <v>1653</v>
       </c>
       <c r="CU142" s="1">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="CV142" s="1">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="CW142" s="1">
-        <v>88</v>
+        <v>104</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -47089,7 +47089,7 @@
         <v>494</v>
       </c>
       <c r="K145" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L145" s="2">
         <v>10</v>
@@ -47353,7 +47353,7 @@
         <v>2476</v>
       </c>
       <c r="CU145" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CV145" s="1">
         <v>51</v>
@@ -47687,7 +47687,7 @@
         <v>47</v>
       </c>
       <c r="G147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="2">
         <v>3</v>
@@ -47963,7 +47963,7 @@
         <v>219</v>
       </c>
       <c r="CU147" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV147" s="1">
         <v>14</v>
@@ -50420,7 +50420,7 @@
         <v>2026</v>
       </c>
       <c r="C156" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D156" s="2">
         <v>23</v>
@@ -50708,7 +50708,7 @@
         <v>71484</v>
       </c>
       <c r="CU156" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="CV156" s="1">
         <v>1050</v>
@@ -54397,7 +54397,7 @@
         <v>46</v>
       </c>
       <c r="G169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" s="2">
         <v>3</v>
@@ -54673,7 +54673,7 @@
         <v>364</v>
       </c>
       <c r="CU169" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV169" s="1">
         <v>20</v>
@@ -61520,7 +61520,7 @@
         <v>56</v>
       </c>
       <c r="AQ192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR192" s="2">
         <v>3</v>
@@ -61652,7 +61652,7 @@
         <v>407</v>
       </c>
       <c r="CI192" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CJ192" s="2">
         <v>4</v>
@@ -61688,7 +61688,7 @@
         <v>611</v>
       </c>
       <c r="CU192" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CV192" s="1">
         <v>10</v>
@@ -64217,7 +64217,7 @@
         <v>92</v>
       </c>
       <c r="AA201" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB201" s="2">
         <v>3</v>
@@ -64433,7 +64433,7 @@
         <v>88076</v>
       </c>
       <c r="CU201" s="1">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="CV201" s="1">
         <v>2006</v>
@@ -66585,7 +66585,7 @@
         <v>458</v>
       </c>
       <c r="C209" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D209" s="2">
         <v>19</v>
@@ -66873,7 +66873,7 @@
         <v>726</v>
       </c>
       <c r="CU209" s="1">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="CV209" s="1">
         <v>63</v>
@@ -67010,7 +67010,7 @@
         <v>52</v>
       </c>
       <c r="AQ210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR210" s="2">
         <v>2</v>
@@ -67142,7 +67142,7 @@
         <v>391</v>
       </c>
       <c r="CI210" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CJ210" s="2">
         <v>6</v>
@@ -67178,7 +67178,7 @@
         <v>868</v>
       </c>
       <c r="CU210" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="CV210" s="1">
         <v>18</v>
@@ -69897,7 +69897,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="E74" t="s">
         <v>715</v>
@@ -69997,7 +69997,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="E79" t="s">
         <v>715</v>
@@ -71126,7 +71126,7 @@
         <v>646</v>
       </c>
       <c r="D135">
-        <v>10261</v>
+        <v>10251</v>
       </c>
       <c r="E135" t="s">
         <v>715</v>
